--- a/faltantes_por_estados.xlsx
+++ b/faltantes_por_estados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3282" uniqueCount="2194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3273" uniqueCount="2188">
   <si>
     <t>entidad</t>
   </si>
@@ -1510,9 +1510,6 @@
     <t>GRIMB006172</t>
   </si>
   <si>
-    <t>GRIMB006336</t>
-  </si>
-  <si>
     <t>GRIMB006394</t>
   </si>
   <si>
@@ -3052,9 +3049,6 @@
     <t>TCIMB005510</t>
   </si>
   <si>
-    <t>TSIMB000111</t>
-  </si>
-  <si>
     <t>TSIMB000222</t>
   </si>
   <si>
@@ -3145,9 +3139,6 @@
     <t>TSIMB001453</t>
   </si>
   <si>
-    <t>TSIMB001692</t>
-  </si>
-  <si>
     <t>TSIMB001716</t>
   </si>
   <si>
@@ -4759,9 +4750,6 @@
     <t>R-01 TECALPULCO</t>
   </si>
   <si>
-    <t>R-01 PERICON EL</t>
-  </si>
-  <si>
     <t>R-01 EL CAMARON</t>
   </si>
   <si>
@@ -6289,9 +6277,6 @@
     <t>C.S. LAGARTERA 2DA.</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD BARRA DE MORÓN</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD BUSTAMANTE</t>
   </si>
   <si>
@@ -6380,9 +6365,6 @@
   </si>
   <si>
     <t>CENTRO DE SALUD MANUEL PARREÑO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LA PESCA</t>
   </si>
   <si>
     <t>CENTRO DE SALUD LAS AMÉRICAS</t>
@@ -6953,7 +6935,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1094"/>
+  <dimension ref="A1:C1091"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6975,7 +6957,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6986,7 +6968,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6997,7 +6979,7 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -7008,7 +6990,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7019,7 +7001,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7030,7 +7012,7 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7041,7 +7023,7 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7052,7 +7034,7 @@
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7063,7 +7045,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7074,7 +7056,7 @@
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -7085,7 +7067,7 @@
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -7096,7 +7078,7 @@
         <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -7107,7 +7089,7 @@
         <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -7118,7 +7100,7 @@
         <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7129,7 +7111,7 @@
         <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -7151,7 +7133,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -7162,7 +7144,7 @@
         <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -7173,7 +7155,7 @@
         <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -7184,7 +7166,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -7195,7 +7177,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -7206,7 +7188,7 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -7217,7 +7199,7 @@
         <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -7228,7 +7210,7 @@
         <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -7239,7 +7221,7 @@
         <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -7261,7 +7243,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -7283,7 +7265,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -7294,7 +7276,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -7305,7 +7287,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -7316,7 +7298,7 @@
         <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -7327,7 +7309,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -7338,7 +7320,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -7349,7 +7331,7 @@
         <v>59</v>
       </c>
       <c r="C36" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -7360,7 +7342,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -7371,7 +7353,7 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -7382,7 +7364,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -7393,7 +7375,7 @@
         <v>63</v>
       </c>
       <c r="C40" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -7404,7 +7386,7 @@
         <v>64</v>
       </c>
       <c r="C41" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -7415,7 +7397,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -7426,7 +7408,7 @@
         <v>66</v>
       </c>
       <c r="C43" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -7437,7 +7419,7 @@
         <v>67</v>
       </c>
       <c r="C44" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -7448,7 +7430,7 @@
         <v>68</v>
       </c>
       <c r="C45" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -7459,7 +7441,7 @@
         <v>69</v>
       </c>
       <c r="C46" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -7470,7 +7452,7 @@
         <v>70</v>
       </c>
       <c r="C47" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -7481,7 +7463,7 @@
         <v>71</v>
       </c>
       <c r="C48" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -7492,7 +7474,7 @@
         <v>72</v>
       </c>
       <c r="C49" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -7503,7 +7485,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -7514,7 +7496,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -7525,7 +7507,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -7536,7 +7518,7 @@
         <v>76</v>
       </c>
       <c r="C53" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -7547,7 +7529,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -7558,7 +7540,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -7569,7 +7551,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -7580,7 +7562,7 @@
         <v>80</v>
       </c>
       <c r="C57" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -7591,7 +7573,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -7602,7 +7584,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -7624,7 +7606,7 @@
         <v>84</v>
       </c>
       <c r="C61" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -7635,7 +7617,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -7646,7 +7628,7 @@
         <v>86</v>
       </c>
       <c r="C63" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -7657,7 +7639,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -7668,7 +7650,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -7679,7 +7661,7 @@
         <v>89</v>
       </c>
       <c r="C66" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -7690,7 +7672,7 @@
         <v>90</v>
       </c>
       <c r="C67" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -7701,7 +7683,7 @@
         <v>91</v>
       </c>
       <c r="C68" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -7712,7 +7694,7 @@
         <v>92</v>
       </c>
       <c r="C69" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -7723,7 +7705,7 @@
         <v>93</v>
       </c>
       <c r="C70" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -7734,7 +7716,7 @@
         <v>94</v>
       </c>
       <c r="C71" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -7745,7 +7727,7 @@
         <v>95</v>
       </c>
       <c r="C72" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -7756,7 +7738,7 @@
         <v>96</v>
       </c>
       <c r="C73" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -7767,7 +7749,7 @@
         <v>97</v>
       </c>
       <c r="C74" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -7778,7 +7760,7 @@
         <v>98</v>
       </c>
       <c r="C75" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -7789,7 +7771,7 @@
         <v>99</v>
       </c>
       <c r="C76" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -7800,7 +7782,7 @@
         <v>100</v>
       </c>
       <c r="C77" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -7811,7 +7793,7 @@
         <v>101</v>
       </c>
       <c r="C78" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -7822,7 +7804,7 @@
         <v>102</v>
       </c>
       <c r="C79" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -7833,7 +7815,7 @@
         <v>103</v>
       </c>
       <c r="C80" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -7844,7 +7826,7 @@
         <v>104</v>
       </c>
       <c r="C81" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -7855,7 +7837,7 @@
         <v>105</v>
       </c>
       <c r="C82" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -7866,7 +7848,7 @@
         <v>106</v>
       </c>
       <c r="C83" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -7877,7 +7859,7 @@
         <v>107</v>
       </c>
       <c r="C84" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -7888,7 +7870,7 @@
         <v>108</v>
       </c>
       <c r="C85" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -7899,7 +7881,7 @@
         <v>109</v>
       </c>
       <c r="C86" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -7910,7 +7892,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -7921,7 +7903,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -7932,7 +7914,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -7943,7 +7925,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -7954,7 +7936,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -7965,7 +7947,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -7976,7 +7958,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -7987,7 +7969,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -7998,7 +7980,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -8009,7 +7991,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -8020,7 +8002,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -8031,7 +8013,7 @@
         <v>121</v>
       </c>
       <c r="C98" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -8042,7 +8024,7 @@
         <v>122</v>
       </c>
       <c r="C99" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -8053,7 +8035,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -8064,7 +8046,7 @@
         <v>124</v>
       </c>
       <c r="C101" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -8075,7 +8057,7 @@
         <v>125</v>
       </c>
       <c r="C102" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -8086,7 +8068,7 @@
         <v>126</v>
       </c>
       <c r="C103" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -8097,7 +8079,7 @@
         <v>127</v>
       </c>
       <c r="C104" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -8108,7 +8090,7 @@
         <v>128</v>
       </c>
       <c r="C105" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -8119,7 +8101,7 @@
         <v>129</v>
       </c>
       <c r="C106" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -8130,7 +8112,7 @@
         <v>130</v>
       </c>
       <c r="C107" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -8141,7 +8123,7 @@
         <v>131</v>
       </c>
       <c r="C108" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -8152,7 +8134,7 @@
         <v>132</v>
       </c>
       <c r="C109" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -8163,7 +8145,7 @@
         <v>133</v>
       </c>
       <c r="C110" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -8174,7 +8156,7 @@
         <v>134</v>
       </c>
       <c r="C111" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -8185,7 +8167,7 @@
         <v>135</v>
       </c>
       <c r="C112" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -8196,7 +8178,7 @@
         <v>136</v>
       </c>
       <c r="C113" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -8207,7 +8189,7 @@
         <v>137</v>
       </c>
       <c r="C114" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -8218,7 +8200,7 @@
         <v>138</v>
       </c>
       <c r="C115" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -8229,7 +8211,7 @@
         <v>139</v>
       </c>
       <c r="C116" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -8240,7 +8222,7 @@
         <v>140</v>
       </c>
       <c r="C117" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -8251,7 +8233,7 @@
         <v>141</v>
       </c>
       <c r="C118" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -8262,7 +8244,7 @@
         <v>142</v>
       </c>
       <c r="C119" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -8273,7 +8255,7 @@
         <v>143</v>
       </c>
       <c r="C120" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -8284,7 +8266,7 @@
         <v>144</v>
       </c>
       <c r="C121" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -8295,7 +8277,7 @@
         <v>145</v>
       </c>
       <c r="C122" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -8306,7 +8288,7 @@
         <v>146</v>
       </c>
       <c r="C123" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -8317,7 +8299,7 @@
         <v>147</v>
       </c>
       <c r="C124" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -8328,7 +8310,7 @@
         <v>148</v>
       </c>
       <c r="C125" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -8339,7 +8321,7 @@
         <v>149</v>
       </c>
       <c r="C126" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -8350,7 +8332,7 @@
         <v>150</v>
       </c>
       <c r="C127" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -8361,7 +8343,7 @@
         <v>151</v>
       </c>
       <c r="C128" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -8372,7 +8354,7 @@
         <v>152</v>
       </c>
       <c r="C129" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -8383,7 +8365,7 @@
         <v>153</v>
       </c>
       <c r="C130" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -8394,7 +8376,7 @@
         <v>154</v>
       </c>
       <c r="C131" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -8405,7 +8387,7 @@
         <v>155</v>
       </c>
       <c r="C132" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -8416,7 +8398,7 @@
         <v>156</v>
       </c>
       <c r="C133" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -8427,7 +8409,7 @@
         <v>157</v>
       </c>
       <c r="C134" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -8438,7 +8420,7 @@
         <v>158</v>
       </c>
       <c r="C135" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -8449,7 +8431,7 @@
         <v>159</v>
       </c>
       <c r="C136" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -8460,7 +8442,7 @@
         <v>160</v>
       </c>
       <c r="C137" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -8471,7 +8453,7 @@
         <v>161</v>
       </c>
       <c r="C138" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -8482,7 +8464,7 @@
         <v>162</v>
       </c>
       <c r="C139" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -8493,7 +8475,7 @@
         <v>163</v>
       </c>
       <c r="C140" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -8504,7 +8486,7 @@
         <v>164</v>
       </c>
       <c r="C141" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -8515,7 +8497,7 @@
         <v>165</v>
       </c>
       <c r="C142" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -8526,7 +8508,7 @@
         <v>166</v>
       </c>
       <c r="C143" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -8537,7 +8519,7 @@
         <v>167</v>
       </c>
       <c r="C144" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -8548,7 +8530,7 @@
         <v>168</v>
       </c>
       <c r="C145" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -8559,7 +8541,7 @@
         <v>169</v>
       </c>
       <c r="C146" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -8570,7 +8552,7 @@
         <v>170</v>
       </c>
       <c r="C147" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -8581,7 +8563,7 @@
         <v>171</v>
       </c>
       <c r="C148" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -8592,7 +8574,7 @@
         <v>172</v>
       </c>
       <c r="C149" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -8603,7 +8585,7 @@
         <v>173</v>
       </c>
       <c r="C150" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -8614,7 +8596,7 @@
         <v>174</v>
       </c>
       <c r="C151" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -8625,7 +8607,7 @@
         <v>175</v>
       </c>
       <c r="C152" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -8636,7 +8618,7 @@
         <v>176</v>
       </c>
       <c r="C153" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -8647,7 +8629,7 @@
         <v>177</v>
       </c>
       <c r="C154" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -8658,7 +8640,7 @@
         <v>178</v>
       </c>
       <c r="C155" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -8669,7 +8651,7 @@
         <v>179</v>
       </c>
       <c r="C156" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -8680,7 +8662,7 @@
         <v>180</v>
       </c>
       <c r="C157" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -8691,7 +8673,7 @@
         <v>181</v>
       </c>
       <c r="C158" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -8702,7 +8684,7 @@
         <v>182</v>
       </c>
       <c r="C159" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -8713,7 +8695,7 @@
         <v>183</v>
       </c>
       <c r="C160" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -8724,7 +8706,7 @@
         <v>184</v>
       </c>
       <c r="C161" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -8735,7 +8717,7 @@
         <v>185</v>
       </c>
       <c r="C162" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -8746,7 +8728,7 @@
         <v>186</v>
       </c>
       <c r="C163" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -8757,7 +8739,7 @@
         <v>187</v>
       </c>
       <c r="C164" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -8768,7 +8750,7 @@
         <v>188</v>
       </c>
       <c r="C165" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -8779,7 +8761,7 @@
         <v>189</v>
       </c>
       <c r="C166" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -8790,7 +8772,7 @@
         <v>190</v>
       </c>
       <c r="C167" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -8801,7 +8783,7 @@
         <v>191</v>
       </c>
       <c r="C168" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -8812,7 +8794,7 @@
         <v>192</v>
       </c>
       <c r="C169" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -8823,7 +8805,7 @@
         <v>193</v>
       </c>
       <c r="C170" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -8834,7 +8816,7 @@
         <v>194</v>
       </c>
       <c r="C171" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -8845,7 +8827,7 @@
         <v>195</v>
       </c>
       <c r="C172" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -8856,7 +8838,7 @@
         <v>196</v>
       </c>
       <c r="C173" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -8867,7 +8849,7 @@
         <v>197</v>
       </c>
       <c r="C174" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -8878,7 +8860,7 @@
         <v>198</v>
       </c>
       <c r="C175" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -8889,7 +8871,7 @@
         <v>199</v>
       </c>
       <c r="C176" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -8900,7 +8882,7 @@
         <v>200</v>
       </c>
       <c r="C177" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -8911,7 +8893,7 @@
         <v>201</v>
       </c>
       <c r="C178" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -8922,7 +8904,7 @@
         <v>202</v>
       </c>
       <c r="C179" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -8933,7 +8915,7 @@
         <v>203</v>
       </c>
       <c r="C180" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -8944,7 +8926,7 @@
         <v>204</v>
       </c>
       <c r="C181" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -8955,7 +8937,7 @@
         <v>205</v>
       </c>
       <c r="C182" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -8966,7 +8948,7 @@
         <v>206</v>
       </c>
       <c r="C183" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -8977,7 +8959,7 @@
         <v>207</v>
       </c>
       <c r="C184" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -8988,7 +8970,7 @@
         <v>208</v>
       </c>
       <c r="C185" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -8999,7 +8981,7 @@
         <v>209</v>
       </c>
       <c r="C186" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -9010,7 +8992,7 @@
         <v>210</v>
       </c>
       <c r="C187" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -9021,7 +9003,7 @@
         <v>211</v>
       </c>
       <c r="C188" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -9032,7 +9014,7 @@
         <v>212</v>
       </c>
       <c r="C189" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -9043,7 +9025,7 @@
         <v>213</v>
       </c>
       <c r="C190" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -9054,7 +9036,7 @@
         <v>214</v>
       </c>
       <c r="C191" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -9065,7 +9047,7 @@
         <v>215</v>
       </c>
       <c r="C192" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -9076,7 +9058,7 @@
         <v>216</v>
       </c>
       <c r="C193" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -9087,7 +9069,7 @@
         <v>217</v>
       </c>
       <c r="C194" t="s">
-        <v>1305</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -9098,7 +9080,7 @@
         <v>218</v>
       </c>
       <c r="C195" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -9109,7 +9091,7 @@
         <v>219</v>
       </c>
       <c r="C196" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -9120,7 +9102,7 @@
         <v>220</v>
       </c>
       <c r="C197" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -9131,7 +9113,7 @@
         <v>221</v>
       </c>
       <c r="C198" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -9142,7 +9124,7 @@
         <v>222</v>
       </c>
       <c r="C199" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -9153,7 +9135,7 @@
         <v>223</v>
       </c>
       <c r="C200" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -9164,7 +9146,7 @@
         <v>224</v>
       </c>
       <c r="C201" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -9175,7 +9157,7 @@
         <v>225</v>
       </c>
       <c r="C202" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -9186,7 +9168,7 @@
         <v>226</v>
       </c>
       <c r="C203" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -9197,7 +9179,7 @@
         <v>227</v>
       </c>
       <c r="C204" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -9208,7 +9190,7 @@
         <v>228</v>
       </c>
       <c r="C205" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -9219,7 +9201,7 @@
         <v>229</v>
       </c>
       <c r="C206" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -9230,7 +9212,7 @@
         <v>230</v>
       </c>
       <c r="C207" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -9241,7 +9223,7 @@
         <v>231</v>
       </c>
       <c r="C208" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -9252,7 +9234,7 @@
         <v>232</v>
       </c>
       <c r="C209" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -9263,7 +9245,7 @@
         <v>233</v>
       </c>
       <c r="C210" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -9274,7 +9256,7 @@
         <v>234</v>
       </c>
       <c r="C211" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -9285,7 +9267,7 @@
         <v>235</v>
       </c>
       <c r="C212" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -9296,7 +9278,7 @@
         <v>236</v>
       </c>
       <c r="C213" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -9307,7 +9289,7 @@
         <v>237</v>
       </c>
       <c r="C214" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -9318,7 +9300,7 @@
         <v>238</v>
       </c>
       <c r="C215" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -9329,7 +9311,7 @@
         <v>239</v>
       </c>
       <c r="C216" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -9340,7 +9322,7 @@
         <v>240</v>
       </c>
       <c r="C217" t="s">
-        <v>1328</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -9351,7 +9333,7 @@
         <v>241</v>
       </c>
       <c r="C218" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -9362,7 +9344,7 @@
         <v>242</v>
       </c>
       <c r="C219" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -9373,7 +9355,7 @@
         <v>243</v>
       </c>
       <c r="C220" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -9384,7 +9366,7 @@
         <v>244</v>
       </c>
       <c r="C221" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -9395,7 +9377,7 @@
         <v>245</v>
       </c>
       <c r="C222" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -9406,7 +9388,7 @@
         <v>246</v>
       </c>
       <c r="C223" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -9417,7 +9399,7 @@
         <v>247</v>
       </c>
       <c r="C224" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -9428,7 +9410,7 @@
         <v>248</v>
       </c>
       <c r="C225" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -9439,7 +9421,7 @@
         <v>249</v>
       </c>
       <c r="C226" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -9450,7 +9432,7 @@
         <v>250</v>
       </c>
       <c r="C227" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -9461,7 +9443,7 @@
         <v>251</v>
       </c>
       <c r="C228" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -9472,7 +9454,7 @@
         <v>252</v>
       </c>
       <c r="C229" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -9483,7 +9465,7 @@
         <v>253</v>
       </c>
       <c r="C230" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -9494,7 +9476,7 @@
         <v>254</v>
       </c>
       <c r="C231" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -9505,7 +9487,7 @@
         <v>255</v>
       </c>
       <c r="C232" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -9516,7 +9498,7 @@
         <v>256</v>
       </c>
       <c r="C233" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -9527,7 +9509,7 @@
         <v>257</v>
       </c>
       <c r="C234" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -9538,7 +9520,7 @@
         <v>258</v>
       </c>
       <c r="C235" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -9549,7 +9531,7 @@
         <v>259</v>
       </c>
       <c r="C236" t="s">
-        <v>1347</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -9560,7 +9542,7 @@
         <v>260</v>
       </c>
       <c r="C237" t="s">
-        <v>1348</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -9571,7 +9553,7 @@
         <v>261</v>
       </c>
       <c r="C238" t="s">
-        <v>1349</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -9582,7 +9564,7 @@
         <v>262</v>
       </c>
       <c r="C239" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -9593,7 +9575,7 @@
         <v>263</v>
       </c>
       <c r="C240" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -9604,7 +9586,7 @@
         <v>264</v>
       </c>
       <c r="C241" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -9615,7 +9597,7 @@
         <v>265</v>
       </c>
       <c r="C242" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -9626,7 +9608,7 @@
         <v>266</v>
       </c>
       <c r="C243" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -9637,7 +9619,7 @@
         <v>267</v>
       </c>
       <c r="C244" t="s">
-        <v>1355</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -9648,7 +9630,7 @@
         <v>268</v>
       </c>
       <c r="C245" t="s">
-        <v>1356</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -9659,7 +9641,7 @@
         <v>269</v>
       </c>
       <c r="C246" t="s">
-        <v>1357</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -9670,7 +9652,7 @@
         <v>270</v>
       </c>
       <c r="C247" t="s">
-        <v>1358</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -9681,7 +9663,7 @@
         <v>271</v>
       </c>
       <c r="C248" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -9692,7 +9674,7 @@
         <v>272</v>
       </c>
       <c r="C249" t="s">
-        <v>1360</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -9703,7 +9685,7 @@
         <v>273</v>
       </c>
       <c r="C250" t="s">
-        <v>1361</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -9714,7 +9696,7 @@
         <v>274</v>
       </c>
       <c r="C251" t="s">
-        <v>1362</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -9725,7 +9707,7 @@
         <v>275</v>
       </c>
       <c r="C252" t="s">
-        <v>1363</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -9736,7 +9718,7 @@
         <v>276</v>
       </c>
       <c r="C253" t="s">
-        <v>1364</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -9747,7 +9729,7 @@
         <v>277</v>
       </c>
       <c r="C254" t="s">
-        <v>1365</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -9758,7 +9740,7 @@
         <v>278</v>
       </c>
       <c r="C255" t="s">
-        <v>1366</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -9769,7 +9751,7 @@
         <v>279</v>
       </c>
       <c r="C256" t="s">
-        <v>1367</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -9780,7 +9762,7 @@
         <v>280</v>
       </c>
       <c r="C257" t="s">
-        <v>1368</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -9791,7 +9773,7 @@
         <v>281</v>
       </c>
       <c r="C258" t="s">
-        <v>1369</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="259" spans="1:3">
@@ -9802,7 +9784,7 @@
         <v>282</v>
       </c>
       <c r="C259" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -9813,7 +9795,7 @@
         <v>283</v>
       </c>
       <c r="C260" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="261" spans="1:3">
@@ -9824,7 +9806,7 @@
         <v>284</v>
       </c>
       <c r="C261" t="s">
-        <v>1372</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="262" spans="1:3">
@@ -9835,7 +9817,7 @@
         <v>285</v>
       </c>
       <c r="C262" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -9846,7 +9828,7 @@
         <v>286</v>
       </c>
       <c r="C263" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="264" spans="1:3">
@@ -9857,7 +9839,7 @@
         <v>287</v>
       </c>
       <c r="C264" t="s">
-        <v>1375</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -9868,7 +9850,7 @@
         <v>288</v>
       </c>
       <c r="C265" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="266" spans="1:3">
@@ -9879,7 +9861,7 @@
         <v>289</v>
       </c>
       <c r="C266" t="s">
-        <v>1377</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="267" spans="1:3">
@@ -9890,7 +9872,7 @@
         <v>290</v>
       </c>
       <c r="C267" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="268" spans="1:3">
@@ -9901,7 +9883,7 @@
         <v>291</v>
       </c>
       <c r="C268" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="269" spans="1:3">
@@ -9912,7 +9894,7 @@
         <v>292</v>
       </c>
       <c r="C269" t="s">
-        <v>1380</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="270" spans="1:3">
@@ -9923,7 +9905,7 @@
         <v>293</v>
       </c>
       <c r="C270" t="s">
-        <v>1381</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="271" spans="1:3">
@@ -9934,7 +9916,7 @@
         <v>294</v>
       </c>
       <c r="C271" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="272" spans="1:3">
@@ -9945,7 +9927,7 @@
         <v>295</v>
       </c>
       <c r="C272" t="s">
-        <v>1383</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="273" spans="1:3">
@@ -9956,7 +9938,7 @@
         <v>296</v>
       </c>
       <c r="C273" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="274" spans="1:3">
@@ -9967,7 +9949,7 @@
         <v>297</v>
       </c>
       <c r="C274" t="s">
-        <v>1385</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="275" spans="1:3">
@@ -9978,7 +9960,7 @@
         <v>298</v>
       </c>
       <c r="C275" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="276" spans="1:3">
@@ -9989,7 +9971,7 @@
         <v>299</v>
       </c>
       <c r="C276" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="277" spans="1:3">
@@ -10000,7 +9982,7 @@
         <v>300</v>
       </c>
       <c r="C277" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="278" spans="1:3">
@@ -10011,7 +9993,7 @@
         <v>301</v>
       </c>
       <c r="C278" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="279" spans="1:3">
@@ -10022,7 +10004,7 @@
         <v>302</v>
       </c>
       <c r="C279" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="280" spans="1:3">
@@ -10033,7 +10015,7 @@
         <v>303</v>
       </c>
       <c r="C280" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -10044,7 +10026,7 @@
         <v>304</v>
       </c>
       <c r="C281" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="282" spans="1:3">
@@ -10055,7 +10037,7 @@
         <v>305</v>
       </c>
       <c r="C282" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="283" spans="1:3">
@@ -10066,7 +10048,7 @@
         <v>306</v>
       </c>
       <c r="C283" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="284" spans="1:3">
@@ -10077,7 +10059,7 @@
         <v>307</v>
       </c>
       <c r="C284" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="285" spans="1:3">
@@ -10088,7 +10070,7 @@
         <v>308</v>
       </c>
       <c r="C285" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="286" spans="1:3">
@@ -10099,7 +10081,7 @@
         <v>309</v>
       </c>
       <c r="C286" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="287" spans="1:3">
@@ -10110,7 +10092,7 @@
         <v>310</v>
       </c>
       <c r="C287" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="288" spans="1:3">
@@ -10121,7 +10103,7 @@
         <v>311</v>
       </c>
       <c r="C288" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="289" spans="1:3">
@@ -10132,7 +10114,7 @@
         <v>312</v>
       </c>
       <c r="C289" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="290" spans="1:3">
@@ -10143,7 +10125,7 @@
         <v>313</v>
       </c>
       <c r="C290" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="291" spans="1:3">
@@ -10154,7 +10136,7 @@
         <v>314</v>
       </c>
       <c r="C291" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="292" spans="1:3">
@@ -10165,7 +10147,7 @@
         <v>315</v>
       </c>
       <c r="C292" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="293" spans="1:3">
@@ -10176,7 +10158,7 @@
         <v>316</v>
       </c>
       <c r="C293" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="294" spans="1:3">
@@ -10187,7 +10169,7 @@
         <v>317</v>
       </c>
       <c r="C294" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="295" spans="1:3">
@@ -10198,7 +10180,7 @@
         <v>318</v>
       </c>
       <c r="C295" t="s">
-        <v>1405</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="296" spans="1:3">
@@ -10209,7 +10191,7 @@
         <v>319</v>
       </c>
       <c r="C296" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="297" spans="1:3">
@@ -10220,7 +10202,7 @@
         <v>320</v>
       </c>
       <c r="C297" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="298" spans="1:3">
@@ -10231,7 +10213,7 @@
         <v>321</v>
       </c>
       <c r="C298" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="299" spans="1:3">
@@ -10242,7 +10224,7 @@
         <v>322</v>
       </c>
       <c r="C299" t="s">
-        <v>1409</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="300" spans="1:3">
@@ -10253,7 +10235,7 @@
         <v>323</v>
       </c>
       <c r="C300" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="301" spans="1:3">
@@ -10264,7 +10246,7 @@
         <v>324</v>
       </c>
       <c r="C301" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -10275,7 +10257,7 @@
         <v>325</v>
       </c>
       <c r="C302" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="303" spans="1:3">
@@ -10286,7 +10268,7 @@
         <v>326</v>
       </c>
       <c r="C303" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="304" spans="1:3">
@@ -10297,7 +10279,7 @@
         <v>327</v>
       </c>
       <c r="C304" t="s">
-        <v>1414</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -10308,7 +10290,7 @@
         <v>328</v>
       </c>
       <c r="C305" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="306" spans="1:3">
@@ -10319,7 +10301,7 @@
         <v>329</v>
       </c>
       <c r="C306" t="s">
-        <v>1416</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="307" spans="1:3">
@@ -10330,7 +10312,7 @@
         <v>330</v>
       </c>
       <c r="C307" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="308" spans="1:3">
@@ -10341,7 +10323,7 @@
         <v>331</v>
       </c>
       <c r="C308" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="309" spans="1:3">
@@ -10352,7 +10334,7 @@
         <v>332</v>
       </c>
       <c r="C309" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="310" spans="1:3">
@@ -10363,7 +10345,7 @@
         <v>333</v>
       </c>
       <c r="C310" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="311" spans="1:3">
@@ -10374,7 +10356,7 @@
         <v>334</v>
       </c>
       <c r="C311" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="312" spans="1:3">
@@ -10385,7 +10367,7 @@
         <v>335</v>
       </c>
       <c r="C312" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="313" spans="1:3">
@@ -10396,7 +10378,7 @@
         <v>336</v>
       </c>
       <c r="C313" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="314" spans="1:3">
@@ -10407,7 +10389,7 @@
         <v>337</v>
       </c>
       <c r="C314" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="315" spans="1:3">
@@ -10418,7 +10400,7 @@
         <v>338</v>
       </c>
       <c r="C315" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="316" spans="1:3">
@@ -10429,7 +10411,7 @@
         <v>339</v>
       </c>
       <c r="C316" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="317" spans="1:3">
@@ -10440,7 +10422,7 @@
         <v>340</v>
       </c>
       <c r="C317" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="318" spans="1:3">
@@ -10451,7 +10433,7 @@
         <v>341</v>
       </c>
       <c r="C318" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="319" spans="1:3">
@@ -10462,7 +10444,7 @@
         <v>342</v>
       </c>
       <c r="C319" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="320" spans="1:3">
@@ -10473,7 +10455,7 @@
         <v>343</v>
       </c>
       <c r="C320" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="321" spans="1:3">
@@ -10484,7 +10466,7 @@
         <v>344</v>
       </c>
       <c r="C321" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -10495,7 +10477,7 @@
         <v>345</v>
       </c>
       <c r="C322" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="323" spans="1:3">
@@ -10506,7 +10488,7 @@
         <v>346</v>
       </c>
       <c r="C323" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="324" spans="1:3">
@@ -10517,7 +10499,7 @@
         <v>347</v>
       </c>
       <c r="C324" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -10528,7 +10510,7 @@
         <v>348</v>
       </c>
       <c r="C325" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="326" spans="1:3">
@@ -10539,7 +10521,7 @@
         <v>349</v>
       </c>
       <c r="C326" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="327" spans="1:3">
@@ -10550,7 +10532,7 @@
         <v>350</v>
       </c>
       <c r="C327" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="328" spans="1:3">
@@ -10561,7 +10543,7 @@
         <v>351</v>
       </c>
       <c r="C328" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="329" spans="1:3">
@@ -10572,7 +10554,7 @@
         <v>352</v>
       </c>
       <c r="C329" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="330" spans="1:3">
@@ -10583,7 +10565,7 @@
         <v>353</v>
       </c>
       <c r="C330" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -10594,7 +10576,7 @@
         <v>354</v>
       </c>
       <c r="C331" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="332" spans="1:3">
@@ -10605,7 +10587,7 @@
         <v>355</v>
       </c>
       <c r="C332" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="333" spans="1:3">
@@ -10616,7 +10598,7 @@
         <v>356</v>
       </c>
       <c r="C333" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="334" spans="1:3">
@@ -10627,7 +10609,7 @@
         <v>357</v>
       </c>
       <c r="C334" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="335" spans="1:3">
@@ -10638,7 +10620,7 @@
         <v>358</v>
       </c>
       <c r="C335" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="336" spans="1:3">
@@ -10649,7 +10631,7 @@
         <v>359</v>
       </c>
       <c r="C336" t="s">
-        <v>1445</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="337" spans="1:3">
@@ -10660,7 +10642,7 @@
         <v>360</v>
       </c>
       <c r="C337" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="338" spans="1:3">
@@ -10671,7 +10653,7 @@
         <v>361</v>
       </c>
       <c r="C338" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="339" spans="1:3">
@@ -10682,7 +10664,7 @@
         <v>362</v>
       </c>
       <c r="C339" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="340" spans="1:3">
@@ -10693,7 +10675,7 @@
         <v>363</v>
       </c>
       <c r="C340" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="341" spans="1:3">
@@ -10704,7 +10686,7 @@
         <v>364</v>
       </c>
       <c r="C341" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -10715,7 +10697,7 @@
         <v>365</v>
       </c>
       <c r="C342" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="343" spans="1:3">
@@ -10726,7 +10708,7 @@
         <v>366</v>
       </c>
       <c r="C343" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="344" spans="1:3">
@@ -10737,7 +10719,7 @@
         <v>367</v>
       </c>
       <c r="C344" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="345" spans="1:3">
@@ -10748,7 +10730,7 @@
         <v>368</v>
       </c>
       <c r="C345" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="346" spans="1:3">
@@ -10759,7 +10741,7 @@
         <v>369</v>
       </c>
       <c r="C346" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="347" spans="1:3">
@@ -10770,7 +10752,7 @@
         <v>370</v>
       </c>
       <c r="C347" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="348" spans="1:3">
@@ -10781,7 +10763,7 @@
         <v>371</v>
       </c>
       <c r="C348" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="349" spans="1:3">
@@ -10792,7 +10774,7 @@
         <v>372</v>
       </c>
       <c r="C349" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -10803,7 +10785,7 @@
         <v>373</v>
       </c>
       <c r="C350" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="351" spans="1:3">
@@ -10814,7 +10796,7 @@
         <v>374</v>
       </c>
       <c r="C351" t="s">
-        <v>1460</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -10825,7 +10807,7 @@
         <v>375</v>
       </c>
       <c r="C352" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="353" spans="1:3">
@@ -10836,7 +10818,7 @@
         <v>376</v>
       </c>
       <c r="C353" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="354" spans="1:3">
@@ -10847,7 +10829,7 @@
         <v>377</v>
       </c>
       <c r="C354" t="s">
-        <v>1462</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -10858,7 +10840,7 @@
         <v>378</v>
       </c>
       <c r="C355" t="s">
-        <v>1463</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="356" spans="1:3">
@@ -10869,7 +10851,7 @@
         <v>379</v>
       </c>
       <c r="C356" t="s">
-        <v>1464</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="357" spans="1:3">
@@ -10880,7 +10862,7 @@
         <v>380</v>
       </c>
       <c r="C357" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="358" spans="1:3">
@@ -10891,7 +10873,7 @@
         <v>381</v>
       </c>
       <c r="C358" t="s">
-        <v>1466</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="359" spans="1:3">
@@ -10902,7 +10884,7 @@
         <v>382</v>
       </c>
       <c r="C359" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -10913,7 +10895,7 @@
         <v>383</v>
       </c>
       <c r="C360" t="s">
-        <v>1468</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="361" spans="1:3">
@@ -10924,7 +10906,7 @@
         <v>384</v>
       </c>
       <c r="C361" t="s">
-        <v>1469</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="362" spans="1:3">
@@ -10935,7 +10917,7 @@
         <v>385</v>
       </c>
       <c r="C362" t="s">
-        <v>1470</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="363" spans="1:3">
@@ -10946,7 +10928,7 @@
         <v>386</v>
       </c>
       <c r="C363" t="s">
-        <v>1471</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="364" spans="1:3">
@@ -10957,7 +10939,7 @@
         <v>387</v>
       </c>
       <c r="C364" t="s">
-        <v>1472</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="365" spans="1:3">
@@ -10968,7 +10950,7 @@
         <v>388</v>
       </c>
       <c r="C365" t="s">
-        <v>1473</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="366" spans="1:3">
@@ -10979,7 +10961,7 @@
         <v>389</v>
       </c>
       <c r="C366" t="s">
-        <v>1474</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="367" spans="1:3">
@@ -10990,7 +10972,7 @@
         <v>390</v>
       </c>
       <c r="C367" t="s">
-        <v>1475</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="368" spans="1:3">
@@ -11001,7 +10983,7 @@
         <v>391</v>
       </c>
       <c r="C368" t="s">
-        <v>1476</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="369" spans="1:3">
@@ -11012,7 +10994,7 @@
         <v>392</v>
       </c>
       <c r="C369" t="s">
-        <v>1477</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="370" spans="1:3">
@@ -11023,7 +11005,7 @@
         <v>393</v>
       </c>
       <c r="C370" t="s">
-        <v>1478</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="371" spans="1:3">
@@ -11034,7 +11016,7 @@
         <v>394</v>
       </c>
       <c r="C371" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -11045,7 +11027,7 @@
         <v>395</v>
       </c>
       <c r="C372" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="373" spans="1:3">
@@ -11056,7 +11038,7 @@
         <v>396</v>
       </c>
       <c r="C373" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="374" spans="1:3">
@@ -11067,7 +11049,7 @@
         <v>397</v>
       </c>
       <c r="C374" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="375" spans="1:3">
@@ -11078,7 +11060,7 @@
         <v>398</v>
       </c>
       <c r="C375" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="376" spans="1:3">
@@ -11089,7 +11071,7 @@
         <v>399</v>
       </c>
       <c r="C376" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="377" spans="1:3">
@@ -11100,7 +11082,7 @@
         <v>400</v>
       </c>
       <c r="C377" t="s">
-        <v>1485</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="378" spans="1:3">
@@ -11111,7 +11093,7 @@
         <v>401</v>
       </c>
       <c r="C378" t="s">
-        <v>1486</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="379" spans="1:3">
@@ -11122,7 +11104,7 @@
         <v>402</v>
       </c>
       <c r="C379" t="s">
-        <v>1487</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="380" spans="1:3">
@@ -11133,7 +11115,7 @@
         <v>403</v>
       </c>
       <c r="C380" t="s">
-        <v>1488</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="381" spans="1:3">
@@ -11144,7 +11126,7 @@
         <v>404</v>
       </c>
       <c r="C381" t="s">
-        <v>1489</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="382" spans="1:3">
@@ -11155,7 +11137,7 @@
         <v>405</v>
       </c>
       <c r="C382" t="s">
-        <v>1490</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="383" spans="1:3">
@@ -11166,7 +11148,7 @@
         <v>406</v>
       </c>
       <c r="C383" t="s">
-        <v>1491</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="384" spans="1:3">
@@ -11177,7 +11159,7 @@
         <v>407</v>
       </c>
       <c r="C384" t="s">
-        <v>1492</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="385" spans="1:3">
@@ -11188,7 +11170,7 @@
         <v>408</v>
       </c>
       <c r="C385" t="s">
-        <v>1493</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="386" spans="1:3">
@@ -11199,7 +11181,7 @@
         <v>409</v>
       </c>
       <c r="C386" t="s">
-        <v>1494</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="387" spans="1:3">
@@ -11210,7 +11192,7 @@
         <v>410</v>
       </c>
       <c r="C387" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="388" spans="1:3">
@@ -11221,7 +11203,7 @@
         <v>411</v>
       </c>
       <c r="C388" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="389" spans="1:3">
@@ -11232,7 +11214,7 @@
         <v>412</v>
       </c>
       <c r="C389" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="390" spans="1:3">
@@ -11243,7 +11225,7 @@
         <v>413</v>
       </c>
       <c r="C390" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="391" spans="1:3">
@@ -11254,7 +11236,7 @@
         <v>414</v>
       </c>
       <c r="C391" t="s">
-        <v>1499</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="392" spans="1:3">
@@ -11265,7 +11247,7 @@
         <v>415</v>
       </c>
       <c r="C392" t="s">
-        <v>1500</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="393" spans="1:3">
@@ -11276,7 +11258,7 @@
         <v>416</v>
       </c>
       <c r="C393" t="s">
-        <v>1501</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="394" spans="1:3">
@@ -11287,7 +11269,7 @@
         <v>417</v>
       </c>
       <c r="C394" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="395" spans="1:3">
@@ -11298,7 +11280,7 @@
         <v>418</v>
       </c>
       <c r="C395" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="396" spans="1:3">
@@ -11309,7 +11291,7 @@
         <v>419</v>
       </c>
       <c r="C396" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="397" spans="1:3">
@@ -11320,7 +11302,7 @@
         <v>420</v>
       </c>
       <c r="C397" t="s">
-        <v>1505</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="398" spans="1:3">
@@ -11331,7 +11313,7 @@
         <v>421</v>
       </c>
       <c r="C398" t="s">
-        <v>1506</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="399" spans="1:3">
@@ -11342,7 +11324,7 @@
         <v>422</v>
       </c>
       <c r="C399" t="s">
-        <v>1507</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="400" spans="1:3">
@@ -11353,7 +11335,7 @@
         <v>423</v>
       </c>
       <c r="C400" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="401" spans="1:3">
@@ -11364,7 +11346,7 @@
         <v>424</v>
       </c>
       <c r="C401" t="s">
-        <v>1509</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="402" spans="1:3">
@@ -11375,7 +11357,7 @@
         <v>425</v>
       </c>
       <c r="C402" t="s">
-        <v>1510</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="403" spans="1:3">
@@ -11386,7 +11368,7 @@
         <v>426</v>
       </c>
       <c r="C403" t="s">
-        <v>1511</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="404" spans="1:3">
@@ -11397,7 +11379,7 @@
         <v>427</v>
       </c>
       <c r="C404" t="s">
-        <v>1512</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="405" spans="1:3">
@@ -11408,7 +11390,7 @@
         <v>428</v>
       </c>
       <c r="C405" t="s">
-        <v>1513</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="406" spans="1:3">
@@ -11419,7 +11401,7 @@
         <v>429</v>
       </c>
       <c r="C406" t="s">
-        <v>1514</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="407" spans="1:3">
@@ -11430,7 +11412,7 @@
         <v>430</v>
       </c>
       <c r="C407" t="s">
-        <v>1515</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="408" spans="1:3">
@@ -11441,7 +11423,7 @@
         <v>431</v>
       </c>
       <c r="C408" t="s">
-        <v>1516</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="409" spans="1:3">
@@ -11452,7 +11434,7 @@
         <v>432</v>
       </c>
       <c r="C409" t="s">
-        <v>1517</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="410" spans="1:3">
@@ -11463,7 +11445,7 @@
         <v>433</v>
       </c>
       <c r="C410" t="s">
-        <v>1518</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="411" spans="1:3">
@@ -11474,7 +11456,7 @@
         <v>434</v>
       </c>
       <c r="C411" t="s">
-        <v>1519</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="412" spans="1:3">
@@ -11485,7 +11467,7 @@
         <v>435</v>
       </c>
       <c r="C412" t="s">
-        <v>1520</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="413" spans="1:3">
@@ -11496,7 +11478,7 @@
         <v>436</v>
       </c>
       <c r="C413" t="s">
-        <v>1521</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="414" spans="1:3">
@@ -11507,7 +11489,7 @@
         <v>437</v>
       </c>
       <c r="C414" t="s">
-        <v>1522</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="415" spans="1:3">
@@ -11518,7 +11500,7 @@
         <v>438</v>
       </c>
       <c r="C415" t="s">
-        <v>1523</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="416" spans="1:3">
@@ -11529,7 +11511,7 @@
         <v>439</v>
       </c>
       <c r="C416" t="s">
-        <v>1524</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="417" spans="1:3">
@@ -11540,7 +11522,7 @@
         <v>440</v>
       </c>
       <c r="C417" t="s">
-        <v>1525</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="418" spans="1:3">
@@ -11551,7 +11533,7 @@
         <v>441</v>
       </c>
       <c r="C418" t="s">
-        <v>1526</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="419" spans="1:3">
@@ -11562,7 +11544,7 @@
         <v>442</v>
       </c>
       <c r="C419" t="s">
-        <v>1527</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="420" spans="1:3">
@@ -11573,7 +11555,7 @@
         <v>443</v>
       </c>
       <c r="C420" t="s">
-        <v>1528</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="421" spans="1:3">
@@ -11584,7 +11566,7 @@
         <v>444</v>
       </c>
       <c r="C421" t="s">
-        <v>1529</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="422" spans="1:3">
@@ -11595,7 +11577,7 @@
         <v>445</v>
       </c>
       <c r="C422" t="s">
-        <v>1530</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="423" spans="1:3">
@@ -11606,7 +11588,7 @@
         <v>446</v>
       </c>
       <c r="C423" t="s">
-        <v>1531</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="424" spans="1:3">
@@ -11617,7 +11599,7 @@
         <v>447</v>
       </c>
       <c r="C424" t="s">
-        <v>1532</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="425" spans="1:3">
@@ -11628,7 +11610,7 @@
         <v>448</v>
       </c>
       <c r="C425" t="s">
-        <v>1533</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="426" spans="1:3">
@@ -11639,7 +11621,7 @@
         <v>449</v>
       </c>
       <c r="C426" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="427" spans="1:3">
@@ -11650,7 +11632,7 @@
         <v>450</v>
       </c>
       <c r="C427" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="428" spans="1:3">
@@ -11661,7 +11643,7 @@
         <v>451</v>
       </c>
       <c r="C428" t="s">
-        <v>1536</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="429" spans="1:3">
@@ -11672,7 +11654,7 @@
         <v>452</v>
       </c>
       <c r="C429" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="430" spans="1:3">
@@ -11683,7 +11665,7 @@
         <v>453</v>
       </c>
       <c r="C430" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="431" spans="1:3">
@@ -11694,7 +11676,7 @@
         <v>454</v>
       </c>
       <c r="C431" t="s">
-        <v>1539</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="432" spans="1:3">
@@ -11705,7 +11687,7 @@
         <v>455</v>
       </c>
       <c r="C432" t="s">
-        <v>1540</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="433" spans="1:3">
@@ -11716,7 +11698,7 @@
         <v>456</v>
       </c>
       <c r="C433" t="s">
-        <v>1541</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="434" spans="1:3">
@@ -11727,7 +11709,7 @@
         <v>457</v>
       </c>
       <c r="C434" t="s">
-        <v>1542</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="435" spans="1:3">
@@ -11738,7 +11720,7 @@
         <v>458</v>
       </c>
       <c r="C435" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="436" spans="1:3">
@@ -11749,7 +11731,7 @@
         <v>459</v>
       </c>
       <c r="C436" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="437" spans="1:3">
@@ -11760,7 +11742,7 @@
         <v>460</v>
       </c>
       <c r="C437" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="438" spans="1:3">
@@ -11771,7 +11753,7 @@
         <v>461</v>
       </c>
       <c r="C438" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="439" spans="1:3">
@@ -11782,7 +11764,7 @@
         <v>462</v>
       </c>
       <c r="C439" t="s">
-        <v>1547</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="440" spans="1:3">
@@ -11793,7 +11775,7 @@
         <v>463</v>
       </c>
       <c r="C440" t="s">
-        <v>1548</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="441" spans="1:3">
@@ -11804,7 +11786,7 @@
         <v>464</v>
       </c>
       <c r="C441" t="s">
-        <v>1549</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="442" spans="1:3">
@@ -11815,7 +11797,7 @@
         <v>465</v>
       </c>
       <c r="C442" t="s">
-        <v>1550</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="443" spans="1:3">
@@ -11826,7 +11808,7 @@
         <v>466</v>
       </c>
       <c r="C443" t="s">
-        <v>1551</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="444" spans="1:3">
@@ -11837,7 +11819,7 @@
         <v>467</v>
       </c>
       <c r="C444" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="445" spans="1:3">
@@ -11848,7 +11830,7 @@
         <v>468</v>
       </c>
       <c r="C445" t="s">
-        <v>1553</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="446" spans="1:3">
@@ -11859,7 +11841,7 @@
         <v>469</v>
       </c>
       <c r="C446" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="447" spans="1:3">
@@ -11870,7 +11852,7 @@
         <v>470</v>
       </c>
       <c r="C447" t="s">
-        <v>1555</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="448" spans="1:3">
@@ -11881,7 +11863,7 @@
         <v>471</v>
       </c>
       <c r="C448" t="s">
-        <v>1556</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="449" spans="1:3">
@@ -11892,7 +11874,7 @@
         <v>472</v>
       </c>
       <c r="C449" t="s">
-        <v>1557</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="450" spans="1:3">
@@ -11903,7 +11885,7 @@
         <v>473</v>
       </c>
       <c r="C450" t="s">
-        <v>1558</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="451" spans="1:3">
@@ -11914,7 +11896,7 @@
         <v>474</v>
       </c>
       <c r="C451" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="452" spans="1:3">
@@ -11925,7 +11907,7 @@
         <v>475</v>
       </c>
       <c r="C452" t="s">
-        <v>1560</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="453" spans="1:3">
@@ -11936,7 +11918,7 @@
         <v>476</v>
       </c>
       <c r="C453" t="s">
-        <v>1561</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="454" spans="1:3">
@@ -11947,7 +11929,7 @@
         <v>477</v>
       </c>
       <c r="C454" t="s">
-        <v>1562</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="455" spans="1:3">
@@ -11958,7 +11940,7 @@
         <v>478</v>
       </c>
       <c r="C455" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="456" spans="1:3">
@@ -11969,7 +11951,7 @@
         <v>479</v>
       </c>
       <c r="C456" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="457" spans="1:3">
@@ -11980,7 +11962,7 @@
         <v>480</v>
       </c>
       <c r="C457" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="458" spans="1:3">
@@ -11991,7 +11973,7 @@
         <v>481</v>
       </c>
       <c r="C458" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="459" spans="1:3">
@@ -12002,7 +11984,7 @@
         <v>482</v>
       </c>
       <c r="C459" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="460" spans="1:3">
@@ -12013,7 +11995,7 @@
         <v>483</v>
       </c>
       <c r="C460" t="s">
-        <v>1568</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="461" spans="1:3">
@@ -12024,7 +12006,7 @@
         <v>484</v>
       </c>
       <c r="C461" t="s">
-        <v>1569</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="462" spans="1:3">
@@ -12035,7 +12017,7 @@
         <v>485</v>
       </c>
       <c r="C462" t="s">
-        <v>1570</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="463" spans="1:3">
@@ -12046,7 +12028,7 @@
         <v>486</v>
       </c>
       <c r="C463" t="s">
-        <v>1571</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="464" spans="1:3">
@@ -12057,7 +12039,7 @@
         <v>487</v>
       </c>
       <c r="C464" t="s">
-        <v>1572</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="465" spans="1:3">
@@ -12068,7 +12050,7 @@
         <v>488</v>
       </c>
       <c r="C465" t="s">
-        <v>1573</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="466" spans="1:3">
@@ -12079,7 +12061,7 @@
         <v>489</v>
       </c>
       <c r="C466" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="467" spans="1:3">
@@ -12090,7 +12072,7 @@
         <v>490</v>
       </c>
       <c r="C467" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="468" spans="1:3">
@@ -12101,7 +12083,7 @@
         <v>491</v>
       </c>
       <c r="C468" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="469" spans="1:3">
@@ -12112,7 +12094,7 @@
         <v>492</v>
       </c>
       <c r="C469" t="s">
-        <v>1577</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="470" spans="1:3">
@@ -12123,7 +12105,7 @@
         <v>493</v>
       </c>
       <c r="C470" t="s">
-        <v>1578</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="471" spans="1:3">
@@ -12134,7 +12116,7 @@
         <v>494</v>
       </c>
       <c r="C471" t="s">
-        <v>1547</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="472" spans="1:3">
@@ -12145,7 +12127,7 @@
         <v>495</v>
       </c>
       <c r="C472" t="s">
-        <v>1539</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="473" spans="1:3">
@@ -12156,7 +12138,7 @@
         <v>496</v>
       </c>
       <c r="C473" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="474" spans="1:3">
@@ -12167,7 +12149,7 @@
         <v>497</v>
       </c>
       <c r="C474" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="475" spans="1:3">
@@ -12178,7 +12160,7 @@
         <v>498</v>
       </c>
       <c r="C475" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="476" spans="1:3">
@@ -12189,7 +12171,7 @@
         <v>499</v>
       </c>
       <c r="C476" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="477" spans="1:3">
@@ -12200,7 +12182,7 @@
         <v>500</v>
       </c>
       <c r="C477" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="478" spans="1:3">
@@ -12211,7 +12193,7 @@
         <v>501</v>
       </c>
       <c r="C478" t="s">
-        <v>1584</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="479" spans="1:3">
@@ -12222,7 +12204,7 @@
         <v>502</v>
       </c>
       <c r="C479" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="480" spans="1:3">
@@ -12233,7 +12215,7 @@
         <v>503</v>
       </c>
       <c r="C480" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="481" spans="1:3">
@@ -12244,7 +12226,7 @@
         <v>504</v>
       </c>
       <c r="C481" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="482" spans="1:3">
@@ -12255,7 +12237,7 @@
         <v>505</v>
       </c>
       <c r="C482" t="s">
-        <v>1588</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="483" spans="1:3">
@@ -12266,7 +12248,7 @@
         <v>506</v>
       </c>
       <c r="C483" t="s">
-        <v>1589</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="484" spans="1:3">
@@ -12277,7 +12259,7 @@
         <v>507</v>
       </c>
       <c r="C484" t="s">
-        <v>1590</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="485" spans="1:3">
@@ -12288,7 +12270,7 @@
         <v>508</v>
       </c>
       <c r="C485" t="s">
-        <v>1591</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="486" spans="1:3">
@@ -12299,7 +12281,7 @@
         <v>509</v>
       </c>
       <c r="C486" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="487" spans="1:3">
@@ -12310,7 +12292,7 @@
         <v>510</v>
       </c>
       <c r="C487" t="s">
-        <v>1593</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="488" spans="1:3">
@@ -12321,7 +12303,7 @@
         <v>511</v>
       </c>
       <c r="C488" t="s">
-        <v>1594</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="489" spans="1:3">
@@ -12332,7 +12314,7 @@
         <v>512</v>
       </c>
       <c r="C489" t="s">
-        <v>1595</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="490" spans="1:3">
@@ -12343,7 +12325,7 @@
         <v>513</v>
       </c>
       <c r="C490" t="s">
-        <v>1596</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="491" spans="1:3">
@@ -12354,7 +12336,7 @@
         <v>514</v>
       </c>
       <c r="C491" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="492" spans="1:3">
@@ -12365,7 +12347,7 @@
         <v>515</v>
       </c>
       <c r="C492" t="s">
-        <v>1598</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="493" spans="1:3">
@@ -12376,7 +12358,7 @@
         <v>516</v>
       </c>
       <c r="C493" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="494" spans="1:3">
@@ -12387,7 +12369,7 @@
         <v>517</v>
       </c>
       <c r="C494" t="s">
-        <v>1600</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="495" spans="1:3">
@@ -12398,7 +12380,7 @@
         <v>518</v>
       </c>
       <c r="C495" t="s">
-        <v>1601</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="496" spans="1:3">
@@ -12409,7 +12391,7 @@
         <v>519</v>
       </c>
       <c r="C496" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="497" spans="1:3">
@@ -12420,7 +12402,7 @@
         <v>520</v>
       </c>
       <c r="C497" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="498" spans="1:3">
@@ -12431,7 +12413,7 @@
         <v>521</v>
       </c>
       <c r="C498" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="499" spans="1:3">
@@ -12442,7 +12424,7 @@
         <v>522</v>
       </c>
       <c r="C499" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="500" spans="1:3">
@@ -12453,7 +12435,7 @@
         <v>523</v>
       </c>
       <c r="C500" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="501" spans="1:3">
@@ -12464,7 +12446,7 @@
         <v>524</v>
       </c>
       <c r="C501" t="s">
-        <v>1607</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="502" spans="1:3">
@@ -12475,7 +12457,7 @@
         <v>525</v>
       </c>
       <c r="C502" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="503" spans="1:3">
@@ -12486,7 +12468,7 @@
         <v>526</v>
       </c>
       <c r="C503" t="s">
-        <v>1609</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="504" spans="1:3">
@@ -12497,7 +12479,7 @@
         <v>527</v>
       </c>
       <c r="C504" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="505" spans="1:3">
@@ -12508,7 +12490,7 @@
         <v>528</v>
       </c>
       <c r="C505" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="506" spans="1:3">
@@ -12519,7 +12501,7 @@
         <v>529</v>
       </c>
       <c r="C506" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="507" spans="1:3">
@@ -12530,7 +12512,7 @@
         <v>530</v>
       </c>
       <c r="C507" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="508" spans="1:3">
@@ -12541,7 +12523,7 @@
         <v>531</v>
       </c>
       <c r="C508" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="509" spans="1:3">
@@ -12552,7 +12534,7 @@
         <v>532</v>
       </c>
       <c r="C509" t="s">
-        <v>1615</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="510" spans="1:3">
@@ -12563,7 +12545,7 @@
         <v>533</v>
       </c>
       <c r="C510" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="511" spans="1:3">
@@ -12574,7 +12556,7 @@
         <v>534</v>
       </c>
       <c r="C511" t="s">
-        <v>1617</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="512" spans="1:3">
@@ -12585,7 +12567,7 @@
         <v>535</v>
       </c>
       <c r="C512" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="513" spans="1:3">
@@ -12596,7 +12578,7 @@
         <v>536</v>
       </c>
       <c r="C513" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="514" spans="1:3">
@@ -12607,7 +12589,7 @@
         <v>537</v>
       </c>
       <c r="C514" t="s">
-        <v>1620</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="515" spans="1:3">
@@ -12618,7 +12600,7 @@
         <v>538</v>
       </c>
       <c r="C515" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="516" spans="1:3">
@@ -12629,7 +12611,7 @@
         <v>539</v>
       </c>
       <c r="C516" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="517" spans="1:3">
@@ -12640,7 +12622,7 @@
         <v>540</v>
       </c>
       <c r="C517" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="518" spans="1:3">
@@ -12651,7 +12633,7 @@
         <v>541</v>
       </c>
       <c r="C518" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="519" spans="1:3">
@@ -12662,7 +12644,7 @@
         <v>542</v>
       </c>
       <c r="C519" t="s">
-        <v>1625</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="520" spans="1:3">
@@ -12673,7 +12655,7 @@
         <v>543</v>
       </c>
       <c r="C520" t="s">
-        <v>1626</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="521" spans="1:3">
@@ -12684,7 +12666,7 @@
         <v>544</v>
       </c>
       <c r="C521" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="522" spans="1:3">
@@ -12695,7 +12677,7 @@
         <v>545</v>
       </c>
       <c r="C522" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="523" spans="1:3">
@@ -12706,7 +12688,7 @@
         <v>546</v>
       </c>
       <c r="C523" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="524" spans="1:3">
@@ -12717,7 +12699,7 @@
         <v>547</v>
       </c>
       <c r="C524" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="525" spans="1:3">
@@ -12728,7 +12710,7 @@
         <v>548</v>
       </c>
       <c r="C525" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="526" spans="1:3">
@@ -12739,7 +12721,7 @@
         <v>549</v>
       </c>
       <c r="C526" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="527" spans="1:3">
@@ -12750,7 +12732,7 @@
         <v>550</v>
       </c>
       <c r="C527" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="528" spans="1:3">
@@ -12761,7 +12743,7 @@
         <v>551</v>
       </c>
       <c r="C528" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="529" spans="1:3">
@@ -12772,7 +12754,7 @@
         <v>552</v>
       </c>
       <c r="C529" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="530" spans="1:3">
@@ -12783,7 +12765,7 @@
         <v>553</v>
       </c>
       <c r="C530" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="531" spans="1:3">
@@ -12794,7 +12776,7 @@
         <v>554</v>
       </c>
       <c r="C531" t="s">
-        <v>1637</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="532" spans="1:3">
@@ -12805,7 +12787,7 @@
         <v>555</v>
       </c>
       <c r="C532" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="533" spans="1:3">
@@ -12816,7 +12798,7 @@
         <v>556</v>
       </c>
       <c r="C533" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="534" spans="1:3">
@@ -12827,7 +12809,7 @@
         <v>557</v>
       </c>
       <c r="C534" t="s">
-        <v>1640</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="535" spans="1:3">
@@ -12838,7 +12820,7 @@
         <v>558</v>
       </c>
       <c r="C535" t="s">
-        <v>1641</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="536" spans="1:3">
@@ -12849,7 +12831,7 @@
         <v>559</v>
       </c>
       <c r="C536" t="s">
-        <v>1642</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="537" spans="1:3">
@@ -12860,18 +12842,18 @@
         <v>560</v>
       </c>
       <c r="C537" t="s">
-        <v>1643</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="538" spans="1:3">
       <c r="A538" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B538" t="s">
         <v>561</v>
       </c>
       <c r="C538" t="s">
-        <v>1644</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="539" spans="1:3">
@@ -12882,7 +12864,7 @@
         <v>562</v>
       </c>
       <c r="C539" t="s">
-        <v>1645</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="540" spans="1:3">
@@ -12893,7 +12875,7 @@
         <v>563</v>
       </c>
       <c r="C540" t="s">
-        <v>1646</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="541" spans="1:3">
@@ -12904,7 +12886,7 @@
         <v>564</v>
       </c>
       <c r="C541" t="s">
-        <v>1647</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="542" spans="1:3">
@@ -12915,7 +12897,7 @@
         <v>565</v>
       </c>
       <c r="C542" t="s">
-        <v>1648</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="543" spans="1:3">
@@ -12926,7 +12908,7 @@
         <v>566</v>
       </c>
       <c r="C543" t="s">
-        <v>1649</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="544" spans="1:3">
@@ -12937,7 +12919,7 @@
         <v>567</v>
       </c>
       <c r="C544" t="s">
-        <v>1650</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="545" spans="1:3">
@@ -12948,7 +12930,7 @@
         <v>568</v>
       </c>
       <c r="C545" t="s">
-        <v>1651</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="546" spans="1:3">
@@ -12959,7 +12941,7 @@
         <v>569</v>
       </c>
       <c r="C546" t="s">
-        <v>1652</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="547" spans="1:3">
@@ -12970,7 +12952,7 @@
         <v>570</v>
       </c>
       <c r="C547" t="s">
-        <v>1653</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="548" spans="1:3">
@@ -12981,7 +12963,7 @@
         <v>571</v>
       </c>
       <c r="C548" t="s">
-        <v>1654</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="549" spans="1:3">
@@ -12992,7 +12974,7 @@
         <v>572</v>
       </c>
       <c r="C549" t="s">
-        <v>1655</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="550" spans="1:3">
@@ -13003,7 +12985,7 @@
         <v>573</v>
       </c>
       <c r="C550" t="s">
-        <v>1656</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="551" spans="1:3">
@@ -13014,7 +12996,7 @@
         <v>574</v>
       </c>
       <c r="C551" t="s">
-        <v>1657</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="552" spans="1:3">
@@ -13025,7 +13007,7 @@
         <v>575</v>
       </c>
       <c r="C552" t="s">
-        <v>1658</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="553" spans="1:3">
@@ -13036,7 +13018,7 @@
         <v>576</v>
       </c>
       <c r="C553" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="554" spans="1:3">
@@ -13047,7 +13029,7 @@
         <v>577</v>
       </c>
       <c r="C554" t="s">
-        <v>1660</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="555" spans="1:3">
@@ -13058,7 +13040,7 @@
         <v>578</v>
       </c>
       <c r="C555" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="556" spans="1:3">
@@ -13069,7 +13051,7 @@
         <v>579</v>
       </c>
       <c r="C556" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="557" spans="1:3">
@@ -13080,7 +13062,7 @@
         <v>580</v>
       </c>
       <c r="C557" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="558" spans="1:3">
@@ -13091,7 +13073,7 @@
         <v>581</v>
       </c>
       <c r="C558" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="559" spans="1:3">
@@ -13102,18 +13084,18 @@
         <v>582</v>
       </c>
       <c r="C559" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="560" spans="1:3">
       <c r="A560" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B560" t="s">
         <v>583</v>
       </c>
       <c r="C560" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="561" spans="1:3">
@@ -13124,7 +13106,7 @@
         <v>584</v>
       </c>
       <c r="C561" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="562" spans="1:3">
@@ -13135,7 +13117,7 @@
         <v>585</v>
       </c>
       <c r="C562" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="563" spans="1:3">
@@ -13146,7 +13128,7 @@
         <v>586</v>
       </c>
       <c r="C563" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="564" spans="1:3">
@@ -13157,7 +13139,7 @@
         <v>587</v>
       </c>
       <c r="C564" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="565" spans="1:3">
@@ -13168,7 +13150,7 @@
         <v>588</v>
       </c>
       <c r="C565" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="566" spans="1:3">
@@ -13179,7 +13161,7 @@
         <v>589</v>
       </c>
       <c r="C566" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="567" spans="1:3">
@@ -13190,7 +13172,7 @@
         <v>590</v>
       </c>
       <c r="C567" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="568" spans="1:3">
@@ -13201,7 +13183,7 @@
         <v>591</v>
       </c>
       <c r="C568" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="569" spans="1:3">
@@ -13212,7 +13194,7 @@
         <v>592</v>
       </c>
       <c r="C569" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="570" spans="1:3">
@@ -13223,7 +13205,7 @@
         <v>593</v>
       </c>
       <c r="C570" t="s">
-        <v>1676</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="571" spans="1:3">
@@ -13234,7 +13216,7 @@
         <v>594</v>
       </c>
       <c r="C571" t="s">
-        <v>1677</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="572" spans="1:3">
@@ -13245,7 +13227,7 @@
         <v>595</v>
       </c>
       <c r="C572" t="s">
-        <v>1678</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="573" spans="1:3">
@@ -13256,7 +13238,7 @@
         <v>596</v>
       </c>
       <c r="C573" t="s">
-        <v>1679</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="574" spans="1:3">
@@ -13267,7 +13249,7 @@
         <v>597</v>
       </c>
       <c r="C574" t="s">
-        <v>1680</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="575" spans="1:3">
@@ -13278,7 +13260,7 @@
         <v>598</v>
       </c>
       <c r="C575" t="s">
-        <v>1681</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="576" spans="1:3">
@@ -13289,7 +13271,7 @@
         <v>599</v>
       </c>
       <c r="C576" t="s">
-        <v>1682</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="577" spans="1:3">
@@ -13300,7 +13282,7 @@
         <v>600</v>
       </c>
       <c r="C577" t="s">
-        <v>1683</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="578" spans="1:3">
@@ -13311,7 +13293,7 @@
         <v>601</v>
       </c>
       <c r="C578" t="s">
-        <v>1684</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="579" spans="1:3">
@@ -13322,7 +13304,7 @@
         <v>602</v>
       </c>
       <c r="C579" t="s">
-        <v>1685</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="580" spans="1:3">
@@ -13333,7 +13315,7 @@
         <v>603</v>
       </c>
       <c r="C580" t="s">
-        <v>1686</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="581" spans="1:3">
@@ -13344,7 +13326,7 @@
         <v>604</v>
       </c>
       <c r="C581" t="s">
-        <v>1687</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="582" spans="1:3">
@@ -13355,7 +13337,7 @@
         <v>605</v>
       </c>
       <c r="C582" t="s">
-        <v>1688</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="583" spans="1:3">
@@ -13366,7 +13348,7 @@
         <v>606</v>
       </c>
       <c r="C583" t="s">
-        <v>1689</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="584" spans="1:3">
@@ -13377,7 +13359,7 @@
         <v>607</v>
       </c>
       <c r="C584" t="s">
-        <v>1690</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="585" spans="1:3">
@@ -13388,7 +13370,7 @@
         <v>608</v>
       </c>
       <c r="C585" t="s">
-        <v>1691</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="586" spans="1:3">
@@ -13399,7 +13381,7 @@
         <v>609</v>
       </c>
       <c r="C586" t="s">
-        <v>1692</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="587" spans="1:3">
@@ -13410,7 +13392,7 @@
         <v>610</v>
       </c>
       <c r="C587" t="s">
-        <v>1693</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="588" spans="1:3">
@@ -13421,7 +13403,7 @@
         <v>611</v>
       </c>
       <c r="C588" t="s">
-        <v>1694</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="589" spans="1:3">
@@ -13432,7 +13414,7 @@
         <v>612</v>
       </c>
       <c r="C589" t="s">
-        <v>1695</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="590" spans="1:3">
@@ -13443,7 +13425,7 @@
         <v>613</v>
       </c>
       <c r="C590" t="s">
-        <v>1696</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="591" spans="1:3">
@@ -13454,7 +13436,7 @@
         <v>614</v>
       </c>
       <c r="C591" t="s">
-        <v>1697</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="592" spans="1:3">
@@ -13465,7 +13447,7 @@
         <v>615</v>
       </c>
       <c r="C592" t="s">
-        <v>1698</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="593" spans="1:3">
@@ -13476,7 +13458,7 @@
         <v>616</v>
       </c>
       <c r="C593" t="s">
-        <v>1699</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="594" spans="1:3">
@@ -13487,7 +13469,7 @@
         <v>617</v>
       </c>
       <c r="C594" t="s">
-        <v>1700</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="595" spans="1:3">
@@ -13498,7 +13480,7 @@
         <v>618</v>
       </c>
       <c r="C595" t="s">
-        <v>1701</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="596" spans="1:3">
@@ -13509,7 +13491,7 @@
         <v>619</v>
       </c>
       <c r="C596" t="s">
-        <v>1702</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="597" spans="1:3">
@@ -13520,7 +13502,7 @@
         <v>620</v>
       </c>
       <c r="C597" t="s">
-        <v>1703</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="598" spans="1:3">
@@ -13531,7 +13513,7 @@
         <v>621</v>
       </c>
       <c r="C598" t="s">
-        <v>1673</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="599" spans="1:3">
@@ -13542,7 +13524,7 @@
         <v>622</v>
       </c>
       <c r="C599" t="s">
-        <v>1704</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="600" spans="1:3">
@@ -13553,7 +13535,7 @@
         <v>623</v>
       </c>
       <c r="C600" t="s">
-        <v>1705</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="601" spans="1:3">
@@ -13564,7 +13546,7 @@
         <v>624</v>
       </c>
       <c r="C601" t="s">
-        <v>1706</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="602" spans="1:3">
@@ -13575,7 +13557,7 @@
         <v>625</v>
       </c>
       <c r="C602" t="s">
-        <v>1707</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="603" spans="1:3">
@@ -13586,18 +13568,18 @@
         <v>626</v>
       </c>
       <c r="C603" t="s">
-        <v>1708</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="604" spans="1:3">
       <c r="A604" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B604" t="s">
         <v>627</v>
       </c>
       <c r="C604" t="s">
-        <v>1709</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="605" spans="1:3">
@@ -13608,7 +13590,7 @@
         <v>628</v>
       </c>
       <c r="C605" t="s">
-        <v>1710</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="606" spans="1:3">
@@ -13619,7 +13601,7 @@
         <v>629</v>
       </c>
       <c r="C606" t="s">
-        <v>1711</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="607" spans="1:3">
@@ -13630,7 +13612,7 @@
         <v>630</v>
       </c>
       <c r="C607" t="s">
-        <v>1712</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="608" spans="1:3">
@@ -13641,7 +13623,7 @@
         <v>631</v>
       </c>
       <c r="C608" t="s">
-        <v>1713</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="609" spans="1:3">
@@ -13652,7 +13634,7 @@
         <v>632</v>
       </c>
       <c r="C609" t="s">
-        <v>1714</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="610" spans="1:3">
@@ -13663,7 +13645,7 @@
         <v>633</v>
       </c>
       <c r="C610" t="s">
-        <v>1715</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="611" spans="1:3">
@@ -13674,7 +13656,7 @@
         <v>634</v>
       </c>
       <c r="C611" t="s">
-        <v>1716</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="612" spans="1:3">
@@ -13685,7 +13667,7 @@
         <v>635</v>
       </c>
       <c r="C612" t="s">
-        <v>1717</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="613" spans="1:3">
@@ -13696,7 +13678,7 @@
         <v>636</v>
       </c>
       <c r="C613" t="s">
-        <v>1718</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="614" spans="1:3">
@@ -13707,18 +13689,18 @@
         <v>637</v>
       </c>
       <c r="C614" t="s">
-        <v>1719</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="615" spans="1:3">
       <c r="A615" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B615" t="s">
         <v>638</v>
       </c>
       <c r="C615" t="s">
-        <v>1720</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="616" spans="1:3">
@@ -13729,7 +13711,7 @@
         <v>639</v>
       </c>
       <c r="C616" t="s">
-        <v>1721</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="617" spans="1:3">
@@ -13740,7 +13722,7 @@
         <v>640</v>
       </c>
       <c r="C617" t="s">
-        <v>1722</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="618" spans="1:3">
@@ -13751,7 +13733,7 @@
         <v>641</v>
       </c>
       <c r="C618" t="s">
-        <v>1723</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="619" spans="1:3">
@@ -13762,7 +13744,7 @@
         <v>642</v>
       </c>
       <c r="C619" t="s">
-        <v>1724</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="620" spans="1:3">
@@ -13773,7 +13755,7 @@
         <v>643</v>
       </c>
       <c r="C620" t="s">
-        <v>1725</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="621" spans="1:3">
@@ -13784,7 +13766,7 @@
         <v>644</v>
       </c>
       <c r="C621" t="s">
-        <v>1726</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="622" spans="1:3">
@@ -13795,7 +13777,7 @@
         <v>645</v>
       </c>
       <c r="C622" t="s">
-        <v>1727</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="623" spans="1:3">
@@ -13806,7 +13788,7 @@
         <v>646</v>
       </c>
       <c r="C623" t="s">
-        <v>1728</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="624" spans="1:3">
@@ -13817,7 +13799,7 @@
         <v>647</v>
       </c>
       <c r="C624" t="s">
-        <v>1729</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="625" spans="1:3">
@@ -13828,7 +13810,7 @@
         <v>648</v>
       </c>
       <c r="C625" t="s">
-        <v>1730</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="626" spans="1:3">
@@ -13839,7 +13821,7 @@
         <v>649</v>
       </c>
       <c r="C626" t="s">
-        <v>1731</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="627" spans="1:3">
@@ -13850,7 +13832,7 @@
         <v>650</v>
       </c>
       <c r="C627" t="s">
-        <v>1732</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="628" spans="1:3">
@@ -13861,7 +13843,7 @@
         <v>651</v>
       </c>
       <c r="C628" t="s">
-        <v>1733</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="629" spans="1:3">
@@ -13872,7 +13854,7 @@
         <v>652</v>
       </c>
       <c r="C629" t="s">
-        <v>1734</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="630" spans="1:3">
@@ -13883,7 +13865,7 @@
         <v>653</v>
       </c>
       <c r="C630" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="631" spans="1:3">
@@ -13894,7 +13876,7 @@
         <v>654</v>
       </c>
       <c r="C631" t="s">
-        <v>1736</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="632" spans="1:3">
@@ -13905,7 +13887,7 @@
         <v>655</v>
       </c>
       <c r="C632" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="633" spans="1:3">
@@ -13916,7 +13898,7 @@
         <v>656</v>
       </c>
       <c r="C633" t="s">
-        <v>1738</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="634" spans="1:3">
@@ -13927,7 +13909,7 @@
         <v>657</v>
       </c>
       <c r="C634" t="s">
-        <v>1739</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="635" spans="1:3">
@@ -13938,7 +13920,7 @@
         <v>658</v>
       </c>
       <c r="C635" t="s">
-        <v>1740</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="636" spans="1:3">
@@ -13949,7 +13931,7 @@
         <v>659</v>
       </c>
       <c r="C636" t="s">
-        <v>1741</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="637" spans="1:3">
@@ -13960,7 +13942,7 @@
         <v>660</v>
       </c>
       <c r="C637" t="s">
-        <v>1742</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="638" spans="1:3">
@@ -13971,7 +13953,7 @@
         <v>661</v>
       </c>
       <c r="C638" t="s">
-        <v>1743</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="639" spans="1:3">
@@ -13982,7 +13964,7 @@
         <v>662</v>
       </c>
       <c r="C639" t="s">
-        <v>1744</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="640" spans="1:3">
@@ -13993,18 +13975,18 @@
         <v>663</v>
       </c>
       <c r="C640" t="s">
-        <v>1745</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="641" spans="1:3">
       <c r="A641" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B641" t="s">
         <v>664</v>
       </c>
       <c r="C641" t="s">
-        <v>1746</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="642" spans="1:3">
@@ -14015,7 +13997,7 @@
         <v>665</v>
       </c>
       <c r="C642" t="s">
-        <v>1747</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="643" spans="1:3">
@@ -14026,7 +14008,7 @@
         <v>666</v>
       </c>
       <c r="C643" t="s">
-        <v>1748</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="644" spans="1:3">
@@ -14037,7 +14019,7 @@
         <v>667</v>
       </c>
       <c r="C644" t="s">
-        <v>1749</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="645" spans="1:3">
@@ -14048,7 +14030,7 @@
         <v>668</v>
       </c>
       <c r="C645" t="s">
-        <v>1750</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="646" spans="1:3">
@@ -14059,7 +14041,7 @@
         <v>669</v>
       </c>
       <c r="C646" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="647" spans="1:3">
@@ -14070,7 +14052,7 @@
         <v>670</v>
       </c>
       <c r="C647" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="648" spans="1:3">
@@ -14081,7 +14063,7 @@
         <v>671</v>
       </c>
       <c r="C648" t="s">
-        <v>1753</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="649" spans="1:3">
@@ -14092,7 +14074,7 @@
         <v>672</v>
       </c>
       <c r="C649" t="s">
-        <v>1754</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="650" spans="1:3">
@@ -14103,7 +14085,7 @@
         <v>673</v>
       </c>
       <c r="C650" t="s">
-        <v>1755</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="651" spans="1:3">
@@ -14114,7 +14096,7 @@
         <v>674</v>
       </c>
       <c r="C651" t="s">
-        <v>1756</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="652" spans="1:3">
@@ -14125,7 +14107,7 @@
         <v>675</v>
       </c>
       <c r="C652" t="s">
-        <v>1757</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="653" spans="1:3">
@@ -14136,7 +14118,7 @@
         <v>676</v>
       </c>
       <c r="C653" t="s">
-        <v>1758</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="654" spans="1:3">
@@ -14147,7 +14129,7 @@
         <v>677</v>
       </c>
       <c r="C654" t="s">
-        <v>1759</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="655" spans="1:3">
@@ -14158,18 +14140,18 @@
         <v>678</v>
       </c>
       <c r="C655" t="s">
-        <v>1760</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="656" spans="1:3">
       <c r="A656" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B656" t="s">
         <v>679</v>
       </c>
       <c r="C656" t="s">
-        <v>1761</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="657" spans="1:3">
@@ -14180,7 +14162,7 @@
         <v>680</v>
       </c>
       <c r="C657" t="s">
-        <v>1762</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="658" spans="1:3">
@@ -14191,7 +14173,7 @@
         <v>681</v>
       </c>
       <c r="C658" t="s">
-        <v>1763</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="659" spans="1:3">
@@ -14202,7 +14184,7 @@
         <v>682</v>
       </c>
       <c r="C659" t="s">
-        <v>1764</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="660" spans="1:3">
@@ -14213,7 +14195,7 @@
         <v>683</v>
       </c>
       <c r="C660" t="s">
-        <v>1765</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="661" spans="1:3">
@@ -14224,7 +14206,7 @@
         <v>684</v>
       </c>
       <c r="C661" t="s">
-        <v>1766</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="662" spans="1:3">
@@ -14235,7 +14217,7 @@
         <v>685</v>
       </c>
       <c r="C662" t="s">
-        <v>1767</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="663" spans="1:3">
@@ -14246,7 +14228,7 @@
         <v>686</v>
       </c>
       <c r="C663" t="s">
-        <v>1768</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="664" spans="1:3">
@@ -14257,7 +14239,7 @@
         <v>687</v>
       </c>
       <c r="C664" t="s">
-        <v>1769</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="665" spans="1:3">
@@ -14268,7 +14250,7 @@
         <v>688</v>
       </c>
       <c r="C665" t="s">
-        <v>1770</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="666" spans="1:3">
@@ -14279,7 +14261,7 @@
         <v>689</v>
       </c>
       <c r="C666" t="s">
-        <v>1771</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="667" spans="1:3">
@@ -14290,7 +14272,7 @@
         <v>690</v>
       </c>
       <c r="C667" t="s">
-        <v>1772</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="668" spans="1:3">
@@ -14301,7 +14283,7 @@
         <v>691</v>
       </c>
       <c r="C668" t="s">
-        <v>1773</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="669" spans="1:3">
@@ -14312,7 +14294,7 @@
         <v>692</v>
       </c>
       <c r="C669" t="s">
-        <v>1774</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="670" spans="1:3">
@@ -14323,7 +14305,7 @@
         <v>693</v>
       </c>
       <c r="C670" t="s">
-        <v>1775</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="671" spans="1:3">
@@ -14334,7 +14316,7 @@
         <v>694</v>
       </c>
       <c r="C671" t="s">
-        <v>1776</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="672" spans="1:3">
@@ -14345,7 +14327,7 @@
         <v>695</v>
       </c>
       <c r="C672" t="s">
-        <v>1777</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="673" spans="1:3">
@@ -14356,7 +14338,7 @@
         <v>696</v>
       </c>
       <c r="C673" t="s">
-        <v>1778</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="674" spans="1:3">
@@ -14367,7 +14349,7 @@
         <v>697</v>
       </c>
       <c r="C674" t="s">
-        <v>1779</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="675" spans="1:3">
@@ -14378,7 +14360,7 @@
         <v>698</v>
       </c>
       <c r="C675" t="s">
-        <v>1780</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="676" spans="1:3">
@@ -14389,7 +14371,7 @@
         <v>699</v>
       </c>
       <c r="C676" t="s">
-        <v>1781</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="677" spans="1:3">
@@ -14400,7 +14382,7 @@
         <v>700</v>
       </c>
       <c r="C677" t="s">
-        <v>1782</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="678" spans="1:3">
@@ -14411,7 +14393,7 @@
         <v>701</v>
       </c>
       <c r="C678" t="s">
-        <v>1783</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="679" spans="1:3">
@@ -14422,7 +14404,7 @@
         <v>702</v>
       </c>
       <c r="C679" t="s">
-        <v>1784</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="680" spans="1:3">
@@ -14433,18 +14415,18 @@
         <v>703</v>
       </c>
       <c r="C680" t="s">
-        <v>1785</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="681" spans="1:3">
       <c r="A681" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B681" t="s">
         <v>704</v>
       </c>
       <c r="C681" t="s">
-        <v>1786</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="682" spans="1:3">
@@ -14455,7 +14437,7 @@
         <v>705</v>
       </c>
       <c r="C682" t="s">
-        <v>1787</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="683" spans="1:3">
@@ -14466,7 +14448,7 @@
         <v>706</v>
       </c>
       <c r="C683" t="s">
-        <v>1788</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="684" spans="1:3">
@@ -14477,7 +14459,7 @@
         <v>707</v>
       </c>
       <c r="C684" t="s">
-        <v>1789</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="685" spans="1:3">
@@ -14488,7 +14470,7 @@
         <v>708</v>
       </c>
       <c r="C685" t="s">
-        <v>1790</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="686" spans="1:3">
@@ -14499,7 +14481,7 @@
         <v>709</v>
       </c>
       <c r="C686" t="s">
-        <v>1791</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="687" spans="1:3">
@@ -14510,7 +14492,7 @@
         <v>710</v>
       </c>
       <c r="C687" t="s">
-        <v>1792</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="688" spans="1:3">
@@ -14521,7 +14503,7 @@
         <v>711</v>
       </c>
       <c r="C688" t="s">
-        <v>1793</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="689" spans="1:3">
@@ -14532,7 +14514,7 @@
         <v>712</v>
       </c>
       <c r="C689" t="s">
-        <v>1794</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="690" spans="1:3">
@@ -14543,7 +14525,7 @@
         <v>713</v>
       </c>
       <c r="C690" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="691" spans="1:3">
@@ -14554,7 +14536,7 @@
         <v>714</v>
       </c>
       <c r="C691" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="692" spans="1:3">
@@ -14565,7 +14547,7 @@
         <v>715</v>
       </c>
       <c r="C692" t="s">
-        <v>1797</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="693" spans="1:3">
@@ -14576,7 +14558,7 @@
         <v>716</v>
       </c>
       <c r="C693" t="s">
-        <v>1798</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="694" spans="1:3">
@@ -14587,7 +14569,7 @@
         <v>717</v>
       </c>
       <c r="C694" t="s">
-        <v>1799</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="695" spans="1:3">
@@ -14598,7 +14580,7 @@
         <v>718</v>
       </c>
       <c r="C695" t="s">
-        <v>1800</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="696" spans="1:3">
@@ -14609,18 +14591,18 @@
         <v>719</v>
       </c>
       <c r="C696" t="s">
-        <v>1801</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="697" spans="1:3">
       <c r="A697" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B697" t="s">
         <v>720</v>
       </c>
       <c r="C697" t="s">
-        <v>1213</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="698" spans="1:3">
@@ -14631,7 +14613,7 @@
         <v>721</v>
       </c>
       <c r="C698" t="s">
-        <v>1802</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="699" spans="1:3">
@@ -14642,7 +14624,7 @@
         <v>722</v>
       </c>
       <c r="C699" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="700" spans="1:3">
@@ -14653,7 +14635,7 @@
         <v>723</v>
       </c>
       <c r="C700" t="s">
-        <v>1804</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="701" spans="1:3">
@@ -14664,7 +14646,7 @@
         <v>724</v>
       </c>
       <c r="C701" t="s">
-        <v>1805</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="702" spans="1:3">
@@ -14675,7 +14657,7 @@
         <v>725</v>
       </c>
       <c r="C702" t="s">
-        <v>1806</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="703" spans="1:3">
@@ -14686,7 +14668,7 @@
         <v>726</v>
       </c>
       <c r="C703" t="s">
-        <v>1807</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="704" spans="1:3">
@@ -14697,7 +14679,7 @@
         <v>727</v>
       </c>
       <c r="C704" t="s">
-        <v>1808</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="705" spans="1:3">
@@ -14708,7 +14690,7 @@
         <v>728</v>
       </c>
       <c r="C705" t="s">
-        <v>1809</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="706" spans="1:3">
@@ -14719,7 +14701,7 @@
         <v>729</v>
       </c>
       <c r="C706" t="s">
-        <v>1810</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="707" spans="1:3">
@@ -14730,7 +14712,7 @@
         <v>730</v>
       </c>
       <c r="C707" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="708" spans="1:3">
@@ -14741,7 +14723,7 @@
         <v>731</v>
       </c>
       <c r="C708" t="s">
-        <v>1812</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="709" spans="1:3">
@@ -14752,7 +14734,7 @@
         <v>732</v>
       </c>
       <c r="C709" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="710" spans="1:3">
@@ -14763,7 +14745,7 @@
         <v>733</v>
       </c>
       <c r="C710" t="s">
-        <v>1814</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="711" spans="1:3">
@@ -14774,7 +14756,7 @@
         <v>734</v>
       </c>
       <c r="C711" t="s">
-        <v>1815</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="712" spans="1:3">
@@ -14785,7 +14767,7 @@
         <v>735</v>
       </c>
       <c r="C712" t="s">
-        <v>1816</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="713" spans="1:3">
@@ -14796,7 +14778,7 @@
         <v>736</v>
       </c>
       <c r="C713" t="s">
-        <v>1817</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="714" spans="1:3">
@@ -14807,7 +14789,7 @@
         <v>737</v>
       </c>
       <c r="C714" t="s">
-        <v>1818</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="715" spans="1:3">
@@ -14818,7 +14800,7 @@
         <v>738</v>
       </c>
       <c r="C715" t="s">
-        <v>1819</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="716" spans="1:3">
@@ -14829,7 +14811,7 @@
         <v>739</v>
       </c>
       <c r="C716" t="s">
-        <v>1820</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="717" spans="1:3">
@@ -14840,7 +14822,7 @@
         <v>740</v>
       </c>
       <c r="C717" t="s">
-        <v>1821</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="718" spans="1:3">
@@ -14851,7 +14833,7 @@
         <v>741</v>
       </c>
       <c r="C718" t="s">
-        <v>1822</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="719" spans="1:3">
@@ -14862,7 +14844,7 @@
         <v>742</v>
       </c>
       <c r="C719" t="s">
-        <v>1823</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="720" spans="1:3">
@@ -14873,7 +14855,7 @@
         <v>743</v>
       </c>
       <c r="C720" t="s">
-        <v>1824</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="721" spans="1:3">
@@ -14884,7 +14866,7 @@
         <v>744</v>
       </c>
       <c r="C721" t="s">
-        <v>1825</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="722" spans="1:3">
@@ -14895,7 +14877,7 @@
         <v>745</v>
       </c>
       <c r="C722" t="s">
-        <v>1826</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="723" spans="1:3">
@@ -14906,7 +14888,7 @@
         <v>746</v>
       </c>
       <c r="C723" t="s">
-        <v>1827</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="724" spans="1:3">
@@ -14917,7 +14899,7 @@
         <v>747</v>
       </c>
       <c r="C724" t="s">
-        <v>1828</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="725" spans="1:3">
@@ -14928,7 +14910,7 @@
         <v>748</v>
       </c>
       <c r="C725" t="s">
-        <v>1829</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="726" spans="1:3">
@@ -14939,7 +14921,7 @@
         <v>749</v>
       </c>
       <c r="C726" t="s">
-        <v>1830</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="727" spans="1:3">
@@ -14950,7 +14932,7 @@
         <v>750</v>
       </c>
       <c r="C727" t="s">
-        <v>1831</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="728" spans="1:3">
@@ -14961,7 +14943,7 @@
         <v>751</v>
       </c>
       <c r="C728" t="s">
-        <v>1832</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="729" spans="1:3">
@@ -14972,7 +14954,7 @@
         <v>752</v>
       </c>
       <c r="C729" t="s">
-        <v>1833</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="730" spans="1:3">
@@ -14983,7 +14965,7 @@
         <v>753</v>
       </c>
       <c r="C730" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="731" spans="1:3">
@@ -14994,7 +14976,7 @@
         <v>754</v>
       </c>
       <c r="C731" t="s">
-        <v>1835</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="732" spans="1:3">
@@ -15005,7 +14987,7 @@
         <v>755</v>
       </c>
       <c r="C732" t="s">
-        <v>1836</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="733" spans="1:3">
@@ -15016,7 +14998,7 @@
         <v>756</v>
       </c>
       <c r="C733" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="734" spans="1:3">
@@ -15027,7 +15009,7 @@
         <v>757</v>
       </c>
       <c r="C734" t="s">
-        <v>1838</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="735" spans="1:3">
@@ -15038,7 +15020,7 @@
         <v>758</v>
       </c>
       <c r="C735" t="s">
-        <v>1839</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="736" spans="1:3">
@@ -15049,7 +15031,7 @@
         <v>759</v>
       </c>
       <c r="C736" t="s">
-        <v>1840</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="737" spans="1:3">
@@ -15060,7 +15042,7 @@
         <v>760</v>
       </c>
       <c r="C737" t="s">
-        <v>1841</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="738" spans="1:3">
@@ -15071,29 +15053,29 @@
         <v>761</v>
       </c>
       <c r="C738" t="s">
-        <v>1842</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="739" spans="1:3">
       <c r="A739" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B739" t="s">
         <v>762</v>
       </c>
       <c r="C739" t="s">
-        <v>1843</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="740" spans="1:3">
       <c r="A740" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B740" t="s">
         <v>763</v>
       </c>
       <c r="C740" t="s">
-        <v>1844</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="741" spans="1:3">
@@ -15104,7 +15086,7 @@
         <v>764</v>
       </c>
       <c r="C741" t="s">
-        <v>1845</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="742" spans="1:3">
@@ -15115,7 +15097,7 @@
         <v>765</v>
       </c>
       <c r="C742" t="s">
-        <v>1846</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="743" spans="1:3">
@@ -15126,7 +15108,7 @@
         <v>766</v>
       </c>
       <c r="C743" t="s">
-        <v>1847</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="744" spans="1:3">
@@ -15137,7 +15119,7 @@
         <v>767</v>
       </c>
       <c r="C744" t="s">
-        <v>1848</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="745" spans="1:3">
@@ -15148,7 +15130,7 @@
         <v>768</v>
       </c>
       <c r="C745" t="s">
-        <v>1849</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="746" spans="1:3">
@@ -15159,7 +15141,7 @@
         <v>769</v>
       </c>
       <c r="C746" t="s">
-        <v>1850</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="747" spans="1:3">
@@ -15170,7 +15152,7 @@
         <v>770</v>
       </c>
       <c r="C747" t="s">
-        <v>1851</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="748" spans="1:3">
@@ -15181,7 +15163,7 @@
         <v>771</v>
       </c>
       <c r="C748" t="s">
-        <v>1852</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="749" spans="1:3">
@@ -15192,7 +15174,7 @@
         <v>772</v>
       </c>
       <c r="C749" t="s">
-        <v>1853</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="750" spans="1:3">
@@ -15203,7 +15185,7 @@
         <v>773</v>
       </c>
       <c r="C750" t="s">
-        <v>1854</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="751" spans="1:3">
@@ -15214,7 +15196,7 @@
         <v>774</v>
       </c>
       <c r="C751" t="s">
-        <v>1441</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="752" spans="1:3">
@@ -15225,18 +15207,18 @@
         <v>775</v>
       </c>
       <c r="C752" t="s">
-        <v>1855</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="753" spans="1:3">
       <c r="A753" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B753" t="s">
         <v>776</v>
       </c>
       <c r="C753" t="s">
-        <v>1856</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="754" spans="1:3">
@@ -15247,7 +15229,7 @@
         <v>777</v>
       </c>
       <c r="C754" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="755" spans="1:3">
@@ -15258,7 +15240,7 @@
         <v>778</v>
       </c>
       <c r="C755" t="s">
-        <v>1858</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="756" spans="1:3">
@@ -15269,7 +15251,7 @@
         <v>779</v>
       </c>
       <c r="C756" t="s">
-        <v>1859</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="757" spans="1:3">
@@ -15280,7 +15262,7 @@
         <v>780</v>
       </c>
       <c r="C757" t="s">
-        <v>1860</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="758" spans="1:3">
@@ -15291,7 +15273,7 @@
         <v>781</v>
       </c>
       <c r="C758" t="s">
-        <v>1861</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="759" spans="1:3">
@@ -15302,7 +15284,7 @@
         <v>782</v>
       </c>
       <c r="C759" t="s">
-        <v>1862</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="760" spans="1:3">
@@ -15313,7 +15295,7 @@
         <v>783</v>
       </c>
       <c r="C760" t="s">
-        <v>1863</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="761" spans="1:3">
@@ -15324,7 +15306,7 @@
         <v>784</v>
       </c>
       <c r="C761" t="s">
-        <v>1864</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="762" spans="1:3">
@@ -15335,7 +15317,7 @@
         <v>785</v>
       </c>
       <c r="C762" t="s">
-        <v>1865</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="763" spans="1:3">
@@ -15346,7 +15328,7 @@
         <v>786</v>
       </c>
       <c r="C763" t="s">
-        <v>1866</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="764" spans="1:3">
@@ -15357,7 +15339,7 @@
         <v>787</v>
       </c>
       <c r="C764" t="s">
-        <v>1867</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="765" spans="1:3">
@@ -15368,7 +15350,7 @@
         <v>788</v>
       </c>
       <c r="C765" t="s">
-        <v>1868</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="766" spans="1:3">
@@ -15379,7 +15361,7 @@
         <v>789</v>
       </c>
       <c r="C766" t="s">
-        <v>1869</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="767" spans="1:3">
@@ -15390,7 +15372,7 @@
         <v>790</v>
       </c>
       <c r="C767" t="s">
-        <v>1870</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="768" spans="1:3">
@@ -15401,7 +15383,7 @@
         <v>791</v>
       </c>
       <c r="C768" t="s">
-        <v>1871</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="769" spans="1:3">
@@ -15412,7 +15394,7 @@
         <v>792</v>
       </c>
       <c r="C769" t="s">
-        <v>1872</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="770" spans="1:3">
@@ -15423,7 +15405,7 @@
         <v>793</v>
       </c>
       <c r="C770" t="s">
-        <v>1873</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="771" spans="1:3">
@@ -15434,7 +15416,7 @@
         <v>794</v>
       </c>
       <c r="C771" t="s">
-        <v>1874</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="772" spans="1:3">
@@ -15445,7 +15427,7 @@
         <v>795</v>
       </c>
       <c r="C772" t="s">
-        <v>1875</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="773" spans="1:3">
@@ -15456,7 +15438,7 @@
         <v>796</v>
       </c>
       <c r="C773" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="774" spans="1:3">
@@ -15467,7 +15449,7 @@
         <v>797</v>
       </c>
       <c r="C774" t="s">
-        <v>1877</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="775" spans="1:3">
@@ -15478,7 +15460,7 @@
         <v>798</v>
       </c>
       <c r="C775" t="s">
-        <v>1878</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="776" spans="1:3">
@@ -15489,7 +15471,7 @@
         <v>799</v>
       </c>
       <c r="C776" t="s">
-        <v>1879</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="777" spans="1:3">
@@ -15500,7 +15482,7 @@
         <v>800</v>
       </c>
       <c r="C777" t="s">
-        <v>1880</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="778" spans="1:3">
@@ -15511,7 +15493,7 @@
         <v>801</v>
       </c>
       <c r="C778" t="s">
-        <v>1881</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="779" spans="1:3">
@@ -15522,7 +15504,7 @@
         <v>802</v>
       </c>
       <c r="C779" t="s">
-        <v>1882</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="780" spans="1:3">
@@ -15533,7 +15515,7 @@
         <v>803</v>
       </c>
       <c r="C780" t="s">
-        <v>1883</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="781" spans="1:3">
@@ -15544,7 +15526,7 @@
         <v>804</v>
       </c>
       <c r="C781" t="s">
-        <v>1884</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="782" spans="1:3">
@@ -15555,7 +15537,7 @@
         <v>805</v>
       </c>
       <c r="C782" t="s">
-        <v>1885</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="783" spans="1:3">
@@ -15566,7 +15548,7 @@
         <v>806</v>
       </c>
       <c r="C783" t="s">
-        <v>1886</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="784" spans="1:3">
@@ -15577,7 +15559,7 @@
         <v>807</v>
       </c>
       <c r="C784" t="s">
-        <v>1887</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="785" spans="1:3">
@@ -15588,7 +15570,7 @@
         <v>808</v>
       </c>
       <c r="C785" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="786" spans="1:3">
@@ -15599,7 +15581,7 @@
         <v>809</v>
       </c>
       <c r="C786" t="s">
-        <v>1889</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="787" spans="1:3">
@@ -15610,7 +15592,7 @@
         <v>810</v>
       </c>
       <c r="C787" t="s">
-        <v>1890</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="788" spans="1:3">
@@ -15621,7 +15603,7 @@
         <v>811</v>
       </c>
       <c r="C788" t="s">
-        <v>1891</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="789" spans="1:3">
@@ -15632,7 +15614,7 @@
         <v>812</v>
       </c>
       <c r="C789" t="s">
-        <v>1892</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="790" spans="1:3">
@@ -15643,7 +15625,7 @@
         <v>813</v>
       </c>
       <c r="C790" t="s">
-        <v>1893</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="791" spans="1:3">
@@ -15654,7 +15636,7 @@
         <v>814</v>
       </c>
       <c r="C791" t="s">
-        <v>1894</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="792" spans="1:3">
@@ -15665,7 +15647,7 @@
         <v>815</v>
       </c>
       <c r="C792" t="s">
-        <v>1895</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="793" spans="1:3">
@@ -15676,7 +15658,7 @@
         <v>816</v>
       </c>
       <c r="C793" t="s">
-        <v>1896</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="794" spans="1:3">
@@ -15687,7 +15669,7 @@
         <v>817</v>
       </c>
       <c r="C794" t="s">
-        <v>1897</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="795" spans="1:3">
@@ -15698,7 +15680,7 @@
         <v>818</v>
       </c>
       <c r="C795" t="s">
-        <v>1898</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="796" spans="1:3">
@@ -15709,7 +15691,7 @@
         <v>819</v>
       </c>
       <c r="C796" t="s">
-        <v>1899</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="797" spans="1:3">
@@ -15720,7 +15702,7 @@
         <v>820</v>
       </c>
       <c r="C797" t="s">
-        <v>1900</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="798" spans="1:3">
@@ -15731,7 +15713,7 @@
         <v>821</v>
       </c>
       <c r="C798" t="s">
-        <v>1901</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="799" spans="1:3">
@@ -15742,7 +15724,7 @@
         <v>822</v>
       </c>
       <c r="C799" t="s">
-        <v>1902</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="800" spans="1:3">
@@ -15753,7 +15735,7 @@
         <v>823</v>
       </c>
       <c r="C800" t="s">
-        <v>1903</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="801" spans="1:3">
@@ -15764,7 +15746,7 @@
         <v>824</v>
       </c>
       <c r="C801" t="s">
-        <v>1904</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="802" spans="1:3">
@@ -15775,7 +15757,7 @@
         <v>825</v>
       </c>
       <c r="C802" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="803" spans="1:3">
@@ -15786,7 +15768,7 @@
         <v>826</v>
       </c>
       <c r="C803" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="804" spans="1:3">
@@ -15797,7 +15779,7 @@
         <v>827</v>
       </c>
       <c r="C804" t="s">
-        <v>1907</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="805" spans="1:3">
@@ -15808,7 +15790,7 @@
         <v>828</v>
       </c>
       <c r="C805" t="s">
-        <v>1825</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="806" spans="1:3">
@@ -15819,7 +15801,7 @@
         <v>829</v>
       </c>
       <c r="C806" t="s">
-        <v>1908</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="807" spans="1:3">
@@ -15830,7 +15812,7 @@
         <v>830</v>
       </c>
       <c r="C807" t="s">
-        <v>1909</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="808" spans="1:3">
@@ -15841,7 +15823,7 @@
         <v>831</v>
       </c>
       <c r="C808" t="s">
-        <v>1910</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="809" spans="1:3">
@@ -15852,7 +15834,7 @@
         <v>832</v>
       </c>
       <c r="C809" t="s">
-        <v>1911</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="810" spans="1:3">
@@ -15863,7 +15845,7 @@
         <v>833</v>
       </c>
       <c r="C810" t="s">
-        <v>1912</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="811" spans="1:3">
@@ -15874,7 +15856,7 @@
         <v>834</v>
       </c>
       <c r="C811" t="s">
-        <v>1913</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="812" spans="1:3">
@@ -15885,7 +15867,7 @@
         <v>835</v>
       </c>
       <c r="C812" t="s">
-        <v>1914</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="813" spans="1:3">
@@ -15896,7 +15878,7 @@
         <v>836</v>
       </c>
       <c r="C813" t="s">
-        <v>1915</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="814" spans="1:3">
@@ -15907,7 +15889,7 @@
         <v>837</v>
       </c>
       <c r="C814" t="s">
-        <v>1916</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="815" spans="1:3">
@@ -15918,7 +15900,7 @@
         <v>838</v>
       </c>
       <c r="C815" t="s">
-        <v>1917</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="816" spans="1:3">
@@ -15929,7 +15911,7 @@
         <v>839</v>
       </c>
       <c r="C816" t="s">
-        <v>1918</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="817" spans="1:3">
@@ -15940,7 +15922,7 @@
         <v>840</v>
       </c>
       <c r="C817" t="s">
-        <v>1919</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="818" spans="1:3">
@@ -15951,7 +15933,7 @@
         <v>841</v>
       </c>
       <c r="C818" t="s">
-        <v>1920</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="819" spans="1:3">
@@ -15962,7 +15944,7 @@
         <v>842</v>
       </c>
       <c r="C819" t="s">
-        <v>1921</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="820" spans="1:3">
@@ -15973,7 +15955,7 @@
         <v>843</v>
       </c>
       <c r="C820" t="s">
-        <v>1922</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="821" spans="1:3">
@@ -15984,7 +15966,7 @@
         <v>844</v>
       </c>
       <c r="C821" t="s">
-        <v>1923</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="822" spans="1:3">
@@ -15995,7 +15977,7 @@
         <v>845</v>
       </c>
       <c r="C822" t="s">
-        <v>1924</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="823" spans="1:3">
@@ -16006,7 +15988,7 @@
         <v>846</v>
       </c>
       <c r="C823" t="s">
-        <v>1925</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="824" spans="1:3">
@@ -16017,7 +15999,7 @@
         <v>847</v>
       </c>
       <c r="C824" t="s">
-        <v>1926</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="825" spans="1:3">
@@ -16028,7 +16010,7 @@
         <v>848</v>
       </c>
       <c r="C825" t="s">
-        <v>1927</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="826" spans="1:3">
@@ -16039,7 +16021,7 @@
         <v>849</v>
       </c>
       <c r="C826" t="s">
-        <v>1928</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="827" spans="1:3">
@@ -16050,7 +16032,7 @@
         <v>850</v>
       </c>
       <c r="C827" t="s">
-        <v>1929</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="828" spans="1:3">
@@ -16061,7 +16043,7 @@
         <v>851</v>
       </c>
       <c r="C828" t="s">
-        <v>1930</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="829" spans="1:3">
@@ -16072,7 +16054,7 @@
         <v>852</v>
       </c>
       <c r="C829" t="s">
-        <v>1931</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="830" spans="1:3">
@@ -16083,7 +16065,7 @@
         <v>853</v>
       </c>
       <c r="C830" t="s">
-        <v>1932</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="831" spans="1:3">
@@ -16094,7 +16076,7 @@
         <v>854</v>
       </c>
       <c r="C831" t="s">
-        <v>1933</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="832" spans="1:3">
@@ -16105,7 +16087,7 @@
         <v>855</v>
       </c>
       <c r="C832" t="s">
-        <v>1934</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="833" spans="1:3">
@@ -16116,7 +16098,7 @@
         <v>856</v>
       </c>
       <c r="C833" t="s">
-        <v>1935</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="834" spans="1:3">
@@ -16127,7 +16109,7 @@
         <v>857</v>
       </c>
       <c r="C834" t="s">
-        <v>1936</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="835" spans="1:3">
@@ -16138,7 +16120,7 @@
         <v>858</v>
       </c>
       <c r="C835" t="s">
-        <v>1937</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="836" spans="1:3">
@@ -16149,7 +16131,7 @@
         <v>859</v>
       </c>
       <c r="C836" t="s">
-        <v>1938</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="837" spans="1:3">
@@ -16160,7 +16142,7 @@
         <v>860</v>
       </c>
       <c r="C837" t="s">
-        <v>1939</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="838" spans="1:3">
@@ -16171,7 +16153,7 @@
         <v>861</v>
       </c>
       <c r="C838" t="s">
-        <v>1940</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="839" spans="1:3">
@@ -16182,7 +16164,7 @@
         <v>862</v>
       </c>
       <c r="C839" t="s">
-        <v>1941</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="840" spans="1:3">
@@ -16193,7 +16175,7 @@
         <v>863</v>
       </c>
       <c r="C840" t="s">
-        <v>1942</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="841" spans="1:3">
@@ -16204,7 +16186,7 @@
         <v>864</v>
       </c>
       <c r="C841" t="s">
-        <v>1943</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="842" spans="1:3">
@@ -16215,7 +16197,7 @@
         <v>865</v>
       </c>
       <c r="C842" t="s">
-        <v>1944</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="843" spans="1:3">
@@ -16226,7 +16208,7 @@
         <v>866</v>
       </c>
       <c r="C843" t="s">
-        <v>1945</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="844" spans="1:3">
@@ -16237,7 +16219,7 @@
         <v>867</v>
       </c>
       <c r="C844" t="s">
-        <v>1946</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="845" spans="1:3">
@@ -16248,7 +16230,7 @@
         <v>868</v>
       </c>
       <c r="C845" t="s">
-        <v>1947</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="846" spans="1:3">
@@ -16259,7 +16241,7 @@
         <v>869</v>
       </c>
       <c r="C846" t="s">
-        <v>1948</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="847" spans="1:3">
@@ -16270,7 +16252,7 @@
         <v>870</v>
       </c>
       <c r="C847" t="s">
-        <v>1949</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="848" spans="1:3">
@@ -16281,7 +16263,7 @@
         <v>871</v>
       </c>
       <c r="C848" t="s">
-        <v>1950</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="849" spans="1:3">
@@ -16292,7 +16274,7 @@
         <v>872</v>
       </c>
       <c r="C849" t="s">
-        <v>1951</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="850" spans="1:3">
@@ -16303,7 +16285,7 @@
         <v>873</v>
       </c>
       <c r="C850" t="s">
-        <v>1952</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="851" spans="1:3">
@@ -16314,7 +16296,7 @@
         <v>874</v>
       </c>
       <c r="C851" t="s">
-        <v>1953</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="852" spans="1:3">
@@ -16325,7 +16307,7 @@
         <v>875</v>
       </c>
       <c r="C852" t="s">
-        <v>1954</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="853" spans="1:3">
@@ -16336,7 +16318,7 @@
         <v>876</v>
       </c>
       <c r="C853" t="s">
-        <v>1955</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="854" spans="1:3">
@@ -16347,7 +16329,7 @@
         <v>877</v>
       </c>
       <c r="C854" t="s">
-        <v>1956</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="855" spans="1:3">
@@ -16358,7 +16340,7 @@
         <v>878</v>
       </c>
       <c r="C855" t="s">
-        <v>1957</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="856" spans="1:3">
@@ -16369,7 +16351,7 @@
         <v>879</v>
       </c>
       <c r="C856" t="s">
-        <v>1958</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="857" spans="1:3">
@@ -16380,7 +16362,7 @@
         <v>880</v>
       </c>
       <c r="C857" t="s">
-        <v>1959</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="858" spans="1:3">
@@ -16391,7 +16373,7 @@
         <v>881</v>
       </c>
       <c r="C858" t="s">
-        <v>1960</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="859" spans="1:3">
@@ -16402,7 +16384,7 @@
         <v>882</v>
       </c>
       <c r="C859" t="s">
-        <v>1961</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="860" spans="1:3">
@@ -16413,7 +16395,7 @@
         <v>883</v>
       </c>
       <c r="C860" t="s">
-        <v>1962</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="861" spans="1:3">
@@ -16424,7 +16406,7 @@
         <v>884</v>
       </c>
       <c r="C861" t="s">
-        <v>1963</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="862" spans="1:3">
@@ -16435,7 +16417,7 @@
         <v>885</v>
       </c>
       <c r="C862" t="s">
-        <v>1964</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="863" spans="1:3">
@@ -16446,7 +16428,7 @@
         <v>886</v>
       </c>
       <c r="C863" t="s">
-        <v>1965</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="864" spans="1:3">
@@ -16457,7 +16439,7 @@
         <v>887</v>
       </c>
       <c r="C864" t="s">
-        <v>1966</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="865" spans="1:3">
@@ -16468,7 +16450,7 @@
         <v>888</v>
       </c>
       <c r="C865" t="s">
-        <v>1967</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="866" spans="1:3">
@@ -16479,7 +16461,7 @@
         <v>889</v>
       </c>
       <c r="C866" t="s">
-        <v>1968</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="867" spans="1:3">
@@ -16490,7 +16472,7 @@
         <v>890</v>
       </c>
       <c r="C867" t="s">
-        <v>1969</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="868" spans="1:3">
@@ -16501,7 +16483,7 @@
         <v>891</v>
       </c>
       <c r="C868" t="s">
-        <v>1970</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="869" spans="1:3">
@@ -16512,7 +16494,7 @@
         <v>892</v>
       </c>
       <c r="C869" t="s">
-        <v>1971</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="870" spans="1:3">
@@ -16523,7 +16505,7 @@
         <v>893</v>
       </c>
       <c r="C870" t="s">
-        <v>1972</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="871" spans="1:3">
@@ -16534,7 +16516,7 @@
         <v>894</v>
       </c>
       <c r="C871" t="s">
-        <v>1973</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="872" spans="1:3">
@@ -16545,7 +16527,7 @@
         <v>895</v>
       </c>
       <c r="C872" t="s">
-        <v>1974</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="873" spans="1:3">
@@ -16556,7 +16538,7 @@
         <v>896</v>
       </c>
       <c r="C873" t="s">
-        <v>1975</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="874" spans="1:3">
@@ -16567,7 +16549,7 @@
         <v>897</v>
       </c>
       <c r="C874" t="s">
-        <v>1976</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="875" spans="1:3">
@@ -16578,18 +16560,18 @@
         <v>898</v>
       </c>
       <c r="C875" t="s">
-        <v>1977</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="876" spans="1:3">
       <c r="A876" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B876" t="s">
         <v>899</v>
       </c>
       <c r="C876" t="s">
-        <v>1978</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="877" spans="1:3">
@@ -16600,7 +16582,7 @@
         <v>900</v>
       </c>
       <c r="C877" t="s">
-        <v>1979</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="878" spans="1:3">
@@ -16611,7 +16593,7 @@
         <v>901</v>
       </c>
       <c r="C878" t="s">
-        <v>1980</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="879" spans="1:3">
@@ -16622,7 +16604,7 @@
         <v>902</v>
       </c>
       <c r="C879" t="s">
-        <v>1981</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="880" spans="1:3">
@@ -16633,7 +16615,7 @@
         <v>903</v>
       </c>
       <c r="C880" t="s">
-        <v>1982</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="881" spans="1:3">
@@ -16644,7 +16626,7 @@
         <v>904</v>
       </c>
       <c r="C881" t="s">
-        <v>1983</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="882" spans="1:3">
@@ -16655,7 +16637,7 @@
         <v>905</v>
       </c>
       <c r="C882" t="s">
-        <v>1984</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="883" spans="1:3">
@@ -16666,7 +16648,7 @@
         <v>906</v>
       </c>
       <c r="C883" t="s">
-        <v>1985</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="884" spans="1:3">
@@ -16677,7 +16659,7 @@
         <v>907</v>
       </c>
       <c r="C884" t="s">
-        <v>1986</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="885" spans="1:3">
@@ -16688,7 +16670,7 @@
         <v>908</v>
       </c>
       <c r="C885" t="s">
-        <v>1987</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="886" spans="1:3">
@@ -16699,7 +16681,7 @@
         <v>909</v>
       </c>
       <c r="C886" t="s">
-        <v>1988</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="887" spans="1:3">
@@ -16710,7 +16692,7 @@
         <v>910</v>
       </c>
       <c r="C887" t="s">
-        <v>1989</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="888" spans="1:3">
@@ -16721,7 +16703,7 @@
         <v>911</v>
       </c>
       <c r="C888" t="s">
-        <v>1990</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="889" spans="1:3">
@@ -16732,7 +16714,7 @@
         <v>912</v>
       </c>
       <c r="C889" t="s">
-        <v>1991</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="890" spans="1:3">
@@ -16743,7 +16725,7 @@
         <v>913</v>
       </c>
       <c r="C890" t="s">
-        <v>1992</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="891" spans="1:3">
@@ -16754,7 +16736,7 @@
         <v>914</v>
       </c>
       <c r="C891" t="s">
-        <v>1993</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="892" spans="1:3">
@@ -16765,7 +16747,7 @@
         <v>915</v>
       </c>
       <c r="C892" t="s">
-        <v>1994</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="893" spans="1:3">
@@ -16776,7 +16758,7 @@
         <v>916</v>
       </c>
       <c r="C893" t="s">
-        <v>1995</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="894" spans="1:3">
@@ -16787,7 +16769,7 @@
         <v>917</v>
       </c>
       <c r="C894" t="s">
-        <v>1996</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="895" spans="1:3">
@@ -16798,7 +16780,7 @@
         <v>918</v>
       </c>
       <c r="C895" t="s">
-        <v>1997</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="896" spans="1:3">
@@ -16809,7 +16791,7 @@
         <v>919</v>
       </c>
       <c r="C896" t="s">
-        <v>1998</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="897" spans="1:3">
@@ -16820,7 +16802,7 @@
         <v>920</v>
       </c>
       <c r="C897" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="898" spans="1:3">
@@ -16831,7 +16813,7 @@
         <v>921</v>
       </c>
       <c r="C898" t="s">
-        <v>2000</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="899" spans="1:3">
@@ -16842,7 +16824,7 @@
         <v>922</v>
       </c>
       <c r="C899" t="s">
-        <v>2001</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="900" spans="1:3">
@@ -16853,7 +16835,7 @@
         <v>923</v>
       </c>
       <c r="C900" t="s">
-        <v>2002</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="901" spans="1:3">
@@ -16864,7 +16846,7 @@
         <v>924</v>
       </c>
       <c r="C901" t="s">
-        <v>2003</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="902" spans="1:3">
@@ -16875,7 +16857,7 @@
         <v>925</v>
       </c>
       <c r="C902" t="s">
-        <v>2004</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="903" spans="1:3">
@@ -16886,7 +16868,7 @@
         <v>926</v>
       </c>
       <c r="C903" t="s">
-        <v>2005</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="904" spans="1:3">
@@ -16897,7 +16879,7 @@
         <v>927</v>
       </c>
       <c r="C904" t="s">
-        <v>2006</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="905" spans="1:3">
@@ -16908,7 +16890,7 @@
         <v>928</v>
       </c>
       <c r="C905" t="s">
-        <v>2007</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="906" spans="1:3">
@@ -16919,7 +16901,7 @@
         <v>929</v>
       </c>
       <c r="C906" t="s">
-        <v>2008</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="907" spans="1:3">
@@ -16930,7 +16912,7 @@
         <v>930</v>
       </c>
       <c r="C907" t="s">
-        <v>2009</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="908" spans="1:3">
@@ -16941,7 +16923,7 @@
         <v>931</v>
       </c>
       <c r="C908" t="s">
-        <v>2010</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="909" spans="1:3">
@@ -16952,7 +16934,7 @@
         <v>932</v>
       </c>
       <c r="C909" t="s">
-        <v>2011</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="910" spans="1:3">
@@ -16963,7 +16945,7 @@
         <v>933</v>
       </c>
       <c r="C910" t="s">
-        <v>2012</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="911" spans="1:3">
@@ -16974,7 +16956,7 @@
         <v>934</v>
       </c>
       <c r="C911" t="s">
-        <v>2013</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="912" spans="1:3">
@@ -16985,7 +16967,7 @@
         <v>935</v>
       </c>
       <c r="C912" t="s">
-        <v>2014</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="913" spans="1:3">
@@ -16996,7 +16978,7 @@
         <v>936</v>
       </c>
       <c r="C913" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="914" spans="1:3">
@@ -17007,7 +16989,7 @@
         <v>937</v>
       </c>
       <c r="C914" t="s">
-        <v>2016</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="915" spans="1:3">
@@ -17018,7 +17000,7 @@
         <v>938</v>
       </c>
       <c r="C915" t="s">
-        <v>2017</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="916" spans="1:3">
@@ -17029,7 +17011,7 @@
         <v>939</v>
       </c>
       <c r="C916" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="917" spans="1:3">
@@ -17040,7 +17022,7 @@
         <v>940</v>
       </c>
       <c r="C917" t="s">
-        <v>2019</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="918" spans="1:3">
@@ -17051,7 +17033,7 @@
         <v>941</v>
       </c>
       <c r="C918" t="s">
-        <v>2020</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="919" spans="1:3">
@@ -17062,7 +17044,7 @@
         <v>942</v>
       </c>
       <c r="C919" t="s">
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="920" spans="1:3">
@@ -17073,7 +17055,7 @@
         <v>943</v>
       </c>
       <c r="C920" t="s">
-        <v>2022</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="921" spans="1:3">
@@ -17084,7 +17066,7 @@
         <v>944</v>
       </c>
       <c r="C921" t="s">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="922" spans="1:3">
@@ -17095,7 +17077,7 @@
         <v>945</v>
       </c>
       <c r="C922" t="s">
-        <v>2024</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="923" spans="1:3">
@@ -17106,7 +17088,7 @@
         <v>946</v>
       </c>
       <c r="C923" t="s">
-        <v>2025</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="924" spans="1:3">
@@ -17117,7 +17099,7 @@
         <v>947</v>
       </c>
       <c r="C924" t="s">
-        <v>2026</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="925" spans="1:3">
@@ -17128,7 +17110,7 @@
         <v>948</v>
       </c>
       <c r="C925" t="s">
-        <v>2027</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="926" spans="1:3">
@@ -17139,7 +17121,7 @@
         <v>949</v>
       </c>
       <c r="C926" t="s">
-        <v>2028</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="927" spans="1:3">
@@ -17150,7 +17132,7 @@
         <v>950</v>
       </c>
       <c r="C927" t="s">
-        <v>2029</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="928" spans="1:3">
@@ -17161,7 +17143,7 @@
         <v>951</v>
       </c>
       <c r="C928" t="s">
-        <v>2030</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="929" spans="1:3">
@@ -17172,7 +17154,7 @@
         <v>952</v>
       </c>
       <c r="C929" t="s">
-        <v>2031</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="930" spans="1:3">
@@ -17183,7 +17165,7 @@
         <v>953</v>
       </c>
       <c r="C930" t="s">
-        <v>2032</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="931" spans="1:3">
@@ -17194,7 +17176,7 @@
         <v>954</v>
       </c>
       <c r="C931" t="s">
-        <v>2033</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="932" spans="1:3">
@@ -17205,7 +17187,7 @@
         <v>955</v>
       </c>
       <c r="C932" t="s">
-        <v>2034</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="933" spans="1:3">
@@ -17216,7 +17198,7 @@
         <v>956</v>
       </c>
       <c r="C933" t="s">
-        <v>2035</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="934" spans="1:3">
@@ -17227,7 +17209,7 @@
         <v>957</v>
       </c>
       <c r="C934" t="s">
-        <v>2036</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="935" spans="1:3">
@@ -17238,7 +17220,7 @@
         <v>958</v>
       </c>
       <c r="C935" t="s">
-        <v>2037</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="936" spans="1:3">
@@ -17249,7 +17231,7 @@
         <v>959</v>
       </c>
       <c r="C936" t="s">
-        <v>2038</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="937" spans="1:3">
@@ -17260,7 +17242,7 @@
         <v>960</v>
       </c>
       <c r="C937" t="s">
-        <v>2039</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="938" spans="1:3">
@@ -17271,7 +17253,7 @@
         <v>961</v>
       </c>
       <c r="C938" t="s">
-        <v>2040</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="939" spans="1:3">
@@ -17282,7 +17264,7 @@
         <v>962</v>
       </c>
       <c r="C939" t="s">
-        <v>2041</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="940" spans="1:3">
@@ -17293,7 +17275,7 @@
         <v>963</v>
       </c>
       <c r="C940" t="s">
-        <v>2042</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="941" spans="1:3">
@@ -17304,7 +17286,7 @@
         <v>964</v>
       </c>
       <c r="C941" t="s">
-        <v>2043</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="942" spans="1:3">
@@ -17315,7 +17297,7 @@
         <v>965</v>
       </c>
       <c r="C942" t="s">
-        <v>2044</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="943" spans="1:3">
@@ -17326,7 +17308,7 @@
         <v>966</v>
       </c>
       <c r="C943" t="s">
-        <v>2045</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="944" spans="1:3">
@@ -17337,7 +17319,7 @@
         <v>967</v>
       </c>
       <c r="C944" t="s">
-        <v>2046</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="945" spans="1:3">
@@ -17348,7 +17330,7 @@
         <v>968</v>
       </c>
       <c r="C945" t="s">
-        <v>2047</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="946" spans="1:3">
@@ -17359,7 +17341,7 @@
         <v>969</v>
       </c>
       <c r="C946" t="s">
-        <v>2048</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="947" spans="1:3">
@@ -17370,7 +17352,7 @@
         <v>970</v>
       </c>
       <c r="C947" t="s">
-        <v>2049</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="948" spans="1:3">
@@ -17381,7 +17363,7 @@
         <v>971</v>
       </c>
       <c r="C948" t="s">
-        <v>2050</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="949" spans="1:3">
@@ -17392,7 +17374,7 @@
         <v>972</v>
       </c>
       <c r="C949" t="s">
-        <v>2051</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="950" spans="1:3">
@@ -17403,7 +17385,7 @@
         <v>973</v>
       </c>
       <c r="C950" t="s">
-        <v>2052</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="951" spans="1:3">
@@ -17414,7 +17396,7 @@
         <v>974</v>
       </c>
       <c r="C951" t="s">
-        <v>2053</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="952" spans="1:3">
@@ -17425,7 +17407,7 @@
         <v>975</v>
       </c>
       <c r="C952" t="s">
-        <v>2054</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="953" spans="1:3">
@@ -17436,7 +17418,7 @@
         <v>976</v>
       </c>
       <c r="C953" t="s">
-        <v>2055</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="954" spans="1:3">
@@ -17447,7 +17429,7 @@
         <v>977</v>
       </c>
       <c r="C954" t="s">
-        <v>2056</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="955" spans="1:3">
@@ -17458,7 +17440,7 @@
         <v>978</v>
       </c>
       <c r="C955" t="s">
-        <v>2057</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="956" spans="1:3">
@@ -17469,7 +17451,7 @@
         <v>979</v>
       </c>
       <c r="C956" t="s">
-        <v>2058</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="957" spans="1:3">
@@ -17480,7 +17462,7 @@
         <v>980</v>
       </c>
       <c r="C957" t="s">
-        <v>2059</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="958" spans="1:3">
@@ -17491,7 +17473,7 @@
         <v>981</v>
       </c>
       <c r="C958" t="s">
-        <v>2060</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="959" spans="1:3">
@@ -17502,7 +17484,7 @@
         <v>982</v>
       </c>
       <c r="C959" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="960" spans="1:3">
@@ -17513,7 +17495,7 @@
         <v>983</v>
       </c>
       <c r="C960" t="s">
-        <v>2062</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="961" spans="1:3">
@@ -17524,7 +17506,7 @@
         <v>984</v>
       </c>
       <c r="C961" t="s">
-        <v>2063</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="962" spans="1:3">
@@ -17535,7 +17517,7 @@
         <v>985</v>
       </c>
       <c r="C962" t="s">
-        <v>2064</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="963" spans="1:3">
@@ -17546,7 +17528,7 @@
         <v>986</v>
       </c>
       <c r="C963" t="s">
-        <v>2065</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="964" spans="1:3">
@@ -17557,7 +17539,7 @@
         <v>987</v>
       </c>
       <c r="C964" t="s">
-        <v>2066</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="965" spans="1:3">
@@ -17568,7 +17550,7 @@
         <v>988</v>
       </c>
       <c r="C965" t="s">
-        <v>2067</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="966" spans="1:3">
@@ -17579,7 +17561,7 @@
         <v>989</v>
       </c>
       <c r="C966" t="s">
-        <v>2068</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="967" spans="1:3">
@@ -17590,7 +17572,7 @@
         <v>990</v>
       </c>
       <c r="C967" t="s">
-        <v>2069</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="968" spans="1:3">
@@ -17601,7 +17583,7 @@
         <v>991</v>
       </c>
       <c r="C968" t="s">
-        <v>2070</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="969" spans="1:3">
@@ -17612,7 +17594,7 @@
         <v>992</v>
       </c>
       <c r="C969" t="s">
-        <v>2071</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="970" spans="1:3">
@@ -17623,7 +17605,7 @@
         <v>993</v>
       </c>
       <c r="C970" t="s">
-        <v>2072</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="971" spans="1:3">
@@ -17634,7 +17616,7 @@
         <v>994</v>
       </c>
       <c r="C971" t="s">
-        <v>2073</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="972" spans="1:3">
@@ -17645,7 +17627,7 @@
         <v>995</v>
       </c>
       <c r="C972" t="s">
-        <v>2074</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="973" spans="1:3">
@@ -17656,7 +17638,7 @@
         <v>996</v>
       </c>
       <c r="C973" t="s">
-        <v>2075</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="974" spans="1:3">
@@ -17667,7 +17649,7 @@
         <v>997</v>
       </c>
       <c r="C974" t="s">
-        <v>2076</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="975" spans="1:3">
@@ -17678,7 +17660,7 @@
         <v>998</v>
       </c>
       <c r="C975" t="s">
-        <v>2077</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="976" spans="1:3">
@@ -17689,7 +17671,7 @@
         <v>999</v>
       </c>
       <c r="C976" t="s">
-        <v>2078</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="977" spans="1:3">
@@ -17700,7 +17682,7 @@
         <v>1000</v>
       </c>
       <c r="C977" t="s">
-        <v>2079</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="978" spans="1:3">
@@ -17711,7 +17693,7 @@
         <v>1001</v>
       </c>
       <c r="C978" t="s">
-        <v>2080</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="979" spans="1:3">
@@ -17722,7 +17704,7 @@
         <v>1002</v>
       </c>
       <c r="C979" t="s">
-        <v>2081</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="980" spans="1:3">
@@ -17733,7 +17715,7 @@
         <v>1003</v>
       </c>
       <c r="C980" t="s">
-        <v>2082</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="981" spans="1:3">
@@ -17744,7 +17726,7 @@
         <v>1004</v>
       </c>
       <c r="C981" t="s">
-        <v>2083</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="982" spans="1:3">
@@ -17755,7 +17737,7 @@
         <v>1005</v>
       </c>
       <c r="C982" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="983" spans="1:3">
@@ -17766,7 +17748,7 @@
         <v>1006</v>
       </c>
       <c r="C983" t="s">
-        <v>2085</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="984" spans="1:3">
@@ -17777,7 +17759,7 @@
         <v>1007</v>
       </c>
       <c r="C984" t="s">
-        <v>2086</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="985" spans="1:3">
@@ -17788,7 +17770,7 @@
         <v>1008</v>
       </c>
       <c r="C985" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="986" spans="1:3">
@@ -17799,7 +17781,7 @@
         <v>1009</v>
       </c>
       <c r="C986" t="s">
-        <v>2088</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="987" spans="1:3">
@@ -17810,18 +17792,18 @@
         <v>1010</v>
       </c>
       <c r="C987" t="s">
-        <v>2089</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="988" spans="1:3">
       <c r="A988" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B988" t="s">
         <v>1011</v>
       </c>
       <c r="C988" t="s">
-        <v>2090</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="989" spans="1:3">
@@ -17832,7 +17814,7 @@
         <v>1012</v>
       </c>
       <c r="C989" t="s">
-        <v>2091</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="990" spans="1:3">
@@ -17843,7 +17825,7 @@
         <v>1013</v>
       </c>
       <c r="C990" t="s">
-        <v>2092</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="991" spans="1:3">
@@ -17854,7 +17836,7 @@
         <v>1014</v>
       </c>
       <c r="C991" t="s">
-        <v>2093</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="992" spans="1:3">
@@ -17865,7 +17847,7 @@
         <v>1015</v>
       </c>
       <c r="C992" t="s">
-        <v>2094</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="993" spans="1:3">
@@ -17876,7 +17858,7 @@
         <v>1016</v>
       </c>
       <c r="C993" t="s">
-        <v>2095</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="994" spans="1:3">
@@ -17887,7 +17869,7 @@
         <v>1017</v>
       </c>
       <c r="C994" t="s">
-        <v>2096</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="995" spans="1:3">
@@ -17898,7 +17880,7 @@
         <v>1018</v>
       </c>
       <c r="C995" t="s">
-        <v>2097</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="996" spans="1:3">
@@ -17909,7 +17891,7 @@
         <v>1019</v>
       </c>
       <c r="C996" t="s">
-        <v>2098</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="997" spans="1:3">
@@ -17920,7 +17902,7 @@
         <v>1020</v>
       </c>
       <c r="C997" t="s">
-        <v>2099</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="998" spans="1:3">
@@ -17931,7 +17913,7 @@
         <v>1021</v>
       </c>
       <c r="C998" t="s">
-        <v>2100</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="999" spans="1:3">
@@ -17942,7 +17924,7 @@
         <v>1022</v>
       </c>
       <c r="C999" t="s">
-        <v>2101</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="1000" spans="1:3">
@@ -17953,7 +17935,7 @@
         <v>1023</v>
       </c>
       <c r="C1000" t="s">
-        <v>2102</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="1001" spans="1:3">
@@ -17964,7 +17946,7 @@
         <v>1024</v>
       </c>
       <c r="C1001" t="s">
-        <v>2103</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="1002" spans="1:3">
@@ -17975,7 +17957,7 @@
         <v>1025</v>
       </c>
       <c r="C1002" t="s">
-        <v>2104</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="1003" spans="1:3">
@@ -17986,7 +17968,7 @@
         <v>1026</v>
       </c>
       <c r="C1003" t="s">
-        <v>2105</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="1004" spans="1:3">
@@ -17997,7 +17979,7 @@
         <v>1027</v>
       </c>
       <c r="C1004" t="s">
-        <v>2106</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="1005" spans="1:3">
@@ -18008,7 +17990,7 @@
         <v>1028</v>
       </c>
       <c r="C1005" t="s">
-        <v>2107</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="1006" spans="1:3">
@@ -18019,7 +18001,7 @@
         <v>1029</v>
       </c>
       <c r="C1006" t="s">
-        <v>2108</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="1007" spans="1:3">
@@ -18030,7 +18012,7 @@
         <v>1030</v>
       </c>
       <c r="C1007" t="s">
-        <v>2109</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="1008" spans="1:3">
@@ -18041,7 +18023,7 @@
         <v>1031</v>
       </c>
       <c r="C1008" t="s">
-        <v>2110</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="1009" spans="1:3">
@@ -18052,7 +18034,7 @@
         <v>1032</v>
       </c>
       <c r="C1009" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="1010" spans="1:3">
@@ -18063,7 +18045,7 @@
         <v>1033</v>
       </c>
       <c r="C1010" t="s">
-        <v>2112</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="1011" spans="1:3">
@@ -18074,7 +18056,7 @@
         <v>1034</v>
       </c>
       <c r="C1011" t="s">
-        <v>2113</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="1012" spans="1:3">
@@ -18085,7 +18067,7 @@
         <v>1035</v>
       </c>
       <c r="C1012" t="s">
-        <v>2114</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="1013" spans="1:3">
@@ -18096,7 +18078,7 @@
         <v>1036</v>
       </c>
       <c r="C1013" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="1014" spans="1:3">
@@ -18107,7 +18089,7 @@
         <v>1037</v>
       </c>
       <c r="C1014" t="s">
-        <v>2116</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="1015" spans="1:3">
@@ -18118,7 +18100,7 @@
         <v>1038</v>
       </c>
       <c r="C1015" t="s">
-        <v>2117</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="1016" spans="1:3">
@@ -18129,7 +18111,7 @@
         <v>1039</v>
       </c>
       <c r="C1016" t="s">
-        <v>2118</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="1017" spans="1:3">
@@ -18140,7 +18122,7 @@
         <v>1040</v>
       </c>
       <c r="C1017" t="s">
-        <v>2119</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="1018" spans="1:3">
@@ -18151,7 +18133,7 @@
         <v>1041</v>
       </c>
       <c r="C1018" t="s">
-        <v>2120</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="1019" spans="1:3">
@@ -18162,7 +18144,7 @@
         <v>1042</v>
       </c>
       <c r="C1019" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="1020" spans="1:3">
@@ -18173,7 +18155,7 @@
         <v>1043</v>
       </c>
       <c r="C1020" t="s">
-        <v>2122</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="1021" spans="1:3">
@@ -18184,7 +18166,7 @@
         <v>1044</v>
       </c>
       <c r="C1021" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="1022" spans="1:3">
@@ -18195,7 +18177,7 @@
         <v>1045</v>
       </c>
       <c r="C1022" t="s">
-        <v>2124</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="1023" spans="1:3">
@@ -18206,7 +18188,7 @@
         <v>1046</v>
       </c>
       <c r="C1023" t="s">
-        <v>2125</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="1024" spans="1:3">
@@ -18217,7 +18199,7 @@
         <v>1047</v>
       </c>
       <c r="C1024" t="s">
-        <v>2126</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="1025" spans="1:3">
@@ -18228,7 +18210,7 @@
         <v>1048</v>
       </c>
       <c r="C1025" t="s">
-        <v>2127</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="1026" spans="1:3">
@@ -18239,7 +18221,7 @@
         <v>1049</v>
       </c>
       <c r="C1026" t="s">
-        <v>2128</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="1027" spans="1:3">
@@ -18250,7 +18232,7 @@
         <v>1050</v>
       </c>
       <c r="C1027" t="s">
-        <v>2129</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="1028" spans="1:3">
@@ -18261,7 +18243,7 @@
         <v>1051</v>
       </c>
       <c r="C1028" t="s">
-        <v>2130</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="1029" spans="1:3">
@@ -18272,7 +18254,7 @@
         <v>1052</v>
       </c>
       <c r="C1029" t="s">
-        <v>2131</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="1030" spans="1:3">
@@ -18283,7 +18265,7 @@
         <v>1053</v>
       </c>
       <c r="C1030" t="s">
-        <v>2132</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="1031" spans="1:3">
@@ -18294,7 +18276,7 @@
         <v>1054</v>
       </c>
       <c r="C1031" t="s">
-        <v>2125</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="1032" spans="1:3">
@@ -18305,7 +18287,7 @@
         <v>1055</v>
       </c>
       <c r="C1032" t="s">
-        <v>2133</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="1033" spans="1:3">
@@ -18316,7 +18298,7 @@
         <v>1056</v>
       </c>
       <c r="C1033" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="1034" spans="1:3">
@@ -18327,7 +18309,7 @@
         <v>1057</v>
       </c>
       <c r="C1034" t="s">
-        <v>2135</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="1035" spans="1:3">
@@ -18338,7 +18320,7 @@
         <v>1058</v>
       </c>
       <c r="C1035" t="s">
-        <v>2136</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="1036" spans="1:3">
@@ -18349,7 +18331,7 @@
         <v>1059</v>
       </c>
       <c r="C1036" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="1037" spans="1:3">
@@ -18360,7 +18342,7 @@
         <v>1060</v>
       </c>
       <c r="C1037" t="s">
-        <v>2138</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="1038" spans="1:3">
@@ -18371,7 +18353,7 @@
         <v>1061</v>
       </c>
       <c r="C1038" t="s">
-        <v>2139</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="1039" spans="1:3">
@@ -18382,7 +18364,7 @@
         <v>1062</v>
       </c>
       <c r="C1039" t="s">
-        <v>2140</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="1040" spans="1:3">
@@ -18393,7 +18375,7 @@
         <v>1063</v>
       </c>
       <c r="C1040" t="s">
-        <v>2141</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="1041" spans="1:3">
@@ -18404,7 +18386,7 @@
         <v>1064</v>
       </c>
       <c r="C1041" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="1042" spans="1:3">
@@ -18415,7 +18397,7 @@
         <v>1065</v>
       </c>
       <c r="C1042" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="1043" spans="1:3">
@@ -18426,7 +18408,7 @@
         <v>1066</v>
       </c>
       <c r="C1043" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="1044" spans="1:3">
@@ -18437,7 +18419,7 @@
         <v>1067</v>
       </c>
       <c r="C1044" t="s">
-        <v>2145</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="1045" spans="1:3">
@@ -18448,7 +18430,7 @@
         <v>1068</v>
       </c>
       <c r="C1045" t="s">
-        <v>2146</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="1046" spans="1:3">
@@ -18459,7 +18441,7 @@
         <v>1069</v>
       </c>
       <c r="C1046" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1047" spans="1:3">
@@ -18470,7 +18452,7 @@
         <v>1070</v>
       </c>
       <c r="C1047" t="s">
-        <v>2148</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="1048" spans="1:3">
@@ -18481,7 +18463,7 @@
         <v>1071</v>
       </c>
       <c r="C1048" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="1049" spans="1:3">
@@ -18492,7 +18474,7 @@
         <v>1072</v>
       </c>
       <c r="C1049" t="s">
-        <v>2150</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="1050" spans="1:3">
@@ -18503,7 +18485,7 @@
         <v>1073</v>
       </c>
       <c r="C1050" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="1051" spans="1:3">
@@ -18514,7 +18496,7 @@
         <v>1074</v>
       </c>
       <c r="C1051" t="s">
-        <v>2152</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1052" spans="1:3">
@@ -18525,7 +18507,7 @@
         <v>1075</v>
       </c>
       <c r="C1052" t="s">
-        <v>2153</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="1053" spans="1:3">
@@ -18536,7 +18518,7 @@
         <v>1076</v>
       </c>
       <c r="C1053" t="s">
-        <v>2154</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="1054" spans="1:3">
@@ -18547,7 +18529,7 @@
         <v>1077</v>
       </c>
       <c r="C1054" t="s">
-        <v>2155</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="1055" spans="1:3">
@@ -18558,7 +18540,7 @@
         <v>1078</v>
       </c>
       <c r="C1055" t="s">
-        <v>2126</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="1056" spans="1:3">
@@ -18569,7 +18551,7 @@
         <v>1079</v>
       </c>
       <c r="C1056" t="s">
-        <v>2156</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="1057" spans="1:3">
@@ -18580,7 +18562,7 @@
         <v>1080</v>
       </c>
       <c r="C1057" t="s">
-        <v>2157</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="1058" spans="1:3">
@@ -18591,7 +18573,7 @@
         <v>1081</v>
       </c>
       <c r="C1058" t="s">
-        <v>2158</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="1059" spans="1:3">
@@ -18602,7 +18584,7 @@
         <v>1082</v>
       </c>
       <c r="C1059" t="s">
-        <v>2106</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="1060" spans="1:3">
@@ -18613,7 +18595,7 @@
         <v>1083</v>
       </c>
       <c r="C1060" t="s">
-        <v>2159</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="1061" spans="1:3">
@@ -18624,7 +18606,7 @@
         <v>1084</v>
       </c>
       <c r="C1061" t="s">
-        <v>2160</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="1062" spans="1:3">
@@ -18635,7 +18617,7 @@
         <v>1085</v>
       </c>
       <c r="C1062" t="s">
-        <v>2161</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="1063" spans="1:3">
@@ -18646,40 +18628,40 @@
         <v>1086</v>
       </c>
       <c r="C1063" t="s">
-        <v>2162</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="1064" spans="1:3">
       <c r="A1064" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1064" t="s">
         <v>1087</v>
       </c>
       <c r="C1064" t="s">
-        <v>2163</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="1065" spans="1:3">
       <c r="A1065" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1065" t="s">
         <v>1088</v>
       </c>
       <c r="C1065" t="s">
-        <v>2164</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="1066" spans="1:3">
       <c r="A1066" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1066" t="s">
         <v>1089</v>
       </c>
       <c r="C1066" t="s">
-        <v>2165</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="1067" spans="1:3">
@@ -18690,7 +18672,7 @@
         <v>1090</v>
       </c>
       <c r="C1067" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1068" spans="1:3">
@@ -18701,7 +18683,7 @@
         <v>1091</v>
       </c>
       <c r="C1068" t="s">
-        <v>2167</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="1069" spans="1:3">
@@ -18712,7 +18694,7 @@
         <v>1092</v>
       </c>
       <c r="C1069" t="s">
-        <v>2168</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="1070" spans="1:3">
@@ -18723,7 +18705,7 @@
         <v>1093</v>
       </c>
       <c r="C1070" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="1071" spans="1:3">
@@ -18734,7 +18716,7 @@
         <v>1094</v>
       </c>
       <c r="C1071" t="s">
-        <v>2170</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="1072" spans="1:3">
@@ -18745,7 +18727,7 @@
         <v>1095</v>
       </c>
       <c r="C1072" t="s">
-        <v>2171</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1073" spans="1:3">
@@ -18756,7 +18738,7 @@
         <v>1096</v>
       </c>
       <c r="C1073" t="s">
-        <v>2172</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="1074" spans="1:3">
@@ -18767,7 +18749,7 @@
         <v>1097</v>
       </c>
       <c r="C1074" t="s">
-        <v>2173</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="1075" spans="1:3">
@@ -18778,7 +18760,7 @@
         <v>1098</v>
       </c>
       <c r="C1075" t="s">
-        <v>2174</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="1076" spans="1:3">
@@ -18789,7 +18771,7 @@
         <v>1099</v>
       </c>
       <c r="C1076" t="s">
-        <v>2175</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="1077" spans="1:3">
@@ -18800,7 +18782,7 @@
         <v>1100</v>
       </c>
       <c r="C1077" t="s">
-        <v>2176</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="1078" spans="1:3">
@@ -18811,7 +18793,7 @@
         <v>1101</v>
       </c>
       <c r="C1078" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="1079" spans="1:3">
@@ -18822,7 +18804,7 @@
         <v>1102</v>
       </c>
       <c r="C1079" t="s">
-        <v>2178</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="1080" spans="1:3">
@@ -18833,7 +18815,7 @@
         <v>1103</v>
       </c>
       <c r="C1080" t="s">
-        <v>2179</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="1081" spans="1:3">
@@ -18844,7 +18826,7 @@
         <v>1104</v>
       </c>
       <c r="C1081" t="s">
-        <v>2180</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="1082" spans="1:3">
@@ -18855,7 +18837,7 @@
         <v>1105</v>
       </c>
       <c r="C1082" t="s">
-        <v>2181</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="1083" spans="1:3">
@@ -18866,7 +18848,7 @@
         <v>1106</v>
       </c>
       <c r="C1083" t="s">
-        <v>2182</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="1084" spans="1:3">
@@ -18877,7 +18859,7 @@
         <v>1107</v>
       </c>
       <c r="C1084" t="s">
-        <v>2183</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="1085" spans="1:3">
@@ -18888,7 +18870,7 @@
         <v>1108</v>
       </c>
       <c r="C1085" t="s">
-        <v>2184</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="1086" spans="1:3">
@@ -18899,7 +18881,7 @@
         <v>1109</v>
       </c>
       <c r="C1086" t="s">
-        <v>2185</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="1087" spans="1:3">
@@ -18910,7 +18892,7 @@
         <v>1110</v>
       </c>
       <c r="C1087" t="s">
-        <v>2186</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="1088" spans="1:3">
@@ -18921,7 +18903,7 @@
         <v>1111</v>
       </c>
       <c r="C1088" t="s">
-        <v>2187</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="1089" spans="1:3">
@@ -18932,7 +18914,7 @@
         <v>1112</v>
       </c>
       <c r="C1089" t="s">
-        <v>2188</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="1090" spans="1:3">
@@ -18943,51 +18925,18 @@
         <v>1113</v>
       </c>
       <c r="C1090" t="s">
-        <v>2189</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="1091" spans="1:3">
       <c r="A1091" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1091" t="s">
         <v>1114</v>
       </c>
       <c r="C1091" t="s">
-        <v>2190</v>
-      </c>
-    </row>
-    <row r="1092" spans="1:3">
-      <c r="A1092" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1092" t="s">
-        <v>1115</v>
-      </c>
-      <c r="C1092" t="s">
-        <v>2191</v>
-      </c>
-    </row>
-    <row r="1093" spans="1:3">
-      <c r="A1093" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1093" t="s">
-        <v>1116</v>
-      </c>
-      <c r="C1093" t="s">
-        <v>2192</v>
-      </c>
-    </row>
-    <row r="1094" spans="1:3">
-      <c r="A1094" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1094" t="s">
-        <v>1117</v>
-      </c>
-      <c r="C1094" t="s">
-        <v>2193</v>
+        <v>2187</v>
       </c>
     </row>
   </sheetData>

--- a/faltantes_por_estados.xlsx
+++ b/faltantes_por_estados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3273" uniqueCount="2188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3264" uniqueCount="2182">
   <si>
     <t>entidad</t>
   </si>
@@ -2047,9 +2047,6 @@
     <t>NTIMB001601</t>
   </si>
   <si>
-    <t>NTIMB001625</t>
-  </si>
-  <si>
     <t>NTIMB001782</t>
   </si>
   <si>
@@ -3175,9 +3172,6 @@
     <t>TSIMB002013</t>
   </si>
   <si>
-    <t>TSIMB002025</t>
-  </si>
-  <si>
     <t>TSIMB002030</t>
   </si>
   <si>
@@ -3187,9 +3181,6 @@
     <t>TSIMB002054</t>
   </si>
   <si>
-    <t>TSIMB002100</t>
-  </si>
-  <si>
     <t>TSIMB002124</t>
   </si>
   <si>
@@ -5284,9 +5275,6 @@
     <t>LA CRUZ DE HUANACAXTLE</t>
   </si>
   <si>
-    <t>HIGUERA BLANCA</t>
-  </si>
-  <si>
     <t>SAN MIGUEL</t>
   </si>
   <si>
@@ -6400,9 +6388,6 @@
     <t>CENTRO DE SALUD COL. ESTUDIANTIL</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD COL. EMILIO PORTES GIL</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD COL. ENRIQUE CÁRDENAS GONZÁLEZ</t>
   </si>
   <si>
@@ -6410,9 +6395,6 @@
   </si>
   <si>
     <t>CENTRO DE SALUD LA LIBERTAD</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD FLECHADORES</t>
   </si>
   <si>
     <t>CENTRO DE SALUD COL. NUEVA ERA</t>
@@ -6935,7 +6917,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1091"/>
+  <dimension ref="A1:C1088"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6957,7 +6939,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6968,7 +6950,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6979,7 +6961,7 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6990,7 +6972,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7001,7 +6983,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7012,7 +6994,7 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7023,7 +7005,7 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7034,7 +7016,7 @@
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7045,7 +7027,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7056,7 +7038,7 @@
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -7067,7 +7049,7 @@
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -7078,7 +7060,7 @@
         <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -7089,7 +7071,7 @@
         <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -7100,7 +7082,7 @@
         <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7111,7 +7093,7 @@
         <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -7133,7 +7115,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -7144,7 +7126,7 @@
         <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -7155,7 +7137,7 @@
         <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -7166,7 +7148,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -7177,7 +7159,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -7188,7 +7170,7 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -7199,7 +7181,7 @@
         <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -7210,7 +7192,7 @@
         <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -7221,7 +7203,7 @@
         <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -7243,7 +7225,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -7265,7 +7247,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -7276,7 +7258,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -7287,7 +7269,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -7298,7 +7280,7 @@
         <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -7309,7 +7291,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -7320,7 +7302,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -7331,7 +7313,7 @@
         <v>59</v>
       </c>
       <c r="C36" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -7342,7 +7324,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -7353,7 +7335,7 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -7364,7 +7346,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -7375,7 +7357,7 @@
         <v>63</v>
       </c>
       <c r="C40" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -7386,7 +7368,7 @@
         <v>64</v>
       </c>
       <c r="C41" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -7397,7 +7379,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -7408,7 +7390,7 @@
         <v>66</v>
       </c>
       <c r="C43" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -7419,7 +7401,7 @@
         <v>67</v>
       </c>
       <c r="C44" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -7430,7 +7412,7 @@
         <v>68</v>
       </c>
       <c r="C45" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -7441,7 +7423,7 @@
         <v>69</v>
       </c>
       <c r="C46" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -7452,7 +7434,7 @@
         <v>70</v>
       </c>
       <c r="C47" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -7463,7 +7445,7 @@
         <v>71</v>
       </c>
       <c r="C48" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -7474,7 +7456,7 @@
         <v>72</v>
       </c>
       <c r="C49" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -7485,7 +7467,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -7496,7 +7478,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -7507,7 +7489,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -7518,7 +7500,7 @@
         <v>76</v>
       </c>
       <c r="C53" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -7529,7 +7511,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -7540,7 +7522,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -7551,7 +7533,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -7562,7 +7544,7 @@
         <v>80</v>
       </c>
       <c r="C57" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -7573,7 +7555,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -7584,7 +7566,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -7606,7 +7588,7 @@
         <v>84</v>
       </c>
       <c r="C61" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -7617,7 +7599,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -7628,7 +7610,7 @@
         <v>86</v>
       </c>
       <c r="C63" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -7639,7 +7621,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -7650,7 +7632,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -7661,7 +7643,7 @@
         <v>89</v>
       </c>
       <c r="C66" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -7672,7 +7654,7 @@
         <v>90</v>
       </c>
       <c r="C67" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -7683,7 +7665,7 @@
         <v>91</v>
       </c>
       <c r="C68" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -7694,7 +7676,7 @@
         <v>92</v>
       </c>
       <c r="C69" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -7705,7 +7687,7 @@
         <v>93</v>
       </c>
       <c r="C70" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -7716,7 +7698,7 @@
         <v>94</v>
       </c>
       <c r="C71" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -7727,7 +7709,7 @@
         <v>95</v>
       </c>
       <c r="C72" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -7738,7 +7720,7 @@
         <v>96</v>
       </c>
       <c r="C73" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -7749,7 +7731,7 @@
         <v>97</v>
       </c>
       <c r="C74" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -7760,7 +7742,7 @@
         <v>98</v>
       </c>
       <c r="C75" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -7771,7 +7753,7 @@
         <v>99</v>
       </c>
       <c r="C76" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -7782,7 +7764,7 @@
         <v>100</v>
       </c>
       <c r="C77" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -7793,7 +7775,7 @@
         <v>101</v>
       </c>
       <c r="C78" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -7804,7 +7786,7 @@
         <v>102</v>
       </c>
       <c r="C79" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -7815,7 +7797,7 @@
         <v>103</v>
       </c>
       <c r="C80" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -7826,7 +7808,7 @@
         <v>104</v>
       </c>
       <c r="C81" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -7837,7 +7819,7 @@
         <v>105</v>
       </c>
       <c r="C82" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -7848,7 +7830,7 @@
         <v>106</v>
       </c>
       <c r="C83" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -7859,7 +7841,7 @@
         <v>107</v>
       </c>
       <c r="C84" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -7870,7 +7852,7 @@
         <v>108</v>
       </c>
       <c r="C85" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -7881,7 +7863,7 @@
         <v>109</v>
       </c>
       <c r="C86" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -7892,7 +7874,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -7903,7 +7885,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -7914,7 +7896,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -7925,7 +7907,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -7936,7 +7918,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -7947,7 +7929,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -7958,7 +7940,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -7969,7 +7951,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -7980,7 +7962,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -7991,7 +7973,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -8002,7 +7984,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -8013,7 +7995,7 @@
         <v>121</v>
       </c>
       <c r="C98" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -8024,7 +8006,7 @@
         <v>122</v>
       </c>
       <c r="C99" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -8035,7 +8017,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -8046,7 +8028,7 @@
         <v>124</v>
       </c>
       <c r="C101" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -8057,7 +8039,7 @@
         <v>125</v>
       </c>
       <c r="C102" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -8068,7 +8050,7 @@
         <v>126</v>
       </c>
       <c r="C103" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -8079,7 +8061,7 @@
         <v>127</v>
       </c>
       <c r="C104" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -8090,7 +8072,7 @@
         <v>128</v>
       </c>
       <c r="C105" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -8101,7 +8083,7 @@
         <v>129</v>
       </c>
       <c r="C106" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -8112,7 +8094,7 @@
         <v>130</v>
       </c>
       <c r="C107" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -8123,7 +8105,7 @@
         <v>131</v>
       </c>
       <c r="C108" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -8134,7 +8116,7 @@
         <v>132</v>
       </c>
       <c r="C109" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -8145,7 +8127,7 @@
         <v>133</v>
       </c>
       <c r="C110" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -8156,7 +8138,7 @@
         <v>134</v>
       </c>
       <c r="C111" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -8167,7 +8149,7 @@
         <v>135</v>
       </c>
       <c r="C112" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -8178,7 +8160,7 @@
         <v>136</v>
       </c>
       <c r="C113" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -8189,7 +8171,7 @@
         <v>137</v>
       </c>
       <c r="C114" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -8200,7 +8182,7 @@
         <v>138</v>
       </c>
       <c r="C115" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -8211,7 +8193,7 @@
         <v>139</v>
       </c>
       <c r="C116" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -8222,7 +8204,7 @@
         <v>140</v>
       </c>
       <c r="C117" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -8233,7 +8215,7 @@
         <v>141</v>
       </c>
       <c r="C118" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -8244,7 +8226,7 @@
         <v>142</v>
       </c>
       <c r="C119" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -8255,7 +8237,7 @@
         <v>143</v>
       </c>
       <c r="C120" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -8266,7 +8248,7 @@
         <v>144</v>
       </c>
       <c r="C121" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -8277,7 +8259,7 @@
         <v>145</v>
       </c>
       <c r="C122" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -8288,7 +8270,7 @@
         <v>146</v>
       </c>
       <c r="C123" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -8299,7 +8281,7 @@
         <v>147</v>
       </c>
       <c r="C124" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -8310,7 +8292,7 @@
         <v>148</v>
       </c>
       <c r="C125" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -8321,7 +8303,7 @@
         <v>149</v>
       </c>
       <c r="C126" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -8332,7 +8314,7 @@
         <v>150</v>
       </c>
       <c r="C127" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -8343,7 +8325,7 @@
         <v>151</v>
       </c>
       <c r="C128" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -8354,7 +8336,7 @@
         <v>152</v>
       </c>
       <c r="C129" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -8365,7 +8347,7 @@
         <v>153</v>
       </c>
       <c r="C130" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -8376,7 +8358,7 @@
         <v>154</v>
       </c>
       <c r="C131" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -8387,7 +8369,7 @@
         <v>155</v>
       </c>
       <c r="C132" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -8398,7 +8380,7 @@
         <v>156</v>
       </c>
       <c r="C133" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -8409,7 +8391,7 @@
         <v>157</v>
       </c>
       <c r="C134" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -8420,7 +8402,7 @@
         <v>158</v>
       </c>
       <c r="C135" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -8431,7 +8413,7 @@
         <v>159</v>
       </c>
       <c r="C136" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -8442,7 +8424,7 @@
         <v>160</v>
       </c>
       <c r="C137" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -8453,7 +8435,7 @@
         <v>161</v>
       </c>
       <c r="C138" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -8464,7 +8446,7 @@
         <v>162</v>
       </c>
       <c r="C139" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -8475,7 +8457,7 @@
         <v>163</v>
       </c>
       <c r="C140" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -8486,7 +8468,7 @@
         <v>164</v>
       </c>
       <c r="C141" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -8497,7 +8479,7 @@
         <v>165</v>
       </c>
       <c r="C142" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -8508,7 +8490,7 @@
         <v>166</v>
       </c>
       <c r="C143" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -8519,7 +8501,7 @@
         <v>167</v>
       </c>
       <c r="C144" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -8530,7 +8512,7 @@
         <v>168</v>
       </c>
       <c r="C145" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -8541,7 +8523,7 @@
         <v>169</v>
       </c>
       <c r="C146" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -8552,7 +8534,7 @@
         <v>170</v>
       </c>
       <c r="C147" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -8563,7 +8545,7 @@
         <v>171</v>
       </c>
       <c r="C148" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -8574,7 +8556,7 @@
         <v>172</v>
       </c>
       <c r="C149" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -8585,7 +8567,7 @@
         <v>173</v>
       </c>
       <c r="C150" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -8596,7 +8578,7 @@
         <v>174</v>
       </c>
       <c r="C151" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -8607,7 +8589,7 @@
         <v>175</v>
       </c>
       <c r="C152" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -8618,7 +8600,7 @@
         <v>176</v>
       </c>
       <c r="C153" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -8629,7 +8611,7 @@
         <v>177</v>
       </c>
       <c r="C154" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -8640,7 +8622,7 @@
         <v>178</v>
       </c>
       <c r="C155" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -8651,7 +8633,7 @@
         <v>179</v>
       </c>
       <c r="C156" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -8662,7 +8644,7 @@
         <v>180</v>
       </c>
       <c r="C157" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -8673,7 +8655,7 @@
         <v>181</v>
       </c>
       <c r="C158" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -8684,7 +8666,7 @@
         <v>182</v>
       </c>
       <c r="C159" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -8695,7 +8677,7 @@
         <v>183</v>
       </c>
       <c r="C160" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -8706,7 +8688,7 @@
         <v>184</v>
       </c>
       <c r="C161" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -8717,7 +8699,7 @@
         <v>185</v>
       </c>
       <c r="C162" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -8728,7 +8710,7 @@
         <v>186</v>
       </c>
       <c r="C163" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -8739,7 +8721,7 @@
         <v>187</v>
       </c>
       <c r="C164" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -8750,7 +8732,7 @@
         <v>188</v>
       </c>
       <c r="C165" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -8761,7 +8743,7 @@
         <v>189</v>
       </c>
       <c r="C166" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -8772,7 +8754,7 @@
         <v>190</v>
       </c>
       <c r="C167" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -8783,7 +8765,7 @@
         <v>191</v>
       </c>
       <c r="C168" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -8794,7 +8776,7 @@
         <v>192</v>
       </c>
       <c r="C169" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -8805,7 +8787,7 @@
         <v>193</v>
       </c>
       <c r="C170" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -8816,7 +8798,7 @@
         <v>194</v>
       </c>
       <c r="C171" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -8827,7 +8809,7 @@
         <v>195</v>
       </c>
       <c r="C172" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -8838,7 +8820,7 @@
         <v>196</v>
       </c>
       <c r="C173" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -8849,7 +8831,7 @@
         <v>197</v>
       </c>
       <c r="C174" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -8860,7 +8842,7 @@
         <v>198</v>
       </c>
       <c r="C175" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -8871,7 +8853,7 @@
         <v>199</v>
       </c>
       <c r="C176" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -8882,7 +8864,7 @@
         <v>200</v>
       </c>
       <c r="C177" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -8893,7 +8875,7 @@
         <v>201</v>
       </c>
       <c r="C178" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -8904,7 +8886,7 @@
         <v>202</v>
       </c>
       <c r="C179" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -8915,7 +8897,7 @@
         <v>203</v>
       </c>
       <c r="C180" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -8926,7 +8908,7 @@
         <v>204</v>
       </c>
       <c r="C181" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -8937,7 +8919,7 @@
         <v>205</v>
       </c>
       <c r="C182" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -8948,7 +8930,7 @@
         <v>206</v>
       </c>
       <c r="C183" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -8959,7 +8941,7 @@
         <v>207</v>
       </c>
       <c r="C184" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -8970,7 +8952,7 @@
         <v>208</v>
       </c>
       <c r="C185" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -8981,7 +8963,7 @@
         <v>209</v>
       </c>
       <c r="C186" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -8992,7 +8974,7 @@
         <v>210</v>
       </c>
       <c r="C187" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -9003,7 +8985,7 @@
         <v>211</v>
       </c>
       <c r="C188" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -9014,7 +8996,7 @@
         <v>212</v>
       </c>
       <c r="C189" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -9025,7 +9007,7 @@
         <v>213</v>
       </c>
       <c r="C190" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -9036,7 +9018,7 @@
         <v>214</v>
       </c>
       <c r="C191" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -9047,7 +9029,7 @@
         <v>215</v>
       </c>
       <c r="C192" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -9058,7 +9040,7 @@
         <v>216</v>
       </c>
       <c r="C193" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -9069,7 +9051,7 @@
         <v>217</v>
       </c>
       <c r="C194" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -9080,7 +9062,7 @@
         <v>218</v>
       </c>
       <c r="C195" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -9091,7 +9073,7 @@
         <v>219</v>
       </c>
       <c r="C196" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -9102,7 +9084,7 @@
         <v>220</v>
       </c>
       <c r="C197" t="s">
-        <v>1305</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -9113,7 +9095,7 @@
         <v>221</v>
       </c>
       <c r="C198" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -9124,7 +9106,7 @@
         <v>222</v>
       </c>
       <c r="C199" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -9135,7 +9117,7 @@
         <v>223</v>
       </c>
       <c r="C200" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -9146,7 +9128,7 @@
         <v>224</v>
       </c>
       <c r="C201" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -9157,7 +9139,7 @@
         <v>225</v>
       </c>
       <c r="C202" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -9168,7 +9150,7 @@
         <v>226</v>
       </c>
       <c r="C203" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -9179,7 +9161,7 @@
         <v>227</v>
       </c>
       <c r="C204" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -9190,7 +9172,7 @@
         <v>228</v>
       </c>
       <c r="C205" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -9201,7 +9183,7 @@
         <v>229</v>
       </c>
       <c r="C206" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -9212,7 +9194,7 @@
         <v>230</v>
       </c>
       <c r="C207" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -9223,7 +9205,7 @@
         <v>231</v>
       </c>
       <c r="C208" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -9234,7 +9216,7 @@
         <v>232</v>
       </c>
       <c r="C209" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -9245,7 +9227,7 @@
         <v>233</v>
       </c>
       <c r="C210" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -9256,7 +9238,7 @@
         <v>234</v>
       </c>
       <c r="C211" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -9267,7 +9249,7 @@
         <v>235</v>
       </c>
       <c r="C212" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -9278,7 +9260,7 @@
         <v>236</v>
       </c>
       <c r="C213" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -9289,7 +9271,7 @@
         <v>237</v>
       </c>
       <c r="C214" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -9300,7 +9282,7 @@
         <v>238</v>
       </c>
       <c r="C215" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -9311,7 +9293,7 @@
         <v>239</v>
       </c>
       <c r="C216" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -9322,7 +9304,7 @@
         <v>240</v>
       </c>
       <c r="C217" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -9333,7 +9315,7 @@
         <v>241</v>
       </c>
       <c r="C218" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -9344,7 +9326,7 @@
         <v>242</v>
       </c>
       <c r="C219" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -9355,7 +9337,7 @@
         <v>243</v>
       </c>
       <c r="C220" t="s">
-        <v>1328</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -9366,7 +9348,7 @@
         <v>244</v>
       </c>
       <c r="C221" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -9377,7 +9359,7 @@
         <v>245</v>
       </c>
       <c r="C222" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -9388,7 +9370,7 @@
         <v>246</v>
       </c>
       <c r="C223" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -9399,7 +9381,7 @@
         <v>247</v>
       </c>
       <c r="C224" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -9410,7 +9392,7 @@
         <v>248</v>
       </c>
       <c r="C225" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -9421,7 +9403,7 @@
         <v>249</v>
       </c>
       <c r="C226" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -9432,7 +9414,7 @@
         <v>250</v>
       </c>
       <c r="C227" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -9443,7 +9425,7 @@
         <v>251</v>
       </c>
       <c r="C228" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -9454,7 +9436,7 @@
         <v>252</v>
       </c>
       <c r="C229" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -9465,7 +9447,7 @@
         <v>253</v>
       </c>
       <c r="C230" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -9476,7 +9458,7 @@
         <v>254</v>
       </c>
       <c r="C231" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -9487,7 +9469,7 @@
         <v>255</v>
       </c>
       <c r="C232" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -9498,7 +9480,7 @@
         <v>256</v>
       </c>
       <c r="C233" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -9509,7 +9491,7 @@
         <v>257</v>
       </c>
       <c r="C234" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -9520,7 +9502,7 @@
         <v>258</v>
       </c>
       <c r="C235" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -9531,7 +9513,7 @@
         <v>259</v>
       </c>
       <c r="C236" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -9542,7 +9524,7 @@
         <v>260</v>
       </c>
       <c r="C237" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -9553,7 +9535,7 @@
         <v>261</v>
       </c>
       <c r="C238" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -9564,7 +9546,7 @@
         <v>262</v>
       </c>
       <c r="C239" t="s">
-        <v>1347</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -9575,7 +9557,7 @@
         <v>263</v>
       </c>
       <c r="C240" t="s">
-        <v>1348</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -9586,7 +9568,7 @@
         <v>264</v>
       </c>
       <c r="C241" t="s">
-        <v>1349</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -9597,7 +9579,7 @@
         <v>265</v>
       </c>
       <c r="C242" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -9608,7 +9590,7 @@
         <v>266</v>
       </c>
       <c r="C243" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -9619,7 +9601,7 @@
         <v>267</v>
       </c>
       <c r="C244" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -9630,7 +9612,7 @@
         <v>268</v>
       </c>
       <c r="C245" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -9641,7 +9623,7 @@
         <v>269</v>
       </c>
       <c r="C246" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -9652,7 +9634,7 @@
         <v>270</v>
       </c>
       <c r="C247" t="s">
-        <v>1355</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -9663,7 +9645,7 @@
         <v>271</v>
       </c>
       <c r="C248" t="s">
-        <v>1356</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -9674,7 +9656,7 @@
         <v>272</v>
       </c>
       <c r="C249" t="s">
-        <v>1357</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -9685,7 +9667,7 @@
         <v>273</v>
       </c>
       <c r="C250" t="s">
-        <v>1358</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -9696,7 +9678,7 @@
         <v>274</v>
       </c>
       <c r="C251" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -9707,7 +9689,7 @@
         <v>275</v>
       </c>
       <c r="C252" t="s">
-        <v>1360</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -9718,7 +9700,7 @@
         <v>276</v>
       </c>
       <c r="C253" t="s">
-        <v>1361</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -9729,7 +9711,7 @@
         <v>277</v>
       </c>
       <c r="C254" t="s">
-        <v>1362</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -9740,7 +9722,7 @@
         <v>278</v>
       </c>
       <c r="C255" t="s">
-        <v>1363</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -9751,7 +9733,7 @@
         <v>279</v>
       </c>
       <c r="C256" t="s">
-        <v>1364</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -9762,7 +9744,7 @@
         <v>280</v>
       </c>
       <c r="C257" t="s">
-        <v>1365</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -9773,7 +9755,7 @@
         <v>281</v>
       </c>
       <c r="C258" t="s">
-        <v>1366</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="259" spans="1:3">
@@ -9784,7 +9766,7 @@
         <v>282</v>
       </c>
       <c r="C259" t="s">
-        <v>1367</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -9795,7 +9777,7 @@
         <v>283</v>
       </c>
       <c r="C260" t="s">
-        <v>1368</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="261" spans="1:3">
@@ -9806,7 +9788,7 @@
         <v>284</v>
       </c>
       <c r="C261" t="s">
-        <v>1369</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="262" spans="1:3">
@@ -9817,7 +9799,7 @@
         <v>285</v>
       </c>
       <c r="C262" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -9828,7 +9810,7 @@
         <v>286</v>
       </c>
       <c r="C263" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="264" spans="1:3">
@@ -9839,7 +9821,7 @@
         <v>287</v>
       </c>
       <c r="C264" t="s">
-        <v>1372</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -9850,7 +9832,7 @@
         <v>288</v>
       </c>
       <c r="C265" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="266" spans="1:3">
@@ -9861,7 +9843,7 @@
         <v>289</v>
       </c>
       <c r="C266" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="267" spans="1:3">
@@ -9872,7 +9854,7 @@
         <v>290</v>
       </c>
       <c r="C267" t="s">
-        <v>1375</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="268" spans="1:3">
@@ -9883,7 +9865,7 @@
         <v>291</v>
       </c>
       <c r="C268" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="269" spans="1:3">
@@ -9894,7 +9876,7 @@
         <v>292</v>
       </c>
       <c r="C269" t="s">
-        <v>1377</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="270" spans="1:3">
@@ -9905,7 +9887,7 @@
         <v>293</v>
       </c>
       <c r="C270" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="271" spans="1:3">
@@ -9916,7 +9898,7 @@
         <v>294</v>
       </c>
       <c r="C271" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="272" spans="1:3">
@@ -9927,7 +9909,7 @@
         <v>295</v>
       </c>
       <c r="C272" t="s">
-        <v>1380</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="273" spans="1:3">
@@ -9938,7 +9920,7 @@
         <v>296</v>
       </c>
       <c r="C273" t="s">
-        <v>1381</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="274" spans="1:3">
@@ -9949,7 +9931,7 @@
         <v>297</v>
       </c>
       <c r="C274" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="275" spans="1:3">
@@ -9960,7 +9942,7 @@
         <v>298</v>
       </c>
       <c r="C275" t="s">
-        <v>1383</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="276" spans="1:3">
@@ -9971,7 +9953,7 @@
         <v>299</v>
       </c>
       <c r="C276" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="277" spans="1:3">
@@ -9982,7 +9964,7 @@
         <v>300</v>
       </c>
       <c r="C277" t="s">
-        <v>1385</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="278" spans="1:3">
@@ -9993,7 +9975,7 @@
         <v>301</v>
       </c>
       <c r="C278" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="279" spans="1:3">
@@ -10004,7 +9986,7 @@
         <v>302</v>
       </c>
       <c r="C279" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="280" spans="1:3">
@@ -10015,7 +9997,7 @@
         <v>303</v>
       </c>
       <c r="C280" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -10026,7 +10008,7 @@
         <v>304</v>
       </c>
       <c r="C281" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="282" spans="1:3">
@@ -10037,7 +10019,7 @@
         <v>305</v>
       </c>
       <c r="C282" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="283" spans="1:3">
@@ -10048,7 +10030,7 @@
         <v>306</v>
       </c>
       <c r="C283" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="284" spans="1:3">
@@ -10059,7 +10041,7 @@
         <v>307</v>
       </c>
       <c r="C284" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="285" spans="1:3">
@@ -10070,7 +10052,7 @@
         <v>308</v>
       </c>
       <c r="C285" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="286" spans="1:3">
@@ -10081,7 +10063,7 @@
         <v>309</v>
       </c>
       <c r="C286" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="287" spans="1:3">
@@ -10092,7 +10074,7 @@
         <v>310</v>
       </c>
       <c r="C287" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="288" spans="1:3">
@@ -10103,7 +10085,7 @@
         <v>311</v>
       </c>
       <c r="C288" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="289" spans="1:3">
@@ -10114,7 +10096,7 @@
         <v>312</v>
       </c>
       <c r="C289" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="290" spans="1:3">
@@ -10125,7 +10107,7 @@
         <v>313</v>
       </c>
       <c r="C290" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="291" spans="1:3">
@@ -10136,7 +10118,7 @@
         <v>314</v>
       </c>
       <c r="C291" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="292" spans="1:3">
@@ -10147,7 +10129,7 @@
         <v>315</v>
       </c>
       <c r="C292" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="293" spans="1:3">
@@ -10158,7 +10140,7 @@
         <v>316</v>
       </c>
       <c r="C293" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="294" spans="1:3">
@@ -10169,7 +10151,7 @@
         <v>317</v>
       </c>
       <c r="C294" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="295" spans="1:3">
@@ -10180,7 +10162,7 @@
         <v>318</v>
       </c>
       <c r="C295" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="296" spans="1:3">
@@ -10191,7 +10173,7 @@
         <v>319</v>
       </c>
       <c r="C296" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="297" spans="1:3">
@@ -10202,7 +10184,7 @@
         <v>320</v>
       </c>
       <c r="C297" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="298" spans="1:3">
@@ -10213,7 +10195,7 @@
         <v>321</v>
       </c>
       <c r="C298" t="s">
-        <v>1405</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="299" spans="1:3">
@@ -10224,7 +10206,7 @@
         <v>322</v>
       </c>
       <c r="C299" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="300" spans="1:3">
@@ -10235,7 +10217,7 @@
         <v>323</v>
       </c>
       <c r="C300" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="301" spans="1:3">
@@ -10246,7 +10228,7 @@
         <v>324</v>
       </c>
       <c r="C301" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -10257,7 +10239,7 @@
         <v>325</v>
       </c>
       <c r="C302" t="s">
-        <v>1409</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="303" spans="1:3">
@@ -10268,7 +10250,7 @@
         <v>326</v>
       </c>
       <c r="C303" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="304" spans="1:3">
@@ -10279,7 +10261,7 @@
         <v>327</v>
       </c>
       <c r="C304" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -10290,7 +10272,7 @@
         <v>328</v>
       </c>
       <c r="C305" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="306" spans="1:3">
@@ -10301,7 +10283,7 @@
         <v>329</v>
       </c>
       <c r="C306" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="307" spans="1:3">
@@ -10312,7 +10294,7 @@
         <v>330</v>
       </c>
       <c r="C307" t="s">
-        <v>1414</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="308" spans="1:3">
@@ -10323,7 +10305,7 @@
         <v>331</v>
       </c>
       <c r="C308" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="309" spans="1:3">
@@ -10334,7 +10316,7 @@
         <v>332</v>
       </c>
       <c r="C309" t="s">
-        <v>1416</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="310" spans="1:3">
@@ -10345,7 +10327,7 @@
         <v>333</v>
       </c>
       <c r="C310" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="311" spans="1:3">
@@ -10356,7 +10338,7 @@
         <v>334</v>
       </c>
       <c r="C311" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="312" spans="1:3">
@@ -10367,7 +10349,7 @@
         <v>335</v>
       </c>
       <c r="C312" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="313" spans="1:3">
@@ -10378,7 +10360,7 @@
         <v>336</v>
       </c>
       <c r="C313" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="314" spans="1:3">
@@ -10389,7 +10371,7 @@
         <v>337</v>
       </c>
       <c r="C314" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="315" spans="1:3">
@@ -10400,7 +10382,7 @@
         <v>338</v>
       </c>
       <c r="C315" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="316" spans="1:3">
@@ -10411,7 +10393,7 @@
         <v>339</v>
       </c>
       <c r="C316" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="317" spans="1:3">
@@ -10422,7 +10404,7 @@
         <v>340</v>
       </c>
       <c r="C317" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="318" spans="1:3">
@@ -10433,7 +10415,7 @@
         <v>341</v>
       </c>
       <c r="C318" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="319" spans="1:3">
@@ -10444,7 +10426,7 @@
         <v>342</v>
       </c>
       <c r="C319" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="320" spans="1:3">
@@ -10455,7 +10437,7 @@
         <v>343</v>
       </c>
       <c r="C320" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="321" spans="1:3">
@@ -10466,7 +10448,7 @@
         <v>344</v>
       </c>
       <c r="C321" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -10477,7 +10459,7 @@
         <v>345</v>
       </c>
       <c r="C322" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="323" spans="1:3">
@@ -10488,7 +10470,7 @@
         <v>346</v>
       </c>
       <c r="C323" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="324" spans="1:3">
@@ -10499,7 +10481,7 @@
         <v>347</v>
       </c>
       <c r="C324" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -10510,7 +10492,7 @@
         <v>348</v>
       </c>
       <c r="C325" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="326" spans="1:3">
@@ -10521,7 +10503,7 @@
         <v>349</v>
       </c>
       <c r="C326" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="327" spans="1:3">
@@ -10532,7 +10514,7 @@
         <v>350</v>
       </c>
       <c r="C327" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="328" spans="1:3">
@@ -10543,7 +10525,7 @@
         <v>351</v>
       </c>
       <c r="C328" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="329" spans="1:3">
@@ -10554,7 +10536,7 @@
         <v>352</v>
       </c>
       <c r="C329" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="330" spans="1:3">
@@ -10565,7 +10547,7 @@
         <v>353</v>
       </c>
       <c r="C330" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -10576,7 +10558,7 @@
         <v>354</v>
       </c>
       <c r="C331" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="332" spans="1:3">
@@ -10587,7 +10569,7 @@
         <v>355</v>
       </c>
       <c r="C332" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="333" spans="1:3">
@@ -10598,7 +10580,7 @@
         <v>356</v>
       </c>
       <c r="C333" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="334" spans="1:3">
@@ -10609,7 +10591,7 @@
         <v>357</v>
       </c>
       <c r="C334" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="335" spans="1:3">
@@ -10620,7 +10602,7 @@
         <v>358</v>
       </c>
       <c r="C335" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="336" spans="1:3">
@@ -10631,7 +10613,7 @@
         <v>359</v>
       </c>
       <c r="C336" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="337" spans="1:3">
@@ -10642,7 +10624,7 @@
         <v>360</v>
       </c>
       <c r="C337" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="338" spans="1:3">
@@ -10653,7 +10635,7 @@
         <v>361</v>
       </c>
       <c r="C338" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="339" spans="1:3">
@@ -10664,7 +10646,7 @@
         <v>362</v>
       </c>
       <c r="C339" t="s">
-        <v>1445</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="340" spans="1:3">
@@ -10675,7 +10657,7 @@
         <v>363</v>
       </c>
       <c r="C340" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="341" spans="1:3">
@@ -10686,7 +10668,7 @@
         <v>364</v>
       </c>
       <c r="C341" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -10697,7 +10679,7 @@
         <v>365</v>
       </c>
       <c r="C342" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="343" spans="1:3">
@@ -10708,7 +10690,7 @@
         <v>366</v>
       </c>
       <c r="C343" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="344" spans="1:3">
@@ -10719,7 +10701,7 @@
         <v>367</v>
       </c>
       <c r="C344" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="345" spans="1:3">
@@ -10730,7 +10712,7 @@
         <v>368</v>
       </c>
       <c r="C345" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="346" spans="1:3">
@@ -10741,7 +10723,7 @@
         <v>369</v>
       </c>
       <c r="C346" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="347" spans="1:3">
@@ -10752,7 +10734,7 @@
         <v>370</v>
       </c>
       <c r="C347" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="348" spans="1:3">
@@ -10763,7 +10745,7 @@
         <v>371</v>
       </c>
       <c r="C348" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="349" spans="1:3">
@@ -10774,7 +10756,7 @@
         <v>372</v>
       </c>
       <c r="C349" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -10785,7 +10767,7 @@
         <v>373</v>
       </c>
       <c r="C350" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="351" spans="1:3">
@@ -10796,7 +10778,7 @@
         <v>374</v>
       </c>
       <c r="C351" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -10807,7 +10789,7 @@
         <v>375</v>
       </c>
       <c r="C352" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="353" spans="1:3">
@@ -10818,7 +10800,7 @@
         <v>376</v>
       </c>
       <c r="C353" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="354" spans="1:3">
@@ -10829,7 +10811,7 @@
         <v>377</v>
       </c>
       <c r="C354" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -10840,7 +10822,7 @@
         <v>378</v>
       </c>
       <c r="C355" t="s">
-        <v>1460</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="356" spans="1:3">
@@ -10851,7 +10833,7 @@
         <v>379</v>
       </c>
       <c r="C356" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="357" spans="1:3">
@@ -10862,7 +10844,7 @@
         <v>380</v>
       </c>
       <c r="C357" t="s">
-        <v>1462</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="358" spans="1:3">
@@ -10873,7 +10855,7 @@
         <v>381</v>
       </c>
       <c r="C358" t="s">
-        <v>1463</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="359" spans="1:3">
@@ -10884,7 +10866,7 @@
         <v>382</v>
       </c>
       <c r="C359" t="s">
-        <v>1464</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -10895,7 +10877,7 @@
         <v>383</v>
       </c>
       <c r="C360" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="361" spans="1:3">
@@ -10906,7 +10888,7 @@
         <v>384</v>
       </c>
       <c r="C361" t="s">
-        <v>1466</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="362" spans="1:3">
@@ -10917,7 +10899,7 @@
         <v>385</v>
       </c>
       <c r="C362" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="363" spans="1:3">
@@ -10928,7 +10910,7 @@
         <v>386</v>
       </c>
       <c r="C363" t="s">
-        <v>1468</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="364" spans="1:3">
@@ -10939,7 +10921,7 @@
         <v>387</v>
       </c>
       <c r="C364" t="s">
-        <v>1469</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="365" spans="1:3">
@@ -10950,7 +10932,7 @@
         <v>388</v>
       </c>
       <c r="C365" t="s">
-        <v>1470</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="366" spans="1:3">
@@ -10961,7 +10943,7 @@
         <v>389</v>
       </c>
       <c r="C366" t="s">
-        <v>1471</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="367" spans="1:3">
@@ -10972,7 +10954,7 @@
         <v>390</v>
       </c>
       <c r="C367" t="s">
-        <v>1472</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="368" spans="1:3">
@@ -10983,7 +10965,7 @@
         <v>391</v>
       </c>
       <c r="C368" t="s">
-        <v>1473</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="369" spans="1:3">
@@ -10994,7 +10976,7 @@
         <v>392</v>
       </c>
       <c r="C369" t="s">
-        <v>1474</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="370" spans="1:3">
@@ -11005,7 +10987,7 @@
         <v>393</v>
       </c>
       <c r="C370" t="s">
-        <v>1475</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="371" spans="1:3">
@@ -11016,7 +10998,7 @@
         <v>394</v>
       </c>
       <c r="C371" t="s">
-        <v>1476</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -11027,7 +11009,7 @@
         <v>395</v>
       </c>
       <c r="C372" t="s">
-        <v>1477</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="373" spans="1:3">
@@ -11038,7 +11020,7 @@
         <v>396</v>
       </c>
       <c r="C373" t="s">
-        <v>1478</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="374" spans="1:3">
@@ -11049,7 +11031,7 @@
         <v>397</v>
       </c>
       <c r="C374" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="375" spans="1:3">
@@ -11060,7 +11042,7 @@
         <v>398</v>
       </c>
       <c r="C375" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="376" spans="1:3">
@@ -11071,7 +11053,7 @@
         <v>399</v>
       </c>
       <c r="C376" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="377" spans="1:3">
@@ -11082,7 +11064,7 @@
         <v>400</v>
       </c>
       <c r="C377" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="378" spans="1:3">
@@ -11093,7 +11075,7 @@
         <v>401</v>
       </c>
       <c r="C378" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="379" spans="1:3">
@@ -11104,7 +11086,7 @@
         <v>402</v>
       </c>
       <c r="C379" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="380" spans="1:3">
@@ -11115,7 +11097,7 @@
         <v>403</v>
       </c>
       <c r="C380" t="s">
-        <v>1485</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="381" spans="1:3">
@@ -11126,7 +11108,7 @@
         <v>404</v>
       </c>
       <c r="C381" t="s">
-        <v>1486</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="382" spans="1:3">
@@ -11137,7 +11119,7 @@
         <v>405</v>
       </c>
       <c r="C382" t="s">
-        <v>1487</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="383" spans="1:3">
@@ -11148,7 +11130,7 @@
         <v>406</v>
       </c>
       <c r="C383" t="s">
-        <v>1488</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="384" spans="1:3">
@@ -11159,7 +11141,7 @@
         <v>407</v>
       </c>
       <c r="C384" t="s">
-        <v>1489</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="385" spans="1:3">
@@ -11170,7 +11152,7 @@
         <v>408</v>
       </c>
       <c r="C385" t="s">
-        <v>1490</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="386" spans="1:3">
@@ -11181,7 +11163,7 @@
         <v>409</v>
       </c>
       <c r="C386" t="s">
-        <v>1491</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="387" spans="1:3">
@@ -11192,7 +11174,7 @@
         <v>410</v>
       </c>
       <c r="C387" t="s">
-        <v>1492</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="388" spans="1:3">
@@ -11203,7 +11185,7 @@
         <v>411</v>
       </c>
       <c r="C388" t="s">
-        <v>1493</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="389" spans="1:3">
@@ -11214,7 +11196,7 @@
         <v>412</v>
       </c>
       <c r="C389" t="s">
-        <v>1494</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="390" spans="1:3">
@@ -11225,7 +11207,7 @@
         <v>413</v>
       </c>
       <c r="C390" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="391" spans="1:3">
@@ -11236,7 +11218,7 @@
         <v>414</v>
       </c>
       <c r="C391" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="392" spans="1:3">
@@ -11247,7 +11229,7 @@
         <v>415</v>
       </c>
       <c r="C392" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="393" spans="1:3">
@@ -11258,7 +11240,7 @@
         <v>416</v>
       </c>
       <c r="C393" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="394" spans="1:3">
@@ -11269,7 +11251,7 @@
         <v>417</v>
       </c>
       <c r="C394" t="s">
-        <v>1499</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="395" spans="1:3">
@@ -11280,7 +11262,7 @@
         <v>418</v>
       </c>
       <c r="C395" t="s">
-        <v>1500</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="396" spans="1:3">
@@ -11291,7 +11273,7 @@
         <v>419</v>
       </c>
       <c r="C396" t="s">
-        <v>1501</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="397" spans="1:3">
@@ -11302,7 +11284,7 @@
         <v>420</v>
       </c>
       <c r="C397" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="398" spans="1:3">
@@ -11313,7 +11295,7 @@
         <v>421</v>
       </c>
       <c r="C398" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="399" spans="1:3">
@@ -11324,7 +11306,7 @@
         <v>422</v>
       </c>
       <c r="C399" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="400" spans="1:3">
@@ -11335,7 +11317,7 @@
         <v>423</v>
       </c>
       <c r="C400" t="s">
-        <v>1505</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="401" spans="1:3">
@@ -11346,7 +11328,7 @@
         <v>424</v>
       </c>
       <c r="C401" t="s">
-        <v>1506</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="402" spans="1:3">
@@ -11357,7 +11339,7 @@
         <v>425</v>
       </c>
       <c r="C402" t="s">
-        <v>1507</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="403" spans="1:3">
@@ -11368,7 +11350,7 @@
         <v>426</v>
       </c>
       <c r="C403" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="404" spans="1:3">
@@ -11379,7 +11361,7 @@
         <v>427</v>
       </c>
       <c r="C404" t="s">
-        <v>1509</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="405" spans="1:3">
@@ -11390,7 +11372,7 @@
         <v>428</v>
       </c>
       <c r="C405" t="s">
-        <v>1510</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="406" spans="1:3">
@@ -11401,7 +11383,7 @@
         <v>429</v>
       </c>
       <c r="C406" t="s">
-        <v>1511</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="407" spans="1:3">
@@ -11412,7 +11394,7 @@
         <v>430</v>
       </c>
       <c r="C407" t="s">
-        <v>1512</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="408" spans="1:3">
@@ -11423,7 +11405,7 @@
         <v>431</v>
       </c>
       <c r="C408" t="s">
-        <v>1513</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="409" spans="1:3">
@@ -11434,7 +11416,7 @@
         <v>432</v>
       </c>
       <c r="C409" t="s">
-        <v>1514</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="410" spans="1:3">
@@ -11445,7 +11427,7 @@
         <v>433</v>
       </c>
       <c r="C410" t="s">
-        <v>1515</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="411" spans="1:3">
@@ -11456,7 +11438,7 @@
         <v>434</v>
       </c>
       <c r="C411" t="s">
-        <v>1516</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="412" spans="1:3">
@@ -11467,7 +11449,7 @@
         <v>435</v>
       </c>
       <c r="C412" t="s">
-        <v>1517</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="413" spans="1:3">
@@ -11478,7 +11460,7 @@
         <v>436</v>
       </c>
       <c r="C413" t="s">
-        <v>1518</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="414" spans="1:3">
@@ -11489,7 +11471,7 @@
         <v>437</v>
       </c>
       <c r="C414" t="s">
-        <v>1519</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="415" spans="1:3">
@@ -11500,7 +11482,7 @@
         <v>438</v>
       </c>
       <c r="C415" t="s">
-        <v>1520</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="416" spans="1:3">
@@ -11511,7 +11493,7 @@
         <v>439</v>
       </c>
       <c r="C416" t="s">
-        <v>1521</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="417" spans="1:3">
@@ -11522,7 +11504,7 @@
         <v>440</v>
       </c>
       <c r="C417" t="s">
-        <v>1522</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="418" spans="1:3">
@@ -11533,7 +11515,7 @@
         <v>441</v>
       </c>
       <c r="C418" t="s">
-        <v>1523</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="419" spans="1:3">
@@ -11544,7 +11526,7 @@
         <v>442</v>
       </c>
       <c r="C419" t="s">
-        <v>1524</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="420" spans="1:3">
@@ -11555,7 +11537,7 @@
         <v>443</v>
       </c>
       <c r="C420" t="s">
-        <v>1525</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="421" spans="1:3">
@@ -11566,7 +11548,7 @@
         <v>444</v>
       </c>
       <c r="C421" t="s">
-        <v>1526</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="422" spans="1:3">
@@ -11577,7 +11559,7 @@
         <v>445</v>
       </c>
       <c r="C422" t="s">
-        <v>1527</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="423" spans="1:3">
@@ -11588,7 +11570,7 @@
         <v>446</v>
       </c>
       <c r="C423" t="s">
-        <v>1528</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="424" spans="1:3">
@@ -11599,7 +11581,7 @@
         <v>447</v>
       </c>
       <c r="C424" t="s">
-        <v>1529</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="425" spans="1:3">
@@ -11610,7 +11592,7 @@
         <v>448</v>
       </c>
       <c r="C425" t="s">
-        <v>1530</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="426" spans="1:3">
@@ -11621,7 +11603,7 @@
         <v>449</v>
       </c>
       <c r="C426" t="s">
-        <v>1531</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="427" spans="1:3">
@@ -11632,7 +11614,7 @@
         <v>450</v>
       </c>
       <c r="C427" t="s">
-        <v>1532</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="428" spans="1:3">
@@ -11643,7 +11625,7 @@
         <v>451</v>
       </c>
       <c r="C428" t="s">
-        <v>1533</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="429" spans="1:3">
@@ -11654,7 +11636,7 @@
         <v>452</v>
       </c>
       <c r="C429" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="430" spans="1:3">
@@ -11665,7 +11647,7 @@
         <v>453</v>
       </c>
       <c r="C430" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="431" spans="1:3">
@@ -11676,7 +11658,7 @@
         <v>454</v>
       </c>
       <c r="C431" t="s">
-        <v>1536</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="432" spans="1:3">
@@ -11687,7 +11669,7 @@
         <v>455</v>
       </c>
       <c r="C432" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="433" spans="1:3">
@@ -11698,7 +11680,7 @@
         <v>456</v>
       </c>
       <c r="C433" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="434" spans="1:3">
@@ -11709,7 +11691,7 @@
         <v>457</v>
       </c>
       <c r="C434" t="s">
-        <v>1539</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="435" spans="1:3">
@@ -11720,7 +11702,7 @@
         <v>458</v>
       </c>
       <c r="C435" t="s">
-        <v>1540</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="436" spans="1:3">
@@ -11731,7 +11713,7 @@
         <v>459</v>
       </c>
       <c r="C436" t="s">
-        <v>1541</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="437" spans="1:3">
@@ -11742,7 +11724,7 @@
         <v>460</v>
       </c>
       <c r="C437" t="s">
-        <v>1542</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="438" spans="1:3">
@@ -11753,7 +11735,7 @@
         <v>461</v>
       </c>
       <c r="C438" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="439" spans="1:3">
@@ -11764,7 +11746,7 @@
         <v>462</v>
       </c>
       <c r="C439" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="440" spans="1:3">
@@ -11775,7 +11757,7 @@
         <v>463</v>
       </c>
       <c r="C440" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="441" spans="1:3">
@@ -11786,7 +11768,7 @@
         <v>464</v>
       </c>
       <c r="C441" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="442" spans="1:3">
@@ -11797,7 +11779,7 @@
         <v>465</v>
       </c>
       <c r="C442" t="s">
-        <v>1547</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="443" spans="1:3">
@@ -11808,7 +11790,7 @@
         <v>466</v>
       </c>
       <c r="C443" t="s">
-        <v>1548</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="444" spans="1:3">
@@ -11819,7 +11801,7 @@
         <v>467</v>
       </c>
       <c r="C444" t="s">
-        <v>1549</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="445" spans="1:3">
@@ -11830,7 +11812,7 @@
         <v>468</v>
       </c>
       <c r="C445" t="s">
-        <v>1550</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="446" spans="1:3">
@@ -11841,7 +11823,7 @@
         <v>469</v>
       </c>
       <c r="C446" t="s">
-        <v>1551</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="447" spans="1:3">
@@ -11852,7 +11834,7 @@
         <v>470</v>
       </c>
       <c r="C447" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="448" spans="1:3">
@@ -11863,7 +11845,7 @@
         <v>471</v>
       </c>
       <c r="C448" t="s">
-        <v>1553</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="449" spans="1:3">
@@ -11874,7 +11856,7 @@
         <v>472</v>
       </c>
       <c r="C449" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="450" spans="1:3">
@@ -11885,7 +11867,7 @@
         <v>473</v>
       </c>
       <c r="C450" t="s">
-        <v>1555</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="451" spans="1:3">
@@ -11896,7 +11878,7 @@
         <v>474</v>
       </c>
       <c r="C451" t="s">
-        <v>1556</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="452" spans="1:3">
@@ -11907,7 +11889,7 @@
         <v>475</v>
       </c>
       <c r="C452" t="s">
-        <v>1557</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="453" spans="1:3">
@@ -11918,7 +11900,7 @@
         <v>476</v>
       </c>
       <c r="C453" t="s">
-        <v>1558</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="454" spans="1:3">
@@ -11929,7 +11911,7 @@
         <v>477</v>
       </c>
       <c r="C454" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="455" spans="1:3">
@@ -11940,7 +11922,7 @@
         <v>478</v>
       </c>
       <c r="C455" t="s">
-        <v>1560</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="456" spans="1:3">
@@ -11951,7 +11933,7 @@
         <v>479</v>
       </c>
       <c r="C456" t="s">
-        <v>1561</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="457" spans="1:3">
@@ -11962,7 +11944,7 @@
         <v>480</v>
       </c>
       <c r="C457" t="s">
-        <v>1562</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="458" spans="1:3">
@@ -11973,7 +11955,7 @@
         <v>481</v>
       </c>
       <c r="C458" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="459" spans="1:3">
@@ -11984,7 +11966,7 @@
         <v>482</v>
       </c>
       <c r="C459" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="460" spans="1:3">
@@ -11995,7 +11977,7 @@
         <v>483</v>
       </c>
       <c r="C460" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="461" spans="1:3">
@@ -12006,7 +11988,7 @@
         <v>484</v>
       </c>
       <c r="C461" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="462" spans="1:3">
@@ -12017,7 +11999,7 @@
         <v>485</v>
       </c>
       <c r="C462" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="463" spans="1:3">
@@ -12028,7 +12010,7 @@
         <v>486</v>
       </c>
       <c r="C463" t="s">
-        <v>1568</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="464" spans="1:3">
@@ -12039,7 +12021,7 @@
         <v>487</v>
       </c>
       <c r="C464" t="s">
-        <v>1569</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="465" spans="1:3">
@@ -12050,7 +12032,7 @@
         <v>488</v>
       </c>
       <c r="C465" t="s">
-        <v>1570</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="466" spans="1:3">
@@ -12061,7 +12043,7 @@
         <v>489</v>
       </c>
       <c r="C466" t="s">
-        <v>1571</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="467" spans="1:3">
@@ -12072,7 +12054,7 @@
         <v>490</v>
       </c>
       <c r="C467" t="s">
-        <v>1572</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="468" spans="1:3">
@@ -12083,7 +12065,7 @@
         <v>491</v>
       </c>
       <c r="C468" t="s">
-        <v>1573</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="469" spans="1:3">
@@ -12094,7 +12076,7 @@
         <v>492</v>
       </c>
       <c r="C469" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="470" spans="1:3">
@@ -12105,7 +12087,7 @@
         <v>493</v>
       </c>
       <c r="C470" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="471" spans="1:3">
@@ -12116,7 +12098,7 @@
         <v>494</v>
       </c>
       <c r="C471" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="472" spans="1:3">
@@ -12127,7 +12109,7 @@
         <v>495</v>
       </c>
       <c r="C472" t="s">
-        <v>1536</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="473" spans="1:3">
@@ -12138,7 +12120,7 @@
         <v>496</v>
       </c>
       <c r="C473" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="474" spans="1:3">
@@ -12149,7 +12131,7 @@
         <v>497</v>
       </c>
       <c r="C474" t="s">
-        <v>1577</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="475" spans="1:3">
@@ -12160,7 +12142,7 @@
         <v>498</v>
       </c>
       <c r="C475" t="s">
-        <v>1578</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="476" spans="1:3">
@@ -12171,7 +12153,7 @@
         <v>499</v>
       </c>
       <c r="C476" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="477" spans="1:3">
@@ -12182,7 +12164,7 @@
         <v>500</v>
       </c>
       <c r="C477" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="478" spans="1:3">
@@ -12193,7 +12175,7 @@
         <v>501</v>
       </c>
       <c r="C478" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="479" spans="1:3">
@@ -12204,7 +12186,7 @@
         <v>502</v>
       </c>
       <c r="C479" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="480" spans="1:3">
@@ -12215,7 +12197,7 @@
         <v>503</v>
       </c>
       <c r="C480" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="481" spans="1:3">
@@ -12226,7 +12208,7 @@
         <v>504</v>
       </c>
       <c r="C481" t="s">
-        <v>1584</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="482" spans="1:3">
@@ -12237,7 +12219,7 @@
         <v>505</v>
       </c>
       <c r="C482" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="483" spans="1:3">
@@ -12248,7 +12230,7 @@
         <v>506</v>
       </c>
       <c r="C483" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="484" spans="1:3">
@@ -12259,7 +12241,7 @@
         <v>507</v>
       </c>
       <c r="C484" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="485" spans="1:3">
@@ -12270,7 +12252,7 @@
         <v>508</v>
       </c>
       <c r="C485" t="s">
-        <v>1588</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="486" spans="1:3">
@@ -12281,7 +12263,7 @@
         <v>509</v>
       </c>
       <c r="C486" t="s">
-        <v>1589</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="487" spans="1:3">
@@ -12292,7 +12274,7 @@
         <v>510</v>
       </c>
       <c r="C487" t="s">
-        <v>1590</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="488" spans="1:3">
@@ -12303,7 +12285,7 @@
         <v>511</v>
       </c>
       <c r="C488" t="s">
-        <v>1591</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="489" spans="1:3">
@@ -12314,7 +12296,7 @@
         <v>512</v>
       </c>
       <c r="C489" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="490" spans="1:3">
@@ -12325,7 +12307,7 @@
         <v>513</v>
       </c>
       <c r="C490" t="s">
-        <v>1593</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="491" spans="1:3">
@@ -12336,7 +12318,7 @@
         <v>514</v>
       </c>
       <c r="C491" t="s">
-        <v>1594</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="492" spans="1:3">
@@ -12347,7 +12329,7 @@
         <v>515</v>
       </c>
       <c r="C492" t="s">
-        <v>1595</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="493" spans="1:3">
@@ -12358,7 +12340,7 @@
         <v>516</v>
       </c>
       <c r="C493" t="s">
-        <v>1596</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="494" spans="1:3">
@@ -12369,7 +12351,7 @@
         <v>517</v>
       </c>
       <c r="C494" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="495" spans="1:3">
@@ -12380,7 +12362,7 @@
         <v>518</v>
       </c>
       <c r="C495" t="s">
-        <v>1598</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="496" spans="1:3">
@@ -12391,7 +12373,7 @@
         <v>519</v>
       </c>
       <c r="C496" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="497" spans="1:3">
@@ -12402,7 +12384,7 @@
         <v>520</v>
       </c>
       <c r="C497" t="s">
-        <v>1600</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="498" spans="1:3">
@@ -12413,7 +12395,7 @@
         <v>521</v>
       </c>
       <c r="C498" t="s">
-        <v>1601</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="499" spans="1:3">
@@ -12424,7 +12406,7 @@
         <v>522</v>
       </c>
       <c r="C499" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="500" spans="1:3">
@@ -12435,7 +12417,7 @@
         <v>523</v>
       </c>
       <c r="C500" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="501" spans="1:3">
@@ -12446,7 +12428,7 @@
         <v>524</v>
       </c>
       <c r="C501" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="502" spans="1:3">
@@ -12457,7 +12439,7 @@
         <v>525</v>
       </c>
       <c r="C502" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="503" spans="1:3">
@@ -12468,7 +12450,7 @@
         <v>526</v>
       </c>
       <c r="C503" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="504" spans="1:3">
@@ -12479,7 +12461,7 @@
         <v>527</v>
       </c>
       <c r="C504" t="s">
-        <v>1607</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="505" spans="1:3">
@@ -12490,7 +12472,7 @@
         <v>528</v>
       </c>
       <c r="C505" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="506" spans="1:3">
@@ -12501,7 +12483,7 @@
         <v>529</v>
       </c>
       <c r="C506" t="s">
-        <v>1609</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="507" spans="1:3">
@@ -12512,7 +12494,7 @@
         <v>530</v>
       </c>
       <c r="C507" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="508" spans="1:3">
@@ -12523,7 +12505,7 @@
         <v>531</v>
       </c>
       <c r="C508" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="509" spans="1:3">
@@ -12534,7 +12516,7 @@
         <v>532</v>
       </c>
       <c r="C509" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="510" spans="1:3">
@@ -12545,7 +12527,7 @@
         <v>533</v>
       </c>
       <c r="C510" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="511" spans="1:3">
@@ -12556,7 +12538,7 @@
         <v>534</v>
       </c>
       <c r="C511" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="512" spans="1:3">
@@ -12567,7 +12549,7 @@
         <v>535</v>
       </c>
       <c r="C512" t="s">
-        <v>1615</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="513" spans="1:3">
@@ -12578,7 +12560,7 @@
         <v>536</v>
       </c>
       <c r="C513" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="514" spans="1:3">
@@ -12589,7 +12571,7 @@
         <v>537</v>
       </c>
       <c r="C514" t="s">
-        <v>1617</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="515" spans="1:3">
@@ -12600,7 +12582,7 @@
         <v>538</v>
       </c>
       <c r="C515" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="516" spans="1:3">
@@ -12611,7 +12593,7 @@
         <v>539</v>
       </c>
       <c r="C516" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="517" spans="1:3">
@@ -12622,7 +12604,7 @@
         <v>540</v>
       </c>
       <c r="C517" t="s">
-        <v>1620</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="518" spans="1:3">
@@ -12633,7 +12615,7 @@
         <v>541</v>
       </c>
       <c r="C518" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="519" spans="1:3">
@@ -12644,7 +12626,7 @@
         <v>542</v>
       </c>
       <c r="C519" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="520" spans="1:3">
@@ -12655,7 +12637,7 @@
         <v>543</v>
       </c>
       <c r="C520" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="521" spans="1:3">
@@ -12666,7 +12648,7 @@
         <v>544</v>
       </c>
       <c r="C521" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="522" spans="1:3">
@@ -12677,7 +12659,7 @@
         <v>545</v>
       </c>
       <c r="C522" t="s">
-        <v>1625</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="523" spans="1:3">
@@ -12688,7 +12670,7 @@
         <v>546</v>
       </c>
       <c r="C523" t="s">
-        <v>1626</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="524" spans="1:3">
@@ -12699,7 +12681,7 @@
         <v>547</v>
       </c>
       <c r="C524" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="525" spans="1:3">
@@ -12710,7 +12692,7 @@
         <v>548</v>
       </c>
       <c r="C525" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="526" spans="1:3">
@@ -12721,7 +12703,7 @@
         <v>549</v>
       </c>
       <c r="C526" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="527" spans="1:3">
@@ -12732,7 +12714,7 @@
         <v>550</v>
       </c>
       <c r="C527" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="528" spans="1:3">
@@ -12743,7 +12725,7 @@
         <v>551</v>
       </c>
       <c r="C528" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="529" spans="1:3">
@@ -12754,7 +12736,7 @@
         <v>552</v>
       </c>
       <c r="C529" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="530" spans="1:3">
@@ -12765,7 +12747,7 @@
         <v>553</v>
       </c>
       <c r="C530" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="531" spans="1:3">
@@ -12776,7 +12758,7 @@
         <v>554</v>
       </c>
       <c r="C531" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="532" spans="1:3">
@@ -12787,7 +12769,7 @@
         <v>555</v>
       </c>
       <c r="C532" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="533" spans="1:3">
@@ -12798,7 +12780,7 @@
         <v>556</v>
       </c>
       <c r="C533" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="534" spans="1:3">
@@ -12809,7 +12791,7 @@
         <v>557</v>
       </c>
       <c r="C534" t="s">
-        <v>1637</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="535" spans="1:3">
@@ -12820,7 +12802,7 @@
         <v>558</v>
       </c>
       <c r="C535" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="536" spans="1:3">
@@ -12831,7 +12813,7 @@
         <v>559</v>
       </c>
       <c r="C536" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="537" spans="1:3">
@@ -12842,7 +12824,7 @@
         <v>560</v>
       </c>
       <c r="C537" t="s">
-        <v>1640</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="538" spans="1:3">
@@ -12853,7 +12835,7 @@
         <v>561</v>
       </c>
       <c r="C538" t="s">
-        <v>1641</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="539" spans="1:3">
@@ -12864,7 +12846,7 @@
         <v>562</v>
       </c>
       <c r="C539" t="s">
-        <v>1642</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="540" spans="1:3">
@@ -12875,7 +12857,7 @@
         <v>563</v>
       </c>
       <c r="C540" t="s">
-        <v>1643</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="541" spans="1:3">
@@ -12886,7 +12868,7 @@
         <v>564</v>
       </c>
       <c r="C541" t="s">
-        <v>1644</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="542" spans="1:3">
@@ -12897,7 +12879,7 @@
         <v>565</v>
       </c>
       <c r="C542" t="s">
-        <v>1645</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="543" spans="1:3">
@@ -12908,7 +12890,7 @@
         <v>566</v>
       </c>
       <c r="C543" t="s">
-        <v>1646</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="544" spans="1:3">
@@ -12919,7 +12901,7 @@
         <v>567</v>
       </c>
       <c r="C544" t="s">
-        <v>1647</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="545" spans="1:3">
@@ -12930,7 +12912,7 @@
         <v>568</v>
       </c>
       <c r="C545" t="s">
-        <v>1648</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="546" spans="1:3">
@@ -12941,7 +12923,7 @@
         <v>569</v>
       </c>
       <c r="C546" t="s">
-        <v>1649</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="547" spans="1:3">
@@ -12952,7 +12934,7 @@
         <v>570</v>
       </c>
       <c r="C547" t="s">
-        <v>1650</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="548" spans="1:3">
@@ -12963,7 +12945,7 @@
         <v>571</v>
       </c>
       <c r="C548" t="s">
-        <v>1651</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="549" spans="1:3">
@@ -12974,7 +12956,7 @@
         <v>572</v>
       </c>
       <c r="C549" t="s">
-        <v>1652</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="550" spans="1:3">
@@ -12985,7 +12967,7 @@
         <v>573</v>
       </c>
       <c r="C550" t="s">
-        <v>1653</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="551" spans="1:3">
@@ -12996,7 +12978,7 @@
         <v>574</v>
       </c>
       <c r="C551" t="s">
-        <v>1654</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="552" spans="1:3">
@@ -13007,7 +12989,7 @@
         <v>575</v>
       </c>
       <c r="C552" t="s">
-        <v>1655</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="553" spans="1:3">
@@ -13018,7 +13000,7 @@
         <v>576</v>
       </c>
       <c r="C553" t="s">
-        <v>1656</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="554" spans="1:3">
@@ -13029,7 +13011,7 @@
         <v>577</v>
       </c>
       <c r="C554" t="s">
-        <v>1657</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="555" spans="1:3">
@@ -13040,7 +13022,7 @@
         <v>578</v>
       </c>
       <c r="C555" t="s">
-        <v>1658</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="556" spans="1:3">
@@ -13051,7 +13033,7 @@
         <v>579</v>
       </c>
       <c r="C556" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="557" spans="1:3">
@@ -13062,7 +13044,7 @@
         <v>580</v>
       </c>
       <c r="C557" t="s">
-        <v>1660</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="558" spans="1:3">
@@ -13073,7 +13055,7 @@
         <v>581</v>
       </c>
       <c r="C558" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="559" spans="1:3">
@@ -13084,7 +13066,7 @@
         <v>582</v>
       </c>
       <c r="C559" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="560" spans="1:3">
@@ -13095,7 +13077,7 @@
         <v>583</v>
       </c>
       <c r="C560" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="561" spans="1:3">
@@ -13106,7 +13088,7 @@
         <v>584</v>
       </c>
       <c r="C561" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="562" spans="1:3">
@@ -13117,7 +13099,7 @@
         <v>585</v>
       </c>
       <c r="C562" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="563" spans="1:3">
@@ -13128,7 +13110,7 @@
         <v>586</v>
       </c>
       <c r="C563" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="564" spans="1:3">
@@ -13139,7 +13121,7 @@
         <v>587</v>
       </c>
       <c r="C564" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="565" spans="1:3">
@@ -13150,7 +13132,7 @@
         <v>588</v>
       </c>
       <c r="C565" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="566" spans="1:3">
@@ -13161,7 +13143,7 @@
         <v>589</v>
       </c>
       <c r="C566" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="567" spans="1:3">
@@ -13172,7 +13154,7 @@
         <v>590</v>
       </c>
       <c r="C567" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="568" spans="1:3">
@@ -13183,7 +13165,7 @@
         <v>591</v>
       </c>
       <c r="C568" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="569" spans="1:3">
@@ -13194,7 +13176,7 @@
         <v>592</v>
       </c>
       <c r="C569" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="570" spans="1:3">
@@ -13205,7 +13187,7 @@
         <v>593</v>
       </c>
       <c r="C570" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="571" spans="1:3">
@@ -13216,7 +13198,7 @@
         <v>594</v>
       </c>
       <c r="C571" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="572" spans="1:3">
@@ -13227,7 +13209,7 @@
         <v>595</v>
       </c>
       <c r="C572" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="573" spans="1:3">
@@ -13238,7 +13220,7 @@
         <v>596</v>
       </c>
       <c r="C573" t="s">
-        <v>1676</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="574" spans="1:3">
@@ -13249,7 +13231,7 @@
         <v>597</v>
       </c>
       <c r="C574" t="s">
-        <v>1677</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="575" spans="1:3">
@@ -13260,7 +13242,7 @@
         <v>598</v>
       </c>
       <c r="C575" t="s">
-        <v>1678</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="576" spans="1:3">
@@ -13271,7 +13253,7 @@
         <v>599</v>
       </c>
       <c r="C576" t="s">
-        <v>1679</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="577" spans="1:3">
@@ -13282,7 +13264,7 @@
         <v>600</v>
       </c>
       <c r="C577" t="s">
-        <v>1680</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="578" spans="1:3">
@@ -13293,7 +13275,7 @@
         <v>601</v>
       </c>
       <c r="C578" t="s">
-        <v>1681</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="579" spans="1:3">
@@ -13304,7 +13286,7 @@
         <v>602</v>
       </c>
       <c r="C579" t="s">
-        <v>1682</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="580" spans="1:3">
@@ -13315,7 +13297,7 @@
         <v>603</v>
       </c>
       <c r="C580" t="s">
-        <v>1683</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="581" spans="1:3">
@@ -13326,7 +13308,7 @@
         <v>604</v>
       </c>
       <c r="C581" t="s">
-        <v>1684</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="582" spans="1:3">
@@ -13337,7 +13319,7 @@
         <v>605</v>
       </c>
       <c r="C582" t="s">
-        <v>1685</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="583" spans="1:3">
@@ -13348,7 +13330,7 @@
         <v>606</v>
       </c>
       <c r="C583" t="s">
-        <v>1686</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="584" spans="1:3">
@@ -13359,7 +13341,7 @@
         <v>607</v>
       </c>
       <c r="C584" t="s">
-        <v>1687</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="585" spans="1:3">
@@ -13370,7 +13352,7 @@
         <v>608</v>
       </c>
       <c r="C585" t="s">
-        <v>1688</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="586" spans="1:3">
@@ -13381,7 +13363,7 @@
         <v>609</v>
       </c>
       <c r="C586" t="s">
-        <v>1689</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="587" spans="1:3">
@@ -13392,7 +13374,7 @@
         <v>610</v>
       </c>
       <c r="C587" t="s">
-        <v>1690</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="588" spans="1:3">
@@ -13403,7 +13385,7 @@
         <v>611</v>
       </c>
       <c r="C588" t="s">
-        <v>1691</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="589" spans="1:3">
@@ -13414,7 +13396,7 @@
         <v>612</v>
       </c>
       <c r="C589" t="s">
-        <v>1692</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="590" spans="1:3">
@@ -13425,7 +13407,7 @@
         <v>613</v>
       </c>
       <c r="C590" t="s">
-        <v>1693</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="591" spans="1:3">
@@ -13436,7 +13418,7 @@
         <v>614</v>
       </c>
       <c r="C591" t="s">
-        <v>1694</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="592" spans="1:3">
@@ -13447,7 +13429,7 @@
         <v>615</v>
       </c>
       <c r="C592" t="s">
-        <v>1695</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="593" spans="1:3">
@@ -13458,7 +13440,7 @@
         <v>616</v>
       </c>
       <c r="C593" t="s">
-        <v>1696</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="594" spans="1:3">
@@ -13469,7 +13451,7 @@
         <v>617</v>
       </c>
       <c r="C594" t="s">
-        <v>1697</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="595" spans="1:3">
@@ -13480,7 +13462,7 @@
         <v>618</v>
       </c>
       <c r="C595" t="s">
-        <v>1698</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="596" spans="1:3">
@@ -13491,7 +13473,7 @@
         <v>619</v>
       </c>
       <c r="C596" t="s">
-        <v>1699</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="597" spans="1:3">
@@ -13502,7 +13484,7 @@
         <v>620</v>
       </c>
       <c r="C597" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="598" spans="1:3">
@@ -13513,7 +13495,7 @@
         <v>621</v>
       </c>
       <c r="C598" t="s">
-        <v>1700</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="599" spans="1:3">
@@ -13524,7 +13506,7 @@
         <v>622</v>
       </c>
       <c r="C599" t="s">
-        <v>1701</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="600" spans="1:3">
@@ -13535,7 +13517,7 @@
         <v>623</v>
       </c>
       <c r="C600" t="s">
-        <v>1702</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="601" spans="1:3">
@@ -13546,7 +13528,7 @@
         <v>624</v>
       </c>
       <c r="C601" t="s">
-        <v>1703</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="602" spans="1:3">
@@ -13557,7 +13539,7 @@
         <v>625</v>
       </c>
       <c r="C602" t="s">
-        <v>1704</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="603" spans="1:3">
@@ -13568,7 +13550,7 @@
         <v>626</v>
       </c>
       <c r="C603" t="s">
-        <v>1705</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="604" spans="1:3">
@@ -13579,7 +13561,7 @@
         <v>627</v>
       </c>
       <c r="C604" t="s">
-        <v>1706</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="605" spans="1:3">
@@ -13590,7 +13572,7 @@
         <v>628</v>
       </c>
       <c r="C605" t="s">
-        <v>1707</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="606" spans="1:3">
@@ -13601,7 +13583,7 @@
         <v>629</v>
       </c>
       <c r="C606" t="s">
-        <v>1708</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="607" spans="1:3">
@@ -13612,7 +13594,7 @@
         <v>630</v>
       </c>
       <c r="C607" t="s">
-        <v>1709</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="608" spans="1:3">
@@ -13623,7 +13605,7 @@
         <v>631</v>
       </c>
       <c r="C608" t="s">
-        <v>1710</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="609" spans="1:3">
@@ -13634,7 +13616,7 @@
         <v>632</v>
       </c>
       <c r="C609" t="s">
-        <v>1711</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="610" spans="1:3">
@@ -13645,7 +13627,7 @@
         <v>633</v>
       </c>
       <c r="C610" t="s">
-        <v>1712</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="611" spans="1:3">
@@ -13656,7 +13638,7 @@
         <v>634</v>
       </c>
       <c r="C611" t="s">
-        <v>1713</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="612" spans="1:3">
@@ -13667,7 +13649,7 @@
         <v>635</v>
       </c>
       <c r="C612" t="s">
-        <v>1714</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="613" spans="1:3">
@@ -13678,7 +13660,7 @@
         <v>636</v>
       </c>
       <c r="C613" t="s">
-        <v>1715</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="614" spans="1:3">
@@ -13689,7 +13671,7 @@
         <v>637</v>
       </c>
       <c r="C614" t="s">
-        <v>1716</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="615" spans="1:3">
@@ -13700,7 +13682,7 @@
         <v>638</v>
       </c>
       <c r="C615" t="s">
-        <v>1717</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="616" spans="1:3">
@@ -13711,7 +13693,7 @@
         <v>639</v>
       </c>
       <c r="C616" t="s">
-        <v>1718</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="617" spans="1:3">
@@ -13722,7 +13704,7 @@
         <v>640</v>
       </c>
       <c r="C617" t="s">
-        <v>1719</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="618" spans="1:3">
@@ -13733,7 +13715,7 @@
         <v>641</v>
       </c>
       <c r="C618" t="s">
-        <v>1720</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="619" spans="1:3">
@@ -13744,7 +13726,7 @@
         <v>642</v>
       </c>
       <c r="C619" t="s">
-        <v>1721</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="620" spans="1:3">
@@ -13755,7 +13737,7 @@
         <v>643</v>
       </c>
       <c r="C620" t="s">
-        <v>1722</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="621" spans="1:3">
@@ -13766,7 +13748,7 @@
         <v>644</v>
       </c>
       <c r="C621" t="s">
-        <v>1723</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="622" spans="1:3">
@@ -13777,7 +13759,7 @@
         <v>645</v>
       </c>
       <c r="C622" t="s">
-        <v>1724</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="623" spans="1:3">
@@ -13788,7 +13770,7 @@
         <v>646</v>
       </c>
       <c r="C623" t="s">
-        <v>1725</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="624" spans="1:3">
@@ -13799,7 +13781,7 @@
         <v>647</v>
       </c>
       <c r="C624" t="s">
-        <v>1726</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="625" spans="1:3">
@@ -13810,7 +13792,7 @@
         <v>648</v>
       </c>
       <c r="C625" t="s">
-        <v>1727</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="626" spans="1:3">
@@ -13821,7 +13803,7 @@
         <v>649</v>
       </c>
       <c r="C626" t="s">
-        <v>1728</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="627" spans="1:3">
@@ -13832,7 +13814,7 @@
         <v>650</v>
       </c>
       <c r="C627" t="s">
-        <v>1729</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="628" spans="1:3">
@@ -13843,7 +13825,7 @@
         <v>651</v>
       </c>
       <c r="C628" t="s">
-        <v>1730</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="629" spans="1:3">
@@ -13854,7 +13836,7 @@
         <v>652</v>
       </c>
       <c r="C629" t="s">
-        <v>1731</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="630" spans="1:3">
@@ -13865,7 +13847,7 @@
         <v>653</v>
       </c>
       <c r="C630" t="s">
-        <v>1732</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="631" spans="1:3">
@@ -13876,7 +13858,7 @@
         <v>654</v>
       </c>
       <c r="C631" t="s">
-        <v>1733</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="632" spans="1:3">
@@ -13887,7 +13869,7 @@
         <v>655</v>
       </c>
       <c r="C632" t="s">
-        <v>1734</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="633" spans="1:3">
@@ -13898,7 +13880,7 @@
         <v>656</v>
       </c>
       <c r="C633" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="634" spans="1:3">
@@ -13909,7 +13891,7 @@
         <v>657</v>
       </c>
       <c r="C634" t="s">
-        <v>1736</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="635" spans="1:3">
@@ -13920,7 +13902,7 @@
         <v>658</v>
       </c>
       <c r="C635" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="636" spans="1:3">
@@ -13931,7 +13913,7 @@
         <v>659</v>
       </c>
       <c r="C636" t="s">
-        <v>1738</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="637" spans="1:3">
@@ -13942,7 +13924,7 @@
         <v>660</v>
       </c>
       <c r="C637" t="s">
-        <v>1739</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="638" spans="1:3">
@@ -13953,7 +13935,7 @@
         <v>661</v>
       </c>
       <c r="C638" t="s">
-        <v>1740</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="639" spans="1:3">
@@ -13964,7 +13946,7 @@
         <v>662</v>
       </c>
       <c r="C639" t="s">
-        <v>1741</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="640" spans="1:3">
@@ -13975,7 +13957,7 @@
         <v>663</v>
       </c>
       <c r="C640" t="s">
-        <v>1742</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="641" spans="1:3">
@@ -13986,7 +13968,7 @@
         <v>664</v>
       </c>
       <c r="C641" t="s">
-        <v>1743</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="642" spans="1:3">
@@ -13997,7 +13979,7 @@
         <v>665</v>
       </c>
       <c r="C642" t="s">
-        <v>1744</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="643" spans="1:3">
@@ -14008,7 +13990,7 @@
         <v>666</v>
       </c>
       <c r="C643" t="s">
-        <v>1745</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="644" spans="1:3">
@@ -14019,7 +14001,7 @@
         <v>667</v>
       </c>
       <c r="C644" t="s">
-        <v>1746</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="645" spans="1:3">
@@ -14030,7 +14012,7 @@
         <v>668</v>
       </c>
       <c r="C645" t="s">
-        <v>1747</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="646" spans="1:3">
@@ -14041,7 +14023,7 @@
         <v>669</v>
       </c>
       <c r="C646" t="s">
-        <v>1748</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="647" spans="1:3">
@@ -14052,7 +14034,7 @@
         <v>670</v>
       </c>
       <c r="C647" t="s">
-        <v>1749</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="648" spans="1:3">
@@ -14063,7 +14045,7 @@
         <v>671</v>
       </c>
       <c r="C648" t="s">
-        <v>1750</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="649" spans="1:3">
@@ -14074,7 +14056,7 @@
         <v>672</v>
       </c>
       <c r="C649" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="650" spans="1:3">
@@ -14085,7 +14067,7 @@
         <v>673</v>
       </c>
       <c r="C650" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="651" spans="1:3">
@@ -14096,7 +14078,7 @@
         <v>674</v>
       </c>
       <c r="C651" t="s">
-        <v>1753</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="652" spans="1:3">
@@ -14107,7 +14089,7 @@
         <v>675</v>
       </c>
       <c r="C652" t="s">
-        <v>1754</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="653" spans="1:3">
@@ -14118,7 +14100,7 @@
         <v>676</v>
       </c>
       <c r="C653" t="s">
-        <v>1755</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="654" spans="1:3">
@@ -14129,18 +14111,18 @@
         <v>677</v>
       </c>
       <c r="C654" t="s">
-        <v>1756</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="655" spans="1:3">
       <c r="A655" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B655" t="s">
         <v>678</v>
       </c>
       <c r="C655" t="s">
-        <v>1757</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="656" spans="1:3">
@@ -14151,7 +14133,7 @@
         <v>679</v>
       </c>
       <c r="C656" t="s">
-        <v>1758</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="657" spans="1:3">
@@ -14162,7 +14144,7 @@
         <v>680</v>
       </c>
       <c r="C657" t="s">
-        <v>1759</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="658" spans="1:3">
@@ -14173,7 +14155,7 @@
         <v>681</v>
       </c>
       <c r="C658" t="s">
-        <v>1760</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="659" spans="1:3">
@@ -14184,7 +14166,7 @@
         <v>682</v>
       </c>
       <c r="C659" t="s">
-        <v>1761</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="660" spans="1:3">
@@ -14195,7 +14177,7 @@
         <v>683</v>
       </c>
       <c r="C660" t="s">
-        <v>1762</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="661" spans="1:3">
@@ -14206,7 +14188,7 @@
         <v>684</v>
       </c>
       <c r="C661" t="s">
-        <v>1763</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="662" spans="1:3">
@@ -14217,7 +14199,7 @@
         <v>685</v>
       </c>
       <c r="C662" t="s">
-        <v>1764</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="663" spans="1:3">
@@ -14228,7 +14210,7 @@
         <v>686</v>
       </c>
       <c r="C663" t="s">
-        <v>1765</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="664" spans="1:3">
@@ -14239,7 +14221,7 @@
         <v>687</v>
       </c>
       <c r="C664" t="s">
-        <v>1766</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="665" spans="1:3">
@@ -14250,7 +14232,7 @@
         <v>688</v>
       </c>
       <c r="C665" t="s">
-        <v>1767</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="666" spans="1:3">
@@ -14261,7 +14243,7 @@
         <v>689</v>
       </c>
       <c r="C666" t="s">
-        <v>1768</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="667" spans="1:3">
@@ -14272,7 +14254,7 @@
         <v>690</v>
       </c>
       <c r="C667" t="s">
-        <v>1769</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="668" spans="1:3">
@@ -14283,7 +14265,7 @@
         <v>691</v>
       </c>
       <c r="C668" t="s">
-        <v>1770</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="669" spans="1:3">
@@ -14294,7 +14276,7 @@
         <v>692</v>
       </c>
       <c r="C669" t="s">
-        <v>1771</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="670" spans="1:3">
@@ -14305,7 +14287,7 @@
         <v>693</v>
       </c>
       <c r="C670" t="s">
-        <v>1772</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="671" spans="1:3">
@@ -14316,7 +14298,7 @@
         <v>694</v>
       </c>
       <c r="C671" t="s">
-        <v>1773</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="672" spans="1:3">
@@ -14327,7 +14309,7 @@
         <v>695</v>
       </c>
       <c r="C672" t="s">
-        <v>1774</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="673" spans="1:3">
@@ -14338,7 +14320,7 @@
         <v>696</v>
       </c>
       <c r="C673" t="s">
-        <v>1775</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="674" spans="1:3">
@@ -14349,7 +14331,7 @@
         <v>697</v>
       </c>
       <c r="C674" t="s">
-        <v>1776</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="675" spans="1:3">
@@ -14360,7 +14342,7 @@
         <v>698</v>
       </c>
       <c r="C675" t="s">
-        <v>1777</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="676" spans="1:3">
@@ -14371,7 +14353,7 @@
         <v>699</v>
       </c>
       <c r="C676" t="s">
-        <v>1778</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="677" spans="1:3">
@@ -14382,7 +14364,7 @@
         <v>700</v>
       </c>
       <c r="C677" t="s">
-        <v>1779</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="678" spans="1:3">
@@ -14393,7 +14375,7 @@
         <v>701</v>
       </c>
       <c r="C678" t="s">
-        <v>1780</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="679" spans="1:3">
@@ -14404,18 +14386,18 @@
         <v>702</v>
       </c>
       <c r="C679" t="s">
-        <v>1781</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="680" spans="1:3">
       <c r="A680" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B680" t="s">
         <v>703</v>
       </c>
       <c r="C680" t="s">
-        <v>1782</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="681" spans="1:3">
@@ -14426,7 +14408,7 @@
         <v>704</v>
       </c>
       <c r="C681" t="s">
-        <v>1783</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="682" spans="1:3">
@@ -14437,7 +14419,7 @@
         <v>705</v>
       </c>
       <c r="C682" t="s">
-        <v>1784</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="683" spans="1:3">
@@ -14448,7 +14430,7 @@
         <v>706</v>
       </c>
       <c r="C683" t="s">
-        <v>1785</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="684" spans="1:3">
@@ -14459,7 +14441,7 @@
         <v>707</v>
       </c>
       <c r="C684" t="s">
-        <v>1786</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="685" spans="1:3">
@@ -14470,7 +14452,7 @@
         <v>708</v>
       </c>
       <c r="C685" t="s">
-        <v>1787</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="686" spans="1:3">
@@ -14481,7 +14463,7 @@
         <v>709</v>
       </c>
       <c r="C686" t="s">
-        <v>1788</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="687" spans="1:3">
@@ -14492,7 +14474,7 @@
         <v>710</v>
       </c>
       <c r="C687" t="s">
-        <v>1789</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="688" spans="1:3">
@@ -14503,7 +14485,7 @@
         <v>711</v>
       </c>
       <c r="C688" t="s">
-        <v>1790</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="689" spans="1:3">
@@ -14514,7 +14496,7 @@
         <v>712</v>
       </c>
       <c r="C689" t="s">
-        <v>1791</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="690" spans="1:3">
@@ -14525,7 +14507,7 @@
         <v>713</v>
       </c>
       <c r="C690" t="s">
-        <v>1792</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="691" spans="1:3">
@@ -14536,7 +14518,7 @@
         <v>714</v>
       </c>
       <c r="C691" t="s">
-        <v>1793</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="692" spans="1:3">
@@ -14547,7 +14529,7 @@
         <v>715</v>
       </c>
       <c r="C692" t="s">
-        <v>1794</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="693" spans="1:3">
@@ -14558,7 +14540,7 @@
         <v>716</v>
       </c>
       <c r="C693" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="694" spans="1:3">
@@ -14569,7 +14551,7 @@
         <v>717</v>
       </c>
       <c r="C694" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="695" spans="1:3">
@@ -14580,18 +14562,18 @@
         <v>718</v>
       </c>
       <c r="C695" t="s">
-        <v>1797</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="696" spans="1:3">
       <c r="A696" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B696" t="s">
         <v>719</v>
       </c>
       <c r="C696" t="s">
-        <v>1210</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="697" spans="1:3">
@@ -14602,7 +14584,7 @@
         <v>720</v>
       </c>
       <c r="C697" t="s">
-        <v>1798</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="698" spans="1:3">
@@ -14613,7 +14595,7 @@
         <v>721</v>
       </c>
       <c r="C698" t="s">
-        <v>1799</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="699" spans="1:3">
@@ -14624,7 +14606,7 @@
         <v>722</v>
       </c>
       <c r="C699" t="s">
-        <v>1800</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="700" spans="1:3">
@@ -14635,7 +14617,7 @@
         <v>723</v>
       </c>
       <c r="C700" t="s">
-        <v>1801</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="701" spans="1:3">
@@ -14646,7 +14628,7 @@
         <v>724</v>
       </c>
       <c r="C701" t="s">
-        <v>1802</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="702" spans="1:3">
@@ -14657,7 +14639,7 @@
         <v>725</v>
       </c>
       <c r="C702" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="703" spans="1:3">
@@ -14668,7 +14650,7 @@
         <v>726</v>
       </c>
       <c r="C703" t="s">
-        <v>1804</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="704" spans="1:3">
@@ -14679,7 +14661,7 @@
         <v>727</v>
       </c>
       <c r="C704" t="s">
-        <v>1805</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="705" spans="1:3">
@@ -14690,7 +14672,7 @@
         <v>728</v>
       </c>
       <c r="C705" t="s">
-        <v>1806</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="706" spans="1:3">
@@ -14701,7 +14683,7 @@
         <v>729</v>
       </c>
       <c r="C706" t="s">
-        <v>1807</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="707" spans="1:3">
@@ -14712,7 +14694,7 @@
         <v>730</v>
       </c>
       <c r="C707" t="s">
-        <v>1808</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="708" spans="1:3">
@@ -14723,7 +14705,7 @@
         <v>731</v>
       </c>
       <c r="C708" t="s">
-        <v>1809</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="709" spans="1:3">
@@ -14734,7 +14716,7 @@
         <v>732</v>
       </c>
       <c r="C709" t="s">
-        <v>1810</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="710" spans="1:3">
@@ -14745,7 +14727,7 @@
         <v>733</v>
       </c>
       <c r="C710" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="711" spans="1:3">
@@ -14756,7 +14738,7 @@
         <v>734</v>
       </c>
       <c r="C711" t="s">
-        <v>1812</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="712" spans="1:3">
@@ -14767,7 +14749,7 @@
         <v>735</v>
       </c>
       <c r="C712" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="713" spans="1:3">
@@ -14778,7 +14760,7 @@
         <v>736</v>
       </c>
       <c r="C713" t="s">
-        <v>1814</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="714" spans="1:3">
@@ -14789,7 +14771,7 @@
         <v>737</v>
       </c>
       <c r="C714" t="s">
-        <v>1815</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="715" spans="1:3">
@@ -14800,7 +14782,7 @@
         <v>738</v>
       </c>
       <c r="C715" t="s">
-        <v>1816</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="716" spans="1:3">
@@ -14811,7 +14793,7 @@
         <v>739</v>
       </c>
       <c r="C716" t="s">
-        <v>1817</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="717" spans="1:3">
@@ -14822,7 +14804,7 @@
         <v>740</v>
       </c>
       <c r="C717" t="s">
-        <v>1818</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="718" spans="1:3">
@@ -14833,7 +14815,7 @@
         <v>741</v>
       </c>
       <c r="C718" t="s">
-        <v>1819</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="719" spans="1:3">
@@ -14844,7 +14826,7 @@
         <v>742</v>
       </c>
       <c r="C719" t="s">
-        <v>1820</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="720" spans="1:3">
@@ -14855,7 +14837,7 @@
         <v>743</v>
       </c>
       <c r="C720" t="s">
-        <v>1821</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="721" spans="1:3">
@@ -14866,7 +14848,7 @@
         <v>744</v>
       </c>
       <c r="C721" t="s">
-        <v>1822</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="722" spans="1:3">
@@ -14877,7 +14859,7 @@
         <v>745</v>
       </c>
       <c r="C722" t="s">
-        <v>1823</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="723" spans="1:3">
@@ -14888,7 +14870,7 @@
         <v>746</v>
       </c>
       <c r="C723" t="s">
-        <v>1824</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="724" spans="1:3">
@@ -14899,7 +14881,7 @@
         <v>747</v>
       </c>
       <c r="C724" t="s">
-        <v>1825</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="725" spans="1:3">
@@ -14910,7 +14892,7 @@
         <v>748</v>
       </c>
       <c r="C725" t="s">
-        <v>1826</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="726" spans="1:3">
@@ -14921,7 +14903,7 @@
         <v>749</v>
       </c>
       <c r="C726" t="s">
-        <v>1827</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="727" spans="1:3">
@@ -14932,7 +14914,7 @@
         <v>750</v>
       </c>
       <c r="C727" t="s">
-        <v>1828</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="728" spans="1:3">
@@ -14943,7 +14925,7 @@
         <v>751</v>
       </c>
       <c r="C728" t="s">
-        <v>1829</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="729" spans="1:3">
@@ -14954,7 +14936,7 @@
         <v>752</v>
       </c>
       <c r="C729" t="s">
-        <v>1830</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="730" spans="1:3">
@@ -14965,7 +14947,7 @@
         <v>753</v>
       </c>
       <c r="C730" t="s">
-        <v>1831</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="731" spans="1:3">
@@ -14976,7 +14958,7 @@
         <v>754</v>
       </c>
       <c r="C731" t="s">
-        <v>1832</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="732" spans="1:3">
@@ -14987,7 +14969,7 @@
         <v>755</v>
       </c>
       <c r="C732" t="s">
-        <v>1833</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="733" spans="1:3">
@@ -14998,7 +14980,7 @@
         <v>756</v>
       </c>
       <c r="C733" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="734" spans="1:3">
@@ -15009,7 +14991,7 @@
         <v>757</v>
       </c>
       <c r="C734" t="s">
-        <v>1835</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="735" spans="1:3">
@@ -15020,7 +15002,7 @@
         <v>758</v>
       </c>
       <c r="C735" t="s">
-        <v>1836</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="736" spans="1:3">
@@ -15031,7 +15013,7 @@
         <v>759</v>
       </c>
       <c r="C736" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="737" spans="1:3">
@@ -15042,29 +15024,29 @@
         <v>760</v>
       </c>
       <c r="C737" t="s">
-        <v>1838</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="738" spans="1:3">
       <c r="A738" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B738" t="s">
         <v>761</v>
       </c>
       <c r="C738" t="s">
-        <v>1839</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="739" spans="1:3">
       <c r="A739" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B739" t="s">
         <v>762</v>
       </c>
       <c r="C739" t="s">
-        <v>1840</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="740" spans="1:3">
@@ -15075,7 +15057,7 @@
         <v>763</v>
       </c>
       <c r="C740" t="s">
-        <v>1841</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="741" spans="1:3">
@@ -15086,7 +15068,7 @@
         <v>764</v>
       </c>
       <c r="C741" t="s">
-        <v>1842</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="742" spans="1:3">
@@ -15097,7 +15079,7 @@
         <v>765</v>
       </c>
       <c r="C742" t="s">
-        <v>1843</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="743" spans="1:3">
@@ -15108,7 +15090,7 @@
         <v>766</v>
       </c>
       <c r="C743" t="s">
-        <v>1844</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="744" spans="1:3">
@@ -15119,7 +15101,7 @@
         <v>767</v>
       </c>
       <c r="C744" t="s">
-        <v>1845</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="745" spans="1:3">
@@ -15130,7 +15112,7 @@
         <v>768</v>
       </c>
       <c r="C745" t="s">
-        <v>1846</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="746" spans="1:3">
@@ -15141,7 +15123,7 @@
         <v>769</v>
       </c>
       <c r="C746" t="s">
-        <v>1847</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="747" spans="1:3">
@@ -15152,7 +15134,7 @@
         <v>770</v>
       </c>
       <c r="C747" t="s">
-        <v>1848</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="748" spans="1:3">
@@ -15163,7 +15145,7 @@
         <v>771</v>
       </c>
       <c r="C748" t="s">
-        <v>1849</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="749" spans="1:3">
@@ -15174,7 +15156,7 @@
         <v>772</v>
       </c>
       <c r="C749" t="s">
-        <v>1850</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="750" spans="1:3">
@@ -15185,7 +15167,7 @@
         <v>773</v>
       </c>
       <c r="C750" t="s">
-        <v>1438</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="751" spans="1:3">
@@ -15196,18 +15178,18 @@
         <v>774</v>
       </c>
       <c r="C751" t="s">
-        <v>1851</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="752" spans="1:3">
       <c r="A752" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B752" t="s">
         <v>775</v>
       </c>
       <c r="C752" t="s">
-        <v>1852</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="753" spans="1:3">
@@ -15218,7 +15200,7 @@
         <v>776</v>
       </c>
       <c r="C753" t="s">
-        <v>1853</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="754" spans="1:3">
@@ -15229,7 +15211,7 @@
         <v>777</v>
       </c>
       <c r="C754" t="s">
-        <v>1854</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="755" spans="1:3">
@@ -15240,7 +15222,7 @@
         <v>778</v>
       </c>
       <c r="C755" t="s">
-        <v>1855</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="756" spans="1:3">
@@ -15251,7 +15233,7 @@
         <v>779</v>
       </c>
       <c r="C756" t="s">
-        <v>1856</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="757" spans="1:3">
@@ -15262,7 +15244,7 @@
         <v>780</v>
       </c>
       <c r="C757" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="758" spans="1:3">
@@ -15273,7 +15255,7 @@
         <v>781</v>
       </c>
       <c r="C758" t="s">
-        <v>1858</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="759" spans="1:3">
@@ -15284,7 +15266,7 @@
         <v>782</v>
       </c>
       <c r="C759" t="s">
-        <v>1859</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="760" spans="1:3">
@@ -15295,7 +15277,7 @@
         <v>783</v>
       </c>
       <c r="C760" t="s">
-        <v>1860</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="761" spans="1:3">
@@ -15306,7 +15288,7 @@
         <v>784</v>
       </c>
       <c r="C761" t="s">
-        <v>1861</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="762" spans="1:3">
@@ -15317,7 +15299,7 @@
         <v>785</v>
       </c>
       <c r="C762" t="s">
-        <v>1862</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="763" spans="1:3">
@@ -15328,7 +15310,7 @@
         <v>786</v>
       </c>
       <c r="C763" t="s">
-        <v>1863</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="764" spans="1:3">
@@ -15339,7 +15321,7 @@
         <v>787</v>
       </c>
       <c r="C764" t="s">
-        <v>1864</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="765" spans="1:3">
@@ -15350,7 +15332,7 @@
         <v>788</v>
       </c>
       <c r="C765" t="s">
-        <v>1865</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="766" spans="1:3">
@@ -15361,7 +15343,7 @@
         <v>789</v>
       </c>
       <c r="C766" t="s">
-        <v>1866</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="767" spans="1:3">
@@ -15372,7 +15354,7 @@
         <v>790</v>
       </c>
       <c r="C767" t="s">
-        <v>1867</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="768" spans="1:3">
@@ -15383,7 +15365,7 @@
         <v>791</v>
       </c>
       <c r="C768" t="s">
-        <v>1868</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="769" spans="1:3">
@@ -15394,7 +15376,7 @@
         <v>792</v>
       </c>
       <c r="C769" t="s">
-        <v>1869</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="770" spans="1:3">
@@ -15405,7 +15387,7 @@
         <v>793</v>
       </c>
       <c r="C770" t="s">
-        <v>1870</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="771" spans="1:3">
@@ -15416,7 +15398,7 @@
         <v>794</v>
       </c>
       <c r="C771" t="s">
-        <v>1871</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="772" spans="1:3">
@@ -15427,7 +15409,7 @@
         <v>795</v>
       </c>
       <c r="C772" t="s">
-        <v>1872</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="773" spans="1:3">
@@ -15438,7 +15420,7 @@
         <v>796</v>
       </c>
       <c r="C773" t="s">
-        <v>1873</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="774" spans="1:3">
@@ -15449,7 +15431,7 @@
         <v>797</v>
       </c>
       <c r="C774" t="s">
-        <v>1874</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="775" spans="1:3">
@@ -15460,7 +15442,7 @@
         <v>798</v>
       </c>
       <c r="C775" t="s">
-        <v>1875</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="776" spans="1:3">
@@ -15471,7 +15453,7 @@
         <v>799</v>
       </c>
       <c r="C776" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="777" spans="1:3">
@@ -15482,7 +15464,7 @@
         <v>800</v>
       </c>
       <c r="C777" t="s">
-        <v>1877</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="778" spans="1:3">
@@ -15493,7 +15475,7 @@
         <v>801</v>
       </c>
       <c r="C778" t="s">
-        <v>1878</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="779" spans="1:3">
@@ -15504,7 +15486,7 @@
         <v>802</v>
       </c>
       <c r="C779" t="s">
-        <v>1879</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="780" spans="1:3">
@@ -15515,7 +15497,7 @@
         <v>803</v>
       </c>
       <c r="C780" t="s">
-        <v>1880</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="781" spans="1:3">
@@ -15526,7 +15508,7 @@
         <v>804</v>
       </c>
       <c r="C781" t="s">
-        <v>1881</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="782" spans="1:3">
@@ -15537,7 +15519,7 @@
         <v>805</v>
       </c>
       <c r="C782" t="s">
-        <v>1882</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="783" spans="1:3">
@@ -15548,7 +15530,7 @@
         <v>806</v>
       </c>
       <c r="C783" t="s">
-        <v>1883</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="784" spans="1:3">
@@ -15559,7 +15541,7 @@
         <v>807</v>
       </c>
       <c r="C784" t="s">
-        <v>1884</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="785" spans="1:3">
@@ -15570,7 +15552,7 @@
         <v>808</v>
       </c>
       <c r="C785" t="s">
-        <v>1885</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="786" spans="1:3">
@@ -15581,7 +15563,7 @@
         <v>809</v>
       </c>
       <c r="C786" t="s">
-        <v>1886</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="787" spans="1:3">
@@ -15592,7 +15574,7 @@
         <v>810</v>
       </c>
       <c r="C787" t="s">
-        <v>1887</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="788" spans="1:3">
@@ -15603,7 +15585,7 @@
         <v>811</v>
       </c>
       <c r="C788" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="789" spans="1:3">
@@ -15614,7 +15596,7 @@
         <v>812</v>
       </c>
       <c r="C789" t="s">
-        <v>1889</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="790" spans="1:3">
@@ -15625,7 +15607,7 @@
         <v>813</v>
       </c>
       <c r="C790" t="s">
-        <v>1890</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="791" spans="1:3">
@@ -15636,7 +15618,7 @@
         <v>814</v>
       </c>
       <c r="C791" t="s">
-        <v>1891</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="792" spans="1:3">
@@ -15647,7 +15629,7 @@
         <v>815</v>
       </c>
       <c r="C792" t="s">
-        <v>1892</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="793" spans="1:3">
@@ -15658,7 +15640,7 @@
         <v>816</v>
       </c>
       <c r="C793" t="s">
-        <v>1893</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="794" spans="1:3">
@@ -15669,7 +15651,7 @@
         <v>817</v>
       </c>
       <c r="C794" t="s">
-        <v>1894</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="795" spans="1:3">
@@ -15680,7 +15662,7 @@
         <v>818</v>
       </c>
       <c r="C795" t="s">
-        <v>1895</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="796" spans="1:3">
@@ -15691,7 +15673,7 @@
         <v>819</v>
       </c>
       <c r="C796" t="s">
-        <v>1896</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="797" spans="1:3">
@@ -15702,7 +15684,7 @@
         <v>820</v>
       </c>
       <c r="C797" t="s">
-        <v>1897</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="798" spans="1:3">
@@ -15713,7 +15695,7 @@
         <v>821</v>
       </c>
       <c r="C798" t="s">
-        <v>1898</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="799" spans="1:3">
@@ -15724,7 +15706,7 @@
         <v>822</v>
       </c>
       <c r="C799" t="s">
-        <v>1899</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="800" spans="1:3">
@@ -15735,7 +15717,7 @@
         <v>823</v>
       </c>
       <c r="C800" t="s">
-        <v>1900</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="801" spans="1:3">
@@ -15746,7 +15728,7 @@
         <v>824</v>
       </c>
       <c r="C801" t="s">
-        <v>1901</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="802" spans="1:3">
@@ -15757,7 +15739,7 @@
         <v>825</v>
       </c>
       <c r="C802" t="s">
-        <v>1902</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="803" spans="1:3">
@@ -15768,7 +15750,7 @@
         <v>826</v>
       </c>
       <c r="C803" t="s">
-        <v>1903</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="804" spans="1:3">
@@ -15779,7 +15761,7 @@
         <v>827</v>
       </c>
       <c r="C804" t="s">
-        <v>1821</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="805" spans="1:3">
@@ -15790,7 +15772,7 @@
         <v>828</v>
       </c>
       <c r="C805" t="s">
-        <v>1904</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="806" spans="1:3">
@@ -15801,7 +15783,7 @@
         <v>829</v>
       </c>
       <c r="C806" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="807" spans="1:3">
@@ -15812,7 +15794,7 @@
         <v>830</v>
       </c>
       <c r="C807" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="808" spans="1:3">
@@ -15823,7 +15805,7 @@
         <v>831</v>
       </c>
       <c r="C808" t="s">
-        <v>1907</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="809" spans="1:3">
@@ -15834,7 +15816,7 @@
         <v>832</v>
       </c>
       <c r="C809" t="s">
-        <v>1908</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="810" spans="1:3">
@@ -15845,7 +15827,7 @@
         <v>833</v>
       </c>
       <c r="C810" t="s">
-        <v>1909</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="811" spans="1:3">
@@ -15856,7 +15838,7 @@
         <v>834</v>
       </c>
       <c r="C811" t="s">
-        <v>1910</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="812" spans="1:3">
@@ -15867,7 +15849,7 @@
         <v>835</v>
       </c>
       <c r="C812" t="s">
-        <v>1911</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="813" spans="1:3">
@@ -15878,7 +15860,7 @@
         <v>836</v>
       </c>
       <c r="C813" t="s">
-        <v>1912</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="814" spans="1:3">
@@ -15889,7 +15871,7 @@
         <v>837</v>
       </c>
       <c r="C814" t="s">
-        <v>1913</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="815" spans="1:3">
@@ -15900,7 +15882,7 @@
         <v>838</v>
       </c>
       <c r="C815" t="s">
-        <v>1914</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="816" spans="1:3">
@@ -15911,7 +15893,7 @@
         <v>839</v>
       </c>
       <c r="C816" t="s">
-        <v>1915</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="817" spans="1:3">
@@ -15922,7 +15904,7 @@
         <v>840</v>
       </c>
       <c r="C817" t="s">
-        <v>1916</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="818" spans="1:3">
@@ -15933,7 +15915,7 @@
         <v>841</v>
       </c>
       <c r="C818" t="s">
-        <v>1917</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="819" spans="1:3">
@@ -15944,7 +15926,7 @@
         <v>842</v>
       </c>
       <c r="C819" t="s">
-        <v>1918</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="820" spans="1:3">
@@ -15955,7 +15937,7 @@
         <v>843</v>
       </c>
       <c r="C820" t="s">
-        <v>1919</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="821" spans="1:3">
@@ -15966,7 +15948,7 @@
         <v>844</v>
       </c>
       <c r="C821" t="s">
-        <v>1920</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="822" spans="1:3">
@@ -15977,7 +15959,7 @@
         <v>845</v>
       </c>
       <c r="C822" t="s">
-        <v>1921</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="823" spans="1:3">
@@ -15988,7 +15970,7 @@
         <v>846</v>
       </c>
       <c r="C823" t="s">
-        <v>1922</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="824" spans="1:3">
@@ -15999,7 +15981,7 @@
         <v>847</v>
       </c>
       <c r="C824" t="s">
-        <v>1923</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="825" spans="1:3">
@@ -16010,7 +15992,7 @@
         <v>848</v>
       </c>
       <c r="C825" t="s">
-        <v>1924</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="826" spans="1:3">
@@ -16021,7 +16003,7 @@
         <v>849</v>
       </c>
       <c r="C826" t="s">
-        <v>1925</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="827" spans="1:3">
@@ -16032,7 +16014,7 @@
         <v>850</v>
       </c>
       <c r="C827" t="s">
-        <v>1926</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="828" spans="1:3">
@@ -16043,7 +16025,7 @@
         <v>851</v>
       </c>
       <c r="C828" t="s">
-        <v>1927</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="829" spans="1:3">
@@ -16054,7 +16036,7 @@
         <v>852</v>
       </c>
       <c r="C829" t="s">
-        <v>1928</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="830" spans="1:3">
@@ -16065,7 +16047,7 @@
         <v>853</v>
       </c>
       <c r="C830" t="s">
-        <v>1929</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="831" spans="1:3">
@@ -16076,7 +16058,7 @@
         <v>854</v>
       </c>
       <c r="C831" t="s">
-        <v>1930</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="832" spans="1:3">
@@ -16087,7 +16069,7 @@
         <v>855</v>
       </c>
       <c r="C832" t="s">
-        <v>1931</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="833" spans="1:3">
@@ -16098,7 +16080,7 @@
         <v>856</v>
       </c>
       <c r="C833" t="s">
-        <v>1932</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="834" spans="1:3">
@@ -16109,7 +16091,7 @@
         <v>857</v>
       </c>
       <c r="C834" t="s">
-        <v>1933</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="835" spans="1:3">
@@ -16120,7 +16102,7 @@
         <v>858</v>
       </c>
       <c r="C835" t="s">
-        <v>1934</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="836" spans="1:3">
@@ -16131,7 +16113,7 @@
         <v>859</v>
       </c>
       <c r="C836" t="s">
-        <v>1935</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="837" spans="1:3">
@@ -16142,7 +16124,7 @@
         <v>860</v>
       </c>
       <c r="C837" t="s">
-        <v>1936</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="838" spans="1:3">
@@ -16153,7 +16135,7 @@
         <v>861</v>
       </c>
       <c r="C838" t="s">
-        <v>1937</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="839" spans="1:3">
@@ -16164,7 +16146,7 @@
         <v>862</v>
       </c>
       <c r="C839" t="s">
-        <v>1938</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="840" spans="1:3">
@@ -16175,7 +16157,7 @@
         <v>863</v>
       </c>
       <c r="C840" t="s">
-        <v>1939</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="841" spans="1:3">
@@ -16186,7 +16168,7 @@
         <v>864</v>
       </c>
       <c r="C841" t="s">
-        <v>1940</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="842" spans="1:3">
@@ -16197,7 +16179,7 @@
         <v>865</v>
       </c>
       <c r="C842" t="s">
-        <v>1941</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="843" spans="1:3">
@@ -16208,7 +16190,7 @@
         <v>866</v>
       </c>
       <c r="C843" t="s">
-        <v>1942</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="844" spans="1:3">
@@ -16219,7 +16201,7 @@
         <v>867</v>
       </c>
       <c r="C844" t="s">
-        <v>1943</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="845" spans="1:3">
@@ -16230,7 +16212,7 @@
         <v>868</v>
       </c>
       <c r="C845" t="s">
-        <v>1944</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="846" spans="1:3">
@@ -16241,7 +16223,7 @@
         <v>869</v>
       </c>
       <c r="C846" t="s">
-        <v>1945</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="847" spans="1:3">
@@ -16252,7 +16234,7 @@
         <v>870</v>
       </c>
       <c r="C847" t="s">
-        <v>1946</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="848" spans="1:3">
@@ -16263,7 +16245,7 @@
         <v>871</v>
       </c>
       <c r="C848" t="s">
-        <v>1947</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="849" spans="1:3">
@@ -16274,7 +16256,7 @@
         <v>872</v>
       </c>
       <c r="C849" t="s">
-        <v>1948</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="850" spans="1:3">
@@ -16285,7 +16267,7 @@
         <v>873</v>
       </c>
       <c r="C850" t="s">
-        <v>1949</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="851" spans="1:3">
@@ -16296,7 +16278,7 @@
         <v>874</v>
       </c>
       <c r="C851" t="s">
-        <v>1950</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="852" spans="1:3">
@@ -16307,7 +16289,7 @@
         <v>875</v>
       </c>
       <c r="C852" t="s">
-        <v>1951</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="853" spans="1:3">
@@ -16318,7 +16300,7 @@
         <v>876</v>
       </c>
       <c r="C853" t="s">
-        <v>1952</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="854" spans="1:3">
@@ -16329,7 +16311,7 @@
         <v>877</v>
       </c>
       <c r="C854" t="s">
-        <v>1953</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="855" spans="1:3">
@@ -16340,7 +16322,7 @@
         <v>878</v>
       </c>
       <c r="C855" t="s">
-        <v>1954</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="856" spans="1:3">
@@ -16351,7 +16333,7 @@
         <v>879</v>
       </c>
       <c r="C856" t="s">
-        <v>1955</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="857" spans="1:3">
@@ -16362,7 +16344,7 @@
         <v>880</v>
       </c>
       <c r="C857" t="s">
-        <v>1956</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="858" spans="1:3">
@@ -16373,7 +16355,7 @@
         <v>881</v>
       </c>
       <c r="C858" t="s">
-        <v>1957</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="859" spans="1:3">
@@ -16384,7 +16366,7 @@
         <v>882</v>
       </c>
       <c r="C859" t="s">
-        <v>1958</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="860" spans="1:3">
@@ -16395,7 +16377,7 @@
         <v>883</v>
       </c>
       <c r="C860" t="s">
-        <v>1959</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="861" spans="1:3">
@@ -16406,7 +16388,7 @@
         <v>884</v>
       </c>
       <c r="C861" t="s">
-        <v>1960</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="862" spans="1:3">
@@ -16417,7 +16399,7 @@
         <v>885</v>
       </c>
       <c r="C862" t="s">
-        <v>1961</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="863" spans="1:3">
@@ -16428,7 +16410,7 @@
         <v>886</v>
       </c>
       <c r="C863" t="s">
-        <v>1962</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="864" spans="1:3">
@@ -16439,7 +16421,7 @@
         <v>887</v>
       </c>
       <c r="C864" t="s">
-        <v>1963</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="865" spans="1:3">
@@ -16450,7 +16432,7 @@
         <v>888</v>
       </c>
       <c r="C865" t="s">
-        <v>1964</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="866" spans="1:3">
@@ -16461,7 +16443,7 @@
         <v>889</v>
       </c>
       <c r="C866" t="s">
-        <v>1965</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="867" spans="1:3">
@@ -16472,7 +16454,7 @@
         <v>890</v>
       </c>
       <c r="C867" t="s">
-        <v>1966</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="868" spans="1:3">
@@ -16483,7 +16465,7 @@
         <v>891</v>
       </c>
       <c r="C868" t="s">
-        <v>1967</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="869" spans="1:3">
@@ -16494,7 +16476,7 @@
         <v>892</v>
       </c>
       <c r="C869" t="s">
-        <v>1968</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="870" spans="1:3">
@@ -16505,7 +16487,7 @@
         <v>893</v>
       </c>
       <c r="C870" t="s">
-        <v>1969</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="871" spans="1:3">
@@ -16516,7 +16498,7 @@
         <v>894</v>
       </c>
       <c r="C871" t="s">
-        <v>1970</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="872" spans="1:3">
@@ -16527,7 +16509,7 @@
         <v>895</v>
       </c>
       <c r="C872" t="s">
-        <v>1971</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="873" spans="1:3">
@@ -16538,7 +16520,7 @@
         <v>896</v>
       </c>
       <c r="C873" t="s">
-        <v>1972</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="874" spans="1:3">
@@ -16549,18 +16531,18 @@
         <v>897</v>
       </c>
       <c r="C874" t="s">
-        <v>1973</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="875" spans="1:3">
       <c r="A875" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B875" t="s">
         <v>898</v>
       </c>
       <c r="C875" t="s">
-        <v>1974</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="876" spans="1:3">
@@ -16571,7 +16553,7 @@
         <v>899</v>
       </c>
       <c r="C876" t="s">
-        <v>1975</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="877" spans="1:3">
@@ -16582,7 +16564,7 @@
         <v>900</v>
       </c>
       <c r="C877" t="s">
-        <v>1976</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="878" spans="1:3">
@@ -16593,7 +16575,7 @@
         <v>901</v>
       </c>
       <c r="C878" t="s">
-        <v>1977</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="879" spans="1:3">
@@ -16604,7 +16586,7 @@
         <v>902</v>
       </c>
       <c r="C879" t="s">
-        <v>1978</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="880" spans="1:3">
@@ -16615,7 +16597,7 @@
         <v>903</v>
       </c>
       <c r="C880" t="s">
-        <v>1979</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="881" spans="1:3">
@@ -16626,7 +16608,7 @@
         <v>904</v>
       </c>
       <c r="C881" t="s">
-        <v>1980</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="882" spans="1:3">
@@ -16637,7 +16619,7 @@
         <v>905</v>
       </c>
       <c r="C882" t="s">
-        <v>1981</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="883" spans="1:3">
@@ -16648,7 +16630,7 @@
         <v>906</v>
       </c>
       <c r="C883" t="s">
-        <v>1982</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="884" spans="1:3">
@@ -16659,7 +16641,7 @@
         <v>907</v>
       </c>
       <c r="C884" t="s">
-        <v>1983</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="885" spans="1:3">
@@ -16670,7 +16652,7 @@
         <v>908</v>
       </c>
       <c r="C885" t="s">
-        <v>1984</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="886" spans="1:3">
@@ -16681,7 +16663,7 @@
         <v>909</v>
       </c>
       <c r="C886" t="s">
-        <v>1985</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="887" spans="1:3">
@@ -16692,7 +16674,7 @@
         <v>910</v>
       </c>
       <c r="C887" t="s">
-        <v>1986</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="888" spans="1:3">
@@ -16703,7 +16685,7 @@
         <v>911</v>
       </c>
       <c r="C888" t="s">
-        <v>1987</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="889" spans="1:3">
@@ -16714,7 +16696,7 @@
         <v>912</v>
       </c>
       <c r="C889" t="s">
-        <v>1988</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="890" spans="1:3">
@@ -16725,7 +16707,7 @@
         <v>913</v>
       </c>
       <c r="C890" t="s">
-        <v>1989</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="891" spans="1:3">
@@ -16736,7 +16718,7 @@
         <v>914</v>
       </c>
       <c r="C891" t="s">
-        <v>1990</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="892" spans="1:3">
@@ -16747,7 +16729,7 @@
         <v>915</v>
       </c>
       <c r="C892" t="s">
-        <v>1991</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="893" spans="1:3">
@@ -16758,7 +16740,7 @@
         <v>916</v>
       </c>
       <c r="C893" t="s">
-        <v>1992</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="894" spans="1:3">
@@ -16769,7 +16751,7 @@
         <v>917</v>
       </c>
       <c r="C894" t="s">
-        <v>1993</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="895" spans="1:3">
@@ -16780,7 +16762,7 @@
         <v>918</v>
       </c>
       <c r="C895" t="s">
-        <v>1994</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="896" spans="1:3">
@@ -16791,7 +16773,7 @@
         <v>919</v>
       </c>
       <c r="C896" t="s">
-        <v>1995</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="897" spans="1:3">
@@ -16802,7 +16784,7 @@
         <v>920</v>
       </c>
       <c r="C897" t="s">
-        <v>1996</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="898" spans="1:3">
@@ -16813,7 +16795,7 @@
         <v>921</v>
       </c>
       <c r="C898" t="s">
-        <v>1997</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="899" spans="1:3">
@@ -16824,7 +16806,7 @@
         <v>922</v>
       </c>
       <c r="C899" t="s">
-        <v>1998</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="900" spans="1:3">
@@ -16835,7 +16817,7 @@
         <v>923</v>
       </c>
       <c r="C900" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="901" spans="1:3">
@@ -16846,7 +16828,7 @@
         <v>924</v>
       </c>
       <c r="C901" t="s">
-        <v>2000</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="902" spans="1:3">
@@ -16857,7 +16839,7 @@
         <v>925</v>
       </c>
       <c r="C902" t="s">
-        <v>2001</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="903" spans="1:3">
@@ -16868,7 +16850,7 @@
         <v>926</v>
       </c>
       <c r="C903" t="s">
-        <v>2002</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="904" spans="1:3">
@@ -16879,7 +16861,7 @@
         <v>927</v>
       </c>
       <c r="C904" t="s">
-        <v>2003</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="905" spans="1:3">
@@ -16890,7 +16872,7 @@
         <v>928</v>
       </c>
       <c r="C905" t="s">
-        <v>2004</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="906" spans="1:3">
@@ -16901,7 +16883,7 @@
         <v>929</v>
       </c>
       <c r="C906" t="s">
-        <v>2005</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="907" spans="1:3">
@@ -16912,7 +16894,7 @@
         <v>930</v>
       </c>
       <c r="C907" t="s">
-        <v>2006</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="908" spans="1:3">
@@ -16923,7 +16905,7 @@
         <v>931</v>
       </c>
       <c r="C908" t="s">
-        <v>2007</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="909" spans="1:3">
@@ -16934,7 +16916,7 @@
         <v>932</v>
       </c>
       <c r="C909" t="s">
-        <v>2008</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="910" spans="1:3">
@@ -16945,7 +16927,7 @@
         <v>933</v>
       </c>
       <c r="C910" t="s">
-        <v>2009</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="911" spans="1:3">
@@ -16956,7 +16938,7 @@
         <v>934</v>
       </c>
       <c r="C911" t="s">
-        <v>2010</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="912" spans="1:3">
@@ -16967,7 +16949,7 @@
         <v>935</v>
       </c>
       <c r="C912" t="s">
-        <v>2011</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="913" spans="1:3">
@@ -16978,7 +16960,7 @@
         <v>936</v>
       </c>
       <c r="C913" t="s">
-        <v>2012</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="914" spans="1:3">
@@ -16989,7 +16971,7 @@
         <v>937</v>
       </c>
       <c r="C914" t="s">
-        <v>2013</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="915" spans="1:3">
@@ -17000,7 +16982,7 @@
         <v>938</v>
       </c>
       <c r="C915" t="s">
-        <v>2014</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="916" spans="1:3">
@@ -17011,7 +16993,7 @@
         <v>939</v>
       </c>
       <c r="C916" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="917" spans="1:3">
@@ -17022,7 +17004,7 @@
         <v>940</v>
       </c>
       <c r="C917" t="s">
-        <v>2016</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="918" spans="1:3">
@@ -17033,7 +17015,7 @@
         <v>941</v>
       </c>
       <c r="C918" t="s">
-        <v>2017</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="919" spans="1:3">
@@ -17044,7 +17026,7 @@
         <v>942</v>
       </c>
       <c r="C919" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="920" spans="1:3">
@@ -17055,7 +17037,7 @@
         <v>943</v>
       </c>
       <c r="C920" t="s">
-        <v>2019</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="921" spans="1:3">
@@ -17066,7 +17048,7 @@
         <v>944</v>
       </c>
       <c r="C921" t="s">
-        <v>2020</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="922" spans="1:3">
@@ -17077,7 +17059,7 @@
         <v>945</v>
       </c>
       <c r="C922" t="s">
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="923" spans="1:3">
@@ -17088,7 +17070,7 @@
         <v>946</v>
       </c>
       <c r="C923" t="s">
-        <v>2022</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="924" spans="1:3">
@@ -17099,7 +17081,7 @@
         <v>947</v>
       </c>
       <c r="C924" t="s">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="925" spans="1:3">
@@ -17110,7 +17092,7 @@
         <v>948</v>
       </c>
       <c r="C925" t="s">
-        <v>2024</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="926" spans="1:3">
@@ -17121,7 +17103,7 @@
         <v>949</v>
       </c>
       <c r="C926" t="s">
-        <v>2025</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="927" spans="1:3">
@@ -17132,7 +17114,7 @@
         <v>950</v>
       </c>
       <c r="C927" t="s">
-        <v>2026</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="928" spans="1:3">
@@ -17143,7 +17125,7 @@
         <v>951</v>
       </c>
       <c r="C928" t="s">
-        <v>2027</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="929" spans="1:3">
@@ -17154,7 +17136,7 @@
         <v>952</v>
       </c>
       <c r="C929" t="s">
-        <v>2028</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="930" spans="1:3">
@@ -17165,7 +17147,7 @@
         <v>953</v>
       </c>
       <c r="C930" t="s">
-        <v>2029</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="931" spans="1:3">
@@ -17176,7 +17158,7 @@
         <v>954</v>
       </c>
       <c r="C931" t="s">
-        <v>2030</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="932" spans="1:3">
@@ -17187,7 +17169,7 @@
         <v>955</v>
       </c>
       <c r="C932" t="s">
-        <v>2031</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="933" spans="1:3">
@@ -17198,7 +17180,7 @@
         <v>956</v>
       </c>
       <c r="C933" t="s">
-        <v>2032</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="934" spans="1:3">
@@ -17209,7 +17191,7 @@
         <v>957</v>
       </c>
       <c r="C934" t="s">
-        <v>2033</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="935" spans="1:3">
@@ -17220,7 +17202,7 @@
         <v>958</v>
       </c>
       <c r="C935" t="s">
-        <v>2034</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="936" spans="1:3">
@@ -17231,7 +17213,7 @@
         <v>959</v>
       </c>
       <c r="C936" t="s">
-        <v>2035</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="937" spans="1:3">
@@ -17242,7 +17224,7 @@
         <v>960</v>
       </c>
       <c r="C937" t="s">
-        <v>2036</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="938" spans="1:3">
@@ -17253,7 +17235,7 @@
         <v>961</v>
       </c>
       <c r="C938" t="s">
-        <v>2037</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="939" spans="1:3">
@@ -17264,7 +17246,7 @@
         <v>962</v>
       </c>
       <c r="C939" t="s">
-        <v>2038</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="940" spans="1:3">
@@ -17275,7 +17257,7 @@
         <v>963</v>
       </c>
       <c r="C940" t="s">
-        <v>2039</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="941" spans="1:3">
@@ -17286,7 +17268,7 @@
         <v>964</v>
       </c>
       <c r="C941" t="s">
-        <v>2040</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="942" spans="1:3">
@@ -17297,7 +17279,7 @@
         <v>965</v>
       </c>
       <c r="C942" t="s">
-        <v>2041</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="943" spans="1:3">
@@ -17308,7 +17290,7 @@
         <v>966</v>
       </c>
       <c r="C943" t="s">
-        <v>2042</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="944" spans="1:3">
@@ -17319,7 +17301,7 @@
         <v>967</v>
       </c>
       <c r="C944" t="s">
-        <v>2043</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="945" spans="1:3">
@@ -17330,7 +17312,7 @@
         <v>968</v>
       </c>
       <c r="C945" t="s">
-        <v>2044</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="946" spans="1:3">
@@ -17341,7 +17323,7 @@
         <v>969</v>
       </c>
       <c r="C946" t="s">
-        <v>2045</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="947" spans="1:3">
@@ -17352,7 +17334,7 @@
         <v>970</v>
       </c>
       <c r="C947" t="s">
-        <v>2046</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="948" spans="1:3">
@@ -17363,7 +17345,7 @@
         <v>971</v>
       </c>
       <c r="C948" t="s">
-        <v>2047</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="949" spans="1:3">
@@ -17374,7 +17356,7 @@
         <v>972</v>
       </c>
       <c r="C949" t="s">
-        <v>2048</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="950" spans="1:3">
@@ -17385,7 +17367,7 @@
         <v>973</v>
       </c>
       <c r="C950" t="s">
-        <v>2049</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="951" spans="1:3">
@@ -17396,7 +17378,7 @@
         <v>974</v>
       </c>
       <c r="C951" t="s">
-        <v>2050</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="952" spans="1:3">
@@ -17407,7 +17389,7 @@
         <v>975</v>
       </c>
       <c r="C952" t="s">
-        <v>2051</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="953" spans="1:3">
@@ -17418,7 +17400,7 @@
         <v>976</v>
       </c>
       <c r="C953" t="s">
-        <v>2052</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="954" spans="1:3">
@@ -17429,7 +17411,7 @@
         <v>977</v>
       </c>
       <c r="C954" t="s">
-        <v>2053</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="955" spans="1:3">
@@ -17440,7 +17422,7 @@
         <v>978</v>
       </c>
       <c r="C955" t="s">
-        <v>2054</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="956" spans="1:3">
@@ -17451,7 +17433,7 @@
         <v>979</v>
       </c>
       <c r="C956" t="s">
-        <v>2055</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="957" spans="1:3">
@@ -17462,7 +17444,7 @@
         <v>980</v>
       </c>
       <c r="C957" t="s">
-        <v>2056</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="958" spans="1:3">
@@ -17473,7 +17455,7 @@
         <v>981</v>
       </c>
       <c r="C958" t="s">
-        <v>2057</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="959" spans="1:3">
@@ -17484,7 +17466,7 @@
         <v>982</v>
       </c>
       <c r="C959" t="s">
-        <v>2058</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="960" spans="1:3">
@@ -17495,7 +17477,7 @@
         <v>983</v>
       </c>
       <c r="C960" t="s">
-        <v>2059</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="961" spans="1:3">
@@ -17506,7 +17488,7 @@
         <v>984</v>
       </c>
       <c r="C961" t="s">
-        <v>2060</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="962" spans="1:3">
@@ -17517,7 +17499,7 @@
         <v>985</v>
       </c>
       <c r="C962" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="963" spans="1:3">
@@ -17528,7 +17510,7 @@
         <v>986</v>
       </c>
       <c r="C963" t="s">
-        <v>2062</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="964" spans="1:3">
@@ -17539,7 +17521,7 @@
         <v>987</v>
       </c>
       <c r="C964" t="s">
-        <v>2063</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="965" spans="1:3">
@@ -17550,7 +17532,7 @@
         <v>988</v>
       </c>
       <c r="C965" t="s">
-        <v>2064</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="966" spans="1:3">
@@ -17561,7 +17543,7 @@
         <v>989</v>
       </c>
       <c r="C966" t="s">
-        <v>2065</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="967" spans="1:3">
@@ -17572,7 +17554,7 @@
         <v>990</v>
       </c>
       <c r="C967" t="s">
-        <v>2066</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="968" spans="1:3">
@@ -17583,7 +17565,7 @@
         <v>991</v>
       </c>
       <c r="C968" t="s">
-        <v>2067</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="969" spans="1:3">
@@ -17594,7 +17576,7 @@
         <v>992</v>
       </c>
       <c r="C969" t="s">
-        <v>2068</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="970" spans="1:3">
@@ -17605,7 +17587,7 @@
         <v>993</v>
       </c>
       <c r="C970" t="s">
-        <v>2069</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="971" spans="1:3">
@@ -17616,7 +17598,7 @@
         <v>994</v>
       </c>
       <c r="C971" t="s">
-        <v>2070</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="972" spans="1:3">
@@ -17627,7 +17609,7 @@
         <v>995</v>
       </c>
       <c r="C972" t="s">
-        <v>2071</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="973" spans="1:3">
@@ -17638,7 +17620,7 @@
         <v>996</v>
       </c>
       <c r="C973" t="s">
-        <v>2072</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="974" spans="1:3">
@@ -17649,7 +17631,7 @@
         <v>997</v>
       </c>
       <c r="C974" t="s">
-        <v>2073</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="975" spans="1:3">
@@ -17660,7 +17642,7 @@
         <v>998</v>
       </c>
       <c r="C975" t="s">
-        <v>2074</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="976" spans="1:3">
@@ -17671,7 +17653,7 @@
         <v>999</v>
       </c>
       <c r="C976" t="s">
-        <v>2075</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="977" spans="1:3">
@@ -17682,7 +17664,7 @@
         <v>1000</v>
       </c>
       <c r="C977" t="s">
-        <v>2076</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="978" spans="1:3">
@@ -17693,7 +17675,7 @@
         <v>1001</v>
       </c>
       <c r="C978" t="s">
-        <v>2077</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="979" spans="1:3">
@@ -17704,7 +17686,7 @@
         <v>1002</v>
       </c>
       <c r="C979" t="s">
-        <v>2078</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="980" spans="1:3">
@@ -17715,7 +17697,7 @@
         <v>1003</v>
       </c>
       <c r="C980" t="s">
-        <v>2079</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="981" spans="1:3">
@@ -17726,7 +17708,7 @@
         <v>1004</v>
       </c>
       <c r="C981" t="s">
-        <v>2080</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="982" spans="1:3">
@@ -17737,7 +17719,7 @@
         <v>1005</v>
       </c>
       <c r="C982" t="s">
-        <v>2081</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="983" spans="1:3">
@@ -17748,7 +17730,7 @@
         <v>1006</v>
       </c>
       <c r="C983" t="s">
-        <v>2082</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="984" spans="1:3">
@@ -17759,7 +17741,7 @@
         <v>1007</v>
       </c>
       <c r="C984" t="s">
-        <v>2083</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="985" spans="1:3">
@@ -17770,7 +17752,7 @@
         <v>1008</v>
       </c>
       <c r="C985" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="986" spans="1:3">
@@ -17781,18 +17763,18 @@
         <v>1009</v>
       </c>
       <c r="C986" t="s">
-        <v>2085</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="987" spans="1:3">
       <c r="A987" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B987" t="s">
         <v>1010</v>
       </c>
       <c r="C987" t="s">
-        <v>2086</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="988" spans="1:3">
@@ -17803,7 +17785,7 @@
         <v>1011</v>
       </c>
       <c r="C988" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="989" spans="1:3">
@@ -17814,7 +17796,7 @@
         <v>1012</v>
       </c>
       <c r="C989" t="s">
-        <v>2088</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="990" spans="1:3">
@@ -17825,7 +17807,7 @@
         <v>1013</v>
       </c>
       <c r="C990" t="s">
-        <v>2089</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="991" spans="1:3">
@@ -17836,7 +17818,7 @@
         <v>1014</v>
       </c>
       <c r="C991" t="s">
-        <v>2090</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="992" spans="1:3">
@@ -17847,7 +17829,7 @@
         <v>1015</v>
       </c>
       <c r="C992" t="s">
-        <v>2091</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="993" spans="1:3">
@@ -17858,7 +17840,7 @@
         <v>1016</v>
       </c>
       <c r="C993" t="s">
-        <v>2092</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="994" spans="1:3">
@@ -17869,7 +17851,7 @@
         <v>1017</v>
       </c>
       <c r="C994" t="s">
-        <v>2093</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="995" spans="1:3">
@@ -17880,7 +17862,7 @@
         <v>1018</v>
       </c>
       <c r="C995" t="s">
-        <v>2094</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="996" spans="1:3">
@@ -17891,7 +17873,7 @@
         <v>1019</v>
       </c>
       <c r="C996" t="s">
-        <v>2095</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="997" spans="1:3">
@@ -17902,7 +17884,7 @@
         <v>1020</v>
       </c>
       <c r="C997" t="s">
-        <v>2096</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="998" spans="1:3">
@@ -17913,7 +17895,7 @@
         <v>1021</v>
       </c>
       <c r="C998" t="s">
-        <v>2097</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="999" spans="1:3">
@@ -17924,7 +17906,7 @@
         <v>1022</v>
       </c>
       <c r="C999" t="s">
-        <v>2098</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="1000" spans="1:3">
@@ -17935,7 +17917,7 @@
         <v>1023</v>
       </c>
       <c r="C1000" t="s">
-        <v>2099</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="1001" spans="1:3">
@@ -17946,7 +17928,7 @@
         <v>1024</v>
       </c>
       <c r="C1001" t="s">
-        <v>2100</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="1002" spans="1:3">
@@ -17957,7 +17939,7 @@
         <v>1025</v>
       </c>
       <c r="C1002" t="s">
-        <v>2101</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="1003" spans="1:3">
@@ -17968,7 +17950,7 @@
         <v>1026</v>
       </c>
       <c r="C1003" t="s">
-        <v>2102</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="1004" spans="1:3">
@@ -17979,7 +17961,7 @@
         <v>1027</v>
       </c>
       <c r="C1004" t="s">
-        <v>2103</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="1005" spans="1:3">
@@ -17990,7 +17972,7 @@
         <v>1028</v>
       </c>
       <c r="C1005" t="s">
-        <v>2104</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="1006" spans="1:3">
@@ -18001,7 +17983,7 @@
         <v>1029</v>
       </c>
       <c r="C1006" t="s">
-        <v>2105</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="1007" spans="1:3">
@@ -18012,7 +17994,7 @@
         <v>1030</v>
       </c>
       <c r="C1007" t="s">
-        <v>2106</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="1008" spans="1:3">
@@ -18023,7 +18005,7 @@
         <v>1031</v>
       </c>
       <c r="C1008" t="s">
-        <v>2107</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="1009" spans="1:3">
@@ -18034,7 +18016,7 @@
         <v>1032</v>
       </c>
       <c r="C1009" t="s">
-        <v>2108</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="1010" spans="1:3">
@@ -18045,7 +18027,7 @@
         <v>1033</v>
       </c>
       <c r="C1010" t="s">
-        <v>2109</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="1011" spans="1:3">
@@ -18056,7 +18038,7 @@
         <v>1034</v>
       </c>
       <c r="C1011" t="s">
-        <v>2110</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="1012" spans="1:3">
@@ -18067,7 +18049,7 @@
         <v>1035</v>
       </c>
       <c r="C1012" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="1013" spans="1:3">
@@ -18078,7 +18060,7 @@
         <v>1036</v>
       </c>
       <c r="C1013" t="s">
-        <v>2112</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="1014" spans="1:3">
@@ -18089,7 +18071,7 @@
         <v>1037</v>
       </c>
       <c r="C1014" t="s">
-        <v>2113</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="1015" spans="1:3">
@@ -18100,7 +18082,7 @@
         <v>1038</v>
       </c>
       <c r="C1015" t="s">
-        <v>2114</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="1016" spans="1:3">
@@ -18111,7 +18093,7 @@
         <v>1039</v>
       </c>
       <c r="C1016" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="1017" spans="1:3">
@@ -18122,7 +18104,7 @@
         <v>1040</v>
       </c>
       <c r="C1017" t="s">
-        <v>2116</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="1018" spans="1:3">
@@ -18133,7 +18115,7 @@
         <v>1041</v>
       </c>
       <c r="C1018" t="s">
-        <v>2117</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="1019" spans="1:3">
@@ -18144,7 +18126,7 @@
         <v>1042</v>
       </c>
       <c r="C1019" t="s">
-        <v>2118</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="1020" spans="1:3">
@@ -18155,7 +18137,7 @@
         <v>1043</v>
       </c>
       <c r="C1020" t="s">
-        <v>2119</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="1021" spans="1:3">
@@ -18166,7 +18148,7 @@
         <v>1044</v>
       </c>
       <c r="C1021" t="s">
-        <v>2120</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="1022" spans="1:3">
@@ -18177,7 +18159,7 @@
         <v>1045</v>
       </c>
       <c r="C1022" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="1023" spans="1:3">
@@ -18188,7 +18170,7 @@
         <v>1046</v>
       </c>
       <c r="C1023" t="s">
-        <v>2122</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="1024" spans="1:3">
@@ -18199,7 +18181,7 @@
         <v>1047</v>
       </c>
       <c r="C1024" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="1025" spans="1:3">
@@ -18210,7 +18192,7 @@
         <v>1048</v>
       </c>
       <c r="C1025" t="s">
-        <v>2124</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="1026" spans="1:3">
@@ -18221,7 +18203,7 @@
         <v>1049</v>
       </c>
       <c r="C1026" t="s">
-        <v>2125</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="1027" spans="1:3">
@@ -18232,7 +18214,7 @@
         <v>1050</v>
       </c>
       <c r="C1027" t="s">
-        <v>2126</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="1028" spans="1:3">
@@ -18243,7 +18225,7 @@
         <v>1051</v>
       </c>
       <c r="C1028" t="s">
-        <v>2119</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="1029" spans="1:3">
@@ -18254,7 +18236,7 @@
         <v>1052</v>
       </c>
       <c r="C1029" t="s">
-        <v>2127</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="1030" spans="1:3">
@@ -18265,7 +18247,7 @@
         <v>1053</v>
       </c>
       <c r="C1030" t="s">
-        <v>2128</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="1031" spans="1:3">
@@ -18276,7 +18258,7 @@
         <v>1054</v>
       </c>
       <c r="C1031" t="s">
-        <v>2129</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="1032" spans="1:3">
@@ -18287,7 +18269,7 @@
         <v>1055</v>
       </c>
       <c r="C1032" t="s">
-        <v>2130</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="1033" spans="1:3">
@@ -18298,7 +18280,7 @@
         <v>1056</v>
       </c>
       <c r="C1033" t="s">
-        <v>2131</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="1034" spans="1:3">
@@ -18309,7 +18291,7 @@
         <v>1057</v>
       </c>
       <c r="C1034" t="s">
-        <v>2132</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="1035" spans="1:3">
@@ -18320,7 +18302,7 @@
         <v>1058</v>
       </c>
       <c r="C1035" t="s">
-        <v>2133</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="1036" spans="1:3">
@@ -18331,7 +18313,7 @@
         <v>1059</v>
       </c>
       <c r="C1036" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="1037" spans="1:3">
@@ -18342,7 +18324,7 @@
         <v>1060</v>
       </c>
       <c r="C1037" t="s">
-        <v>2135</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="1038" spans="1:3">
@@ -18353,7 +18335,7 @@
         <v>1061</v>
       </c>
       <c r="C1038" t="s">
-        <v>2136</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="1039" spans="1:3">
@@ -18364,7 +18346,7 @@
         <v>1062</v>
       </c>
       <c r="C1039" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="1040" spans="1:3">
@@ -18375,7 +18357,7 @@
         <v>1063</v>
       </c>
       <c r="C1040" t="s">
-        <v>2138</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="1041" spans="1:3">
@@ -18386,7 +18368,7 @@
         <v>1064</v>
       </c>
       <c r="C1041" t="s">
-        <v>2139</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="1042" spans="1:3">
@@ -18397,7 +18379,7 @@
         <v>1065</v>
       </c>
       <c r="C1042" t="s">
-        <v>2140</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="1043" spans="1:3">
@@ -18408,7 +18390,7 @@
         <v>1066</v>
       </c>
       <c r="C1043" t="s">
-        <v>2141</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="1044" spans="1:3">
@@ -18419,7 +18401,7 @@
         <v>1067</v>
       </c>
       <c r="C1044" t="s">
-        <v>2142</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="1045" spans="1:3">
@@ -18430,7 +18412,7 @@
         <v>1068</v>
       </c>
       <c r="C1045" t="s">
-        <v>2143</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="1046" spans="1:3">
@@ -18441,7 +18423,7 @@
         <v>1069</v>
       </c>
       <c r="C1046" t="s">
-        <v>2144</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="1047" spans="1:3">
@@ -18452,7 +18434,7 @@
         <v>1070</v>
       </c>
       <c r="C1047" t="s">
-        <v>2145</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="1048" spans="1:3">
@@ -18463,7 +18445,7 @@
         <v>1071</v>
       </c>
       <c r="C1048" t="s">
-        <v>2146</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="1049" spans="1:3">
@@ -18474,7 +18456,7 @@
         <v>1072</v>
       </c>
       <c r="C1049" t="s">
-        <v>2147</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="1050" spans="1:3">
@@ -18485,7 +18467,7 @@
         <v>1073</v>
       </c>
       <c r="C1050" t="s">
-        <v>2148</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1051" spans="1:3">
@@ -18496,7 +18478,7 @@
         <v>1074</v>
       </c>
       <c r="C1051" t="s">
-        <v>2149</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="1052" spans="1:3">
@@ -18507,7 +18489,7 @@
         <v>1075</v>
       </c>
       <c r="C1052" t="s">
-        <v>2120</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="1053" spans="1:3">
@@ -18518,7 +18500,7 @@
         <v>1076</v>
       </c>
       <c r="C1053" t="s">
-        <v>2150</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="1054" spans="1:3">
@@ -18529,7 +18511,7 @@
         <v>1077</v>
       </c>
       <c r="C1054" t="s">
-        <v>2151</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="1055" spans="1:3">
@@ -18540,7 +18522,7 @@
         <v>1078</v>
       </c>
       <c r="C1055" t="s">
-        <v>2152</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="1056" spans="1:3">
@@ -18551,7 +18533,7 @@
         <v>1079</v>
       </c>
       <c r="C1056" t="s">
-        <v>2101</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1057" spans="1:3">
@@ -18562,7 +18544,7 @@
         <v>1080</v>
       </c>
       <c r="C1057" t="s">
-        <v>2153</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="1058" spans="1:3">
@@ -18573,7 +18555,7 @@
         <v>1081</v>
       </c>
       <c r="C1058" t="s">
-        <v>2154</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="1059" spans="1:3">
@@ -18584,7 +18566,7 @@
         <v>1082</v>
       </c>
       <c r="C1059" t="s">
-        <v>2155</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="1060" spans="1:3">
@@ -18595,40 +18577,40 @@
         <v>1083</v>
       </c>
       <c r="C1060" t="s">
-        <v>2156</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="1061" spans="1:3">
       <c r="A1061" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1061" t="s">
         <v>1084</v>
       </c>
       <c r="C1061" t="s">
-        <v>2157</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="1062" spans="1:3">
       <c r="A1062" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1062" t="s">
         <v>1085</v>
       </c>
       <c r="C1062" t="s">
-        <v>2158</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="1063" spans="1:3">
       <c r="A1063" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1063" t="s">
         <v>1086</v>
       </c>
       <c r="C1063" t="s">
-        <v>2159</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="1064" spans="1:3">
@@ -18639,7 +18621,7 @@
         <v>1087</v>
       </c>
       <c r="C1064" t="s">
-        <v>2160</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="1065" spans="1:3">
@@ -18650,7 +18632,7 @@
         <v>1088</v>
       </c>
       <c r="C1065" t="s">
-        <v>2161</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="1066" spans="1:3">
@@ -18661,7 +18643,7 @@
         <v>1089</v>
       </c>
       <c r="C1066" t="s">
-        <v>2162</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="1067" spans="1:3">
@@ -18672,7 +18654,7 @@
         <v>1090</v>
       </c>
       <c r="C1067" t="s">
-        <v>2163</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="1068" spans="1:3">
@@ -18683,7 +18665,7 @@
         <v>1091</v>
       </c>
       <c r="C1068" t="s">
-        <v>2164</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="1069" spans="1:3">
@@ -18694,7 +18676,7 @@
         <v>1092</v>
       </c>
       <c r="C1069" t="s">
-        <v>2165</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="1070" spans="1:3">
@@ -18705,7 +18687,7 @@
         <v>1093</v>
       </c>
       <c r="C1070" t="s">
-        <v>2166</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="1071" spans="1:3">
@@ -18716,7 +18698,7 @@
         <v>1094</v>
       </c>
       <c r="C1071" t="s">
-        <v>2167</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="1072" spans="1:3">
@@ -18727,7 +18709,7 @@
         <v>1095</v>
       </c>
       <c r="C1072" t="s">
-        <v>2168</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="1073" spans="1:3">
@@ -18738,7 +18720,7 @@
         <v>1096</v>
       </c>
       <c r="C1073" t="s">
-        <v>2169</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="1074" spans="1:3">
@@ -18749,7 +18731,7 @@
         <v>1097</v>
       </c>
       <c r="C1074" t="s">
-        <v>2170</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="1075" spans="1:3">
@@ -18760,7 +18742,7 @@
         <v>1098</v>
       </c>
       <c r="C1075" t="s">
-        <v>2171</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="1076" spans="1:3">
@@ -18771,7 +18753,7 @@
         <v>1099</v>
       </c>
       <c r="C1076" t="s">
-        <v>2172</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="1077" spans="1:3">
@@ -18782,7 +18764,7 @@
         <v>1100</v>
       </c>
       <c r="C1077" t="s">
-        <v>2173</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="1078" spans="1:3">
@@ -18793,7 +18775,7 @@
         <v>1101</v>
       </c>
       <c r="C1078" t="s">
-        <v>2174</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="1079" spans="1:3">
@@ -18804,7 +18786,7 @@
         <v>1102</v>
       </c>
       <c r="C1079" t="s">
-        <v>2175</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="1080" spans="1:3">
@@ -18815,7 +18797,7 @@
         <v>1103</v>
       </c>
       <c r="C1080" t="s">
-        <v>2176</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="1081" spans="1:3">
@@ -18826,7 +18808,7 @@
         <v>1104</v>
       </c>
       <c r="C1081" t="s">
-        <v>2177</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="1082" spans="1:3">
@@ -18837,7 +18819,7 @@
         <v>1105</v>
       </c>
       <c r="C1082" t="s">
-        <v>2178</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="1083" spans="1:3">
@@ -18848,7 +18830,7 @@
         <v>1106</v>
       </c>
       <c r="C1083" t="s">
-        <v>2179</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="1084" spans="1:3">
@@ -18859,7 +18841,7 @@
         <v>1107</v>
       </c>
       <c r="C1084" t="s">
-        <v>2180</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="1085" spans="1:3">
@@ -18870,7 +18852,7 @@
         <v>1108</v>
       </c>
       <c r="C1085" t="s">
-        <v>2181</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="1086" spans="1:3">
@@ -18881,7 +18863,7 @@
         <v>1109</v>
       </c>
       <c r="C1086" t="s">
-        <v>2182</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="1087" spans="1:3">
@@ -18892,51 +18874,18 @@
         <v>1110</v>
       </c>
       <c r="C1087" t="s">
-        <v>2183</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="1088" spans="1:3">
       <c r="A1088" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1088" t="s">
         <v>1111</v>
       </c>
       <c r="C1088" t="s">
-        <v>2184</v>
-      </c>
-    </row>
-    <row r="1089" spans="1:3">
-      <c r="A1089" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1089" t="s">
-        <v>1112</v>
-      </c>
-      <c r="C1089" t="s">
-        <v>2185</v>
-      </c>
-    </row>
-    <row r="1090" spans="1:3">
-      <c r="A1090" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1090" t="s">
-        <v>1113</v>
-      </c>
-      <c r="C1090" t="s">
-        <v>2186</v>
-      </c>
-    </row>
-    <row r="1091" spans="1:3">
-      <c r="A1091" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1091" t="s">
-        <v>1114</v>
-      </c>
-      <c r="C1091" t="s">
-        <v>2187</v>
+        <v>2181</v>
       </c>
     </row>
   </sheetData>

--- a/faltantes_por_estados.xlsx
+++ b/faltantes_por_estados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3228" uniqueCount="2158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3222" uniqueCount="2154">
   <si>
     <t>entidad</t>
   </si>
@@ -319,9 +319,6 @@
     <t>BSIMB000136</t>
   </si>
   <si>
-    <t>BSIMB000153</t>
-  </si>
-  <si>
     <t>BSIMB000165</t>
   </si>
   <si>
@@ -397,9 +394,6 @@
     <t>BSIMB000450</t>
   </si>
   <si>
-    <t>BSIMB000462</t>
-  </si>
-  <si>
     <t>BSIMB000474</t>
   </si>
   <si>
@@ -3529,9 +3523,6 @@
     <t>CENTRO DE SALUD BAHÍA TORTUGAS</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD GUSTAVO DÍAZ ORDAZ</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD HEROICA MULEGÉ</t>
   </si>
   <si>
@@ -3605,9 +3596,6 @@
   </si>
   <si>
     <t>CENTRO DE SALUD LOMAS DEL SOL, CABO SAN LUCAS</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD LOS CANGREJOS, CABO SAN LUCAS</t>
   </si>
   <si>
     <t>CENTRO DE SALUD EL ZACATAL</t>
@@ -6845,7 +6833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1076"/>
+  <dimension ref="A1:C1074"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6867,7 +6855,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6878,7 +6866,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6889,7 +6877,7 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6900,7 +6888,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6911,7 +6899,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6922,7 +6910,7 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6933,7 +6921,7 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6944,7 +6932,7 @@
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6955,7 +6943,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6966,7 +6954,7 @@
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6977,7 +6965,7 @@
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6988,7 +6976,7 @@
         <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6999,7 +6987,7 @@
         <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -7010,7 +6998,7 @@
         <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7021,7 +7009,7 @@
         <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -7043,7 +7031,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -7054,7 +7042,7 @@
         <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -7065,7 +7053,7 @@
         <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -7076,7 +7064,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -7087,7 +7075,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -7098,7 +7086,7 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -7109,7 +7097,7 @@
         <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -7120,7 +7108,7 @@
         <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -7131,7 +7119,7 @@
         <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -7153,7 +7141,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -7175,7 +7163,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -7186,7 +7174,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -7197,7 +7185,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -7208,7 +7196,7 @@
         <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -7219,7 +7207,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -7230,7 +7218,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -7241,7 +7229,7 @@
         <v>59</v>
       </c>
       <c r="C36" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -7252,7 +7240,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -7263,7 +7251,7 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -7274,7 +7262,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -7285,7 +7273,7 @@
         <v>63</v>
       </c>
       <c r="C40" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -7296,7 +7284,7 @@
         <v>64</v>
       </c>
       <c r="C41" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -7307,7 +7295,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -7318,7 +7306,7 @@
         <v>66</v>
       </c>
       <c r="C43" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -7329,7 +7317,7 @@
         <v>67</v>
       </c>
       <c r="C44" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -7340,7 +7328,7 @@
         <v>68</v>
       </c>
       <c r="C45" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -7351,7 +7339,7 @@
         <v>69</v>
       </c>
       <c r="C46" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -7362,7 +7350,7 @@
         <v>70</v>
       </c>
       <c r="C47" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -7373,7 +7361,7 @@
         <v>71</v>
       </c>
       <c r="C48" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -7384,7 +7372,7 @@
         <v>72</v>
       </c>
       <c r="C49" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -7395,7 +7383,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -7406,7 +7394,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -7417,7 +7405,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -7428,7 +7416,7 @@
         <v>76</v>
       </c>
       <c r="C53" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -7439,7 +7427,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -7450,7 +7438,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -7461,7 +7449,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -7472,7 +7460,7 @@
         <v>80</v>
       </c>
       <c r="C57" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -7483,7 +7471,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -7494,7 +7482,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -7516,7 +7504,7 @@
         <v>84</v>
       </c>
       <c r="C61" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -7527,7 +7515,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -7538,7 +7526,7 @@
         <v>86</v>
       </c>
       <c r="C63" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -7549,7 +7537,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -7560,7 +7548,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -7571,7 +7559,7 @@
         <v>89</v>
       </c>
       <c r="C66" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -7582,7 +7570,7 @@
         <v>90</v>
       </c>
       <c r="C67" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -7593,7 +7581,7 @@
         <v>91</v>
       </c>
       <c r="C68" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -7604,7 +7592,7 @@
         <v>92</v>
       </c>
       <c r="C69" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -7615,7 +7603,7 @@
         <v>93</v>
       </c>
       <c r="C70" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -7626,7 +7614,7 @@
         <v>94</v>
       </c>
       <c r="C71" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -7637,7 +7625,7 @@
         <v>95</v>
       </c>
       <c r="C72" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -7648,7 +7636,7 @@
         <v>96</v>
       </c>
       <c r="C73" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -7659,7 +7647,7 @@
         <v>97</v>
       </c>
       <c r="C74" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -7670,7 +7658,7 @@
         <v>98</v>
       </c>
       <c r="C75" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -7681,7 +7669,7 @@
         <v>99</v>
       </c>
       <c r="C76" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -7692,7 +7680,7 @@
         <v>100</v>
       </c>
       <c r="C77" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -7703,7 +7691,7 @@
         <v>101</v>
       </c>
       <c r="C78" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -7714,7 +7702,7 @@
         <v>102</v>
       </c>
       <c r="C79" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -7725,7 +7713,7 @@
         <v>103</v>
       </c>
       <c r="C80" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -7736,7 +7724,7 @@
         <v>104</v>
       </c>
       <c r="C81" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -7747,7 +7735,7 @@
         <v>105</v>
       </c>
       <c r="C82" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -7758,7 +7746,7 @@
         <v>106</v>
       </c>
       <c r="C83" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -7769,7 +7757,7 @@
         <v>107</v>
       </c>
       <c r="C84" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -7780,7 +7768,7 @@
         <v>108</v>
       </c>
       <c r="C85" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -7791,7 +7779,7 @@
         <v>109</v>
       </c>
       <c r="C86" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -7802,7 +7790,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -7813,7 +7801,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -7824,7 +7812,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -7835,7 +7823,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -7846,7 +7834,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -7857,7 +7845,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -7868,7 +7856,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -7879,7 +7867,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -7890,7 +7878,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -7901,7 +7889,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -7912,7 +7900,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -7923,7 +7911,7 @@
         <v>121</v>
       </c>
       <c r="C98" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -7934,7 +7922,7 @@
         <v>122</v>
       </c>
       <c r="C99" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -7945,7 +7933,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -7956,7 +7944,7 @@
         <v>124</v>
       </c>
       <c r="C101" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -7967,7 +7955,7 @@
         <v>125</v>
       </c>
       <c r="C102" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -7978,7 +7966,7 @@
         <v>126</v>
       </c>
       <c r="C103" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -7989,7 +7977,7 @@
         <v>127</v>
       </c>
       <c r="C104" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -8000,7 +7988,7 @@
         <v>128</v>
       </c>
       <c r="C105" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -8011,7 +7999,7 @@
         <v>129</v>
       </c>
       <c r="C106" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -8022,7 +8010,7 @@
         <v>130</v>
       </c>
       <c r="C107" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -8033,7 +8021,7 @@
         <v>131</v>
       </c>
       <c r="C108" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -8044,7 +8032,7 @@
         <v>132</v>
       </c>
       <c r="C109" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -8055,7 +8043,7 @@
         <v>133</v>
       </c>
       <c r="C110" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -8066,7 +8054,7 @@
         <v>134</v>
       </c>
       <c r="C111" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -8077,7 +8065,7 @@
         <v>135</v>
       </c>
       <c r="C112" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -8088,7 +8076,7 @@
         <v>136</v>
       </c>
       <c r="C113" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -8099,29 +8087,29 @@
         <v>137</v>
       </c>
       <c r="C114" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B115" t="s">
         <v>138</v>
       </c>
       <c r="C115" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B116" t="s">
         <v>139</v>
       </c>
       <c r="C116" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -8132,7 +8120,7 @@
         <v>140</v>
       </c>
       <c r="C117" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -8143,7 +8131,7 @@
         <v>141</v>
       </c>
       <c r="C118" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -8154,7 +8142,7 @@
         <v>142</v>
       </c>
       <c r="C119" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -8165,7 +8153,7 @@
         <v>143</v>
       </c>
       <c r="C120" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -8176,7 +8164,7 @@
         <v>144</v>
       </c>
       <c r="C121" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -8187,7 +8175,7 @@
         <v>145</v>
       </c>
       <c r="C122" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -8198,7 +8186,7 @@
         <v>146</v>
       </c>
       <c r="C123" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -8209,7 +8197,7 @@
         <v>147</v>
       </c>
       <c r="C124" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -8220,7 +8208,7 @@
         <v>148</v>
       </c>
       <c r="C125" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -8231,7 +8219,7 @@
         <v>149</v>
       </c>
       <c r="C126" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -8242,7 +8230,7 @@
         <v>150</v>
       </c>
       <c r="C127" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -8253,7 +8241,7 @@
         <v>151</v>
       </c>
       <c r="C128" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -8264,40 +8252,40 @@
         <v>152</v>
       </c>
       <c r="C129" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B130" t="s">
         <v>153</v>
       </c>
       <c r="C130" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B131" t="s">
         <v>154</v>
       </c>
       <c r="C131" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B132" t="s">
         <v>155</v>
       </c>
       <c r="C132" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -8308,7 +8296,7 @@
         <v>156</v>
       </c>
       <c r="C133" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -8319,7 +8307,7 @@
         <v>157</v>
       </c>
       <c r="C134" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -8330,7 +8318,7 @@
         <v>158</v>
       </c>
       <c r="C135" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -8341,7 +8329,7 @@
         <v>159</v>
       </c>
       <c r="C136" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -8352,7 +8340,7 @@
         <v>160</v>
       </c>
       <c r="C137" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -8363,7 +8351,7 @@
         <v>161</v>
       </c>
       <c r="C138" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -8374,7 +8362,7 @@
         <v>162</v>
       </c>
       <c r="C139" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -8385,7 +8373,7 @@
         <v>163</v>
       </c>
       <c r="C140" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -8396,7 +8384,7 @@
         <v>164</v>
       </c>
       <c r="C141" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -8407,7 +8395,7 @@
         <v>165</v>
       </c>
       <c r="C142" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -8418,7 +8406,7 @@
         <v>166</v>
       </c>
       <c r="C143" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -8429,7 +8417,7 @@
         <v>167</v>
       </c>
       <c r="C144" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -8440,7 +8428,7 @@
         <v>168</v>
       </c>
       <c r="C145" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -8451,7 +8439,7 @@
         <v>169</v>
       </c>
       <c r="C146" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -8462,7 +8450,7 @@
         <v>170</v>
       </c>
       <c r="C147" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -8473,7 +8461,7 @@
         <v>171</v>
       </c>
       <c r="C148" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -8484,7 +8472,7 @@
         <v>172</v>
       </c>
       <c r="C149" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -8495,7 +8483,7 @@
         <v>173</v>
       </c>
       <c r="C150" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -8506,7 +8494,7 @@
         <v>174</v>
       </c>
       <c r="C151" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -8517,7 +8505,7 @@
         <v>175</v>
       </c>
       <c r="C152" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -8528,7 +8516,7 @@
         <v>176</v>
       </c>
       <c r="C153" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -8539,7 +8527,7 @@
         <v>177</v>
       </c>
       <c r="C154" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -8550,7 +8538,7 @@
         <v>178</v>
       </c>
       <c r="C155" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -8561,7 +8549,7 @@
         <v>179</v>
       </c>
       <c r="C156" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -8572,7 +8560,7 @@
         <v>180</v>
       </c>
       <c r="C157" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -8583,7 +8571,7 @@
         <v>181</v>
       </c>
       <c r="C158" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -8594,7 +8582,7 @@
         <v>182</v>
       </c>
       <c r="C159" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -8605,7 +8593,7 @@
         <v>183</v>
       </c>
       <c r="C160" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -8616,7 +8604,7 @@
         <v>184</v>
       </c>
       <c r="C161" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -8627,7 +8615,7 @@
         <v>185</v>
       </c>
       <c r="C162" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -8638,7 +8626,7 @@
         <v>186</v>
       </c>
       <c r="C163" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -8649,7 +8637,7 @@
         <v>187</v>
       </c>
       <c r="C164" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -8660,7 +8648,7 @@
         <v>188</v>
       </c>
       <c r="C165" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -8671,7 +8659,7 @@
         <v>189</v>
       </c>
       <c r="C166" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -8682,7 +8670,7 @@
         <v>190</v>
       </c>
       <c r="C167" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -8693,7 +8681,7 @@
         <v>191</v>
       </c>
       <c r="C168" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -8704,7 +8692,7 @@
         <v>192</v>
       </c>
       <c r="C169" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -8715,7 +8703,7 @@
         <v>193</v>
       </c>
       <c r="C170" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -8726,7 +8714,7 @@
         <v>194</v>
       </c>
       <c r="C171" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -8737,7 +8725,7 @@
         <v>195</v>
       </c>
       <c r="C172" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -8748,7 +8736,7 @@
         <v>196</v>
       </c>
       <c r="C173" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -8759,7 +8747,7 @@
         <v>197</v>
       </c>
       <c r="C174" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -8770,7 +8758,7 @@
         <v>198</v>
       </c>
       <c r="C175" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -8781,7 +8769,7 @@
         <v>199</v>
       </c>
       <c r="C176" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -8792,7 +8780,7 @@
         <v>200</v>
       </c>
       <c r="C177" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -8803,7 +8791,7 @@
         <v>201</v>
       </c>
       <c r="C178" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -8814,7 +8802,7 @@
         <v>202</v>
       </c>
       <c r="C179" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -8825,7 +8813,7 @@
         <v>203</v>
       </c>
       <c r="C180" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -8836,7 +8824,7 @@
         <v>204</v>
       </c>
       <c r="C181" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -8847,7 +8835,7 @@
         <v>205</v>
       </c>
       <c r="C182" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -8858,7 +8846,7 @@
         <v>206</v>
       </c>
       <c r="C183" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -8869,7 +8857,7 @@
         <v>207</v>
       </c>
       <c r="C184" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -8880,7 +8868,7 @@
         <v>208</v>
       </c>
       <c r="C185" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -8891,7 +8879,7 @@
         <v>209</v>
       </c>
       <c r="C186" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -8902,7 +8890,7 @@
         <v>210</v>
       </c>
       <c r="C187" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -8913,7 +8901,7 @@
         <v>211</v>
       </c>
       <c r="C188" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -8924,7 +8912,7 @@
         <v>212</v>
       </c>
       <c r="C189" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -8935,7 +8923,7 @@
         <v>213</v>
       </c>
       <c r="C190" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -8946,7 +8934,7 @@
         <v>214</v>
       </c>
       <c r="C191" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -8957,7 +8945,7 @@
         <v>215</v>
       </c>
       <c r="C192" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -8968,7 +8956,7 @@
         <v>216</v>
       </c>
       <c r="C193" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -8979,7 +8967,7 @@
         <v>217</v>
       </c>
       <c r="C194" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -8990,7 +8978,7 @@
         <v>218</v>
       </c>
       <c r="C195" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -9001,7 +8989,7 @@
         <v>219</v>
       </c>
       <c r="C196" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -9012,7 +9000,7 @@
         <v>220</v>
       </c>
       <c r="C197" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -9023,7 +9011,7 @@
         <v>221</v>
       </c>
       <c r="C198" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -9034,7 +9022,7 @@
         <v>222</v>
       </c>
       <c r="C199" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -9045,7 +9033,7 @@
         <v>223</v>
       </c>
       <c r="C200" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -9056,7 +9044,7 @@
         <v>224</v>
       </c>
       <c r="C201" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -9067,7 +9055,7 @@
         <v>225</v>
       </c>
       <c r="C202" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -9078,7 +9066,7 @@
         <v>226</v>
       </c>
       <c r="C203" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -9089,7 +9077,7 @@
         <v>227</v>
       </c>
       <c r="C204" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -9100,7 +9088,7 @@
         <v>228</v>
       </c>
       <c r="C205" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -9111,7 +9099,7 @@
         <v>229</v>
       </c>
       <c r="C206" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -9122,7 +9110,7 @@
         <v>230</v>
       </c>
       <c r="C207" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -9133,7 +9121,7 @@
         <v>231</v>
       </c>
       <c r="C208" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -9144,7 +9132,7 @@
         <v>232</v>
       </c>
       <c r="C209" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -9155,7 +9143,7 @@
         <v>233</v>
       </c>
       <c r="C210" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -9166,7 +9154,7 @@
         <v>234</v>
       </c>
       <c r="C211" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -9177,7 +9165,7 @@
         <v>235</v>
       </c>
       <c r="C212" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -9188,7 +9176,7 @@
         <v>236</v>
       </c>
       <c r="C213" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -9199,7 +9187,7 @@
         <v>237</v>
       </c>
       <c r="C214" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -9210,7 +9198,7 @@
         <v>238</v>
       </c>
       <c r="C215" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -9221,7 +9209,7 @@
         <v>239</v>
       </c>
       <c r="C216" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -9232,7 +9220,7 @@
         <v>240</v>
       </c>
       <c r="C217" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -9243,7 +9231,7 @@
         <v>241</v>
       </c>
       <c r="C218" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -9254,7 +9242,7 @@
         <v>242</v>
       </c>
       <c r="C219" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -9265,7 +9253,7 @@
         <v>243</v>
       </c>
       <c r="C220" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -9276,7 +9264,7 @@
         <v>244</v>
       </c>
       <c r="C221" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -9287,7 +9275,7 @@
         <v>245</v>
       </c>
       <c r="C222" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -9298,7 +9286,7 @@
         <v>246</v>
       </c>
       <c r="C223" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -9309,7 +9297,7 @@
         <v>247</v>
       </c>
       <c r="C224" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -9320,7 +9308,7 @@
         <v>248</v>
       </c>
       <c r="C225" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -9331,7 +9319,7 @@
         <v>249</v>
       </c>
       <c r="C226" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -9342,7 +9330,7 @@
         <v>250</v>
       </c>
       <c r="C227" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -9353,7 +9341,7 @@
         <v>251</v>
       </c>
       <c r="C228" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -9364,7 +9352,7 @@
         <v>252</v>
       </c>
       <c r="C229" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -9375,7 +9363,7 @@
         <v>253</v>
       </c>
       <c r="C230" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -9386,7 +9374,7 @@
         <v>254</v>
       </c>
       <c r="C231" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -9397,7 +9385,7 @@
         <v>255</v>
       </c>
       <c r="C232" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -9408,7 +9396,7 @@
         <v>256</v>
       </c>
       <c r="C233" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -9419,7 +9407,7 @@
         <v>257</v>
       </c>
       <c r="C234" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -9430,7 +9418,7 @@
         <v>258</v>
       </c>
       <c r="C235" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -9441,7 +9429,7 @@
         <v>259</v>
       </c>
       <c r="C236" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -9452,7 +9440,7 @@
         <v>260</v>
       </c>
       <c r="C237" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -9463,7 +9451,7 @@
         <v>261</v>
       </c>
       <c r="C238" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -9474,7 +9462,7 @@
         <v>262</v>
       </c>
       <c r="C239" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -9485,7 +9473,7 @@
         <v>263</v>
       </c>
       <c r="C240" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -9496,7 +9484,7 @@
         <v>264</v>
       </c>
       <c r="C241" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -9507,7 +9495,7 @@
         <v>265</v>
       </c>
       <c r="C242" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -9518,7 +9506,7 @@
         <v>266</v>
       </c>
       <c r="C243" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -9529,7 +9517,7 @@
         <v>267</v>
       </c>
       <c r="C244" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -9540,7 +9528,7 @@
         <v>268</v>
       </c>
       <c r="C245" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -9551,7 +9539,7 @@
         <v>269</v>
       </c>
       <c r="C246" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -9562,7 +9550,7 @@
         <v>270</v>
       </c>
       <c r="C247" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -9573,7 +9561,7 @@
         <v>271</v>
       </c>
       <c r="C248" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -9584,7 +9572,7 @@
         <v>272</v>
       </c>
       <c r="C249" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -9595,7 +9583,7 @@
         <v>273</v>
       </c>
       <c r="C250" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -9606,7 +9594,7 @@
         <v>274</v>
       </c>
       <c r="C251" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -9617,7 +9605,7 @@
         <v>275</v>
       </c>
       <c r="C252" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -9628,7 +9616,7 @@
         <v>276</v>
       </c>
       <c r="C253" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -9639,7 +9627,7 @@
         <v>277</v>
       </c>
       <c r="C254" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -9650,7 +9638,7 @@
         <v>278</v>
       </c>
       <c r="C255" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -9661,7 +9649,7 @@
         <v>279</v>
       </c>
       <c r="C256" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -9672,7 +9660,7 @@
         <v>280</v>
       </c>
       <c r="C257" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -9683,7 +9671,7 @@
         <v>281</v>
       </c>
       <c r="C258" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="259" spans="1:3">
@@ -9694,7 +9682,7 @@
         <v>282</v>
       </c>
       <c r="C259" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -9705,7 +9693,7 @@
         <v>283</v>
       </c>
       <c r="C260" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="261" spans="1:3">
@@ -9716,7 +9704,7 @@
         <v>284</v>
       </c>
       <c r="C261" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="262" spans="1:3">
@@ -9727,7 +9715,7 @@
         <v>285</v>
       </c>
       <c r="C262" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -9738,7 +9726,7 @@
         <v>286</v>
       </c>
       <c r="C263" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="264" spans="1:3">
@@ -9749,7 +9737,7 @@
         <v>287</v>
       </c>
       <c r="C264" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -9760,7 +9748,7 @@
         <v>288</v>
       </c>
       <c r="C265" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="266" spans="1:3">
@@ -9771,7 +9759,7 @@
         <v>289</v>
       </c>
       <c r="C266" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="267" spans="1:3">
@@ -9782,7 +9770,7 @@
         <v>290</v>
       </c>
       <c r="C267" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="268" spans="1:3">
@@ -9793,7 +9781,7 @@
         <v>291</v>
       </c>
       <c r="C268" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="269" spans="1:3">
@@ -9804,7 +9792,7 @@
         <v>292</v>
       </c>
       <c r="C269" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="270" spans="1:3">
@@ -9815,7 +9803,7 @@
         <v>293</v>
       </c>
       <c r="C270" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="271" spans="1:3">
@@ -9826,7 +9814,7 @@
         <v>294</v>
       </c>
       <c r="C271" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="272" spans="1:3">
@@ -9837,7 +9825,7 @@
         <v>295</v>
       </c>
       <c r="C272" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="273" spans="1:3">
@@ -9848,7 +9836,7 @@
         <v>296</v>
       </c>
       <c r="C273" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="274" spans="1:3">
@@ -9859,7 +9847,7 @@
         <v>297</v>
       </c>
       <c r="C274" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="275" spans="1:3">
@@ -9870,7 +9858,7 @@
         <v>298</v>
       </c>
       <c r="C275" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="276" spans="1:3">
@@ -9881,7 +9869,7 @@
         <v>299</v>
       </c>
       <c r="C276" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="277" spans="1:3">
@@ -9892,7 +9880,7 @@
         <v>300</v>
       </c>
       <c r="C277" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="278" spans="1:3">
@@ -9903,7 +9891,7 @@
         <v>301</v>
       </c>
       <c r="C278" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="279" spans="1:3">
@@ -9914,7 +9902,7 @@
         <v>302</v>
       </c>
       <c r="C279" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="280" spans="1:3">
@@ -9925,7 +9913,7 @@
         <v>303</v>
       </c>
       <c r="C280" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -9936,7 +9924,7 @@
         <v>304</v>
       </c>
       <c r="C281" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="282" spans="1:3">
@@ -9947,7 +9935,7 @@
         <v>305</v>
       </c>
       <c r="C282" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="283" spans="1:3">
@@ -9958,7 +9946,7 @@
         <v>306</v>
       </c>
       <c r="C283" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="284" spans="1:3">
@@ -9969,7 +9957,7 @@
         <v>307</v>
       </c>
       <c r="C284" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="285" spans="1:3">
@@ -9980,7 +9968,7 @@
         <v>308</v>
       </c>
       <c r="C285" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="286" spans="1:3">
@@ -9991,7 +9979,7 @@
         <v>309</v>
       </c>
       <c r="C286" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="287" spans="1:3">
@@ -10002,7 +9990,7 @@
         <v>310</v>
       </c>
       <c r="C287" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="288" spans="1:3">
@@ -10013,7 +10001,7 @@
         <v>311</v>
       </c>
       <c r="C288" t="s">
-        <v>1381</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="289" spans="1:3">
@@ -10024,7 +10012,7 @@
         <v>312</v>
       </c>
       <c r="C289" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="290" spans="1:3">
@@ -10035,7 +10023,7 @@
         <v>313</v>
       </c>
       <c r="C290" t="s">
-        <v>1300</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="291" spans="1:3">
@@ -10046,7 +10034,7 @@
         <v>314</v>
       </c>
       <c r="C291" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="292" spans="1:3">
@@ -10057,7 +10045,7 @@
         <v>315</v>
       </c>
       <c r="C292" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="293" spans="1:3">
@@ -10068,7 +10056,7 @@
         <v>316</v>
       </c>
       <c r="C293" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="294" spans="1:3">
@@ -10079,7 +10067,7 @@
         <v>317</v>
       </c>
       <c r="C294" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="295" spans="1:3">
@@ -10090,7 +10078,7 @@
         <v>318</v>
       </c>
       <c r="C295" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="296" spans="1:3">
@@ -10101,7 +10089,7 @@
         <v>319</v>
       </c>
       <c r="C296" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="297" spans="1:3">
@@ -10112,7 +10100,7 @@
         <v>320</v>
       </c>
       <c r="C297" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="298" spans="1:3">
@@ -10123,7 +10111,7 @@
         <v>321</v>
       </c>
       <c r="C298" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="299" spans="1:3">
@@ -10134,7 +10122,7 @@
         <v>322</v>
       </c>
       <c r="C299" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="300" spans="1:3">
@@ -10145,7 +10133,7 @@
         <v>323</v>
       </c>
       <c r="C300" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="301" spans="1:3">
@@ -10156,7 +10144,7 @@
         <v>324</v>
       </c>
       <c r="C301" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -10167,7 +10155,7 @@
         <v>325</v>
       </c>
       <c r="C302" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="303" spans="1:3">
@@ -10178,7 +10166,7 @@
         <v>326</v>
       </c>
       <c r="C303" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="304" spans="1:3">
@@ -10189,7 +10177,7 @@
         <v>327</v>
       </c>
       <c r="C304" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -10200,7 +10188,7 @@
         <v>328</v>
       </c>
       <c r="C305" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="306" spans="1:3">
@@ -10211,7 +10199,7 @@
         <v>329</v>
       </c>
       <c r="C306" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="307" spans="1:3">
@@ -10222,7 +10210,7 @@
         <v>330</v>
       </c>
       <c r="C307" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="308" spans="1:3">
@@ -10233,7 +10221,7 @@
         <v>331</v>
       </c>
       <c r="C308" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="309" spans="1:3">
@@ -10244,7 +10232,7 @@
         <v>332</v>
       </c>
       <c r="C309" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="310" spans="1:3">
@@ -10255,7 +10243,7 @@
         <v>333</v>
       </c>
       <c r="C310" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="311" spans="1:3">
@@ -10266,7 +10254,7 @@
         <v>334</v>
       </c>
       <c r="C311" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="312" spans="1:3">
@@ -10277,7 +10265,7 @@
         <v>335</v>
       </c>
       <c r="C312" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="313" spans="1:3">
@@ -10288,7 +10276,7 @@
         <v>336</v>
       </c>
       <c r="C313" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="314" spans="1:3">
@@ -10299,7 +10287,7 @@
         <v>337</v>
       </c>
       <c r="C314" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="315" spans="1:3">
@@ -10310,7 +10298,7 @@
         <v>338</v>
       </c>
       <c r="C315" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="316" spans="1:3">
@@ -10321,7 +10309,7 @@
         <v>339</v>
       </c>
       <c r="C316" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="317" spans="1:3">
@@ -10332,7 +10320,7 @@
         <v>340</v>
       </c>
       <c r="C317" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="318" spans="1:3">
@@ -10343,7 +10331,7 @@
         <v>341</v>
       </c>
       <c r="C318" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="319" spans="1:3">
@@ -10354,7 +10342,7 @@
         <v>342</v>
       </c>
       <c r="C319" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="320" spans="1:3">
@@ -10365,7 +10353,7 @@
         <v>343</v>
       </c>
       <c r="C320" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="321" spans="1:3">
@@ -10376,7 +10364,7 @@
         <v>344</v>
       </c>
       <c r="C321" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -10387,29 +10375,29 @@
         <v>345</v>
       </c>
       <c r="C322" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="323" spans="1:3">
       <c r="A323" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B323" t="s">
         <v>346</v>
       </c>
       <c r="C323" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="324" spans="1:3">
       <c r="A324" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B324" t="s">
         <v>347</v>
       </c>
       <c r="C324" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -10420,7 +10408,7 @@
         <v>348</v>
       </c>
       <c r="C325" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="326" spans="1:3">
@@ -10431,7 +10419,7 @@
         <v>349</v>
       </c>
       <c r="C326" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="327" spans="1:3">
@@ -10442,7 +10430,7 @@
         <v>350</v>
       </c>
       <c r="C327" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="328" spans="1:3">
@@ -10453,7 +10441,7 @@
         <v>351</v>
       </c>
       <c r="C328" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="329" spans="1:3">
@@ -10464,7 +10452,7 @@
         <v>352</v>
       </c>
       <c r="C329" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="330" spans="1:3">
@@ -10475,7 +10463,7 @@
         <v>353</v>
       </c>
       <c r="C330" t="s">
-        <v>1422</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -10486,7 +10474,7 @@
         <v>354</v>
       </c>
       <c r="C331" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="332" spans="1:3">
@@ -10497,7 +10485,7 @@
         <v>355</v>
       </c>
       <c r="C332" t="s">
-        <v>1194</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="333" spans="1:3">
@@ -10508,7 +10496,7 @@
         <v>356</v>
       </c>
       <c r="C333" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="334" spans="1:3">
@@ -10519,7 +10507,7 @@
         <v>357</v>
       </c>
       <c r="C334" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="335" spans="1:3">
@@ -10530,7 +10518,7 @@
         <v>358</v>
       </c>
       <c r="C335" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="336" spans="1:3">
@@ -10541,7 +10529,7 @@
         <v>359</v>
       </c>
       <c r="C336" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="337" spans="1:3">
@@ -10552,7 +10540,7 @@
         <v>360</v>
       </c>
       <c r="C337" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="338" spans="1:3">
@@ -10563,7 +10551,7 @@
         <v>361</v>
       </c>
       <c r="C338" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="339" spans="1:3">
@@ -10574,7 +10562,7 @@
         <v>362</v>
       </c>
       <c r="C339" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="340" spans="1:3">
@@ -10585,7 +10573,7 @@
         <v>363</v>
       </c>
       <c r="C340" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="341" spans="1:3">
@@ -10596,7 +10584,7 @@
         <v>364</v>
       </c>
       <c r="C341" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -10607,7 +10595,7 @@
         <v>365</v>
       </c>
       <c r="C342" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="343" spans="1:3">
@@ -10618,7 +10606,7 @@
         <v>366</v>
       </c>
       <c r="C343" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="344" spans="1:3">
@@ -10629,7 +10617,7 @@
         <v>367</v>
       </c>
       <c r="C344" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="345" spans="1:3">
@@ -10640,7 +10628,7 @@
         <v>368</v>
       </c>
       <c r="C345" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="346" spans="1:3">
@@ -10651,7 +10639,7 @@
         <v>369</v>
       </c>
       <c r="C346" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="347" spans="1:3">
@@ -10662,7 +10650,7 @@
         <v>370</v>
       </c>
       <c r="C347" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="348" spans="1:3">
@@ -10673,7 +10661,7 @@
         <v>371</v>
       </c>
       <c r="C348" t="s">
-        <v>1439</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="349" spans="1:3">
@@ -10684,7 +10672,7 @@
         <v>372</v>
       </c>
       <c r="C349" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -10695,7 +10683,7 @@
         <v>373</v>
       </c>
       <c r="C350" t="s">
-        <v>1183</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="351" spans="1:3">
@@ -10706,7 +10694,7 @@
         <v>374</v>
       </c>
       <c r="C351" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -10717,7 +10705,7 @@
         <v>375</v>
       </c>
       <c r="C352" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="353" spans="1:3">
@@ -10728,7 +10716,7 @@
         <v>376</v>
       </c>
       <c r="C353" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="354" spans="1:3">
@@ -10739,7 +10727,7 @@
         <v>377</v>
       </c>
       <c r="C354" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -10750,7 +10738,7 @@
         <v>378</v>
       </c>
       <c r="C355" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="356" spans="1:3">
@@ -10761,7 +10749,7 @@
         <v>379</v>
       </c>
       <c r="C356" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="357" spans="1:3">
@@ -10772,7 +10760,7 @@
         <v>380</v>
       </c>
       <c r="C357" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="358" spans="1:3">
@@ -10783,29 +10771,29 @@
         <v>381</v>
       </c>
       <c r="C358" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="359" spans="1:3">
       <c r="A359" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B359" t="s">
         <v>382</v>
       </c>
       <c r="C359" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="360" spans="1:3">
       <c r="A360" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B360" t="s">
         <v>383</v>
       </c>
       <c r="C360" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="361" spans="1:3">
@@ -10816,7 +10804,7 @@
         <v>384</v>
       </c>
       <c r="C361" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="362" spans="1:3">
@@ -10827,7 +10815,7 @@
         <v>385</v>
       </c>
       <c r="C362" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="363" spans="1:3">
@@ -10838,7 +10826,7 @@
         <v>386</v>
       </c>
       <c r="C363" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="364" spans="1:3">
@@ -10849,7 +10837,7 @@
         <v>387</v>
       </c>
       <c r="C364" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="365" spans="1:3">
@@ -10860,7 +10848,7 @@
         <v>388</v>
       </c>
       <c r="C365" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="366" spans="1:3">
@@ -10871,7 +10859,7 @@
         <v>389</v>
       </c>
       <c r="C366" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="367" spans="1:3">
@@ -10882,7 +10870,7 @@
         <v>390</v>
       </c>
       <c r="C367" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="368" spans="1:3">
@@ -10893,7 +10881,7 @@
         <v>391</v>
       </c>
       <c r="C368" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="369" spans="1:3">
@@ -10904,7 +10892,7 @@
         <v>392</v>
       </c>
       <c r="C369" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="370" spans="1:3">
@@ -10915,7 +10903,7 @@
         <v>393</v>
       </c>
       <c r="C370" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="371" spans="1:3">
@@ -10926,7 +10914,7 @@
         <v>394</v>
       </c>
       <c r="C371" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -10937,7 +10925,7 @@
         <v>395</v>
       </c>
       <c r="C372" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="373" spans="1:3">
@@ -10948,7 +10936,7 @@
         <v>396</v>
       </c>
       <c r="C373" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="374" spans="1:3">
@@ -10959,7 +10947,7 @@
         <v>397</v>
       </c>
       <c r="C374" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="375" spans="1:3">
@@ -10970,7 +10958,7 @@
         <v>398</v>
       </c>
       <c r="C375" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="376" spans="1:3">
@@ -10981,7 +10969,7 @@
         <v>399</v>
       </c>
       <c r="C376" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="377" spans="1:3">
@@ -10992,7 +10980,7 @@
         <v>400</v>
       </c>
       <c r="C377" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="378" spans="1:3">
@@ -11003,7 +10991,7 @@
         <v>401</v>
       </c>
       <c r="C378" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="379" spans="1:3">
@@ -11014,7 +11002,7 @@
         <v>402</v>
       </c>
       <c r="C379" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="380" spans="1:3">
@@ -11025,7 +11013,7 @@
         <v>403</v>
       </c>
       <c r="C380" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="381" spans="1:3">
@@ -11036,7 +11024,7 @@
         <v>404</v>
       </c>
       <c r="C381" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="382" spans="1:3">
@@ -11047,7 +11035,7 @@
         <v>405</v>
       </c>
       <c r="C382" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="383" spans="1:3">
@@ -11058,7 +11046,7 @@
         <v>406</v>
       </c>
       <c r="C383" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="384" spans="1:3">
@@ -11069,7 +11057,7 @@
         <v>407</v>
       </c>
       <c r="C384" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="385" spans="1:3">
@@ -11080,7 +11068,7 @@
         <v>408</v>
       </c>
       <c r="C385" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="386" spans="1:3">
@@ -11091,7 +11079,7 @@
         <v>409</v>
       </c>
       <c r="C386" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="387" spans="1:3">
@@ -11102,7 +11090,7 @@
         <v>410</v>
       </c>
       <c r="C387" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="388" spans="1:3">
@@ -11113,7 +11101,7 @@
         <v>411</v>
       </c>
       <c r="C388" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="389" spans="1:3">
@@ -11124,7 +11112,7 @@
         <v>412</v>
       </c>
       <c r="C389" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="390" spans="1:3">
@@ -11135,7 +11123,7 @@
         <v>413</v>
       </c>
       <c r="C390" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="391" spans="1:3">
@@ -11146,7 +11134,7 @@
         <v>414</v>
       </c>
       <c r="C391" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="392" spans="1:3">
@@ -11157,7 +11145,7 @@
         <v>415</v>
       </c>
       <c r="C392" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="393" spans="1:3">
@@ -11168,7 +11156,7 @@
         <v>416</v>
       </c>
       <c r="C393" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="394" spans="1:3">
@@ -11179,7 +11167,7 @@
         <v>417</v>
       </c>
       <c r="C394" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="395" spans="1:3">
@@ -11190,7 +11178,7 @@
         <v>418</v>
       </c>
       <c r="C395" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="396" spans="1:3">
@@ -11201,7 +11189,7 @@
         <v>419</v>
       </c>
       <c r="C396" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="397" spans="1:3">
@@ -11212,7 +11200,7 @@
         <v>420</v>
       </c>
       <c r="C397" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="398" spans="1:3">
@@ -11223,7 +11211,7 @@
         <v>421</v>
       </c>
       <c r="C398" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="399" spans="1:3">
@@ -11234,7 +11222,7 @@
         <v>422</v>
       </c>
       <c r="C399" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="400" spans="1:3">
@@ -11245,7 +11233,7 @@
         <v>423</v>
       </c>
       <c r="C400" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="401" spans="1:3">
@@ -11256,7 +11244,7 @@
         <v>424</v>
       </c>
       <c r="C401" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="402" spans="1:3">
@@ -11267,7 +11255,7 @@
         <v>425</v>
       </c>
       <c r="C402" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="403" spans="1:3">
@@ -11278,7 +11266,7 @@
         <v>426</v>
       </c>
       <c r="C403" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="404" spans="1:3">
@@ -11289,7 +11277,7 @@
         <v>427</v>
       </c>
       <c r="C404" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="405" spans="1:3">
@@ -11300,7 +11288,7 @@
         <v>428</v>
       </c>
       <c r="C405" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="406" spans="1:3">
@@ -11311,7 +11299,7 @@
         <v>429</v>
       </c>
       <c r="C406" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="407" spans="1:3">
@@ -11322,7 +11310,7 @@
         <v>430</v>
       </c>
       <c r="C407" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="408" spans="1:3">
@@ -11333,7 +11321,7 @@
         <v>431</v>
       </c>
       <c r="C408" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="409" spans="1:3">
@@ -11344,7 +11332,7 @@
         <v>432</v>
       </c>
       <c r="C409" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="410" spans="1:3">
@@ -11355,7 +11343,7 @@
         <v>433</v>
       </c>
       <c r="C410" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="411" spans="1:3">
@@ -11366,7 +11354,7 @@
         <v>434</v>
       </c>
       <c r="C411" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="412" spans="1:3">
@@ -11377,7 +11365,7 @@
         <v>435</v>
       </c>
       <c r="C412" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="413" spans="1:3">
@@ -11388,7 +11376,7 @@
         <v>436</v>
       </c>
       <c r="C413" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="414" spans="1:3">
@@ -11399,7 +11387,7 @@
         <v>437</v>
       </c>
       <c r="C414" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="415" spans="1:3">
@@ -11410,7 +11398,7 @@
         <v>438</v>
       </c>
       <c r="C415" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="416" spans="1:3">
@@ -11421,7 +11409,7 @@
         <v>439</v>
       </c>
       <c r="C416" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="417" spans="1:3">
@@ -11432,7 +11420,7 @@
         <v>440</v>
       </c>
       <c r="C417" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="418" spans="1:3">
@@ -11443,7 +11431,7 @@
         <v>441</v>
       </c>
       <c r="C418" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="419" spans="1:3">
@@ -11454,7 +11442,7 @@
         <v>442</v>
       </c>
       <c r="C419" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="420" spans="1:3">
@@ -11465,7 +11453,7 @@
         <v>443</v>
       </c>
       <c r="C420" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="421" spans="1:3">
@@ -11476,7 +11464,7 @@
         <v>444</v>
       </c>
       <c r="C421" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="422" spans="1:3">
@@ -11487,7 +11475,7 @@
         <v>445</v>
       </c>
       <c r="C422" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="423" spans="1:3">
@@ -11498,7 +11486,7 @@
         <v>446</v>
       </c>
       <c r="C423" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="424" spans="1:3">
@@ -11509,7 +11497,7 @@
         <v>447</v>
       </c>
       <c r="C424" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="425" spans="1:3">
@@ -11520,7 +11508,7 @@
         <v>448</v>
       </c>
       <c r="C425" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="426" spans="1:3">
@@ -11531,7 +11519,7 @@
         <v>449</v>
       </c>
       <c r="C426" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="427" spans="1:3">
@@ -11542,7 +11530,7 @@
         <v>450</v>
       </c>
       <c r="C427" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="428" spans="1:3">
@@ -11553,7 +11541,7 @@
         <v>451</v>
       </c>
       <c r="C428" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="429" spans="1:3">
@@ -11564,7 +11552,7 @@
         <v>452</v>
       </c>
       <c r="C429" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="430" spans="1:3">
@@ -11575,7 +11563,7 @@
         <v>453</v>
       </c>
       <c r="C430" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="431" spans="1:3">
@@ -11586,7 +11574,7 @@
         <v>454</v>
       </c>
       <c r="C431" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="432" spans="1:3">
@@ -11597,7 +11585,7 @@
         <v>455</v>
       </c>
       <c r="C432" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="433" spans="1:3">
@@ -11608,7 +11596,7 @@
         <v>456</v>
       </c>
       <c r="C433" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="434" spans="1:3">
@@ -11619,7 +11607,7 @@
         <v>457</v>
       </c>
       <c r="C434" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="435" spans="1:3">
@@ -11630,7 +11618,7 @@
         <v>458</v>
       </c>
       <c r="C435" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="436" spans="1:3">
@@ -11641,7 +11629,7 @@
         <v>459</v>
       </c>
       <c r="C436" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="437" spans="1:3">
@@ -11652,7 +11640,7 @@
         <v>460</v>
       </c>
       <c r="C437" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="438" spans="1:3">
@@ -11663,7 +11651,7 @@
         <v>461</v>
       </c>
       <c r="C438" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="439" spans="1:3">
@@ -11674,7 +11662,7 @@
         <v>462</v>
       </c>
       <c r="C439" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="440" spans="1:3">
@@ -11685,7 +11673,7 @@
         <v>463</v>
       </c>
       <c r="C440" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="441" spans="1:3">
@@ -11696,7 +11684,7 @@
         <v>464</v>
       </c>
       <c r="C441" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="442" spans="1:3">
@@ -11707,7 +11695,7 @@
         <v>465</v>
       </c>
       <c r="C442" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="443" spans="1:3">
@@ -11718,7 +11706,7 @@
         <v>466</v>
       </c>
       <c r="C443" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="444" spans="1:3">
@@ -11729,7 +11717,7 @@
         <v>467</v>
       </c>
       <c r="C444" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="445" spans="1:3">
@@ -11740,7 +11728,7 @@
         <v>468</v>
       </c>
       <c r="C445" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="446" spans="1:3">
@@ -11751,7 +11739,7 @@
         <v>469</v>
       </c>
       <c r="C446" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="447" spans="1:3">
@@ -11762,7 +11750,7 @@
         <v>470</v>
       </c>
       <c r="C447" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="448" spans="1:3">
@@ -11773,7 +11761,7 @@
         <v>471</v>
       </c>
       <c r="C448" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="449" spans="1:3">
@@ -11784,7 +11772,7 @@
         <v>472</v>
       </c>
       <c r="C449" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="450" spans="1:3">
@@ -11795,7 +11783,7 @@
         <v>473</v>
       </c>
       <c r="C450" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="451" spans="1:3">
@@ -11806,7 +11794,7 @@
         <v>474</v>
       </c>
       <c r="C451" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="452" spans="1:3">
@@ -11817,7 +11805,7 @@
         <v>475</v>
       </c>
       <c r="C452" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="453" spans="1:3">
@@ -11828,7 +11816,7 @@
         <v>476</v>
       </c>
       <c r="C453" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="454" spans="1:3">
@@ -11839,7 +11827,7 @@
         <v>477</v>
       </c>
       <c r="C454" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="455" spans="1:3">
@@ -11850,7 +11838,7 @@
         <v>478</v>
       </c>
       <c r="C455" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="456" spans="1:3">
@@ -11861,7 +11849,7 @@
         <v>479</v>
       </c>
       <c r="C456" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="457" spans="1:3">
@@ -11872,7 +11860,7 @@
         <v>480</v>
       </c>
       <c r="C457" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="458" spans="1:3">
@@ -11883,7 +11871,7 @@
         <v>481</v>
       </c>
       <c r="C458" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="459" spans="1:3">
@@ -11894,7 +11882,7 @@
         <v>482</v>
       </c>
       <c r="C459" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="460" spans="1:3">
@@ -11905,7 +11893,7 @@
         <v>483</v>
       </c>
       <c r="C460" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="461" spans="1:3">
@@ -11916,7 +11904,7 @@
         <v>484</v>
       </c>
       <c r="C461" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="462" spans="1:3">
@@ -11927,7 +11915,7 @@
         <v>485</v>
       </c>
       <c r="C462" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="463" spans="1:3">
@@ -11938,7 +11926,7 @@
         <v>486</v>
       </c>
       <c r="C463" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="464" spans="1:3">
@@ -11949,7 +11937,7 @@
         <v>487</v>
       </c>
       <c r="C464" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="465" spans="1:3">
@@ -11960,7 +11948,7 @@
         <v>488</v>
       </c>
       <c r="C465" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="466" spans="1:3">
@@ -11971,7 +11959,7 @@
         <v>489</v>
       </c>
       <c r="C466" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="467" spans="1:3">
@@ -11982,7 +11970,7 @@
         <v>490</v>
       </c>
       <c r="C467" t="s">
-        <v>1557</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="468" spans="1:3">
@@ -11993,7 +11981,7 @@
         <v>491</v>
       </c>
       <c r="C468" t="s">
-        <v>1558</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="469" spans="1:3">
@@ -12004,7 +11992,7 @@
         <v>492</v>
       </c>
       <c r="C469" t="s">
-        <v>1527</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="470" spans="1:3">
@@ -12015,7 +12003,7 @@
         <v>493</v>
       </c>
       <c r="C470" t="s">
-        <v>1519</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="471" spans="1:3">
@@ -12026,7 +12014,7 @@
         <v>494</v>
       </c>
       <c r="C471" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="472" spans="1:3">
@@ -12037,7 +12025,7 @@
         <v>495</v>
       </c>
       <c r="C472" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="473" spans="1:3">
@@ -12048,7 +12036,7 @@
         <v>496</v>
       </c>
       <c r="C473" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="474" spans="1:3">
@@ -12059,7 +12047,7 @@
         <v>497</v>
       </c>
       <c r="C474" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="475" spans="1:3">
@@ -12070,7 +12058,7 @@
         <v>498</v>
       </c>
       <c r="C475" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="476" spans="1:3">
@@ -12081,7 +12069,7 @@
         <v>499</v>
       </c>
       <c r="C476" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="477" spans="1:3">
@@ -12092,7 +12080,7 @@
         <v>500</v>
       </c>
       <c r="C477" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="478" spans="1:3">
@@ -12103,7 +12091,7 @@
         <v>501</v>
       </c>
       <c r="C478" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="479" spans="1:3">
@@ -12114,7 +12102,7 @@
         <v>502</v>
       </c>
       <c r="C479" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="480" spans="1:3">
@@ -12125,7 +12113,7 @@
         <v>503</v>
       </c>
       <c r="C480" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="481" spans="1:3">
@@ -12136,7 +12124,7 @@
         <v>504</v>
       </c>
       <c r="C481" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="482" spans="1:3">
@@ -12147,7 +12135,7 @@
         <v>505</v>
       </c>
       <c r="C482" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="483" spans="1:3">
@@ -12158,7 +12146,7 @@
         <v>506</v>
       </c>
       <c r="C483" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="484" spans="1:3">
@@ -12169,7 +12157,7 @@
         <v>507</v>
       </c>
       <c r="C484" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="485" spans="1:3">
@@ -12180,7 +12168,7 @@
         <v>508</v>
       </c>
       <c r="C485" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="486" spans="1:3">
@@ -12191,7 +12179,7 @@
         <v>509</v>
       </c>
       <c r="C486" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="487" spans="1:3">
@@ -12202,7 +12190,7 @@
         <v>510</v>
       </c>
       <c r="C487" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="488" spans="1:3">
@@ -12213,7 +12201,7 @@
         <v>511</v>
       </c>
       <c r="C488" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="489" spans="1:3">
@@ -12224,7 +12212,7 @@
         <v>512</v>
       </c>
       <c r="C489" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="490" spans="1:3">
@@ -12235,7 +12223,7 @@
         <v>513</v>
       </c>
       <c r="C490" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="491" spans="1:3">
@@ -12246,7 +12234,7 @@
         <v>514</v>
       </c>
       <c r="C491" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="492" spans="1:3">
@@ -12257,7 +12245,7 @@
         <v>515</v>
       </c>
       <c r="C492" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="493" spans="1:3">
@@ -12268,7 +12256,7 @@
         <v>516</v>
       </c>
       <c r="C493" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="494" spans="1:3">
@@ -12279,7 +12267,7 @@
         <v>517</v>
       </c>
       <c r="C494" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="495" spans="1:3">
@@ -12290,7 +12278,7 @@
         <v>518</v>
       </c>
       <c r="C495" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="496" spans="1:3">
@@ -12301,7 +12289,7 @@
         <v>519</v>
       </c>
       <c r="C496" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="497" spans="1:3">
@@ -12312,7 +12300,7 @@
         <v>520</v>
       </c>
       <c r="C497" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="498" spans="1:3">
@@ -12323,7 +12311,7 @@
         <v>521</v>
       </c>
       <c r="C498" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="499" spans="1:3">
@@ -12334,7 +12322,7 @@
         <v>522</v>
       </c>
       <c r="C499" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="500" spans="1:3">
@@ -12345,7 +12333,7 @@
         <v>523</v>
       </c>
       <c r="C500" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="501" spans="1:3">
@@ -12356,7 +12344,7 @@
         <v>524</v>
       </c>
       <c r="C501" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="502" spans="1:3">
@@ -12367,7 +12355,7 @@
         <v>525</v>
       </c>
       <c r="C502" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="503" spans="1:3">
@@ -12378,7 +12366,7 @@
         <v>526</v>
       </c>
       <c r="C503" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="504" spans="1:3">
@@ -12389,7 +12377,7 @@
         <v>527</v>
       </c>
       <c r="C504" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="505" spans="1:3">
@@ -12400,7 +12388,7 @@
         <v>528</v>
       </c>
       <c r="C505" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="506" spans="1:3">
@@ -12411,7 +12399,7 @@
         <v>529</v>
       </c>
       <c r="C506" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="507" spans="1:3">
@@ -12422,7 +12410,7 @@
         <v>530</v>
       </c>
       <c r="C507" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="508" spans="1:3">
@@ -12433,7 +12421,7 @@
         <v>531</v>
       </c>
       <c r="C508" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="509" spans="1:3">
@@ -12444,7 +12432,7 @@
         <v>532</v>
       </c>
       <c r="C509" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="510" spans="1:3">
@@ -12455,7 +12443,7 @@
         <v>533</v>
       </c>
       <c r="C510" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="511" spans="1:3">
@@ -12466,7 +12454,7 @@
         <v>534</v>
       </c>
       <c r="C511" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="512" spans="1:3">
@@ -12477,7 +12465,7 @@
         <v>535</v>
       </c>
       <c r="C512" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="513" spans="1:3">
@@ -12488,7 +12476,7 @@
         <v>536</v>
       </c>
       <c r="C513" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="514" spans="1:3">
@@ -12499,7 +12487,7 @@
         <v>537</v>
       </c>
       <c r="C514" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="515" spans="1:3">
@@ -12510,7 +12498,7 @@
         <v>538</v>
       </c>
       <c r="C515" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="516" spans="1:3">
@@ -12521,7 +12509,7 @@
         <v>539</v>
       </c>
       <c r="C516" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="517" spans="1:3">
@@ -12532,7 +12520,7 @@
         <v>540</v>
       </c>
       <c r="C517" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="518" spans="1:3">
@@ -12543,7 +12531,7 @@
         <v>541</v>
       </c>
       <c r="C518" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="519" spans="1:3">
@@ -12554,7 +12542,7 @@
         <v>542</v>
       </c>
       <c r="C519" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="520" spans="1:3">
@@ -12565,7 +12553,7 @@
         <v>543</v>
       </c>
       <c r="C520" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="521" spans="1:3">
@@ -12576,7 +12564,7 @@
         <v>544</v>
       </c>
       <c r="C521" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="522" spans="1:3">
@@ -12587,7 +12575,7 @@
         <v>545</v>
       </c>
       <c r="C522" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="523" spans="1:3">
@@ -12598,7 +12586,7 @@
         <v>546</v>
       </c>
       <c r="C523" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="524" spans="1:3">
@@ -12609,7 +12597,7 @@
         <v>547</v>
       </c>
       <c r="C524" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="525" spans="1:3">
@@ -12620,7 +12608,7 @@
         <v>548</v>
       </c>
       <c r="C525" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="526" spans="1:3">
@@ -12631,7 +12619,7 @@
         <v>549</v>
       </c>
       <c r="C526" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="527" spans="1:3">
@@ -12642,7 +12630,7 @@
         <v>550</v>
       </c>
       <c r="C527" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="528" spans="1:3">
@@ -12653,7 +12641,7 @@
         <v>551</v>
       </c>
       <c r="C528" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="529" spans="1:3">
@@ -12664,7 +12652,7 @@
         <v>552</v>
       </c>
       <c r="C529" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="530" spans="1:3">
@@ -12675,7 +12663,7 @@
         <v>553</v>
       </c>
       <c r="C530" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="531" spans="1:3">
@@ -12686,7 +12674,7 @@
         <v>554</v>
       </c>
       <c r="C531" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="532" spans="1:3">
@@ -12697,7 +12685,7 @@
         <v>555</v>
       </c>
       <c r="C532" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="533" spans="1:3">
@@ -12708,29 +12696,29 @@
         <v>556</v>
       </c>
       <c r="C533" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="534" spans="1:3">
       <c r="A534" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B534" t="s">
         <v>557</v>
       </c>
       <c r="C534" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="535" spans="1:3">
       <c r="A535" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B535" t="s">
         <v>558</v>
       </c>
       <c r="C535" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="536" spans="1:3">
@@ -12741,7 +12729,7 @@
         <v>559</v>
       </c>
       <c r="C536" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="537" spans="1:3">
@@ -12752,7 +12740,7 @@
         <v>560</v>
       </c>
       <c r="C537" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="538" spans="1:3">
@@ -12763,7 +12751,7 @@
         <v>561</v>
       </c>
       <c r="C538" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="539" spans="1:3">
@@ -12774,7 +12762,7 @@
         <v>562</v>
       </c>
       <c r="C539" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="540" spans="1:3">
@@ -12785,7 +12773,7 @@
         <v>563</v>
       </c>
       <c r="C540" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="541" spans="1:3">
@@ -12796,7 +12784,7 @@
         <v>564</v>
       </c>
       <c r="C541" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="542" spans="1:3">
@@ -12807,7 +12795,7 @@
         <v>565</v>
       </c>
       <c r="C542" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="543" spans="1:3">
@@ -12818,7 +12806,7 @@
         <v>566</v>
       </c>
       <c r="C543" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="544" spans="1:3">
@@ -12829,7 +12817,7 @@
         <v>567</v>
       </c>
       <c r="C544" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="545" spans="1:3">
@@ -12840,7 +12828,7 @@
         <v>568</v>
       </c>
       <c r="C545" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="546" spans="1:3">
@@ -12851,7 +12839,7 @@
         <v>569</v>
       </c>
       <c r="C546" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="547" spans="1:3">
@@ -12862,7 +12850,7 @@
         <v>570</v>
       </c>
       <c r="C547" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="548" spans="1:3">
@@ -12873,7 +12861,7 @@
         <v>571</v>
       </c>
       <c r="C548" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="549" spans="1:3">
@@ -12884,7 +12872,7 @@
         <v>572</v>
       </c>
       <c r="C549" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="550" spans="1:3">
@@ -12895,7 +12883,7 @@
         <v>573</v>
       </c>
       <c r="C550" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="551" spans="1:3">
@@ -12906,7 +12894,7 @@
         <v>574</v>
       </c>
       <c r="C551" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="552" spans="1:3">
@@ -12917,7 +12905,7 @@
         <v>575</v>
       </c>
       <c r="C552" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="553" spans="1:3">
@@ -12928,7 +12916,7 @@
         <v>576</v>
       </c>
       <c r="C553" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="554" spans="1:3">
@@ -12939,7 +12927,7 @@
         <v>577</v>
       </c>
       <c r="C554" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="555" spans="1:3">
@@ -12950,29 +12938,29 @@
         <v>578</v>
       </c>
       <c r="C555" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="556" spans="1:3">
       <c r="A556" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B556" t="s">
         <v>579</v>
       </c>
       <c r="C556" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="557" spans="1:3">
       <c r="A557" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B557" t="s">
         <v>580</v>
       </c>
       <c r="C557" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="558" spans="1:3">
@@ -12983,7 +12971,7 @@
         <v>581</v>
       </c>
       <c r="C558" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="559" spans="1:3">
@@ -12994,7 +12982,7 @@
         <v>582</v>
       </c>
       <c r="C559" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="560" spans="1:3">
@@ -13005,7 +12993,7 @@
         <v>583</v>
       </c>
       <c r="C560" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="561" spans="1:3">
@@ -13016,7 +13004,7 @@
         <v>584</v>
       </c>
       <c r="C561" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="562" spans="1:3">
@@ -13027,7 +13015,7 @@
         <v>585</v>
       </c>
       <c r="C562" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="563" spans="1:3">
@@ -13038,7 +13026,7 @@
         <v>586</v>
       </c>
       <c r="C563" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="564" spans="1:3">
@@ -13049,7 +13037,7 @@
         <v>587</v>
       </c>
       <c r="C564" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="565" spans="1:3">
@@ -13060,7 +13048,7 @@
         <v>588</v>
       </c>
       <c r="C565" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="566" spans="1:3">
@@ -13071,7 +13059,7 @@
         <v>589</v>
       </c>
       <c r="C566" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="567" spans="1:3">
@@ -13082,7 +13070,7 @@
         <v>590</v>
       </c>
       <c r="C567" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="568" spans="1:3">
@@ -13093,7 +13081,7 @@
         <v>591</v>
       </c>
       <c r="C568" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="569" spans="1:3">
@@ -13104,7 +13092,7 @@
         <v>592</v>
       </c>
       <c r="C569" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="570" spans="1:3">
@@ -13115,7 +13103,7 @@
         <v>593</v>
       </c>
       <c r="C570" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="571" spans="1:3">
@@ -13126,7 +13114,7 @@
         <v>594</v>
       </c>
       <c r="C571" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="572" spans="1:3">
@@ -13137,7 +13125,7 @@
         <v>595</v>
       </c>
       <c r="C572" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="573" spans="1:3">
@@ -13148,7 +13136,7 @@
         <v>596</v>
       </c>
       <c r="C573" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="574" spans="1:3">
@@ -13159,7 +13147,7 @@
         <v>597</v>
       </c>
       <c r="C574" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="575" spans="1:3">
@@ -13170,7 +13158,7 @@
         <v>598</v>
       </c>
       <c r="C575" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="576" spans="1:3">
@@ -13181,7 +13169,7 @@
         <v>599</v>
       </c>
       <c r="C576" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="577" spans="1:3">
@@ -13192,7 +13180,7 @@
         <v>600</v>
       </c>
       <c r="C577" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="578" spans="1:3">
@@ -13203,7 +13191,7 @@
         <v>601</v>
       </c>
       <c r="C578" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="579" spans="1:3">
@@ -13214,7 +13202,7 @@
         <v>602</v>
       </c>
       <c r="C579" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="580" spans="1:3">
@@ -13225,7 +13213,7 @@
         <v>603</v>
       </c>
       <c r="C580" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="581" spans="1:3">
@@ -13236,7 +13224,7 @@
         <v>604</v>
       </c>
       <c r="C581" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="582" spans="1:3">
@@ -13247,7 +13235,7 @@
         <v>605</v>
       </c>
       <c r="C582" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="583" spans="1:3">
@@ -13258,7 +13246,7 @@
         <v>606</v>
       </c>
       <c r="C583" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="584" spans="1:3">
@@ -13269,7 +13257,7 @@
         <v>607</v>
       </c>
       <c r="C584" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="585" spans="1:3">
@@ -13280,7 +13268,7 @@
         <v>608</v>
       </c>
       <c r="C585" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="586" spans="1:3">
@@ -13291,7 +13279,7 @@
         <v>609</v>
       </c>
       <c r="C586" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="587" spans="1:3">
@@ -13302,7 +13290,7 @@
         <v>610</v>
       </c>
       <c r="C587" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="588" spans="1:3">
@@ -13313,7 +13301,7 @@
         <v>611</v>
       </c>
       <c r="C588" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="589" spans="1:3">
@@ -13324,7 +13312,7 @@
         <v>612</v>
       </c>
       <c r="C589" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="590" spans="1:3">
@@ -13335,7 +13323,7 @@
         <v>613</v>
       </c>
       <c r="C590" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="591" spans="1:3">
@@ -13346,7 +13334,7 @@
         <v>614</v>
       </c>
       <c r="C591" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="592" spans="1:3">
@@ -13357,7 +13345,7 @@
         <v>615</v>
       </c>
       <c r="C592" t="s">
-        <v>1680</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="593" spans="1:3">
@@ -13368,7 +13356,7 @@
         <v>616</v>
       </c>
       <c r="C593" t="s">
-        <v>1681</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="594" spans="1:3">
@@ -13379,7 +13367,7 @@
         <v>617</v>
       </c>
       <c r="C594" t="s">
-        <v>1651</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="595" spans="1:3">
@@ -13390,7 +13378,7 @@
         <v>618</v>
       </c>
       <c r="C595" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="596" spans="1:3">
@@ -13401,7 +13389,7 @@
         <v>619</v>
       </c>
       <c r="C596" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="597" spans="1:3">
@@ -13412,7 +13400,7 @@
         <v>620</v>
       </c>
       <c r="C597" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="598" spans="1:3">
@@ -13423,29 +13411,29 @@
         <v>621</v>
       </c>
       <c r="C598" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="599" spans="1:3">
       <c r="A599" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B599" t="s">
         <v>622</v>
       </c>
       <c r="C599" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="600" spans="1:3">
       <c r="A600" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B600" t="s">
         <v>623</v>
       </c>
       <c r="C600" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="601" spans="1:3">
@@ -13456,7 +13444,7 @@
         <v>624</v>
       </c>
       <c r="C601" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="602" spans="1:3">
@@ -13467,7 +13455,7 @@
         <v>625</v>
       </c>
       <c r="C602" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="603" spans="1:3">
@@ -13478,7 +13466,7 @@
         <v>626</v>
       </c>
       <c r="C603" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="604" spans="1:3">
@@ -13489,7 +13477,7 @@
         <v>627</v>
       </c>
       <c r="C604" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="605" spans="1:3">
@@ -13500,29 +13488,29 @@
         <v>628</v>
       </c>
       <c r="C605" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="606" spans="1:3">
       <c r="A606" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B606" t="s">
         <v>629</v>
       </c>
       <c r="C606" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="607" spans="1:3">
       <c r="A607" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B607" t="s">
         <v>630</v>
       </c>
       <c r="C607" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="608" spans="1:3">
@@ -13533,7 +13521,7 @@
         <v>631</v>
       </c>
       <c r="C608" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="609" spans="1:3">
@@ -13544,7 +13532,7 @@
         <v>632</v>
       </c>
       <c r="C609" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="610" spans="1:3">
@@ -13555,7 +13543,7 @@
         <v>633</v>
       </c>
       <c r="C610" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="611" spans="1:3">
@@ -13566,7 +13554,7 @@
         <v>634</v>
       </c>
       <c r="C611" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="612" spans="1:3">
@@ -13577,7 +13565,7 @@
         <v>635</v>
       </c>
       <c r="C612" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="613" spans="1:3">
@@ -13588,7 +13576,7 @@
         <v>636</v>
       </c>
       <c r="C613" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="614" spans="1:3">
@@ -13599,7 +13587,7 @@
         <v>637</v>
       </c>
       <c r="C614" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="615" spans="1:3">
@@ -13610,7 +13598,7 @@
         <v>638</v>
       </c>
       <c r="C615" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="616" spans="1:3">
@@ -13621,7 +13609,7 @@
         <v>639</v>
       </c>
       <c r="C616" t="s">
-        <v>1703</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="617" spans="1:3">
@@ -13632,7 +13620,7 @@
         <v>640</v>
       </c>
       <c r="C617" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="618" spans="1:3">
@@ -13643,7 +13631,7 @@
         <v>641</v>
       </c>
       <c r="C618" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="619" spans="1:3">
@@ -13654,7 +13642,7 @@
         <v>642</v>
       </c>
       <c r="C619" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="620" spans="1:3">
@@ -13665,7 +13653,7 @@
         <v>643</v>
       </c>
       <c r="C620" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="621" spans="1:3">
@@ -13676,7 +13664,7 @@
         <v>644</v>
       </c>
       <c r="C621" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="622" spans="1:3">
@@ -13687,7 +13675,7 @@
         <v>645</v>
       </c>
       <c r="C622" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="623" spans="1:3">
@@ -13698,7 +13686,7 @@
         <v>646</v>
       </c>
       <c r="C623" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="624" spans="1:3">
@@ -13709,7 +13697,7 @@
         <v>647</v>
       </c>
       <c r="C624" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="625" spans="1:3">
@@ -13720,7 +13708,7 @@
         <v>648</v>
       </c>
       <c r="C625" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="626" spans="1:3">
@@ -13731,7 +13719,7 @@
         <v>649</v>
       </c>
       <c r="C626" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="627" spans="1:3">
@@ -13742,7 +13730,7 @@
         <v>650</v>
       </c>
       <c r="C627" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="628" spans="1:3">
@@ -13753,7 +13741,7 @@
         <v>651</v>
       </c>
       <c r="C628" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="629" spans="1:3">
@@ -13764,7 +13752,7 @@
         <v>652</v>
       </c>
       <c r="C629" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="630" spans="1:3">
@@ -13775,7 +13763,7 @@
         <v>653</v>
       </c>
       <c r="C630" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="631" spans="1:3">
@@ -13786,29 +13774,29 @@
         <v>654</v>
       </c>
       <c r="C631" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="632" spans="1:3">
       <c r="A632" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B632" t="s">
         <v>655</v>
       </c>
       <c r="C632" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="633" spans="1:3">
       <c r="A633" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B633" t="s">
         <v>656</v>
       </c>
       <c r="C633" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="634" spans="1:3">
@@ -13819,7 +13807,7 @@
         <v>657</v>
       </c>
       <c r="C634" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="635" spans="1:3">
@@ -13830,7 +13818,7 @@
         <v>658</v>
       </c>
       <c r="C635" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="636" spans="1:3">
@@ -13841,7 +13829,7 @@
         <v>659</v>
       </c>
       <c r="C636" t="s">
-        <v>1723</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="637" spans="1:3">
@@ -13852,7 +13840,7 @@
         <v>660</v>
       </c>
       <c r="C637" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="638" spans="1:3">
@@ -13863,7 +13851,7 @@
         <v>661</v>
       </c>
       <c r="C638" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="639" spans="1:3">
@@ -13874,7 +13862,7 @@
         <v>662</v>
       </c>
       <c r="C639" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="640" spans="1:3">
@@ -13885,7 +13873,7 @@
         <v>663</v>
       </c>
       <c r="C640" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="641" spans="1:3">
@@ -13896,7 +13884,7 @@
         <v>664</v>
       </c>
       <c r="C641" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="642" spans="1:3">
@@ -13907,29 +13895,29 @@
         <v>665</v>
       </c>
       <c r="C642" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="643" spans="1:3">
       <c r="A643" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B643" t="s">
         <v>666</v>
       </c>
       <c r="C643" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="644" spans="1:3">
       <c r="A644" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B644" t="s">
         <v>667</v>
       </c>
       <c r="C644" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="645" spans="1:3">
@@ -13940,7 +13928,7 @@
         <v>668</v>
       </c>
       <c r="C645" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="646" spans="1:3">
@@ -13951,7 +13939,7 @@
         <v>669</v>
       </c>
       <c r="C646" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="647" spans="1:3">
@@ -13962,7 +13950,7 @@
         <v>670</v>
       </c>
       <c r="C647" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="648" spans="1:3">
@@ -13973,7 +13961,7 @@
         <v>671</v>
       </c>
       <c r="C648" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="649" spans="1:3">
@@ -13984,7 +13972,7 @@
         <v>672</v>
       </c>
       <c r="C649" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="650" spans="1:3">
@@ -13995,7 +13983,7 @@
         <v>673</v>
       </c>
       <c r="C650" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="651" spans="1:3">
@@ -14006,7 +13994,7 @@
         <v>674</v>
       </c>
       <c r="C651" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="652" spans="1:3">
@@ -14017,7 +14005,7 @@
         <v>675</v>
       </c>
       <c r="C652" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="653" spans="1:3">
@@ -14028,7 +14016,7 @@
         <v>676</v>
       </c>
       <c r="C653" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="654" spans="1:3">
@@ -14039,7 +14027,7 @@
         <v>677</v>
       </c>
       <c r="C654" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="655" spans="1:3">
@@ -14050,7 +14038,7 @@
         <v>678</v>
       </c>
       <c r="C655" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="656" spans="1:3">
@@ -14061,7 +14049,7 @@
         <v>679</v>
       </c>
       <c r="C656" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="657" spans="1:3">
@@ -14072,7 +14060,7 @@
         <v>680</v>
       </c>
       <c r="C657" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="658" spans="1:3">
@@ -14083,7 +14071,7 @@
         <v>681</v>
       </c>
       <c r="C658" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="659" spans="1:3">
@@ -14094,7 +14082,7 @@
         <v>682</v>
       </c>
       <c r="C659" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="660" spans="1:3">
@@ -14105,7 +14093,7 @@
         <v>683</v>
       </c>
       <c r="C660" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="661" spans="1:3">
@@ -14116,7 +14104,7 @@
         <v>684</v>
       </c>
       <c r="C661" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="662" spans="1:3">
@@ -14127,7 +14115,7 @@
         <v>685</v>
       </c>
       <c r="C662" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="663" spans="1:3">
@@ -14138,7 +14126,7 @@
         <v>686</v>
       </c>
       <c r="C663" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="664" spans="1:3">
@@ -14149,7 +14137,7 @@
         <v>687</v>
       </c>
       <c r="C664" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="665" spans="1:3">
@@ -14160,7 +14148,7 @@
         <v>688</v>
       </c>
       <c r="C665" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="666" spans="1:3">
@@ -14171,7 +14159,7 @@
         <v>689</v>
       </c>
       <c r="C666" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="667" spans="1:3">
@@ -14182,29 +14170,29 @@
         <v>690</v>
       </c>
       <c r="C667" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="668" spans="1:3">
       <c r="A668" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B668" t="s">
         <v>691</v>
       </c>
       <c r="C668" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="669" spans="1:3">
       <c r="A669" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B669" t="s">
         <v>692</v>
       </c>
       <c r="C669" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="670" spans="1:3">
@@ -14215,7 +14203,7 @@
         <v>693</v>
       </c>
       <c r="C670" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="671" spans="1:3">
@@ -14226,7 +14214,7 @@
         <v>694</v>
       </c>
       <c r="C671" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="672" spans="1:3">
@@ -14237,7 +14225,7 @@
         <v>695</v>
       </c>
       <c r="C672" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="673" spans="1:3">
@@ -14248,7 +14236,7 @@
         <v>696</v>
       </c>
       <c r="C673" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="674" spans="1:3">
@@ -14259,7 +14247,7 @@
         <v>697</v>
       </c>
       <c r="C674" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="675" spans="1:3">
@@ -14270,7 +14258,7 @@
         <v>698</v>
       </c>
       <c r="C675" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="676" spans="1:3">
@@ -14281,7 +14269,7 @@
         <v>699</v>
       </c>
       <c r="C676" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="677" spans="1:3">
@@ -14292,7 +14280,7 @@
         <v>700</v>
       </c>
       <c r="C677" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="678" spans="1:3">
@@ -14303,7 +14291,7 @@
         <v>701</v>
       </c>
       <c r="C678" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="679" spans="1:3">
@@ -14314,7 +14302,7 @@
         <v>702</v>
       </c>
       <c r="C679" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="680" spans="1:3">
@@ -14325,7 +14313,7 @@
         <v>703</v>
       </c>
       <c r="C680" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="681" spans="1:3">
@@ -14336,7 +14324,7 @@
         <v>704</v>
       </c>
       <c r="C681" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="682" spans="1:3">
@@ -14347,7 +14335,7 @@
         <v>705</v>
       </c>
       <c r="C682" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="683" spans="1:3">
@@ -14358,29 +14346,29 @@
         <v>706</v>
       </c>
       <c r="C683" t="s">
-        <v>1770</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="684" spans="1:3">
       <c r="A684" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B684" t="s">
         <v>707</v>
       </c>
       <c r="C684" t="s">
-        <v>1771</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="685" spans="1:3">
       <c r="A685" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B685" t="s">
         <v>708</v>
       </c>
       <c r="C685" t="s">
-        <v>1193</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="686" spans="1:3">
@@ -14391,7 +14379,7 @@
         <v>709</v>
       </c>
       <c r="C686" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="687" spans="1:3">
@@ -14402,7 +14390,7 @@
         <v>710</v>
       </c>
       <c r="C687" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="688" spans="1:3">
@@ -14413,7 +14401,7 @@
         <v>711</v>
       </c>
       <c r="C688" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="689" spans="1:3">
@@ -14424,7 +14412,7 @@
         <v>712</v>
       </c>
       <c r="C689" t="s">
-        <v>1775</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="690" spans="1:3">
@@ -14435,7 +14423,7 @@
         <v>713</v>
       </c>
       <c r="C690" t="s">
-        <v>1776</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="691" spans="1:3">
@@ -14446,7 +14434,7 @@
         <v>714</v>
       </c>
       <c r="C691" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="692" spans="1:3">
@@ -14457,7 +14445,7 @@
         <v>715</v>
       </c>
       <c r="C692" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="693" spans="1:3">
@@ -14468,7 +14456,7 @@
         <v>716</v>
       </c>
       <c r="C693" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="694" spans="1:3">
@@ -14479,7 +14467,7 @@
         <v>717</v>
       </c>
       <c r="C694" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="695" spans="1:3">
@@ -14490,7 +14478,7 @@
         <v>718</v>
       </c>
       <c r="C695" t="s">
-        <v>1781</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="696" spans="1:3">
@@ -14501,7 +14489,7 @@
         <v>719</v>
       </c>
       <c r="C696" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="697" spans="1:3">
@@ -14512,7 +14500,7 @@
         <v>720</v>
       </c>
       <c r="C697" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="698" spans="1:3">
@@ -14523,7 +14511,7 @@
         <v>721</v>
       </c>
       <c r="C698" t="s">
-        <v>1784</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="699" spans="1:3">
@@ -14534,7 +14522,7 @@
         <v>722</v>
       </c>
       <c r="C699" t="s">
-        <v>1785</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="700" spans="1:3">
@@ -14545,7 +14533,7 @@
         <v>723</v>
       </c>
       <c r="C700" t="s">
-        <v>1786</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="701" spans="1:3">
@@ -14556,7 +14544,7 @@
         <v>724</v>
       </c>
       <c r="C701" t="s">
-        <v>1787</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="702" spans="1:3">
@@ -14567,7 +14555,7 @@
         <v>725</v>
       </c>
       <c r="C702" t="s">
-        <v>1788</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="703" spans="1:3">
@@ -14578,7 +14566,7 @@
         <v>726</v>
       </c>
       <c r="C703" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="704" spans="1:3">
@@ -14589,7 +14577,7 @@
         <v>727</v>
       </c>
       <c r="C704" t="s">
-        <v>1790</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="705" spans="1:3">
@@ -14600,7 +14588,7 @@
         <v>728</v>
       </c>
       <c r="C705" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="706" spans="1:3">
@@ -14611,7 +14599,7 @@
         <v>729</v>
       </c>
       <c r="C706" t="s">
-        <v>1792</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="707" spans="1:3">
@@ -14622,7 +14610,7 @@
         <v>730</v>
       </c>
       <c r="C707" t="s">
-        <v>1793</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="708" spans="1:3">
@@ -14633,7 +14621,7 @@
         <v>731</v>
       </c>
       <c r="C708" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="709" spans="1:3">
@@ -14644,7 +14632,7 @@
         <v>732</v>
       </c>
       <c r="C709" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="710" spans="1:3">
@@ -14655,7 +14643,7 @@
         <v>733</v>
       </c>
       <c r="C710" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="711" spans="1:3">
@@ -14666,7 +14654,7 @@
         <v>734</v>
       </c>
       <c r="C711" t="s">
-        <v>1797</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="712" spans="1:3">
@@ -14677,7 +14665,7 @@
         <v>735</v>
       </c>
       <c r="C712" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="713" spans="1:3">
@@ -14688,7 +14676,7 @@
         <v>736</v>
       </c>
       <c r="C713" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="714" spans="1:3">
@@ -14699,7 +14687,7 @@
         <v>737</v>
       </c>
       <c r="C714" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="715" spans="1:3">
@@ -14710,7 +14698,7 @@
         <v>738</v>
       </c>
       <c r="C715" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="716" spans="1:3">
@@ -14721,7 +14709,7 @@
         <v>739</v>
       </c>
       <c r="C716" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="717" spans="1:3">
@@ -14732,7 +14720,7 @@
         <v>740</v>
       </c>
       <c r="C717" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="718" spans="1:3">
@@ -14743,7 +14731,7 @@
         <v>741</v>
       </c>
       <c r="C718" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="719" spans="1:3">
@@ -14754,7 +14742,7 @@
         <v>742</v>
       </c>
       <c r="C719" t="s">
-        <v>1805</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="720" spans="1:3">
@@ -14765,7 +14753,7 @@
         <v>743</v>
       </c>
       <c r="C720" t="s">
-        <v>1806</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="721" spans="1:3">
@@ -14776,7 +14764,7 @@
         <v>744</v>
       </c>
       <c r="C721" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="722" spans="1:3">
@@ -14787,7 +14775,7 @@
         <v>745</v>
       </c>
       <c r="C722" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="723" spans="1:3">
@@ -14798,7 +14786,7 @@
         <v>746</v>
       </c>
       <c r="C723" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="724" spans="1:3">
@@ -14809,7 +14797,7 @@
         <v>747</v>
       </c>
       <c r="C724" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="725" spans="1:3">
@@ -14820,40 +14808,40 @@
         <v>748</v>
       </c>
       <c r="C725" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="726" spans="1:3">
       <c r="A726" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B726" t="s">
         <v>749</v>
       </c>
       <c r="C726" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="727" spans="1:3">
       <c r="A727" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B727" t="s">
         <v>750</v>
       </c>
       <c r="C727" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="728" spans="1:3">
       <c r="A728" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B728" t="s">
         <v>751</v>
       </c>
       <c r="C728" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="729" spans="1:3">
@@ -14864,7 +14852,7 @@
         <v>752</v>
       </c>
       <c r="C729" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="730" spans="1:3">
@@ -14875,7 +14863,7 @@
         <v>753</v>
       </c>
       <c r="C730" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="731" spans="1:3">
@@ -14886,7 +14874,7 @@
         <v>754</v>
       </c>
       <c r="C731" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="732" spans="1:3">
@@ -14897,7 +14885,7 @@
         <v>755</v>
       </c>
       <c r="C732" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="733" spans="1:3">
@@ -14908,7 +14896,7 @@
         <v>756</v>
       </c>
       <c r="C733" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="734" spans="1:3">
@@ -14919,7 +14907,7 @@
         <v>757</v>
       </c>
       <c r="C734" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="735" spans="1:3">
@@ -14930,7 +14918,7 @@
         <v>758</v>
       </c>
       <c r="C735" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="736" spans="1:3">
@@ -14941,7 +14929,7 @@
         <v>759</v>
       </c>
       <c r="C736" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="737" spans="1:3">
@@ -14952,7 +14940,7 @@
         <v>760</v>
       </c>
       <c r="C737" t="s">
-        <v>1823</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="738" spans="1:3">
@@ -14963,7 +14951,7 @@
         <v>761</v>
       </c>
       <c r="C738" t="s">
-        <v>1824</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="739" spans="1:3">
@@ -14974,29 +14962,29 @@
         <v>762</v>
       </c>
       <c r="C739" t="s">
-        <v>1421</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="740" spans="1:3">
       <c r="A740" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B740" t="s">
         <v>763</v>
       </c>
       <c r="C740" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="741" spans="1:3">
       <c r="A741" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B741" t="s">
         <v>764</v>
       </c>
       <c r="C741" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="742" spans="1:3">
@@ -15007,7 +14995,7 @@
         <v>765</v>
       </c>
       <c r="C742" t="s">
-        <v>1827</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="743" spans="1:3">
@@ -15018,7 +15006,7 @@
         <v>766</v>
       </c>
       <c r="C743" t="s">
-        <v>1828</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="744" spans="1:3">
@@ -15029,7 +15017,7 @@
         <v>767</v>
       </c>
       <c r="C744" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="745" spans="1:3">
@@ -15040,7 +15028,7 @@
         <v>768</v>
       </c>
       <c r="C745" t="s">
-        <v>1830</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="746" spans="1:3">
@@ -15051,7 +15039,7 @@
         <v>769</v>
       </c>
       <c r="C746" t="s">
-        <v>1831</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="747" spans="1:3">
@@ -15062,7 +15050,7 @@
         <v>770</v>
       </c>
       <c r="C747" t="s">
-        <v>1832</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="748" spans="1:3">
@@ -15073,7 +15061,7 @@
         <v>771</v>
       </c>
       <c r="C748" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="749" spans="1:3">
@@ -15084,7 +15072,7 @@
         <v>772</v>
       </c>
       <c r="C749" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="750" spans="1:3">
@@ -15095,7 +15083,7 @@
         <v>773</v>
       </c>
       <c r="C750" t="s">
-        <v>1835</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="751" spans="1:3">
@@ -15106,7 +15094,7 @@
         <v>774</v>
       </c>
       <c r="C751" t="s">
-        <v>1836</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="752" spans="1:3">
@@ -15117,7 +15105,7 @@
         <v>775</v>
       </c>
       <c r="C752" t="s">
-        <v>1837</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="753" spans="1:3">
@@ -15128,7 +15116,7 @@
         <v>776</v>
       </c>
       <c r="C753" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="754" spans="1:3">
@@ -15139,7 +15127,7 @@
         <v>777</v>
       </c>
       <c r="C754" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="755" spans="1:3">
@@ -15150,7 +15138,7 @@
         <v>778</v>
       </c>
       <c r="C755" t="s">
-        <v>1840</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="756" spans="1:3">
@@ -15161,7 +15149,7 @@
         <v>779</v>
       </c>
       <c r="C756" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="757" spans="1:3">
@@ -15172,7 +15160,7 @@
         <v>780</v>
       </c>
       <c r="C757" t="s">
-        <v>1842</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="758" spans="1:3">
@@ -15183,7 +15171,7 @@
         <v>781</v>
       </c>
       <c r="C758" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="759" spans="1:3">
@@ -15194,7 +15182,7 @@
         <v>782</v>
       </c>
       <c r="C759" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="760" spans="1:3">
@@ -15205,7 +15193,7 @@
         <v>783</v>
       </c>
       <c r="C760" t="s">
-        <v>1845</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="761" spans="1:3">
@@ -15216,7 +15204,7 @@
         <v>784</v>
       </c>
       <c r="C761" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="762" spans="1:3">
@@ -15227,7 +15215,7 @@
         <v>785</v>
       </c>
       <c r="C762" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="763" spans="1:3">
@@ -15238,7 +15226,7 @@
         <v>786</v>
       </c>
       <c r="C763" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="764" spans="1:3">
@@ -15249,7 +15237,7 @@
         <v>787</v>
       </c>
       <c r="C764" t="s">
-        <v>1849</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="765" spans="1:3">
@@ -15260,7 +15248,7 @@
         <v>788</v>
       </c>
       <c r="C765" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="766" spans="1:3">
@@ -15271,7 +15259,7 @@
         <v>789</v>
       </c>
       <c r="C766" t="s">
-        <v>1851</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="767" spans="1:3">
@@ -15282,7 +15270,7 @@
         <v>790</v>
       </c>
       <c r="C767" t="s">
-        <v>1852</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="768" spans="1:3">
@@ -15293,7 +15281,7 @@
         <v>791</v>
       </c>
       <c r="C768" t="s">
-        <v>1853</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="769" spans="1:3">
@@ -15304,7 +15292,7 @@
         <v>792</v>
       </c>
       <c r="C769" t="s">
-        <v>1854</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="770" spans="1:3">
@@ -15315,7 +15303,7 @@
         <v>793</v>
       </c>
       <c r="C770" t="s">
-        <v>1855</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="771" spans="1:3">
@@ -15326,7 +15314,7 @@
         <v>794</v>
       </c>
       <c r="C771" t="s">
-        <v>1856</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="772" spans="1:3">
@@ -15337,7 +15325,7 @@
         <v>795</v>
       </c>
       <c r="C772" t="s">
-        <v>1857</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="773" spans="1:3">
@@ -15348,7 +15336,7 @@
         <v>796</v>
       </c>
       <c r="C773" t="s">
-        <v>1858</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="774" spans="1:3">
@@ -15359,7 +15347,7 @@
         <v>797</v>
       </c>
       <c r="C774" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="775" spans="1:3">
@@ -15370,7 +15358,7 @@
         <v>798</v>
       </c>
       <c r="C775" t="s">
-        <v>1860</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="776" spans="1:3">
@@ -15381,7 +15369,7 @@
         <v>799</v>
       </c>
       <c r="C776" t="s">
-        <v>1861</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="777" spans="1:3">
@@ -15392,7 +15380,7 @@
         <v>800</v>
       </c>
       <c r="C777" t="s">
-        <v>1862</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="778" spans="1:3">
@@ -15403,7 +15391,7 @@
         <v>801</v>
       </c>
       <c r="C778" t="s">
-        <v>1863</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="779" spans="1:3">
@@ -15414,7 +15402,7 @@
         <v>802</v>
       </c>
       <c r="C779" t="s">
-        <v>1864</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="780" spans="1:3">
@@ -15425,7 +15413,7 @@
         <v>803</v>
       </c>
       <c r="C780" t="s">
-        <v>1865</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="781" spans="1:3">
@@ -15436,7 +15424,7 @@
         <v>804</v>
       </c>
       <c r="C781" t="s">
-        <v>1866</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="782" spans="1:3">
@@ -15447,7 +15435,7 @@
         <v>805</v>
       </c>
       <c r="C782" t="s">
-        <v>1867</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="783" spans="1:3">
@@ -15458,7 +15446,7 @@
         <v>806</v>
       </c>
       <c r="C783" t="s">
-        <v>1868</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="784" spans="1:3">
@@ -15469,7 +15457,7 @@
         <v>807</v>
       </c>
       <c r="C784" t="s">
-        <v>1869</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="785" spans="1:3">
@@ -15480,7 +15468,7 @@
         <v>808</v>
       </c>
       <c r="C785" t="s">
-        <v>1870</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="786" spans="1:3">
@@ -15491,7 +15479,7 @@
         <v>809</v>
       </c>
       <c r="C786" t="s">
-        <v>1871</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="787" spans="1:3">
@@ -15502,7 +15490,7 @@
         <v>810</v>
       </c>
       <c r="C787" t="s">
-        <v>1872</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="788" spans="1:3">
@@ -15513,7 +15501,7 @@
         <v>811</v>
       </c>
       <c r="C788" t="s">
-        <v>1873</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="789" spans="1:3">
@@ -15524,7 +15512,7 @@
         <v>812</v>
       </c>
       <c r="C789" t="s">
-        <v>1874</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="790" spans="1:3">
@@ -15535,7 +15523,7 @@
         <v>813</v>
       </c>
       <c r="C790" t="s">
-        <v>1875</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="791" spans="1:3">
@@ -15546,7 +15534,7 @@
         <v>814</v>
       </c>
       <c r="C791" t="s">
-        <v>1876</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="792" spans="1:3">
@@ -15557,7 +15545,7 @@
         <v>815</v>
       </c>
       <c r="C792" t="s">
-        <v>1877</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="793" spans="1:3">
@@ -15568,7 +15556,7 @@
         <v>816</v>
       </c>
       <c r="C793" t="s">
-        <v>1795</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="794" spans="1:3">
@@ -15579,7 +15567,7 @@
         <v>817</v>
       </c>
       <c r="C794" t="s">
-        <v>1878</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="795" spans="1:3">
@@ -15590,7 +15578,7 @@
         <v>818</v>
       </c>
       <c r="C795" t="s">
-        <v>1879</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="796" spans="1:3">
@@ -15601,7 +15589,7 @@
         <v>819</v>
       </c>
       <c r="C796" t="s">
-        <v>1880</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="797" spans="1:3">
@@ -15612,7 +15600,7 @@
         <v>820</v>
       </c>
       <c r="C797" t="s">
-        <v>1881</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="798" spans="1:3">
@@ -15623,7 +15611,7 @@
         <v>821</v>
       </c>
       <c r="C798" t="s">
-        <v>1882</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="799" spans="1:3">
@@ -15634,7 +15622,7 @@
         <v>822</v>
       </c>
       <c r="C799" t="s">
-        <v>1883</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="800" spans="1:3">
@@ -15645,7 +15633,7 @@
         <v>823</v>
       </c>
       <c r="C800" t="s">
-        <v>1884</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="801" spans="1:3">
@@ -15656,7 +15644,7 @@
         <v>824</v>
       </c>
       <c r="C801" t="s">
-        <v>1885</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="802" spans="1:3">
@@ -15667,7 +15655,7 @@
         <v>825</v>
       </c>
       <c r="C802" t="s">
-        <v>1886</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="803" spans="1:3">
@@ -15678,7 +15666,7 @@
         <v>826</v>
       </c>
       <c r="C803" t="s">
-        <v>1887</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="804" spans="1:3">
@@ -15689,7 +15677,7 @@
         <v>827</v>
       </c>
       <c r="C804" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="805" spans="1:3">
@@ -15700,7 +15688,7 @@
         <v>828</v>
       </c>
       <c r="C805" t="s">
-        <v>1889</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="806" spans="1:3">
@@ -15711,7 +15699,7 @@
         <v>829</v>
       </c>
       <c r="C806" t="s">
-        <v>1890</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="807" spans="1:3">
@@ -15722,7 +15710,7 @@
         <v>830</v>
       </c>
       <c r="C807" t="s">
-        <v>1891</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="808" spans="1:3">
@@ -15733,7 +15721,7 @@
         <v>831</v>
       </c>
       <c r="C808" t="s">
-        <v>1892</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="809" spans="1:3">
@@ -15744,7 +15732,7 @@
         <v>832</v>
       </c>
       <c r="C809" t="s">
-        <v>1893</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="810" spans="1:3">
@@ -15755,7 +15743,7 @@
         <v>833</v>
       </c>
       <c r="C810" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="811" spans="1:3">
@@ -15766,7 +15754,7 @@
         <v>834</v>
       </c>
       <c r="C811" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="812" spans="1:3">
@@ -15777,7 +15765,7 @@
         <v>835</v>
       </c>
       <c r="C812" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="813" spans="1:3">
@@ -15788,7 +15776,7 @@
         <v>836</v>
       </c>
       <c r="C813" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="814" spans="1:3">
@@ -15799,7 +15787,7 @@
         <v>837</v>
       </c>
       <c r="C814" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="815" spans="1:3">
@@ -15810,7 +15798,7 @@
         <v>838</v>
       </c>
       <c r="C815" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="816" spans="1:3">
@@ -15821,7 +15809,7 @@
         <v>839</v>
       </c>
       <c r="C816" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="817" spans="1:3">
@@ -15832,7 +15820,7 @@
         <v>840</v>
       </c>
       <c r="C817" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="818" spans="1:3">
@@ -15843,7 +15831,7 @@
         <v>841</v>
       </c>
       <c r="C818" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="819" spans="1:3">
@@ -15854,7 +15842,7 @@
         <v>842</v>
       </c>
       <c r="C819" t="s">
-        <v>1903</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="820" spans="1:3">
@@ -15865,7 +15853,7 @@
         <v>843</v>
       </c>
       <c r="C820" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="821" spans="1:3">
@@ -15876,7 +15864,7 @@
         <v>844</v>
       </c>
       <c r="C821" t="s">
-        <v>1905</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="822" spans="1:3">
@@ -15887,7 +15875,7 @@
         <v>845</v>
       </c>
       <c r="C822" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="823" spans="1:3">
@@ -15898,7 +15886,7 @@
         <v>846</v>
       </c>
       <c r="C823" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="824" spans="1:3">
@@ -15909,7 +15897,7 @@
         <v>847</v>
       </c>
       <c r="C824" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="825" spans="1:3">
@@ -15920,7 +15908,7 @@
         <v>848</v>
       </c>
       <c r="C825" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="826" spans="1:3">
@@ -15931,7 +15919,7 @@
         <v>849</v>
       </c>
       <c r="C826" t="s">
-        <v>1910</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="827" spans="1:3">
@@ -15942,7 +15930,7 @@
         <v>850</v>
       </c>
       <c r="C827" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="828" spans="1:3">
@@ -15953,7 +15941,7 @@
         <v>851</v>
       </c>
       <c r="C828" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="829" spans="1:3">
@@ -15964,7 +15952,7 @@
         <v>852</v>
       </c>
       <c r="C829" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="830" spans="1:3">
@@ -15975,7 +15963,7 @@
         <v>853</v>
       </c>
       <c r="C830" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="831" spans="1:3">
@@ -15986,7 +15974,7 @@
         <v>854</v>
       </c>
       <c r="C831" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="832" spans="1:3">
@@ -15997,7 +15985,7 @@
         <v>855</v>
       </c>
       <c r="C832" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="833" spans="1:3">
@@ -16008,7 +15996,7 @@
         <v>856</v>
       </c>
       <c r="C833" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="834" spans="1:3">
@@ -16019,7 +16007,7 @@
         <v>857</v>
       </c>
       <c r="C834" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="835" spans="1:3">
@@ -16030,7 +16018,7 @@
         <v>858</v>
       </c>
       <c r="C835" t="s">
-        <v>1919</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="836" spans="1:3">
@@ -16041,7 +16029,7 @@
         <v>859</v>
       </c>
       <c r="C836" t="s">
-        <v>1920</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="837" spans="1:3">
@@ -16052,7 +16040,7 @@
         <v>860</v>
       </c>
       <c r="C837" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="838" spans="1:3">
@@ -16063,7 +16051,7 @@
         <v>861</v>
       </c>
       <c r="C838" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="839" spans="1:3">
@@ -16074,7 +16062,7 @@
         <v>862</v>
       </c>
       <c r="C839" t="s">
-        <v>1923</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="840" spans="1:3">
@@ -16085,7 +16073,7 @@
         <v>863</v>
       </c>
       <c r="C840" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="841" spans="1:3">
@@ -16096,7 +16084,7 @@
         <v>864</v>
       </c>
       <c r="C841" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="842" spans="1:3">
@@ -16107,7 +16095,7 @@
         <v>865</v>
       </c>
       <c r="C842" t="s">
-        <v>1926</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="843" spans="1:3">
@@ -16118,7 +16106,7 @@
         <v>866</v>
       </c>
       <c r="C843" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="844" spans="1:3">
@@ -16129,7 +16117,7 @@
         <v>867</v>
       </c>
       <c r="C844" t="s">
-        <v>1928</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="845" spans="1:3">
@@ -16140,7 +16128,7 @@
         <v>868</v>
       </c>
       <c r="C845" t="s">
-        <v>1929</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="846" spans="1:3">
@@ -16151,7 +16139,7 @@
         <v>869</v>
       </c>
       <c r="C846" t="s">
-        <v>1930</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="847" spans="1:3">
@@ -16162,7 +16150,7 @@
         <v>870</v>
       </c>
       <c r="C847" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="848" spans="1:3">
@@ -16173,7 +16161,7 @@
         <v>871</v>
       </c>
       <c r="C848" t="s">
-        <v>1932</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="849" spans="1:3">
@@ -16184,7 +16172,7 @@
         <v>872</v>
       </c>
       <c r="C849" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="850" spans="1:3">
@@ -16195,7 +16183,7 @@
         <v>873</v>
       </c>
       <c r="C850" t="s">
-        <v>1934</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="851" spans="1:3">
@@ -16206,7 +16194,7 @@
         <v>874</v>
       </c>
       <c r="C851" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="852" spans="1:3">
@@ -16217,7 +16205,7 @@
         <v>875</v>
       </c>
       <c r="C852" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="853" spans="1:3">
@@ -16228,7 +16216,7 @@
         <v>876</v>
       </c>
       <c r="C853" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="854" spans="1:3">
@@ -16239,7 +16227,7 @@
         <v>877</v>
       </c>
       <c r="C854" t="s">
-        <v>1938</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="855" spans="1:3">
@@ -16250,7 +16238,7 @@
         <v>878</v>
       </c>
       <c r="C855" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="856" spans="1:3">
@@ -16261,7 +16249,7 @@
         <v>879</v>
       </c>
       <c r="C856" t="s">
-        <v>1940</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="857" spans="1:3">
@@ -16272,7 +16260,7 @@
         <v>880</v>
       </c>
       <c r="C857" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="858" spans="1:3">
@@ -16283,7 +16271,7 @@
         <v>881</v>
       </c>
       <c r="C858" t="s">
-        <v>1942</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="859" spans="1:3">
@@ -16294,7 +16282,7 @@
         <v>882</v>
       </c>
       <c r="C859" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="860" spans="1:3">
@@ -16305,7 +16293,7 @@
         <v>883</v>
       </c>
       <c r="C860" t="s">
-        <v>1944</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="861" spans="1:3">
@@ -16316,7 +16304,7 @@
         <v>884</v>
       </c>
       <c r="C861" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="862" spans="1:3">
@@ -16327,29 +16315,29 @@
         <v>885</v>
       </c>
       <c r="C862" t="s">
-        <v>1946</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="863" spans="1:3">
       <c r="A863" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B863" t="s">
         <v>886</v>
       </c>
       <c r="C863" t="s">
-        <v>1947</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="864" spans="1:3">
       <c r="A864" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B864" t="s">
         <v>887</v>
       </c>
       <c r="C864" t="s">
-        <v>1948</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="865" spans="1:3">
@@ -16360,7 +16348,7 @@
         <v>888</v>
       </c>
       <c r="C865" t="s">
-        <v>1949</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="866" spans="1:3">
@@ -16371,7 +16359,7 @@
         <v>889</v>
       </c>
       <c r="C866" t="s">
-        <v>1950</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="867" spans="1:3">
@@ -16382,7 +16370,7 @@
         <v>890</v>
       </c>
       <c r="C867" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="868" spans="1:3">
@@ -16393,7 +16381,7 @@
         <v>891</v>
       </c>
       <c r="C868" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="869" spans="1:3">
@@ -16404,7 +16392,7 @@
         <v>892</v>
       </c>
       <c r="C869" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="870" spans="1:3">
@@ -16415,7 +16403,7 @@
         <v>893</v>
       </c>
       <c r="C870" t="s">
-        <v>1954</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="871" spans="1:3">
@@ -16426,7 +16414,7 @@
         <v>894</v>
       </c>
       <c r="C871" t="s">
-        <v>1955</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="872" spans="1:3">
@@ -16437,7 +16425,7 @@
         <v>895</v>
       </c>
       <c r="C872" t="s">
-        <v>1956</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="873" spans="1:3">
@@ -16448,7 +16436,7 @@
         <v>896</v>
       </c>
       <c r="C873" t="s">
-        <v>1957</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="874" spans="1:3">
@@ -16459,7 +16447,7 @@
         <v>897</v>
       </c>
       <c r="C874" t="s">
-        <v>1958</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="875" spans="1:3">
@@ -16470,7 +16458,7 @@
         <v>898</v>
       </c>
       <c r="C875" t="s">
-        <v>1959</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="876" spans="1:3">
@@ -16481,7 +16469,7 @@
         <v>899</v>
       </c>
       <c r="C876" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="877" spans="1:3">
@@ -16492,7 +16480,7 @@
         <v>900</v>
       </c>
       <c r="C877" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="878" spans="1:3">
@@ -16503,7 +16491,7 @@
         <v>901</v>
       </c>
       <c r="C878" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="879" spans="1:3">
@@ -16514,7 +16502,7 @@
         <v>902</v>
       </c>
       <c r="C879" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="880" spans="1:3">
@@ -16525,7 +16513,7 @@
         <v>903</v>
       </c>
       <c r="C880" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="881" spans="1:3">
@@ -16536,7 +16524,7 @@
         <v>904</v>
       </c>
       <c r="C881" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="882" spans="1:3">
@@ -16547,7 +16535,7 @@
         <v>905</v>
       </c>
       <c r="C882" t="s">
-        <v>1966</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="883" spans="1:3">
@@ -16558,7 +16546,7 @@
         <v>906</v>
       </c>
       <c r="C883" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="884" spans="1:3">
@@ -16569,7 +16557,7 @@
         <v>907</v>
       </c>
       <c r="C884" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="885" spans="1:3">
@@ -16580,7 +16568,7 @@
         <v>908</v>
       </c>
       <c r="C885" t="s">
-        <v>1969</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="886" spans="1:3">
@@ -16591,7 +16579,7 @@
         <v>909</v>
       </c>
       <c r="C886" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="887" spans="1:3">
@@ -16602,7 +16590,7 @@
         <v>910</v>
       </c>
       <c r="C887" t="s">
-        <v>1971</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="888" spans="1:3">
@@ -16613,7 +16601,7 @@
         <v>911</v>
       </c>
       <c r="C888" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="889" spans="1:3">
@@ -16624,7 +16612,7 @@
         <v>912</v>
       </c>
       <c r="C889" t="s">
-        <v>1973</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="890" spans="1:3">
@@ -16635,7 +16623,7 @@
         <v>913</v>
       </c>
       <c r="C890" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="891" spans="1:3">
@@ -16646,7 +16634,7 @@
         <v>914</v>
       </c>
       <c r="C891" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="892" spans="1:3">
@@ -16657,7 +16645,7 @@
         <v>915</v>
       </c>
       <c r="C892" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="893" spans="1:3">
@@ -16668,7 +16656,7 @@
         <v>916</v>
       </c>
       <c r="C893" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="894" spans="1:3">
@@ -16679,7 +16667,7 @@
         <v>917</v>
       </c>
       <c r="C894" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="895" spans="1:3">
@@ -16690,7 +16678,7 @@
         <v>918</v>
       </c>
       <c r="C895" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="896" spans="1:3">
@@ -16701,7 +16689,7 @@
         <v>919</v>
       </c>
       <c r="C896" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="897" spans="1:3">
@@ -16712,7 +16700,7 @@
         <v>920</v>
       </c>
       <c r="C897" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="898" spans="1:3">
@@ -16723,7 +16711,7 @@
         <v>921</v>
       </c>
       <c r="C898" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="899" spans="1:3">
@@ -16734,7 +16722,7 @@
         <v>922</v>
       </c>
       <c r="C899" t="s">
-        <v>1983</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="900" spans="1:3">
@@ -16745,7 +16733,7 @@
         <v>923</v>
       </c>
       <c r="C900" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="901" spans="1:3">
@@ -16756,7 +16744,7 @@
         <v>924</v>
       </c>
       <c r="C901" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="902" spans="1:3">
@@ -16767,7 +16755,7 @@
         <v>925</v>
       </c>
       <c r="C902" t="s">
-        <v>1986</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="903" spans="1:3">
@@ -16778,7 +16766,7 @@
         <v>926</v>
       </c>
       <c r="C903" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="904" spans="1:3">
@@ -16789,7 +16777,7 @@
         <v>927</v>
       </c>
       <c r="C904" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="905" spans="1:3">
@@ -16800,7 +16788,7 @@
         <v>928</v>
       </c>
       <c r="C905" t="s">
-        <v>1989</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="906" spans="1:3">
@@ -16811,7 +16799,7 @@
         <v>929</v>
       </c>
       <c r="C906" t="s">
-        <v>1990</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="907" spans="1:3">
@@ -16822,7 +16810,7 @@
         <v>930</v>
       </c>
       <c r="C907" t="s">
-        <v>1991</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="908" spans="1:3">
@@ -16833,7 +16821,7 @@
         <v>931</v>
       </c>
       <c r="C908" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="909" spans="1:3">
@@ -16844,7 +16832,7 @@
         <v>932</v>
       </c>
       <c r="C909" t="s">
-        <v>1993</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="910" spans="1:3">
@@ -16855,7 +16843,7 @@
         <v>933</v>
       </c>
       <c r="C910" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="911" spans="1:3">
@@ -16866,7 +16854,7 @@
         <v>934</v>
       </c>
       <c r="C911" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="912" spans="1:3">
@@ -16877,7 +16865,7 @@
         <v>935</v>
       </c>
       <c r="C912" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="913" spans="1:3">
@@ -16888,7 +16876,7 @@
         <v>936</v>
       </c>
       <c r="C913" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="914" spans="1:3">
@@ -16899,7 +16887,7 @@
         <v>937</v>
       </c>
       <c r="C914" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="915" spans="1:3">
@@ -16910,7 +16898,7 @@
         <v>938</v>
       </c>
       <c r="C915" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="916" spans="1:3">
@@ -16921,7 +16909,7 @@
         <v>939</v>
       </c>
       <c r="C916" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="917" spans="1:3">
@@ -16932,7 +16920,7 @@
         <v>940</v>
       </c>
       <c r="C917" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="918" spans="1:3">
@@ -16943,7 +16931,7 @@
         <v>941</v>
       </c>
       <c r="C918" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="919" spans="1:3">
@@ -16954,7 +16942,7 @@
         <v>942</v>
       </c>
       <c r="C919" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="920" spans="1:3">
@@ -16965,7 +16953,7 @@
         <v>943</v>
       </c>
       <c r="C920" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="921" spans="1:3">
@@ -16976,7 +16964,7 @@
         <v>944</v>
       </c>
       <c r="C921" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="922" spans="1:3">
@@ -16987,7 +16975,7 @@
         <v>945</v>
       </c>
       <c r="C922" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="923" spans="1:3">
@@ -16998,7 +16986,7 @@
         <v>946</v>
       </c>
       <c r="C923" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="924" spans="1:3">
@@ -17009,7 +16997,7 @@
         <v>947</v>
       </c>
       <c r="C924" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="925" spans="1:3">
@@ -17020,7 +17008,7 @@
         <v>948</v>
       </c>
       <c r="C925" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="926" spans="1:3">
@@ -17031,7 +17019,7 @@
         <v>949</v>
       </c>
       <c r="C926" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="927" spans="1:3">
@@ -17042,7 +17030,7 @@
         <v>950</v>
       </c>
       <c r="C927" t="s">
-        <v>2011</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="928" spans="1:3">
@@ -17053,7 +17041,7 @@
         <v>951</v>
       </c>
       <c r="C928" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="929" spans="1:3">
@@ -17064,7 +17052,7 @@
         <v>952</v>
       </c>
       <c r="C929" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="930" spans="1:3">
@@ -17075,7 +17063,7 @@
         <v>953</v>
       </c>
       <c r="C930" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="931" spans="1:3">
@@ -17086,7 +17074,7 @@
         <v>954</v>
       </c>
       <c r="C931" t="s">
-        <v>2015</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="932" spans="1:3">
@@ -17097,7 +17085,7 @@
         <v>955</v>
       </c>
       <c r="C932" t="s">
-        <v>2016</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="933" spans="1:3">
@@ -17108,7 +17096,7 @@
         <v>956</v>
       </c>
       <c r="C933" t="s">
-        <v>2017</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="934" spans="1:3">
@@ -17119,7 +17107,7 @@
         <v>957</v>
       </c>
       <c r="C934" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="935" spans="1:3">
@@ -17130,7 +17118,7 @@
         <v>958</v>
       </c>
       <c r="C935" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="936" spans="1:3">
@@ -17141,7 +17129,7 @@
         <v>959</v>
       </c>
       <c r="C936" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="937" spans="1:3">
@@ -17152,7 +17140,7 @@
         <v>960</v>
       </c>
       <c r="C937" t="s">
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="938" spans="1:3">
@@ -17163,7 +17151,7 @@
         <v>961</v>
       </c>
       <c r="C938" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="939" spans="1:3">
@@ -17174,7 +17162,7 @@
         <v>962</v>
       </c>
       <c r="C939" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="940" spans="1:3">
@@ -17185,7 +17173,7 @@
         <v>963</v>
       </c>
       <c r="C940" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="941" spans="1:3">
@@ -17196,7 +17184,7 @@
         <v>964</v>
       </c>
       <c r="C941" t="s">
-        <v>2025</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="942" spans="1:3">
@@ -17207,7 +17195,7 @@
         <v>965</v>
       </c>
       <c r="C942" t="s">
-        <v>2026</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="943" spans="1:3">
@@ -17218,7 +17206,7 @@
         <v>966</v>
       </c>
       <c r="C943" t="s">
-        <v>2027</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="944" spans="1:3">
@@ -17229,7 +17217,7 @@
         <v>967</v>
       </c>
       <c r="C944" t="s">
-        <v>2028</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="945" spans="1:3">
@@ -17240,7 +17228,7 @@
         <v>968</v>
       </c>
       <c r="C945" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="946" spans="1:3">
@@ -17251,7 +17239,7 @@
         <v>969</v>
       </c>
       <c r="C946" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="947" spans="1:3">
@@ -17262,7 +17250,7 @@
         <v>970</v>
       </c>
       <c r="C947" t="s">
-        <v>2031</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="948" spans="1:3">
@@ -17273,7 +17261,7 @@
         <v>971</v>
       </c>
       <c r="C948" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="949" spans="1:3">
@@ -17284,7 +17272,7 @@
         <v>972</v>
       </c>
       <c r="C949" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="950" spans="1:3">
@@ -17295,7 +17283,7 @@
         <v>973</v>
       </c>
       <c r="C950" t="s">
-        <v>2034</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="951" spans="1:3">
@@ -17306,7 +17294,7 @@
         <v>974</v>
       </c>
       <c r="C951" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="952" spans="1:3">
@@ -17317,7 +17305,7 @@
         <v>975</v>
       </c>
       <c r="C952" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="953" spans="1:3">
@@ -17328,7 +17316,7 @@
         <v>976</v>
       </c>
       <c r="C953" t="s">
-        <v>2037</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="954" spans="1:3">
@@ -17339,7 +17327,7 @@
         <v>977</v>
       </c>
       <c r="C954" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="955" spans="1:3">
@@ -17350,7 +17338,7 @@
         <v>978</v>
       </c>
       <c r="C955" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="956" spans="1:3">
@@ -17361,7 +17349,7 @@
         <v>979</v>
       </c>
       <c r="C956" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="957" spans="1:3">
@@ -17372,7 +17360,7 @@
         <v>980</v>
       </c>
       <c r="C957" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="958" spans="1:3">
@@ -17383,7 +17371,7 @@
         <v>981</v>
       </c>
       <c r="C958" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="959" spans="1:3">
@@ -17394,7 +17382,7 @@
         <v>982</v>
       </c>
       <c r="C959" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="960" spans="1:3">
@@ -17405,7 +17393,7 @@
         <v>983</v>
       </c>
       <c r="C960" t="s">
-        <v>2044</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="961" spans="1:3">
@@ -17416,7 +17404,7 @@
         <v>984</v>
       </c>
       <c r="C961" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="962" spans="1:3">
@@ -17427,7 +17415,7 @@
         <v>985</v>
       </c>
       <c r="C962" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="963" spans="1:3">
@@ -17438,7 +17426,7 @@
         <v>986</v>
       </c>
       <c r="C963" t="s">
-        <v>2047</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="964" spans="1:3">
@@ -17449,7 +17437,7 @@
         <v>987</v>
       </c>
       <c r="C964" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="965" spans="1:3">
@@ -17460,7 +17448,7 @@
         <v>988</v>
       </c>
       <c r="C965" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="966" spans="1:3">
@@ -17471,7 +17459,7 @@
         <v>989</v>
       </c>
       <c r="C966" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="967" spans="1:3">
@@ -17482,7 +17470,7 @@
         <v>990</v>
       </c>
       <c r="C967" t="s">
-        <v>2051</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="968" spans="1:3">
@@ -17493,7 +17481,7 @@
         <v>991</v>
       </c>
       <c r="C968" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="969" spans="1:3">
@@ -17504,7 +17492,7 @@
         <v>992</v>
       </c>
       <c r="C969" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="970" spans="1:3">
@@ -17515,7 +17503,7 @@
         <v>993</v>
       </c>
       <c r="C970" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="971" spans="1:3">
@@ -17526,7 +17514,7 @@
         <v>994</v>
       </c>
       <c r="C971" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="972" spans="1:3">
@@ -17537,7 +17525,7 @@
         <v>995</v>
       </c>
       <c r="C972" t="s">
-        <v>2056</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="973" spans="1:3">
@@ -17548,7 +17536,7 @@
         <v>996</v>
       </c>
       <c r="C973" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="974" spans="1:3">
@@ -17559,29 +17547,29 @@
         <v>997</v>
       </c>
       <c r="C974" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="975" spans="1:3">
       <c r="A975" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B975" t="s">
         <v>998</v>
       </c>
       <c r="C975" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="976" spans="1:3">
       <c r="A976" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B976" t="s">
         <v>999</v>
       </c>
       <c r="C976" t="s">
-        <v>2060</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="977" spans="1:3">
@@ -17592,7 +17580,7 @@
         <v>1000</v>
       </c>
       <c r="C977" t="s">
-        <v>2061</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="978" spans="1:3">
@@ -17603,7 +17591,7 @@
         <v>1001</v>
       </c>
       <c r="C978" t="s">
-        <v>2062</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="979" spans="1:3">
@@ -17614,7 +17602,7 @@
         <v>1002</v>
       </c>
       <c r="C979" t="s">
-        <v>2063</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="980" spans="1:3">
@@ -17625,7 +17613,7 @@
         <v>1003</v>
       </c>
       <c r="C980" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="981" spans="1:3">
@@ -17636,7 +17624,7 @@
         <v>1004</v>
       </c>
       <c r="C981" t="s">
-        <v>2065</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="982" spans="1:3">
@@ -17647,7 +17635,7 @@
         <v>1005</v>
       </c>
       <c r="C982" t="s">
-        <v>2066</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="983" spans="1:3">
@@ -17658,7 +17646,7 @@
         <v>1006</v>
       </c>
       <c r="C983" t="s">
-        <v>2067</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="984" spans="1:3">
@@ -17669,7 +17657,7 @@
         <v>1007</v>
       </c>
       <c r="C984" t="s">
-        <v>2068</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="985" spans="1:3">
@@ -17680,7 +17668,7 @@
         <v>1008</v>
       </c>
       <c r="C985" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="986" spans="1:3">
@@ -17691,7 +17679,7 @@
         <v>1009</v>
       </c>
       <c r="C986" t="s">
-        <v>2070</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="987" spans="1:3">
@@ -17702,7 +17690,7 @@
         <v>1010</v>
       </c>
       <c r="C987" t="s">
-        <v>2071</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="988" spans="1:3">
@@ -17713,7 +17701,7 @@
         <v>1011</v>
       </c>
       <c r="C988" t="s">
-        <v>2072</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="989" spans="1:3">
@@ -17724,7 +17712,7 @@
         <v>1012</v>
       </c>
       <c r="C989" t="s">
-        <v>2073</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="990" spans="1:3">
@@ -17735,7 +17723,7 @@
         <v>1013</v>
       </c>
       <c r="C990" t="s">
-        <v>2074</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="991" spans="1:3">
@@ -17746,7 +17734,7 @@
         <v>1014</v>
       </c>
       <c r="C991" t="s">
-        <v>2075</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="992" spans="1:3">
@@ -17757,7 +17745,7 @@
         <v>1015</v>
       </c>
       <c r="C992" t="s">
-        <v>2076</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="993" spans="1:3">
@@ -17768,7 +17756,7 @@
         <v>1016</v>
       </c>
       <c r="C993" t="s">
-        <v>2077</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="994" spans="1:3">
@@ -17779,7 +17767,7 @@
         <v>1017</v>
       </c>
       <c r="C994" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="995" spans="1:3">
@@ -17790,7 +17778,7 @@
         <v>1018</v>
       </c>
       <c r="C995" t="s">
-        <v>2079</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="996" spans="1:3">
@@ -17801,7 +17789,7 @@
         <v>1019</v>
       </c>
       <c r="C996" t="s">
-        <v>2080</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="997" spans="1:3">
@@ -17812,7 +17800,7 @@
         <v>1020</v>
       </c>
       <c r="C997" t="s">
-        <v>2081</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="998" spans="1:3">
@@ -17823,7 +17811,7 @@
         <v>1021</v>
       </c>
       <c r="C998" t="s">
-        <v>2082</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="999" spans="1:3">
@@ -17834,7 +17822,7 @@
         <v>1022</v>
       </c>
       <c r="C999" t="s">
-        <v>2083</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="1000" spans="1:3">
@@ -17845,7 +17833,7 @@
         <v>1023</v>
       </c>
       <c r="C1000" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="1001" spans="1:3">
@@ -17856,7 +17844,7 @@
         <v>1024</v>
       </c>
       <c r="C1001" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="1002" spans="1:3">
@@ -17867,7 +17855,7 @@
         <v>1025</v>
       </c>
       <c r="C1002" t="s">
-        <v>2086</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="1003" spans="1:3">
@@ -17878,7 +17866,7 @@
         <v>1026</v>
       </c>
       <c r="C1003" t="s">
-        <v>2087</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="1004" spans="1:3">
@@ -17889,7 +17877,7 @@
         <v>1027</v>
       </c>
       <c r="C1004" t="s">
-        <v>2088</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="1005" spans="1:3">
@@ -17900,7 +17888,7 @@
         <v>1028</v>
       </c>
       <c r="C1005" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="1006" spans="1:3">
@@ -17911,7 +17899,7 @@
         <v>1029</v>
       </c>
       <c r="C1006" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="1007" spans="1:3">
@@ -17922,7 +17910,7 @@
         <v>1030</v>
       </c>
       <c r="C1007" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="1008" spans="1:3">
@@ -17933,7 +17921,7 @@
         <v>1031</v>
       </c>
       <c r="C1008" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="1009" spans="1:3">
@@ -17944,7 +17932,7 @@
         <v>1032</v>
       </c>
       <c r="C1009" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="1010" spans="1:3">
@@ -17955,7 +17943,7 @@
         <v>1033</v>
       </c>
       <c r="C1010" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="1011" spans="1:3">
@@ -17966,7 +17954,7 @@
         <v>1034</v>
       </c>
       <c r="C1011" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="1012" spans="1:3">
@@ -17977,7 +17965,7 @@
         <v>1035</v>
       </c>
       <c r="C1012" t="s">
-        <v>2096</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="1013" spans="1:3">
@@ -17988,7 +17976,7 @@
         <v>1036</v>
       </c>
       <c r="C1013" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="1014" spans="1:3">
@@ -17999,7 +17987,7 @@
         <v>1037</v>
       </c>
       <c r="C1014" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="1015" spans="1:3">
@@ -18010,7 +17998,7 @@
         <v>1038</v>
       </c>
       <c r="C1015" t="s">
-        <v>2099</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="1016" spans="1:3">
@@ -18021,7 +18009,7 @@
         <v>1039</v>
       </c>
       <c r="C1016" t="s">
-        <v>2093</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="1017" spans="1:3">
@@ -18032,7 +18020,7 @@
         <v>1040</v>
       </c>
       <c r="C1017" t="s">
-        <v>2100</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="1018" spans="1:3">
@@ -18043,7 +18031,7 @@
         <v>1041</v>
       </c>
       <c r="C1018" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="1019" spans="1:3">
@@ -18054,7 +18042,7 @@
         <v>1042</v>
       </c>
       <c r="C1019" t="s">
-        <v>2102</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="1020" spans="1:3">
@@ -18065,7 +18053,7 @@
         <v>1043</v>
       </c>
       <c r="C1020" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="1021" spans="1:3">
@@ -18076,7 +18064,7 @@
         <v>1044</v>
       </c>
       <c r="C1021" t="s">
-        <v>2104</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="1022" spans="1:3">
@@ -18087,7 +18075,7 @@
         <v>1045</v>
       </c>
       <c r="C1022" t="s">
-        <v>2105</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="1023" spans="1:3">
@@ -18098,7 +18086,7 @@
         <v>1046</v>
       </c>
       <c r="C1023" t="s">
-        <v>2106</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="1024" spans="1:3">
@@ -18109,7 +18097,7 @@
         <v>1047</v>
       </c>
       <c r="C1024" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="1025" spans="1:3">
@@ -18120,7 +18108,7 @@
         <v>1048</v>
       </c>
       <c r="C1025" t="s">
-        <v>2108</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="1026" spans="1:3">
@@ -18131,7 +18119,7 @@
         <v>1049</v>
       </c>
       <c r="C1026" t="s">
-        <v>2109</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="1027" spans="1:3">
@@ -18142,7 +18130,7 @@
         <v>1050</v>
       </c>
       <c r="C1027" t="s">
-        <v>2110</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="1028" spans="1:3">
@@ -18153,7 +18141,7 @@
         <v>1051</v>
       </c>
       <c r="C1028" t="s">
-        <v>2111</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="1029" spans="1:3">
@@ -18164,7 +18152,7 @@
         <v>1052</v>
       </c>
       <c r="C1029" t="s">
-        <v>2112</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="1030" spans="1:3">
@@ -18175,7 +18163,7 @@
         <v>1053</v>
       </c>
       <c r="C1030" t="s">
-        <v>2113</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="1031" spans="1:3">
@@ -18186,7 +18174,7 @@
         <v>1054</v>
       </c>
       <c r="C1031" t="s">
-        <v>2114</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="1032" spans="1:3">
@@ -18197,7 +18185,7 @@
         <v>1055</v>
       </c>
       <c r="C1032" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="1033" spans="1:3">
@@ -18208,7 +18196,7 @@
         <v>1056</v>
       </c>
       <c r="C1033" t="s">
-        <v>2116</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="1034" spans="1:3">
@@ -18219,7 +18207,7 @@
         <v>1057</v>
       </c>
       <c r="C1034" t="s">
-        <v>2117</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="1035" spans="1:3">
@@ -18230,7 +18218,7 @@
         <v>1058</v>
       </c>
       <c r="C1035" t="s">
-        <v>2118</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="1036" spans="1:3">
@@ -18241,7 +18229,7 @@
         <v>1059</v>
       </c>
       <c r="C1036" t="s">
-        <v>2119</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="1037" spans="1:3">
@@ -18252,7 +18240,7 @@
         <v>1060</v>
       </c>
       <c r="C1037" t="s">
-        <v>2120</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="1038" spans="1:3">
@@ -18263,7 +18251,7 @@
         <v>1061</v>
       </c>
       <c r="C1038" t="s">
-        <v>2094</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="1039" spans="1:3">
@@ -18274,7 +18262,7 @@
         <v>1062</v>
       </c>
       <c r="C1039" t="s">
-        <v>2121</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="1040" spans="1:3">
@@ -18285,7 +18273,7 @@
         <v>1063</v>
       </c>
       <c r="C1040" t="s">
-        <v>2122</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="1041" spans="1:3">
@@ -18296,7 +18284,7 @@
         <v>1064</v>
       </c>
       <c r="C1041" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="1042" spans="1:3">
@@ -18307,7 +18295,7 @@
         <v>1065</v>
       </c>
       <c r="C1042" t="s">
-        <v>2075</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="1043" spans="1:3">
@@ -18318,7 +18306,7 @@
         <v>1066</v>
       </c>
       <c r="C1043" t="s">
-        <v>2124</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="1044" spans="1:3">
@@ -18329,7 +18317,7 @@
         <v>1067</v>
       </c>
       <c r="C1044" t="s">
-        <v>2125</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="1045" spans="1:3">
@@ -18340,7 +18328,7 @@
         <v>1068</v>
       </c>
       <c r="C1045" t="s">
-        <v>2126</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="1046" spans="1:3">
@@ -18351,29 +18339,29 @@
         <v>1069</v>
       </c>
       <c r="C1046" t="s">
-        <v>2127</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="1047" spans="1:3">
       <c r="A1047" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1047" t="s">
         <v>1070</v>
       </c>
       <c r="C1047" t="s">
-        <v>2128</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="1048" spans="1:3">
       <c r="A1048" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1048" t="s">
         <v>1071</v>
       </c>
       <c r="C1048" t="s">
-        <v>2129</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="1049" spans="1:3">
@@ -18384,7 +18372,7 @@
         <v>1072</v>
       </c>
       <c r="C1049" t="s">
-        <v>2130</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="1050" spans="1:3">
@@ -18395,7 +18383,7 @@
         <v>1073</v>
       </c>
       <c r="C1050" t="s">
-        <v>2131</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="1051" spans="1:3">
@@ -18406,7 +18394,7 @@
         <v>1074</v>
       </c>
       <c r="C1051" t="s">
-        <v>2132</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="1052" spans="1:3">
@@ -18417,7 +18405,7 @@
         <v>1075</v>
       </c>
       <c r="C1052" t="s">
-        <v>2133</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="1053" spans="1:3">
@@ -18428,7 +18416,7 @@
         <v>1076</v>
       </c>
       <c r="C1053" t="s">
-        <v>2134</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="1054" spans="1:3">
@@ -18439,7 +18427,7 @@
         <v>1077</v>
       </c>
       <c r="C1054" t="s">
-        <v>2135</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="1055" spans="1:3">
@@ -18450,7 +18438,7 @@
         <v>1078</v>
       </c>
       <c r="C1055" t="s">
-        <v>2136</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="1056" spans="1:3">
@@ -18461,7 +18449,7 @@
         <v>1079</v>
       </c>
       <c r="C1056" t="s">
-        <v>2137</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="1057" spans="1:3">
@@ -18472,7 +18460,7 @@
         <v>1080</v>
       </c>
       <c r="C1057" t="s">
-        <v>2138</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="1058" spans="1:3">
@@ -18483,7 +18471,7 @@
         <v>1081</v>
       </c>
       <c r="C1058" t="s">
-        <v>2139</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="1059" spans="1:3">
@@ -18494,7 +18482,7 @@
         <v>1082</v>
       </c>
       <c r="C1059" t="s">
-        <v>2140</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="1060" spans="1:3">
@@ -18505,7 +18493,7 @@
         <v>1083</v>
       </c>
       <c r="C1060" t="s">
-        <v>2141</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="1061" spans="1:3">
@@ -18516,7 +18504,7 @@
         <v>1084</v>
       </c>
       <c r="C1061" t="s">
-        <v>2142</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="1062" spans="1:3">
@@ -18527,7 +18515,7 @@
         <v>1085</v>
       </c>
       <c r="C1062" t="s">
-        <v>2143</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="1063" spans="1:3">
@@ -18538,7 +18526,7 @@
         <v>1086</v>
       </c>
       <c r="C1063" t="s">
-        <v>2144</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="1064" spans="1:3">
@@ -18549,7 +18537,7 @@
         <v>1087</v>
       </c>
       <c r="C1064" t="s">
-        <v>2145</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="1065" spans="1:3">
@@ -18560,7 +18548,7 @@
         <v>1088</v>
       </c>
       <c r="C1065" t="s">
-        <v>2146</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="1066" spans="1:3">
@@ -18571,7 +18559,7 @@
         <v>1089</v>
       </c>
       <c r="C1066" t="s">
-        <v>2147</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="1067" spans="1:3">
@@ -18582,7 +18570,7 @@
         <v>1090</v>
       </c>
       <c r="C1067" t="s">
-        <v>2148</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="1068" spans="1:3">
@@ -18593,7 +18581,7 @@
         <v>1091</v>
       </c>
       <c r="C1068" t="s">
-        <v>2149</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="1069" spans="1:3">
@@ -18604,7 +18592,7 @@
         <v>1092</v>
       </c>
       <c r="C1069" t="s">
-        <v>2150</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="1070" spans="1:3">
@@ -18615,7 +18603,7 @@
         <v>1093</v>
       </c>
       <c r="C1070" t="s">
-        <v>2151</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1071" spans="1:3">
@@ -18626,7 +18614,7 @@
         <v>1094</v>
       </c>
       <c r="C1071" t="s">
-        <v>2152</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="1072" spans="1:3">
@@ -18637,7 +18625,7 @@
         <v>1095</v>
       </c>
       <c r="C1072" t="s">
-        <v>2153</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="1073" spans="1:3">
@@ -18648,40 +18636,18 @@
         <v>1096</v>
       </c>
       <c r="C1073" t="s">
-        <v>2154</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="1074" spans="1:3">
       <c r="A1074" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1074" t="s">
         <v>1097</v>
       </c>
       <c r="C1074" t="s">
-        <v>2155</v>
-      </c>
-    </row>
-    <row r="1075" spans="1:3">
-      <c r="A1075" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1075" t="s">
-        <v>1098</v>
-      </c>
-      <c r="C1075" t="s">
-        <v>2156</v>
-      </c>
-    </row>
-    <row r="1076" spans="1:3">
-      <c r="A1076" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1076" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C1076" t="s">
-        <v>2157</v>
+        <v>2153</v>
       </c>
     </row>
   </sheetData>

--- a/faltantes_por_estados.xlsx
+++ b/faltantes_por_estados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3183" uniqueCount="2129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3174" uniqueCount="2123">
   <si>
     <t>entidad</t>
   </si>
@@ -1723,9 +1723,6 @@
     <t>HGIMB003890</t>
   </si>
   <si>
-    <t>HGIMB004276</t>
-  </si>
-  <si>
     <t>HGIMB004404</t>
   </si>
   <si>
@@ -2251,9 +2248,6 @@
     <t>SLIMB000801</t>
   </si>
   <si>
-    <t>SLIMB000813</t>
-  </si>
-  <si>
     <t>SLIMB001472</t>
   </si>
   <si>
@@ -2269,9 +2263,6 @@
     <t>SLIMB002201</t>
   </si>
   <si>
-    <t>SLIMB003012</t>
-  </si>
-  <si>
     <t>SRIMB000045</t>
   </si>
   <si>
@@ -4873,9 +4864,6 @@
     <t>EJIDO EL PARAÍSO</t>
   </si>
   <si>
-    <t>DOS CARLOS PUEBLO NUEVO</t>
-  </si>
-  <si>
     <t>NICOLÁS BRAVO</t>
   </si>
   <si>
@@ -5395,9 +5383,6 @@
     <t>QUILA</t>
   </si>
   <si>
-    <t>SAN LORENZO</t>
-  </si>
-  <si>
     <t>LA NORIA DE SAN ANTONIO (LA NORIA)</t>
   </si>
   <si>
@@ -5411,9 +5396,6 @@
   </si>
   <si>
     <t>VALLE DEL JARIPILLO</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD MOCHIS II</t>
   </si>
   <si>
     <t>CENTRO DE SALUD RURAL COLONIA MORELOS</t>
@@ -6758,7 +6740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1061"/>
+  <dimension ref="A1:C1058"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6780,7 +6762,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6791,7 +6773,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6802,7 +6784,7 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6813,7 +6795,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6824,7 +6806,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6835,7 +6817,7 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6846,7 +6828,7 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6857,7 +6839,7 @@
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6868,7 +6850,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6879,7 +6861,7 @@
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6890,7 +6872,7 @@
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6901,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6912,7 +6894,7 @@
         <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6923,7 +6905,7 @@
         <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -6934,7 +6916,7 @@
         <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6956,7 +6938,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6967,7 +6949,7 @@
         <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6978,7 +6960,7 @@
         <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6989,7 +6971,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -7000,7 +6982,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -7011,7 +6993,7 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -7022,7 +7004,7 @@
         <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -7033,7 +7015,7 @@
         <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -7044,7 +7026,7 @@
         <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -7066,7 +7048,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -7088,7 +7070,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -7099,7 +7081,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -7110,7 +7092,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -7121,7 +7103,7 @@
         <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -7132,7 +7114,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -7143,7 +7125,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -7154,7 +7136,7 @@
         <v>59</v>
       </c>
       <c r="C36" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -7165,7 +7147,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -7176,7 +7158,7 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -7187,7 +7169,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -7198,7 +7180,7 @@
         <v>63</v>
       </c>
       <c r="C40" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -7209,7 +7191,7 @@
         <v>64</v>
       </c>
       <c r="C41" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -7220,7 +7202,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -7231,7 +7213,7 @@
         <v>66</v>
       </c>
       <c r="C43" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -7242,7 +7224,7 @@
         <v>67</v>
       </c>
       <c r="C44" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -7253,7 +7235,7 @@
         <v>68</v>
       </c>
       <c r="C45" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -7264,7 +7246,7 @@
         <v>69</v>
       </c>
       <c r="C46" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -7275,7 +7257,7 @@
         <v>70</v>
       </c>
       <c r="C47" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -7286,7 +7268,7 @@
         <v>71</v>
       </c>
       <c r="C48" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -7297,7 +7279,7 @@
         <v>72</v>
       </c>
       <c r="C49" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -7308,7 +7290,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -7319,7 +7301,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -7330,7 +7312,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -7341,7 +7323,7 @@
         <v>76</v>
       </c>
       <c r="C53" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -7352,7 +7334,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -7363,7 +7345,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -7374,7 +7356,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -7385,7 +7367,7 @@
         <v>80</v>
       </c>
       <c r="C57" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -7396,7 +7378,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -7407,7 +7389,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -7429,7 +7411,7 @@
         <v>84</v>
       </c>
       <c r="C61" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -7440,7 +7422,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -7451,7 +7433,7 @@
         <v>86</v>
       </c>
       <c r="C63" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -7462,7 +7444,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -7473,7 +7455,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -7484,7 +7466,7 @@
         <v>89</v>
       </c>
       <c r="C66" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -7495,7 +7477,7 @@
         <v>90</v>
       </c>
       <c r="C67" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -7506,7 +7488,7 @@
         <v>91</v>
       </c>
       <c r="C68" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -7517,7 +7499,7 @@
         <v>92</v>
       </c>
       <c r="C69" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -7528,7 +7510,7 @@
         <v>93</v>
       </c>
       <c r="C70" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -7539,7 +7521,7 @@
         <v>94</v>
       </c>
       <c r="C71" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -7550,7 +7532,7 @@
         <v>95</v>
       </c>
       <c r="C72" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -7561,7 +7543,7 @@
         <v>96</v>
       </c>
       <c r="C73" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -7572,7 +7554,7 @@
         <v>97</v>
       </c>
       <c r="C74" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -7583,7 +7565,7 @@
         <v>98</v>
       </c>
       <c r="C75" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -7594,7 +7576,7 @@
         <v>99</v>
       </c>
       <c r="C76" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -7605,7 +7587,7 @@
         <v>100</v>
       </c>
       <c r="C77" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -7616,7 +7598,7 @@
         <v>101</v>
       </c>
       <c r="C78" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -7627,7 +7609,7 @@
         <v>102</v>
       </c>
       <c r="C79" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -7638,7 +7620,7 @@
         <v>103</v>
       </c>
       <c r="C80" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -7649,7 +7631,7 @@
         <v>104</v>
       </c>
       <c r="C81" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -7660,7 +7642,7 @@
         <v>105</v>
       </c>
       <c r="C82" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -7671,7 +7653,7 @@
         <v>106</v>
       </c>
       <c r="C83" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -7682,7 +7664,7 @@
         <v>107</v>
       </c>
       <c r="C84" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -7693,7 +7675,7 @@
         <v>108</v>
       </c>
       <c r="C85" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -7704,7 +7686,7 @@
         <v>109</v>
       </c>
       <c r="C86" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -7715,7 +7697,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -7726,7 +7708,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -7737,7 +7719,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -7748,7 +7730,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -7759,7 +7741,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -7770,7 +7752,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -7781,7 +7763,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -7792,7 +7774,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -7803,7 +7785,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -7814,7 +7796,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -7825,7 +7807,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -7836,7 +7818,7 @@
         <v>121</v>
       </c>
       <c r="C98" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -7847,7 +7829,7 @@
         <v>122</v>
       </c>
       <c r="C99" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -7858,7 +7840,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -7869,7 +7851,7 @@
         <v>124</v>
       </c>
       <c r="C101" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -7880,7 +7862,7 @@
         <v>125</v>
       </c>
       <c r="C102" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -7891,7 +7873,7 @@
         <v>126</v>
       </c>
       <c r="C103" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -7902,7 +7884,7 @@
         <v>127</v>
       </c>
       <c r="C104" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -7913,7 +7895,7 @@
         <v>128</v>
       </c>
       <c r="C105" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -7924,7 +7906,7 @@
         <v>129</v>
       </c>
       <c r="C106" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -7935,7 +7917,7 @@
         <v>130</v>
       </c>
       <c r="C107" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -7946,7 +7928,7 @@
         <v>131</v>
       </c>
       <c r="C108" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -7957,7 +7939,7 @@
         <v>132</v>
       </c>
       <c r="C109" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -7968,7 +7950,7 @@
         <v>133</v>
       </c>
       <c r="C110" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -7979,7 +7961,7 @@
         <v>134</v>
       </c>
       <c r="C111" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -7990,7 +7972,7 @@
         <v>135</v>
       </c>
       <c r="C112" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -8001,7 +7983,7 @@
         <v>136</v>
       </c>
       <c r="C113" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -8012,7 +7994,7 @@
         <v>137</v>
       </c>
       <c r="C114" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -8023,7 +8005,7 @@
         <v>138</v>
       </c>
       <c r="C115" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -8034,7 +8016,7 @@
         <v>139</v>
       </c>
       <c r="C116" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -8045,7 +8027,7 @@
         <v>140</v>
       </c>
       <c r="C117" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -8056,7 +8038,7 @@
         <v>141</v>
       </c>
       <c r="C118" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -8067,7 +8049,7 @@
         <v>142</v>
       </c>
       <c r="C119" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -8078,7 +8060,7 @@
         <v>143</v>
       </c>
       <c r="C120" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -8089,7 +8071,7 @@
         <v>144</v>
       </c>
       <c r="C121" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -8100,7 +8082,7 @@
         <v>145</v>
       </c>
       <c r="C122" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -8111,7 +8093,7 @@
         <v>146</v>
       </c>
       <c r="C123" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -8122,7 +8104,7 @@
         <v>147</v>
       </c>
       <c r="C124" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -8133,7 +8115,7 @@
         <v>148</v>
       </c>
       <c r="C125" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -8144,7 +8126,7 @@
         <v>149</v>
       </c>
       <c r="C126" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -8155,7 +8137,7 @@
         <v>150</v>
       </c>
       <c r="C127" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -8166,7 +8148,7 @@
         <v>151</v>
       </c>
       <c r="C128" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -8177,7 +8159,7 @@
         <v>152</v>
       </c>
       <c r="C129" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -8188,7 +8170,7 @@
         <v>153</v>
       </c>
       <c r="C130" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -8199,7 +8181,7 @@
         <v>154</v>
       </c>
       <c r="C131" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -8210,7 +8192,7 @@
         <v>155</v>
       </c>
       <c r="C132" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -8221,7 +8203,7 @@
         <v>156</v>
       </c>
       <c r="C133" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -8232,7 +8214,7 @@
         <v>157</v>
       </c>
       <c r="C134" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -8243,7 +8225,7 @@
         <v>158</v>
       </c>
       <c r="C135" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -8254,7 +8236,7 @@
         <v>159</v>
       </c>
       <c r="C136" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -8265,7 +8247,7 @@
         <v>160</v>
       </c>
       <c r="C137" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -8276,7 +8258,7 @@
         <v>161</v>
       </c>
       <c r="C138" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -8287,7 +8269,7 @@
         <v>162</v>
       </c>
       <c r="C139" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -8298,7 +8280,7 @@
         <v>163</v>
       </c>
       <c r="C140" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -8309,7 +8291,7 @@
         <v>164</v>
       </c>
       <c r="C141" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -8320,7 +8302,7 @@
         <v>165</v>
       </c>
       <c r="C142" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -8331,7 +8313,7 @@
         <v>166</v>
       </c>
       <c r="C143" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -8342,7 +8324,7 @@
         <v>167</v>
       </c>
       <c r="C144" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -8353,7 +8335,7 @@
         <v>168</v>
       </c>
       <c r="C145" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -8364,7 +8346,7 @@
         <v>169</v>
       </c>
       <c r="C146" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -8375,7 +8357,7 @@
         <v>170</v>
       </c>
       <c r="C147" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -8386,7 +8368,7 @@
         <v>171</v>
       </c>
       <c r="C148" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -8397,7 +8379,7 @@
         <v>172</v>
       </c>
       <c r="C149" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -8408,7 +8390,7 @@
         <v>173</v>
       </c>
       <c r="C150" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -8419,7 +8401,7 @@
         <v>174</v>
       </c>
       <c r="C151" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -8430,7 +8412,7 @@
         <v>175</v>
       </c>
       <c r="C152" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -8441,7 +8423,7 @@
         <v>176</v>
       </c>
       <c r="C153" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -8452,7 +8434,7 @@
         <v>177</v>
       </c>
       <c r="C154" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -8463,7 +8445,7 @@
         <v>178</v>
       </c>
       <c r="C155" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -8474,7 +8456,7 @@
         <v>179</v>
       </c>
       <c r="C156" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -8485,7 +8467,7 @@
         <v>180</v>
       </c>
       <c r="C157" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -8496,7 +8478,7 @@
         <v>181</v>
       </c>
       <c r="C158" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -8507,7 +8489,7 @@
         <v>182</v>
       </c>
       <c r="C159" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -8518,7 +8500,7 @@
         <v>183</v>
       </c>
       <c r="C160" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -8529,7 +8511,7 @@
         <v>184</v>
       </c>
       <c r="C161" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -8540,7 +8522,7 @@
         <v>185</v>
       </c>
       <c r="C162" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -8551,7 +8533,7 @@
         <v>186</v>
       </c>
       <c r="C163" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -8562,7 +8544,7 @@
         <v>187</v>
       </c>
       <c r="C164" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -8573,7 +8555,7 @@
         <v>188</v>
       </c>
       <c r="C165" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -8584,7 +8566,7 @@
         <v>189</v>
       </c>
       <c r="C166" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -8595,7 +8577,7 @@
         <v>190</v>
       </c>
       <c r="C167" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -8606,7 +8588,7 @@
         <v>191</v>
       </c>
       <c r="C168" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -8617,7 +8599,7 @@
         <v>192</v>
       </c>
       <c r="C169" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -8628,7 +8610,7 @@
         <v>193</v>
       </c>
       <c r="C170" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -8639,7 +8621,7 @@
         <v>194</v>
       </c>
       <c r="C171" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -8650,7 +8632,7 @@
         <v>195</v>
       </c>
       <c r="C172" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -8661,7 +8643,7 @@
         <v>196</v>
       </c>
       <c r="C173" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -8672,7 +8654,7 @@
         <v>197</v>
       </c>
       <c r="C174" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -8683,7 +8665,7 @@
         <v>198</v>
       </c>
       <c r="C175" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -8694,7 +8676,7 @@
         <v>199</v>
       </c>
       <c r="C176" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -8705,7 +8687,7 @@
         <v>200</v>
       </c>
       <c r="C177" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -8716,7 +8698,7 @@
         <v>201</v>
       </c>
       <c r="C178" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -8727,7 +8709,7 @@
         <v>202</v>
       </c>
       <c r="C179" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -8738,7 +8720,7 @@
         <v>203</v>
       </c>
       <c r="C180" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -8749,7 +8731,7 @@
         <v>204</v>
       </c>
       <c r="C181" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -8760,7 +8742,7 @@
         <v>205</v>
       </c>
       <c r="C182" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -8771,7 +8753,7 @@
         <v>206</v>
       </c>
       <c r="C183" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -8782,7 +8764,7 @@
         <v>207</v>
       </c>
       <c r="C184" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -8793,7 +8775,7 @@
         <v>208</v>
       </c>
       <c r="C185" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -8804,7 +8786,7 @@
         <v>209</v>
       </c>
       <c r="C186" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -8815,7 +8797,7 @@
         <v>210</v>
       </c>
       <c r="C187" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -8826,7 +8808,7 @@
         <v>211</v>
       </c>
       <c r="C188" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -8837,7 +8819,7 @@
         <v>212</v>
       </c>
       <c r="C189" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -8848,7 +8830,7 @@
         <v>213</v>
       </c>
       <c r="C190" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -8859,7 +8841,7 @@
         <v>214</v>
       </c>
       <c r="C191" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -8870,7 +8852,7 @@
         <v>215</v>
       </c>
       <c r="C192" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -8881,7 +8863,7 @@
         <v>216</v>
       </c>
       <c r="C193" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -8892,7 +8874,7 @@
         <v>217</v>
       </c>
       <c r="C194" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -8903,7 +8885,7 @@
         <v>218</v>
       </c>
       <c r="C195" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -8914,7 +8896,7 @@
         <v>219</v>
       </c>
       <c r="C196" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -8925,7 +8907,7 @@
         <v>220</v>
       </c>
       <c r="C197" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -8936,7 +8918,7 @@
         <v>221</v>
       </c>
       <c r="C198" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -8947,7 +8929,7 @@
         <v>222</v>
       </c>
       <c r="C199" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -8958,7 +8940,7 @@
         <v>223</v>
       </c>
       <c r="C200" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -8969,7 +8951,7 @@
         <v>224</v>
       </c>
       <c r="C201" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -8980,7 +8962,7 @@
         <v>225</v>
       </c>
       <c r="C202" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -8991,7 +8973,7 @@
         <v>226</v>
       </c>
       <c r="C203" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -9002,7 +8984,7 @@
         <v>227</v>
       </c>
       <c r="C204" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -9013,7 +8995,7 @@
         <v>228</v>
       </c>
       <c r="C205" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -9024,7 +9006,7 @@
         <v>229</v>
       </c>
       <c r="C206" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -9035,7 +9017,7 @@
         <v>230</v>
       </c>
       <c r="C207" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -9046,7 +9028,7 @@
         <v>231</v>
       </c>
       <c r="C208" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -9057,7 +9039,7 @@
         <v>232</v>
       </c>
       <c r="C209" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -9068,7 +9050,7 @@
         <v>233</v>
       </c>
       <c r="C210" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -9079,7 +9061,7 @@
         <v>234</v>
       </c>
       <c r="C211" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -9090,7 +9072,7 @@
         <v>235</v>
       </c>
       <c r="C212" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -9101,7 +9083,7 @@
         <v>236</v>
       </c>
       <c r="C213" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -9112,7 +9094,7 @@
         <v>237</v>
       </c>
       <c r="C214" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -9123,7 +9105,7 @@
         <v>238</v>
       </c>
       <c r="C215" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -9134,7 +9116,7 @@
         <v>239</v>
       </c>
       <c r="C216" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -9145,7 +9127,7 @@
         <v>240</v>
       </c>
       <c r="C217" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -9156,7 +9138,7 @@
         <v>241</v>
       </c>
       <c r="C218" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -9167,7 +9149,7 @@
         <v>242</v>
       </c>
       <c r="C219" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -9178,7 +9160,7 @@
         <v>243</v>
       </c>
       <c r="C220" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -9189,7 +9171,7 @@
         <v>244</v>
       </c>
       <c r="C221" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -9200,7 +9182,7 @@
         <v>245</v>
       </c>
       <c r="C222" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -9211,7 +9193,7 @@
         <v>246</v>
       </c>
       <c r="C223" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -9222,7 +9204,7 @@
         <v>247</v>
       </c>
       <c r="C224" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -9233,7 +9215,7 @@
         <v>248</v>
       </c>
       <c r="C225" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -9244,7 +9226,7 @@
         <v>249</v>
       </c>
       <c r="C226" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -9255,7 +9237,7 @@
         <v>250</v>
       </c>
       <c r="C227" t="s">
-        <v>1305</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -9266,7 +9248,7 @@
         <v>251</v>
       </c>
       <c r="C228" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -9277,7 +9259,7 @@
         <v>252</v>
       </c>
       <c r="C229" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -9288,7 +9270,7 @@
         <v>253</v>
       </c>
       <c r="C230" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -9299,7 +9281,7 @@
         <v>254</v>
       </c>
       <c r="C231" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -9310,7 +9292,7 @@
         <v>255</v>
       </c>
       <c r="C232" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -9321,7 +9303,7 @@
         <v>256</v>
       </c>
       <c r="C233" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -9332,7 +9314,7 @@
         <v>257</v>
       </c>
       <c r="C234" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -9343,7 +9325,7 @@
         <v>258</v>
       </c>
       <c r="C235" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -9354,7 +9336,7 @@
         <v>259</v>
       </c>
       <c r="C236" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -9365,7 +9347,7 @@
         <v>260</v>
       </c>
       <c r="C237" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -9376,7 +9358,7 @@
         <v>261</v>
       </c>
       <c r="C238" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -9387,7 +9369,7 @@
         <v>262</v>
       </c>
       <c r="C239" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -9398,7 +9380,7 @@
         <v>263</v>
       </c>
       <c r="C240" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -9409,7 +9391,7 @@
         <v>264</v>
       </c>
       <c r="C241" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -9420,7 +9402,7 @@
         <v>265</v>
       </c>
       <c r="C242" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -9431,7 +9413,7 @@
         <v>266</v>
       </c>
       <c r="C243" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -9442,7 +9424,7 @@
         <v>267</v>
       </c>
       <c r="C244" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -9453,7 +9435,7 @@
         <v>268</v>
       </c>
       <c r="C245" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -9464,7 +9446,7 @@
         <v>269</v>
       </c>
       <c r="C246" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -9475,7 +9457,7 @@
         <v>270</v>
       </c>
       <c r="C247" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -9486,7 +9468,7 @@
         <v>271</v>
       </c>
       <c r="C248" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -9497,7 +9479,7 @@
         <v>272</v>
       </c>
       <c r="C249" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -9508,7 +9490,7 @@
         <v>273</v>
       </c>
       <c r="C250" t="s">
-        <v>1328</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -9519,7 +9501,7 @@
         <v>274</v>
       </c>
       <c r="C251" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -9530,7 +9512,7 @@
         <v>275</v>
       </c>
       <c r="C252" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -9541,7 +9523,7 @@
         <v>276</v>
       </c>
       <c r="C253" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -9552,7 +9534,7 @@
         <v>277</v>
       </c>
       <c r="C254" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -9563,7 +9545,7 @@
         <v>278</v>
       </c>
       <c r="C255" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -9574,7 +9556,7 @@
         <v>279</v>
       </c>
       <c r="C256" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -9585,7 +9567,7 @@
         <v>280</v>
       </c>
       <c r="C257" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -9596,7 +9578,7 @@
         <v>281</v>
       </c>
       <c r="C258" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="259" spans="1:3">
@@ -9607,7 +9589,7 @@
         <v>282</v>
       </c>
       <c r="C259" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -9618,7 +9600,7 @@
         <v>283</v>
       </c>
       <c r="C260" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="261" spans="1:3">
@@ -9629,7 +9611,7 @@
         <v>284</v>
       </c>
       <c r="C261" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="262" spans="1:3">
@@ -9640,7 +9622,7 @@
         <v>285</v>
       </c>
       <c r="C262" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -9651,7 +9633,7 @@
         <v>286</v>
       </c>
       <c r="C263" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="264" spans="1:3">
@@ -9662,7 +9644,7 @@
         <v>287</v>
       </c>
       <c r="C264" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -9673,7 +9655,7 @@
         <v>288</v>
       </c>
       <c r="C265" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="266" spans="1:3">
@@ -9684,7 +9666,7 @@
         <v>289</v>
       </c>
       <c r="C266" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="267" spans="1:3">
@@ -9695,7 +9677,7 @@
         <v>290</v>
       </c>
       <c r="C267" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="268" spans="1:3">
@@ -9706,7 +9688,7 @@
         <v>291</v>
       </c>
       <c r="C268" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="269" spans="1:3">
@@ -9717,7 +9699,7 @@
         <v>292</v>
       </c>
       <c r="C269" t="s">
-        <v>1347</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="270" spans="1:3">
@@ -9728,7 +9710,7 @@
         <v>293</v>
       </c>
       <c r="C270" t="s">
-        <v>1348</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="271" spans="1:3">
@@ -9739,7 +9721,7 @@
         <v>294</v>
       </c>
       <c r="C271" t="s">
-        <v>1349</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="272" spans="1:3">
@@ -9750,7 +9732,7 @@
         <v>295</v>
       </c>
       <c r="C272" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="273" spans="1:3">
@@ -9761,7 +9743,7 @@
         <v>296</v>
       </c>
       <c r="C273" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="274" spans="1:3">
@@ -9772,7 +9754,7 @@
         <v>297</v>
       </c>
       <c r="C274" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="275" spans="1:3">
@@ -9783,7 +9765,7 @@
         <v>298</v>
       </c>
       <c r="C275" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="276" spans="1:3">
@@ -9794,7 +9776,7 @@
         <v>299</v>
       </c>
       <c r="C276" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="277" spans="1:3">
@@ -9805,7 +9787,7 @@
         <v>300</v>
       </c>
       <c r="C277" t="s">
-        <v>1355</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="278" spans="1:3">
@@ -9816,7 +9798,7 @@
         <v>301</v>
       </c>
       <c r="C278" t="s">
-        <v>1356</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="279" spans="1:3">
@@ -9827,7 +9809,7 @@
         <v>302</v>
       </c>
       <c r="C279" t="s">
-        <v>1357</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="280" spans="1:3">
@@ -9838,7 +9820,7 @@
         <v>303</v>
       </c>
       <c r="C280" t="s">
-        <v>1358</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -9849,7 +9831,7 @@
         <v>304</v>
       </c>
       <c r="C281" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="282" spans="1:3">
@@ -9860,7 +9842,7 @@
         <v>305</v>
       </c>
       <c r="C282" t="s">
-        <v>1360</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="283" spans="1:3">
@@ -9871,7 +9853,7 @@
         <v>306</v>
       </c>
       <c r="C283" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="284" spans="1:3">
@@ -9882,7 +9864,7 @@
         <v>307</v>
       </c>
       <c r="C284" t="s">
-        <v>1361</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="285" spans="1:3">
@@ -9893,7 +9875,7 @@
         <v>308</v>
       </c>
       <c r="C285" t="s">
-        <v>1362</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="286" spans="1:3">
@@ -9904,7 +9886,7 @@
         <v>309</v>
       </c>
       <c r="C286" t="s">
-        <v>1363</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="287" spans="1:3">
@@ -9915,7 +9897,7 @@
         <v>310</v>
       </c>
       <c r="C287" t="s">
-        <v>1364</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="288" spans="1:3">
@@ -9926,7 +9908,7 @@
         <v>311</v>
       </c>
       <c r="C288" t="s">
-        <v>1365</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="289" spans="1:3">
@@ -9937,7 +9919,7 @@
         <v>312</v>
       </c>
       <c r="C289" t="s">
-        <v>1366</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="290" spans="1:3">
@@ -9948,7 +9930,7 @@
         <v>313</v>
       </c>
       <c r="C290" t="s">
-        <v>1367</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="291" spans="1:3">
@@ -9959,7 +9941,7 @@
         <v>314</v>
       </c>
       <c r="C291" t="s">
-        <v>1368</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="292" spans="1:3">
@@ -9970,7 +9952,7 @@
         <v>315</v>
       </c>
       <c r="C292" t="s">
-        <v>1369</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="293" spans="1:3">
@@ -9981,7 +9963,7 @@
         <v>316</v>
       </c>
       <c r="C293" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="294" spans="1:3">
@@ -9992,7 +9974,7 @@
         <v>317</v>
       </c>
       <c r="C294" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="295" spans="1:3">
@@ -10003,7 +9985,7 @@
         <v>318</v>
       </c>
       <c r="C295" t="s">
-        <v>1372</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="296" spans="1:3">
@@ -10014,7 +9996,7 @@
         <v>319</v>
       </c>
       <c r="C296" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="297" spans="1:3">
@@ -10025,7 +10007,7 @@
         <v>320</v>
       </c>
       <c r="C297" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="298" spans="1:3">
@@ -10036,7 +10018,7 @@
         <v>321</v>
       </c>
       <c r="C298" t="s">
-        <v>1375</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="299" spans="1:3">
@@ -10047,7 +10029,7 @@
         <v>322</v>
       </c>
       <c r="C299" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="300" spans="1:3">
@@ -10058,7 +10040,7 @@
         <v>323</v>
       </c>
       <c r="C300" t="s">
-        <v>1377</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="301" spans="1:3">
@@ -10069,7 +10051,7 @@
         <v>324</v>
       </c>
       <c r="C301" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -10080,7 +10062,7 @@
         <v>325</v>
       </c>
       <c r="C302" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="303" spans="1:3">
@@ -10091,7 +10073,7 @@
         <v>326</v>
       </c>
       <c r="C303" t="s">
-        <v>1380</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="304" spans="1:3">
@@ -10102,7 +10084,7 @@
         <v>327</v>
       </c>
       <c r="C304" t="s">
-        <v>1381</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -10113,7 +10095,7 @@
         <v>328</v>
       </c>
       <c r="C305" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="306" spans="1:3">
@@ -10124,7 +10106,7 @@
         <v>329</v>
       </c>
       <c r="C306" t="s">
-        <v>1383</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="307" spans="1:3">
@@ -10135,7 +10117,7 @@
         <v>330</v>
       </c>
       <c r="C307" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="308" spans="1:3">
@@ -10146,7 +10128,7 @@
         <v>331</v>
       </c>
       <c r="C308" t="s">
-        <v>1385</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="309" spans="1:3">
@@ -10157,7 +10139,7 @@
         <v>332</v>
       </c>
       <c r="C309" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="310" spans="1:3">
@@ -10168,7 +10150,7 @@
         <v>333</v>
       </c>
       <c r="C310" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="311" spans="1:3">
@@ -10179,7 +10161,7 @@
         <v>334</v>
       </c>
       <c r="C311" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="312" spans="1:3">
@@ -10190,7 +10172,7 @@
         <v>335</v>
       </c>
       <c r="C312" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="313" spans="1:3">
@@ -10201,7 +10183,7 @@
         <v>336</v>
       </c>
       <c r="C313" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="314" spans="1:3">
@@ -10212,7 +10194,7 @@
         <v>337</v>
       </c>
       <c r="C314" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="315" spans="1:3">
@@ -10223,7 +10205,7 @@
         <v>338</v>
       </c>
       <c r="C315" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="316" spans="1:3">
@@ -10234,7 +10216,7 @@
         <v>339</v>
       </c>
       <c r="C316" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="317" spans="1:3">
@@ -10245,7 +10227,7 @@
         <v>340</v>
       </c>
       <c r="C317" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="318" spans="1:3">
@@ -10256,7 +10238,7 @@
         <v>341</v>
       </c>
       <c r="C318" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="319" spans="1:3">
@@ -10267,7 +10249,7 @@
         <v>342</v>
       </c>
       <c r="C319" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="320" spans="1:3">
@@ -10278,7 +10260,7 @@
         <v>343</v>
       </c>
       <c r="C320" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="321" spans="1:3">
@@ -10289,7 +10271,7 @@
         <v>344</v>
       </c>
       <c r="C321" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -10300,7 +10282,7 @@
         <v>345</v>
       </c>
       <c r="C322" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="323" spans="1:3">
@@ -10311,7 +10293,7 @@
         <v>346</v>
       </c>
       <c r="C323" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="324" spans="1:3">
@@ -10322,7 +10304,7 @@
         <v>347</v>
       </c>
       <c r="C324" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -10333,7 +10315,7 @@
         <v>348</v>
       </c>
       <c r="C325" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="326" spans="1:3">
@@ -10344,7 +10326,7 @@
         <v>349</v>
       </c>
       <c r="C326" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="327" spans="1:3">
@@ -10355,7 +10337,7 @@
         <v>350</v>
       </c>
       <c r="C327" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="328" spans="1:3">
@@ -10366,7 +10348,7 @@
         <v>351</v>
       </c>
       <c r="C328" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="329" spans="1:3">
@@ -10377,7 +10359,7 @@
         <v>352</v>
       </c>
       <c r="C329" t="s">
-        <v>1405</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="330" spans="1:3">
@@ -10388,7 +10370,7 @@
         <v>353</v>
       </c>
       <c r="C330" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -10399,7 +10381,7 @@
         <v>354</v>
       </c>
       <c r="C331" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="332" spans="1:3">
@@ -10410,7 +10392,7 @@
         <v>355</v>
       </c>
       <c r="C332" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="333" spans="1:3">
@@ -10421,7 +10403,7 @@
         <v>356</v>
       </c>
       <c r="C333" t="s">
-        <v>1409</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="334" spans="1:3">
@@ -10432,7 +10414,7 @@
         <v>357</v>
       </c>
       <c r="C334" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="335" spans="1:3">
@@ -10443,7 +10425,7 @@
         <v>358</v>
       </c>
       <c r="C335" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="336" spans="1:3">
@@ -10454,7 +10436,7 @@
         <v>359</v>
       </c>
       <c r="C336" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="337" spans="1:3">
@@ -10465,7 +10447,7 @@
         <v>360</v>
       </c>
       <c r="C337" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="338" spans="1:3">
@@ -10476,7 +10458,7 @@
         <v>361</v>
       </c>
       <c r="C338" t="s">
-        <v>1414</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="339" spans="1:3">
@@ -10487,7 +10469,7 @@
         <v>362</v>
       </c>
       <c r="C339" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="340" spans="1:3">
@@ -10498,7 +10480,7 @@
         <v>363</v>
       </c>
       <c r="C340" t="s">
-        <v>1416</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="341" spans="1:3">
@@ -10509,7 +10491,7 @@
         <v>364</v>
       </c>
       <c r="C341" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -10520,7 +10502,7 @@
         <v>365</v>
       </c>
       <c r="C342" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="343" spans="1:3">
@@ -10531,7 +10513,7 @@
         <v>366</v>
       </c>
       <c r="C343" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="344" spans="1:3">
@@ -10542,7 +10524,7 @@
         <v>367</v>
       </c>
       <c r="C344" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="345" spans="1:3">
@@ -10553,7 +10535,7 @@
         <v>368</v>
       </c>
       <c r="C345" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="346" spans="1:3">
@@ -10564,7 +10546,7 @@
         <v>369</v>
       </c>
       <c r="C346" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="347" spans="1:3">
@@ -10575,7 +10557,7 @@
         <v>370</v>
       </c>
       <c r="C347" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="348" spans="1:3">
@@ -10586,7 +10568,7 @@
         <v>371</v>
       </c>
       <c r="C348" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="349" spans="1:3">
@@ -10597,7 +10579,7 @@
         <v>372</v>
       </c>
       <c r="C349" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -10608,7 +10590,7 @@
         <v>373</v>
       </c>
       <c r="C350" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="351" spans="1:3">
@@ -10619,7 +10601,7 @@
         <v>374</v>
       </c>
       <c r="C351" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -10630,7 +10612,7 @@
         <v>375</v>
       </c>
       <c r="C352" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="353" spans="1:3">
@@ -10641,7 +10623,7 @@
         <v>376</v>
       </c>
       <c r="C353" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="354" spans="1:3">
@@ -10652,7 +10634,7 @@
         <v>377</v>
       </c>
       <c r="C354" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -10663,7 +10645,7 @@
         <v>378</v>
       </c>
       <c r="C355" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="356" spans="1:3">
@@ -10674,7 +10656,7 @@
         <v>379</v>
       </c>
       <c r="C356" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="357" spans="1:3">
@@ -10685,7 +10667,7 @@
         <v>380</v>
       </c>
       <c r="C357" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="358" spans="1:3">
@@ -10696,7 +10678,7 @@
         <v>381</v>
       </c>
       <c r="C358" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="359" spans="1:3">
@@ -10707,7 +10689,7 @@
         <v>382</v>
       </c>
       <c r="C359" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -10718,7 +10700,7 @@
         <v>383</v>
       </c>
       <c r="C360" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="361" spans="1:3">
@@ -10729,7 +10711,7 @@
         <v>384</v>
       </c>
       <c r="C361" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="362" spans="1:3">
@@ -10740,7 +10722,7 @@
         <v>385</v>
       </c>
       <c r="C362" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="363" spans="1:3">
@@ -10751,7 +10733,7 @@
         <v>386</v>
       </c>
       <c r="C363" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="364" spans="1:3">
@@ -10762,7 +10744,7 @@
         <v>387</v>
       </c>
       <c r="C364" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="365" spans="1:3">
@@ -10773,7 +10755,7 @@
         <v>388</v>
       </c>
       <c r="C365" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="366" spans="1:3">
@@ -10784,7 +10766,7 @@
         <v>389</v>
       </c>
       <c r="C366" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="367" spans="1:3">
@@ -10795,7 +10777,7 @@
         <v>390</v>
       </c>
       <c r="C367" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="368" spans="1:3">
@@ -10806,7 +10788,7 @@
         <v>391</v>
       </c>
       <c r="C368" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="369" spans="1:3">
@@ -10817,7 +10799,7 @@
         <v>392</v>
       </c>
       <c r="C369" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="370" spans="1:3">
@@ -10828,7 +10810,7 @@
         <v>393</v>
       </c>
       <c r="C370" t="s">
-        <v>1445</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="371" spans="1:3">
@@ -10839,7 +10821,7 @@
         <v>394</v>
       </c>
       <c r="C371" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -10850,7 +10832,7 @@
         <v>395</v>
       </c>
       <c r="C372" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="373" spans="1:3">
@@ -10861,7 +10843,7 @@
         <v>396</v>
       </c>
       <c r="C373" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="374" spans="1:3">
@@ -10872,7 +10854,7 @@
         <v>397</v>
       </c>
       <c r="C374" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="375" spans="1:3">
@@ -10883,7 +10865,7 @@
         <v>398</v>
       </c>
       <c r="C375" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="376" spans="1:3">
@@ -10894,7 +10876,7 @@
         <v>399</v>
       </c>
       <c r="C376" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="377" spans="1:3">
@@ -10905,7 +10887,7 @@
         <v>400</v>
       </c>
       <c r="C377" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="378" spans="1:3">
@@ -10916,7 +10898,7 @@
         <v>401</v>
       </c>
       <c r="C378" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="379" spans="1:3">
@@ -10927,7 +10909,7 @@
         <v>402</v>
       </c>
       <c r="C379" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="380" spans="1:3">
@@ -10938,7 +10920,7 @@
         <v>403</v>
       </c>
       <c r="C380" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="381" spans="1:3">
@@ -10949,7 +10931,7 @@
         <v>404</v>
       </c>
       <c r="C381" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="382" spans="1:3">
@@ -10960,7 +10942,7 @@
         <v>405</v>
       </c>
       <c r="C382" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="383" spans="1:3">
@@ -10971,7 +10953,7 @@
         <v>406</v>
       </c>
       <c r="C383" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="384" spans="1:3">
@@ -10982,7 +10964,7 @@
         <v>407</v>
       </c>
       <c r="C384" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="385" spans="1:3">
@@ -10993,7 +10975,7 @@
         <v>408</v>
       </c>
       <c r="C385" t="s">
-        <v>1460</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="386" spans="1:3">
@@ -11004,7 +10986,7 @@
         <v>409</v>
       </c>
       <c r="C386" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="387" spans="1:3">
@@ -11015,7 +10997,7 @@
         <v>410</v>
       </c>
       <c r="C387" t="s">
-        <v>1462</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="388" spans="1:3">
@@ -11026,7 +11008,7 @@
         <v>411</v>
       </c>
       <c r="C388" t="s">
-        <v>1463</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="389" spans="1:3">
@@ -11037,7 +11019,7 @@
         <v>412</v>
       </c>
       <c r="C389" t="s">
-        <v>1464</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="390" spans="1:3">
@@ -11048,7 +11030,7 @@
         <v>413</v>
       </c>
       <c r="C390" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="391" spans="1:3">
@@ -11059,7 +11041,7 @@
         <v>414</v>
       </c>
       <c r="C391" t="s">
-        <v>1466</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="392" spans="1:3">
@@ -11070,7 +11052,7 @@
         <v>415</v>
       </c>
       <c r="C392" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="393" spans="1:3">
@@ -11081,7 +11063,7 @@
         <v>416</v>
       </c>
       <c r="C393" t="s">
-        <v>1468</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="394" spans="1:3">
@@ -11092,7 +11074,7 @@
         <v>417</v>
       </c>
       <c r="C394" t="s">
-        <v>1469</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="395" spans="1:3">
@@ -11103,7 +11085,7 @@
         <v>418</v>
       </c>
       <c r="C395" t="s">
-        <v>1470</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="396" spans="1:3">
@@ -11114,7 +11096,7 @@
         <v>419</v>
       </c>
       <c r="C396" t="s">
-        <v>1471</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="397" spans="1:3">
@@ -11125,7 +11107,7 @@
         <v>420</v>
       </c>
       <c r="C397" t="s">
-        <v>1472</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="398" spans="1:3">
@@ -11136,7 +11118,7 @@
         <v>421</v>
       </c>
       <c r="C398" t="s">
-        <v>1473</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="399" spans="1:3">
@@ -11147,7 +11129,7 @@
         <v>422</v>
       </c>
       <c r="C399" t="s">
-        <v>1474</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="400" spans="1:3">
@@ -11158,7 +11140,7 @@
         <v>423</v>
       </c>
       <c r="C400" t="s">
-        <v>1475</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="401" spans="1:3">
@@ -11169,7 +11151,7 @@
         <v>424</v>
       </c>
       <c r="C401" t="s">
-        <v>1476</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="402" spans="1:3">
@@ -11180,7 +11162,7 @@
         <v>425</v>
       </c>
       <c r="C402" t="s">
-        <v>1477</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="403" spans="1:3">
@@ -11191,7 +11173,7 @@
         <v>426</v>
       </c>
       <c r="C403" t="s">
-        <v>1478</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="404" spans="1:3">
@@ -11202,7 +11184,7 @@
         <v>427</v>
       </c>
       <c r="C404" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="405" spans="1:3">
@@ -11213,7 +11195,7 @@
         <v>428</v>
       </c>
       <c r="C405" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="406" spans="1:3">
@@ -11224,7 +11206,7 @@
         <v>429</v>
       </c>
       <c r="C406" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="407" spans="1:3">
@@ -11235,7 +11217,7 @@
         <v>430</v>
       </c>
       <c r="C407" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="408" spans="1:3">
@@ -11246,7 +11228,7 @@
         <v>431</v>
       </c>
       <c r="C408" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="409" spans="1:3">
@@ -11257,7 +11239,7 @@
         <v>432</v>
       </c>
       <c r="C409" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="410" spans="1:3">
@@ -11268,7 +11250,7 @@
         <v>433</v>
       </c>
       <c r="C410" t="s">
-        <v>1485</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="411" spans="1:3">
@@ -11279,7 +11261,7 @@
         <v>434</v>
       </c>
       <c r="C411" t="s">
-        <v>1486</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="412" spans="1:3">
@@ -11290,7 +11272,7 @@
         <v>435</v>
       </c>
       <c r="C412" t="s">
-        <v>1487</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="413" spans="1:3">
@@ -11301,7 +11283,7 @@
         <v>436</v>
       </c>
       <c r="C413" t="s">
-        <v>1488</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="414" spans="1:3">
@@ -11312,7 +11294,7 @@
         <v>437</v>
       </c>
       <c r="C414" t="s">
-        <v>1489</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="415" spans="1:3">
@@ -11323,7 +11305,7 @@
         <v>438</v>
       </c>
       <c r="C415" t="s">
-        <v>1490</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="416" spans="1:3">
@@ -11334,7 +11316,7 @@
         <v>439</v>
       </c>
       <c r="C416" t="s">
-        <v>1491</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="417" spans="1:3">
@@ -11345,7 +11327,7 @@
         <v>440</v>
       </c>
       <c r="C417" t="s">
-        <v>1492</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="418" spans="1:3">
@@ -11356,7 +11338,7 @@
         <v>441</v>
       </c>
       <c r="C418" t="s">
-        <v>1493</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="419" spans="1:3">
@@ -11367,7 +11349,7 @@
         <v>442</v>
       </c>
       <c r="C419" t="s">
-        <v>1494</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="420" spans="1:3">
@@ -11378,7 +11360,7 @@
         <v>443</v>
       </c>
       <c r="C420" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="421" spans="1:3">
@@ -11389,7 +11371,7 @@
         <v>444</v>
       </c>
       <c r="C421" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="422" spans="1:3">
@@ -11400,7 +11382,7 @@
         <v>445</v>
       </c>
       <c r="C422" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="423" spans="1:3">
@@ -11411,7 +11393,7 @@
         <v>446</v>
       </c>
       <c r="C423" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="424" spans="1:3">
@@ -11422,7 +11404,7 @@
         <v>447</v>
       </c>
       <c r="C424" t="s">
-        <v>1499</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="425" spans="1:3">
@@ -11433,7 +11415,7 @@
         <v>448</v>
       </c>
       <c r="C425" t="s">
-        <v>1500</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="426" spans="1:3">
@@ -11444,7 +11426,7 @@
         <v>449</v>
       </c>
       <c r="C426" t="s">
-        <v>1501</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="427" spans="1:3">
@@ -11455,7 +11437,7 @@
         <v>450</v>
       </c>
       <c r="C427" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="428" spans="1:3">
@@ -11466,7 +11448,7 @@
         <v>451</v>
       </c>
       <c r="C428" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="429" spans="1:3">
@@ -11477,7 +11459,7 @@
         <v>452</v>
       </c>
       <c r="C429" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="430" spans="1:3">
@@ -11488,7 +11470,7 @@
         <v>453</v>
       </c>
       <c r="C430" t="s">
-        <v>1505</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="431" spans="1:3">
@@ -11499,7 +11481,7 @@
         <v>454</v>
       </c>
       <c r="C431" t="s">
-        <v>1506</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="432" spans="1:3">
@@ -11510,7 +11492,7 @@
         <v>455</v>
       </c>
       <c r="C432" t="s">
-        <v>1507</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="433" spans="1:3">
@@ -11521,7 +11503,7 @@
         <v>456</v>
       </c>
       <c r="C433" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="434" spans="1:3">
@@ -11532,7 +11514,7 @@
         <v>457</v>
       </c>
       <c r="C434" t="s">
-        <v>1509</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="435" spans="1:3">
@@ -11543,7 +11525,7 @@
         <v>458</v>
       </c>
       <c r="C435" t="s">
-        <v>1510</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="436" spans="1:3">
@@ -11554,7 +11536,7 @@
         <v>459</v>
       </c>
       <c r="C436" t="s">
-        <v>1511</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="437" spans="1:3">
@@ -11565,7 +11547,7 @@
         <v>460</v>
       </c>
       <c r="C437" t="s">
-        <v>1512</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="438" spans="1:3">
@@ -11576,7 +11558,7 @@
         <v>461</v>
       </c>
       <c r="C438" t="s">
-        <v>1513</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="439" spans="1:3">
@@ -11587,7 +11569,7 @@
         <v>462</v>
       </c>
       <c r="C439" t="s">
-        <v>1514</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="440" spans="1:3">
@@ -11598,7 +11580,7 @@
         <v>463</v>
       </c>
       <c r="C440" t="s">
-        <v>1515</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="441" spans="1:3">
@@ -11609,7 +11591,7 @@
         <v>464</v>
       </c>
       <c r="C441" t="s">
-        <v>1516</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="442" spans="1:3">
@@ -11620,7 +11602,7 @@
         <v>465</v>
       </c>
       <c r="C442" t="s">
-        <v>1517</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="443" spans="1:3">
@@ -11631,7 +11613,7 @@
         <v>466</v>
       </c>
       <c r="C443" t="s">
-        <v>1518</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="444" spans="1:3">
@@ -11642,7 +11624,7 @@
         <v>467</v>
       </c>
       <c r="C444" t="s">
-        <v>1519</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="445" spans="1:3">
@@ -11653,7 +11635,7 @@
         <v>468</v>
       </c>
       <c r="C445" t="s">
-        <v>1520</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="446" spans="1:3">
@@ -11664,7 +11646,7 @@
         <v>469</v>
       </c>
       <c r="C446" t="s">
-        <v>1521</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="447" spans="1:3">
@@ -11675,7 +11657,7 @@
         <v>470</v>
       </c>
       <c r="C447" t="s">
-        <v>1522</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="448" spans="1:3">
@@ -11686,7 +11668,7 @@
         <v>471</v>
       </c>
       <c r="C448" t="s">
-        <v>1523</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="449" spans="1:3">
@@ -11697,7 +11679,7 @@
         <v>472</v>
       </c>
       <c r="C449" t="s">
-        <v>1524</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="450" spans="1:3">
@@ -11708,7 +11690,7 @@
         <v>473</v>
       </c>
       <c r="C450" t="s">
-        <v>1525</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="451" spans="1:3">
@@ -11719,7 +11701,7 @@
         <v>474</v>
       </c>
       <c r="C451" t="s">
-        <v>1526</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="452" spans="1:3">
@@ -11730,7 +11712,7 @@
         <v>475</v>
       </c>
       <c r="C452" t="s">
-        <v>1527</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="453" spans="1:3">
@@ -11741,7 +11723,7 @@
         <v>476</v>
       </c>
       <c r="C453" t="s">
-        <v>1528</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="454" spans="1:3">
@@ -11752,7 +11734,7 @@
         <v>477</v>
       </c>
       <c r="C454" t="s">
-        <v>1529</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="455" spans="1:3">
@@ -11763,7 +11745,7 @@
         <v>478</v>
       </c>
       <c r="C455" t="s">
-        <v>1530</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="456" spans="1:3">
@@ -11774,7 +11756,7 @@
         <v>479</v>
       </c>
       <c r="C456" t="s">
-        <v>1531</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="457" spans="1:3">
@@ -11785,7 +11767,7 @@
         <v>480</v>
       </c>
       <c r="C457" t="s">
-        <v>1532</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="458" spans="1:3">
@@ -11796,7 +11778,7 @@
         <v>481</v>
       </c>
       <c r="C458" t="s">
-        <v>1533</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="459" spans="1:3">
@@ -11807,7 +11789,7 @@
         <v>482</v>
       </c>
       <c r="C459" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="460" spans="1:3">
@@ -11818,7 +11800,7 @@
         <v>483</v>
       </c>
       <c r="C460" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="461" spans="1:3">
@@ -11829,7 +11811,7 @@
         <v>484</v>
       </c>
       <c r="C461" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="462" spans="1:3">
@@ -11840,7 +11822,7 @@
         <v>485</v>
       </c>
       <c r="C462" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="463" spans="1:3">
@@ -11851,7 +11833,7 @@
         <v>486</v>
       </c>
       <c r="C463" t="s">
-        <v>1536</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="464" spans="1:3">
@@ -11862,7 +11844,7 @@
         <v>487</v>
       </c>
       <c r="C464" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="465" spans="1:3">
@@ -11873,7 +11855,7 @@
         <v>488</v>
       </c>
       <c r="C465" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="466" spans="1:3">
@@ -11884,7 +11866,7 @@
         <v>489</v>
       </c>
       <c r="C466" t="s">
-        <v>1539</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="467" spans="1:3">
@@ -11895,7 +11877,7 @@
         <v>490</v>
       </c>
       <c r="C467" t="s">
-        <v>1540</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="468" spans="1:3">
@@ -11906,7 +11888,7 @@
         <v>491</v>
       </c>
       <c r="C468" t="s">
-        <v>1541</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="469" spans="1:3">
@@ -11917,7 +11899,7 @@
         <v>492</v>
       </c>
       <c r="C469" t="s">
-        <v>1542</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="470" spans="1:3">
@@ -11928,7 +11910,7 @@
         <v>493</v>
       </c>
       <c r="C470" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="471" spans="1:3">
@@ -11939,7 +11921,7 @@
         <v>494</v>
       </c>
       <c r="C471" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="472" spans="1:3">
@@ -11950,7 +11932,7 @@
         <v>495</v>
       </c>
       <c r="C472" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="473" spans="1:3">
@@ -11961,7 +11943,7 @@
         <v>496</v>
       </c>
       <c r="C473" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="474" spans="1:3">
@@ -11972,7 +11954,7 @@
         <v>497</v>
       </c>
       <c r="C474" t="s">
-        <v>1547</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="475" spans="1:3">
@@ -11983,7 +11965,7 @@
         <v>498</v>
       </c>
       <c r="C475" t="s">
-        <v>1548</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="476" spans="1:3">
@@ -11994,7 +11976,7 @@
         <v>499</v>
       </c>
       <c r="C476" t="s">
-        <v>1549</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="477" spans="1:3">
@@ -12005,7 +11987,7 @@
         <v>500</v>
       </c>
       <c r="C477" t="s">
-        <v>1550</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="478" spans="1:3">
@@ -12016,7 +11998,7 @@
         <v>501</v>
       </c>
       <c r="C478" t="s">
-        <v>1551</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="479" spans="1:3">
@@ -12027,7 +12009,7 @@
         <v>502</v>
       </c>
       <c r="C479" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="480" spans="1:3">
@@ -12038,7 +12020,7 @@
         <v>503</v>
       </c>
       <c r="C480" t="s">
-        <v>1553</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="481" spans="1:3">
@@ -12049,7 +12031,7 @@
         <v>504</v>
       </c>
       <c r="C481" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="482" spans="1:3">
@@ -12060,7 +12042,7 @@
         <v>505</v>
       </c>
       <c r="C482" t="s">
-        <v>1555</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="483" spans="1:3">
@@ -12071,7 +12053,7 @@
         <v>506</v>
       </c>
       <c r="C483" t="s">
-        <v>1556</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="484" spans="1:3">
@@ -12082,7 +12064,7 @@
         <v>507</v>
       </c>
       <c r="C484" t="s">
-        <v>1557</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="485" spans="1:3">
@@ -12093,7 +12075,7 @@
         <v>508</v>
       </c>
       <c r="C485" t="s">
-        <v>1558</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="486" spans="1:3">
@@ -12104,7 +12086,7 @@
         <v>509</v>
       </c>
       <c r="C486" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="487" spans="1:3">
@@ -12115,7 +12097,7 @@
         <v>510</v>
       </c>
       <c r="C487" t="s">
-        <v>1560</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="488" spans="1:3">
@@ -12126,7 +12108,7 @@
         <v>511</v>
       </c>
       <c r="C488" t="s">
-        <v>1561</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="489" spans="1:3">
@@ -12137,7 +12119,7 @@
         <v>512</v>
       </c>
       <c r="C489" t="s">
-        <v>1562</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="490" spans="1:3">
@@ -12148,7 +12130,7 @@
         <v>513</v>
       </c>
       <c r="C490" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="491" spans="1:3">
@@ -12159,7 +12141,7 @@
         <v>514</v>
       </c>
       <c r="C491" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="492" spans="1:3">
@@ -12170,7 +12152,7 @@
         <v>515</v>
       </c>
       <c r="C492" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="493" spans="1:3">
@@ -12181,7 +12163,7 @@
         <v>516</v>
       </c>
       <c r="C493" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="494" spans="1:3">
@@ -12192,7 +12174,7 @@
         <v>517</v>
       </c>
       <c r="C494" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="495" spans="1:3">
@@ -12203,7 +12185,7 @@
         <v>518</v>
       </c>
       <c r="C495" t="s">
-        <v>1568</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="496" spans="1:3">
@@ -12214,7 +12196,7 @@
         <v>519</v>
       </c>
       <c r="C496" t="s">
-        <v>1569</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="497" spans="1:3">
@@ -12225,7 +12207,7 @@
         <v>520</v>
       </c>
       <c r="C497" t="s">
-        <v>1570</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="498" spans="1:3">
@@ -12236,7 +12218,7 @@
         <v>521</v>
       </c>
       <c r="C498" t="s">
-        <v>1571</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="499" spans="1:3">
@@ -12247,7 +12229,7 @@
         <v>522</v>
       </c>
       <c r="C499" t="s">
-        <v>1572</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="500" spans="1:3">
@@ -12258,7 +12240,7 @@
         <v>523</v>
       </c>
       <c r="C500" t="s">
-        <v>1573</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="501" spans="1:3">
@@ -12269,7 +12251,7 @@
         <v>524</v>
       </c>
       <c r="C501" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="502" spans="1:3">
@@ -12280,7 +12262,7 @@
         <v>525</v>
       </c>
       <c r="C502" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="503" spans="1:3">
@@ -12291,7 +12273,7 @@
         <v>526</v>
       </c>
       <c r="C503" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="504" spans="1:3">
@@ -12302,7 +12284,7 @@
         <v>527</v>
       </c>
       <c r="C504" t="s">
-        <v>1577</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="505" spans="1:3">
@@ -12313,7 +12295,7 @@
         <v>528</v>
       </c>
       <c r="C505" t="s">
-        <v>1578</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="506" spans="1:3">
@@ -12324,7 +12306,7 @@
         <v>529</v>
       </c>
       <c r="C506" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="507" spans="1:3">
@@ -12335,7 +12317,7 @@
         <v>530</v>
       </c>
       <c r="C507" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="508" spans="1:3">
@@ -12346,7 +12328,7 @@
         <v>531</v>
       </c>
       <c r="C508" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="509" spans="1:3">
@@ -12357,7 +12339,7 @@
         <v>532</v>
       </c>
       <c r="C509" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="510" spans="1:3">
@@ -12368,7 +12350,7 @@
         <v>533</v>
       </c>
       <c r="C510" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="511" spans="1:3">
@@ -12379,7 +12361,7 @@
         <v>534</v>
       </c>
       <c r="C511" t="s">
-        <v>1584</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="512" spans="1:3">
@@ -12390,7 +12372,7 @@
         <v>535</v>
       </c>
       <c r="C512" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="513" spans="1:3">
@@ -12401,7 +12383,7 @@
         <v>536</v>
       </c>
       <c r="C513" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="514" spans="1:3">
@@ -12412,7 +12394,7 @@
         <v>537</v>
       </c>
       <c r="C514" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="515" spans="1:3">
@@ -12423,7 +12405,7 @@
         <v>538</v>
       </c>
       <c r="C515" t="s">
-        <v>1588</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="516" spans="1:3">
@@ -12434,7 +12416,7 @@
         <v>539</v>
       </c>
       <c r="C516" t="s">
-        <v>1589</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="517" spans="1:3">
@@ -12445,7 +12427,7 @@
         <v>540</v>
       </c>
       <c r="C517" t="s">
-        <v>1590</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="518" spans="1:3">
@@ -12456,7 +12438,7 @@
         <v>541</v>
       </c>
       <c r="C518" t="s">
-        <v>1591</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="519" spans="1:3">
@@ -12467,7 +12449,7 @@
         <v>542</v>
       </c>
       <c r="C519" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="520" spans="1:3">
@@ -12478,7 +12460,7 @@
         <v>543</v>
       </c>
       <c r="C520" t="s">
-        <v>1593</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="521" spans="1:3">
@@ -12489,7 +12471,7 @@
         <v>544</v>
       </c>
       <c r="C521" t="s">
-        <v>1594</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="522" spans="1:3">
@@ -12500,7 +12482,7 @@
         <v>545</v>
       </c>
       <c r="C522" t="s">
-        <v>1595</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="523" spans="1:3">
@@ -12511,7 +12493,7 @@
         <v>546</v>
       </c>
       <c r="C523" t="s">
-        <v>1596</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="524" spans="1:3">
@@ -12522,7 +12504,7 @@
         <v>547</v>
       </c>
       <c r="C524" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="525" spans="1:3">
@@ -12533,7 +12515,7 @@
         <v>548</v>
       </c>
       <c r="C525" t="s">
-        <v>1598</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="526" spans="1:3">
@@ -12544,7 +12526,7 @@
         <v>549</v>
       </c>
       <c r="C526" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="527" spans="1:3">
@@ -12555,7 +12537,7 @@
         <v>550</v>
       </c>
       <c r="C527" t="s">
-        <v>1600</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="528" spans="1:3">
@@ -12566,7 +12548,7 @@
         <v>551</v>
       </c>
       <c r="C528" t="s">
-        <v>1601</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="529" spans="1:3">
@@ -12577,7 +12559,7 @@
         <v>552</v>
       </c>
       <c r="C529" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="530" spans="1:3">
@@ -12588,7 +12570,7 @@
         <v>553</v>
       </c>
       <c r="C530" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="531" spans="1:3">
@@ -12599,7 +12581,7 @@
         <v>554</v>
       </c>
       <c r="C531" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="532" spans="1:3">
@@ -12610,7 +12592,7 @@
         <v>555</v>
       </c>
       <c r="C532" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="533" spans="1:3">
@@ -12621,7 +12603,7 @@
         <v>556</v>
       </c>
       <c r="C533" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="534" spans="1:3">
@@ -12632,7 +12614,7 @@
         <v>557</v>
       </c>
       <c r="C534" t="s">
-        <v>1607</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="535" spans="1:3">
@@ -12643,7 +12625,7 @@
         <v>558</v>
       </c>
       <c r="C535" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="536" spans="1:3">
@@ -12654,7 +12636,7 @@
         <v>559</v>
       </c>
       <c r="C536" t="s">
-        <v>1609</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="537" spans="1:3">
@@ -12665,7 +12647,7 @@
         <v>560</v>
       </c>
       <c r="C537" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="538" spans="1:3">
@@ -12676,7 +12658,7 @@
         <v>561</v>
       </c>
       <c r="C538" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="539" spans="1:3">
@@ -12687,7 +12669,7 @@
         <v>562</v>
       </c>
       <c r="C539" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="540" spans="1:3">
@@ -12698,7 +12680,7 @@
         <v>563</v>
       </c>
       <c r="C540" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="541" spans="1:3">
@@ -12709,7 +12691,7 @@
         <v>564</v>
       </c>
       <c r="C541" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="542" spans="1:3">
@@ -12720,7 +12702,7 @@
         <v>565</v>
       </c>
       <c r="C542" t="s">
-        <v>1615</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="543" spans="1:3">
@@ -12731,7 +12713,7 @@
         <v>566</v>
       </c>
       <c r="C543" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="544" spans="1:3">
@@ -12742,7 +12724,7 @@
         <v>567</v>
       </c>
       <c r="C544" t="s">
-        <v>1617</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="545" spans="1:3">
@@ -12753,7 +12735,7 @@
         <v>568</v>
       </c>
       <c r="C545" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="546" spans="1:3">
@@ -12764,7 +12746,7 @@
         <v>569</v>
       </c>
       <c r="C546" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="547" spans="1:3">
@@ -12775,18 +12757,18 @@
         <v>570</v>
       </c>
       <c r="C547" t="s">
-        <v>1620</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="548" spans="1:3">
       <c r="A548" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B548" t="s">
         <v>571</v>
       </c>
       <c r="C548" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="549" spans="1:3">
@@ -12797,7 +12779,7 @@
         <v>572</v>
       </c>
       <c r="C549" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="550" spans="1:3">
@@ -12808,7 +12790,7 @@
         <v>573</v>
       </c>
       <c r="C550" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="551" spans="1:3">
@@ -12819,7 +12801,7 @@
         <v>574</v>
       </c>
       <c r="C551" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="552" spans="1:3">
@@ -12830,7 +12812,7 @@
         <v>575</v>
       </c>
       <c r="C552" t="s">
-        <v>1625</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="553" spans="1:3">
@@ -12841,7 +12823,7 @@
         <v>576</v>
       </c>
       <c r="C553" t="s">
-        <v>1626</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="554" spans="1:3">
@@ -12852,7 +12834,7 @@
         <v>577</v>
       </c>
       <c r="C554" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="555" spans="1:3">
@@ -12863,7 +12845,7 @@
         <v>578</v>
       </c>
       <c r="C555" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="556" spans="1:3">
@@ -12874,7 +12856,7 @@
         <v>579</v>
       </c>
       <c r="C556" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="557" spans="1:3">
@@ -12885,7 +12867,7 @@
         <v>580</v>
       </c>
       <c r="C557" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="558" spans="1:3">
@@ -12896,7 +12878,7 @@
         <v>581</v>
       </c>
       <c r="C558" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="559" spans="1:3">
@@ -12907,7 +12889,7 @@
         <v>582</v>
       </c>
       <c r="C559" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="560" spans="1:3">
@@ -12918,7 +12900,7 @@
         <v>583</v>
       </c>
       <c r="C560" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="561" spans="1:3">
@@ -12929,7 +12911,7 @@
         <v>584</v>
       </c>
       <c r="C561" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="562" spans="1:3">
@@ -12940,7 +12922,7 @@
         <v>585</v>
       </c>
       <c r="C562" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="563" spans="1:3">
@@ -12951,7 +12933,7 @@
         <v>586</v>
       </c>
       <c r="C563" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="564" spans="1:3">
@@ -12962,7 +12944,7 @@
         <v>587</v>
       </c>
       <c r="C564" t="s">
-        <v>1637</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="565" spans="1:3">
@@ -12973,7 +12955,7 @@
         <v>588</v>
       </c>
       <c r="C565" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="566" spans="1:3">
@@ -12984,7 +12966,7 @@
         <v>589</v>
       </c>
       <c r="C566" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="567" spans="1:3">
@@ -12995,7 +12977,7 @@
         <v>590</v>
       </c>
       <c r="C567" t="s">
-        <v>1640</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="568" spans="1:3">
@@ -13006,7 +12988,7 @@
         <v>591</v>
       </c>
       <c r="C568" t="s">
-        <v>1641</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="569" spans="1:3">
@@ -13017,7 +12999,7 @@
         <v>592</v>
       </c>
       <c r="C569" t="s">
-        <v>1642</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="570" spans="1:3">
@@ -13028,7 +13010,7 @@
         <v>593</v>
       </c>
       <c r="C570" t="s">
-        <v>1643</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="571" spans="1:3">
@@ -13039,7 +13021,7 @@
         <v>594</v>
       </c>
       <c r="C571" t="s">
-        <v>1644</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="572" spans="1:3">
@@ -13050,7 +13032,7 @@
         <v>595</v>
       </c>
       <c r="C572" t="s">
-        <v>1645</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="573" spans="1:3">
@@ -13061,7 +13043,7 @@
         <v>596</v>
       </c>
       <c r="C573" t="s">
-        <v>1646</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="574" spans="1:3">
@@ -13072,7 +13054,7 @@
         <v>597</v>
       </c>
       <c r="C574" t="s">
-        <v>1647</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="575" spans="1:3">
@@ -13083,7 +13065,7 @@
         <v>598</v>
       </c>
       <c r="C575" t="s">
-        <v>1648</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="576" spans="1:3">
@@ -13094,7 +13076,7 @@
         <v>599</v>
       </c>
       <c r="C576" t="s">
-        <v>1649</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="577" spans="1:3">
@@ -13105,7 +13087,7 @@
         <v>600</v>
       </c>
       <c r="C577" t="s">
-        <v>1650</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="578" spans="1:3">
@@ -13116,7 +13098,7 @@
         <v>601</v>
       </c>
       <c r="C578" t="s">
-        <v>1651</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="579" spans="1:3">
@@ -13127,7 +13109,7 @@
         <v>602</v>
       </c>
       <c r="C579" t="s">
-        <v>1652</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="580" spans="1:3">
@@ -13138,7 +13120,7 @@
         <v>603</v>
       </c>
       <c r="C580" t="s">
-        <v>1653</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="581" spans="1:3">
@@ -13149,7 +13131,7 @@
         <v>604</v>
       </c>
       <c r="C581" t="s">
-        <v>1654</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="582" spans="1:3">
@@ -13160,7 +13142,7 @@
         <v>605</v>
       </c>
       <c r="C582" t="s">
-        <v>1655</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="583" spans="1:3">
@@ -13171,7 +13153,7 @@
         <v>606</v>
       </c>
       <c r="C583" t="s">
-        <v>1656</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="584" spans="1:3">
@@ -13182,7 +13164,7 @@
         <v>607</v>
       </c>
       <c r="C584" t="s">
-        <v>1657</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="585" spans="1:3">
@@ -13193,7 +13175,7 @@
         <v>608</v>
       </c>
       <c r="C585" t="s">
-        <v>1627</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="586" spans="1:3">
@@ -13204,7 +13186,7 @@
         <v>609</v>
       </c>
       <c r="C586" t="s">
-        <v>1658</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="587" spans="1:3">
@@ -13215,7 +13197,7 @@
         <v>610</v>
       </c>
       <c r="C587" t="s">
-        <v>1659</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="588" spans="1:3">
@@ -13226,7 +13208,7 @@
         <v>611</v>
       </c>
       <c r="C588" t="s">
-        <v>1660</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="589" spans="1:3">
@@ -13237,7 +13219,7 @@
         <v>612</v>
       </c>
       <c r="C589" t="s">
-        <v>1661</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="590" spans="1:3">
@@ -13248,18 +13230,18 @@
         <v>613</v>
       </c>
       <c r="C590" t="s">
-        <v>1662</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="591" spans="1:3">
       <c r="A591" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B591" t="s">
         <v>614</v>
       </c>
       <c r="C591" t="s">
-        <v>1663</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="592" spans="1:3">
@@ -13270,7 +13252,7 @@
         <v>615</v>
       </c>
       <c r="C592" t="s">
-        <v>1664</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="593" spans="1:3">
@@ -13281,7 +13263,7 @@
         <v>616</v>
       </c>
       <c r="C593" t="s">
-        <v>1665</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="594" spans="1:3">
@@ -13292,7 +13274,7 @@
         <v>617</v>
       </c>
       <c r="C594" t="s">
-        <v>1666</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="595" spans="1:3">
@@ -13303,7 +13285,7 @@
         <v>618</v>
       </c>
       <c r="C595" t="s">
-        <v>1667</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="596" spans="1:3">
@@ -13314,7 +13296,7 @@
         <v>619</v>
       </c>
       <c r="C596" t="s">
-        <v>1668</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="597" spans="1:3">
@@ -13325,18 +13307,18 @@
         <v>620</v>
       </c>
       <c r="C597" t="s">
-        <v>1669</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="598" spans="1:3">
       <c r="A598" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B598" t="s">
         <v>621</v>
       </c>
       <c r="C598" t="s">
-        <v>1670</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="599" spans="1:3">
@@ -13347,7 +13329,7 @@
         <v>622</v>
       </c>
       <c r="C599" t="s">
-        <v>1671</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="600" spans="1:3">
@@ -13358,7 +13340,7 @@
         <v>623</v>
       </c>
       <c r="C600" t="s">
-        <v>1672</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="601" spans="1:3">
@@ -13369,7 +13351,7 @@
         <v>624</v>
       </c>
       <c r="C601" t="s">
-        <v>1673</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="602" spans="1:3">
@@ -13380,7 +13362,7 @@
         <v>625</v>
       </c>
       <c r="C602" t="s">
-        <v>1674</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="603" spans="1:3">
@@ -13391,7 +13373,7 @@
         <v>626</v>
       </c>
       <c r="C603" t="s">
-        <v>1675</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="604" spans="1:3">
@@ -13402,7 +13384,7 @@
         <v>627</v>
       </c>
       <c r="C604" t="s">
-        <v>1676</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="605" spans="1:3">
@@ -13413,7 +13395,7 @@
         <v>628</v>
       </c>
       <c r="C605" t="s">
-        <v>1677</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="606" spans="1:3">
@@ -13424,7 +13406,7 @@
         <v>629</v>
       </c>
       <c r="C606" t="s">
-        <v>1678</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="607" spans="1:3">
@@ -13435,7 +13417,7 @@
         <v>630</v>
       </c>
       <c r="C607" t="s">
-        <v>1679</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="608" spans="1:3">
@@ -13446,7 +13428,7 @@
         <v>631</v>
       </c>
       <c r="C608" t="s">
-        <v>1680</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="609" spans="1:3">
@@ -13457,7 +13439,7 @@
         <v>632</v>
       </c>
       <c r="C609" t="s">
-        <v>1681</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="610" spans="1:3">
@@ -13468,7 +13450,7 @@
         <v>633</v>
       </c>
       <c r="C610" t="s">
-        <v>1682</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="611" spans="1:3">
@@ -13479,7 +13461,7 @@
         <v>634</v>
       </c>
       <c r="C611" t="s">
-        <v>1683</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="612" spans="1:3">
@@ -13490,7 +13472,7 @@
         <v>635</v>
       </c>
       <c r="C612" t="s">
-        <v>1684</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="613" spans="1:3">
@@ -13501,7 +13483,7 @@
         <v>636</v>
       </c>
       <c r="C613" t="s">
-        <v>1685</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="614" spans="1:3">
@@ -13512,7 +13494,7 @@
         <v>637</v>
       </c>
       <c r="C614" t="s">
-        <v>1686</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="615" spans="1:3">
@@ -13523,7 +13505,7 @@
         <v>638</v>
       </c>
       <c r="C615" t="s">
-        <v>1687</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="616" spans="1:3">
@@ -13534,7 +13516,7 @@
         <v>639</v>
       </c>
       <c r="C616" t="s">
-        <v>1688</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="617" spans="1:3">
@@ -13545,7 +13527,7 @@
         <v>640</v>
       </c>
       <c r="C617" t="s">
-        <v>1689</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="618" spans="1:3">
@@ -13556,7 +13538,7 @@
         <v>641</v>
       </c>
       <c r="C618" t="s">
-        <v>1690</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="619" spans="1:3">
@@ -13567,7 +13549,7 @@
         <v>642</v>
       </c>
       <c r="C619" t="s">
-        <v>1691</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="620" spans="1:3">
@@ -13578,7 +13560,7 @@
         <v>643</v>
       </c>
       <c r="C620" t="s">
-        <v>1692</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="621" spans="1:3">
@@ -13589,7 +13571,7 @@
         <v>644</v>
       </c>
       <c r="C621" t="s">
-        <v>1693</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="622" spans="1:3">
@@ -13600,7 +13582,7 @@
         <v>645</v>
       </c>
       <c r="C622" t="s">
-        <v>1694</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="623" spans="1:3">
@@ -13611,18 +13593,18 @@
         <v>646</v>
       </c>
       <c r="C623" t="s">
-        <v>1695</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="624" spans="1:3">
       <c r="A624" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B624" t="s">
         <v>647</v>
       </c>
       <c r="C624" t="s">
-        <v>1696</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="625" spans="1:3">
@@ -13633,7 +13615,7 @@
         <v>648</v>
       </c>
       <c r="C625" t="s">
-        <v>1697</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="626" spans="1:3">
@@ -13644,7 +13626,7 @@
         <v>649</v>
       </c>
       <c r="C626" t="s">
-        <v>1698</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="627" spans="1:3">
@@ -13655,7 +13637,7 @@
         <v>650</v>
       </c>
       <c r="C627" t="s">
-        <v>1699</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="628" spans="1:3">
@@ -13666,7 +13648,7 @@
         <v>651</v>
       </c>
       <c r="C628" t="s">
-        <v>1700</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="629" spans="1:3">
@@ -13677,7 +13659,7 @@
         <v>652</v>
       </c>
       <c r="C629" t="s">
-        <v>1701</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="630" spans="1:3">
@@ -13688,7 +13670,7 @@
         <v>653</v>
       </c>
       <c r="C630" t="s">
-        <v>1702</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="631" spans="1:3">
@@ -13699,7 +13681,7 @@
         <v>654</v>
       </c>
       <c r="C631" t="s">
-        <v>1703</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="632" spans="1:3">
@@ -13710,7 +13692,7 @@
         <v>655</v>
       </c>
       <c r="C632" t="s">
-        <v>1704</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="633" spans="1:3">
@@ -13721,7 +13703,7 @@
         <v>656</v>
       </c>
       <c r="C633" t="s">
-        <v>1705</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="634" spans="1:3">
@@ -13732,18 +13714,18 @@
         <v>657</v>
       </c>
       <c r="C634" t="s">
-        <v>1706</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="635" spans="1:3">
       <c r="A635" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B635" t="s">
         <v>658</v>
       </c>
       <c r="C635" t="s">
-        <v>1707</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="636" spans="1:3">
@@ -13754,7 +13736,7 @@
         <v>659</v>
       </c>
       <c r="C636" t="s">
-        <v>1708</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="637" spans="1:3">
@@ -13765,7 +13747,7 @@
         <v>660</v>
       </c>
       <c r="C637" t="s">
-        <v>1709</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="638" spans="1:3">
@@ -13776,7 +13758,7 @@
         <v>661</v>
       </c>
       <c r="C638" t="s">
-        <v>1710</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="639" spans="1:3">
@@ -13787,7 +13769,7 @@
         <v>662</v>
       </c>
       <c r="C639" t="s">
-        <v>1711</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="640" spans="1:3">
@@ -13798,7 +13780,7 @@
         <v>663</v>
       </c>
       <c r="C640" t="s">
-        <v>1712</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="641" spans="1:3">
@@ -13809,7 +13791,7 @@
         <v>664</v>
       </c>
       <c r="C641" t="s">
-        <v>1713</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="642" spans="1:3">
@@ -13820,7 +13802,7 @@
         <v>665</v>
       </c>
       <c r="C642" t="s">
-        <v>1714</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="643" spans="1:3">
@@ -13831,7 +13813,7 @@
         <v>666</v>
       </c>
       <c r="C643" t="s">
-        <v>1715</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="644" spans="1:3">
@@ -13842,7 +13824,7 @@
         <v>667</v>
       </c>
       <c r="C644" t="s">
-        <v>1716</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="645" spans="1:3">
@@ -13853,7 +13835,7 @@
         <v>668</v>
       </c>
       <c r="C645" t="s">
-        <v>1717</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="646" spans="1:3">
@@ -13864,7 +13846,7 @@
         <v>669</v>
       </c>
       <c r="C646" t="s">
-        <v>1718</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="647" spans="1:3">
@@ -13875,7 +13857,7 @@
         <v>670</v>
       </c>
       <c r="C647" t="s">
-        <v>1719</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="648" spans="1:3">
@@ -13886,7 +13868,7 @@
         <v>671</v>
       </c>
       <c r="C648" t="s">
-        <v>1720</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="649" spans="1:3">
@@ -13897,7 +13879,7 @@
         <v>672</v>
       </c>
       <c r="C649" t="s">
-        <v>1721</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="650" spans="1:3">
@@ -13908,7 +13890,7 @@
         <v>673</v>
       </c>
       <c r="C650" t="s">
-        <v>1722</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="651" spans="1:3">
@@ -13919,7 +13901,7 @@
         <v>674</v>
       </c>
       <c r="C651" t="s">
-        <v>1723</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="652" spans="1:3">
@@ -13930,7 +13912,7 @@
         <v>675</v>
       </c>
       <c r="C652" t="s">
-        <v>1724</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="653" spans="1:3">
@@ -13941,7 +13923,7 @@
         <v>676</v>
       </c>
       <c r="C653" t="s">
-        <v>1725</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="654" spans="1:3">
@@ -13952,7 +13934,7 @@
         <v>677</v>
       </c>
       <c r="C654" t="s">
-        <v>1726</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="655" spans="1:3">
@@ -13963,7 +13945,7 @@
         <v>678</v>
       </c>
       <c r="C655" t="s">
-        <v>1727</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="656" spans="1:3">
@@ -13974,7 +13956,7 @@
         <v>679</v>
       </c>
       <c r="C656" t="s">
-        <v>1728</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="657" spans="1:3">
@@ -13985,7 +13967,7 @@
         <v>680</v>
       </c>
       <c r="C657" t="s">
-        <v>1729</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="658" spans="1:3">
@@ -13996,7 +13978,7 @@
         <v>681</v>
       </c>
       <c r="C658" t="s">
-        <v>1730</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="659" spans="1:3">
@@ -14007,18 +13989,18 @@
         <v>682</v>
       </c>
       <c r="C659" t="s">
-        <v>1731</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="660" spans="1:3">
       <c r="A660" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B660" t="s">
         <v>683</v>
       </c>
       <c r="C660" t="s">
-        <v>1732</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="661" spans="1:3">
@@ -14029,7 +14011,7 @@
         <v>684</v>
       </c>
       <c r="C661" t="s">
-        <v>1733</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="662" spans="1:3">
@@ -14040,7 +14022,7 @@
         <v>685</v>
       </c>
       <c r="C662" t="s">
-        <v>1734</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="663" spans="1:3">
@@ -14051,7 +14033,7 @@
         <v>686</v>
       </c>
       <c r="C663" t="s">
-        <v>1735</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="664" spans="1:3">
@@ -14062,7 +14044,7 @@
         <v>687</v>
       </c>
       <c r="C664" t="s">
-        <v>1736</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="665" spans="1:3">
@@ -14073,7 +14055,7 @@
         <v>688</v>
       </c>
       <c r="C665" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="666" spans="1:3">
@@ -14084,7 +14066,7 @@
         <v>689</v>
       </c>
       <c r="C666" t="s">
-        <v>1738</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="667" spans="1:3">
@@ -14095,7 +14077,7 @@
         <v>690</v>
       </c>
       <c r="C667" t="s">
-        <v>1739</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="668" spans="1:3">
@@ -14106,7 +14088,7 @@
         <v>691</v>
       </c>
       <c r="C668" t="s">
-        <v>1740</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="669" spans="1:3">
@@ -14117,7 +14099,7 @@
         <v>692</v>
       </c>
       <c r="C669" t="s">
-        <v>1741</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="670" spans="1:3">
@@ -14128,7 +14110,7 @@
         <v>693</v>
       </c>
       <c r="C670" t="s">
-        <v>1742</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="671" spans="1:3">
@@ -14139,7 +14121,7 @@
         <v>694</v>
       </c>
       <c r="C671" t="s">
-        <v>1743</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="672" spans="1:3">
@@ -14150,7 +14132,7 @@
         <v>695</v>
       </c>
       <c r="C672" t="s">
-        <v>1744</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="673" spans="1:3">
@@ -14161,7 +14143,7 @@
         <v>696</v>
       </c>
       <c r="C673" t="s">
-        <v>1745</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="674" spans="1:3">
@@ -14172,7 +14154,7 @@
         <v>697</v>
       </c>
       <c r="C674" t="s">
-        <v>1746</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="675" spans="1:3">
@@ -14183,18 +14165,18 @@
         <v>698</v>
       </c>
       <c r="C675" t="s">
-        <v>1747</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="676" spans="1:3">
       <c r="A676" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B676" t="s">
         <v>699</v>
       </c>
       <c r="C676" t="s">
-        <v>1173</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="677" spans="1:3">
@@ -14205,7 +14187,7 @@
         <v>700</v>
       </c>
       <c r="C677" t="s">
-        <v>1748</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="678" spans="1:3">
@@ -14216,7 +14198,7 @@
         <v>701</v>
       </c>
       <c r="C678" t="s">
-        <v>1749</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="679" spans="1:3">
@@ -14227,7 +14209,7 @@
         <v>702</v>
       </c>
       <c r="C679" t="s">
-        <v>1750</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="680" spans="1:3">
@@ -14238,7 +14220,7 @@
         <v>703</v>
       </c>
       <c r="C680" t="s">
-        <v>1751</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="681" spans="1:3">
@@ -14249,7 +14231,7 @@
         <v>704</v>
       </c>
       <c r="C681" t="s">
-        <v>1752</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="682" spans="1:3">
@@ -14260,7 +14242,7 @@
         <v>705</v>
       </c>
       <c r="C682" t="s">
-        <v>1753</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="683" spans="1:3">
@@ -14271,7 +14253,7 @@
         <v>706</v>
       </c>
       <c r="C683" t="s">
-        <v>1754</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="684" spans="1:3">
@@ -14282,7 +14264,7 @@
         <v>707</v>
       </c>
       <c r="C684" t="s">
-        <v>1755</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="685" spans="1:3">
@@ -14293,7 +14275,7 @@
         <v>708</v>
       </c>
       <c r="C685" t="s">
-        <v>1756</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="686" spans="1:3">
@@ -14304,7 +14286,7 @@
         <v>709</v>
       </c>
       <c r="C686" t="s">
-        <v>1757</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="687" spans="1:3">
@@ -14315,7 +14297,7 @@
         <v>710</v>
       </c>
       <c r="C687" t="s">
-        <v>1758</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="688" spans="1:3">
@@ -14326,7 +14308,7 @@
         <v>711</v>
       </c>
       <c r="C688" t="s">
-        <v>1759</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="689" spans="1:3">
@@ -14337,7 +14319,7 @@
         <v>712</v>
       </c>
       <c r="C689" t="s">
-        <v>1760</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="690" spans="1:3">
@@ -14348,7 +14330,7 @@
         <v>713</v>
       </c>
       <c r="C690" t="s">
-        <v>1761</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="691" spans="1:3">
@@ -14359,7 +14341,7 @@
         <v>714</v>
       </c>
       <c r="C691" t="s">
-        <v>1762</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="692" spans="1:3">
@@ -14370,7 +14352,7 @@
         <v>715</v>
       </c>
       <c r="C692" t="s">
-        <v>1763</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="693" spans="1:3">
@@ -14381,7 +14363,7 @@
         <v>716</v>
       </c>
       <c r="C693" t="s">
-        <v>1764</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="694" spans="1:3">
@@ -14392,7 +14374,7 @@
         <v>717</v>
       </c>
       <c r="C694" t="s">
-        <v>1765</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="695" spans="1:3">
@@ -14403,7 +14385,7 @@
         <v>718</v>
       </c>
       <c r="C695" t="s">
-        <v>1766</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="696" spans="1:3">
@@ -14414,7 +14396,7 @@
         <v>719</v>
       </c>
       <c r="C696" t="s">
-        <v>1767</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="697" spans="1:3">
@@ -14425,7 +14407,7 @@
         <v>720</v>
       </c>
       <c r="C697" t="s">
-        <v>1768</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="698" spans="1:3">
@@ -14436,7 +14418,7 @@
         <v>721</v>
       </c>
       <c r="C698" t="s">
-        <v>1769</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="699" spans="1:3">
@@ -14447,7 +14429,7 @@
         <v>722</v>
       </c>
       <c r="C699" t="s">
-        <v>1770</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="700" spans="1:3">
@@ -14458,7 +14440,7 @@
         <v>723</v>
       </c>
       <c r="C700" t="s">
-        <v>1771</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="701" spans="1:3">
@@ -14469,7 +14451,7 @@
         <v>724</v>
       </c>
       <c r="C701" t="s">
-        <v>1772</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="702" spans="1:3">
@@ -14480,7 +14462,7 @@
         <v>725</v>
       </c>
       <c r="C702" t="s">
-        <v>1773</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="703" spans="1:3">
@@ -14491,7 +14473,7 @@
         <v>726</v>
       </c>
       <c r="C703" t="s">
-        <v>1774</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="704" spans="1:3">
@@ -14502,7 +14484,7 @@
         <v>727</v>
       </c>
       <c r="C704" t="s">
-        <v>1775</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="705" spans="1:3">
@@ -14513,7 +14495,7 @@
         <v>728</v>
       </c>
       <c r="C705" t="s">
-        <v>1776</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="706" spans="1:3">
@@ -14524,7 +14506,7 @@
         <v>729</v>
       </c>
       <c r="C706" t="s">
-        <v>1777</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="707" spans="1:3">
@@ -14535,7 +14517,7 @@
         <v>730</v>
       </c>
       <c r="C707" t="s">
-        <v>1778</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="708" spans="1:3">
@@ -14546,7 +14528,7 @@
         <v>731</v>
       </c>
       <c r="C708" t="s">
-        <v>1779</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="709" spans="1:3">
@@ -14557,7 +14539,7 @@
         <v>732</v>
       </c>
       <c r="C709" t="s">
-        <v>1780</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="710" spans="1:3">
@@ -14568,7 +14550,7 @@
         <v>733</v>
       </c>
       <c r="C710" t="s">
-        <v>1781</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="711" spans="1:3">
@@ -14579,7 +14561,7 @@
         <v>734</v>
       </c>
       <c r="C711" t="s">
-        <v>1782</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="712" spans="1:3">
@@ -14590,7 +14572,7 @@
         <v>735</v>
       </c>
       <c r="C712" t="s">
-        <v>1783</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="713" spans="1:3">
@@ -14601,7 +14583,7 @@
         <v>736</v>
       </c>
       <c r="C713" t="s">
-        <v>1784</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="714" spans="1:3">
@@ -14612,7 +14594,7 @@
         <v>737</v>
       </c>
       <c r="C714" t="s">
-        <v>1785</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="715" spans="1:3">
@@ -14623,7 +14605,7 @@
         <v>738</v>
       </c>
       <c r="C715" t="s">
-        <v>1786</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="716" spans="1:3">
@@ -14634,29 +14616,29 @@
         <v>739</v>
       </c>
       <c r="C716" t="s">
-        <v>1787</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="717" spans="1:3">
       <c r="A717" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B717" t="s">
         <v>740</v>
       </c>
       <c r="C717" t="s">
-        <v>1788</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="718" spans="1:3">
       <c r="A718" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B718" t="s">
         <v>741</v>
       </c>
       <c r="C718" t="s">
-        <v>1789</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="719" spans="1:3">
@@ -14667,7 +14649,7 @@
         <v>742</v>
       </c>
       <c r="C719" t="s">
-        <v>1790</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="720" spans="1:3">
@@ -14678,7 +14660,7 @@
         <v>743</v>
       </c>
       <c r="C720" t="s">
-        <v>1791</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="721" spans="1:3">
@@ -14689,7 +14671,7 @@
         <v>744</v>
       </c>
       <c r="C721" t="s">
-        <v>1792</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="722" spans="1:3">
@@ -14700,7 +14682,7 @@
         <v>745</v>
       </c>
       <c r="C722" t="s">
-        <v>1793</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="723" spans="1:3">
@@ -14711,7 +14693,7 @@
         <v>746</v>
       </c>
       <c r="C723" t="s">
-        <v>1794</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="724" spans="1:3">
@@ -14722,7 +14704,7 @@
         <v>747</v>
       </c>
       <c r="C724" t="s">
-        <v>1795</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="725" spans="1:3">
@@ -14733,40 +14715,40 @@
         <v>748</v>
       </c>
       <c r="C725" t="s">
-        <v>1796</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="726" spans="1:3">
       <c r="A726" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B726" t="s">
         <v>749</v>
       </c>
       <c r="C726" t="s">
-        <v>1797</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="727" spans="1:3">
       <c r="A727" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B727" t="s">
         <v>750</v>
       </c>
       <c r="C727" t="s">
-        <v>1798</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="728" spans="1:3">
       <c r="A728" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B728" t="s">
         <v>751</v>
       </c>
       <c r="C728" t="s">
-        <v>1799</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="729" spans="1:3">
@@ -14777,7 +14759,7 @@
         <v>752</v>
       </c>
       <c r="C729" t="s">
-        <v>1800</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="730" spans="1:3">
@@ -14788,7 +14770,7 @@
         <v>753</v>
       </c>
       <c r="C730" t="s">
-        <v>1801</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="731" spans="1:3">
@@ -14799,7 +14781,7 @@
         <v>754</v>
       </c>
       <c r="C731" t="s">
-        <v>1802</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="732" spans="1:3">
@@ -14810,7 +14792,7 @@
         <v>755</v>
       </c>
       <c r="C732" t="s">
-        <v>1803</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="733" spans="1:3">
@@ -14821,7 +14803,7 @@
         <v>756</v>
       </c>
       <c r="C733" t="s">
-        <v>1804</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="734" spans="1:3">
@@ -14832,7 +14814,7 @@
         <v>757</v>
       </c>
       <c r="C734" t="s">
-        <v>1805</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="735" spans="1:3">
@@ -14843,7 +14825,7 @@
         <v>758</v>
       </c>
       <c r="C735" t="s">
-        <v>1806</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="736" spans="1:3">
@@ -14854,7 +14836,7 @@
         <v>759</v>
       </c>
       <c r="C736" t="s">
-        <v>1807</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="737" spans="1:3">
@@ -14865,7 +14847,7 @@
         <v>760</v>
       </c>
       <c r="C737" t="s">
-        <v>1808</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="738" spans="1:3">
@@ -14876,7 +14858,7 @@
         <v>761</v>
       </c>
       <c r="C738" t="s">
-        <v>1809</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="739" spans="1:3">
@@ -14887,7 +14869,7 @@
         <v>762</v>
       </c>
       <c r="C739" t="s">
-        <v>1810</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="740" spans="1:3">
@@ -14898,7 +14880,7 @@
         <v>763</v>
       </c>
       <c r="C740" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="741" spans="1:3">
@@ -14909,7 +14891,7 @@
         <v>764</v>
       </c>
       <c r="C741" t="s">
-        <v>1812</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="742" spans="1:3">
@@ -14920,7 +14902,7 @@
         <v>765</v>
       </c>
       <c r="C742" t="s">
-        <v>1813</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="743" spans="1:3">
@@ -14931,7 +14913,7 @@
         <v>766</v>
       </c>
       <c r="C743" t="s">
-        <v>1814</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="744" spans="1:3">
@@ -14942,7 +14924,7 @@
         <v>767</v>
       </c>
       <c r="C744" t="s">
-        <v>1815</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="745" spans="1:3">
@@ -14953,7 +14935,7 @@
         <v>768</v>
       </c>
       <c r="C745" t="s">
-        <v>1816</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="746" spans="1:3">
@@ -14964,7 +14946,7 @@
         <v>769</v>
       </c>
       <c r="C746" t="s">
-        <v>1817</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="747" spans="1:3">
@@ -14975,7 +14957,7 @@
         <v>770</v>
       </c>
       <c r="C747" t="s">
-        <v>1818</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="748" spans="1:3">
@@ -14986,7 +14968,7 @@
         <v>771</v>
       </c>
       <c r="C748" t="s">
-        <v>1819</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="749" spans="1:3">
@@ -14997,7 +14979,7 @@
         <v>772</v>
       </c>
       <c r="C749" t="s">
-        <v>1820</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="750" spans="1:3">
@@ -15008,7 +14990,7 @@
         <v>773</v>
       </c>
       <c r="C750" t="s">
-        <v>1821</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="751" spans="1:3">
@@ -15019,7 +15001,7 @@
         <v>774</v>
       </c>
       <c r="C751" t="s">
-        <v>1822</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="752" spans="1:3">
@@ -15030,7 +15012,7 @@
         <v>775</v>
       </c>
       <c r="C752" t="s">
-        <v>1823</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="753" spans="1:3">
@@ -15041,7 +15023,7 @@
         <v>776</v>
       </c>
       <c r="C753" t="s">
-        <v>1824</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="754" spans="1:3">
@@ -15052,7 +15034,7 @@
         <v>777</v>
       </c>
       <c r="C754" t="s">
-        <v>1825</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="755" spans="1:3">
@@ -15063,7 +15045,7 @@
         <v>778</v>
       </c>
       <c r="C755" t="s">
-        <v>1826</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="756" spans="1:3">
@@ -15074,7 +15056,7 @@
         <v>779</v>
       </c>
       <c r="C756" t="s">
-        <v>1827</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="757" spans="1:3">
@@ -15085,7 +15067,7 @@
         <v>780</v>
       </c>
       <c r="C757" t="s">
-        <v>1828</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="758" spans="1:3">
@@ -15096,7 +15078,7 @@
         <v>781</v>
       </c>
       <c r="C758" t="s">
-        <v>1829</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="759" spans="1:3">
@@ -15107,7 +15089,7 @@
         <v>782</v>
       </c>
       <c r="C759" t="s">
-        <v>1830</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="760" spans="1:3">
@@ -15118,7 +15100,7 @@
         <v>783</v>
       </c>
       <c r="C760" t="s">
-        <v>1831</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="761" spans="1:3">
@@ -15129,7 +15111,7 @@
         <v>784</v>
       </c>
       <c r="C761" t="s">
-        <v>1832</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="762" spans="1:3">
@@ -15140,7 +15122,7 @@
         <v>785</v>
       </c>
       <c r="C762" t="s">
-        <v>1833</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="763" spans="1:3">
@@ -15151,7 +15133,7 @@
         <v>786</v>
       </c>
       <c r="C763" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="764" spans="1:3">
@@ -15162,7 +15144,7 @@
         <v>787</v>
       </c>
       <c r="C764" t="s">
-        <v>1835</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="765" spans="1:3">
@@ -15173,7 +15155,7 @@
         <v>788</v>
       </c>
       <c r="C765" t="s">
-        <v>1836</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="766" spans="1:3">
@@ -15184,7 +15166,7 @@
         <v>789</v>
       </c>
       <c r="C766" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="767" spans="1:3">
@@ -15195,7 +15177,7 @@
         <v>790</v>
       </c>
       <c r="C767" t="s">
-        <v>1838</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="768" spans="1:3">
@@ -15206,7 +15188,7 @@
         <v>791</v>
       </c>
       <c r="C768" t="s">
-        <v>1839</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="769" spans="1:3">
@@ -15217,7 +15199,7 @@
         <v>792</v>
       </c>
       <c r="C769" t="s">
-        <v>1840</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="770" spans="1:3">
@@ -15228,7 +15210,7 @@
         <v>793</v>
       </c>
       <c r="C770" t="s">
-        <v>1841</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="771" spans="1:3">
@@ -15239,7 +15221,7 @@
         <v>794</v>
       </c>
       <c r="C771" t="s">
-        <v>1842</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="772" spans="1:3">
@@ -15250,7 +15232,7 @@
         <v>795</v>
       </c>
       <c r="C772" t="s">
-        <v>1843</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="773" spans="1:3">
@@ -15261,7 +15243,7 @@
         <v>796</v>
       </c>
       <c r="C773" t="s">
-        <v>1844</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="774" spans="1:3">
@@ -15272,7 +15254,7 @@
         <v>797</v>
       </c>
       <c r="C774" t="s">
-        <v>1845</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="775" spans="1:3">
@@ -15283,7 +15265,7 @@
         <v>798</v>
       </c>
       <c r="C775" t="s">
-        <v>1846</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="776" spans="1:3">
@@ -15294,7 +15276,7 @@
         <v>799</v>
       </c>
       <c r="C776" t="s">
-        <v>1847</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="777" spans="1:3">
@@ -15305,7 +15287,7 @@
         <v>800</v>
       </c>
       <c r="C777" t="s">
-        <v>1848</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="778" spans="1:3">
@@ -15316,7 +15298,7 @@
         <v>801</v>
       </c>
       <c r="C778" t="s">
-        <v>1849</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="779" spans="1:3">
@@ -15327,7 +15309,7 @@
         <v>802</v>
       </c>
       <c r="C779" t="s">
-        <v>1850</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="780" spans="1:3">
@@ -15338,7 +15320,7 @@
         <v>803</v>
       </c>
       <c r="C780" t="s">
-        <v>1771</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="781" spans="1:3">
@@ -15349,7 +15331,7 @@
         <v>804</v>
       </c>
       <c r="C781" t="s">
-        <v>1851</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="782" spans="1:3">
@@ -15360,7 +15342,7 @@
         <v>805</v>
       </c>
       <c r="C782" t="s">
-        <v>1852</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="783" spans="1:3">
@@ -15371,7 +15353,7 @@
         <v>806</v>
       </c>
       <c r="C783" t="s">
-        <v>1853</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="784" spans="1:3">
@@ -15382,7 +15364,7 @@
         <v>807</v>
       </c>
       <c r="C784" t="s">
-        <v>1854</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="785" spans="1:3">
@@ -15393,7 +15375,7 @@
         <v>808</v>
       </c>
       <c r="C785" t="s">
-        <v>1855</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="786" spans="1:3">
@@ -15404,7 +15386,7 @@
         <v>809</v>
       </c>
       <c r="C786" t="s">
-        <v>1856</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="787" spans="1:3">
@@ -15415,7 +15397,7 @@
         <v>810</v>
       </c>
       <c r="C787" t="s">
-        <v>1857</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="788" spans="1:3">
@@ -15426,7 +15408,7 @@
         <v>811</v>
       </c>
       <c r="C788" t="s">
-        <v>1858</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="789" spans="1:3">
@@ -15437,7 +15419,7 @@
         <v>812</v>
       </c>
       <c r="C789" t="s">
-        <v>1859</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="790" spans="1:3">
@@ -15448,7 +15430,7 @@
         <v>813</v>
       </c>
       <c r="C790" t="s">
-        <v>1860</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="791" spans="1:3">
@@ -15459,7 +15441,7 @@
         <v>814</v>
       </c>
       <c r="C791" t="s">
-        <v>1861</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="792" spans="1:3">
@@ -15470,7 +15452,7 @@
         <v>815</v>
       </c>
       <c r="C792" t="s">
-        <v>1862</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="793" spans="1:3">
@@ -15481,7 +15463,7 @@
         <v>816</v>
       </c>
       <c r="C793" t="s">
-        <v>1863</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="794" spans="1:3">
@@ -15492,7 +15474,7 @@
         <v>817</v>
       </c>
       <c r="C794" t="s">
-        <v>1864</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="795" spans="1:3">
@@ -15503,7 +15485,7 @@
         <v>818</v>
       </c>
       <c r="C795" t="s">
-        <v>1865</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="796" spans="1:3">
@@ -15514,7 +15496,7 @@
         <v>819</v>
       </c>
       <c r="C796" t="s">
-        <v>1866</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="797" spans="1:3">
@@ -15525,7 +15507,7 @@
         <v>820</v>
       </c>
       <c r="C797" t="s">
-        <v>1867</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="798" spans="1:3">
@@ -15536,7 +15518,7 @@
         <v>821</v>
       </c>
       <c r="C798" t="s">
-        <v>1868</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="799" spans="1:3">
@@ -15547,7 +15529,7 @@
         <v>822</v>
       </c>
       <c r="C799" t="s">
-        <v>1869</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="800" spans="1:3">
@@ -15558,7 +15540,7 @@
         <v>823</v>
       </c>
       <c r="C800" t="s">
-        <v>1870</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="801" spans="1:3">
@@ -15569,7 +15551,7 @@
         <v>824</v>
       </c>
       <c r="C801" t="s">
-        <v>1871</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="802" spans="1:3">
@@ -15580,7 +15562,7 @@
         <v>825</v>
       </c>
       <c r="C802" t="s">
-        <v>1872</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="803" spans="1:3">
@@ -15591,7 +15573,7 @@
         <v>826</v>
       </c>
       <c r="C803" t="s">
-        <v>1873</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="804" spans="1:3">
@@ -15602,7 +15584,7 @@
         <v>827</v>
       </c>
       <c r="C804" t="s">
-        <v>1874</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="805" spans="1:3">
@@ -15613,7 +15595,7 @@
         <v>828</v>
       </c>
       <c r="C805" t="s">
-        <v>1875</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="806" spans="1:3">
@@ -15624,7 +15606,7 @@
         <v>829</v>
       </c>
       <c r="C806" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="807" spans="1:3">
@@ -15635,7 +15617,7 @@
         <v>830</v>
       </c>
       <c r="C807" t="s">
-        <v>1877</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="808" spans="1:3">
@@ -15646,7 +15628,7 @@
         <v>831</v>
       </c>
       <c r="C808" t="s">
-        <v>1878</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="809" spans="1:3">
@@ -15657,7 +15639,7 @@
         <v>832</v>
       </c>
       <c r="C809" t="s">
-        <v>1879</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="810" spans="1:3">
@@ -15668,7 +15650,7 @@
         <v>833</v>
       </c>
       <c r="C810" t="s">
-        <v>1880</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="811" spans="1:3">
@@ -15679,7 +15661,7 @@
         <v>834</v>
       </c>
       <c r="C811" t="s">
-        <v>1881</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="812" spans="1:3">
@@ -15690,7 +15672,7 @@
         <v>835</v>
       </c>
       <c r="C812" t="s">
-        <v>1882</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="813" spans="1:3">
@@ -15701,7 +15683,7 @@
         <v>836</v>
       </c>
       <c r="C813" t="s">
-        <v>1883</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="814" spans="1:3">
@@ -15712,7 +15694,7 @@
         <v>837</v>
       </c>
       <c r="C814" t="s">
-        <v>1884</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="815" spans="1:3">
@@ -15723,7 +15705,7 @@
         <v>838</v>
       </c>
       <c r="C815" t="s">
-        <v>1885</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="816" spans="1:3">
@@ -15734,7 +15716,7 @@
         <v>839</v>
       </c>
       <c r="C816" t="s">
-        <v>1886</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="817" spans="1:3">
@@ -15745,7 +15727,7 @@
         <v>840</v>
       </c>
       <c r="C817" t="s">
-        <v>1887</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="818" spans="1:3">
@@ -15756,7 +15738,7 @@
         <v>841</v>
       </c>
       <c r="C818" t="s">
-        <v>1888</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="819" spans="1:3">
@@ -15767,7 +15749,7 @@
         <v>842</v>
       </c>
       <c r="C819" t="s">
-        <v>1889</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="820" spans="1:3">
@@ -15778,7 +15760,7 @@
         <v>843</v>
       </c>
       <c r="C820" t="s">
-        <v>1890</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="821" spans="1:3">
@@ -15789,7 +15771,7 @@
         <v>844</v>
       </c>
       <c r="C821" t="s">
-        <v>1891</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="822" spans="1:3">
@@ -15800,7 +15782,7 @@
         <v>845</v>
       </c>
       <c r="C822" t="s">
-        <v>1892</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="823" spans="1:3">
@@ -15811,7 +15793,7 @@
         <v>846</v>
       </c>
       <c r="C823" t="s">
-        <v>1893</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="824" spans="1:3">
@@ -15822,7 +15804,7 @@
         <v>847</v>
       </c>
       <c r="C824" t="s">
-        <v>1894</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="825" spans="1:3">
@@ -15833,7 +15815,7 @@
         <v>848</v>
       </c>
       <c r="C825" t="s">
-        <v>1895</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="826" spans="1:3">
@@ -15844,7 +15826,7 @@
         <v>849</v>
       </c>
       <c r="C826" t="s">
-        <v>1896</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="827" spans="1:3">
@@ -15855,7 +15837,7 @@
         <v>850</v>
       </c>
       <c r="C827" t="s">
-        <v>1897</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="828" spans="1:3">
@@ -15866,7 +15848,7 @@
         <v>851</v>
       </c>
       <c r="C828" t="s">
-        <v>1898</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="829" spans="1:3">
@@ -15877,7 +15859,7 @@
         <v>852</v>
       </c>
       <c r="C829" t="s">
-        <v>1899</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="830" spans="1:3">
@@ -15888,7 +15870,7 @@
         <v>853</v>
       </c>
       <c r="C830" t="s">
-        <v>1900</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="831" spans="1:3">
@@ -15899,7 +15881,7 @@
         <v>854</v>
       </c>
       <c r="C831" t="s">
-        <v>1901</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="832" spans="1:3">
@@ -15910,7 +15892,7 @@
         <v>855</v>
       </c>
       <c r="C832" t="s">
-        <v>1902</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="833" spans="1:3">
@@ -15921,7 +15903,7 @@
         <v>856</v>
       </c>
       <c r="C833" t="s">
-        <v>1903</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="834" spans="1:3">
@@ -15932,7 +15914,7 @@
         <v>857</v>
       </c>
       <c r="C834" t="s">
-        <v>1904</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="835" spans="1:3">
@@ -15943,7 +15925,7 @@
         <v>858</v>
       </c>
       <c r="C835" t="s">
-        <v>1905</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="836" spans="1:3">
@@ -15954,7 +15936,7 @@
         <v>859</v>
       </c>
       <c r="C836" t="s">
-        <v>1906</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="837" spans="1:3">
@@ -15965,7 +15947,7 @@
         <v>860</v>
       </c>
       <c r="C837" t="s">
-        <v>1907</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="838" spans="1:3">
@@ -15976,7 +15958,7 @@
         <v>861</v>
       </c>
       <c r="C838" t="s">
-        <v>1908</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="839" spans="1:3">
@@ -15987,7 +15969,7 @@
         <v>862</v>
       </c>
       <c r="C839" t="s">
-        <v>1909</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="840" spans="1:3">
@@ -15998,7 +15980,7 @@
         <v>863</v>
       </c>
       <c r="C840" t="s">
-        <v>1910</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="841" spans="1:3">
@@ -16009,7 +15991,7 @@
         <v>864</v>
       </c>
       <c r="C841" t="s">
-        <v>1911</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="842" spans="1:3">
@@ -16020,7 +16002,7 @@
         <v>865</v>
       </c>
       <c r="C842" t="s">
-        <v>1912</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="843" spans="1:3">
@@ -16031,7 +16013,7 @@
         <v>866</v>
       </c>
       <c r="C843" t="s">
-        <v>1913</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="844" spans="1:3">
@@ -16042,7 +16024,7 @@
         <v>867</v>
       </c>
       <c r="C844" t="s">
-        <v>1914</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="845" spans="1:3">
@@ -16053,7 +16035,7 @@
         <v>868</v>
       </c>
       <c r="C845" t="s">
-        <v>1915</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="846" spans="1:3">
@@ -16064,7 +16046,7 @@
         <v>869</v>
       </c>
       <c r="C846" t="s">
-        <v>1916</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="847" spans="1:3">
@@ -16075,7 +16057,7 @@
         <v>870</v>
       </c>
       <c r="C847" t="s">
-        <v>1917</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="848" spans="1:3">
@@ -16086,40 +16068,40 @@
         <v>871</v>
       </c>
       <c r="C848" t="s">
-        <v>1918</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="849" spans="1:3">
       <c r="A849" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B849" t="s">
         <v>872</v>
       </c>
       <c r="C849" t="s">
-        <v>1919</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="850" spans="1:3">
       <c r="A850" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B850" t="s">
         <v>873</v>
       </c>
       <c r="C850" t="s">
-        <v>1920</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="851" spans="1:3">
       <c r="A851" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B851" t="s">
         <v>874</v>
       </c>
       <c r="C851" t="s">
-        <v>1921</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="852" spans="1:3">
@@ -16130,7 +16112,7 @@
         <v>875</v>
       </c>
       <c r="C852" t="s">
-        <v>1922</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="853" spans="1:3">
@@ -16141,7 +16123,7 @@
         <v>876</v>
       </c>
       <c r="C853" t="s">
-        <v>1923</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="854" spans="1:3">
@@ -16152,7 +16134,7 @@
         <v>877</v>
       </c>
       <c r="C854" t="s">
-        <v>1924</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="855" spans="1:3">
@@ -16163,7 +16145,7 @@
         <v>878</v>
       </c>
       <c r="C855" t="s">
-        <v>1925</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="856" spans="1:3">
@@ -16174,7 +16156,7 @@
         <v>879</v>
       </c>
       <c r="C856" t="s">
-        <v>1926</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="857" spans="1:3">
@@ -16185,7 +16167,7 @@
         <v>880</v>
       </c>
       <c r="C857" t="s">
-        <v>1927</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="858" spans="1:3">
@@ -16196,7 +16178,7 @@
         <v>881</v>
       </c>
       <c r="C858" t="s">
-        <v>1928</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="859" spans="1:3">
@@ -16207,7 +16189,7 @@
         <v>882</v>
       </c>
       <c r="C859" t="s">
-        <v>1929</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="860" spans="1:3">
@@ -16218,7 +16200,7 @@
         <v>883</v>
       </c>
       <c r="C860" t="s">
-        <v>1930</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="861" spans="1:3">
@@ -16229,7 +16211,7 @@
         <v>884</v>
       </c>
       <c r="C861" t="s">
-        <v>1931</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="862" spans="1:3">
@@ -16240,7 +16222,7 @@
         <v>885</v>
       </c>
       <c r="C862" t="s">
-        <v>1932</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="863" spans="1:3">
@@ -16251,7 +16233,7 @@
         <v>886</v>
       </c>
       <c r="C863" t="s">
-        <v>1933</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="864" spans="1:3">
@@ -16262,7 +16244,7 @@
         <v>887</v>
       </c>
       <c r="C864" t="s">
-        <v>1934</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="865" spans="1:3">
@@ -16273,7 +16255,7 @@
         <v>888</v>
       </c>
       <c r="C865" t="s">
-        <v>1935</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="866" spans="1:3">
@@ -16284,7 +16266,7 @@
         <v>889</v>
       </c>
       <c r="C866" t="s">
-        <v>1936</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="867" spans="1:3">
@@ -16295,7 +16277,7 @@
         <v>890</v>
       </c>
       <c r="C867" t="s">
-        <v>1937</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="868" spans="1:3">
@@ -16306,7 +16288,7 @@
         <v>891</v>
       </c>
       <c r="C868" t="s">
-        <v>1938</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="869" spans="1:3">
@@ -16317,7 +16299,7 @@
         <v>892</v>
       </c>
       <c r="C869" t="s">
-        <v>1939</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="870" spans="1:3">
@@ -16328,7 +16310,7 @@
         <v>893</v>
       </c>
       <c r="C870" t="s">
-        <v>1940</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="871" spans="1:3">
@@ -16339,7 +16321,7 @@
         <v>894</v>
       </c>
       <c r="C871" t="s">
-        <v>1941</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="872" spans="1:3">
@@ -16350,7 +16332,7 @@
         <v>895</v>
       </c>
       <c r="C872" t="s">
-        <v>1942</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="873" spans="1:3">
@@ -16361,7 +16343,7 @@
         <v>896</v>
       </c>
       <c r="C873" t="s">
-        <v>1943</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="874" spans="1:3">
@@ -16372,7 +16354,7 @@
         <v>897</v>
       </c>
       <c r="C874" t="s">
-        <v>1944</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="875" spans="1:3">
@@ -16383,7 +16365,7 @@
         <v>898</v>
       </c>
       <c r="C875" t="s">
-        <v>1945</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="876" spans="1:3">
@@ -16394,7 +16376,7 @@
         <v>899</v>
       </c>
       <c r="C876" t="s">
-        <v>1946</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="877" spans="1:3">
@@ -16405,7 +16387,7 @@
         <v>900</v>
       </c>
       <c r="C877" t="s">
-        <v>1947</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="878" spans="1:3">
@@ -16416,7 +16398,7 @@
         <v>901</v>
       </c>
       <c r="C878" t="s">
-        <v>1948</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="879" spans="1:3">
@@ -16427,7 +16409,7 @@
         <v>902</v>
       </c>
       <c r="C879" t="s">
-        <v>1949</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="880" spans="1:3">
@@ -16438,7 +16420,7 @@
         <v>903</v>
       </c>
       <c r="C880" t="s">
-        <v>1950</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="881" spans="1:3">
@@ -16449,7 +16431,7 @@
         <v>904</v>
       </c>
       <c r="C881" t="s">
-        <v>1951</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="882" spans="1:3">
@@ -16460,7 +16442,7 @@
         <v>905</v>
       </c>
       <c r="C882" t="s">
-        <v>1952</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="883" spans="1:3">
@@ -16471,7 +16453,7 @@
         <v>906</v>
       </c>
       <c r="C883" t="s">
-        <v>1953</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="884" spans="1:3">
@@ -16482,7 +16464,7 @@
         <v>907</v>
       </c>
       <c r="C884" t="s">
-        <v>1954</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="885" spans="1:3">
@@ -16493,7 +16475,7 @@
         <v>908</v>
       </c>
       <c r="C885" t="s">
-        <v>1955</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="886" spans="1:3">
@@ -16504,7 +16486,7 @@
         <v>909</v>
       </c>
       <c r="C886" t="s">
-        <v>1956</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="887" spans="1:3">
@@ -16515,7 +16497,7 @@
         <v>910</v>
       </c>
       <c r="C887" t="s">
-        <v>1957</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="888" spans="1:3">
@@ -16526,7 +16508,7 @@
         <v>911</v>
       </c>
       <c r="C888" t="s">
-        <v>1958</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="889" spans="1:3">
@@ -16537,7 +16519,7 @@
         <v>912</v>
       </c>
       <c r="C889" t="s">
-        <v>1959</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="890" spans="1:3">
@@ -16548,7 +16530,7 @@
         <v>913</v>
       </c>
       <c r="C890" t="s">
-        <v>1960</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="891" spans="1:3">
@@ -16559,7 +16541,7 @@
         <v>914</v>
       </c>
       <c r="C891" t="s">
-        <v>1961</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="892" spans="1:3">
@@ -16570,7 +16552,7 @@
         <v>915</v>
       </c>
       <c r="C892" t="s">
-        <v>1962</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="893" spans="1:3">
@@ -16581,7 +16563,7 @@
         <v>916</v>
       </c>
       <c r="C893" t="s">
-        <v>1963</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="894" spans="1:3">
@@ -16592,7 +16574,7 @@
         <v>917</v>
       </c>
       <c r="C894" t="s">
-        <v>1964</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="895" spans="1:3">
@@ -16603,7 +16585,7 @@
         <v>918</v>
       </c>
       <c r="C895" t="s">
-        <v>1965</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="896" spans="1:3">
@@ -16614,7 +16596,7 @@
         <v>919</v>
       </c>
       <c r="C896" t="s">
-        <v>1966</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="897" spans="1:3">
@@ -16625,7 +16607,7 @@
         <v>920</v>
       </c>
       <c r="C897" t="s">
-        <v>1967</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="898" spans="1:3">
@@ -16636,7 +16618,7 @@
         <v>921</v>
       </c>
       <c r="C898" t="s">
-        <v>1968</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="899" spans="1:3">
@@ -16647,7 +16629,7 @@
         <v>922</v>
       </c>
       <c r="C899" t="s">
-        <v>1969</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="900" spans="1:3">
@@ -16658,7 +16640,7 @@
         <v>923</v>
       </c>
       <c r="C900" t="s">
-        <v>1970</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="901" spans="1:3">
@@ -16669,7 +16651,7 @@
         <v>924</v>
       </c>
       <c r="C901" t="s">
-        <v>1971</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="902" spans="1:3">
@@ -16680,7 +16662,7 @@
         <v>925</v>
       </c>
       <c r="C902" t="s">
-        <v>1972</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="903" spans="1:3">
@@ -16691,7 +16673,7 @@
         <v>926</v>
       </c>
       <c r="C903" t="s">
-        <v>1973</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="904" spans="1:3">
@@ -16702,7 +16684,7 @@
         <v>927</v>
       </c>
       <c r="C904" t="s">
-        <v>1974</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="905" spans="1:3">
@@ -16713,7 +16695,7 @@
         <v>928</v>
       </c>
       <c r="C905" t="s">
-        <v>1975</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="906" spans="1:3">
@@ -16724,7 +16706,7 @@
         <v>929</v>
       </c>
       <c r="C906" t="s">
-        <v>1976</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="907" spans="1:3">
@@ -16735,7 +16717,7 @@
         <v>930</v>
       </c>
       <c r="C907" t="s">
-        <v>1977</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="908" spans="1:3">
@@ -16746,7 +16728,7 @@
         <v>931</v>
       </c>
       <c r="C908" t="s">
-        <v>1978</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="909" spans="1:3">
@@ -16757,7 +16739,7 @@
         <v>932</v>
       </c>
       <c r="C909" t="s">
-        <v>1979</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="910" spans="1:3">
@@ -16768,7 +16750,7 @@
         <v>933</v>
       </c>
       <c r="C910" t="s">
-        <v>1980</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="911" spans="1:3">
@@ -16779,7 +16761,7 @@
         <v>934</v>
       </c>
       <c r="C911" t="s">
-        <v>1981</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="912" spans="1:3">
@@ -16790,7 +16772,7 @@
         <v>935</v>
       </c>
       <c r="C912" t="s">
-        <v>1982</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="913" spans="1:3">
@@ -16801,7 +16783,7 @@
         <v>936</v>
       </c>
       <c r="C913" t="s">
-        <v>1983</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="914" spans="1:3">
@@ -16812,7 +16794,7 @@
         <v>937</v>
       </c>
       <c r="C914" t="s">
-        <v>1984</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="915" spans="1:3">
@@ -16823,7 +16805,7 @@
         <v>938</v>
       </c>
       <c r="C915" t="s">
-        <v>1985</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="916" spans="1:3">
@@ -16834,7 +16816,7 @@
         <v>939</v>
       </c>
       <c r="C916" t="s">
-        <v>1986</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="917" spans="1:3">
@@ -16845,7 +16827,7 @@
         <v>940</v>
       </c>
       <c r="C917" t="s">
-        <v>1987</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="918" spans="1:3">
@@ -16856,7 +16838,7 @@
         <v>941</v>
       </c>
       <c r="C918" t="s">
-        <v>1988</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="919" spans="1:3">
@@ -16867,7 +16849,7 @@
         <v>942</v>
       </c>
       <c r="C919" t="s">
-        <v>1989</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="920" spans="1:3">
@@ -16878,7 +16860,7 @@
         <v>943</v>
       </c>
       <c r="C920" t="s">
-        <v>1990</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="921" spans="1:3">
@@ -16889,7 +16871,7 @@
         <v>944</v>
       </c>
       <c r="C921" t="s">
-        <v>1991</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="922" spans="1:3">
@@ -16900,7 +16882,7 @@
         <v>945</v>
       </c>
       <c r="C922" t="s">
-        <v>1992</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="923" spans="1:3">
@@ -16911,7 +16893,7 @@
         <v>946</v>
       </c>
       <c r="C923" t="s">
-        <v>1993</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="924" spans="1:3">
@@ -16922,7 +16904,7 @@
         <v>947</v>
       </c>
       <c r="C924" t="s">
-        <v>1994</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="925" spans="1:3">
@@ -16933,7 +16915,7 @@
         <v>948</v>
       </c>
       <c r="C925" t="s">
-        <v>1995</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="926" spans="1:3">
@@ -16944,7 +16926,7 @@
         <v>949</v>
       </c>
       <c r="C926" t="s">
-        <v>1996</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="927" spans="1:3">
@@ -16955,7 +16937,7 @@
         <v>950</v>
       </c>
       <c r="C927" t="s">
-        <v>1997</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="928" spans="1:3">
@@ -16966,7 +16948,7 @@
         <v>951</v>
       </c>
       <c r="C928" t="s">
-        <v>1998</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="929" spans="1:3">
@@ -16977,7 +16959,7 @@
         <v>952</v>
       </c>
       <c r="C929" t="s">
-        <v>1999</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="930" spans="1:3">
@@ -16988,7 +16970,7 @@
         <v>953</v>
       </c>
       <c r="C930" t="s">
-        <v>2000</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="931" spans="1:3">
@@ -16999,7 +16981,7 @@
         <v>954</v>
       </c>
       <c r="C931" t="s">
-        <v>2001</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="932" spans="1:3">
@@ -17010,7 +16992,7 @@
         <v>955</v>
       </c>
       <c r="C932" t="s">
-        <v>2002</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="933" spans="1:3">
@@ -17021,7 +17003,7 @@
         <v>956</v>
       </c>
       <c r="C933" t="s">
-        <v>2003</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="934" spans="1:3">
@@ -17032,7 +17014,7 @@
         <v>957</v>
       </c>
       <c r="C934" t="s">
-        <v>2004</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="935" spans="1:3">
@@ -17043,7 +17025,7 @@
         <v>958</v>
       </c>
       <c r="C935" t="s">
-        <v>2005</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="936" spans="1:3">
@@ -17054,7 +17036,7 @@
         <v>959</v>
       </c>
       <c r="C936" t="s">
-        <v>2006</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="937" spans="1:3">
@@ -17065,7 +17047,7 @@
         <v>960</v>
       </c>
       <c r="C937" t="s">
-        <v>2007</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="938" spans="1:3">
@@ -17076,7 +17058,7 @@
         <v>961</v>
       </c>
       <c r="C938" t="s">
-        <v>2008</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="939" spans="1:3">
@@ -17087,7 +17069,7 @@
         <v>962</v>
       </c>
       <c r="C939" t="s">
-        <v>2009</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="940" spans="1:3">
@@ -17098,7 +17080,7 @@
         <v>963</v>
       </c>
       <c r="C940" t="s">
-        <v>2010</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="941" spans="1:3">
@@ -17109,7 +17091,7 @@
         <v>964</v>
       </c>
       <c r="C941" t="s">
-        <v>2011</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="942" spans="1:3">
@@ -17120,7 +17102,7 @@
         <v>965</v>
       </c>
       <c r="C942" t="s">
-        <v>2012</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="943" spans="1:3">
@@ -17131,7 +17113,7 @@
         <v>966</v>
       </c>
       <c r="C943" t="s">
-        <v>2013</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="944" spans="1:3">
@@ -17142,7 +17124,7 @@
         <v>967</v>
       </c>
       <c r="C944" t="s">
-        <v>2014</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="945" spans="1:3">
@@ -17153,7 +17135,7 @@
         <v>968</v>
       </c>
       <c r="C945" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="946" spans="1:3">
@@ -17164,7 +17146,7 @@
         <v>969</v>
       </c>
       <c r="C946" t="s">
-        <v>2016</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="947" spans="1:3">
@@ -17175,7 +17157,7 @@
         <v>970</v>
       </c>
       <c r="C947" t="s">
-        <v>2017</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="948" spans="1:3">
@@ -17186,7 +17168,7 @@
         <v>971</v>
       </c>
       <c r="C948" t="s">
-        <v>2018</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="949" spans="1:3">
@@ -17197,7 +17179,7 @@
         <v>972</v>
       </c>
       <c r="C949" t="s">
-        <v>2019</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="950" spans="1:3">
@@ -17208,7 +17190,7 @@
         <v>973</v>
       </c>
       <c r="C950" t="s">
-        <v>2020</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="951" spans="1:3">
@@ -17219,7 +17201,7 @@
         <v>974</v>
       </c>
       <c r="C951" t="s">
-        <v>2021</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="952" spans="1:3">
@@ -17230,7 +17212,7 @@
         <v>975</v>
       </c>
       <c r="C952" t="s">
-        <v>2022</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="953" spans="1:3">
@@ -17241,7 +17223,7 @@
         <v>976</v>
       </c>
       <c r="C953" t="s">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="954" spans="1:3">
@@ -17252,7 +17234,7 @@
         <v>977</v>
       </c>
       <c r="C954" t="s">
-        <v>2024</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="955" spans="1:3">
@@ -17263,7 +17245,7 @@
         <v>978</v>
       </c>
       <c r="C955" t="s">
-        <v>2025</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="956" spans="1:3">
@@ -17274,7 +17256,7 @@
         <v>979</v>
       </c>
       <c r="C956" t="s">
-        <v>2026</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="957" spans="1:3">
@@ -17285,7 +17267,7 @@
         <v>980</v>
       </c>
       <c r="C957" t="s">
-        <v>2027</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="958" spans="1:3">
@@ -17296,7 +17278,7 @@
         <v>981</v>
       </c>
       <c r="C958" t="s">
-        <v>2028</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="959" spans="1:3">
@@ -17307,40 +17289,40 @@
         <v>982</v>
       </c>
       <c r="C959" t="s">
-        <v>2029</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="960" spans="1:3">
       <c r="A960" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B960" t="s">
         <v>983</v>
       </c>
       <c r="C960" t="s">
-        <v>2030</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="961" spans="1:3">
       <c r="A961" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B961" t="s">
         <v>984</v>
       </c>
       <c r="C961" t="s">
-        <v>2031</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="962" spans="1:3">
       <c r="A962" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B962" t="s">
         <v>985</v>
       </c>
       <c r="C962" t="s">
-        <v>2032</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="963" spans="1:3">
@@ -17351,7 +17333,7 @@
         <v>986</v>
       </c>
       <c r="C963" t="s">
-        <v>2033</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="964" spans="1:3">
@@ -17362,7 +17344,7 @@
         <v>987</v>
       </c>
       <c r="C964" t="s">
-        <v>2034</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="965" spans="1:3">
@@ -17373,7 +17355,7 @@
         <v>988</v>
       </c>
       <c r="C965" t="s">
-        <v>2035</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="966" spans="1:3">
@@ -17384,7 +17366,7 @@
         <v>989</v>
       </c>
       <c r="C966" t="s">
-        <v>2036</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="967" spans="1:3">
@@ -17395,7 +17377,7 @@
         <v>990</v>
       </c>
       <c r="C967" t="s">
-        <v>2037</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="968" spans="1:3">
@@ -17406,7 +17388,7 @@
         <v>991</v>
       </c>
       <c r="C968" t="s">
-        <v>2038</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="969" spans="1:3">
@@ -17417,7 +17399,7 @@
         <v>992</v>
       </c>
       <c r="C969" t="s">
-        <v>2039</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="970" spans="1:3">
@@ -17428,7 +17410,7 @@
         <v>993</v>
       </c>
       <c r="C970" t="s">
-        <v>2040</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="971" spans="1:3">
@@ -17439,7 +17421,7 @@
         <v>994</v>
       </c>
       <c r="C971" t="s">
-        <v>2041</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="972" spans="1:3">
@@ -17450,7 +17432,7 @@
         <v>995</v>
       </c>
       <c r="C972" t="s">
-        <v>2042</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="973" spans="1:3">
@@ -17461,7 +17443,7 @@
         <v>996</v>
       </c>
       <c r="C973" t="s">
-        <v>2043</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="974" spans="1:3">
@@ -17472,7 +17454,7 @@
         <v>997</v>
       </c>
       <c r="C974" t="s">
-        <v>2044</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="975" spans="1:3">
@@ -17483,7 +17465,7 @@
         <v>998</v>
       </c>
       <c r="C975" t="s">
-        <v>2045</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="976" spans="1:3">
@@ -17494,7 +17476,7 @@
         <v>999</v>
       </c>
       <c r="C976" t="s">
-        <v>2046</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="977" spans="1:3">
@@ -17505,7 +17487,7 @@
         <v>1000</v>
       </c>
       <c r="C977" t="s">
-        <v>2047</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="978" spans="1:3">
@@ -17516,7 +17498,7 @@
         <v>1001</v>
       </c>
       <c r="C978" t="s">
-        <v>2048</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="979" spans="1:3">
@@ -17527,7 +17509,7 @@
         <v>1002</v>
       </c>
       <c r="C979" t="s">
-        <v>2049</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="980" spans="1:3">
@@ -17538,7 +17520,7 @@
         <v>1003</v>
       </c>
       <c r="C980" t="s">
-        <v>2050</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="981" spans="1:3">
@@ -17549,7 +17531,7 @@
         <v>1004</v>
       </c>
       <c r="C981" t="s">
-        <v>2051</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="982" spans="1:3">
@@ -17560,7 +17542,7 @@
         <v>1005</v>
       </c>
       <c r="C982" t="s">
-        <v>2052</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="983" spans="1:3">
@@ -17571,7 +17553,7 @@
         <v>1006</v>
       </c>
       <c r="C983" t="s">
-        <v>2053</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="984" spans="1:3">
@@ -17582,7 +17564,7 @@
         <v>1007</v>
       </c>
       <c r="C984" t="s">
-        <v>2054</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="985" spans="1:3">
@@ -17593,7 +17575,7 @@
         <v>1008</v>
       </c>
       <c r="C985" t="s">
-        <v>2055</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="986" spans="1:3">
@@ -17604,7 +17586,7 @@
         <v>1009</v>
       </c>
       <c r="C986" t="s">
-        <v>2056</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="987" spans="1:3">
@@ -17615,7 +17597,7 @@
         <v>1010</v>
       </c>
       <c r="C987" t="s">
-        <v>2057</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="988" spans="1:3">
@@ -17626,7 +17608,7 @@
         <v>1011</v>
       </c>
       <c r="C988" t="s">
-        <v>2058</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="989" spans="1:3">
@@ -17637,7 +17619,7 @@
         <v>1012</v>
       </c>
       <c r="C989" t="s">
-        <v>2059</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="990" spans="1:3">
@@ -17648,7 +17630,7 @@
         <v>1013</v>
       </c>
       <c r="C990" t="s">
-        <v>2060</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="991" spans="1:3">
@@ -17659,7 +17641,7 @@
         <v>1014</v>
       </c>
       <c r="C991" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="992" spans="1:3">
@@ -17670,7 +17652,7 @@
         <v>1015</v>
       </c>
       <c r="C992" t="s">
-        <v>2062</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="993" spans="1:3">
@@ -17681,7 +17663,7 @@
         <v>1016</v>
       </c>
       <c r="C993" t="s">
-        <v>2063</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="994" spans="1:3">
@@ -17692,7 +17674,7 @@
         <v>1017</v>
       </c>
       <c r="C994" t="s">
-        <v>2064</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="995" spans="1:3">
@@ -17703,7 +17685,7 @@
         <v>1018</v>
       </c>
       <c r="C995" t="s">
-        <v>2065</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="996" spans="1:3">
@@ -17714,7 +17696,7 @@
         <v>1019</v>
       </c>
       <c r="C996" t="s">
-        <v>2066</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="997" spans="1:3">
@@ -17725,7 +17707,7 @@
         <v>1020</v>
       </c>
       <c r="C997" t="s">
-        <v>2067</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="998" spans="1:3">
@@ -17736,7 +17718,7 @@
         <v>1021</v>
       </c>
       <c r="C998" t="s">
-        <v>2068</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="999" spans="1:3">
@@ -17747,7 +17729,7 @@
         <v>1022</v>
       </c>
       <c r="C999" t="s">
-        <v>2069</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="1000" spans="1:3">
@@ -17758,7 +17740,7 @@
         <v>1023</v>
       </c>
       <c r="C1000" t="s">
-        <v>2070</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="1001" spans="1:3">
@@ -17769,7 +17751,7 @@
         <v>1024</v>
       </c>
       <c r="C1001" t="s">
-        <v>2071</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1002" spans="1:3">
@@ -17780,7 +17762,7 @@
         <v>1025</v>
       </c>
       <c r="C1002" t="s">
-        <v>2065</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="1003" spans="1:3">
@@ -17791,7 +17773,7 @@
         <v>1026</v>
       </c>
       <c r="C1003" t="s">
-        <v>2072</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="1004" spans="1:3">
@@ -17802,7 +17784,7 @@
         <v>1027</v>
       </c>
       <c r="C1004" t="s">
-        <v>2073</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="1005" spans="1:3">
@@ -17813,7 +17795,7 @@
         <v>1028</v>
       </c>
       <c r="C1005" t="s">
-        <v>2074</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="1006" spans="1:3">
@@ -17824,7 +17806,7 @@
         <v>1029</v>
       </c>
       <c r="C1006" t="s">
-        <v>2075</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1007" spans="1:3">
@@ -17835,7 +17817,7 @@
         <v>1030</v>
       </c>
       <c r="C1007" t="s">
-        <v>2076</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="1008" spans="1:3">
@@ -17846,7 +17828,7 @@
         <v>1031</v>
       </c>
       <c r="C1008" t="s">
-        <v>2077</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="1009" spans="1:3">
@@ -17857,7 +17839,7 @@
         <v>1032</v>
       </c>
       <c r="C1009" t="s">
-        <v>2078</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="1010" spans="1:3">
@@ -17868,7 +17850,7 @@
         <v>1033</v>
       </c>
       <c r="C1010" t="s">
-        <v>2079</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="1011" spans="1:3">
@@ -17879,7 +17861,7 @@
         <v>1034</v>
       </c>
       <c r="C1011" t="s">
-        <v>2080</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="1012" spans="1:3">
@@ -17890,7 +17872,7 @@
         <v>1035</v>
       </c>
       <c r="C1012" t="s">
-        <v>2081</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="1013" spans="1:3">
@@ -17901,7 +17883,7 @@
         <v>1036</v>
       </c>
       <c r="C1013" t="s">
-        <v>2082</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="1014" spans="1:3">
@@ -17912,7 +17894,7 @@
         <v>1037</v>
       </c>
       <c r="C1014" t="s">
-        <v>2083</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="1015" spans="1:3">
@@ -17923,7 +17905,7 @@
         <v>1038</v>
       </c>
       <c r="C1015" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="1016" spans="1:3">
@@ -17934,7 +17916,7 @@
         <v>1039</v>
       </c>
       <c r="C1016" t="s">
-        <v>2085</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="1017" spans="1:3">
@@ -17945,7 +17927,7 @@
         <v>1040</v>
       </c>
       <c r="C1017" t="s">
-        <v>2086</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="1018" spans="1:3">
@@ -17956,7 +17938,7 @@
         <v>1041</v>
       </c>
       <c r="C1018" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="1019" spans="1:3">
@@ -17967,7 +17949,7 @@
         <v>1042</v>
       </c>
       <c r="C1019" t="s">
-        <v>2088</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="1020" spans="1:3">
@@ -17978,7 +17960,7 @@
         <v>1043</v>
       </c>
       <c r="C1020" t="s">
-        <v>2089</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="1021" spans="1:3">
@@ -17989,7 +17971,7 @@
         <v>1044</v>
       </c>
       <c r="C1021" t="s">
-        <v>2090</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="1022" spans="1:3">
@@ -18000,7 +17982,7 @@
         <v>1045</v>
       </c>
       <c r="C1022" t="s">
-        <v>2091</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="1023" spans="1:3">
@@ -18011,7 +17993,7 @@
         <v>1046</v>
       </c>
       <c r="C1023" t="s">
-        <v>2066</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="1024" spans="1:3">
@@ -18022,7 +18004,7 @@
         <v>1047</v>
       </c>
       <c r="C1024" t="s">
-        <v>2092</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="1025" spans="1:3">
@@ -18033,7 +18015,7 @@
         <v>1048</v>
       </c>
       <c r="C1025" t="s">
-        <v>2093</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="1026" spans="1:3">
@@ -18044,7 +18026,7 @@
         <v>1049</v>
       </c>
       <c r="C1026" t="s">
-        <v>2094</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="1027" spans="1:3">
@@ -18055,7 +18037,7 @@
         <v>1050</v>
       </c>
       <c r="C1027" t="s">
-        <v>2047</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="1028" spans="1:3">
@@ -18066,7 +18048,7 @@
         <v>1051</v>
       </c>
       <c r="C1028" t="s">
-        <v>2095</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="1029" spans="1:3">
@@ -18077,7 +18059,7 @@
         <v>1052</v>
       </c>
       <c r="C1029" t="s">
-        <v>2096</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="1030" spans="1:3">
@@ -18088,40 +18070,40 @@
         <v>1053</v>
       </c>
       <c r="C1030" t="s">
-        <v>2097</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="1031" spans="1:3">
       <c r="A1031" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1031" t="s">
         <v>1054</v>
       </c>
       <c r="C1031" t="s">
-        <v>2098</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="1032" spans="1:3">
       <c r="A1032" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1032" t="s">
         <v>1055</v>
       </c>
       <c r="C1032" t="s">
-        <v>2099</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="1033" spans="1:3">
       <c r="A1033" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1033" t="s">
         <v>1056</v>
       </c>
       <c r="C1033" t="s">
-        <v>2100</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="1034" spans="1:3">
@@ -18132,7 +18114,7 @@
         <v>1057</v>
       </c>
       <c r="C1034" t="s">
-        <v>2101</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="1035" spans="1:3">
@@ -18143,7 +18125,7 @@
         <v>1058</v>
       </c>
       <c r="C1035" t="s">
-        <v>2102</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="1036" spans="1:3">
@@ -18154,7 +18136,7 @@
         <v>1059</v>
       </c>
       <c r="C1036" t="s">
-        <v>2103</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="1037" spans="1:3">
@@ -18165,7 +18147,7 @@
         <v>1060</v>
       </c>
       <c r="C1037" t="s">
-        <v>2104</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="1038" spans="1:3">
@@ -18176,7 +18158,7 @@
         <v>1061</v>
       </c>
       <c r="C1038" t="s">
-        <v>2105</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="1039" spans="1:3">
@@ -18187,7 +18169,7 @@
         <v>1062</v>
       </c>
       <c r="C1039" t="s">
-        <v>2106</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="1040" spans="1:3">
@@ -18198,7 +18180,7 @@
         <v>1063</v>
       </c>
       <c r="C1040" t="s">
-        <v>2107</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="1041" spans="1:3">
@@ -18209,7 +18191,7 @@
         <v>1064</v>
       </c>
       <c r="C1041" t="s">
-        <v>2108</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="1042" spans="1:3">
@@ -18220,7 +18202,7 @@
         <v>1065</v>
       </c>
       <c r="C1042" t="s">
-        <v>2109</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="1043" spans="1:3">
@@ -18231,7 +18213,7 @@
         <v>1066</v>
       </c>
       <c r="C1043" t="s">
-        <v>2110</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="1044" spans="1:3">
@@ -18242,7 +18224,7 @@
         <v>1067</v>
       </c>
       <c r="C1044" t="s">
-        <v>2111</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="1045" spans="1:3">
@@ -18253,7 +18235,7 @@
         <v>1068</v>
       </c>
       <c r="C1045" t="s">
-        <v>2112</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="1046" spans="1:3">
@@ -18264,7 +18246,7 @@
         <v>1069</v>
       </c>
       <c r="C1046" t="s">
-        <v>2113</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="1047" spans="1:3">
@@ -18275,7 +18257,7 @@
         <v>1070</v>
       </c>
       <c r="C1047" t="s">
-        <v>2114</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="1048" spans="1:3">
@@ -18286,7 +18268,7 @@
         <v>1071</v>
       </c>
       <c r="C1048" t="s">
-        <v>2115</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="1049" spans="1:3">
@@ -18297,7 +18279,7 @@
         <v>1072</v>
       </c>
       <c r="C1049" t="s">
-        <v>2116</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="1050" spans="1:3">
@@ -18308,7 +18290,7 @@
         <v>1073</v>
       </c>
       <c r="C1050" t="s">
-        <v>2117</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="1051" spans="1:3">
@@ -18319,7 +18301,7 @@
         <v>1074</v>
       </c>
       <c r="C1051" t="s">
-        <v>2118</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="1052" spans="1:3">
@@ -18330,7 +18312,7 @@
         <v>1075</v>
       </c>
       <c r="C1052" t="s">
-        <v>2119</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="1053" spans="1:3">
@@ -18341,7 +18323,7 @@
         <v>1076</v>
       </c>
       <c r="C1053" t="s">
-        <v>2120</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="1054" spans="1:3">
@@ -18352,7 +18334,7 @@
         <v>1077</v>
       </c>
       <c r="C1054" t="s">
-        <v>2121</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="1055" spans="1:3">
@@ -18363,7 +18345,7 @@
         <v>1078</v>
       </c>
       <c r="C1055" t="s">
-        <v>2122</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="1056" spans="1:3">
@@ -18374,7 +18356,7 @@
         <v>1079</v>
       </c>
       <c r="C1056" t="s">
-        <v>2123</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="1057" spans="1:3">
@@ -18385,51 +18367,18 @@
         <v>1080</v>
       </c>
       <c r="C1057" t="s">
-        <v>2124</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="1058" spans="1:3">
       <c r="A1058" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1058" t="s">
         <v>1081</v>
       </c>
       <c r="C1058" t="s">
-        <v>2125</v>
-      </c>
-    </row>
-    <row r="1059" spans="1:3">
-      <c r="A1059" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1059" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C1059" t="s">
-        <v>2126</v>
-      </c>
-    </row>
-    <row r="1060" spans="1:3">
-      <c r="A1060" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1060" t="s">
-        <v>1083</v>
-      </c>
-      <c r="C1060" t="s">
-        <v>2127</v>
-      </c>
-    </row>
-    <row r="1061" spans="1:3">
-      <c r="A1061" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1061" t="s">
-        <v>1084</v>
-      </c>
-      <c r="C1061" t="s">
-        <v>2128</v>
+        <v>2122</v>
       </c>
     </row>
   </sheetData>

--- a/faltantes_por_estados.xlsx
+++ b/faltantes_por_estados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3174" uniqueCount="2123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3171" uniqueCount="2121">
   <si>
     <t>entidad</t>
   </si>
@@ -1672,9 +1672,6 @@
     <t>HGIMB000530</t>
   </si>
   <si>
-    <t>HGIMB002292</t>
-  </si>
-  <si>
     <t>HGIMB002316</t>
   </si>
   <si>
@@ -4811,9 +4808,6 @@
   </si>
   <si>
     <t>PROGRESO EL DE ATOTONILCO DE TULA</t>
-  </si>
-  <si>
-    <t>PIRACANTOS</t>
   </si>
   <si>
     <t>AQUILES SERDÁN</t>
@@ -6740,7 +6734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1058"/>
+  <dimension ref="A1:C1057"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6762,7 +6756,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6773,7 +6767,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6784,7 +6778,7 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6795,7 +6789,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6806,7 +6800,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6817,7 +6811,7 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6828,7 +6822,7 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6839,7 +6833,7 @@
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6850,7 +6844,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6861,7 +6855,7 @@
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6872,7 +6866,7 @@
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6883,7 +6877,7 @@
         <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6894,7 +6888,7 @@
         <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6905,7 +6899,7 @@
         <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -6916,7 +6910,7 @@
         <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6938,7 +6932,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6949,7 +6943,7 @@
         <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6960,7 +6954,7 @@
         <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6971,7 +6965,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6982,7 +6976,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6993,7 +6987,7 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -7004,7 +6998,7 @@
         <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -7015,7 +7009,7 @@
         <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -7026,7 +7020,7 @@
         <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -7048,7 +7042,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -7070,7 +7064,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -7081,7 +7075,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -7092,7 +7086,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -7103,7 +7097,7 @@
         <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -7114,7 +7108,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -7125,7 +7119,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -7136,7 +7130,7 @@
         <v>59</v>
       </c>
       <c r="C36" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -7147,7 +7141,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -7158,7 +7152,7 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -7169,7 +7163,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -7180,7 +7174,7 @@
         <v>63</v>
       </c>
       <c r="C40" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -7191,7 +7185,7 @@
         <v>64</v>
       </c>
       <c r="C41" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -7202,7 +7196,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -7213,7 +7207,7 @@
         <v>66</v>
       </c>
       <c r="C43" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -7224,7 +7218,7 @@
         <v>67</v>
       </c>
       <c r="C44" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -7235,7 +7229,7 @@
         <v>68</v>
       </c>
       <c r="C45" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -7246,7 +7240,7 @@
         <v>69</v>
       </c>
       <c r="C46" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -7257,7 +7251,7 @@
         <v>70</v>
       </c>
       <c r="C47" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -7268,7 +7262,7 @@
         <v>71</v>
       </c>
       <c r="C48" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -7279,7 +7273,7 @@
         <v>72</v>
       </c>
       <c r="C49" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -7290,7 +7284,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -7301,7 +7295,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -7312,7 +7306,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -7323,7 +7317,7 @@
         <v>76</v>
       </c>
       <c r="C53" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -7334,7 +7328,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -7345,7 +7339,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -7356,7 +7350,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -7367,7 +7361,7 @@
         <v>80</v>
       </c>
       <c r="C57" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -7378,7 +7372,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -7389,7 +7383,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -7411,7 +7405,7 @@
         <v>84</v>
       </c>
       <c r="C61" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -7422,7 +7416,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -7433,7 +7427,7 @@
         <v>86</v>
       </c>
       <c r="C63" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -7444,7 +7438,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -7455,7 +7449,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -7466,7 +7460,7 @@
         <v>89</v>
       </c>
       <c r="C66" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -7477,7 +7471,7 @@
         <v>90</v>
       </c>
       <c r="C67" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -7488,7 +7482,7 @@
         <v>91</v>
       </c>
       <c r="C68" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -7499,7 +7493,7 @@
         <v>92</v>
       </c>
       <c r="C69" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -7510,7 +7504,7 @@
         <v>93</v>
       </c>
       <c r="C70" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -7521,7 +7515,7 @@
         <v>94</v>
       </c>
       <c r="C71" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -7532,7 +7526,7 @@
         <v>95</v>
       </c>
       <c r="C72" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -7543,7 +7537,7 @@
         <v>96</v>
       </c>
       <c r="C73" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -7554,7 +7548,7 @@
         <v>97</v>
       </c>
       <c r="C74" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -7565,7 +7559,7 @@
         <v>98</v>
       </c>
       <c r="C75" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -7576,7 +7570,7 @@
         <v>99</v>
       </c>
       <c r="C76" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -7587,7 +7581,7 @@
         <v>100</v>
       </c>
       <c r="C77" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -7598,7 +7592,7 @@
         <v>101</v>
       </c>
       <c r="C78" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -7609,7 +7603,7 @@
         <v>102</v>
       </c>
       <c r="C79" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -7620,7 +7614,7 @@
         <v>103</v>
       </c>
       <c r="C80" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -7631,7 +7625,7 @@
         <v>104</v>
       </c>
       <c r="C81" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -7642,7 +7636,7 @@
         <v>105</v>
       </c>
       <c r="C82" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -7653,7 +7647,7 @@
         <v>106</v>
       </c>
       <c r="C83" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -7664,7 +7658,7 @@
         <v>107</v>
       </c>
       <c r="C84" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -7675,7 +7669,7 @@
         <v>108</v>
       </c>
       <c r="C85" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -7686,7 +7680,7 @@
         <v>109</v>
       </c>
       <c r="C86" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -7697,7 +7691,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -7708,7 +7702,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -7719,7 +7713,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -7730,7 +7724,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -7741,7 +7735,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -7752,7 +7746,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -7763,7 +7757,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -7774,7 +7768,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -7785,7 +7779,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -7796,7 +7790,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -7807,7 +7801,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -7818,7 +7812,7 @@
         <v>121</v>
       </c>
       <c r="C98" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -7829,7 +7823,7 @@
         <v>122</v>
       </c>
       <c r="C99" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -7840,7 +7834,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -7851,7 +7845,7 @@
         <v>124</v>
       </c>
       <c r="C101" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -7862,7 +7856,7 @@
         <v>125</v>
       </c>
       <c r="C102" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -7873,7 +7867,7 @@
         <v>126</v>
       </c>
       <c r="C103" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -7884,7 +7878,7 @@
         <v>127</v>
       </c>
       <c r="C104" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -7895,7 +7889,7 @@
         <v>128</v>
       </c>
       <c r="C105" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -7906,7 +7900,7 @@
         <v>129</v>
       </c>
       <c r="C106" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -7917,7 +7911,7 @@
         <v>130</v>
       </c>
       <c r="C107" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -7928,7 +7922,7 @@
         <v>131</v>
       </c>
       <c r="C108" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -7939,7 +7933,7 @@
         <v>132</v>
       </c>
       <c r="C109" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -7950,7 +7944,7 @@
         <v>133</v>
       </c>
       <c r="C110" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -7961,7 +7955,7 @@
         <v>134</v>
       </c>
       <c r="C111" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -7972,7 +7966,7 @@
         <v>135</v>
       </c>
       <c r="C112" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -7983,7 +7977,7 @@
         <v>136</v>
       </c>
       <c r="C113" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -7994,7 +7988,7 @@
         <v>137</v>
       </c>
       <c r="C114" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -8005,7 +7999,7 @@
         <v>138</v>
       </c>
       <c r="C115" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -8016,7 +8010,7 @@
         <v>139</v>
       </c>
       <c r="C116" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -8027,7 +8021,7 @@
         <v>140</v>
       </c>
       <c r="C117" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -8038,7 +8032,7 @@
         <v>141</v>
       </c>
       <c r="C118" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -8049,7 +8043,7 @@
         <v>142</v>
       </c>
       <c r="C119" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -8060,7 +8054,7 @@
         <v>143</v>
       </c>
       <c r="C120" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -8071,7 +8065,7 @@
         <v>144</v>
       </c>
       <c r="C121" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -8082,7 +8076,7 @@
         <v>145</v>
       </c>
       <c r="C122" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -8093,7 +8087,7 @@
         <v>146</v>
       </c>
       <c r="C123" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -8104,7 +8098,7 @@
         <v>147</v>
       </c>
       <c r="C124" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -8115,7 +8109,7 @@
         <v>148</v>
       </c>
       <c r="C125" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -8126,7 +8120,7 @@
         <v>149</v>
       </c>
       <c r="C126" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -8137,7 +8131,7 @@
         <v>150</v>
       </c>
       <c r="C127" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -8148,7 +8142,7 @@
         <v>151</v>
       </c>
       <c r="C128" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -8159,7 +8153,7 @@
         <v>152</v>
       </c>
       <c r="C129" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -8170,7 +8164,7 @@
         <v>153</v>
       </c>
       <c r="C130" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -8181,7 +8175,7 @@
         <v>154</v>
       </c>
       <c r="C131" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -8192,7 +8186,7 @@
         <v>155</v>
       </c>
       <c r="C132" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -8203,7 +8197,7 @@
         <v>156</v>
       </c>
       <c r="C133" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -8214,7 +8208,7 @@
         <v>157</v>
       </c>
       <c r="C134" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -8225,7 +8219,7 @@
         <v>158</v>
       </c>
       <c r="C135" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -8236,7 +8230,7 @@
         <v>159</v>
       </c>
       <c r="C136" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -8247,7 +8241,7 @@
         <v>160</v>
       </c>
       <c r="C137" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -8258,7 +8252,7 @@
         <v>161</v>
       </c>
       <c r="C138" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -8269,7 +8263,7 @@
         <v>162</v>
       </c>
       <c r="C139" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -8280,7 +8274,7 @@
         <v>163</v>
       </c>
       <c r="C140" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -8291,7 +8285,7 @@
         <v>164</v>
       </c>
       <c r="C141" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -8302,7 +8296,7 @@
         <v>165</v>
       </c>
       <c r="C142" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -8313,7 +8307,7 @@
         <v>166</v>
       </c>
       <c r="C143" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -8324,7 +8318,7 @@
         <v>167</v>
       </c>
       <c r="C144" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -8335,7 +8329,7 @@
         <v>168</v>
       </c>
       <c r="C145" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -8346,7 +8340,7 @@
         <v>169</v>
       </c>
       <c r="C146" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -8357,7 +8351,7 @@
         <v>170</v>
       </c>
       <c r="C147" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -8368,7 +8362,7 @@
         <v>171</v>
       </c>
       <c r="C148" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -8379,7 +8373,7 @@
         <v>172</v>
       </c>
       <c r="C149" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -8390,7 +8384,7 @@
         <v>173</v>
       </c>
       <c r="C150" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -8401,7 +8395,7 @@
         <v>174</v>
       </c>
       <c r="C151" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -8412,7 +8406,7 @@
         <v>175</v>
       </c>
       <c r="C152" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -8423,7 +8417,7 @@
         <v>176</v>
       </c>
       <c r="C153" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -8434,7 +8428,7 @@
         <v>177</v>
       </c>
       <c r="C154" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -8445,7 +8439,7 @@
         <v>178</v>
       </c>
       <c r="C155" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -8456,7 +8450,7 @@
         <v>179</v>
       </c>
       <c r="C156" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -8467,7 +8461,7 @@
         <v>180</v>
       </c>
       <c r="C157" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -8478,7 +8472,7 @@
         <v>181</v>
       </c>
       <c r="C158" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -8489,7 +8483,7 @@
         <v>182</v>
       </c>
       <c r="C159" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -8500,7 +8494,7 @@
         <v>183</v>
       </c>
       <c r="C160" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -8511,7 +8505,7 @@
         <v>184</v>
       </c>
       <c r="C161" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -8522,7 +8516,7 @@
         <v>185</v>
       </c>
       <c r="C162" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -8533,7 +8527,7 @@
         <v>186</v>
       </c>
       <c r="C163" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -8544,7 +8538,7 @@
         <v>187</v>
       </c>
       <c r="C164" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -8555,7 +8549,7 @@
         <v>188</v>
       </c>
       <c r="C165" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -8566,7 +8560,7 @@
         <v>189</v>
       </c>
       <c r="C166" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -8577,7 +8571,7 @@
         <v>190</v>
       </c>
       <c r="C167" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -8588,7 +8582,7 @@
         <v>191</v>
       </c>
       <c r="C168" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -8599,7 +8593,7 @@
         <v>192</v>
       </c>
       <c r="C169" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -8610,7 +8604,7 @@
         <v>193</v>
       </c>
       <c r="C170" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -8621,7 +8615,7 @@
         <v>194</v>
       </c>
       <c r="C171" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -8632,7 +8626,7 @@
         <v>195</v>
       </c>
       <c r="C172" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -8643,7 +8637,7 @@
         <v>196</v>
       </c>
       <c r="C173" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -8654,7 +8648,7 @@
         <v>197</v>
       </c>
       <c r="C174" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -8665,7 +8659,7 @@
         <v>198</v>
       </c>
       <c r="C175" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -8676,7 +8670,7 @@
         <v>199</v>
       </c>
       <c r="C176" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -8687,7 +8681,7 @@
         <v>200</v>
       </c>
       <c r="C177" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -8698,7 +8692,7 @@
         <v>201</v>
       </c>
       <c r="C178" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -8709,7 +8703,7 @@
         <v>202</v>
       </c>
       <c r="C179" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -8720,7 +8714,7 @@
         <v>203</v>
       </c>
       <c r="C180" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -8731,7 +8725,7 @@
         <v>204</v>
       </c>
       <c r="C181" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -8742,7 +8736,7 @@
         <v>205</v>
       </c>
       <c r="C182" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -8753,7 +8747,7 @@
         <v>206</v>
       </c>
       <c r="C183" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -8764,7 +8758,7 @@
         <v>207</v>
       </c>
       <c r="C184" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -8775,7 +8769,7 @@
         <v>208</v>
       </c>
       <c r="C185" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -8786,7 +8780,7 @@
         <v>209</v>
       </c>
       <c r="C186" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -8797,7 +8791,7 @@
         <v>210</v>
       </c>
       <c r="C187" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -8808,7 +8802,7 @@
         <v>211</v>
       </c>
       <c r="C188" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -8819,7 +8813,7 @@
         <v>212</v>
       </c>
       <c r="C189" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -8830,7 +8824,7 @@
         <v>213</v>
       </c>
       <c r="C190" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -8841,7 +8835,7 @@
         <v>214</v>
       </c>
       <c r="C191" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -8852,7 +8846,7 @@
         <v>215</v>
       </c>
       <c r="C192" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -8863,7 +8857,7 @@
         <v>216</v>
       </c>
       <c r="C193" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -8874,7 +8868,7 @@
         <v>217</v>
       </c>
       <c r="C194" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -8885,7 +8879,7 @@
         <v>218</v>
       </c>
       <c r="C195" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -8896,7 +8890,7 @@
         <v>219</v>
       </c>
       <c r="C196" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -8907,7 +8901,7 @@
         <v>220</v>
       </c>
       <c r="C197" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -8918,7 +8912,7 @@
         <v>221</v>
       </c>
       <c r="C198" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -8929,7 +8923,7 @@
         <v>222</v>
       </c>
       <c r="C199" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -8940,7 +8934,7 @@
         <v>223</v>
       </c>
       <c r="C200" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -8951,7 +8945,7 @@
         <v>224</v>
       </c>
       <c r="C201" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -8962,7 +8956,7 @@
         <v>225</v>
       </c>
       <c r="C202" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -8973,7 +8967,7 @@
         <v>226</v>
       </c>
       <c r="C203" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -8984,7 +8978,7 @@
         <v>227</v>
       </c>
       <c r="C204" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -8995,7 +8989,7 @@
         <v>228</v>
       </c>
       <c r="C205" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -9006,7 +9000,7 @@
         <v>229</v>
       </c>
       <c r="C206" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -9017,7 +9011,7 @@
         <v>230</v>
       </c>
       <c r="C207" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -9028,7 +9022,7 @@
         <v>231</v>
       </c>
       <c r="C208" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -9039,7 +9033,7 @@
         <v>232</v>
       </c>
       <c r="C209" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -9050,7 +9044,7 @@
         <v>233</v>
       </c>
       <c r="C210" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -9061,7 +9055,7 @@
         <v>234</v>
       </c>
       <c r="C211" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -9072,7 +9066,7 @@
         <v>235</v>
       </c>
       <c r="C212" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -9083,7 +9077,7 @@
         <v>236</v>
       </c>
       <c r="C213" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -9094,7 +9088,7 @@
         <v>237</v>
       </c>
       <c r="C214" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -9105,7 +9099,7 @@
         <v>238</v>
       </c>
       <c r="C215" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -9116,7 +9110,7 @@
         <v>239</v>
       </c>
       <c r="C216" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -9127,7 +9121,7 @@
         <v>240</v>
       </c>
       <c r="C217" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -9138,7 +9132,7 @@
         <v>241</v>
       </c>
       <c r="C218" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -9149,7 +9143,7 @@
         <v>242</v>
       </c>
       <c r="C219" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -9160,7 +9154,7 @@
         <v>243</v>
       </c>
       <c r="C220" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -9171,7 +9165,7 @@
         <v>244</v>
       </c>
       <c r="C221" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -9182,7 +9176,7 @@
         <v>245</v>
       </c>
       <c r="C222" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -9193,7 +9187,7 @@
         <v>246</v>
       </c>
       <c r="C223" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -9204,7 +9198,7 @@
         <v>247</v>
       </c>
       <c r="C224" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -9215,7 +9209,7 @@
         <v>248</v>
       </c>
       <c r="C225" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -9226,7 +9220,7 @@
         <v>249</v>
       </c>
       <c r="C226" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -9237,7 +9231,7 @@
         <v>250</v>
       </c>
       <c r="C227" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -9248,7 +9242,7 @@
         <v>251</v>
       </c>
       <c r="C228" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -9259,7 +9253,7 @@
         <v>252</v>
       </c>
       <c r="C229" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -9270,7 +9264,7 @@
         <v>253</v>
       </c>
       <c r="C230" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -9281,7 +9275,7 @@
         <v>254</v>
       </c>
       <c r="C231" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -9292,7 +9286,7 @@
         <v>255</v>
       </c>
       <c r="C232" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -9303,7 +9297,7 @@
         <v>256</v>
       </c>
       <c r="C233" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -9314,7 +9308,7 @@
         <v>257</v>
       </c>
       <c r="C234" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -9325,7 +9319,7 @@
         <v>258</v>
       </c>
       <c r="C235" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -9336,7 +9330,7 @@
         <v>259</v>
       </c>
       <c r="C236" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -9347,7 +9341,7 @@
         <v>260</v>
       </c>
       <c r="C237" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -9358,7 +9352,7 @@
         <v>261</v>
       </c>
       <c r="C238" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -9369,7 +9363,7 @@
         <v>262</v>
       </c>
       <c r="C239" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -9380,7 +9374,7 @@
         <v>263</v>
       </c>
       <c r="C240" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -9391,7 +9385,7 @@
         <v>264</v>
       </c>
       <c r="C241" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -9402,7 +9396,7 @@
         <v>265</v>
       </c>
       <c r="C242" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -9413,7 +9407,7 @@
         <v>266</v>
       </c>
       <c r="C243" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -9424,7 +9418,7 @@
         <v>267</v>
       </c>
       <c r="C244" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -9435,7 +9429,7 @@
         <v>268</v>
       </c>
       <c r="C245" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -9446,7 +9440,7 @@
         <v>269</v>
       </c>
       <c r="C246" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -9457,7 +9451,7 @@
         <v>270</v>
       </c>
       <c r="C247" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -9468,7 +9462,7 @@
         <v>271</v>
       </c>
       <c r="C248" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -9479,7 +9473,7 @@
         <v>272</v>
       </c>
       <c r="C249" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -9490,7 +9484,7 @@
         <v>273</v>
       </c>
       <c r="C250" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -9501,7 +9495,7 @@
         <v>274</v>
       </c>
       <c r="C251" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -9512,7 +9506,7 @@
         <v>275</v>
       </c>
       <c r="C252" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -9523,7 +9517,7 @@
         <v>276</v>
       </c>
       <c r="C253" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -9534,7 +9528,7 @@
         <v>277</v>
       </c>
       <c r="C254" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -9545,7 +9539,7 @@
         <v>278</v>
       </c>
       <c r="C255" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -9556,7 +9550,7 @@
         <v>279</v>
       </c>
       <c r="C256" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -9567,7 +9561,7 @@
         <v>280</v>
       </c>
       <c r="C257" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -9578,7 +9572,7 @@
         <v>281</v>
       </c>
       <c r="C258" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="259" spans="1:3">
@@ -9589,7 +9583,7 @@
         <v>282</v>
       </c>
       <c r="C259" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -9600,7 +9594,7 @@
         <v>283</v>
       </c>
       <c r="C260" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="261" spans="1:3">
@@ -9611,7 +9605,7 @@
         <v>284</v>
       </c>
       <c r="C261" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="262" spans="1:3">
@@ -9622,7 +9616,7 @@
         <v>285</v>
       </c>
       <c r="C262" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -9633,7 +9627,7 @@
         <v>286</v>
       </c>
       <c r="C263" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="264" spans="1:3">
@@ -9644,7 +9638,7 @@
         <v>287</v>
       </c>
       <c r="C264" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -9655,7 +9649,7 @@
         <v>288</v>
       </c>
       <c r="C265" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="266" spans="1:3">
@@ -9666,7 +9660,7 @@
         <v>289</v>
       </c>
       <c r="C266" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="267" spans="1:3">
@@ -9677,7 +9671,7 @@
         <v>290</v>
       </c>
       <c r="C267" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="268" spans="1:3">
@@ -9688,7 +9682,7 @@
         <v>291</v>
       </c>
       <c r="C268" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="269" spans="1:3">
@@ -9699,7 +9693,7 @@
         <v>292</v>
       </c>
       <c r="C269" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="270" spans="1:3">
@@ -9710,7 +9704,7 @@
         <v>293</v>
       </c>
       <c r="C270" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="271" spans="1:3">
@@ -9721,7 +9715,7 @@
         <v>294</v>
       </c>
       <c r="C271" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="272" spans="1:3">
@@ -9732,7 +9726,7 @@
         <v>295</v>
       </c>
       <c r="C272" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="273" spans="1:3">
@@ -9743,7 +9737,7 @@
         <v>296</v>
       </c>
       <c r="C273" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="274" spans="1:3">
@@ -9754,7 +9748,7 @@
         <v>297</v>
       </c>
       <c r="C274" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="275" spans="1:3">
@@ -9765,7 +9759,7 @@
         <v>298</v>
       </c>
       <c r="C275" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="276" spans="1:3">
@@ -9776,7 +9770,7 @@
         <v>299</v>
       </c>
       <c r="C276" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="277" spans="1:3">
@@ -9787,7 +9781,7 @@
         <v>300</v>
       </c>
       <c r="C277" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="278" spans="1:3">
@@ -9798,7 +9792,7 @@
         <v>301</v>
       </c>
       <c r="C278" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="279" spans="1:3">
@@ -9809,7 +9803,7 @@
         <v>302</v>
       </c>
       <c r="C279" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="280" spans="1:3">
@@ -9820,7 +9814,7 @@
         <v>303</v>
       </c>
       <c r="C280" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -9831,7 +9825,7 @@
         <v>304</v>
       </c>
       <c r="C281" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="282" spans="1:3">
@@ -9842,7 +9836,7 @@
         <v>305</v>
       </c>
       <c r="C282" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="283" spans="1:3">
@@ -9853,7 +9847,7 @@
         <v>306</v>
       </c>
       <c r="C283" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="284" spans="1:3">
@@ -9864,7 +9858,7 @@
         <v>307</v>
       </c>
       <c r="C284" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="285" spans="1:3">
@@ -9875,7 +9869,7 @@
         <v>308</v>
       </c>
       <c r="C285" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="286" spans="1:3">
@@ -9886,7 +9880,7 @@
         <v>309</v>
       </c>
       <c r="C286" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="287" spans="1:3">
@@ -9897,7 +9891,7 @@
         <v>310</v>
       </c>
       <c r="C287" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="288" spans="1:3">
@@ -9908,7 +9902,7 @@
         <v>311</v>
       </c>
       <c r="C288" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="289" spans="1:3">
@@ -9919,7 +9913,7 @@
         <v>312</v>
       </c>
       <c r="C289" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="290" spans="1:3">
@@ -9930,7 +9924,7 @@
         <v>313</v>
       </c>
       <c r="C290" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="291" spans="1:3">
@@ -9941,7 +9935,7 @@
         <v>314</v>
       </c>
       <c r="C291" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="292" spans="1:3">
@@ -9952,7 +9946,7 @@
         <v>315</v>
       </c>
       <c r="C292" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="293" spans="1:3">
@@ -9963,7 +9957,7 @@
         <v>316</v>
       </c>
       <c r="C293" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="294" spans="1:3">
@@ -9974,7 +9968,7 @@
         <v>317</v>
       </c>
       <c r="C294" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="295" spans="1:3">
@@ -9985,7 +9979,7 @@
         <v>318</v>
       </c>
       <c r="C295" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="296" spans="1:3">
@@ -9996,7 +9990,7 @@
         <v>319</v>
       </c>
       <c r="C296" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="297" spans="1:3">
@@ -10007,7 +10001,7 @@
         <v>320</v>
       </c>
       <c r="C297" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="298" spans="1:3">
@@ -10018,7 +10012,7 @@
         <v>321</v>
       </c>
       <c r="C298" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="299" spans="1:3">
@@ -10029,7 +10023,7 @@
         <v>322</v>
       </c>
       <c r="C299" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="300" spans="1:3">
@@ -10040,7 +10034,7 @@
         <v>323</v>
       </c>
       <c r="C300" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="301" spans="1:3">
@@ -10051,7 +10045,7 @@
         <v>324</v>
       </c>
       <c r="C301" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -10062,7 +10056,7 @@
         <v>325</v>
       </c>
       <c r="C302" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="303" spans="1:3">
@@ -10073,7 +10067,7 @@
         <v>326</v>
       </c>
       <c r="C303" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="304" spans="1:3">
@@ -10084,7 +10078,7 @@
         <v>327</v>
       </c>
       <c r="C304" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -10095,7 +10089,7 @@
         <v>328</v>
       </c>
       <c r="C305" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="306" spans="1:3">
@@ -10106,7 +10100,7 @@
         <v>329</v>
       </c>
       <c r="C306" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="307" spans="1:3">
@@ -10117,7 +10111,7 @@
         <v>330</v>
       </c>
       <c r="C307" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="308" spans="1:3">
@@ -10128,7 +10122,7 @@
         <v>331</v>
       </c>
       <c r="C308" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="309" spans="1:3">
@@ -10139,7 +10133,7 @@
         <v>332</v>
       </c>
       <c r="C309" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="310" spans="1:3">
@@ -10150,7 +10144,7 @@
         <v>333</v>
       </c>
       <c r="C310" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="311" spans="1:3">
@@ -10161,7 +10155,7 @@
         <v>334</v>
       </c>
       <c r="C311" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="312" spans="1:3">
@@ -10172,7 +10166,7 @@
         <v>335</v>
       </c>
       <c r="C312" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="313" spans="1:3">
@@ -10183,7 +10177,7 @@
         <v>336</v>
       </c>
       <c r="C313" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="314" spans="1:3">
@@ -10194,7 +10188,7 @@
         <v>337</v>
       </c>
       <c r="C314" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="315" spans="1:3">
@@ -10205,7 +10199,7 @@
         <v>338</v>
       </c>
       <c r="C315" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="316" spans="1:3">
@@ -10216,7 +10210,7 @@
         <v>339</v>
       </c>
       <c r="C316" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="317" spans="1:3">
@@ -10227,7 +10221,7 @@
         <v>340</v>
       </c>
       <c r="C317" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="318" spans="1:3">
@@ -10238,7 +10232,7 @@
         <v>341</v>
       </c>
       <c r="C318" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="319" spans="1:3">
@@ -10249,7 +10243,7 @@
         <v>342</v>
       </c>
       <c r="C319" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="320" spans="1:3">
@@ -10260,7 +10254,7 @@
         <v>343</v>
       </c>
       <c r="C320" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="321" spans="1:3">
@@ -10271,7 +10265,7 @@
         <v>344</v>
       </c>
       <c r="C321" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -10282,7 +10276,7 @@
         <v>345</v>
       </c>
       <c r="C322" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="323" spans="1:3">
@@ -10293,7 +10287,7 @@
         <v>346</v>
       </c>
       <c r="C323" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="324" spans="1:3">
@@ -10304,7 +10298,7 @@
         <v>347</v>
       </c>
       <c r="C324" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -10315,7 +10309,7 @@
         <v>348</v>
       </c>
       <c r="C325" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="326" spans="1:3">
@@ -10326,7 +10320,7 @@
         <v>349</v>
       </c>
       <c r="C326" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="327" spans="1:3">
@@ -10337,7 +10331,7 @@
         <v>350</v>
       </c>
       <c r="C327" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="328" spans="1:3">
@@ -10348,7 +10342,7 @@
         <v>351</v>
       </c>
       <c r="C328" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="329" spans="1:3">
@@ -10359,7 +10353,7 @@
         <v>352</v>
       </c>
       <c r="C329" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="330" spans="1:3">
@@ -10370,7 +10364,7 @@
         <v>353</v>
       </c>
       <c r="C330" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -10381,7 +10375,7 @@
         <v>354</v>
       </c>
       <c r="C331" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="332" spans="1:3">
@@ -10392,7 +10386,7 @@
         <v>355</v>
       </c>
       <c r="C332" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="333" spans="1:3">
@@ -10403,7 +10397,7 @@
         <v>356</v>
       </c>
       <c r="C333" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="334" spans="1:3">
@@ -10414,7 +10408,7 @@
         <v>357</v>
       </c>
       <c r="C334" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="335" spans="1:3">
@@ -10425,7 +10419,7 @@
         <v>358</v>
       </c>
       <c r="C335" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="336" spans="1:3">
@@ -10436,7 +10430,7 @@
         <v>359</v>
       </c>
       <c r="C336" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="337" spans="1:3">
@@ -10447,7 +10441,7 @@
         <v>360</v>
       </c>
       <c r="C337" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="338" spans="1:3">
@@ -10458,7 +10452,7 @@
         <v>361</v>
       </c>
       <c r="C338" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="339" spans="1:3">
@@ -10469,7 +10463,7 @@
         <v>362</v>
       </c>
       <c r="C339" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="340" spans="1:3">
@@ -10480,7 +10474,7 @@
         <v>363</v>
       </c>
       <c r="C340" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="341" spans="1:3">
@@ -10491,7 +10485,7 @@
         <v>364</v>
       </c>
       <c r="C341" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -10502,7 +10496,7 @@
         <v>365</v>
       </c>
       <c r="C342" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="343" spans="1:3">
@@ -10513,7 +10507,7 @@
         <v>366</v>
       </c>
       <c r="C343" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="344" spans="1:3">
@@ -10524,7 +10518,7 @@
         <v>367</v>
       </c>
       <c r="C344" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="345" spans="1:3">
@@ -10535,7 +10529,7 @@
         <v>368</v>
       </c>
       <c r="C345" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="346" spans="1:3">
@@ -10546,7 +10540,7 @@
         <v>369</v>
       </c>
       <c r="C346" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="347" spans="1:3">
@@ -10557,7 +10551,7 @@
         <v>370</v>
       </c>
       <c r="C347" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="348" spans="1:3">
@@ -10568,7 +10562,7 @@
         <v>371</v>
       </c>
       <c r="C348" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="349" spans="1:3">
@@ -10579,7 +10573,7 @@
         <v>372</v>
       </c>
       <c r="C349" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -10590,7 +10584,7 @@
         <v>373</v>
       </c>
       <c r="C350" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="351" spans="1:3">
@@ -10601,7 +10595,7 @@
         <v>374</v>
       </c>
       <c r="C351" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -10612,7 +10606,7 @@
         <v>375</v>
       </c>
       <c r="C352" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="353" spans="1:3">
@@ -10623,7 +10617,7 @@
         <v>376</v>
       </c>
       <c r="C353" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="354" spans="1:3">
@@ -10634,7 +10628,7 @@
         <v>377</v>
       </c>
       <c r="C354" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -10645,7 +10639,7 @@
         <v>378</v>
       </c>
       <c r="C355" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="356" spans="1:3">
@@ -10656,7 +10650,7 @@
         <v>379</v>
       </c>
       <c r="C356" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="357" spans="1:3">
@@ -10667,7 +10661,7 @@
         <v>380</v>
       </c>
       <c r="C357" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="358" spans="1:3">
@@ -10678,7 +10672,7 @@
         <v>381</v>
       </c>
       <c r="C358" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="359" spans="1:3">
@@ -10689,7 +10683,7 @@
         <v>382</v>
       </c>
       <c r="C359" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -10700,7 +10694,7 @@
         <v>383</v>
       </c>
       <c r="C360" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="361" spans="1:3">
@@ -10711,7 +10705,7 @@
         <v>384</v>
       </c>
       <c r="C361" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="362" spans="1:3">
@@ -10722,7 +10716,7 @@
         <v>385</v>
       </c>
       <c r="C362" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="363" spans="1:3">
@@ -10733,7 +10727,7 @@
         <v>386</v>
       </c>
       <c r="C363" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="364" spans="1:3">
@@ -10744,7 +10738,7 @@
         <v>387</v>
       </c>
       <c r="C364" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="365" spans="1:3">
@@ -10755,7 +10749,7 @@
         <v>388</v>
       </c>
       <c r="C365" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="366" spans="1:3">
@@ -10766,7 +10760,7 @@
         <v>389</v>
       </c>
       <c r="C366" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="367" spans="1:3">
@@ -10777,7 +10771,7 @@
         <v>390</v>
       </c>
       <c r="C367" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="368" spans="1:3">
@@ -10788,7 +10782,7 @@
         <v>391</v>
       </c>
       <c r="C368" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="369" spans="1:3">
@@ -10799,7 +10793,7 @@
         <v>392</v>
       </c>
       <c r="C369" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="370" spans="1:3">
@@ -10810,7 +10804,7 @@
         <v>393</v>
       </c>
       <c r="C370" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="371" spans="1:3">
@@ -10821,7 +10815,7 @@
         <v>394</v>
       </c>
       <c r="C371" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -10832,7 +10826,7 @@
         <v>395</v>
       </c>
       <c r="C372" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="373" spans="1:3">
@@ -10843,7 +10837,7 @@
         <v>396</v>
       </c>
       <c r="C373" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="374" spans="1:3">
@@ -10854,7 +10848,7 @@
         <v>397</v>
       </c>
       <c r="C374" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="375" spans="1:3">
@@ -10865,7 +10859,7 @@
         <v>398</v>
       </c>
       <c r="C375" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="376" spans="1:3">
@@ -10876,7 +10870,7 @@
         <v>399</v>
       </c>
       <c r="C376" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="377" spans="1:3">
@@ -10887,7 +10881,7 @@
         <v>400</v>
       </c>
       <c r="C377" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="378" spans="1:3">
@@ -10898,7 +10892,7 @@
         <v>401</v>
       </c>
       <c r="C378" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="379" spans="1:3">
@@ -10909,7 +10903,7 @@
         <v>402</v>
       </c>
       <c r="C379" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="380" spans="1:3">
@@ -10920,7 +10914,7 @@
         <v>403</v>
       </c>
       <c r="C380" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="381" spans="1:3">
@@ -10931,7 +10925,7 @@
         <v>404</v>
       </c>
       <c r="C381" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="382" spans="1:3">
@@ -10942,7 +10936,7 @@
         <v>405</v>
       </c>
       <c r="C382" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="383" spans="1:3">
@@ -10953,7 +10947,7 @@
         <v>406</v>
       </c>
       <c r="C383" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="384" spans="1:3">
@@ -10964,7 +10958,7 @@
         <v>407</v>
       </c>
       <c r="C384" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="385" spans="1:3">
@@ -10975,7 +10969,7 @@
         <v>408</v>
       </c>
       <c r="C385" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="386" spans="1:3">
@@ -10986,7 +10980,7 @@
         <v>409</v>
       </c>
       <c r="C386" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="387" spans="1:3">
@@ -10997,7 +10991,7 @@
         <v>410</v>
       </c>
       <c r="C387" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="388" spans="1:3">
@@ -11008,7 +11002,7 @@
         <v>411</v>
       </c>
       <c r="C388" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="389" spans="1:3">
@@ -11019,7 +11013,7 @@
         <v>412</v>
       </c>
       <c r="C389" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="390" spans="1:3">
@@ -11030,7 +11024,7 @@
         <v>413</v>
       </c>
       <c r="C390" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="391" spans="1:3">
@@ -11041,7 +11035,7 @@
         <v>414</v>
       </c>
       <c r="C391" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="392" spans="1:3">
@@ -11052,7 +11046,7 @@
         <v>415</v>
       </c>
       <c r="C392" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="393" spans="1:3">
@@ -11063,7 +11057,7 @@
         <v>416</v>
       </c>
       <c r="C393" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="394" spans="1:3">
@@ -11074,7 +11068,7 @@
         <v>417</v>
       </c>
       <c r="C394" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="395" spans="1:3">
@@ -11085,7 +11079,7 @@
         <v>418</v>
       </c>
       <c r="C395" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="396" spans="1:3">
@@ -11096,7 +11090,7 @@
         <v>419</v>
       </c>
       <c r="C396" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="397" spans="1:3">
@@ -11107,7 +11101,7 @@
         <v>420</v>
       </c>
       <c r="C397" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="398" spans="1:3">
@@ -11118,7 +11112,7 @@
         <v>421</v>
       </c>
       <c r="C398" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="399" spans="1:3">
@@ -11129,7 +11123,7 @@
         <v>422</v>
       </c>
       <c r="C399" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="400" spans="1:3">
@@ -11140,7 +11134,7 @@
         <v>423</v>
       </c>
       <c r="C400" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="401" spans="1:3">
@@ -11151,7 +11145,7 @@
         <v>424</v>
       </c>
       <c r="C401" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="402" spans="1:3">
@@ -11162,7 +11156,7 @@
         <v>425</v>
       </c>
       <c r="C402" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="403" spans="1:3">
@@ -11173,7 +11167,7 @@
         <v>426</v>
       </c>
       <c r="C403" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="404" spans="1:3">
@@ -11184,7 +11178,7 @@
         <v>427</v>
       </c>
       <c r="C404" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="405" spans="1:3">
@@ -11195,7 +11189,7 @@
         <v>428</v>
       </c>
       <c r="C405" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="406" spans="1:3">
@@ -11206,7 +11200,7 @@
         <v>429</v>
       </c>
       <c r="C406" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="407" spans="1:3">
@@ -11217,7 +11211,7 @@
         <v>430</v>
       </c>
       <c r="C407" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="408" spans="1:3">
@@ -11228,7 +11222,7 @@
         <v>431</v>
       </c>
       <c r="C408" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="409" spans="1:3">
@@ -11239,7 +11233,7 @@
         <v>432</v>
       </c>
       <c r="C409" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="410" spans="1:3">
@@ -11250,7 +11244,7 @@
         <v>433</v>
       </c>
       <c r="C410" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="411" spans="1:3">
@@ -11261,7 +11255,7 @@
         <v>434</v>
       </c>
       <c r="C411" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="412" spans="1:3">
@@ -11272,7 +11266,7 @@
         <v>435</v>
       </c>
       <c r="C412" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="413" spans="1:3">
@@ -11283,7 +11277,7 @@
         <v>436</v>
       </c>
       <c r="C413" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="414" spans="1:3">
@@ -11294,7 +11288,7 @@
         <v>437</v>
       </c>
       <c r="C414" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="415" spans="1:3">
@@ -11305,7 +11299,7 @@
         <v>438</v>
       </c>
       <c r="C415" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="416" spans="1:3">
@@ -11316,7 +11310,7 @@
         <v>439</v>
       </c>
       <c r="C416" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="417" spans="1:3">
@@ -11327,7 +11321,7 @@
         <v>440</v>
       </c>
       <c r="C417" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="418" spans="1:3">
@@ -11338,7 +11332,7 @@
         <v>441</v>
       </c>
       <c r="C418" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="419" spans="1:3">
@@ -11349,7 +11343,7 @@
         <v>442</v>
       </c>
       <c r="C419" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="420" spans="1:3">
@@ -11360,7 +11354,7 @@
         <v>443</v>
       </c>
       <c r="C420" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="421" spans="1:3">
@@ -11371,7 +11365,7 @@
         <v>444</v>
       </c>
       <c r="C421" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="422" spans="1:3">
@@ -11382,7 +11376,7 @@
         <v>445</v>
       </c>
       <c r="C422" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="423" spans="1:3">
@@ -11393,7 +11387,7 @@
         <v>446</v>
       </c>
       <c r="C423" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="424" spans="1:3">
@@ -11404,7 +11398,7 @@
         <v>447</v>
       </c>
       <c r="C424" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="425" spans="1:3">
@@ -11415,7 +11409,7 @@
         <v>448</v>
       </c>
       <c r="C425" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="426" spans="1:3">
@@ -11426,7 +11420,7 @@
         <v>449</v>
       </c>
       <c r="C426" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="427" spans="1:3">
@@ -11437,7 +11431,7 @@
         <v>450</v>
       </c>
       <c r="C427" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="428" spans="1:3">
@@ -11448,7 +11442,7 @@
         <v>451</v>
       </c>
       <c r="C428" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="429" spans="1:3">
@@ -11459,7 +11453,7 @@
         <v>452</v>
       </c>
       <c r="C429" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="430" spans="1:3">
@@ -11470,7 +11464,7 @@
         <v>453</v>
       </c>
       <c r="C430" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="431" spans="1:3">
@@ -11481,7 +11475,7 @@
         <v>454</v>
       </c>
       <c r="C431" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="432" spans="1:3">
@@ -11492,7 +11486,7 @@
         <v>455</v>
       </c>
       <c r="C432" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="433" spans="1:3">
@@ -11503,7 +11497,7 @@
         <v>456</v>
       </c>
       <c r="C433" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="434" spans="1:3">
@@ -11514,7 +11508,7 @@
         <v>457</v>
       </c>
       <c r="C434" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="435" spans="1:3">
@@ -11525,7 +11519,7 @@
         <v>458</v>
       </c>
       <c r="C435" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="436" spans="1:3">
@@ -11536,7 +11530,7 @@
         <v>459</v>
       </c>
       <c r="C436" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="437" spans="1:3">
@@ -11547,7 +11541,7 @@
         <v>460</v>
       </c>
       <c r="C437" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="438" spans="1:3">
@@ -11558,7 +11552,7 @@
         <v>461</v>
       </c>
       <c r="C438" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="439" spans="1:3">
@@ -11569,7 +11563,7 @@
         <v>462</v>
       </c>
       <c r="C439" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="440" spans="1:3">
@@ -11580,7 +11574,7 @@
         <v>463</v>
       </c>
       <c r="C440" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="441" spans="1:3">
@@ -11591,7 +11585,7 @@
         <v>464</v>
       </c>
       <c r="C441" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="442" spans="1:3">
@@ -11602,7 +11596,7 @@
         <v>465</v>
       </c>
       <c r="C442" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="443" spans="1:3">
@@ -11613,7 +11607,7 @@
         <v>466</v>
       </c>
       <c r="C443" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="444" spans="1:3">
@@ -11624,7 +11618,7 @@
         <v>467</v>
       </c>
       <c r="C444" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="445" spans="1:3">
@@ -11635,7 +11629,7 @@
         <v>468</v>
       </c>
       <c r="C445" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="446" spans="1:3">
@@ -11646,7 +11640,7 @@
         <v>469</v>
       </c>
       <c r="C446" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="447" spans="1:3">
@@ -11657,7 +11651,7 @@
         <v>470</v>
       </c>
       <c r="C447" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="448" spans="1:3">
@@ -11668,7 +11662,7 @@
         <v>471</v>
       </c>
       <c r="C448" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="449" spans="1:3">
@@ -11679,7 +11673,7 @@
         <v>472</v>
       </c>
       <c r="C449" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="450" spans="1:3">
@@ -11690,7 +11684,7 @@
         <v>473</v>
       </c>
       <c r="C450" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="451" spans="1:3">
@@ -11701,7 +11695,7 @@
         <v>474</v>
       </c>
       <c r="C451" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="452" spans="1:3">
@@ -11712,7 +11706,7 @@
         <v>475</v>
       </c>
       <c r="C452" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="453" spans="1:3">
@@ -11723,7 +11717,7 @@
         <v>476</v>
       </c>
       <c r="C453" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="454" spans="1:3">
@@ -11734,7 +11728,7 @@
         <v>477</v>
       </c>
       <c r="C454" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="455" spans="1:3">
@@ -11745,7 +11739,7 @@
         <v>478</v>
       </c>
       <c r="C455" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="456" spans="1:3">
@@ -11756,7 +11750,7 @@
         <v>479</v>
       </c>
       <c r="C456" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="457" spans="1:3">
@@ -11767,7 +11761,7 @@
         <v>480</v>
       </c>
       <c r="C457" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="458" spans="1:3">
@@ -11778,7 +11772,7 @@
         <v>481</v>
       </c>
       <c r="C458" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="459" spans="1:3">
@@ -11789,7 +11783,7 @@
         <v>482</v>
       </c>
       <c r="C459" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="460" spans="1:3">
@@ -11800,7 +11794,7 @@
         <v>483</v>
       </c>
       <c r="C460" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="461" spans="1:3">
@@ -11811,7 +11805,7 @@
         <v>484</v>
       </c>
       <c r="C461" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="462" spans="1:3">
@@ -11822,7 +11816,7 @@
         <v>485</v>
       </c>
       <c r="C462" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="463" spans="1:3">
@@ -11833,7 +11827,7 @@
         <v>486</v>
       </c>
       <c r="C463" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="464" spans="1:3">
@@ -11844,7 +11838,7 @@
         <v>487</v>
       </c>
       <c r="C464" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="465" spans="1:3">
@@ -11855,7 +11849,7 @@
         <v>488</v>
       </c>
       <c r="C465" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="466" spans="1:3">
@@ -11866,7 +11860,7 @@
         <v>489</v>
       </c>
       <c r="C466" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="467" spans="1:3">
@@ -11877,7 +11871,7 @@
         <v>490</v>
       </c>
       <c r="C467" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="468" spans="1:3">
@@ -11888,7 +11882,7 @@
         <v>491</v>
       </c>
       <c r="C468" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="469" spans="1:3">
@@ -11899,7 +11893,7 @@
         <v>492</v>
       </c>
       <c r="C469" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="470" spans="1:3">
@@ -11910,7 +11904,7 @@
         <v>493</v>
       </c>
       <c r="C470" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="471" spans="1:3">
@@ -11921,7 +11915,7 @@
         <v>494</v>
       </c>
       <c r="C471" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="472" spans="1:3">
@@ -11932,7 +11926,7 @@
         <v>495</v>
       </c>
       <c r="C472" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="473" spans="1:3">
@@ -11943,7 +11937,7 @@
         <v>496</v>
       </c>
       <c r="C473" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="474" spans="1:3">
@@ -11954,7 +11948,7 @@
         <v>497</v>
       </c>
       <c r="C474" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="475" spans="1:3">
@@ -11965,7 +11959,7 @@
         <v>498</v>
       </c>
       <c r="C475" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="476" spans="1:3">
@@ -11976,7 +11970,7 @@
         <v>499</v>
       </c>
       <c r="C476" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="477" spans="1:3">
@@ -11987,7 +11981,7 @@
         <v>500</v>
       </c>
       <c r="C477" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="478" spans="1:3">
@@ -11998,7 +11992,7 @@
         <v>501</v>
       </c>
       <c r="C478" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="479" spans="1:3">
@@ -12009,7 +12003,7 @@
         <v>502</v>
       </c>
       <c r="C479" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="480" spans="1:3">
@@ -12020,7 +12014,7 @@
         <v>503</v>
       </c>
       <c r="C480" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="481" spans="1:3">
@@ -12031,7 +12025,7 @@
         <v>504</v>
       </c>
       <c r="C481" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="482" spans="1:3">
@@ -12042,7 +12036,7 @@
         <v>505</v>
       </c>
       <c r="C482" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="483" spans="1:3">
@@ -12053,7 +12047,7 @@
         <v>506</v>
       </c>
       <c r="C483" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="484" spans="1:3">
@@ -12064,7 +12058,7 @@
         <v>507</v>
       </c>
       <c r="C484" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="485" spans="1:3">
@@ -12075,7 +12069,7 @@
         <v>508</v>
       </c>
       <c r="C485" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="486" spans="1:3">
@@ -12086,7 +12080,7 @@
         <v>509</v>
       </c>
       <c r="C486" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="487" spans="1:3">
@@ -12097,7 +12091,7 @@
         <v>510</v>
       </c>
       <c r="C487" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="488" spans="1:3">
@@ -12108,7 +12102,7 @@
         <v>511</v>
       </c>
       <c r="C488" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="489" spans="1:3">
@@ -12119,7 +12113,7 @@
         <v>512</v>
       </c>
       <c r="C489" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="490" spans="1:3">
@@ -12130,7 +12124,7 @@
         <v>513</v>
       </c>
       <c r="C490" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="491" spans="1:3">
@@ -12141,7 +12135,7 @@
         <v>514</v>
       </c>
       <c r="C491" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="492" spans="1:3">
@@ -12152,7 +12146,7 @@
         <v>515</v>
       </c>
       <c r="C492" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="493" spans="1:3">
@@ -12163,7 +12157,7 @@
         <v>516</v>
       </c>
       <c r="C493" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="494" spans="1:3">
@@ -12174,7 +12168,7 @@
         <v>517</v>
       </c>
       <c r="C494" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="495" spans="1:3">
@@ -12185,7 +12179,7 @@
         <v>518</v>
       </c>
       <c r="C495" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="496" spans="1:3">
@@ -12196,7 +12190,7 @@
         <v>519</v>
       </c>
       <c r="C496" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="497" spans="1:3">
@@ -12207,7 +12201,7 @@
         <v>520</v>
       </c>
       <c r="C497" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="498" spans="1:3">
@@ -12218,7 +12212,7 @@
         <v>521</v>
       </c>
       <c r="C498" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="499" spans="1:3">
@@ -12229,7 +12223,7 @@
         <v>522</v>
       </c>
       <c r="C499" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="500" spans="1:3">
@@ -12240,7 +12234,7 @@
         <v>523</v>
       </c>
       <c r="C500" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="501" spans="1:3">
@@ -12251,7 +12245,7 @@
         <v>524</v>
       </c>
       <c r="C501" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="502" spans="1:3">
@@ -12262,7 +12256,7 @@
         <v>525</v>
       </c>
       <c r="C502" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="503" spans="1:3">
@@ -12273,7 +12267,7 @@
         <v>526</v>
       </c>
       <c r="C503" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="504" spans="1:3">
@@ -12284,7 +12278,7 @@
         <v>527</v>
       </c>
       <c r="C504" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="505" spans="1:3">
@@ -12295,7 +12289,7 @@
         <v>528</v>
       </c>
       <c r="C505" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="506" spans="1:3">
@@ -12306,7 +12300,7 @@
         <v>529</v>
       </c>
       <c r="C506" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="507" spans="1:3">
@@ -12317,7 +12311,7 @@
         <v>530</v>
       </c>
       <c r="C507" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="508" spans="1:3">
@@ -12328,7 +12322,7 @@
         <v>531</v>
       </c>
       <c r="C508" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="509" spans="1:3">
@@ -12339,7 +12333,7 @@
         <v>532</v>
       </c>
       <c r="C509" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="510" spans="1:3">
@@ -12350,7 +12344,7 @@
         <v>533</v>
       </c>
       <c r="C510" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="511" spans="1:3">
@@ -12361,7 +12355,7 @@
         <v>534</v>
       </c>
       <c r="C511" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="512" spans="1:3">
@@ -12372,7 +12366,7 @@
         <v>535</v>
       </c>
       <c r="C512" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="513" spans="1:3">
@@ -12383,7 +12377,7 @@
         <v>536</v>
       </c>
       <c r="C513" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="514" spans="1:3">
@@ -12394,7 +12388,7 @@
         <v>537</v>
       </c>
       <c r="C514" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="515" spans="1:3">
@@ -12405,7 +12399,7 @@
         <v>538</v>
       </c>
       <c r="C515" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="516" spans="1:3">
@@ -12416,7 +12410,7 @@
         <v>539</v>
       </c>
       <c r="C516" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="517" spans="1:3">
@@ -12427,7 +12421,7 @@
         <v>540</v>
       </c>
       <c r="C517" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="518" spans="1:3">
@@ -12438,7 +12432,7 @@
         <v>541</v>
       </c>
       <c r="C518" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="519" spans="1:3">
@@ -12449,7 +12443,7 @@
         <v>542</v>
       </c>
       <c r="C519" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="520" spans="1:3">
@@ -12460,7 +12454,7 @@
         <v>543</v>
       </c>
       <c r="C520" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="521" spans="1:3">
@@ -12471,7 +12465,7 @@
         <v>544</v>
       </c>
       <c r="C521" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="522" spans="1:3">
@@ -12482,7 +12476,7 @@
         <v>545</v>
       </c>
       <c r="C522" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="523" spans="1:3">
@@ -12493,7 +12487,7 @@
         <v>546</v>
       </c>
       <c r="C523" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="524" spans="1:3">
@@ -12504,7 +12498,7 @@
         <v>547</v>
       </c>
       <c r="C524" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="525" spans="1:3">
@@ -12515,7 +12509,7 @@
         <v>548</v>
       </c>
       <c r="C525" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="526" spans="1:3">
@@ -12526,7 +12520,7 @@
         <v>549</v>
       </c>
       <c r="C526" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="527" spans="1:3">
@@ -12537,7 +12531,7 @@
         <v>550</v>
       </c>
       <c r="C527" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="528" spans="1:3">
@@ -12548,7 +12542,7 @@
         <v>551</v>
       </c>
       <c r="C528" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="529" spans="1:3">
@@ -12559,7 +12553,7 @@
         <v>552</v>
       </c>
       <c r="C529" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="530" spans="1:3">
@@ -12570,7 +12564,7 @@
         <v>553</v>
       </c>
       <c r="C530" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="531" spans="1:3">
@@ -12581,7 +12575,7 @@
         <v>554</v>
       </c>
       <c r="C531" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="532" spans="1:3">
@@ -12592,7 +12586,7 @@
         <v>555</v>
       </c>
       <c r="C532" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="533" spans="1:3">
@@ -12603,7 +12597,7 @@
         <v>556</v>
       </c>
       <c r="C533" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="534" spans="1:3">
@@ -12614,7 +12608,7 @@
         <v>557</v>
       </c>
       <c r="C534" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="535" spans="1:3">
@@ -12625,7 +12619,7 @@
         <v>558</v>
       </c>
       <c r="C535" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="536" spans="1:3">
@@ -12636,7 +12630,7 @@
         <v>559</v>
       </c>
       <c r="C536" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="537" spans="1:3">
@@ -12647,7 +12641,7 @@
         <v>560</v>
       </c>
       <c r="C537" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="538" spans="1:3">
@@ -12658,7 +12652,7 @@
         <v>561</v>
       </c>
       <c r="C538" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="539" spans="1:3">
@@ -12669,7 +12663,7 @@
         <v>562</v>
       </c>
       <c r="C539" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="540" spans="1:3">
@@ -12680,7 +12674,7 @@
         <v>563</v>
       </c>
       <c r="C540" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="541" spans="1:3">
@@ -12691,7 +12685,7 @@
         <v>564</v>
       </c>
       <c r="C541" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="542" spans="1:3">
@@ -12702,7 +12696,7 @@
         <v>565</v>
       </c>
       <c r="C542" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="543" spans="1:3">
@@ -12713,7 +12707,7 @@
         <v>566</v>
       </c>
       <c r="C543" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="544" spans="1:3">
@@ -12724,7 +12718,7 @@
         <v>567</v>
       </c>
       <c r="C544" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="545" spans="1:3">
@@ -12735,7 +12729,7 @@
         <v>568</v>
       </c>
       <c r="C545" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="546" spans="1:3">
@@ -12746,18 +12740,18 @@
         <v>569</v>
       </c>
       <c r="C546" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="547" spans="1:3">
       <c r="A547" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B547" t="s">
         <v>570</v>
       </c>
       <c r="C547" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="548" spans="1:3">
@@ -12768,7 +12762,7 @@
         <v>571</v>
       </c>
       <c r="C548" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="549" spans="1:3">
@@ -12779,7 +12773,7 @@
         <v>572</v>
       </c>
       <c r="C549" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="550" spans="1:3">
@@ -12790,7 +12784,7 @@
         <v>573</v>
       </c>
       <c r="C550" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="551" spans="1:3">
@@ -12801,7 +12795,7 @@
         <v>574</v>
       </c>
       <c r="C551" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="552" spans="1:3">
@@ -12812,7 +12806,7 @@
         <v>575</v>
       </c>
       <c r="C552" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="553" spans="1:3">
@@ -12823,7 +12817,7 @@
         <v>576</v>
       </c>
       <c r="C553" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="554" spans="1:3">
@@ -12834,7 +12828,7 @@
         <v>577</v>
       </c>
       <c r="C554" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="555" spans="1:3">
@@ -12845,7 +12839,7 @@
         <v>578</v>
       </c>
       <c r="C555" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="556" spans="1:3">
@@ -12856,7 +12850,7 @@
         <v>579</v>
       </c>
       <c r="C556" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="557" spans="1:3">
@@ -12867,7 +12861,7 @@
         <v>580</v>
       </c>
       <c r="C557" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="558" spans="1:3">
@@ -12878,7 +12872,7 @@
         <v>581</v>
       </c>
       <c r="C558" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="559" spans="1:3">
@@ -12889,7 +12883,7 @@
         <v>582</v>
       </c>
       <c r="C559" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="560" spans="1:3">
@@ -12900,7 +12894,7 @@
         <v>583</v>
       </c>
       <c r="C560" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="561" spans="1:3">
@@ -12911,7 +12905,7 @@
         <v>584</v>
       </c>
       <c r="C561" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="562" spans="1:3">
@@ -12922,7 +12916,7 @@
         <v>585</v>
       </c>
       <c r="C562" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="563" spans="1:3">
@@ -12933,7 +12927,7 @@
         <v>586</v>
       </c>
       <c r="C563" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="564" spans="1:3">
@@ -12944,7 +12938,7 @@
         <v>587</v>
       </c>
       <c r="C564" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="565" spans="1:3">
@@ -12955,7 +12949,7 @@
         <v>588</v>
       </c>
       <c r="C565" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="566" spans="1:3">
@@ -12966,7 +12960,7 @@
         <v>589</v>
       </c>
       <c r="C566" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="567" spans="1:3">
@@ -12977,7 +12971,7 @@
         <v>590</v>
       </c>
       <c r="C567" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="568" spans="1:3">
@@ -12988,7 +12982,7 @@
         <v>591</v>
       </c>
       <c r="C568" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="569" spans="1:3">
@@ -12999,7 +12993,7 @@
         <v>592</v>
       </c>
       <c r="C569" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="570" spans="1:3">
@@ -13010,7 +13004,7 @@
         <v>593</v>
       </c>
       <c r="C570" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="571" spans="1:3">
@@ -13021,7 +13015,7 @@
         <v>594</v>
       </c>
       <c r="C571" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="572" spans="1:3">
@@ -13032,7 +13026,7 @@
         <v>595</v>
       </c>
       <c r="C572" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="573" spans="1:3">
@@ -13043,7 +13037,7 @@
         <v>596</v>
       </c>
       <c r="C573" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="574" spans="1:3">
@@ -13054,7 +13048,7 @@
         <v>597</v>
       </c>
       <c r="C574" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="575" spans="1:3">
@@ -13065,7 +13059,7 @@
         <v>598</v>
       </c>
       <c r="C575" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="576" spans="1:3">
@@ -13076,7 +13070,7 @@
         <v>599</v>
       </c>
       <c r="C576" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="577" spans="1:3">
@@ -13087,7 +13081,7 @@
         <v>600</v>
       </c>
       <c r="C577" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="578" spans="1:3">
@@ -13098,7 +13092,7 @@
         <v>601</v>
       </c>
       <c r="C578" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="579" spans="1:3">
@@ -13109,7 +13103,7 @@
         <v>602</v>
       </c>
       <c r="C579" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="580" spans="1:3">
@@ -13120,7 +13114,7 @@
         <v>603</v>
       </c>
       <c r="C580" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="581" spans="1:3">
@@ -13131,7 +13125,7 @@
         <v>604</v>
       </c>
       <c r="C581" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="582" spans="1:3">
@@ -13142,7 +13136,7 @@
         <v>605</v>
       </c>
       <c r="C582" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="583" spans="1:3">
@@ -13153,7 +13147,7 @@
         <v>606</v>
       </c>
       <c r="C583" t="s">
-        <v>1653</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="584" spans="1:3">
@@ -13164,7 +13158,7 @@
         <v>607</v>
       </c>
       <c r="C584" t="s">
-        <v>1623</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="585" spans="1:3">
@@ -13175,7 +13169,7 @@
         <v>608</v>
       </c>
       <c r="C585" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="586" spans="1:3">
@@ -13186,7 +13180,7 @@
         <v>609</v>
       </c>
       <c r="C586" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="587" spans="1:3">
@@ -13197,7 +13191,7 @@
         <v>610</v>
       </c>
       <c r="C587" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="588" spans="1:3">
@@ -13208,7 +13202,7 @@
         <v>611</v>
       </c>
       <c r="C588" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="589" spans="1:3">
@@ -13219,18 +13213,18 @@
         <v>612</v>
       </c>
       <c r="C589" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="590" spans="1:3">
       <c r="A590" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B590" t="s">
         <v>613</v>
       </c>
       <c r="C590" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="591" spans="1:3">
@@ -13241,7 +13235,7 @@
         <v>614</v>
       </c>
       <c r="C591" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="592" spans="1:3">
@@ -13252,7 +13246,7 @@
         <v>615</v>
       </c>
       <c r="C592" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="593" spans="1:3">
@@ -13263,7 +13257,7 @@
         <v>616</v>
       </c>
       <c r="C593" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="594" spans="1:3">
@@ -13274,7 +13268,7 @@
         <v>617</v>
       </c>
       <c r="C594" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="595" spans="1:3">
@@ -13285,7 +13279,7 @@
         <v>618</v>
       </c>
       <c r="C595" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="596" spans="1:3">
@@ -13296,18 +13290,18 @@
         <v>619</v>
       </c>
       <c r="C596" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="597" spans="1:3">
       <c r="A597" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B597" t="s">
         <v>620</v>
       </c>
       <c r="C597" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="598" spans="1:3">
@@ -13318,7 +13312,7 @@
         <v>621</v>
       </c>
       <c r="C598" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="599" spans="1:3">
@@ -13329,7 +13323,7 @@
         <v>622</v>
       </c>
       <c r="C599" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="600" spans="1:3">
@@ -13340,7 +13334,7 @@
         <v>623</v>
       </c>
       <c r="C600" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="601" spans="1:3">
@@ -13351,7 +13345,7 @@
         <v>624</v>
       </c>
       <c r="C601" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="602" spans="1:3">
@@ -13362,7 +13356,7 @@
         <v>625</v>
       </c>
       <c r="C602" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="603" spans="1:3">
@@ -13373,7 +13367,7 @@
         <v>626</v>
       </c>
       <c r="C603" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="604" spans="1:3">
@@ -13384,7 +13378,7 @@
         <v>627</v>
       </c>
       <c r="C604" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="605" spans="1:3">
@@ -13395,7 +13389,7 @@
         <v>628</v>
       </c>
       <c r="C605" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="606" spans="1:3">
@@ -13406,7 +13400,7 @@
         <v>629</v>
       </c>
       <c r="C606" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="607" spans="1:3">
@@ -13417,7 +13411,7 @@
         <v>630</v>
       </c>
       <c r="C607" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="608" spans="1:3">
@@ -13428,7 +13422,7 @@
         <v>631</v>
       </c>
       <c r="C608" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="609" spans="1:3">
@@ -13439,7 +13433,7 @@
         <v>632</v>
       </c>
       <c r="C609" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="610" spans="1:3">
@@ -13450,7 +13444,7 @@
         <v>633</v>
       </c>
       <c r="C610" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="611" spans="1:3">
@@ -13461,7 +13455,7 @@
         <v>634</v>
       </c>
       <c r="C611" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="612" spans="1:3">
@@ -13472,7 +13466,7 @@
         <v>635</v>
       </c>
       <c r="C612" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="613" spans="1:3">
@@ -13483,7 +13477,7 @@
         <v>636</v>
       </c>
       <c r="C613" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="614" spans="1:3">
@@ -13494,7 +13488,7 @@
         <v>637</v>
       </c>
       <c r="C614" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="615" spans="1:3">
@@ -13505,7 +13499,7 @@
         <v>638</v>
       </c>
       <c r="C615" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="616" spans="1:3">
@@ -13516,7 +13510,7 @@
         <v>639</v>
       </c>
       <c r="C616" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="617" spans="1:3">
@@ -13527,7 +13521,7 @@
         <v>640</v>
       </c>
       <c r="C617" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="618" spans="1:3">
@@ -13538,7 +13532,7 @@
         <v>641</v>
       </c>
       <c r="C618" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="619" spans="1:3">
@@ -13549,7 +13543,7 @@
         <v>642</v>
       </c>
       <c r="C619" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="620" spans="1:3">
@@ -13560,7 +13554,7 @@
         <v>643</v>
       </c>
       <c r="C620" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="621" spans="1:3">
@@ -13571,7 +13565,7 @@
         <v>644</v>
       </c>
       <c r="C621" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="622" spans="1:3">
@@ -13582,18 +13576,18 @@
         <v>645</v>
       </c>
       <c r="C622" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="623" spans="1:3">
       <c r="A623" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B623" t="s">
         <v>646</v>
       </c>
       <c r="C623" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="624" spans="1:3">
@@ -13604,7 +13598,7 @@
         <v>647</v>
       </c>
       <c r="C624" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="625" spans="1:3">
@@ -13615,7 +13609,7 @@
         <v>648</v>
       </c>
       <c r="C625" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="626" spans="1:3">
@@ -13626,7 +13620,7 @@
         <v>649</v>
       </c>
       <c r="C626" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="627" spans="1:3">
@@ -13637,7 +13631,7 @@
         <v>650</v>
       </c>
       <c r="C627" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="628" spans="1:3">
@@ -13648,7 +13642,7 @@
         <v>651</v>
       </c>
       <c r="C628" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="629" spans="1:3">
@@ -13659,7 +13653,7 @@
         <v>652</v>
       </c>
       <c r="C629" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="630" spans="1:3">
@@ -13670,7 +13664,7 @@
         <v>653</v>
       </c>
       <c r="C630" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="631" spans="1:3">
@@ -13681,7 +13675,7 @@
         <v>654</v>
       </c>
       <c r="C631" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="632" spans="1:3">
@@ -13692,7 +13686,7 @@
         <v>655</v>
       </c>
       <c r="C632" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="633" spans="1:3">
@@ -13703,18 +13697,18 @@
         <v>656</v>
       </c>
       <c r="C633" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="634" spans="1:3">
       <c r="A634" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B634" t="s">
         <v>657</v>
       </c>
       <c r="C634" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="635" spans="1:3">
@@ -13725,7 +13719,7 @@
         <v>658</v>
       </c>
       <c r="C635" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="636" spans="1:3">
@@ -13736,7 +13730,7 @@
         <v>659</v>
       </c>
       <c r="C636" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="637" spans="1:3">
@@ -13747,7 +13741,7 @@
         <v>660</v>
       </c>
       <c r="C637" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="638" spans="1:3">
@@ -13758,7 +13752,7 @@
         <v>661</v>
       </c>
       <c r="C638" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="639" spans="1:3">
@@ -13769,7 +13763,7 @@
         <v>662</v>
       </c>
       <c r="C639" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="640" spans="1:3">
@@ -13780,7 +13774,7 @@
         <v>663</v>
       </c>
       <c r="C640" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="641" spans="1:3">
@@ -13791,7 +13785,7 @@
         <v>664</v>
       </c>
       <c r="C641" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="642" spans="1:3">
@@ -13802,7 +13796,7 @@
         <v>665</v>
       </c>
       <c r="C642" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="643" spans="1:3">
@@ -13813,7 +13807,7 @@
         <v>666</v>
       </c>
       <c r="C643" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="644" spans="1:3">
@@ -13824,7 +13818,7 @@
         <v>667</v>
       </c>
       <c r="C644" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="645" spans="1:3">
@@ -13835,7 +13829,7 @@
         <v>668</v>
       </c>
       <c r="C645" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="646" spans="1:3">
@@ -13846,7 +13840,7 @@
         <v>669</v>
       </c>
       <c r="C646" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="647" spans="1:3">
@@ -13857,7 +13851,7 @@
         <v>670</v>
       </c>
       <c r="C647" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="648" spans="1:3">
@@ -13868,7 +13862,7 @@
         <v>671</v>
       </c>
       <c r="C648" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="649" spans="1:3">
@@ -13879,7 +13873,7 @@
         <v>672</v>
       </c>
       <c r="C649" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="650" spans="1:3">
@@ -13890,7 +13884,7 @@
         <v>673</v>
       </c>
       <c r="C650" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="651" spans="1:3">
@@ -13901,7 +13895,7 @@
         <v>674</v>
       </c>
       <c r="C651" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="652" spans="1:3">
@@ -13912,7 +13906,7 @@
         <v>675</v>
       </c>
       <c r="C652" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="653" spans="1:3">
@@ -13923,7 +13917,7 @@
         <v>676</v>
       </c>
       <c r="C653" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="654" spans="1:3">
@@ -13934,7 +13928,7 @@
         <v>677</v>
       </c>
       <c r="C654" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="655" spans="1:3">
@@ -13945,7 +13939,7 @@
         <v>678</v>
       </c>
       <c r="C655" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="656" spans="1:3">
@@ -13956,7 +13950,7 @@
         <v>679</v>
       </c>
       <c r="C656" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="657" spans="1:3">
@@ -13967,7 +13961,7 @@
         <v>680</v>
       </c>
       <c r="C657" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="658" spans="1:3">
@@ -13978,18 +13972,18 @@
         <v>681</v>
       </c>
       <c r="C658" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="659" spans="1:3">
       <c r="A659" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B659" t="s">
         <v>682</v>
       </c>
       <c r="C659" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="660" spans="1:3">
@@ -14000,7 +13994,7 @@
         <v>683</v>
       </c>
       <c r="C660" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="661" spans="1:3">
@@ -14011,7 +14005,7 @@
         <v>684</v>
       </c>
       <c r="C661" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="662" spans="1:3">
@@ -14022,7 +14016,7 @@
         <v>685</v>
       </c>
       <c r="C662" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="663" spans="1:3">
@@ -14033,7 +14027,7 @@
         <v>686</v>
       </c>
       <c r="C663" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="664" spans="1:3">
@@ -14044,7 +14038,7 @@
         <v>687</v>
       </c>
       <c r="C664" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="665" spans="1:3">
@@ -14055,7 +14049,7 @@
         <v>688</v>
       </c>
       <c r="C665" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="666" spans="1:3">
@@ -14066,7 +14060,7 @@
         <v>689</v>
       </c>
       <c r="C666" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="667" spans="1:3">
@@ -14077,7 +14071,7 @@
         <v>690</v>
       </c>
       <c r="C667" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="668" spans="1:3">
@@ -14088,7 +14082,7 @@
         <v>691</v>
       </c>
       <c r="C668" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="669" spans="1:3">
@@ -14099,7 +14093,7 @@
         <v>692</v>
       </c>
       <c r="C669" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="670" spans="1:3">
@@ -14110,7 +14104,7 @@
         <v>693</v>
       </c>
       <c r="C670" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="671" spans="1:3">
@@ -14121,7 +14115,7 @@
         <v>694</v>
       </c>
       <c r="C671" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="672" spans="1:3">
@@ -14132,7 +14126,7 @@
         <v>695</v>
       </c>
       <c r="C672" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="673" spans="1:3">
@@ -14143,7 +14137,7 @@
         <v>696</v>
       </c>
       <c r="C673" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="674" spans="1:3">
@@ -14154,18 +14148,18 @@
         <v>697</v>
       </c>
       <c r="C674" t="s">
-        <v>1743</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="675" spans="1:3">
       <c r="A675" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B675" t="s">
         <v>698</v>
       </c>
       <c r="C675" t="s">
-        <v>1170</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="676" spans="1:3">
@@ -14176,7 +14170,7 @@
         <v>699</v>
       </c>
       <c r="C676" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="677" spans="1:3">
@@ -14187,7 +14181,7 @@
         <v>700</v>
       </c>
       <c r="C677" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="678" spans="1:3">
@@ -14198,7 +14192,7 @@
         <v>701</v>
       </c>
       <c r="C678" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="679" spans="1:3">
@@ -14209,7 +14203,7 @@
         <v>702</v>
       </c>
       <c r="C679" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="680" spans="1:3">
@@ -14220,7 +14214,7 @@
         <v>703</v>
       </c>
       <c r="C680" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="681" spans="1:3">
@@ -14231,7 +14225,7 @@
         <v>704</v>
       </c>
       <c r="C681" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="682" spans="1:3">
@@ -14242,7 +14236,7 @@
         <v>705</v>
       </c>
       <c r="C682" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="683" spans="1:3">
@@ -14253,7 +14247,7 @@
         <v>706</v>
       </c>
       <c r="C683" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="684" spans="1:3">
@@ -14264,7 +14258,7 @@
         <v>707</v>
       </c>
       <c r="C684" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="685" spans="1:3">
@@ -14275,7 +14269,7 @@
         <v>708</v>
       </c>
       <c r="C685" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="686" spans="1:3">
@@ -14286,7 +14280,7 @@
         <v>709</v>
       </c>
       <c r="C686" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="687" spans="1:3">
@@ -14297,7 +14291,7 @@
         <v>710</v>
       </c>
       <c r="C687" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="688" spans="1:3">
@@ -14308,7 +14302,7 @@
         <v>711</v>
       </c>
       <c r="C688" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="689" spans="1:3">
@@ -14319,7 +14313,7 @@
         <v>712</v>
       </c>
       <c r="C689" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="690" spans="1:3">
@@ -14330,7 +14324,7 @@
         <v>713</v>
       </c>
       <c r="C690" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="691" spans="1:3">
@@ -14341,7 +14335,7 @@
         <v>714</v>
       </c>
       <c r="C691" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="692" spans="1:3">
@@ -14352,7 +14346,7 @@
         <v>715</v>
       </c>
       <c r="C692" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="693" spans="1:3">
@@ -14363,7 +14357,7 @@
         <v>716</v>
       </c>
       <c r="C693" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="694" spans="1:3">
@@ -14374,7 +14368,7 @@
         <v>717</v>
       </c>
       <c r="C694" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="695" spans="1:3">
@@ -14385,7 +14379,7 @@
         <v>718</v>
       </c>
       <c r="C695" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="696" spans="1:3">
@@ -14396,7 +14390,7 @@
         <v>719</v>
       </c>
       <c r="C696" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="697" spans="1:3">
@@ -14407,7 +14401,7 @@
         <v>720</v>
       </c>
       <c r="C697" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="698" spans="1:3">
@@ -14418,7 +14412,7 @@
         <v>721</v>
       </c>
       <c r="C698" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="699" spans="1:3">
@@ -14429,7 +14423,7 @@
         <v>722</v>
       </c>
       <c r="C699" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="700" spans="1:3">
@@ -14440,7 +14434,7 @@
         <v>723</v>
       </c>
       <c r="C700" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="701" spans="1:3">
@@ -14451,7 +14445,7 @@
         <v>724</v>
       </c>
       <c r="C701" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="702" spans="1:3">
@@ -14462,7 +14456,7 @@
         <v>725</v>
       </c>
       <c r="C702" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="703" spans="1:3">
@@ -14473,7 +14467,7 @@
         <v>726</v>
       </c>
       <c r="C703" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="704" spans="1:3">
@@ -14484,7 +14478,7 @@
         <v>727</v>
       </c>
       <c r="C704" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="705" spans="1:3">
@@ -14495,7 +14489,7 @@
         <v>728</v>
       </c>
       <c r="C705" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="706" spans="1:3">
@@ -14506,7 +14500,7 @@
         <v>729</v>
       </c>
       <c r="C706" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="707" spans="1:3">
@@ -14517,7 +14511,7 @@
         <v>730</v>
       </c>
       <c r="C707" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="708" spans="1:3">
@@ -14528,7 +14522,7 @@
         <v>731</v>
       </c>
       <c r="C708" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="709" spans="1:3">
@@ -14539,7 +14533,7 @@
         <v>732</v>
       </c>
       <c r="C709" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="710" spans="1:3">
@@ -14550,7 +14544,7 @@
         <v>733</v>
       </c>
       <c r="C710" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="711" spans="1:3">
@@ -14561,7 +14555,7 @@
         <v>734</v>
       </c>
       <c r="C711" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="712" spans="1:3">
@@ -14572,7 +14566,7 @@
         <v>735</v>
       </c>
       <c r="C712" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="713" spans="1:3">
@@ -14583,7 +14577,7 @@
         <v>736</v>
       </c>
       <c r="C713" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="714" spans="1:3">
@@ -14594,7 +14588,7 @@
         <v>737</v>
       </c>
       <c r="C714" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="715" spans="1:3">
@@ -14605,29 +14599,29 @@
         <v>738</v>
       </c>
       <c r="C715" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="716" spans="1:3">
       <c r="A716" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B716" t="s">
         <v>739</v>
       </c>
       <c r="C716" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="717" spans="1:3">
       <c r="A717" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B717" t="s">
         <v>740</v>
       </c>
       <c r="C717" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="718" spans="1:3">
@@ -14638,7 +14632,7 @@
         <v>741</v>
       </c>
       <c r="C718" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="719" spans="1:3">
@@ -14649,7 +14643,7 @@
         <v>742</v>
       </c>
       <c r="C719" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="720" spans="1:3">
@@ -14660,7 +14654,7 @@
         <v>743</v>
       </c>
       <c r="C720" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="721" spans="1:3">
@@ -14671,7 +14665,7 @@
         <v>744</v>
       </c>
       <c r="C721" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="722" spans="1:3">
@@ -14682,7 +14676,7 @@
         <v>745</v>
       </c>
       <c r="C722" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="723" spans="1:3">
@@ -14693,7 +14687,7 @@
         <v>746</v>
       </c>
       <c r="C723" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="724" spans="1:3">
@@ -14704,18 +14698,18 @@
         <v>747</v>
       </c>
       <c r="C724" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="725" spans="1:3">
       <c r="A725" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B725" t="s">
         <v>748</v>
       </c>
       <c r="C725" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="726" spans="1:3">
@@ -14726,7 +14720,7 @@
         <v>749</v>
       </c>
       <c r="C726" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="727" spans="1:3">
@@ -14737,7 +14731,7 @@
         <v>750</v>
       </c>
       <c r="C727" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="728" spans="1:3">
@@ -14748,7 +14742,7 @@
         <v>751</v>
       </c>
       <c r="C728" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="729" spans="1:3">
@@ -14759,7 +14753,7 @@
         <v>752</v>
       </c>
       <c r="C729" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="730" spans="1:3">
@@ -14770,7 +14764,7 @@
         <v>753</v>
       </c>
       <c r="C730" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="731" spans="1:3">
@@ -14781,7 +14775,7 @@
         <v>754</v>
       </c>
       <c r="C731" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="732" spans="1:3">
@@ -14792,7 +14786,7 @@
         <v>755</v>
       </c>
       <c r="C732" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="733" spans="1:3">
@@ -14803,7 +14797,7 @@
         <v>756</v>
       </c>
       <c r="C733" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="734" spans="1:3">
@@ -14814,7 +14808,7 @@
         <v>757</v>
       </c>
       <c r="C734" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="735" spans="1:3">
@@ -14825,7 +14819,7 @@
         <v>758</v>
       </c>
       <c r="C735" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="736" spans="1:3">
@@ -14836,7 +14830,7 @@
         <v>759</v>
       </c>
       <c r="C736" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="737" spans="1:3">
@@ -14847,7 +14841,7 @@
         <v>760</v>
       </c>
       <c r="C737" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="738" spans="1:3">
@@ -14858,7 +14852,7 @@
         <v>761</v>
       </c>
       <c r="C738" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="739" spans="1:3">
@@ -14869,7 +14863,7 @@
         <v>762</v>
       </c>
       <c r="C739" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="740" spans="1:3">
@@ -14880,7 +14874,7 @@
         <v>763</v>
       </c>
       <c r="C740" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="741" spans="1:3">
@@ -14891,7 +14885,7 @@
         <v>764</v>
       </c>
       <c r="C741" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="742" spans="1:3">
@@ -14902,7 +14896,7 @@
         <v>765</v>
       </c>
       <c r="C742" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="743" spans="1:3">
@@ -14913,7 +14907,7 @@
         <v>766</v>
       </c>
       <c r="C743" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="744" spans="1:3">
@@ -14924,7 +14918,7 @@
         <v>767</v>
       </c>
       <c r="C744" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="745" spans="1:3">
@@ -14935,7 +14929,7 @@
         <v>768</v>
       </c>
       <c r="C745" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="746" spans="1:3">
@@ -14946,7 +14940,7 @@
         <v>769</v>
       </c>
       <c r="C746" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="747" spans="1:3">
@@ -14957,7 +14951,7 @@
         <v>770</v>
       </c>
       <c r="C747" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="748" spans="1:3">
@@ -14968,7 +14962,7 @@
         <v>771</v>
       </c>
       <c r="C748" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="749" spans="1:3">
@@ -14979,7 +14973,7 @@
         <v>772</v>
       </c>
       <c r="C749" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="750" spans="1:3">
@@ -14990,7 +14984,7 @@
         <v>773</v>
       </c>
       <c r="C750" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="751" spans="1:3">
@@ -15001,7 +14995,7 @@
         <v>774</v>
       </c>
       <c r="C751" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="752" spans="1:3">
@@ -15012,7 +15006,7 @@
         <v>775</v>
       </c>
       <c r="C752" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="753" spans="1:3">
@@ -15023,7 +15017,7 @@
         <v>776</v>
       </c>
       <c r="C753" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="754" spans="1:3">
@@ -15034,7 +15028,7 @@
         <v>777</v>
       </c>
       <c r="C754" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="755" spans="1:3">
@@ -15045,7 +15039,7 @@
         <v>778</v>
       </c>
       <c r="C755" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="756" spans="1:3">
@@ -15056,7 +15050,7 @@
         <v>779</v>
       </c>
       <c r="C756" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="757" spans="1:3">
@@ -15067,7 +15061,7 @@
         <v>780</v>
       </c>
       <c r="C757" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="758" spans="1:3">
@@ -15078,7 +15072,7 @@
         <v>781</v>
       </c>
       <c r="C758" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="759" spans="1:3">
@@ -15089,7 +15083,7 @@
         <v>782</v>
       </c>
       <c r="C759" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="760" spans="1:3">
@@ -15100,7 +15094,7 @@
         <v>783</v>
       </c>
       <c r="C760" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="761" spans="1:3">
@@ -15111,7 +15105,7 @@
         <v>784</v>
       </c>
       <c r="C761" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="762" spans="1:3">
@@ -15122,7 +15116,7 @@
         <v>785</v>
       </c>
       <c r="C762" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="763" spans="1:3">
@@ -15133,7 +15127,7 @@
         <v>786</v>
       </c>
       <c r="C763" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="764" spans="1:3">
@@ -15144,7 +15138,7 @@
         <v>787</v>
       </c>
       <c r="C764" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="765" spans="1:3">
@@ -15155,7 +15149,7 @@
         <v>788</v>
       </c>
       <c r="C765" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="766" spans="1:3">
@@ -15166,7 +15160,7 @@
         <v>789</v>
       </c>
       <c r="C766" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="767" spans="1:3">
@@ -15177,7 +15171,7 @@
         <v>790</v>
       </c>
       <c r="C767" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="768" spans="1:3">
@@ -15188,7 +15182,7 @@
         <v>791</v>
       </c>
       <c r="C768" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="769" spans="1:3">
@@ -15199,7 +15193,7 @@
         <v>792</v>
       </c>
       <c r="C769" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="770" spans="1:3">
@@ -15210,7 +15204,7 @@
         <v>793</v>
       </c>
       <c r="C770" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="771" spans="1:3">
@@ -15221,7 +15215,7 @@
         <v>794</v>
       </c>
       <c r="C771" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="772" spans="1:3">
@@ -15232,7 +15226,7 @@
         <v>795</v>
       </c>
       <c r="C772" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="773" spans="1:3">
@@ -15243,7 +15237,7 @@
         <v>796</v>
       </c>
       <c r="C773" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="774" spans="1:3">
@@ -15254,7 +15248,7 @@
         <v>797</v>
       </c>
       <c r="C774" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="775" spans="1:3">
@@ -15265,7 +15259,7 @@
         <v>798</v>
       </c>
       <c r="C775" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="776" spans="1:3">
@@ -15276,7 +15270,7 @@
         <v>799</v>
       </c>
       <c r="C776" t="s">
-        <v>1844</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="777" spans="1:3">
@@ -15287,7 +15281,7 @@
         <v>800</v>
       </c>
       <c r="C777" t="s">
-        <v>1767</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="778" spans="1:3">
@@ -15298,7 +15292,7 @@
         <v>801</v>
       </c>
       <c r="C778" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="779" spans="1:3">
@@ -15309,7 +15303,7 @@
         <v>802</v>
       </c>
       <c r="C779" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="780" spans="1:3">
@@ -15320,7 +15314,7 @@
         <v>803</v>
       </c>
       <c r="C780" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="781" spans="1:3">
@@ -15331,7 +15325,7 @@
         <v>804</v>
       </c>
       <c r="C781" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="782" spans="1:3">
@@ -15342,7 +15336,7 @@
         <v>805</v>
       </c>
       <c r="C782" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="783" spans="1:3">
@@ -15353,7 +15347,7 @@
         <v>806</v>
       </c>
       <c r="C783" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="784" spans="1:3">
@@ -15364,7 +15358,7 @@
         <v>807</v>
       </c>
       <c r="C784" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="785" spans="1:3">
@@ -15375,7 +15369,7 @@
         <v>808</v>
       </c>
       <c r="C785" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="786" spans="1:3">
@@ -15386,7 +15380,7 @@
         <v>809</v>
       </c>
       <c r="C786" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="787" spans="1:3">
@@ -15397,7 +15391,7 @@
         <v>810</v>
       </c>
       <c r="C787" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="788" spans="1:3">
@@ -15408,7 +15402,7 @@
         <v>811</v>
       </c>
       <c r="C788" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="789" spans="1:3">
@@ -15419,7 +15413,7 @@
         <v>812</v>
       </c>
       <c r="C789" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="790" spans="1:3">
@@ -15430,7 +15424,7 @@
         <v>813</v>
       </c>
       <c r="C790" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="791" spans="1:3">
@@ -15441,7 +15435,7 @@
         <v>814</v>
       </c>
       <c r="C791" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="792" spans="1:3">
@@ -15452,7 +15446,7 @@
         <v>815</v>
       </c>
       <c r="C792" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="793" spans="1:3">
@@ -15463,7 +15457,7 @@
         <v>816</v>
       </c>
       <c r="C793" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="794" spans="1:3">
@@ -15474,7 +15468,7 @@
         <v>817</v>
       </c>
       <c r="C794" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="795" spans="1:3">
@@ -15485,7 +15479,7 @@
         <v>818</v>
       </c>
       <c r="C795" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="796" spans="1:3">
@@ -15496,7 +15490,7 @@
         <v>819</v>
       </c>
       <c r="C796" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="797" spans="1:3">
@@ -15507,7 +15501,7 @@
         <v>820</v>
       </c>
       <c r="C797" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="798" spans="1:3">
@@ -15518,7 +15512,7 @@
         <v>821</v>
       </c>
       <c r="C798" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="799" spans="1:3">
@@ -15529,7 +15523,7 @@
         <v>822</v>
       </c>
       <c r="C799" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="800" spans="1:3">
@@ -15540,7 +15534,7 @@
         <v>823</v>
       </c>
       <c r="C800" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="801" spans="1:3">
@@ -15551,7 +15545,7 @@
         <v>824</v>
       </c>
       <c r="C801" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="802" spans="1:3">
@@ -15562,7 +15556,7 @@
         <v>825</v>
       </c>
       <c r="C802" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="803" spans="1:3">
@@ -15573,7 +15567,7 @@
         <v>826</v>
       </c>
       <c r="C803" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="804" spans="1:3">
@@ -15584,7 +15578,7 @@
         <v>827</v>
       </c>
       <c r="C804" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="805" spans="1:3">
@@ -15595,7 +15589,7 @@
         <v>828</v>
       </c>
       <c r="C805" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="806" spans="1:3">
@@ -15606,7 +15600,7 @@
         <v>829</v>
       </c>
       <c r="C806" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="807" spans="1:3">
@@ -15617,7 +15611,7 @@
         <v>830</v>
       </c>
       <c r="C807" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="808" spans="1:3">
@@ -15628,7 +15622,7 @@
         <v>831</v>
       </c>
       <c r="C808" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="809" spans="1:3">
@@ -15639,7 +15633,7 @@
         <v>832</v>
       </c>
       <c r="C809" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="810" spans="1:3">
@@ -15650,7 +15644,7 @@
         <v>833</v>
       </c>
       <c r="C810" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="811" spans="1:3">
@@ -15661,7 +15655,7 @@
         <v>834</v>
       </c>
       <c r="C811" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="812" spans="1:3">
@@ -15672,7 +15666,7 @@
         <v>835</v>
       </c>
       <c r="C812" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="813" spans="1:3">
@@ -15683,7 +15677,7 @@
         <v>836</v>
       </c>
       <c r="C813" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="814" spans="1:3">
@@ -15694,7 +15688,7 @@
         <v>837</v>
       </c>
       <c r="C814" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="815" spans="1:3">
@@ -15705,7 +15699,7 @@
         <v>838</v>
       </c>
       <c r="C815" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="816" spans="1:3">
@@ -15716,7 +15710,7 @@
         <v>839</v>
       </c>
       <c r="C816" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="817" spans="1:3">
@@ -15727,7 +15721,7 @@
         <v>840</v>
       </c>
       <c r="C817" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="818" spans="1:3">
@@ -15738,7 +15732,7 @@
         <v>841</v>
       </c>
       <c r="C818" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="819" spans="1:3">
@@ -15749,7 +15743,7 @@
         <v>842</v>
       </c>
       <c r="C819" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="820" spans="1:3">
@@ -15760,7 +15754,7 @@
         <v>843</v>
       </c>
       <c r="C820" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="821" spans="1:3">
@@ -15771,7 +15765,7 @@
         <v>844</v>
       </c>
       <c r="C821" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="822" spans="1:3">
@@ -15782,7 +15776,7 @@
         <v>845</v>
       </c>
       <c r="C822" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="823" spans="1:3">
@@ -15793,7 +15787,7 @@
         <v>846</v>
       </c>
       <c r="C823" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="824" spans="1:3">
@@ -15804,7 +15798,7 @@
         <v>847</v>
       </c>
       <c r="C824" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="825" spans="1:3">
@@ -15815,7 +15809,7 @@
         <v>848</v>
       </c>
       <c r="C825" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="826" spans="1:3">
@@ -15826,7 +15820,7 @@
         <v>849</v>
       </c>
       <c r="C826" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="827" spans="1:3">
@@ -15837,7 +15831,7 @@
         <v>850</v>
       </c>
       <c r="C827" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="828" spans="1:3">
@@ -15848,7 +15842,7 @@
         <v>851</v>
       </c>
       <c r="C828" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="829" spans="1:3">
@@ -15859,7 +15853,7 @@
         <v>852</v>
       </c>
       <c r="C829" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="830" spans="1:3">
@@ -15870,7 +15864,7 @@
         <v>853</v>
       </c>
       <c r="C830" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="831" spans="1:3">
@@ -15881,7 +15875,7 @@
         <v>854</v>
       </c>
       <c r="C831" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="832" spans="1:3">
@@ -15892,7 +15886,7 @@
         <v>855</v>
       </c>
       <c r="C832" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="833" spans="1:3">
@@ -15903,7 +15897,7 @@
         <v>856</v>
       </c>
       <c r="C833" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="834" spans="1:3">
@@ -15914,7 +15908,7 @@
         <v>857</v>
       </c>
       <c r="C834" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="835" spans="1:3">
@@ -15925,7 +15919,7 @@
         <v>858</v>
       </c>
       <c r="C835" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="836" spans="1:3">
@@ -15936,7 +15930,7 @@
         <v>859</v>
       </c>
       <c r="C836" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="837" spans="1:3">
@@ -15947,7 +15941,7 @@
         <v>860</v>
       </c>
       <c r="C837" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="838" spans="1:3">
@@ -15958,7 +15952,7 @@
         <v>861</v>
       </c>
       <c r="C838" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="839" spans="1:3">
@@ -15969,7 +15963,7 @@
         <v>862</v>
       </c>
       <c r="C839" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="840" spans="1:3">
@@ -15980,7 +15974,7 @@
         <v>863</v>
       </c>
       <c r="C840" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="841" spans="1:3">
@@ -15991,7 +15985,7 @@
         <v>864</v>
       </c>
       <c r="C841" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="842" spans="1:3">
@@ -16002,7 +15996,7 @@
         <v>865</v>
       </c>
       <c r="C842" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="843" spans="1:3">
@@ -16013,7 +16007,7 @@
         <v>866</v>
       </c>
       <c r="C843" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="844" spans="1:3">
@@ -16024,7 +16018,7 @@
         <v>867</v>
       </c>
       <c r="C844" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="845" spans="1:3">
@@ -16035,7 +16029,7 @@
         <v>868</v>
       </c>
       <c r="C845" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="846" spans="1:3">
@@ -16046,7 +16040,7 @@
         <v>869</v>
       </c>
       <c r="C846" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="847" spans="1:3">
@@ -16057,18 +16051,18 @@
         <v>870</v>
       </c>
       <c r="C847" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="848" spans="1:3">
       <c r="A848" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B848" t="s">
         <v>871</v>
       </c>
       <c r="C848" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="849" spans="1:3">
@@ -16079,7 +16073,7 @@
         <v>872</v>
       </c>
       <c r="C849" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="850" spans="1:3">
@@ -16090,7 +16084,7 @@
         <v>873</v>
       </c>
       <c r="C850" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="851" spans="1:3">
@@ -16101,7 +16095,7 @@
         <v>874</v>
       </c>
       <c r="C851" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="852" spans="1:3">
@@ -16112,7 +16106,7 @@
         <v>875</v>
       </c>
       <c r="C852" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="853" spans="1:3">
@@ -16123,7 +16117,7 @@
         <v>876</v>
       </c>
       <c r="C853" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="854" spans="1:3">
@@ -16134,7 +16128,7 @@
         <v>877</v>
       </c>
       <c r="C854" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="855" spans="1:3">
@@ -16145,7 +16139,7 @@
         <v>878</v>
       </c>
       <c r="C855" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="856" spans="1:3">
@@ -16156,7 +16150,7 @@
         <v>879</v>
       </c>
       <c r="C856" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="857" spans="1:3">
@@ -16167,7 +16161,7 @@
         <v>880</v>
       </c>
       <c r="C857" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="858" spans="1:3">
@@ -16178,7 +16172,7 @@
         <v>881</v>
       </c>
       <c r="C858" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="859" spans="1:3">
@@ -16189,7 +16183,7 @@
         <v>882</v>
       </c>
       <c r="C859" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="860" spans="1:3">
@@ -16200,7 +16194,7 @@
         <v>883</v>
       </c>
       <c r="C860" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="861" spans="1:3">
@@ -16211,7 +16205,7 @@
         <v>884</v>
       </c>
       <c r="C861" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="862" spans="1:3">
@@ -16222,7 +16216,7 @@
         <v>885</v>
       </c>
       <c r="C862" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="863" spans="1:3">
@@ -16233,7 +16227,7 @@
         <v>886</v>
       </c>
       <c r="C863" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="864" spans="1:3">
@@ -16244,7 +16238,7 @@
         <v>887</v>
       </c>
       <c r="C864" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="865" spans="1:3">
@@ -16255,7 +16249,7 @@
         <v>888</v>
       </c>
       <c r="C865" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="866" spans="1:3">
@@ -16266,7 +16260,7 @@
         <v>889</v>
       </c>
       <c r="C866" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="867" spans="1:3">
@@ -16277,7 +16271,7 @@
         <v>890</v>
       </c>
       <c r="C867" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="868" spans="1:3">
@@ -16288,7 +16282,7 @@
         <v>891</v>
       </c>
       <c r="C868" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="869" spans="1:3">
@@ -16299,7 +16293,7 @@
         <v>892</v>
       </c>
       <c r="C869" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="870" spans="1:3">
@@ -16310,7 +16304,7 @@
         <v>893</v>
       </c>
       <c r="C870" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="871" spans="1:3">
@@ -16321,7 +16315,7 @@
         <v>894</v>
       </c>
       <c r="C871" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="872" spans="1:3">
@@ -16332,7 +16326,7 @@
         <v>895</v>
       </c>
       <c r="C872" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="873" spans="1:3">
@@ -16343,7 +16337,7 @@
         <v>896</v>
       </c>
       <c r="C873" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="874" spans="1:3">
@@ -16354,7 +16348,7 @@
         <v>897</v>
       </c>
       <c r="C874" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="875" spans="1:3">
@@ -16365,7 +16359,7 @@
         <v>898</v>
       </c>
       <c r="C875" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="876" spans="1:3">
@@ -16376,7 +16370,7 @@
         <v>899</v>
       </c>
       <c r="C876" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="877" spans="1:3">
@@ -16387,7 +16381,7 @@
         <v>900</v>
       </c>
       <c r="C877" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="878" spans="1:3">
@@ -16398,7 +16392,7 @@
         <v>901</v>
       </c>
       <c r="C878" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="879" spans="1:3">
@@ -16409,7 +16403,7 @@
         <v>902</v>
       </c>
       <c r="C879" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="880" spans="1:3">
@@ -16420,7 +16414,7 @@
         <v>903</v>
       </c>
       <c r="C880" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="881" spans="1:3">
@@ -16431,7 +16425,7 @@
         <v>904</v>
       </c>
       <c r="C881" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="882" spans="1:3">
@@ -16442,7 +16436,7 @@
         <v>905</v>
       </c>
       <c r="C882" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="883" spans="1:3">
@@ -16453,7 +16447,7 @@
         <v>906</v>
       </c>
       <c r="C883" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="884" spans="1:3">
@@ -16464,7 +16458,7 @@
         <v>907</v>
       </c>
       <c r="C884" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="885" spans="1:3">
@@ -16475,7 +16469,7 @@
         <v>908</v>
       </c>
       <c r="C885" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="886" spans="1:3">
@@ -16486,7 +16480,7 @@
         <v>909</v>
       </c>
       <c r="C886" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="887" spans="1:3">
@@ -16497,7 +16491,7 @@
         <v>910</v>
       </c>
       <c r="C887" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="888" spans="1:3">
@@ -16508,7 +16502,7 @@
         <v>911</v>
       </c>
       <c r="C888" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="889" spans="1:3">
@@ -16519,7 +16513,7 @@
         <v>912</v>
       </c>
       <c r="C889" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="890" spans="1:3">
@@ -16530,7 +16524,7 @@
         <v>913</v>
       </c>
       <c r="C890" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="891" spans="1:3">
@@ -16541,7 +16535,7 @@
         <v>914</v>
       </c>
       <c r="C891" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="892" spans="1:3">
@@ -16552,7 +16546,7 @@
         <v>915</v>
       </c>
       <c r="C892" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="893" spans="1:3">
@@ -16563,7 +16557,7 @@
         <v>916</v>
       </c>
       <c r="C893" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="894" spans="1:3">
@@ -16574,7 +16568,7 @@
         <v>917</v>
       </c>
       <c r="C894" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="895" spans="1:3">
@@ -16585,7 +16579,7 @@
         <v>918</v>
       </c>
       <c r="C895" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="896" spans="1:3">
@@ -16596,7 +16590,7 @@
         <v>919</v>
       </c>
       <c r="C896" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="897" spans="1:3">
@@ -16607,7 +16601,7 @@
         <v>920</v>
       </c>
       <c r="C897" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="898" spans="1:3">
@@ -16618,7 +16612,7 @@
         <v>921</v>
       </c>
       <c r="C898" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="899" spans="1:3">
@@ -16629,7 +16623,7 @@
         <v>922</v>
       </c>
       <c r="C899" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="900" spans="1:3">
@@ -16640,7 +16634,7 @@
         <v>923</v>
       </c>
       <c r="C900" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="901" spans="1:3">
@@ -16651,7 +16645,7 @@
         <v>924</v>
       </c>
       <c r="C901" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="902" spans="1:3">
@@ -16662,7 +16656,7 @@
         <v>925</v>
       </c>
       <c r="C902" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="903" spans="1:3">
@@ -16673,7 +16667,7 @@
         <v>926</v>
       </c>
       <c r="C903" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="904" spans="1:3">
@@ -16684,7 +16678,7 @@
         <v>927</v>
       </c>
       <c r="C904" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="905" spans="1:3">
@@ -16695,7 +16689,7 @@
         <v>928</v>
       </c>
       <c r="C905" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="906" spans="1:3">
@@ -16706,7 +16700,7 @@
         <v>929</v>
       </c>
       <c r="C906" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="907" spans="1:3">
@@ -16717,7 +16711,7 @@
         <v>930</v>
       </c>
       <c r="C907" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="908" spans="1:3">
@@ -16728,7 +16722,7 @@
         <v>931</v>
       </c>
       <c r="C908" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="909" spans="1:3">
@@ -16739,7 +16733,7 @@
         <v>932</v>
       </c>
       <c r="C909" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="910" spans="1:3">
@@ -16750,7 +16744,7 @@
         <v>933</v>
       </c>
       <c r="C910" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="911" spans="1:3">
@@ -16761,7 +16755,7 @@
         <v>934</v>
       </c>
       <c r="C911" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="912" spans="1:3">
@@ -16772,7 +16766,7 @@
         <v>935</v>
       </c>
       <c r="C912" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="913" spans="1:3">
@@ -16783,7 +16777,7 @@
         <v>936</v>
       </c>
       <c r="C913" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="914" spans="1:3">
@@ -16794,7 +16788,7 @@
         <v>937</v>
       </c>
       <c r="C914" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="915" spans="1:3">
@@ -16805,7 +16799,7 @@
         <v>938</v>
       </c>
       <c r="C915" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="916" spans="1:3">
@@ -16816,7 +16810,7 @@
         <v>939</v>
       </c>
       <c r="C916" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="917" spans="1:3">
@@ -16827,7 +16821,7 @@
         <v>940</v>
       </c>
       <c r="C917" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="918" spans="1:3">
@@ -16838,7 +16832,7 @@
         <v>941</v>
       </c>
       <c r="C918" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="919" spans="1:3">
@@ -16849,7 +16843,7 @@
         <v>942</v>
       </c>
       <c r="C919" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="920" spans="1:3">
@@ -16860,7 +16854,7 @@
         <v>943</v>
       </c>
       <c r="C920" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="921" spans="1:3">
@@ -16871,7 +16865,7 @@
         <v>944</v>
       </c>
       <c r="C921" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="922" spans="1:3">
@@ -16882,7 +16876,7 @@
         <v>945</v>
       </c>
       <c r="C922" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="923" spans="1:3">
@@ -16893,7 +16887,7 @@
         <v>946</v>
       </c>
       <c r="C923" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="924" spans="1:3">
@@ -16904,7 +16898,7 @@
         <v>947</v>
       </c>
       <c r="C924" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="925" spans="1:3">
@@ -16915,7 +16909,7 @@
         <v>948</v>
       </c>
       <c r="C925" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="926" spans="1:3">
@@ -16926,7 +16920,7 @@
         <v>949</v>
       </c>
       <c r="C926" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="927" spans="1:3">
@@ -16937,7 +16931,7 @@
         <v>950</v>
       </c>
       <c r="C927" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="928" spans="1:3">
@@ -16948,7 +16942,7 @@
         <v>951</v>
       </c>
       <c r="C928" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="929" spans="1:3">
@@ -16959,7 +16953,7 @@
         <v>952</v>
       </c>
       <c r="C929" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="930" spans="1:3">
@@ -16970,7 +16964,7 @@
         <v>953</v>
       </c>
       <c r="C930" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="931" spans="1:3">
@@ -16981,7 +16975,7 @@
         <v>954</v>
       </c>
       <c r="C931" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="932" spans="1:3">
@@ -16992,7 +16986,7 @@
         <v>955</v>
       </c>
       <c r="C932" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="933" spans="1:3">
@@ -17003,7 +16997,7 @@
         <v>956</v>
       </c>
       <c r="C933" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="934" spans="1:3">
@@ -17014,7 +17008,7 @@
         <v>957</v>
       </c>
       <c r="C934" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="935" spans="1:3">
@@ -17025,7 +17019,7 @@
         <v>958</v>
       </c>
       <c r="C935" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="936" spans="1:3">
@@ -17036,7 +17030,7 @@
         <v>959</v>
       </c>
       <c r="C936" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="937" spans="1:3">
@@ -17047,7 +17041,7 @@
         <v>960</v>
       </c>
       <c r="C937" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="938" spans="1:3">
@@ -17058,7 +17052,7 @@
         <v>961</v>
       </c>
       <c r="C938" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="939" spans="1:3">
@@ -17069,7 +17063,7 @@
         <v>962</v>
       </c>
       <c r="C939" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="940" spans="1:3">
@@ -17080,7 +17074,7 @@
         <v>963</v>
       </c>
       <c r="C940" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="941" spans="1:3">
@@ -17091,7 +17085,7 @@
         <v>964</v>
       </c>
       <c r="C941" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="942" spans="1:3">
@@ -17102,7 +17096,7 @@
         <v>965</v>
       </c>
       <c r="C942" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="943" spans="1:3">
@@ -17113,7 +17107,7 @@
         <v>966</v>
       </c>
       <c r="C943" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="944" spans="1:3">
@@ -17124,7 +17118,7 @@
         <v>967</v>
       </c>
       <c r="C944" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="945" spans="1:3">
@@ -17135,7 +17129,7 @@
         <v>968</v>
       </c>
       <c r="C945" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="946" spans="1:3">
@@ -17146,7 +17140,7 @@
         <v>969</v>
       </c>
       <c r="C946" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="947" spans="1:3">
@@ -17157,7 +17151,7 @@
         <v>970</v>
       </c>
       <c r="C947" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="948" spans="1:3">
@@ -17168,7 +17162,7 @@
         <v>971</v>
       </c>
       <c r="C948" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="949" spans="1:3">
@@ -17179,7 +17173,7 @@
         <v>972</v>
       </c>
       <c r="C949" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="950" spans="1:3">
@@ -17190,7 +17184,7 @@
         <v>973</v>
       </c>
       <c r="C950" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="951" spans="1:3">
@@ -17201,7 +17195,7 @@
         <v>974</v>
       </c>
       <c r="C951" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="952" spans="1:3">
@@ -17212,7 +17206,7 @@
         <v>975</v>
       </c>
       <c r="C952" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="953" spans="1:3">
@@ -17223,7 +17217,7 @@
         <v>976</v>
       </c>
       <c r="C953" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="954" spans="1:3">
@@ -17234,7 +17228,7 @@
         <v>977</v>
       </c>
       <c r="C954" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="955" spans="1:3">
@@ -17245,7 +17239,7 @@
         <v>978</v>
       </c>
       <c r="C955" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="956" spans="1:3">
@@ -17256,7 +17250,7 @@
         <v>979</v>
       </c>
       <c r="C956" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="957" spans="1:3">
@@ -17267,7 +17261,7 @@
         <v>980</v>
       </c>
       <c r="C957" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="958" spans="1:3">
@@ -17278,18 +17272,18 @@
         <v>981</v>
       </c>
       <c r="C958" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="959" spans="1:3">
       <c r="A959" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B959" t="s">
         <v>982</v>
       </c>
       <c r="C959" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="960" spans="1:3">
@@ -17300,7 +17294,7 @@
         <v>983</v>
       </c>
       <c r="C960" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="961" spans="1:3">
@@ -17311,7 +17305,7 @@
         <v>984</v>
       </c>
       <c r="C961" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="962" spans="1:3">
@@ -17322,7 +17316,7 @@
         <v>985</v>
       </c>
       <c r="C962" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="963" spans="1:3">
@@ -17333,7 +17327,7 @@
         <v>986</v>
       </c>
       <c r="C963" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="964" spans="1:3">
@@ -17344,7 +17338,7 @@
         <v>987</v>
       </c>
       <c r="C964" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="965" spans="1:3">
@@ -17355,7 +17349,7 @@
         <v>988</v>
       </c>
       <c r="C965" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="966" spans="1:3">
@@ -17366,7 +17360,7 @@
         <v>989</v>
       </c>
       <c r="C966" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="967" spans="1:3">
@@ -17377,7 +17371,7 @@
         <v>990</v>
       </c>
       <c r="C967" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="968" spans="1:3">
@@ -17388,7 +17382,7 @@
         <v>991</v>
       </c>
       <c r="C968" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="969" spans="1:3">
@@ -17399,7 +17393,7 @@
         <v>992</v>
       </c>
       <c r="C969" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="970" spans="1:3">
@@ -17410,7 +17404,7 @@
         <v>993</v>
       </c>
       <c r="C970" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="971" spans="1:3">
@@ -17421,7 +17415,7 @@
         <v>994</v>
       </c>
       <c r="C971" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="972" spans="1:3">
@@ -17432,7 +17426,7 @@
         <v>995</v>
       </c>
       <c r="C972" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="973" spans="1:3">
@@ -17443,7 +17437,7 @@
         <v>996</v>
       </c>
       <c r="C973" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="974" spans="1:3">
@@ -17454,7 +17448,7 @@
         <v>997</v>
       </c>
       <c r="C974" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="975" spans="1:3">
@@ -17465,7 +17459,7 @@
         <v>998</v>
       </c>
       <c r="C975" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="976" spans="1:3">
@@ -17476,7 +17470,7 @@
         <v>999</v>
       </c>
       <c r="C976" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="977" spans="1:3">
@@ -17487,7 +17481,7 @@
         <v>1000</v>
       </c>
       <c r="C977" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="978" spans="1:3">
@@ -17498,7 +17492,7 @@
         <v>1001</v>
       </c>
       <c r="C978" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="979" spans="1:3">
@@ -17509,7 +17503,7 @@
         <v>1002</v>
       </c>
       <c r="C979" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="980" spans="1:3">
@@ -17520,7 +17514,7 @@
         <v>1003</v>
       </c>
       <c r="C980" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="981" spans="1:3">
@@ -17531,7 +17525,7 @@
         <v>1004</v>
       </c>
       <c r="C981" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="982" spans="1:3">
@@ -17542,7 +17536,7 @@
         <v>1005</v>
       </c>
       <c r="C982" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="983" spans="1:3">
@@ -17553,7 +17547,7 @@
         <v>1006</v>
       </c>
       <c r="C983" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="984" spans="1:3">
@@ -17564,7 +17558,7 @@
         <v>1007</v>
       </c>
       <c r="C984" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="985" spans="1:3">
@@ -17575,7 +17569,7 @@
         <v>1008</v>
       </c>
       <c r="C985" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="986" spans="1:3">
@@ -17586,7 +17580,7 @@
         <v>1009</v>
       </c>
       <c r="C986" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="987" spans="1:3">
@@ -17597,7 +17591,7 @@
         <v>1010</v>
       </c>
       <c r="C987" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="988" spans="1:3">
@@ -17608,7 +17602,7 @@
         <v>1011</v>
       </c>
       <c r="C988" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="989" spans="1:3">
@@ -17619,7 +17613,7 @@
         <v>1012</v>
       </c>
       <c r="C989" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="990" spans="1:3">
@@ -17630,7 +17624,7 @@
         <v>1013</v>
       </c>
       <c r="C990" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="991" spans="1:3">
@@ -17641,7 +17635,7 @@
         <v>1014</v>
       </c>
       <c r="C991" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="992" spans="1:3">
@@ -17652,7 +17646,7 @@
         <v>1015</v>
       </c>
       <c r="C992" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="993" spans="1:3">
@@ -17663,7 +17657,7 @@
         <v>1016</v>
       </c>
       <c r="C993" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="994" spans="1:3">
@@ -17674,7 +17668,7 @@
         <v>1017</v>
       </c>
       <c r="C994" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="995" spans="1:3">
@@ -17685,7 +17679,7 @@
         <v>1018</v>
       </c>
       <c r="C995" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="996" spans="1:3">
@@ -17696,7 +17690,7 @@
         <v>1019</v>
       </c>
       <c r="C996" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="997" spans="1:3">
@@ -17707,7 +17701,7 @@
         <v>1020</v>
       </c>
       <c r="C997" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="998" spans="1:3">
@@ -17718,7 +17712,7 @@
         <v>1021</v>
       </c>
       <c r="C998" t="s">
-        <v>2065</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="999" spans="1:3">
@@ -17729,7 +17723,7 @@
         <v>1022</v>
       </c>
       <c r="C999" t="s">
-        <v>2059</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="1000" spans="1:3">
@@ -17740,7 +17734,7 @@
         <v>1023</v>
       </c>
       <c r="C1000" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="1001" spans="1:3">
@@ -17751,7 +17745,7 @@
         <v>1024</v>
       </c>
       <c r="C1001" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="1002" spans="1:3">
@@ -17762,7 +17756,7 @@
         <v>1025</v>
       </c>
       <c r="C1002" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1003" spans="1:3">
@@ -17773,7 +17767,7 @@
         <v>1026</v>
       </c>
       <c r="C1003" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="1004" spans="1:3">
@@ -17784,7 +17778,7 @@
         <v>1027</v>
       </c>
       <c r="C1004" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="1005" spans="1:3">
@@ -17795,7 +17789,7 @@
         <v>1028</v>
       </c>
       <c r="C1005" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="1006" spans="1:3">
@@ -17806,7 +17800,7 @@
         <v>1029</v>
       </c>
       <c r="C1006" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="1007" spans="1:3">
@@ -17817,7 +17811,7 @@
         <v>1030</v>
       </c>
       <c r="C1007" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="1008" spans="1:3">
@@ -17828,7 +17822,7 @@
         <v>1031</v>
       </c>
       <c r="C1008" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="1009" spans="1:3">
@@ -17839,7 +17833,7 @@
         <v>1032</v>
       </c>
       <c r="C1009" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="1010" spans="1:3">
@@ -17850,7 +17844,7 @@
         <v>1033</v>
       </c>
       <c r="C1010" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="1011" spans="1:3">
@@ -17861,7 +17855,7 @@
         <v>1034</v>
       </c>
       <c r="C1011" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="1012" spans="1:3">
@@ -17872,7 +17866,7 @@
         <v>1035</v>
       </c>
       <c r="C1012" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="1013" spans="1:3">
@@ -17883,7 +17877,7 @@
         <v>1036</v>
       </c>
       <c r="C1013" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="1014" spans="1:3">
@@ -17894,7 +17888,7 @@
         <v>1037</v>
       </c>
       <c r="C1014" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="1015" spans="1:3">
@@ -17905,7 +17899,7 @@
         <v>1038</v>
       </c>
       <c r="C1015" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="1016" spans="1:3">
@@ -17916,7 +17910,7 @@
         <v>1039</v>
       </c>
       <c r="C1016" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="1017" spans="1:3">
@@ -17927,7 +17921,7 @@
         <v>1040</v>
       </c>
       <c r="C1017" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="1018" spans="1:3">
@@ -17938,7 +17932,7 @@
         <v>1041</v>
       </c>
       <c r="C1018" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="1019" spans="1:3">
@@ -17949,7 +17943,7 @@
         <v>1042</v>
       </c>
       <c r="C1019" t="s">
-        <v>2085</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="1020" spans="1:3">
@@ -17960,7 +17954,7 @@
         <v>1043</v>
       </c>
       <c r="C1020" t="s">
-        <v>2060</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="1021" spans="1:3">
@@ -17971,7 +17965,7 @@
         <v>1044</v>
       </c>
       <c r="C1021" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="1022" spans="1:3">
@@ -17982,7 +17976,7 @@
         <v>1045</v>
       </c>
       <c r="C1022" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="1023" spans="1:3">
@@ -17993,7 +17987,7 @@
         <v>1046</v>
       </c>
       <c r="C1023" t="s">
-        <v>2088</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="1024" spans="1:3">
@@ -18004,7 +17998,7 @@
         <v>1047</v>
       </c>
       <c r="C1024" t="s">
-        <v>2041</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="1025" spans="1:3">
@@ -18015,7 +18009,7 @@
         <v>1048</v>
       </c>
       <c r="C1025" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="1026" spans="1:3">
@@ -18026,7 +18020,7 @@
         <v>1049</v>
       </c>
       <c r="C1026" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="1027" spans="1:3">
@@ -18037,7 +18031,7 @@
         <v>1050</v>
       </c>
       <c r="C1027" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="1028" spans="1:3">
@@ -18048,7 +18042,7 @@
         <v>1051</v>
       </c>
       <c r="C1028" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="1029" spans="1:3">
@@ -18059,18 +18053,18 @@
         <v>1052</v>
       </c>
       <c r="C1029" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="1030" spans="1:3">
       <c r="A1030" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1030" t="s">
         <v>1053</v>
       </c>
       <c r="C1030" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="1031" spans="1:3">
@@ -18081,7 +18075,7 @@
         <v>1054</v>
       </c>
       <c r="C1031" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="1032" spans="1:3">
@@ -18092,7 +18086,7 @@
         <v>1055</v>
       </c>
       <c r="C1032" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="1033" spans="1:3">
@@ -18103,7 +18097,7 @@
         <v>1056</v>
       </c>
       <c r="C1033" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="1034" spans="1:3">
@@ -18114,7 +18108,7 @@
         <v>1057</v>
       </c>
       <c r="C1034" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="1035" spans="1:3">
@@ -18125,7 +18119,7 @@
         <v>1058</v>
       </c>
       <c r="C1035" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="1036" spans="1:3">
@@ -18136,7 +18130,7 @@
         <v>1059</v>
       </c>
       <c r="C1036" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="1037" spans="1:3">
@@ -18147,7 +18141,7 @@
         <v>1060</v>
       </c>
       <c r="C1037" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="1038" spans="1:3">
@@ -18158,7 +18152,7 @@
         <v>1061</v>
       </c>
       <c r="C1038" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="1039" spans="1:3">
@@ -18169,7 +18163,7 @@
         <v>1062</v>
       </c>
       <c r="C1039" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="1040" spans="1:3">
@@ -18180,7 +18174,7 @@
         <v>1063</v>
       </c>
       <c r="C1040" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="1041" spans="1:3">
@@ -18191,7 +18185,7 @@
         <v>1064</v>
       </c>
       <c r="C1041" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="1042" spans="1:3">
@@ -18202,7 +18196,7 @@
         <v>1065</v>
       </c>
       <c r="C1042" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="1043" spans="1:3">
@@ -18213,7 +18207,7 @@
         <v>1066</v>
       </c>
       <c r="C1043" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="1044" spans="1:3">
@@ -18224,7 +18218,7 @@
         <v>1067</v>
       </c>
       <c r="C1044" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="1045" spans="1:3">
@@ -18235,7 +18229,7 @@
         <v>1068</v>
       </c>
       <c r="C1045" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="1046" spans="1:3">
@@ -18246,7 +18240,7 @@
         <v>1069</v>
       </c>
       <c r="C1046" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="1047" spans="1:3">
@@ -18257,7 +18251,7 @@
         <v>1070</v>
       </c>
       <c r="C1047" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="1048" spans="1:3">
@@ -18268,7 +18262,7 @@
         <v>1071</v>
       </c>
       <c r="C1048" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="1049" spans="1:3">
@@ -18279,7 +18273,7 @@
         <v>1072</v>
       </c>
       <c r="C1049" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="1050" spans="1:3">
@@ -18290,7 +18284,7 @@
         <v>1073</v>
       </c>
       <c r="C1050" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="1051" spans="1:3">
@@ -18301,7 +18295,7 @@
         <v>1074</v>
       </c>
       <c r="C1051" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="1052" spans="1:3">
@@ -18312,7 +18306,7 @@
         <v>1075</v>
       </c>
       <c r="C1052" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="1053" spans="1:3">
@@ -18323,7 +18317,7 @@
         <v>1076</v>
       </c>
       <c r="C1053" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="1054" spans="1:3">
@@ -18334,7 +18328,7 @@
         <v>1077</v>
       </c>
       <c r="C1054" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="1055" spans="1:3">
@@ -18345,7 +18339,7 @@
         <v>1078</v>
       </c>
       <c r="C1055" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="1056" spans="1:3">
@@ -18356,29 +18350,18 @@
         <v>1079</v>
       </c>
       <c r="C1056" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="1057" spans="1:3">
       <c r="A1057" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1057" t="s">
         <v>1080</v>
       </c>
       <c r="C1057" t="s">
-        <v>2121</v>
-      </c>
-    </row>
-    <row r="1058" spans="1:3">
-      <c r="A1058" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1058" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C1058" t="s">
-        <v>2122</v>
+        <v>2120</v>
       </c>
     </row>
   </sheetData>

--- a/faltantes_por_estados.xlsx
+++ b/faltantes_por_estados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3123" uniqueCount="2089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3099" uniqueCount="2073">
   <si>
     <t>entidad</t>
   </si>
@@ -1675,15 +1675,6 @@
     <t>HGIMB002350</t>
   </si>
   <si>
-    <t>HGIMB002374</t>
-  </si>
-  <si>
-    <t>HGIMB002386</t>
-  </si>
-  <si>
-    <t>HGIMB002391</t>
-  </si>
-  <si>
     <t>HGIMB002403</t>
   </si>
   <si>
@@ -1714,9 +1705,6 @@
     <t>HGIMB004404</t>
   </si>
   <si>
-    <t>HGIMB004783</t>
-  </si>
-  <si>
     <t>MCIMB001713</t>
   </si>
   <si>
@@ -2617,9 +2605,6 @@
     <t>SRIMB002804</t>
   </si>
   <si>
-    <t>TCIMB000045</t>
-  </si>
-  <si>
     <t>TCIMB000050</t>
   </si>
   <si>
@@ -2788,9 +2773,6 @@
     <t>TCIMB003644</t>
   </si>
   <si>
-    <t>TCIMB003661</t>
-  </si>
-  <si>
     <t>TCIMB003702</t>
   </si>
   <si>
@@ -2833,9 +2815,6 @@
     <t>TCIMB004315</t>
   </si>
   <si>
-    <t>TCIMB004320</t>
-  </si>
-  <si>
     <t>TCIMB004385</t>
   </si>
   <si>
@@ -2893,9 +2872,6 @@
     <t>TCIMB004740</t>
   </si>
   <si>
-    <t>TCIMB004846</t>
-  </si>
-  <si>
     <t>TCIMB004991</t>
   </si>
   <si>
@@ -4765,15 +4741,6 @@
     <t>LA ALCANTARILLA</t>
   </si>
   <si>
-    <t>COLONIA CUBITOS</t>
-  </si>
-  <si>
-    <t>COLONIA LA RAZA</t>
-  </si>
-  <si>
-    <t>ABRAHAM KANAN HUEBE</t>
-  </si>
-  <si>
     <t>PACHUCA (DR. JESÚS DEL ROSAL)</t>
   </si>
   <si>
@@ -4804,9 +4771,6 @@
     <t>NICOLÁS BRAVO</t>
   </si>
   <si>
-    <t>LUZ DEL CARMEN</t>
-  </si>
-  <si>
     <t>CEAPS SAN MIGUEL CHAPULTEPEC BICENTENARIO</t>
   </si>
   <si>
@@ -5698,9 +5662,6 @@
     <t>CENTRO DE SALUD RURAL CERRO COLORADO</t>
   </si>
   <si>
-    <t>C.S. SAN PEDRO</t>
-  </si>
-  <si>
     <t>C.S. EL CAPULÍN</t>
   </si>
   <si>
@@ -5869,9 +5830,6 @@
     <t>C.S. ESPERANZA NORTE</t>
   </si>
   <si>
-    <t>C.S. GUAYACAN</t>
-  </si>
-  <si>
     <t>C.S. LA PALMA</t>
   </si>
   <si>
@@ -5914,9 +5872,6 @@
     <t>C.S. BUENAVISTA VEINTITRES</t>
   </si>
   <si>
-    <t>C.S. EJIDO MIGUEL HIDALGO Y COSTILLA</t>
-  </si>
-  <si>
     <t>C.S. ANACLETO CANABAL 1RA.</t>
   </si>
   <si>
@@ -5972,9 +5927,6 @@
   </si>
   <si>
     <t>CENTRO DE SALUD LOMAS ALEGRES DE 1 NB</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON DOS NUCLEOS BASICOS POB.REDENCION DEL CAMPESINO, TENOSIQUE,TABASCO</t>
   </si>
   <si>
     <t>CESSA LA MANGA</t>
@@ -6638,7 +6590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1041"/>
+  <dimension ref="A1:C1033"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6660,7 +6612,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>1065</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6671,7 +6623,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>1066</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6682,7 +6634,7 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>1067</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6693,7 +6645,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>1068</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6704,7 +6656,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>1069</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6715,7 +6667,7 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>1070</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6726,7 +6678,7 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>1071</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6737,7 +6689,7 @@
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>1072</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6748,7 +6700,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>1073</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6759,7 +6711,7 @@
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>1074</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6770,7 +6722,7 @@
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>1075</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6781,7 +6733,7 @@
         <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>1076</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6792,7 +6744,7 @@
         <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>1077</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6803,7 +6755,7 @@
         <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>1078</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -6814,7 +6766,7 @@
         <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>1079</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6836,7 +6788,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>1080</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6847,7 +6799,7 @@
         <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>1081</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6858,7 +6810,7 @@
         <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>1082</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6869,7 +6821,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>1083</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6880,7 +6832,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>1084</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6891,7 +6843,7 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>1085</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6902,7 +6854,7 @@
         <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>1086</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6913,7 +6865,7 @@
         <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>1087</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -6924,7 +6876,7 @@
         <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>1088</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6946,7 +6898,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="s">
-        <v>1089</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6968,7 +6920,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="s">
-        <v>1090</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -6979,7 +6931,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="s">
-        <v>1091</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -6990,7 +6942,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="s">
-        <v>1080</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -7001,7 +6953,7 @@
         <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>1092</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -7012,7 +6964,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="s">
-        <v>1093</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -7023,7 +6975,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="s">
-        <v>1094</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -7034,7 +6986,7 @@
         <v>59</v>
       </c>
       <c r="C36" t="s">
-        <v>1095</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -7045,7 +6997,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="s">
-        <v>1096</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -7056,7 +7008,7 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>1097</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -7067,7 +7019,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="s">
-        <v>1098</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -7078,7 +7030,7 @@
         <v>63</v>
       </c>
       <c r="C40" t="s">
-        <v>1099</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -7089,7 +7041,7 @@
         <v>64</v>
       </c>
       <c r="C41" t="s">
-        <v>1100</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -7100,7 +7052,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="s">
-        <v>1101</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -7111,7 +7063,7 @@
         <v>66</v>
       </c>
       <c r="C43" t="s">
-        <v>1102</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -7122,7 +7074,7 @@
         <v>67</v>
       </c>
       <c r="C44" t="s">
-        <v>1103</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -7133,7 +7085,7 @@
         <v>68</v>
       </c>
       <c r="C45" t="s">
-        <v>1104</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -7144,7 +7096,7 @@
         <v>69</v>
       </c>
       <c r="C46" t="s">
-        <v>1105</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -7155,7 +7107,7 @@
         <v>70</v>
       </c>
       <c r="C47" t="s">
-        <v>1106</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -7166,7 +7118,7 @@
         <v>71</v>
       </c>
       <c r="C48" t="s">
-        <v>1107</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -7177,7 +7129,7 @@
         <v>72</v>
       </c>
       <c r="C49" t="s">
-        <v>1108</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -7188,7 +7140,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>1109</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -7199,7 +7151,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="s">
-        <v>1110</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -7210,7 +7162,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="s">
-        <v>1111</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -7221,7 +7173,7 @@
         <v>76</v>
       </c>
       <c r="C53" t="s">
-        <v>1112</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -7232,7 +7184,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>1113</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -7243,7 +7195,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="s">
-        <v>1114</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -7254,7 +7206,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="s">
-        <v>1115</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -7265,7 +7217,7 @@
         <v>80</v>
       </c>
       <c r="C57" t="s">
-        <v>1116</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -7276,7 +7228,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="s">
-        <v>1117</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -7287,7 +7239,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="s">
-        <v>1118</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -7309,7 +7261,7 @@
         <v>84</v>
       </c>
       <c r="C61" t="s">
-        <v>1119</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -7320,7 +7272,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="s">
-        <v>1120</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -7331,7 +7283,7 @@
         <v>86</v>
       </c>
       <c r="C63" t="s">
-        <v>1121</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -7342,7 +7294,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="s">
-        <v>1122</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -7353,7 +7305,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="s">
-        <v>1123</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -7364,7 +7316,7 @@
         <v>89</v>
       </c>
       <c r="C66" t="s">
-        <v>1124</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -7375,7 +7327,7 @@
         <v>90</v>
       </c>
       <c r="C67" t="s">
-        <v>1125</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -7386,7 +7338,7 @@
         <v>91</v>
       </c>
       <c r="C68" t="s">
-        <v>1126</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -7397,7 +7349,7 @@
         <v>92</v>
       </c>
       <c r="C69" t="s">
-        <v>1127</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -7408,7 +7360,7 @@
         <v>93</v>
       </c>
       <c r="C70" t="s">
-        <v>1128</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -7419,7 +7371,7 @@
         <v>94</v>
       </c>
       <c r="C71" t="s">
-        <v>1129</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -7430,7 +7382,7 @@
         <v>95</v>
       </c>
       <c r="C72" t="s">
-        <v>1130</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -7441,7 +7393,7 @@
         <v>96</v>
       </c>
       <c r="C73" t="s">
-        <v>1131</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -7452,7 +7404,7 @@
         <v>97</v>
       </c>
       <c r="C74" t="s">
-        <v>1132</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -7463,7 +7415,7 @@
         <v>98</v>
       </c>
       <c r="C75" t="s">
-        <v>1133</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -7474,7 +7426,7 @@
         <v>99</v>
       </c>
       <c r="C76" t="s">
-        <v>1134</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -7485,7 +7437,7 @@
         <v>100</v>
       </c>
       <c r="C77" t="s">
-        <v>1135</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -7496,7 +7448,7 @@
         <v>101</v>
       </c>
       <c r="C78" t="s">
-        <v>1136</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -7507,7 +7459,7 @@
         <v>102</v>
       </c>
       <c r="C79" t="s">
-        <v>1137</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -7518,7 +7470,7 @@
         <v>103</v>
       </c>
       <c r="C80" t="s">
-        <v>1138</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -7529,7 +7481,7 @@
         <v>104</v>
       </c>
       <c r="C81" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -7540,7 +7492,7 @@
         <v>105</v>
       </c>
       <c r="C82" t="s">
-        <v>1140</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -7551,7 +7503,7 @@
         <v>106</v>
       </c>
       <c r="C83" t="s">
-        <v>1141</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -7562,7 +7514,7 @@
         <v>107</v>
       </c>
       <c r="C84" t="s">
-        <v>1142</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -7573,7 +7525,7 @@
         <v>108</v>
       </c>
       <c r="C85" t="s">
-        <v>1143</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -7584,7 +7536,7 @@
         <v>109</v>
       </c>
       <c r="C86" t="s">
-        <v>1144</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -7595,7 +7547,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="s">
-        <v>1145</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -7606,7 +7558,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="s">
-        <v>1146</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -7617,7 +7569,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="s">
-        <v>1147</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -7628,7 +7580,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="s">
-        <v>1148</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -7639,7 +7591,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="s">
-        <v>1149</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -7650,7 +7602,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="s">
-        <v>1150</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -7661,7 +7613,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="s">
-        <v>1151</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -7672,7 +7624,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="s">
-        <v>1152</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -7683,7 +7635,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="s">
-        <v>1153</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -7694,7 +7646,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="s">
-        <v>1154</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -7705,7 +7657,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="s">
-        <v>1155</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -7716,7 +7668,7 @@
         <v>121</v>
       </c>
       <c r="C98" t="s">
-        <v>1156</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -7727,7 +7679,7 @@
         <v>122</v>
       </c>
       <c r="C99" t="s">
-        <v>1157</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -7738,7 +7690,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="s">
-        <v>1158</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -7749,7 +7701,7 @@
         <v>124</v>
       </c>
       <c r="C101" t="s">
-        <v>1159</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -7760,7 +7712,7 @@
         <v>125</v>
       </c>
       <c r="C102" t="s">
-        <v>1160</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -7771,7 +7723,7 @@
         <v>126</v>
       </c>
       <c r="C103" t="s">
-        <v>1161</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -7782,7 +7734,7 @@
         <v>127</v>
       </c>
       <c r="C104" t="s">
-        <v>1162</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -7793,7 +7745,7 @@
         <v>128</v>
       </c>
       <c r="C105" t="s">
-        <v>1163</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -7804,7 +7756,7 @@
         <v>129</v>
       </c>
       <c r="C106" t="s">
-        <v>1164</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -7815,7 +7767,7 @@
         <v>130</v>
       </c>
       <c r="C107" t="s">
-        <v>1165</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -7826,7 +7778,7 @@
         <v>131</v>
       </c>
       <c r="C108" t="s">
-        <v>1166</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -7837,7 +7789,7 @@
         <v>132</v>
       </c>
       <c r="C109" t="s">
-        <v>1167</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -7848,7 +7800,7 @@
         <v>133</v>
       </c>
       <c r="C110" t="s">
-        <v>1168</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -7859,7 +7811,7 @@
         <v>134</v>
       </c>
       <c r="C111" t="s">
-        <v>1169</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -7870,7 +7822,7 @@
         <v>135</v>
       </c>
       <c r="C112" t="s">
-        <v>1170</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -7881,7 +7833,7 @@
         <v>136</v>
       </c>
       <c r="C113" t="s">
-        <v>1171</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -7892,7 +7844,7 @@
         <v>137</v>
       </c>
       <c r="C114" t="s">
-        <v>1172</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -7903,7 +7855,7 @@
         <v>138</v>
       </c>
       <c r="C115" t="s">
-        <v>1173</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -7914,7 +7866,7 @@
         <v>139</v>
       </c>
       <c r="C116" t="s">
-        <v>1174</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -7925,7 +7877,7 @@
         <v>140</v>
       </c>
       <c r="C117" t="s">
-        <v>1175</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -7936,7 +7888,7 @@
         <v>141</v>
       </c>
       <c r="C118" t="s">
-        <v>1176</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -7947,7 +7899,7 @@
         <v>142</v>
       </c>
       <c r="C119" t="s">
-        <v>1177</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -7958,7 +7910,7 @@
         <v>143</v>
       </c>
       <c r="C120" t="s">
-        <v>1178</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -7969,7 +7921,7 @@
         <v>144</v>
       </c>
       <c r="C121" t="s">
-        <v>1179</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -7980,7 +7932,7 @@
         <v>145</v>
       </c>
       <c r="C122" t="s">
-        <v>1180</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -7991,7 +7943,7 @@
         <v>146</v>
       </c>
       <c r="C123" t="s">
-        <v>1181</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -8002,7 +7954,7 @@
         <v>147</v>
       </c>
       <c r="C124" t="s">
-        <v>1182</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -8013,7 +7965,7 @@
         <v>148</v>
       </c>
       <c r="C125" t="s">
-        <v>1183</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -8024,7 +7976,7 @@
         <v>149</v>
       </c>
       <c r="C126" t="s">
-        <v>1184</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -8035,7 +7987,7 @@
         <v>150</v>
       </c>
       <c r="C127" t="s">
-        <v>1185</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -8046,7 +7998,7 @@
         <v>151</v>
       </c>
       <c r="C128" t="s">
-        <v>1186</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -8057,7 +8009,7 @@
         <v>152</v>
       </c>
       <c r="C129" t="s">
-        <v>1187</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -8068,7 +8020,7 @@
         <v>153</v>
       </c>
       <c r="C130" t="s">
-        <v>1188</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -8079,7 +8031,7 @@
         <v>154</v>
       </c>
       <c r="C131" t="s">
-        <v>1189</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -8090,7 +8042,7 @@
         <v>155</v>
       </c>
       <c r="C132" t="s">
-        <v>1190</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -8101,7 +8053,7 @@
         <v>156</v>
       </c>
       <c r="C133" t="s">
-        <v>1191</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -8112,7 +8064,7 @@
         <v>157</v>
       </c>
       <c r="C134" t="s">
-        <v>1192</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -8123,7 +8075,7 @@
         <v>158</v>
       </c>
       <c r="C135" t="s">
-        <v>1193</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -8134,7 +8086,7 @@
         <v>159</v>
       </c>
       <c r="C136" t="s">
-        <v>1194</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -8145,7 +8097,7 @@
         <v>160</v>
       </c>
       <c r="C137" t="s">
-        <v>1195</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -8156,7 +8108,7 @@
         <v>161</v>
       </c>
       <c r="C138" t="s">
-        <v>1196</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -8167,7 +8119,7 @@
         <v>162</v>
       </c>
       <c r="C139" t="s">
-        <v>1197</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -8178,7 +8130,7 @@
         <v>163</v>
       </c>
       <c r="C140" t="s">
-        <v>1198</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -8189,7 +8141,7 @@
         <v>164</v>
       </c>
       <c r="C141" t="s">
-        <v>1199</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -8200,7 +8152,7 @@
         <v>165</v>
       </c>
       <c r="C142" t="s">
-        <v>1200</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -8211,7 +8163,7 @@
         <v>166</v>
       </c>
       <c r="C143" t="s">
-        <v>1201</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -8222,7 +8174,7 @@
         <v>167</v>
       </c>
       <c r="C144" t="s">
-        <v>1202</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -8233,7 +8185,7 @@
         <v>168</v>
       </c>
       <c r="C145" t="s">
-        <v>1203</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -8244,7 +8196,7 @@
         <v>169</v>
       </c>
       <c r="C146" t="s">
-        <v>1204</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -8255,7 +8207,7 @@
         <v>170</v>
       </c>
       <c r="C147" t="s">
-        <v>1205</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -8266,7 +8218,7 @@
         <v>171</v>
       </c>
       <c r="C148" t="s">
-        <v>1206</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -8277,7 +8229,7 @@
         <v>172</v>
       </c>
       <c r="C149" t="s">
-        <v>1207</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -8288,7 +8240,7 @@
         <v>173</v>
       </c>
       <c r="C150" t="s">
-        <v>1208</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -8299,7 +8251,7 @@
         <v>174</v>
       </c>
       <c r="C151" t="s">
-        <v>1209</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -8310,7 +8262,7 @@
         <v>175</v>
       </c>
       <c r="C152" t="s">
-        <v>1210</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -8321,7 +8273,7 @@
         <v>176</v>
       </c>
       <c r="C153" t="s">
-        <v>1211</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -8332,7 +8284,7 @@
         <v>177</v>
       </c>
       <c r="C154" t="s">
-        <v>1212</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -8343,7 +8295,7 @@
         <v>178</v>
       </c>
       <c r="C155" t="s">
-        <v>1213</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -8354,7 +8306,7 @@
         <v>179</v>
       </c>
       <c r="C156" t="s">
-        <v>1214</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -8365,7 +8317,7 @@
         <v>180</v>
       </c>
       <c r="C157" t="s">
-        <v>1215</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -8376,7 +8328,7 @@
         <v>181</v>
       </c>
       <c r="C158" t="s">
-        <v>1216</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -8387,7 +8339,7 @@
         <v>182</v>
       </c>
       <c r="C159" t="s">
-        <v>1217</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -8398,7 +8350,7 @@
         <v>183</v>
       </c>
       <c r="C160" t="s">
-        <v>1218</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -8409,7 +8361,7 @@
         <v>184</v>
       </c>
       <c r="C161" t="s">
-        <v>1219</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -8420,7 +8372,7 @@
         <v>185</v>
       </c>
       <c r="C162" t="s">
-        <v>1220</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -8431,7 +8383,7 @@
         <v>186</v>
       </c>
       <c r="C163" t="s">
-        <v>1221</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -8442,7 +8394,7 @@
         <v>187</v>
       </c>
       <c r="C164" t="s">
-        <v>1222</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -8453,7 +8405,7 @@
         <v>188</v>
       </c>
       <c r="C165" t="s">
-        <v>1223</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -8464,7 +8416,7 @@
         <v>189</v>
       </c>
       <c r="C166" t="s">
-        <v>1224</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -8475,7 +8427,7 @@
         <v>190</v>
       </c>
       <c r="C167" t="s">
-        <v>1225</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -8486,7 +8438,7 @@
         <v>191</v>
       </c>
       <c r="C168" t="s">
-        <v>1226</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -8497,7 +8449,7 @@
         <v>192</v>
       </c>
       <c r="C169" t="s">
-        <v>1227</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -8508,7 +8460,7 @@
         <v>193</v>
       </c>
       <c r="C170" t="s">
-        <v>1228</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -8519,7 +8471,7 @@
         <v>194</v>
       </c>
       <c r="C171" t="s">
-        <v>1229</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -8530,7 +8482,7 @@
         <v>195</v>
       </c>
       <c r="C172" t="s">
-        <v>1230</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -8541,7 +8493,7 @@
         <v>196</v>
       </c>
       <c r="C173" t="s">
-        <v>1231</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -8552,7 +8504,7 @@
         <v>197</v>
       </c>
       <c r="C174" t="s">
-        <v>1232</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -8563,7 +8515,7 @@
         <v>198</v>
       </c>
       <c r="C175" t="s">
-        <v>1233</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -8574,7 +8526,7 @@
         <v>199</v>
       </c>
       <c r="C176" t="s">
-        <v>1234</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -8585,7 +8537,7 @@
         <v>200</v>
       </c>
       <c r="C177" t="s">
-        <v>1235</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -8596,7 +8548,7 @@
         <v>201</v>
       </c>
       <c r="C178" t="s">
-        <v>1236</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -8607,7 +8559,7 @@
         <v>202</v>
       </c>
       <c r="C179" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -8618,7 +8570,7 @@
         <v>203</v>
       </c>
       <c r="C180" t="s">
-        <v>1238</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -8629,7 +8581,7 @@
         <v>204</v>
       </c>
       <c r="C181" t="s">
-        <v>1239</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -8640,7 +8592,7 @@
         <v>205</v>
       </c>
       <c r="C182" t="s">
-        <v>1240</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -8651,7 +8603,7 @@
         <v>206</v>
       </c>
       <c r="C183" t="s">
-        <v>1241</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -8662,7 +8614,7 @@
         <v>207</v>
       </c>
       <c r="C184" t="s">
-        <v>1242</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -8673,7 +8625,7 @@
         <v>208</v>
       </c>
       <c r="C185" t="s">
-        <v>1243</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -8684,7 +8636,7 @@
         <v>209</v>
       </c>
       <c r="C186" t="s">
-        <v>1244</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -8695,7 +8647,7 @@
         <v>210</v>
       </c>
       <c r="C187" t="s">
-        <v>1245</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -8706,7 +8658,7 @@
         <v>211</v>
       </c>
       <c r="C188" t="s">
-        <v>1246</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -8717,7 +8669,7 @@
         <v>212</v>
       </c>
       <c r="C189" t="s">
-        <v>1247</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -8728,7 +8680,7 @@
         <v>213</v>
       </c>
       <c r="C190" t="s">
-        <v>1248</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -8739,7 +8691,7 @@
         <v>214</v>
       </c>
       <c r="C191" t="s">
-        <v>1249</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -8750,7 +8702,7 @@
         <v>215</v>
       </c>
       <c r="C192" t="s">
-        <v>1250</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -8761,7 +8713,7 @@
         <v>216</v>
       </c>
       <c r="C193" t="s">
-        <v>1251</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -8772,7 +8724,7 @@
         <v>217</v>
       </c>
       <c r="C194" t="s">
-        <v>1252</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -8783,7 +8735,7 @@
         <v>218</v>
       </c>
       <c r="C195" t="s">
-        <v>1253</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -8794,7 +8746,7 @@
         <v>219</v>
       </c>
       <c r="C196" t="s">
-        <v>1254</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -8805,7 +8757,7 @@
         <v>220</v>
       </c>
       <c r="C197" t="s">
-        <v>1255</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -8816,7 +8768,7 @@
         <v>221</v>
       </c>
       <c r="C198" t="s">
-        <v>1256</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -8827,7 +8779,7 @@
         <v>222</v>
       </c>
       <c r="C199" t="s">
-        <v>1257</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -8838,7 +8790,7 @@
         <v>223</v>
       </c>
       <c r="C200" t="s">
-        <v>1258</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -8849,7 +8801,7 @@
         <v>224</v>
       </c>
       <c r="C201" t="s">
-        <v>1259</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -8860,7 +8812,7 @@
         <v>225</v>
       </c>
       <c r="C202" t="s">
-        <v>1260</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -8871,7 +8823,7 @@
         <v>226</v>
       </c>
       <c r="C203" t="s">
-        <v>1261</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -8882,7 +8834,7 @@
         <v>227</v>
       </c>
       <c r="C204" t="s">
-        <v>1262</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -8893,7 +8845,7 @@
         <v>228</v>
       </c>
       <c r="C205" t="s">
-        <v>1263</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -8904,7 +8856,7 @@
         <v>229</v>
       </c>
       <c r="C206" t="s">
-        <v>1264</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -8915,7 +8867,7 @@
         <v>230</v>
       </c>
       <c r="C207" t="s">
-        <v>1265</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -8926,7 +8878,7 @@
         <v>231</v>
       </c>
       <c r="C208" t="s">
-        <v>1266</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -8937,7 +8889,7 @@
         <v>232</v>
       </c>
       <c r="C209" t="s">
-        <v>1267</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -8948,7 +8900,7 @@
         <v>233</v>
       </c>
       <c r="C210" t="s">
-        <v>1268</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -8959,7 +8911,7 @@
         <v>234</v>
       </c>
       <c r="C211" t="s">
-        <v>1269</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -8970,7 +8922,7 @@
         <v>235</v>
       </c>
       <c r="C212" t="s">
-        <v>1270</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -8981,7 +8933,7 @@
         <v>236</v>
       </c>
       <c r="C213" t="s">
-        <v>1271</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -8992,7 +8944,7 @@
         <v>237</v>
       </c>
       <c r="C214" t="s">
-        <v>1272</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -9003,7 +8955,7 @@
         <v>238</v>
       </c>
       <c r="C215" t="s">
-        <v>1273</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -9014,7 +8966,7 @@
         <v>239</v>
       </c>
       <c r="C216" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -9025,7 +8977,7 @@
         <v>240</v>
       </c>
       <c r="C217" t="s">
-        <v>1275</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -9036,7 +8988,7 @@
         <v>241</v>
       </c>
       <c r="C218" t="s">
-        <v>1276</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -9047,7 +8999,7 @@
         <v>242</v>
       </c>
       <c r="C219" t="s">
-        <v>1277</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -9058,7 +9010,7 @@
         <v>243</v>
       </c>
       <c r="C220" t="s">
-        <v>1278</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -9069,7 +9021,7 @@
         <v>244</v>
       </c>
       <c r="C221" t="s">
-        <v>1279</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -9080,7 +9032,7 @@
         <v>245</v>
       </c>
       <c r="C222" t="s">
-        <v>1280</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -9091,7 +9043,7 @@
         <v>246</v>
       </c>
       <c r="C223" t="s">
-        <v>1281</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -9102,7 +9054,7 @@
         <v>247</v>
       </c>
       <c r="C224" t="s">
-        <v>1282</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -9113,7 +9065,7 @@
         <v>248</v>
       </c>
       <c r="C225" t="s">
-        <v>1283</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -9124,7 +9076,7 @@
         <v>249</v>
       </c>
       <c r="C226" t="s">
-        <v>1284</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -9135,7 +9087,7 @@
         <v>250</v>
       </c>
       <c r="C227" t="s">
-        <v>1285</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -9146,7 +9098,7 @@
         <v>251</v>
       </c>
       <c r="C228" t="s">
-        <v>1286</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -9157,7 +9109,7 @@
         <v>252</v>
       </c>
       <c r="C229" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -9168,7 +9120,7 @@
         <v>253</v>
       </c>
       <c r="C230" t="s">
-        <v>1288</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -9179,7 +9131,7 @@
         <v>254</v>
       </c>
       <c r="C231" t="s">
-        <v>1289</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -9190,7 +9142,7 @@
         <v>255</v>
       </c>
       <c r="C232" t="s">
-        <v>1290</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -9201,7 +9153,7 @@
         <v>256</v>
       </c>
       <c r="C233" t="s">
-        <v>1291</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -9212,7 +9164,7 @@
         <v>257</v>
       </c>
       <c r="C234" t="s">
-        <v>1292</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -9223,7 +9175,7 @@
         <v>258</v>
       </c>
       <c r="C235" t="s">
-        <v>1293</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -9234,7 +9186,7 @@
         <v>259</v>
       </c>
       <c r="C236" t="s">
-        <v>1294</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -9245,7 +9197,7 @@
         <v>260</v>
       </c>
       <c r="C237" t="s">
-        <v>1295</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -9256,7 +9208,7 @@
         <v>261</v>
       </c>
       <c r="C238" t="s">
-        <v>1296</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -9267,7 +9219,7 @@
         <v>262</v>
       </c>
       <c r="C239" t="s">
-        <v>1297</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -9278,7 +9230,7 @@
         <v>263</v>
       </c>
       <c r="C240" t="s">
-        <v>1298</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -9289,7 +9241,7 @@
         <v>264</v>
       </c>
       <c r="C241" t="s">
-        <v>1299</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -9300,7 +9252,7 @@
         <v>265</v>
       </c>
       <c r="C242" t="s">
-        <v>1300</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -9311,7 +9263,7 @@
         <v>266</v>
       </c>
       <c r="C243" t="s">
-        <v>1301</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -9322,7 +9274,7 @@
         <v>267</v>
       </c>
       <c r="C244" t="s">
-        <v>1302</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -9333,7 +9285,7 @@
         <v>268</v>
       </c>
       <c r="C245" t="s">
-        <v>1303</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -9344,7 +9296,7 @@
         <v>269</v>
       </c>
       <c r="C246" t="s">
-        <v>1304</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -9355,7 +9307,7 @@
         <v>270</v>
       </c>
       <c r="C247" t="s">
-        <v>1305</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -9366,7 +9318,7 @@
         <v>271</v>
       </c>
       <c r="C248" t="s">
-        <v>1306</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -9377,7 +9329,7 @@
         <v>272</v>
       </c>
       <c r="C249" t="s">
-        <v>1307</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -9388,7 +9340,7 @@
         <v>273</v>
       </c>
       <c r="C250" t="s">
-        <v>1308</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -9399,7 +9351,7 @@
         <v>274</v>
       </c>
       <c r="C251" t="s">
-        <v>1309</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -9410,7 +9362,7 @@
         <v>275</v>
       </c>
       <c r="C252" t="s">
-        <v>1310</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -9421,7 +9373,7 @@
         <v>276</v>
       </c>
       <c r="C253" t="s">
-        <v>1311</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -9432,7 +9384,7 @@
         <v>277</v>
       </c>
       <c r="C254" t="s">
-        <v>1312</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -9443,7 +9395,7 @@
         <v>278</v>
       </c>
       <c r="C255" t="s">
-        <v>1313</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -9454,7 +9406,7 @@
         <v>279</v>
       </c>
       <c r="C256" t="s">
-        <v>1314</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -9465,7 +9417,7 @@
         <v>280</v>
       </c>
       <c r="C257" t="s">
-        <v>1315</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -9476,7 +9428,7 @@
         <v>281</v>
       </c>
       <c r="C258" t="s">
-        <v>1316</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="259" spans="1:3">
@@ -9487,7 +9439,7 @@
         <v>282</v>
       </c>
       <c r="C259" t="s">
-        <v>1317</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -9498,7 +9450,7 @@
         <v>283</v>
       </c>
       <c r="C260" t="s">
-        <v>1318</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="261" spans="1:3">
@@ -9509,7 +9461,7 @@
         <v>284</v>
       </c>
       <c r="C261" t="s">
-        <v>1319</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="262" spans="1:3">
@@ -9520,7 +9472,7 @@
         <v>285</v>
       </c>
       <c r="C262" t="s">
-        <v>1320</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -9531,7 +9483,7 @@
         <v>286</v>
       </c>
       <c r="C263" t="s">
-        <v>1321</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="264" spans="1:3">
@@ -9542,7 +9494,7 @@
         <v>287</v>
       </c>
       <c r="C264" t="s">
-        <v>1322</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -9553,7 +9505,7 @@
         <v>288</v>
       </c>
       <c r="C265" t="s">
-        <v>1323</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="266" spans="1:3">
@@ -9564,7 +9516,7 @@
         <v>289</v>
       </c>
       <c r="C266" t="s">
-        <v>1324</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="267" spans="1:3">
@@ -9575,7 +9527,7 @@
         <v>290</v>
       </c>
       <c r="C267" t="s">
-        <v>1325</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="268" spans="1:3">
@@ -9586,7 +9538,7 @@
         <v>291</v>
       </c>
       <c r="C268" t="s">
-        <v>1326</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="269" spans="1:3">
@@ -9597,7 +9549,7 @@
         <v>292</v>
       </c>
       <c r="C269" t="s">
-        <v>1327</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="270" spans="1:3">
@@ -9608,7 +9560,7 @@
         <v>293</v>
       </c>
       <c r="C270" t="s">
-        <v>1328</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="271" spans="1:3">
@@ -9619,7 +9571,7 @@
         <v>294</v>
       </c>
       <c r="C271" t="s">
-        <v>1329</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="272" spans="1:3">
@@ -9630,7 +9582,7 @@
         <v>295</v>
       </c>
       <c r="C272" t="s">
-        <v>1330</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="273" spans="1:3">
@@ -9641,7 +9593,7 @@
         <v>296</v>
       </c>
       <c r="C273" t="s">
-        <v>1331</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="274" spans="1:3">
@@ -9652,7 +9604,7 @@
         <v>297</v>
       </c>
       <c r="C274" t="s">
-        <v>1332</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="275" spans="1:3">
@@ -9663,7 +9615,7 @@
         <v>298</v>
       </c>
       <c r="C275" t="s">
-        <v>1333</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="276" spans="1:3">
@@ -9674,7 +9626,7 @@
         <v>299</v>
       </c>
       <c r="C276" t="s">
-        <v>1334</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="277" spans="1:3">
@@ -9685,7 +9637,7 @@
         <v>300</v>
       </c>
       <c r="C277" t="s">
-        <v>1335</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="278" spans="1:3">
@@ -9696,7 +9648,7 @@
         <v>301</v>
       </c>
       <c r="C278" t="s">
-        <v>1336</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="279" spans="1:3">
@@ -9707,7 +9659,7 @@
         <v>302</v>
       </c>
       <c r="C279" t="s">
-        <v>1337</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="280" spans="1:3">
@@ -9718,7 +9670,7 @@
         <v>303</v>
       </c>
       <c r="C280" t="s">
-        <v>1338</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -9729,7 +9681,7 @@
         <v>304</v>
       </c>
       <c r="C281" t="s">
-        <v>1339</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="282" spans="1:3">
@@ -9740,7 +9692,7 @@
         <v>305</v>
       </c>
       <c r="C282" t="s">
-        <v>1340</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="283" spans="1:3">
@@ -9751,7 +9703,7 @@
         <v>306</v>
       </c>
       <c r="C283" t="s">
-        <v>1258</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="284" spans="1:3">
@@ -9762,7 +9714,7 @@
         <v>307</v>
       </c>
       <c r="C284" t="s">
-        <v>1341</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="285" spans="1:3">
@@ -9773,7 +9725,7 @@
         <v>308</v>
       </c>
       <c r="C285" t="s">
-        <v>1342</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="286" spans="1:3">
@@ -9784,7 +9736,7 @@
         <v>309</v>
       </c>
       <c r="C286" t="s">
-        <v>1343</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="287" spans="1:3">
@@ -9795,7 +9747,7 @@
         <v>310</v>
       </c>
       <c r="C287" t="s">
-        <v>1344</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="288" spans="1:3">
@@ -9806,7 +9758,7 @@
         <v>311</v>
       </c>
       <c r="C288" t="s">
-        <v>1345</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="289" spans="1:3">
@@ -9817,7 +9769,7 @@
         <v>312</v>
       </c>
       <c r="C289" t="s">
-        <v>1346</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="290" spans="1:3">
@@ -9828,7 +9780,7 @@
         <v>313</v>
       </c>
       <c r="C290" t="s">
-        <v>1347</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="291" spans="1:3">
@@ -9839,7 +9791,7 @@
         <v>314</v>
       </c>
       <c r="C291" t="s">
-        <v>1348</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="292" spans="1:3">
@@ -9850,7 +9802,7 @@
         <v>315</v>
       </c>
       <c r="C292" t="s">
-        <v>1349</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="293" spans="1:3">
@@ -9861,7 +9813,7 @@
         <v>316</v>
       </c>
       <c r="C293" t="s">
-        <v>1350</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="294" spans="1:3">
@@ -9872,7 +9824,7 @@
         <v>317</v>
       </c>
       <c r="C294" t="s">
-        <v>1351</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="295" spans="1:3">
@@ -9883,7 +9835,7 @@
         <v>318</v>
       </c>
       <c r="C295" t="s">
-        <v>1352</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="296" spans="1:3">
@@ -9894,7 +9846,7 @@
         <v>319</v>
       </c>
       <c r="C296" t="s">
-        <v>1353</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="297" spans="1:3">
@@ -9905,7 +9857,7 @@
         <v>320</v>
       </c>
       <c r="C297" t="s">
-        <v>1354</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="298" spans="1:3">
@@ -9916,7 +9868,7 @@
         <v>321</v>
       </c>
       <c r="C298" t="s">
-        <v>1355</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="299" spans="1:3">
@@ -9927,7 +9879,7 @@
         <v>322</v>
       </c>
       <c r="C299" t="s">
-        <v>1356</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="300" spans="1:3">
@@ -9938,7 +9890,7 @@
         <v>323</v>
       </c>
       <c r="C300" t="s">
-        <v>1357</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="301" spans="1:3">
@@ -9949,7 +9901,7 @@
         <v>324</v>
       </c>
       <c r="C301" t="s">
-        <v>1358</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -9960,7 +9912,7 @@
         <v>325</v>
       </c>
       <c r="C302" t="s">
-        <v>1359</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="303" spans="1:3">
@@ -9971,7 +9923,7 @@
         <v>326</v>
       </c>
       <c r="C303" t="s">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="304" spans="1:3">
@@ -9982,7 +9934,7 @@
         <v>327</v>
       </c>
       <c r="C304" t="s">
-        <v>1361</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -9993,7 +9945,7 @@
         <v>328</v>
       </c>
       <c r="C305" t="s">
-        <v>1362</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="306" spans="1:3">
@@ -10004,7 +9956,7 @@
         <v>329</v>
       </c>
       <c r="C306" t="s">
-        <v>1363</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="307" spans="1:3">
@@ -10015,7 +9967,7 @@
         <v>330</v>
       </c>
       <c r="C307" t="s">
-        <v>1364</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="308" spans="1:3">
@@ -10026,7 +9978,7 @@
         <v>331</v>
       </c>
       <c r="C308" t="s">
-        <v>1365</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="309" spans="1:3">
@@ -10037,7 +9989,7 @@
         <v>332</v>
       </c>
       <c r="C309" t="s">
-        <v>1366</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="310" spans="1:3">
@@ -10048,7 +10000,7 @@
         <v>333</v>
       </c>
       <c r="C310" t="s">
-        <v>1367</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="311" spans="1:3">
@@ -10059,7 +10011,7 @@
         <v>334</v>
       </c>
       <c r="C311" t="s">
-        <v>1368</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="312" spans="1:3">
@@ -10070,7 +10022,7 @@
         <v>335</v>
       </c>
       <c r="C312" t="s">
-        <v>1369</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="313" spans="1:3">
@@ -10081,7 +10033,7 @@
         <v>336</v>
       </c>
       <c r="C313" t="s">
-        <v>1370</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="314" spans="1:3">
@@ -10092,7 +10044,7 @@
         <v>337</v>
       </c>
       <c r="C314" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="315" spans="1:3">
@@ -10103,7 +10055,7 @@
         <v>338</v>
       </c>
       <c r="C315" t="s">
-        <v>1372</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="316" spans="1:3">
@@ -10114,7 +10066,7 @@
         <v>339</v>
       </c>
       <c r="C316" t="s">
-        <v>1373</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="317" spans="1:3">
@@ -10125,7 +10077,7 @@
         <v>340</v>
       </c>
       <c r="C317" t="s">
-        <v>1374</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="318" spans="1:3">
@@ -10136,7 +10088,7 @@
         <v>341</v>
       </c>
       <c r="C318" t="s">
-        <v>1375</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="319" spans="1:3">
@@ -10147,7 +10099,7 @@
         <v>342</v>
       </c>
       <c r="C319" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="320" spans="1:3">
@@ -10158,7 +10110,7 @@
         <v>343</v>
       </c>
       <c r="C320" t="s">
-        <v>1377</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="321" spans="1:3">
@@ -10169,7 +10121,7 @@
         <v>344</v>
       </c>
       <c r="C321" t="s">
-        <v>1378</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -10180,7 +10132,7 @@
         <v>345</v>
       </c>
       <c r="C322" t="s">
-        <v>1379</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="323" spans="1:3">
@@ -10191,7 +10143,7 @@
         <v>346</v>
       </c>
       <c r="C323" t="s">
-        <v>1380</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="324" spans="1:3">
@@ -10202,7 +10154,7 @@
         <v>347</v>
       </c>
       <c r="C324" t="s">
-        <v>1381</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -10213,7 +10165,7 @@
         <v>348</v>
       </c>
       <c r="C325" t="s">
-        <v>1154</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="326" spans="1:3">
@@ -10224,7 +10176,7 @@
         <v>349</v>
       </c>
       <c r="C326" t="s">
-        <v>1382</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="327" spans="1:3">
@@ -10235,7 +10187,7 @@
         <v>350</v>
       </c>
       <c r="C327" t="s">
-        <v>1383</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="328" spans="1:3">
@@ -10246,7 +10198,7 @@
         <v>351</v>
       </c>
       <c r="C328" t="s">
-        <v>1384</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="329" spans="1:3">
@@ -10257,7 +10209,7 @@
         <v>352</v>
       </c>
       <c r="C329" t="s">
-        <v>1385</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="330" spans="1:3">
@@ -10268,7 +10220,7 @@
         <v>353</v>
       </c>
       <c r="C330" t="s">
-        <v>1386</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -10279,7 +10231,7 @@
         <v>354</v>
       </c>
       <c r="C331" t="s">
-        <v>1387</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="332" spans="1:3">
@@ -10290,7 +10242,7 @@
         <v>355</v>
       </c>
       <c r="C332" t="s">
-        <v>1388</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="333" spans="1:3">
@@ -10301,7 +10253,7 @@
         <v>356</v>
       </c>
       <c r="C333" t="s">
-        <v>1389</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="334" spans="1:3">
@@ -10312,7 +10264,7 @@
         <v>357</v>
       </c>
       <c r="C334" t="s">
-        <v>1390</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="335" spans="1:3">
@@ -10323,7 +10275,7 @@
         <v>358</v>
       </c>
       <c r="C335" t="s">
-        <v>1391</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="336" spans="1:3">
@@ -10334,7 +10286,7 @@
         <v>359</v>
       </c>
       <c r="C336" t="s">
-        <v>1392</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="337" spans="1:3">
@@ -10345,7 +10297,7 @@
         <v>360</v>
       </c>
       <c r="C337" t="s">
-        <v>1393</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="338" spans="1:3">
@@ -10356,7 +10308,7 @@
         <v>361</v>
       </c>
       <c r="C338" t="s">
-        <v>1394</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="339" spans="1:3">
@@ -10367,7 +10319,7 @@
         <v>362</v>
       </c>
       <c r="C339" t="s">
-        <v>1395</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="340" spans="1:3">
@@ -10378,7 +10330,7 @@
         <v>363</v>
       </c>
       <c r="C340" t="s">
-        <v>1396</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="341" spans="1:3">
@@ -10389,7 +10341,7 @@
         <v>364</v>
       </c>
       <c r="C341" t="s">
-        <v>1397</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -10400,7 +10352,7 @@
         <v>365</v>
       </c>
       <c r="C342" t="s">
-        <v>1398</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="343" spans="1:3">
@@ -10411,7 +10363,7 @@
         <v>366</v>
       </c>
       <c r="C343" t="s">
-        <v>1145</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="344" spans="1:3">
@@ -10422,7 +10374,7 @@
         <v>367</v>
       </c>
       <c r="C344" t="s">
-        <v>1399</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="345" spans="1:3">
@@ -10433,7 +10385,7 @@
         <v>368</v>
       </c>
       <c r="C345" t="s">
-        <v>1400</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="346" spans="1:3">
@@ -10444,7 +10396,7 @@
         <v>369</v>
       </c>
       <c r="C346" t="s">
-        <v>1401</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="347" spans="1:3">
@@ -10455,7 +10407,7 @@
         <v>370</v>
       </c>
       <c r="C347" t="s">
-        <v>1402</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="348" spans="1:3">
@@ -10466,7 +10418,7 @@
         <v>371</v>
       </c>
       <c r="C348" t="s">
-        <v>1403</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="349" spans="1:3">
@@ -10477,7 +10429,7 @@
         <v>372</v>
       </c>
       <c r="C349" t="s">
-        <v>1404</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -10488,7 +10440,7 @@
         <v>373</v>
       </c>
       <c r="C350" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="351" spans="1:3">
@@ -10499,7 +10451,7 @@
         <v>374</v>
       </c>
       <c r="C351" t="s">
-        <v>1406</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -10510,7 +10462,7 @@
         <v>375</v>
       </c>
       <c r="C352" t="s">
-        <v>1407</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="353" spans="1:3">
@@ -10521,7 +10473,7 @@
         <v>376</v>
       </c>
       <c r="C353" t="s">
-        <v>1408</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="354" spans="1:3">
@@ -10532,7 +10484,7 @@
         <v>377</v>
       </c>
       <c r="C354" t="s">
-        <v>1409</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -10543,7 +10495,7 @@
         <v>378</v>
       </c>
       <c r="C355" t="s">
-        <v>1410</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="356" spans="1:3">
@@ -10554,7 +10506,7 @@
         <v>379</v>
       </c>
       <c r="C356" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="357" spans="1:3">
@@ -10565,7 +10517,7 @@
         <v>380</v>
       </c>
       <c r="C357" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="358" spans="1:3">
@@ -10576,7 +10528,7 @@
         <v>381</v>
       </c>
       <c r="C358" t="s">
-        <v>1413</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="359" spans="1:3">
@@ -10587,7 +10539,7 @@
         <v>382</v>
       </c>
       <c r="C359" t="s">
-        <v>1414</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -10598,7 +10550,7 @@
         <v>383</v>
       </c>
       <c r="C360" t="s">
-        <v>1415</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="361" spans="1:3">
@@ -10609,7 +10561,7 @@
         <v>384</v>
       </c>
       <c r="C361" t="s">
-        <v>1416</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="362" spans="1:3">
@@ -10620,7 +10572,7 @@
         <v>385</v>
       </c>
       <c r="C362" t="s">
-        <v>1417</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="363" spans="1:3">
@@ -10631,7 +10583,7 @@
         <v>386</v>
       </c>
       <c r="C363" t="s">
-        <v>1418</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="364" spans="1:3">
@@ -10642,7 +10594,7 @@
         <v>387</v>
       </c>
       <c r="C364" t="s">
-        <v>1419</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="365" spans="1:3">
@@ -10653,7 +10605,7 @@
         <v>388</v>
       </c>
       <c r="C365" t="s">
-        <v>1420</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="366" spans="1:3">
@@ -10664,7 +10616,7 @@
         <v>389</v>
       </c>
       <c r="C366" t="s">
-        <v>1421</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="367" spans="1:3">
@@ -10675,7 +10627,7 @@
         <v>390</v>
       </c>
       <c r="C367" t="s">
-        <v>1422</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="368" spans="1:3">
@@ -10686,7 +10638,7 @@
         <v>391</v>
       </c>
       <c r="C368" t="s">
-        <v>1423</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="369" spans="1:3">
@@ -10697,7 +10649,7 @@
         <v>392</v>
       </c>
       <c r="C369" t="s">
-        <v>1424</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="370" spans="1:3">
@@ -10708,7 +10660,7 @@
         <v>393</v>
       </c>
       <c r="C370" t="s">
-        <v>1425</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="371" spans="1:3">
@@ -10719,7 +10671,7 @@
         <v>394</v>
       </c>
       <c r="C371" t="s">
-        <v>1426</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -10730,7 +10682,7 @@
         <v>395</v>
       </c>
       <c r="C372" t="s">
-        <v>1427</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="373" spans="1:3">
@@ -10741,7 +10693,7 @@
         <v>396</v>
       </c>
       <c r="C373" t="s">
-        <v>1428</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="374" spans="1:3">
@@ -10752,7 +10704,7 @@
         <v>397</v>
       </c>
       <c r="C374" t="s">
-        <v>1429</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="375" spans="1:3">
@@ -10763,7 +10715,7 @@
         <v>398</v>
       </c>
       <c r="C375" t="s">
-        <v>1430</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="376" spans="1:3">
@@ -10774,7 +10726,7 @@
         <v>399</v>
       </c>
       <c r="C376" t="s">
-        <v>1431</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="377" spans="1:3">
@@ -10785,7 +10737,7 @@
         <v>400</v>
       </c>
       <c r="C377" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="378" spans="1:3">
@@ -10796,7 +10748,7 @@
         <v>401</v>
       </c>
       <c r="C378" t="s">
-        <v>1433</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="379" spans="1:3">
@@ -10807,7 +10759,7 @@
         <v>402</v>
       </c>
       <c r="C379" t="s">
-        <v>1434</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="380" spans="1:3">
@@ -10818,7 +10770,7 @@
         <v>403</v>
       </c>
       <c r="C380" t="s">
-        <v>1435</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="381" spans="1:3">
@@ -10829,7 +10781,7 @@
         <v>404</v>
       </c>
       <c r="C381" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="382" spans="1:3">
@@ -10840,7 +10792,7 @@
         <v>405</v>
       </c>
       <c r="C382" t="s">
-        <v>1437</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="383" spans="1:3">
@@ -10851,7 +10803,7 @@
         <v>406</v>
       </c>
       <c r="C383" t="s">
-        <v>1438</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="384" spans="1:3">
@@ -10862,7 +10814,7 @@
         <v>407</v>
       </c>
       <c r="C384" t="s">
-        <v>1439</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="385" spans="1:3">
@@ -10873,7 +10825,7 @@
         <v>408</v>
       </c>
       <c r="C385" t="s">
-        <v>1440</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="386" spans="1:3">
@@ -10884,7 +10836,7 @@
         <v>409</v>
       </c>
       <c r="C386" t="s">
-        <v>1441</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="387" spans="1:3">
@@ -10895,7 +10847,7 @@
         <v>410</v>
       </c>
       <c r="C387" t="s">
-        <v>1442</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="388" spans="1:3">
@@ -10906,7 +10858,7 @@
         <v>411</v>
       </c>
       <c r="C388" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="389" spans="1:3">
@@ -10917,7 +10869,7 @@
         <v>412</v>
       </c>
       <c r="C389" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="390" spans="1:3">
@@ -10928,7 +10880,7 @@
         <v>413</v>
       </c>
       <c r="C390" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="391" spans="1:3">
@@ -10939,7 +10891,7 @@
         <v>414</v>
       </c>
       <c r="C391" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="392" spans="1:3">
@@ -10950,7 +10902,7 @@
         <v>415</v>
       </c>
       <c r="C392" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="393" spans="1:3">
@@ -10961,7 +10913,7 @@
         <v>416</v>
       </c>
       <c r="C393" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="394" spans="1:3">
@@ -10972,7 +10924,7 @@
         <v>417</v>
       </c>
       <c r="C394" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="395" spans="1:3">
@@ -10983,7 +10935,7 @@
         <v>418</v>
       </c>
       <c r="C395" t="s">
-        <v>1450</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="396" spans="1:3">
@@ -10994,7 +10946,7 @@
         <v>419</v>
       </c>
       <c r="C396" t="s">
-        <v>1451</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="397" spans="1:3">
@@ -11005,7 +10957,7 @@
         <v>420</v>
       </c>
       <c r="C397" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="398" spans="1:3">
@@ -11016,7 +10968,7 @@
         <v>421</v>
       </c>
       <c r="C398" t="s">
-        <v>1453</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="399" spans="1:3">
@@ -11027,7 +10979,7 @@
         <v>422</v>
       </c>
       <c r="C399" t="s">
-        <v>1454</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="400" spans="1:3">
@@ -11038,7 +10990,7 @@
         <v>423</v>
       </c>
       <c r="C400" t="s">
-        <v>1455</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="401" spans="1:3">
@@ -11049,7 +11001,7 @@
         <v>424</v>
       </c>
       <c r="C401" t="s">
-        <v>1456</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="402" spans="1:3">
@@ -11060,7 +11012,7 @@
         <v>425</v>
       </c>
       <c r="C402" t="s">
-        <v>1457</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="403" spans="1:3">
@@ -11071,7 +11023,7 @@
         <v>426</v>
       </c>
       <c r="C403" t="s">
-        <v>1458</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="404" spans="1:3">
@@ -11082,7 +11034,7 @@
         <v>427</v>
       </c>
       <c r="C404" t="s">
-        <v>1459</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="405" spans="1:3">
@@ -11093,7 +11045,7 @@
         <v>428</v>
       </c>
       <c r="C405" t="s">
-        <v>1460</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="406" spans="1:3">
@@ -11104,7 +11056,7 @@
         <v>429</v>
       </c>
       <c r="C406" t="s">
-        <v>1461</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="407" spans="1:3">
@@ -11115,7 +11067,7 @@
         <v>430</v>
       </c>
       <c r="C407" t="s">
-        <v>1462</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="408" spans="1:3">
@@ -11126,7 +11078,7 @@
         <v>431</v>
       </c>
       <c r="C408" t="s">
-        <v>1463</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="409" spans="1:3">
@@ -11137,7 +11089,7 @@
         <v>432</v>
       </c>
       <c r="C409" t="s">
-        <v>1464</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="410" spans="1:3">
@@ -11148,7 +11100,7 @@
         <v>433</v>
       </c>
       <c r="C410" t="s">
-        <v>1465</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="411" spans="1:3">
@@ -11159,7 +11111,7 @@
         <v>434</v>
       </c>
       <c r="C411" t="s">
-        <v>1466</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="412" spans="1:3">
@@ -11170,7 +11122,7 @@
         <v>435</v>
       </c>
       <c r="C412" t="s">
-        <v>1467</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="413" spans="1:3">
@@ -11181,7 +11133,7 @@
         <v>436</v>
       </c>
       <c r="C413" t="s">
-        <v>1468</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="414" spans="1:3">
@@ -11192,7 +11144,7 @@
         <v>437</v>
       </c>
       <c r="C414" t="s">
-        <v>1469</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="415" spans="1:3">
@@ -11203,7 +11155,7 @@
         <v>438</v>
       </c>
       <c r="C415" t="s">
-        <v>1470</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="416" spans="1:3">
@@ -11214,7 +11166,7 @@
         <v>439</v>
       </c>
       <c r="C416" t="s">
-        <v>1471</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="417" spans="1:3">
@@ -11225,7 +11177,7 @@
         <v>440</v>
       </c>
       <c r="C417" t="s">
-        <v>1472</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="418" spans="1:3">
@@ -11236,7 +11188,7 @@
         <v>441</v>
       </c>
       <c r="C418" t="s">
-        <v>1473</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="419" spans="1:3">
@@ -11247,7 +11199,7 @@
         <v>442</v>
       </c>
       <c r="C419" t="s">
-        <v>1474</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="420" spans="1:3">
@@ -11258,7 +11210,7 @@
         <v>443</v>
       </c>
       <c r="C420" t="s">
-        <v>1475</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="421" spans="1:3">
@@ -11269,7 +11221,7 @@
         <v>444</v>
       </c>
       <c r="C421" t="s">
-        <v>1476</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="422" spans="1:3">
@@ -11280,7 +11232,7 @@
         <v>445</v>
       </c>
       <c r="C422" t="s">
-        <v>1477</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="423" spans="1:3">
@@ -11291,7 +11243,7 @@
         <v>446</v>
       </c>
       <c r="C423" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="424" spans="1:3">
@@ -11302,7 +11254,7 @@
         <v>447</v>
       </c>
       <c r="C424" t="s">
-        <v>1479</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="425" spans="1:3">
@@ -11313,7 +11265,7 @@
         <v>448</v>
       </c>
       <c r="C425" t="s">
-        <v>1480</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="426" spans="1:3">
@@ -11324,7 +11276,7 @@
         <v>449</v>
       </c>
       <c r="C426" t="s">
-        <v>1481</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="427" spans="1:3">
@@ -11335,7 +11287,7 @@
         <v>450</v>
       </c>
       <c r="C427" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="428" spans="1:3">
@@ -11346,7 +11298,7 @@
         <v>451</v>
       </c>
       <c r="C428" t="s">
-        <v>1483</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="429" spans="1:3">
@@ -11357,7 +11309,7 @@
         <v>452</v>
       </c>
       <c r="C429" t="s">
-        <v>1484</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="430" spans="1:3">
@@ -11368,7 +11320,7 @@
         <v>453</v>
       </c>
       <c r="C430" t="s">
-        <v>1485</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="431" spans="1:3">
@@ -11379,7 +11331,7 @@
         <v>454</v>
       </c>
       <c r="C431" t="s">
-        <v>1486</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="432" spans="1:3">
@@ -11390,7 +11342,7 @@
         <v>455</v>
       </c>
       <c r="C432" t="s">
-        <v>1487</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="433" spans="1:3">
@@ -11401,7 +11353,7 @@
         <v>456</v>
       </c>
       <c r="C433" t="s">
-        <v>1488</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="434" spans="1:3">
@@ -11412,7 +11364,7 @@
         <v>457</v>
       </c>
       <c r="C434" t="s">
-        <v>1489</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="435" spans="1:3">
@@ -11423,7 +11375,7 @@
         <v>458</v>
       </c>
       <c r="C435" t="s">
-        <v>1490</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="436" spans="1:3">
@@ -11434,7 +11386,7 @@
         <v>459</v>
       </c>
       <c r="C436" t="s">
-        <v>1491</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="437" spans="1:3">
@@ -11445,7 +11397,7 @@
         <v>460</v>
       </c>
       <c r="C437" t="s">
-        <v>1492</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="438" spans="1:3">
@@ -11456,7 +11408,7 @@
         <v>461</v>
       </c>
       <c r="C438" t="s">
-        <v>1493</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="439" spans="1:3">
@@ -11467,7 +11419,7 @@
         <v>462</v>
       </c>
       <c r="C439" t="s">
-        <v>1494</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="440" spans="1:3">
@@ -11478,7 +11430,7 @@
         <v>463</v>
       </c>
       <c r="C440" t="s">
-        <v>1495</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="441" spans="1:3">
@@ -11489,7 +11441,7 @@
         <v>464</v>
       </c>
       <c r="C441" t="s">
-        <v>1496</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="442" spans="1:3">
@@ -11500,7 +11452,7 @@
         <v>465</v>
       </c>
       <c r="C442" t="s">
-        <v>1497</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="443" spans="1:3">
@@ -11511,7 +11463,7 @@
         <v>466</v>
       </c>
       <c r="C443" t="s">
-        <v>1498</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="444" spans="1:3">
@@ -11522,7 +11474,7 @@
         <v>467</v>
       </c>
       <c r="C444" t="s">
-        <v>1499</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="445" spans="1:3">
@@ -11533,7 +11485,7 @@
         <v>468</v>
       </c>
       <c r="C445" t="s">
-        <v>1500</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="446" spans="1:3">
@@ -11544,7 +11496,7 @@
         <v>469</v>
       </c>
       <c r="C446" t="s">
-        <v>1501</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="447" spans="1:3">
@@ -11555,7 +11507,7 @@
         <v>470</v>
       </c>
       <c r="C447" t="s">
-        <v>1502</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="448" spans="1:3">
@@ -11566,7 +11518,7 @@
         <v>471</v>
       </c>
       <c r="C448" t="s">
-        <v>1503</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="449" spans="1:3">
@@ -11577,7 +11529,7 @@
         <v>472</v>
       </c>
       <c r="C449" t="s">
-        <v>1504</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="450" spans="1:3">
@@ -11588,7 +11540,7 @@
         <v>473</v>
       </c>
       <c r="C450" t="s">
-        <v>1505</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="451" spans="1:3">
@@ -11599,7 +11551,7 @@
         <v>474</v>
       </c>
       <c r="C451" t="s">
-        <v>1506</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="452" spans="1:3">
@@ -11610,7 +11562,7 @@
         <v>475</v>
       </c>
       <c r="C452" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="453" spans="1:3">
@@ -11621,7 +11573,7 @@
         <v>476</v>
       </c>
       <c r="C453" t="s">
-        <v>1508</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="454" spans="1:3">
@@ -11632,7 +11584,7 @@
         <v>477</v>
       </c>
       <c r="C454" t="s">
-        <v>1509</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="455" spans="1:3">
@@ -11643,7 +11595,7 @@
         <v>478</v>
       </c>
       <c r="C455" t="s">
-        <v>1510</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="456" spans="1:3">
@@ -11654,7 +11606,7 @@
         <v>479</v>
       </c>
       <c r="C456" t="s">
-        <v>1511</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="457" spans="1:3">
@@ -11665,7 +11617,7 @@
         <v>480</v>
       </c>
       <c r="C457" t="s">
-        <v>1512</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="458" spans="1:3">
@@ -11676,7 +11628,7 @@
         <v>481</v>
       </c>
       <c r="C458" t="s">
-        <v>1513</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="459" spans="1:3">
@@ -11687,7 +11639,7 @@
         <v>482</v>
       </c>
       <c r="C459" t="s">
-        <v>1514</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="460" spans="1:3">
@@ -11698,7 +11650,7 @@
         <v>483</v>
       </c>
       <c r="C460" t="s">
-        <v>1515</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="461" spans="1:3">
@@ -11709,7 +11661,7 @@
         <v>484</v>
       </c>
       <c r="C461" t="s">
-        <v>1484</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="462" spans="1:3">
@@ -11720,7 +11672,7 @@
         <v>485</v>
       </c>
       <c r="C462" t="s">
-        <v>1476</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="463" spans="1:3">
@@ -11731,7 +11683,7 @@
         <v>486</v>
       </c>
       <c r="C463" t="s">
-        <v>1516</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="464" spans="1:3">
@@ -11742,7 +11694,7 @@
         <v>487</v>
       </c>
       <c r="C464" t="s">
-        <v>1517</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="465" spans="1:3">
@@ -11753,7 +11705,7 @@
         <v>488</v>
       </c>
       <c r="C465" t="s">
-        <v>1518</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="466" spans="1:3">
@@ -11764,7 +11716,7 @@
         <v>489</v>
       </c>
       <c r="C466" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="467" spans="1:3">
@@ -11775,7 +11727,7 @@
         <v>490</v>
       </c>
       <c r="C467" t="s">
-        <v>1520</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="468" spans="1:3">
@@ -11786,7 +11738,7 @@
         <v>491</v>
       </c>
       <c r="C468" t="s">
-        <v>1521</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="469" spans="1:3">
@@ -11797,7 +11749,7 @@
         <v>492</v>
       </c>
       <c r="C469" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="470" spans="1:3">
@@ -11808,7 +11760,7 @@
         <v>493</v>
       </c>
       <c r="C470" t="s">
-        <v>1523</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="471" spans="1:3">
@@ -11819,7 +11771,7 @@
         <v>494</v>
       </c>
       <c r="C471" t="s">
-        <v>1524</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="472" spans="1:3">
@@ -11830,7 +11782,7 @@
         <v>495</v>
       </c>
       <c r="C472" t="s">
-        <v>1525</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="473" spans="1:3">
@@ -11841,7 +11793,7 @@
         <v>496</v>
       </c>
       <c r="C473" t="s">
-        <v>1526</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="474" spans="1:3">
@@ -11852,7 +11804,7 @@
         <v>497</v>
       </c>
       <c r="C474" t="s">
-        <v>1527</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="475" spans="1:3">
@@ -11863,7 +11815,7 @@
         <v>498</v>
       </c>
       <c r="C475" t="s">
-        <v>1528</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="476" spans="1:3">
@@ -11874,7 +11826,7 @@
         <v>499</v>
       </c>
       <c r="C476" t="s">
-        <v>1529</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="477" spans="1:3">
@@ -11885,7 +11837,7 @@
         <v>500</v>
       </c>
       <c r="C477" t="s">
-        <v>1530</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="478" spans="1:3">
@@ -11896,7 +11848,7 @@
         <v>501</v>
       </c>
       <c r="C478" t="s">
-        <v>1531</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="479" spans="1:3">
@@ -11907,7 +11859,7 @@
         <v>502</v>
       </c>
       <c r="C479" t="s">
-        <v>1532</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="480" spans="1:3">
@@ -11918,7 +11870,7 @@
         <v>503</v>
       </c>
       <c r="C480" t="s">
-        <v>1533</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="481" spans="1:3">
@@ -11929,7 +11881,7 @@
         <v>504</v>
       </c>
       <c r="C481" t="s">
-        <v>1534</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="482" spans="1:3">
@@ -11940,7 +11892,7 @@
         <v>505</v>
       </c>
       <c r="C482" t="s">
-        <v>1535</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="483" spans="1:3">
@@ -11951,7 +11903,7 @@
         <v>506</v>
       </c>
       <c r="C483" t="s">
-        <v>1536</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="484" spans="1:3">
@@ -11962,7 +11914,7 @@
         <v>507</v>
       </c>
       <c r="C484" t="s">
-        <v>1537</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="485" spans="1:3">
@@ -11973,7 +11925,7 @@
         <v>508</v>
       </c>
       <c r="C485" t="s">
-        <v>1538</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="486" spans="1:3">
@@ -11984,7 +11936,7 @@
         <v>509</v>
       </c>
       <c r="C486" t="s">
-        <v>1539</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="487" spans="1:3">
@@ -11995,7 +11947,7 @@
         <v>510</v>
       </c>
       <c r="C487" t="s">
-        <v>1540</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="488" spans="1:3">
@@ -12006,7 +11958,7 @@
         <v>511</v>
       </c>
       <c r="C488" t="s">
-        <v>1541</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="489" spans="1:3">
@@ -12017,7 +11969,7 @@
         <v>512</v>
       </c>
       <c r="C489" t="s">
-        <v>1542</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="490" spans="1:3">
@@ -12028,7 +11980,7 @@
         <v>513</v>
       </c>
       <c r="C490" t="s">
-        <v>1543</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="491" spans="1:3">
@@ -12039,7 +11991,7 @@
         <v>514</v>
       </c>
       <c r="C491" t="s">
-        <v>1544</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="492" spans="1:3">
@@ -12050,7 +12002,7 @@
         <v>515</v>
       </c>
       <c r="C492" t="s">
-        <v>1545</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="493" spans="1:3">
@@ -12061,7 +12013,7 @@
         <v>516</v>
       </c>
       <c r="C493" t="s">
-        <v>1546</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="494" spans="1:3">
@@ -12072,7 +12024,7 @@
         <v>517</v>
       </c>
       <c r="C494" t="s">
-        <v>1547</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="495" spans="1:3">
@@ -12083,7 +12035,7 @@
         <v>518</v>
       </c>
       <c r="C495" t="s">
-        <v>1548</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="496" spans="1:3">
@@ -12094,7 +12046,7 @@
         <v>519</v>
       </c>
       <c r="C496" t="s">
-        <v>1549</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="497" spans="1:3">
@@ -12105,7 +12057,7 @@
         <v>520</v>
       </c>
       <c r="C497" t="s">
-        <v>1550</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="498" spans="1:3">
@@ -12116,7 +12068,7 @@
         <v>521</v>
       </c>
       <c r="C498" t="s">
-        <v>1551</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="499" spans="1:3">
@@ -12127,7 +12079,7 @@
         <v>522</v>
       </c>
       <c r="C499" t="s">
-        <v>1552</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="500" spans="1:3">
@@ -12138,7 +12090,7 @@
         <v>523</v>
       </c>
       <c r="C500" t="s">
-        <v>1553</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="501" spans="1:3">
@@ -12149,7 +12101,7 @@
         <v>524</v>
       </c>
       <c r="C501" t="s">
-        <v>1554</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="502" spans="1:3">
@@ -12160,7 +12112,7 @@
         <v>525</v>
       </c>
       <c r="C502" t="s">
-        <v>1555</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="503" spans="1:3">
@@ -12171,7 +12123,7 @@
         <v>526</v>
       </c>
       <c r="C503" t="s">
-        <v>1556</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="504" spans="1:3">
@@ -12182,7 +12134,7 @@
         <v>527</v>
       </c>
       <c r="C504" t="s">
-        <v>1557</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="505" spans="1:3">
@@ -12193,7 +12145,7 @@
         <v>528</v>
       </c>
       <c r="C505" t="s">
-        <v>1558</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="506" spans="1:3">
@@ -12204,7 +12156,7 @@
         <v>529</v>
       </c>
       <c r="C506" t="s">
-        <v>1559</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="507" spans="1:3">
@@ -12215,7 +12167,7 @@
         <v>530</v>
       </c>
       <c r="C507" t="s">
-        <v>1560</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="508" spans="1:3">
@@ -12226,7 +12178,7 @@
         <v>531</v>
       </c>
       <c r="C508" t="s">
-        <v>1561</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="509" spans="1:3">
@@ -12237,7 +12189,7 @@
         <v>532</v>
       </c>
       <c r="C509" t="s">
-        <v>1562</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="510" spans="1:3">
@@ -12248,7 +12200,7 @@
         <v>533</v>
       </c>
       <c r="C510" t="s">
-        <v>1563</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="511" spans="1:3">
@@ -12259,7 +12211,7 @@
         <v>534</v>
       </c>
       <c r="C511" t="s">
-        <v>1564</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="512" spans="1:3">
@@ -12270,7 +12222,7 @@
         <v>535</v>
       </c>
       <c r="C512" t="s">
-        <v>1565</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="513" spans="1:3">
@@ -12281,7 +12233,7 @@
         <v>536</v>
       </c>
       <c r="C513" t="s">
-        <v>1566</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="514" spans="1:3">
@@ -12292,7 +12244,7 @@
         <v>537</v>
       </c>
       <c r="C514" t="s">
-        <v>1567</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="515" spans="1:3">
@@ -12303,7 +12255,7 @@
         <v>538</v>
       </c>
       <c r="C515" t="s">
-        <v>1568</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="516" spans="1:3">
@@ -12314,7 +12266,7 @@
         <v>539</v>
       </c>
       <c r="C516" t="s">
-        <v>1569</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="517" spans="1:3">
@@ -12325,7 +12277,7 @@
         <v>540</v>
       </c>
       <c r="C517" t="s">
-        <v>1570</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="518" spans="1:3">
@@ -12336,7 +12288,7 @@
         <v>541</v>
       </c>
       <c r="C518" t="s">
-        <v>1571</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="519" spans="1:3">
@@ -12347,7 +12299,7 @@
         <v>542</v>
       </c>
       <c r="C519" t="s">
-        <v>1572</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="520" spans="1:3">
@@ -12358,7 +12310,7 @@
         <v>543</v>
       </c>
       <c r="C520" t="s">
-        <v>1573</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="521" spans="1:3">
@@ -12369,7 +12321,7 @@
         <v>544</v>
       </c>
       <c r="C521" t="s">
-        <v>1574</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="522" spans="1:3">
@@ -12380,7 +12332,7 @@
         <v>545</v>
       </c>
       <c r="C522" t="s">
-        <v>1575</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="523" spans="1:3">
@@ -12391,7 +12343,7 @@
         <v>546</v>
       </c>
       <c r="C523" t="s">
-        <v>1576</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="524" spans="1:3">
@@ -12402,7 +12354,7 @@
         <v>547</v>
       </c>
       <c r="C524" t="s">
-        <v>1577</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="525" spans="1:3">
@@ -12413,7 +12365,7 @@
         <v>548</v>
       </c>
       <c r="C525" t="s">
-        <v>1578</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="526" spans="1:3">
@@ -12424,7 +12376,7 @@
         <v>549</v>
       </c>
       <c r="C526" t="s">
-        <v>1579</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="527" spans="1:3">
@@ -12435,7 +12387,7 @@
         <v>550</v>
       </c>
       <c r="C527" t="s">
-        <v>1580</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="528" spans="1:3">
@@ -12446,7 +12398,7 @@
         <v>551</v>
       </c>
       <c r="C528" t="s">
-        <v>1581</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="529" spans="1:3">
@@ -12457,7 +12409,7 @@
         <v>552</v>
       </c>
       <c r="C529" t="s">
-        <v>1582</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="530" spans="1:3">
@@ -12468,7 +12420,7 @@
         <v>553</v>
       </c>
       <c r="C530" t="s">
-        <v>1583</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="531" spans="1:3">
@@ -12479,7 +12431,7 @@
         <v>554</v>
       </c>
       <c r="C531" t="s">
-        <v>1584</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="532" spans="1:3">
@@ -12490,7 +12442,7 @@
         <v>555</v>
       </c>
       <c r="C532" t="s">
-        <v>1585</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="533" spans="1:3">
@@ -12501,7 +12453,7 @@
         <v>556</v>
       </c>
       <c r="C533" t="s">
-        <v>1586</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="534" spans="1:3">
@@ -12512,7 +12464,7 @@
         <v>557</v>
       </c>
       <c r="C534" t="s">
-        <v>1587</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="535" spans="1:3">
@@ -12523,7 +12475,7 @@
         <v>558</v>
       </c>
       <c r="C535" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="536" spans="1:3">
@@ -12534,7 +12486,7 @@
         <v>559</v>
       </c>
       <c r="C536" t="s">
-        <v>1589</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="537" spans="1:3">
@@ -12545,7 +12497,7 @@
         <v>560</v>
       </c>
       <c r="C537" t="s">
-        <v>1590</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="538" spans="1:3">
@@ -12556,7 +12508,7 @@
         <v>561</v>
       </c>
       <c r="C538" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="539" spans="1:3">
@@ -12567,51 +12519,51 @@
         <v>562</v>
       </c>
       <c r="C539" t="s">
-        <v>1592</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="540" spans="1:3">
       <c r="A540" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B540" t="s">
         <v>563</v>
       </c>
       <c r="C540" t="s">
-        <v>1593</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="541" spans="1:3">
       <c r="A541" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B541" t="s">
         <v>564</v>
       </c>
       <c r="C541" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="542" spans="1:3">
       <c r="A542" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B542" t="s">
         <v>565</v>
       </c>
       <c r="C542" t="s">
-        <v>1595</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="543" spans="1:3">
       <c r="A543" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B543" t="s">
         <v>566</v>
       </c>
       <c r="C543" t="s">
-        <v>1596</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="544" spans="1:3">
@@ -12622,7 +12574,7 @@
         <v>567</v>
       </c>
       <c r="C544" t="s">
-        <v>1597</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="545" spans="1:3">
@@ -12633,7 +12585,7 @@
         <v>568</v>
       </c>
       <c r="C545" t="s">
-        <v>1598</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="546" spans="1:3">
@@ -12644,7 +12596,7 @@
         <v>569</v>
       </c>
       <c r="C546" t="s">
-        <v>1599</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="547" spans="1:3">
@@ -12655,7 +12607,7 @@
         <v>570</v>
       </c>
       <c r="C547" t="s">
-        <v>1600</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="548" spans="1:3">
@@ -12666,7 +12618,7 @@
         <v>571</v>
       </c>
       <c r="C548" t="s">
-        <v>1601</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="549" spans="1:3">
@@ -12677,7 +12629,7 @@
         <v>572</v>
       </c>
       <c r="C549" t="s">
-        <v>1602</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="550" spans="1:3">
@@ -12688,7 +12640,7 @@
         <v>573</v>
       </c>
       <c r="C550" t="s">
-        <v>1603</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="551" spans="1:3">
@@ -12699,7 +12651,7 @@
         <v>574</v>
       </c>
       <c r="C551" t="s">
-        <v>1604</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="552" spans="1:3">
@@ -12710,7 +12662,7 @@
         <v>575</v>
       </c>
       <c r="C552" t="s">
-        <v>1605</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="553" spans="1:3">
@@ -12721,7 +12673,7 @@
         <v>576</v>
       </c>
       <c r="C553" t="s">
-        <v>1606</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="554" spans="1:3">
@@ -12732,7 +12684,7 @@
         <v>577</v>
       </c>
       <c r="C554" t="s">
-        <v>1607</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="555" spans="1:3">
@@ -12743,7 +12695,7 @@
         <v>578</v>
       </c>
       <c r="C555" t="s">
-        <v>1608</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="556" spans="1:3">
@@ -12754,7 +12706,7 @@
         <v>579</v>
       </c>
       <c r="C556" t="s">
-        <v>1609</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="557" spans="1:3">
@@ -12765,7 +12717,7 @@
         <v>580</v>
       </c>
       <c r="C557" t="s">
-        <v>1610</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="558" spans="1:3">
@@ -12776,7 +12728,7 @@
         <v>581</v>
       </c>
       <c r="C558" t="s">
-        <v>1611</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="559" spans="1:3">
@@ -12787,7 +12739,7 @@
         <v>582</v>
       </c>
       <c r="C559" t="s">
-        <v>1612</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="560" spans="1:3">
@@ -12798,7 +12750,7 @@
         <v>583</v>
       </c>
       <c r="C560" t="s">
-        <v>1613</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="561" spans="1:3">
@@ -12809,7 +12761,7 @@
         <v>584</v>
       </c>
       <c r="C561" t="s">
-        <v>1614</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="562" spans="1:3">
@@ -12820,7 +12772,7 @@
         <v>585</v>
       </c>
       <c r="C562" t="s">
-        <v>1615</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="563" spans="1:3">
@@ -12831,7 +12783,7 @@
         <v>586</v>
       </c>
       <c r="C563" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="564" spans="1:3">
@@ -12842,7 +12794,7 @@
         <v>587</v>
       </c>
       <c r="C564" t="s">
-        <v>1617</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="565" spans="1:3">
@@ -12853,7 +12805,7 @@
         <v>588</v>
       </c>
       <c r="C565" t="s">
-        <v>1618</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="566" spans="1:3">
@@ -12864,7 +12816,7 @@
         <v>589</v>
       </c>
       <c r="C566" t="s">
-        <v>1619</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="567" spans="1:3">
@@ -12875,7 +12827,7 @@
         <v>590</v>
       </c>
       <c r="C567" t="s">
-        <v>1620</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="568" spans="1:3">
@@ -12886,7 +12838,7 @@
         <v>591</v>
       </c>
       <c r="C568" t="s">
-        <v>1621</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="569" spans="1:3">
@@ -12897,7 +12849,7 @@
         <v>592</v>
       </c>
       <c r="C569" t="s">
-        <v>1622</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="570" spans="1:3">
@@ -12908,7 +12860,7 @@
         <v>593</v>
       </c>
       <c r="C570" t="s">
-        <v>1623</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="571" spans="1:3">
@@ -12919,7 +12871,7 @@
         <v>594</v>
       </c>
       <c r="C571" t="s">
-        <v>1624</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="572" spans="1:3">
@@ -12930,7 +12882,7 @@
         <v>595</v>
       </c>
       <c r="C572" t="s">
-        <v>1625</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="573" spans="1:3">
@@ -12941,7 +12893,7 @@
         <v>596</v>
       </c>
       <c r="C573" t="s">
-        <v>1626</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="574" spans="1:3">
@@ -12952,7 +12904,7 @@
         <v>597</v>
       </c>
       <c r="C574" t="s">
-        <v>1627</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="575" spans="1:3">
@@ -12963,7 +12915,7 @@
         <v>598</v>
       </c>
       <c r="C575" t="s">
-        <v>1628</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="576" spans="1:3">
@@ -12974,7 +12926,7 @@
         <v>599</v>
       </c>
       <c r="C576" t="s">
-        <v>1629</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="577" spans="1:3">
@@ -12985,7 +12937,7 @@
         <v>600</v>
       </c>
       <c r="C577" t="s">
-        <v>1630</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="578" spans="1:3">
@@ -12996,7 +12948,7 @@
         <v>601</v>
       </c>
       <c r="C578" t="s">
-        <v>1631</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="579" spans="1:3">
@@ -13007,7 +12959,7 @@
         <v>602</v>
       </c>
       <c r="C579" t="s">
-        <v>1632</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="580" spans="1:3">
@@ -13018,7 +12970,7 @@
         <v>603</v>
       </c>
       <c r="C580" t="s">
-        <v>1602</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="581" spans="1:3">
@@ -13029,7 +12981,7 @@
         <v>604</v>
       </c>
       <c r="C581" t="s">
-        <v>1633</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="582" spans="1:3">
@@ -13040,51 +12992,51 @@
         <v>605</v>
       </c>
       <c r="C582" t="s">
-        <v>1634</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="583" spans="1:3">
       <c r="A583" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B583" t="s">
         <v>606</v>
       </c>
       <c r="C583" t="s">
-        <v>1635</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="584" spans="1:3">
       <c r="A584" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B584" t="s">
         <v>607</v>
       </c>
       <c r="C584" t="s">
-        <v>1636</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="585" spans="1:3">
       <c r="A585" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B585" t="s">
         <v>608</v>
       </c>
       <c r="C585" t="s">
-        <v>1637</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="586" spans="1:3">
       <c r="A586" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B586" t="s">
         <v>609</v>
       </c>
       <c r="C586" t="s">
-        <v>1638</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="587" spans="1:3">
@@ -13095,7 +13047,7 @@
         <v>610</v>
       </c>
       <c r="C587" t="s">
-        <v>1639</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="588" spans="1:3">
@@ -13106,7 +13058,7 @@
         <v>611</v>
       </c>
       <c r="C588" t="s">
-        <v>1640</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="589" spans="1:3">
@@ -13117,51 +13069,51 @@
         <v>612</v>
       </c>
       <c r="C589" t="s">
-        <v>1641</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="590" spans="1:3">
       <c r="A590" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B590" t="s">
         <v>613</v>
       </c>
       <c r="C590" t="s">
-        <v>1642</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="591" spans="1:3">
       <c r="A591" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B591" t="s">
         <v>614</v>
       </c>
       <c r="C591" t="s">
-        <v>1643</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="592" spans="1:3">
       <c r="A592" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B592" t="s">
         <v>615</v>
       </c>
       <c r="C592" t="s">
-        <v>1644</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="593" spans="1:3">
       <c r="A593" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B593" t="s">
         <v>616</v>
       </c>
       <c r="C593" t="s">
-        <v>1645</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="594" spans="1:3">
@@ -13172,7 +13124,7 @@
         <v>617</v>
       </c>
       <c r="C594" t="s">
-        <v>1646</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="595" spans="1:3">
@@ -13183,7 +13135,7 @@
         <v>618</v>
       </c>
       <c r="C595" t="s">
-        <v>1647</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="596" spans="1:3">
@@ -13194,7 +13146,7 @@
         <v>619</v>
       </c>
       <c r="C596" t="s">
-        <v>1648</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="597" spans="1:3">
@@ -13205,7 +13157,7 @@
         <v>620</v>
       </c>
       <c r="C597" t="s">
-        <v>1649</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="598" spans="1:3">
@@ -13216,7 +13168,7 @@
         <v>621</v>
       </c>
       <c r="C598" t="s">
-        <v>1650</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="599" spans="1:3">
@@ -13227,7 +13179,7 @@
         <v>622</v>
       </c>
       <c r="C599" t="s">
-        <v>1651</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="600" spans="1:3">
@@ -13238,7 +13190,7 @@
         <v>623</v>
       </c>
       <c r="C600" t="s">
-        <v>1652</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="601" spans="1:3">
@@ -13249,7 +13201,7 @@
         <v>624</v>
       </c>
       <c r="C601" t="s">
-        <v>1653</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="602" spans="1:3">
@@ -13260,7 +13212,7 @@
         <v>625</v>
       </c>
       <c r="C602" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="603" spans="1:3">
@@ -13271,7 +13223,7 @@
         <v>626</v>
       </c>
       <c r="C603" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="604" spans="1:3">
@@ -13282,7 +13234,7 @@
         <v>627</v>
       </c>
       <c r="C604" t="s">
-        <v>1656</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="605" spans="1:3">
@@ -13293,7 +13245,7 @@
         <v>628</v>
       </c>
       <c r="C605" t="s">
-        <v>1657</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="606" spans="1:3">
@@ -13304,7 +13256,7 @@
         <v>629</v>
       </c>
       <c r="C606" t="s">
-        <v>1658</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="607" spans="1:3">
@@ -13315,7 +13267,7 @@
         <v>630</v>
       </c>
       <c r="C607" t="s">
-        <v>1659</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="608" spans="1:3">
@@ -13326,7 +13278,7 @@
         <v>631</v>
       </c>
       <c r="C608" t="s">
-        <v>1660</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="609" spans="1:3">
@@ -13337,7 +13289,7 @@
         <v>632</v>
       </c>
       <c r="C609" t="s">
-        <v>1661</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="610" spans="1:3">
@@ -13348,7 +13300,7 @@
         <v>633</v>
       </c>
       <c r="C610" t="s">
-        <v>1662</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="611" spans="1:3">
@@ -13359,7 +13311,7 @@
         <v>634</v>
       </c>
       <c r="C611" t="s">
-        <v>1663</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="612" spans="1:3">
@@ -13370,7 +13322,7 @@
         <v>635</v>
       </c>
       <c r="C612" t="s">
-        <v>1664</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="613" spans="1:3">
@@ -13381,7 +13333,7 @@
         <v>636</v>
       </c>
       <c r="C613" t="s">
-        <v>1665</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="614" spans="1:3">
@@ -13392,7 +13344,7 @@
         <v>637</v>
       </c>
       <c r="C614" t="s">
-        <v>1666</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="615" spans="1:3">
@@ -13403,51 +13355,51 @@
         <v>638</v>
       </c>
       <c r="C615" t="s">
-        <v>1667</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="616" spans="1:3">
       <c r="A616" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B616" t="s">
         <v>639</v>
       </c>
       <c r="C616" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="617" spans="1:3">
       <c r="A617" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B617" t="s">
         <v>640</v>
       </c>
       <c r="C617" t="s">
-        <v>1669</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="618" spans="1:3">
       <c r="A618" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B618" t="s">
         <v>641</v>
       </c>
       <c r="C618" t="s">
-        <v>1670</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="619" spans="1:3">
       <c r="A619" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B619" t="s">
         <v>642</v>
       </c>
       <c r="C619" t="s">
-        <v>1671</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="620" spans="1:3">
@@ -13458,7 +13410,7 @@
         <v>643</v>
       </c>
       <c r="C620" t="s">
-        <v>1672</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="621" spans="1:3">
@@ -13469,7 +13421,7 @@
         <v>644</v>
       </c>
       <c r="C621" t="s">
-        <v>1673</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="622" spans="1:3">
@@ -13480,7 +13432,7 @@
         <v>645</v>
       </c>
       <c r="C622" t="s">
-        <v>1674</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="623" spans="1:3">
@@ -13491,7 +13443,7 @@
         <v>646</v>
       </c>
       <c r="C623" t="s">
-        <v>1675</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="624" spans="1:3">
@@ -13502,7 +13454,7 @@
         <v>647</v>
       </c>
       <c r="C624" t="s">
-        <v>1676</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="625" spans="1:3">
@@ -13513,7 +13465,7 @@
         <v>648</v>
       </c>
       <c r="C625" t="s">
-        <v>1677</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="626" spans="1:3">
@@ -13524,51 +13476,51 @@
         <v>649</v>
       </c>
       <c r="C626" t="s">
-        <v>1678</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="627" spans="1:3">
       <c r="A627" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B627" t="s">
         <v>650</v>
       </c>
       <c r="C627" t="s">
-        <v>1679</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="628" spans="1:3">
       <c r="A628" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B628" t="s">
         <v>651</v>
       </c>
       <c r="C628" t="s">
-        <v>1680</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="629" spans="1:3">
       <c r="A629" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B629" t="s">
         <v>652</v>
       </c>
       <c r="C629" t="s">
-        <v>1681</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="630" spans="1:3">
       <c r="A630" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B630" t="s">
         <v>653</v>
       </c>
       <c r="C630" t="s">
-        <v>1682</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="631" spans="1:3">
@@ -13579,7 +13531,7 @@
         <v>654</v>
       </c>
       <c r="C631" t="s">
-        <v>1683</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="632" spans="1:3">
@@ -13590,7 +13542,7 @@
         <v>655</v>
       </c>
       <c r="C632" t="s">
-        <v>1684</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="633" spans="1:3">
@@ -13601,7 +13553,7 @@
         <v>656</v>
       </c>
       <c r="C633" t="s">
-        <v>1685</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="634" spans="1:3">
@@ -13612,7 +13564,7 @@
         <v>657</v>
       </c>
       <c r="C634" t="s">
-        <v>1686</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="635" spans="1:3">
@@ -13623,7 +13575,7 @@
         <v>658</v>
       </c>
       <c r="C635" t="s">
-        <v>1687</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="636" spans="1:3">
@@ -13634,7 +13586,7 @@
         <v>659</v>
       </c>
       <c r="C636" t="s">
-        <v>1688</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="637" spans="1:3">
@@ -13645,7 +13597,7 @@
         <v>660</v>
       </c>
       <c r="C637" t="s">
-        <v>1689</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="638" spans="1:3">
@@ -13656,7 +13608,7 @@
         <v>661</v>
       </c>
       <c r="C638" t="s">
-        <v>1690</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="639" spans="1:3">
@@ -13667,7 +13619,7 @@
         <v>662</v>
       </c>
       <c r="C639" t="s">
-        <v>1691</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="640" spans="1:3">
@@ -13678,7 +13630,7 @@
         <v>663</v>
       </c>
       <c r="C640" t="s">
-        <v>1692</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="641" spans="1:3">
@@ -13689,7 +13641,7 @@
         <v>664</v>
       </c>
       <c r="C641" t="s">
-        <v>1693</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="642" spans="1:3">
@@ -13700,7 +13652,7 @@
         <v>665</v>
       </c>
       <c r="C642" t="s">
-        <v>1694</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="643" spans="1:3">
@@ -13711,7 +13663,7 @@
         <v>666</v>
       </c>
       <c r="C643" t="s">
-        <v>1695</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="644" spans="1:3">
@@ -13722,7 +13674,7 @@
         <v>667</v>
       </c>
       <c r="C644" t="s">
-        <v>1696</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="645" spans="1:3">
@@ -13733,7 +13685,7 @@
         <v>668</v>
       </c>
       <c r="C645" t="s">
-        <v>1697</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="646" spans="1:3">
@@ -13744,7 +13696,7 @@
         <v>669</v>
       </c>
       <c r="C646" t="s">
-        <v>1698</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="647" spans="1:3">
@@ -13755,7 +13707,7 @@
         <v>670</v>
       </c>
       <c r="C647" t="s">
-        <v>1699</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="648" spans="1:3">
@@ -13766,7 +13718,7 @@
         <v>671</v>
       </c>
       <c r="C648" t="s">
-        <v>1700</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="649" spans="1:3">
@@ -13777,7 +13729,7 @@
         <v>672</v>
       </c>
       <c r="C649" t="s">
-        <v>1701</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="650" spans="1:3">
@@ -13788,7 +13740,7 @@
         <v>673</v>
       </c>
       <c r="C650" t="s">
-        <v>1702</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="651" spans="1:3">
@@ -13799,51 +13751,51 @@
         <v>674</v>
       </c>
       <c r="C651" t="s">
-        <v>1703</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="652" spans="1:3">
       <c r="A652" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B652" t="s">
         <v>675</v>
       </c>
       <c r="C652" t="s">
-        <v>1704</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="653" spans="1:3">
       <c r="A653" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B653" t="s">
         <v>676</v>
       </c>
       <c r="C653" t="s">
-        <v>1705</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="654" spans="1:3">
       <c r="A654" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B654" t="s">
         <v>677</v>
       </c>
       <c r="C654" t="s">
-        <v>1706</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="655" spans="1:3">
       <c r="A655" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B655" t="s">
         <v>678</v>
       </c>
       <c r="C655" t="s">
-        <v>1707</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="656" spans="1:3">
@@ -13854,7 +13806,7 @@
         <v>679</v>
       </c>
       <c r="C656" t="s">
-        <v>1708</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="657" spans="1:3">
@@ -13865,7 +13817,7 @@
         <v>680</v>
       </c>
       <c r="C657" t="s">
-        <v>1709</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="658" spans="1:3">
@@ -13876,7 +13828,7 @@
         <v>681</v>
       </c>
       <c r="C658" t="s">
-        <v>1710</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="659" spans="1:3">
@@ -13887,7 +13839,7 @@
         <v>682</v>
       </c>
       <c r="C659" t="s">
-        <v>1711</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="660" spans="1:3">
@@ -13898,7 +13850,7 @@
         <v>683</v>
       </c>
       <c r="C660" t="s">
-        <v>1712</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="661" spans="1:3">
@@ -13909,7 +13861,7 @@
         <v>684</v>
       </c>
       <c r="C661" t="s">
-        <v>1713</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="662" spans="1:3">
@@ -13920,7 +13872,7 @@
         <v>685</v>
       </c>
       <c r="C662" t="s">
-        <v>1714</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="663" spans="1:3">
@@ -13931,7 +13883,7 @@
         <v>686</v>
       </c>
       <c r="C663" t="s">
-        <v>1715</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="664" spans="1:3">
@@ -13942,7 +13894,7 @@
         <v>687</v>
       </c>
       <c r="C664" t="s">
-        <v>1716</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="665" spans="1:3">
@@ -13953,7 +13905,7 @@
         <v>688</v>
       </c>
       <c r="C665" t="s">
-        <v>1717</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="666" spans="1:3">
@@ -13964,7 +13916,7 @@
         <v>689</v>
       </c>
       <c r="C666" t="s">
-        <v>1718</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="667" spans="1:3">
@@ -13975,51 +13927,51 @@
         <v>690</v>
       </c>
       <c r="C667" t="s">
-        <v>1719</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="668" spans="1:3">
       <c r="A668" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B668" t="s">
         <v>691</v>
       </c>
       <c r="C668" t="s">
-        <v>1720</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="669" spans="1:3">
       <c r="A669" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B669" t="s">
         <v>692</v>
       </c>
       <c r="C669" t="s">
-        <v>1721</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="670" spans="1:3">
       <c r="A670" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B670" t="s">
         <v>693</v>
       </c>
       <c r="C670" t="s">
-        <v>1722</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="671" spans="1:3">
       <c r="A671" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B671" t="s">
         <v>694</v>
       </c>
       <c r="C671" t="s">
-        <v>1153</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="672" spans="1:3">
@@ -14030,7 +13982,7 @@
         <v>695</v>
       </c>
       <c r="C672" t="s">
-        <v>1723</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="673" spans="1:3">
@@ -14041,7 +13993,7 @@
         <v>696</v>
       </c>
       <c r="C673" t="s">
-        <v>1724</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="674" spans="1:3">
@@ -14052,7 +14004,7 @@
         <v>697</v>
       </c>
       <c r="C674" t="s">
-        <v>1725</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="675" spans="1:3">
@@ -14063,7 +14015,7 @@
         <v>698</v>
       </c>
       <c r="C675" t="s">
-        <v>1726</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="676" spans="1:3">
@@ -14074,7 +14026,7 @@
         <v>699</v>
       </c>
       <c r="C676" t="s">
-        <v>1727</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="677" spans="1:3">
@@ -14085,7 +14037,7 @@
         <v>700</v>
       </c>
       <c r="C677" t="s">
-        <v>1728</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="678" spans="1:3">
@@ -14096,7 +14048,7 @@
         <v>701</v>
       </c>
       <c r="C678" t="s">
-        <v>1729</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="679" spans="1:3">
@@ -14107,7 +14059,7 @@
         <v>702</v>
       </c>
       <c r="C679" t="s">
-        <v>1730</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="680" spans="1:3">
@@ -14118,7 +14070,7 @@
         <v>703</v>
       </c>
       <c r="C680" t="s">
-        <v>1731</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="681" spans="1:3">
@@ -14129,7 +14081,7 @@
         <v>704</v>
       </c>
       <c r="C681" t="s">
-        <v>1732</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="682" spans="1:3">
@@ -14140,7 +14092,7 @@
         <v>705</v>
       </c>
       <c r="C682" t="s">
-        <v>1733</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="683" spans="1:3">
@@ -14151,7 +14103,7 @@
         <v>706</v>
       </c>
       <c r="C683" t="s">
-        <v>1734</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="684" spans="1:3">
@@ -14162,7 +14114,7 @@
         <v>707</v>
       </c>
       <c r="C684" t="s">
-        <v>1735</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="685" spans="1:3">
@@ -14173,7 +14125,7 @@
         <v>708</v>
       </c>
       <c r="C685" t="s">
-        <v>1736</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="686" spans="1:3">
@@ -14184,7 +14136,7 @@
         <v>709</v>
       </c>
       <c r="C686" t="s">
-        <v>1737</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="687" spans="1:3">
@@ -14195,7 +14147,7 @@
         <v>710</v>
       </c>
       <c r="C687" t="s">
-        <v>1738</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="688" spans="1:3">
@@ -14206,7 +14158,7 @@
         <v>711</v>
       </c>
       <c r="C688" t="s">
-        <v>1739</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="689" spans="1:3">
@@ -14217,7 +14169,7 @@
         <v>712</v>
       </c>
       <c r="C689" t="s">
-        <v>1740</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="690" spans="1:3">
@@ -14228,7 +14180,7 @@
         <v>713</v>
       </c>
       <c r="C690" t="s">
-        <v>1741</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="691" spans="1:3">
@@ -14239,7 +14191,7 @@
         <v>714</v>
       </c>
       <c r="C691" t="s">
-        <v>1742</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="692" spans="1:3">
@@ -14250,7 +14202,7 @@
         <v>715</v>
       </c>
       <c r="C692" t="s">
-        <v>1743</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="693" spans="1:3">
@@ -14261,7 +14213,7 @@
         <v>716</v>
       </c>
       <c r="C693" t="s">
-        <v>1744</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="694" spans="1:3">
@@ -14272,7 +14224,7 @@
         <v>717</v>
       </c>
       <c r="C694" t="s">
-        <v>1745</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="695" spans="1:3">
@@ -14283,7 +14235,7 @@
         <v>718</v>
       </c>
       <c r="C695" t="s">
-        <v>1746</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="696" spans="1:3">
@@ -14294,7 +14246,7 @@
         <v>719</v>
       </c>
       <c r="C696" t="s">
-        <v>1747</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="697" spans="1:3">
@@ -14305,7 +14257,7 @@
         <v>720</v>
       </c>
       <c r="C697" t="s">
-        <v>1748</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="698" spans="1:3">
@@ -14316,7 +14268,7 @@
         <v>721</v>
       </c>
       <c r="C698" t="s">
-        <v>1749</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="699" spans="1:3">
@@ -14327,7 +14279,7 @@
         <v>722</v>
       </c>
       <c r="C699" t="s">
-        <v>1750</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="700" spans="1:3">
@@ -14338,7 +14290,7 @@
         <v>723</v>
       </c>
       <c r="C700" t="s">
-        <v>1751</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="701" spans="1:3">
@@ -14349,7 +14301,7 @@
         <v>724</v>
       </c>
       <c r="C701" t="s">
-        <v>1752</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="702" spans="1:3">
@@ -14360,7 +14312,7 @@
         <v>725</v>
       </c>
       <c r="C702" t="s">
-        <v>1753</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="703" spans="1:3">
@@ -14371,7 +14323,7 @@
         <v>726</v>
       </c>
       <c r="C703" t="s">
-        <v>1754</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="704" spans="1:3">
@@ -14382,7 +14334,7 @@
         <v>727</v>
       </c>
       <c r="C704" t="s">
-        <v>1755</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="705" spans="1:3">
@@ -14393,7 +14345,7 @@
         <v>728</v>
       </c>
       <c r="C705" t="s">
-        <v>1756</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="706" spans="1:3">
@@ -14404,7 +14356,7 @@
         <v>729</v>
       </c>
       <c r="C706" t="s">
-        <v>1757</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="707" spans="1:3">
@@ -14415,7 +14367,7 @@
         <v>730</v>
       </c>
       <c r="C707" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="708" spans="1:3">
@@ -14426,62 +14378,62 @@
         <v>731</v>
       </c>
       <c r="C708" t="s">
-        <v>1759</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="709" spans="1:3">
       <c r="A709" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B709" t="s">
         <v>732</v>
       </c>
       <c r="C709" t="s">
-        <v>1760</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="710" spans="1:3">
       <c r="A710" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B710" t="s">
         <v>733</v>
       </c>
       <c r="C710" t="s">
-        <v>1761</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="711" spans="1:3">
       <c r="A711" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B711" t="s">
         <v>734</v>
       </c>
       <c r="C711" t="s">
-        <v>1762</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="712" spans="1:3">
       <c r="A712" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B712" t="s">
         <v>735</v>
       </c>
       <c r="C712" t="s">
-        <v>1763</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="713" spans="1:3">
       <c r="A713" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B713" t="s">
         <v>736</v>
       </c>
       <c r="C713" t="s">
-        <v>1764</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="714" spans="1:3">
@@ -14492,7 +14444,7 @@
         <v>737</v>
       </c>
       <c r="C714" t="s">
-        <v>1765</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="715" spans="1:3">
@@ -14503,7 +14455,7 @@
         <v>738</v>
       </c>
       <c r="C715" t="s">
-        <v>1766</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="716" spans="1:3">
@@ -14514,51 +14466,51 @@
         <v>739</v>
       </c>
       <c r="C716" t="s">
-        <v>1767</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="717" spans="1:3">
       <c r="A717" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B717" t="s">
         <v>740</v>
       </c>
       <c r="C717" t="s">
-        <v>1768</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="718" spans="1:3">
       <c r="A718" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B718" t="s">
         <v>741</v>
       </c>
       <c r="C718" t="s">
-        <v>1769</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="719" spans="1:3">
       <c r="A719" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B719" t="s">
         <v>742</v>
       </c>
       <c r="C719" t="s">
-        <v>1770</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="720" spans="1:3">
       <c r="A720" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B720" t="s">
         <v>743</v>
       </c>
       <c r="C720" t="s">
-        <v>1771</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="721" spans="1:3">
@@ -14569,7 +14521,7 @@
         <v>744</v>
       </c>
       <c r="C721" t="s">
-        <v>1772</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="722" spans="1:3">
@@ -14580,7 +14532,7 @@
         <v>745</v>
       </c>
       <c r="C722" t="s">
-        <v>1773</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="723" spans="1:3">
@@ -14591,7 +14543,7 @@
         <v>746</v>
       </c>
       <c r="C723" t="s">
-        <v>1774</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="724" spans="1:3">
@@ -14602,7 +14554,7 @@
         <v>747</v>
       </c>
       <c r="C724" t="s">
-        <v>1775</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="725" spans="1:3">
@@ -14613,7 +14565,7 @@
         <v>748</v>
       </c>
       <c r="C725" t="s">
-        <v>1776</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="726" spans="1:3">
@@ -14624,7 +14576,7 @@
         <v>749</v>
       </c>
       <c r="C726" t="s">
-        <v>1777</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="727" spans="1:3">
@@ -14635,7 +14587,7 @@
         <v>750</v>
       </c>
       <c r="C727" t="s">
-        <v>1778</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="728" spans="1:3">
@@ -14646,7 +14598,7 @@
         <v>751</v>
       </c>
       <c r="C728" t="s">
-        <v>1779</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="729" spans="1:3">
@@ -14657,7 +14609,7 @@
         <v>752</v>
       </c>
       <c r="C729" t="s">
-        <v>1780</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="730" spans="1:3">
@@ -14668,7 +14620,7 @@
         <v>753</v>
       </c>
       <c r="C730" t="s">
-        <v>1781</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="731" spans="1:3">
@@ -14679,7 +14631,7 @@
         <v>754</v>
       </c>
       <c r="C731" t="s">
-        <v>1782</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="732" spans="1:3">
@@ -14690,7 +14642,7 @@
         <v>755</v>
       </c>
       <c r="C732" t="s">
-        <v>1783</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="733" spans="1:3">
@@ -14701,7 +14653,7 @@
         <v>756</v>
       </c>
       <c r="C733" t="s">
-        <v>1784</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="734" spans="1:3">
@@ -14712,7 +14664,7 @@
         <v>757</v>
       </c>
       <c r="C734" t="s">
-        <v>1785</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="735" spans="1:3">
@@ -14723,7 +14675,7 @@
         <v>758</v>
       </c>
       <c r="C735" t="s">
-        <v>1786</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="736" spans="1:3">
@@ -14734,7 +14686,7 @@
         <v>759</v>
       </c>
       <c r="C736" t="s">
-        <v>1787</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="737" spans="1:3">
@@ -14745,7 +14697,7 @@
         <v>760</v>
       </c>
       <c r="C737" t="s">
-        <v>1788</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="738" spans="1:3">
@@ -14756,7 +14708,7 @@
         <v>761</v>
       </c>
       <c r="C738" t="s">
-        <v>1789</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="739" spans="1:3">
@@ -14767,7 +14719,7 @@
         <v>762</v>
       </c>
       <c r="C739" t="s">
-        <v>1790</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="740" spans="1:3">
@@ -14778,7 +14730,7 @@
         <v>763</v>
       </c>
       <c r="C740" t="s">
-        <v>1791</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="741" spans="1:3">
@@ -14789,7 +14741,7 @@
         <v>764</v>
       </c>
       <c r="C741" t="s">
-        <v>1792</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="742" spans="1:3">
@@ -14800,7 +14752,7 @@
         <v>765</v>
       </c>
       <c r="C742" t="s">
-        <v>1793</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="743" spans="1:3">
@@ -14811,7 +14763,7 @@
         <v>766</v>
       </c>
       <c r="C743" t="s">
-        <v>1794</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="744" spans="1:3">
@@ -14822,7 +14774,7 @@
         <v>767</v>
       </c>
       <c r="C744" t="s">
-        <v>1795</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="745" spans="1:3">
@@ -14833,7 +14785,7 @@
         <v>768</v>
       </c>
       <c r="C745" t="s">
-        <v>1796</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="746" spans="1:3">
@@ -14844,7 +14796,7 @@
         <v>769</v>
       </c>
       <c r="C746" t="s">
-        <v>1797</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="747" spans="1:3">
@@ -14855,7 +14807,7 @@
         <v>770</v>
       </c>
       <c r="C747" t="s">
-        <v>1798</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="748" spans="1:3">
@@ -14866,7 +14818,7 @@
         <v>771</v>
       </c>
       <c r="C748" t="s">
-        <v>1799</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="749" spans="1:3">
@@ -14877,7 +14829,7 @@
         <v>772</v>
       </c>
       <c r="C749" t="s">
-        <v>1800</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="750" spans="1:3">
@@ -14888,7 +14840,7 @@
         <v>773</v>
       </c>
       <c r="C750" t="s">
-        <v>1801</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="751" spans="1:3">
@@ -14899,7 +14851,7 @@
         <v>774</v>
       </c>
       <c r="C751" t="s">
-        <v>1802</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="752" spans="1:3">
@@ -14910,7 +14862,7 @@
         <v>775</v>
       </c>
       <c r="C752" t="s">
-        <v>1803</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="753" spans="1:3">
@@ -14921,7 +14873,7 @@
         <v>776</v>
       </c>
       <c r="C753" t="s">
-        <v>1804</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="754" spans="1:3">
@@ -14932,7 +14884,7 @@
         <v>777</v>
       </c>
       <c r="C754" t="s">
-        <v>1805</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="755" spans="1:3">
@@ -14943,7 +14895,7 @@
         <v>778</v>
       </c>
       <c r="C755" t="s">
-        <v>1806</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="756" spans="1:3">
@@ -14954,7 +14906,7 @@
         <v>779</v>
       </c>
       <c r="C756" t="s">
-        <v>1807</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="757" spans="1:3">
@@ -14965,7 +14917,7 @@
         <v>780</v>
       </c>
       <c r="C757" t="s">
-        <v>1808</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="758" spans="1:3">
@@ -14976,7 +14928,7 @@
         <v>781</v>
       </c>
       <c r="C758" t="s">
-        <v>1809</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="759" spans="1:3">
@@ -14987,7 +14939,7 @@
         <v>782</v>
       </c>
       <c r="C759" t="s">
-        <v>1810</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="760" spans="1:3">
@@ -14998,7 +14950,7 @@
         <v>783</v>
       </c>
       <c r="C760" t="s">
-        <v>1811</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="761" spans="1:3">
@@ -15009,7 +14961,7 @@
         <v>784</v>
       </c>
       <c r="C761" t="s">
-        <v>1812</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="762" spans="1:3">
@@ -15020,7 +14972,7 @@
         <v>785</v>
       </c>
       <c r="C762" t="s">
-        <v>1813</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="763" spans="1:3">
@@ -15031,7 +14983,7 @@
         <v>786</v>
       </c>
       <c r="C763" t="s">
-        <v>1814</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="764" spans="1:3">
@@ -15042,7 +14994,7 @@
         <v>787</v>
       </c>
       <c r="C764" t="s">
-        <v>1815</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="765" spans="1:3">
@@ -15053,7 +15005,7 @@
         <v>788</v>
       </c>
       <c r="C765" t="s">
-        <v>1816</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="766" spans="1:3">
@@ -15064,7 +15016,7 @@
         <v>789</v>
       </c>
       <c r="C766" t="s">
-        <v>1817</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="767" spans="1:3">
@@ -15075,7 +15027,7 @@
         <v>790</v>
       </c>
       <c r="C767" t="s">
-        <v>1818</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="768" spans="1:3">
@@ -15086,7 +15038,7 @@
         <v>791</v>
       </c>
       <c r="C768" t="s">
-        <v>1819</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="769" spans="1:3">
@@ -15097,7 +15049,7 @@
         <v>792</v>
       </c>
       <c r="C769" t="s">
-        <v>1820</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="770" spans="1:3">
@@ -15108,7 +15060,7 @@
         <v>793</v>
       </c>
       <c r="C770" t="s">
-        <v>1821</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="771" spans="1:3">
@@ -15119,7 +15071,7 @@
         <v>794</v>
       </c>
       <c r="C771" t="s">
-        <v>1822</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="772" spans="1:3">
@@ -15130,7 +15082,7 @@
         <v>795</v>
       </c>
       <c r="C772" t="s">
-        <v>1746</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="773" spans="1:3">
@@ -15141,7 +15093,7 @@
         <v>796</v>
       </c>
       <c r="C773" t="s">
-        <v>1823</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="774" spans="1:3">
@@ -15152,7 +15104,7 @@
         <v>797</v>
       </c>
       <c r="C774" t="s">
-        <v>1824</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="775" spans="1:3">
@@ -15163,7 +15115,7 @@
         <v>798</v>
       </c>
       <c r="C775" t="s">
-        <v>1825</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="776" spans="1:3">
@@ -15174,7 +15126,7 @@
         <v>799</v>
       </c>
       <c r="C776" t="s">
-        <v>1826</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="777" spans="1:3">
@@ -15185,7 +15137,7 @@
         <v>800</v>
       </c>
       <c r="C777" t="s">
-        <v>1827</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="778" spans="1:3">
@@ -15196,7 +15148,7 @@
         <v>801</v>
       </c>
       <c r="C778" t="s">
-        <v>1828</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="779" spans="1:3">
@@ -15207,7 +15159,7 @@
         <v>802</v>
       </c>
       <c r="C779" t="s">
-        <v>1829</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="780" spans="1:3">
@@ -15218,7 +15170,7 @@
         <v>803</v>
       </c>
       <c r="C780" t="s">
-        <v>1830</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="781" spans="1:3">
@@ -15229,7 +15181,7 @@
         <v>804</v>
       </c>
       <c r="C781" t="s">
-        <v>1831</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="782" spans="1:3">
@@ -15240,7 +15192,7 @@
         <v>805</v>
       </c>
       <c r="C782" t="s">
-        <v>1832</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="783" spans="1:3">
@@ -15251,7 +15203,7 @@
         <v>806</v>
       </c>
       <c r="C783" t="s">
-        <v>1833</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="784" spans="1:3">
@@ -15262,7 +15214,7 @@
         <v>807</v>
       </c>
       <c r="C784" t="s">
-        <v>1834</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="785" spans="1:3">
@@ -15273,7 +15225,7 @@
         <v>808</v>
       </c>
       <c r="C785" t="s">
-        <v>1835</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="786" spans="1:3">
@@ -15284,7 +15236,7 @@
         <v>809</v>
       </c>
       <c r="C786" t="s">
-        <v>1836</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="787" spans="1:3">
@@ -15295,7 +15247,7 @@
         <v>810</v>
       </c>
       <c r="C787" t="s">
-        <v>1837</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="788" spans="1:3">
@@ -15306,7 +15258,7 @@
         <v>811</v>
       </c>
       <c r="C788" t="s">
-        <v>1838</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="789" spans="1:3">
@@ -15317,7 +15269,7 @@
         <v>812</v>
       </c>
       <c r="C789" t="s">
-        <v>1839</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="790" spans="1:3">
@@ -15328,7 +15280,7 @@
         <v>813</v>
       </c>
       <c r="C790" t="s">
-        <v>1840</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="791" spans="1:3">
@@ -15339,7 +15291,7 @@
         <v>814</v>
       </c>
       <c r="C791" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="792" spans="1:3">
@@ -15350,7 +15302,7 @@
         <v>815</v>
       </c>
       <c r="C792" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="793" spans="1:3">
@@ -15361,7 +15313,7 @@
         <v>816</v>
       </c>
       <c r="C793" t="s">
-        <v>1843</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="794" spans="1:3">
@@ -15372,7 +15324,7 @@
         <v>817</v>
       </c>
       <c r="C794" t="s">
-        <v>1844</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="795" spans="1:3">
@@ -15383,7 +15335,7 @@
         <v>818</v>
       </c>
       <c r="C795" t="s">
-        <v>1845</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="796" spans="1:3">
@@ -15394,7 +15346,7 @@
         <v>819</v>
       </c>
       <c r="C796" t="s">
-        <v>1846</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="797" spans="1:3">
@@ -15405,7 +15357,7 @@
         <v>820</v>
       </c>
       <c r="C797" t="s">
-        <v>1847</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="798" spans="1:3">
@@ -15416,7 +15368,7 @@
         <v>821</v>
       </c>
       <c r="C798" t="s">
-        <v>1848</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="799" spans="1:3">
@@ -15427,7 +15379,7 @@
         <v>822</v>
       </c>
       <c r="C799" t="s">
-        <v>1849</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="800" spans="1:3">
@@ -15438,7 +15390,7 @@
         <v>823</v>
       </c>
       <c r="C800" t="s">
-        <v>1850</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="801" spans="1:3">
@@ -15449,7 +15401,7 @@
         <v>824</v>
       </c>
       <c r="C801" t="s">
-        <v>1851</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="802" spans="1:3">
@@ -15460,7 +15412,7 @@
         <v>825</v>
       </c>
       <c r="C802" t="s">
-        <v>1852</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="803" spans="1:3">
@@ -15471,7 +15423,7 @@
         <v>826</v>
       </c>
       <c r="C803" t="s">
-        <v>1853</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="804" spans="1:3">
@@ -15482,7 +15434,7 @@
         <v>827</v>
       </c>
       <c r="C804" t="s">
-        <v>1854</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="805" spans="1:3">
@@ -15493,7 +15445,7 @@
         <v>828</v>
       </c>
       <c r="C805" t="s">
-        <v>1855</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="806" spans="1:3">
@@ -15504,7 +15456,7 @@
         <v>829</v>
       </c>
       <c r="C806" t="s">
-        <v>1856</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="807" spans="1:3">
@@ -15515,7 +15467,7 @@
         <v>830</v>
       </c>
       <c r="C807" t="s">
-        <v>1857</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="808" spans="1:3">
@@ -15526,7 +15478,7 @@
         <v>831</v>
       </c>
       <c r="C808" t="s">
-        <v>1858</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="809" spans="1:3">
@@ -15537,7 +15489,7 @@
         <v>832</v>
       </c>
       <c r="C809" t="s">
-        <v>1859</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="810" spans="1:3">
@@ -15548,7 +15500,7 @@
         <v>833</v>
       </c>
       <c r="C810" t="s">
-        <v>1860</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="811" spans="1:3">
@@ -15559,7 +15511,7 @@
         <v>834</v>
       </c>
       <c r="C811" t="s">
-        <v>1861</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="812" spans="1:3">
@@ -15570,7 +15522,7 @@
         <v>835</v>
       </c>
       <c r="C812" t="s">
-        <v>1862</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="813" spans="1:3">
@@ -15581,7 +15533,7 @@
         <v>836</v>
       </c>
       <c r="C813" t="s">
-        <v>1863</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="814" spans="1:3">
@@ -15592,7 +15544,7 @@
         <v>837</v>
       </c>
       <c r="C814" t="s">
-        <v>1864</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="815" spans="1:3">
@@ -15603,7 +15555,7 @@
         <v>838</v>
       </c>
       <c r="C815" t="s">
-        <v>1865</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="816" spans="1:3">
@@ -15614,7 +15566,7 @@
         <v>839</v>
       </c>
       <c r="C816" t="s">
-        <v>1866</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="817" spans="1:3">
@@ -15625,7 +15577,7 @@
         <v>840</v>
       </c>
       <c r="C817" t="s">
-        <v>1867</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="818" spans="1:3">
@@ -15636,7 +15588,7 @@
         <v>841</v>
       </c>
       <c r="C818" t="s">
-        <v>1868</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="819" spans="1:3">
@@ -15647,7 +15599,7 @@
         <v>842</v>
       </c>
       <c r="C819" t="s">
-        <v>1869</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="820" spans="1:3">
@@ -15658,7 +15610,7 @@
         <v>843</v>
       </c>
       <c r="C820" t="s">
-        <v>1870</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="821" spans="1:3">
@@ -15669,7 +15621,7 @@
         <v>844</v>
       </c>
       <c r="C821" t="s">
-        <v>1871</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="822" spans="1:3">
@@ -15680,7 +15632,7 @@
         <v>845</v>
       </c>
       <c r="C822" t="s">
-        <v>1872</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="823" spans="1:3">
@@ -15691,7 +15643,7 @@
         <v>846</v>
       </c>
       <c r="C823" t="s">
-        <v>1873</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="824" spans="1:3">
@@ -15702,7 +15654,7 @@
         <v>847</v>
       </c>
       <c r="C824" t="s">
-        <v>1874</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="825" spans="1:3">
@@ -15713,7 +15665,7 @@
         <v>848</v>
       </c>
       <c r="C825" t="s">
-        <v>1875</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="826" spans="1:3">
@@ -15724,7 +15676,7 @@
         <v>849</v>
       </c>
       <c r="C826" t="s">
-        <v>1876</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="827" spans="1:3">
@@ -15735,7 +15687,7 @@
         <v>850</v>
       </c>
       <c r="C827" t="s">
-        <v>1877</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="828" spans="1:3">
@@ -15746,7 +15698,7 @@
         <v>851</v>
       </c>
       <c r="C828" t="s">
-        <v>1878</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="829" spans="1:3">
@@ -15757,7 +15709,7 @@
         <v>852</v>
       </c>
       <c r="C829" t="s">
-        <v>1879</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="830" spans="1:3">
@@ -15768,7 +15720,7 @@
         <v>853</v>
       </c>
       <c r="C830" t="s">
-        <v>1880</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="831" spans="1:3">
@@ -15779,7 +15731,7 @@
         <v>854</v>
       </c>
       <c r="C831" t="s">
-        <v>1881</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="832" spans="1:3">
@@ -15790,7 +15742,7 @@
         <v>855</v>
       </c>
       <c r="C832" t="s">
-        <v>1882</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="833" spans="1:3">
@@ -15801,7 +15753,7 @@
         <v>856</v>
       </c>
       <c r="C833" t="s">
-        <v>1883</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="834" spans="1:3">
@@ -15812,7 +15764,7 @@
         <v>857</v>
       </c>
       <c r="C834" t="s">
-        <v>1884</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="835" spans="1:3">
@@ -15823,7 +15775,7 @@
         <v>858</v>
       </c>
       <c r="C835" t="s">
-        <v>1885</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="836" spans="1:3">
@@ -15834,7 +15786,7 @@
         <v>859</v>
       </c>
       <c r="C836" t="s">
-        <v>1886</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="837" spans="1:3">
@@ -15845,7 +15797,7 @@
         <v>860</v>
       </c>
       <c r="C837" t="s">
-        <v>1887</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="838" spans="1:3">
@@ -15856,7 +15808,7 @@
         <v>861</v>
       </c>
       <c r="C838" t="s">
-        <v>1888</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="839" spans="1:3">
@@ -15867,51 +15819,51 @@
         <v>862</v>
       </c>
       <c r="C839" t="s">
-        <v>1889</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="840" spans="1:3">
       <c r="A840" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B840" t="s">
         <v>863</v>
       </c>
       <c r="C840" t="s">
-        <v>1890</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="841" spans="1:3">
       <c r="A841" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B841" t="s">
         <v>864</v>
       </c>
       <c r="C841" t="s">
-        <v>1891</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="842" spans="1:3">
       <c r="A842" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B842" t="s">
         <v>865</v>
       </c>
       <c r="C842" t="s">
-        <v>1892</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="843" spans="1:3">
       <c r="A843" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B843" t="s">
         <v>866</v>
       </c>
       <c r="C843" t="s">
-        <v>1893</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="844" spans="1:3">
@@ -15922,7 +15874,7 @@
         <v>867</v>
       </c>
       <c r="C844" t="s">
-        <v>1894</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="845" spans="1:3">
@@ -15933,7 +15885,7 @@
         <v>868</v>
       </c>
       <c r="C845" t="s">
-        <v>1895</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="846" spans="1:3">
@@ -15944,7 +15896,7 @@
         <v>869</v>
       </c>
       <c r="C846" t="s">
-        <v>1896</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="847" spans="1:3">
@@ -15955,7 +15907,7 @@
         <v>870</v>
       </c>
       <c r="C847" t="s">
-        <v>1897</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="848" spans="1:3">
@@ -15966,7 +15918,7 @@
         <v>871</v>
       </c>
       <c r="C848" t="s">
-        <v>1898</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="849" spans="1:3">
@@ -15977,7 +15929,7 @@
         <v>872</v>
       </c>
       <c r="C849" t="s">
-        <v>1899</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="850" spans="1:3">
@@ -15988,7 +15940,7 @@
         <v>873</v>
       </c>
       <c r="C850" t="s">
-        <v>1900</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="851" spans="1:3">
@@ -15999,7 +15951,7 @@
         <v>874</v>
       </c>
       <c r="C851" t="s">
-        <v>1901</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="852" spans="1:3">
@@ -16010,7 +15962,7 @@
         <v>875</v>
       </c>
       <c r="C852" t="s">
-        <v>1902</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="853" spans="1:3">
@@ -16021,7 +15973,7 @@
         <v>876</v>
       </c>
       <c r="C853" t="s">
-        <v>1903</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="854" spans="1:3">
@@ -16032,7 +15984,7 @@
         <v>877</v>
       </c>
       <c r="C854" t="s">
-        <v>1904</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="855" spans="1:3">
@@ -16043,7 +15995,7 @@
         <v>878</v>
       </c>
       <c r="C855" t="s">
-        <v>1905</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="856" spans="1:3">
@@ -16054,7 +16006,7 @@
         <v>879</v>
       </c>
       <c r="C856" t="s">
-        <v>1906</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="857" spans="1:3">
@@ -16065,7 +16017,7 @@
         <v>880</v>
       </c>
       <c r="C857" t="s">
-        <v>1907</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="858" spans="1:3">
@@ -16076,7 +16028,7 @@
         <v>881</v>
       </c>
       <c r="C858" t="s">
-        <v>1908</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="859" spans="1:3">
@@ -16087,7 +16039,7 @@
         <v>882</v>
       </c>
       <c r="C859" t="s">
-        <v>1909</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="860" spans="1:3">
@@ -16098,7 +16050,7 @@
         <v>883</v>
       </c>
       <c r="C860" t="s">
-        <v>1910</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="861" spans="1:3">
@@ -16109,7 +16061,7 @@
         <v>884</v>
       </c>
       <c r="C861" t="s">
-        <v>1911</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="862" spans="1:3">
@@ -16120,7 +16072,7 @@
         <v>885</v>
       </c>
       <c r="C862" t="s">
-        <v>1912</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="863" spans="1:3">
@@ -16131,7 +16083,7 @@
         <v>886</v>
       </c>
       <c r="C863" t="s">
-        <v>1913</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="864" spans="1:3">
@@ -16142,7 +16094,7 @@
         <v>887</v>
       </c>
       <c r="C864" t="s">
-        <v>1914</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="865" spans="1:3">
@@ -16153,7 +16105,7 @@
         <v>888</v>
       </c>
       <c r="C865" t="s">
-        <v>1915</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="866" spans="1:3">
@@ -16164,7 +16116,7 @@
         <v>889</v>
       </c>
       <c r="C866" t="s">
-        <v>1916</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="867" spans="1:3">
@@ -16175,7 +16127,7 @@
         <v>890</v>
       </c>
       <c r="C867" t="s">
-        <v>1917</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="868" spans="1:3">
@@ -16186,7 +16138,7 @@
         <v>891</v>
       </c>
       <c r="C868" t="s">
-        <v>1918</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="869" spans="1:3">
@@ -16197,7 +16149,7 @@
         <v>892</v>
       </c>
       <c r="C869" t="s">
-        <v>1919</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="870" spans="1:3">
@@ -16208,7 +16160,7 @@
         <v>893</v>
       </c>
       <c r="C870" t="s">
-        <v>1920</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="871" spans="1:3">
@@ -16219,7 +16171,7 @@
         <v>894</v>
       </c>
       <c r="C871" t="s">
-        <v>1921</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="872" spans="1:3">
@@ -16230,7 +16182,7 @@
         <v>895</v>
       </c>
       <c r="C872" t="s">
-        <v>1922</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="873" spans="1:3">
@@ -16241,7 +16193,7 @@
         <v>896</v>
       </c>
       <c r="C873" t="s">
-        <v>1923</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="874" spans="1:3">
@@ -16252,7 +16204,7 @@
         <v>897</v>
       </c>
       <c r="C874" t="s">
-        <v>1924</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="875" spans="1:3">
@@ -16263,7 +16215,7 @@
         <v>898</v>
       </c>
       <c r="C875" t="s">
-        <v>1925</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="876" spans="1:3">
@@ -16274,7 +16226,7 @@
         <v>899</v>
       </c>
       <c r="C876" t="s">
-        <v>1926</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="877" spans="1:3">
@@ -16285,7 +16237,7 @@
         <v>900</v>
       </c>
       <c r="C877" t="s">
-        <v>1927</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="878" spans="1:3">
@@ -16296,7 +16248,7 @@
         <v>901</v>
       </c>
       <c r="C878" t="s">
-        <v>1928</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="879" spans="1:3">
@@ -16307,7 +16259,7 @@
         <v>902</v>
       </c>
       <c r="C879" t="s">
-        <v>1929</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="880" spans="1:3">
@@ -16318,7 +16270,7 @@
         <v>903</v>
       </c>
       <c r="C880" t="s">
-        <v>1930</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="881" spans="1:3">
@@ -16329,7 +16281,7 @@
         <v>904</v>
       </c>
       <c r="C881" t="s">
-        <v>1931</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="882" spans="1:3">
@@ -16340,7 +16292,7 @@
         <v>905</v>
       </c>
       <c r="C882" t="s">
-        <v>1932</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="883" spans="1:3">
@@ -16351,7 +16303,7 @@
         <v>906</v>
       </c>
       <c r="C883" t="s">
-        <v>1933</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="884" spans="1:3">
@@ -16362,7 +16314,7 @@
         <v>907</v>
       </c>
       <c r="C884" t="s">
-        <v>1934</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="885" spans="1:3">
@@ -16373,7 +16325,7 @@
         <v>908</v>
       </c>
       <c r="C885" t="s">
-        <v>1935</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="886" spans="1:3">
@@ -16384,7 +16336,7 @@
         <v>909</v>
       </c>
       <c r="C886" t="s">
-        <v>1936</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="887" spans="1:3">
@@ -16395,7 +16347,7 @@
         <v>910</v>
       </c>
       <c r="C887" t="s">
-        <v>1937</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="888" spans="1:3">
@@ -16406,7 +16358,7 @@
         <v>911</v>
       </c>
       <c r="C888" t="s">
-        <v>1938</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="889" spans="1:3">
@@ -16417,7 +16369,7 @@
         <v>912</v>
       </c>
       <c r="C889" t="s">
-        <v>1939</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="890" spans="1:3">
@@ -16428,7 +16380,7 @@
         <v>913</v>
       </c>
       <c r="C890" t="s">
-        <v>1940</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="891" spans="1:3">
@@ -16439,7 +16391,7 @@
         <v>914</v>
       </c>
       <c r="C891" t="s">
-        <v>1941</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="892" spans="1:3">
@@ -16450,7 +16402,7 @@
         <v>915</v>
       </c>
       <c r="C892" t="s">
-        <v>1942</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="893" spans="1:3">
@@ -16461,7 +16413,7 @@
         <v>916</v>
       </c>
       <c r="C893" t="s">
-        <v>1943</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="894" spans="1:3">
@@ -16472,7 +16424,7 @@
         <v>917</v>
       </c>
       <c r="C894" t="s">
-        <v>1944</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="895" spans="1:3">
@@ -16483,7 +16435,7 @@
         <v>918</v>
       </c>
       <c r="C895" t="s">
-        <v>1945</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="896" spans="1:3">
@@ -16494,7 +16446,7 @@
         <v>919</v>
       </c>
       <c r="C896" t="s">
-        <v>1946</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="897" spans="1:3">
@@ -16505,7 +16457,7 @@
         <v>920</v>
       </c>
       <c r="C897" t="s">
-        <v>1947</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="898" spans="1:3">
@@ -16516,7 +16468,7 @@
         <v>921</v>
       </c>
       <c r="C898" t="s">
-        <v>1948</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="899" spans="1:3">
@@ -16527,7 +16479,7 @@
         <v>922</v>
       </c>
       <c r="C899" t="s">
-        <v>1949</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="900" spans="1:3">
@@ -16538,7 +16490,7 @@
         <v>923</v>
       </c>
       <c r="C900" t="s">
-        <v>1950</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="901" spans="1:3">
@@ -16549,7 +16501,7 @@
         <v>924</v>
       </c>
       <c r="C901" t="s">
-        <v>1951</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="902" spans="1:3">
@@ -16560,7 +16512,7 @@
         <v>925</v>
       </c>
       <c r="C902" t="s">
-        <v>1952</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="903" spans="1:3">
@@ -16571,7 +16523,7 @@
         <v>926</v>
       </c>
       <c r="C903" t="s">
-        <v>1953</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="904" spans="1:3">
@@ -16582,7 +16534,7 @@
         <v>927</v>
       </c>
       <c r="C904" t="s">
-        <v>1954</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="905" spans="1:3">
@@ -16593,7 +16545,7 @@
         <v>928</v>
       </c>
       <c r="C905" t="s">
-        <v>1955</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="906" spans="1:3">
@@ -16604,7 +16556,7 @@
         <v>929</v>
       </c>
       <c r="C906" t="s">
-        <v>1956</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="907" spans="1:3">
@@ -16615,7 +16567,7 @@
         <v>930</v>
       </c>
       <c r="C907" t="s">
-        <v>1957</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="908" spans="1:3">
@@ -16626,7 +16578,7 @@
         <v>931</v>
       </c>
       <c r="C908" t="s">
-        <v>1958</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="909" spans="1:3">
@@ -16637,7 +16589,7 @@
         <v>932</v>
       </c>
       <c r="C909" t="s">
-        <v>1959</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="910" spans="1:3">
@@ -16648,7 +16600,7 @@
         <v>933</v>
       </c>
       <c r="C910" t="s">
-        <v>1960</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="911" spans="1:3">
@@ -16659,7 +16611,7 @@
         <v>934</v>
       </c>
       <c r="C911" t="s">
-        <v>1961</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="912" spans="1:3">
@@ -16670,7 +16622,7 @@
         <v>935</v>
       </c>
       <c r="C912" t="s">
-        <v>1962</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="913" spans="1:3">
@@ -16681,7 +16633,7 @@
         <v>936</v>
       </c>
       <c r="C913" t="s">
-        <v>1963</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="914" spans="1:3">
@@ -16692,7 +16644,7 @@
         <v>937</v>
       </c>
       <c r="C914" t="s">
-        <v>1964</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="915" spans="1:3">
@@ -16703,7 +16655,7 @@
         <v>938</v>
       </c>
       <c r="C915" t="s">
-        <v>1965</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="916" spans="1:3">
@@ -16714,7 +16666,7 @@
         <v>939</v>
       </c>
       <c r="C916" t="s">
-        <v>1966</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="917" spans="1:3">
@@ -16725,7 +16677,7 @@
         <v>940</v>
       </c>
       <c r="C917" t="s">
-        <v>1967</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="918" spans="1:3">
@@ -16736,7 +16688,7 @@
         <v>941</v>
       </c>
       <c r="C918" t="s">
-        <v>1968</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="919" spans="1:3">
@@ -16747,7 +16699,7 @@
         <v>942</v>
       </c>
       <c r="C919" t="s">
-        <v>1969</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="920" spans="1:3">
@@ -16758,7 +16710,7 @@
         <v>943</v>
       </c>
       <c r="C920" t="s">
-        <v>1970</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="921" spans="1:3">
@@ -16769,7 +16721,7 @@
         <v>944</v>
       </c>
       <c r="C921" t="s">
-        <v>1971</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="922" spans="1:3">
@@ -16780,7 +16732,7 @@
         <v>945</v>
       </c>
       <c r="C922" t="s">
-        <v>1972</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="923" spans="1:3">
@@ -16791,7 +16743,7 @@
         <v>946</v>
       </c>
       <c r="C923" t="s">
-        <v>1973</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="924" spans="1:3">
@@ -16802,7 +16754,7 @@
         <v>947</v>
       </c>
       <c r="C924" t="s">
-        <v>1974</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="925" spans="1:3">
@@ -16813,7 +16765,7 @@
         <v>948</v>
       </c>
       <c r="C925" t="s">
-        <v>1975</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="926" spans="1:3">
@@ -16824,7 +16776,7 @@
         <v>949</v>
       </c>
       <c r="C926" t="s">
-        <v>1976</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="927" spans="1:3">
@@ -16835,7 +16787,7 @@
         <v>950</v>
       </c>
       <c r="C927" t="s">
-        <v>1977</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="928" spans="1:3">
@@ -16846,7 +16798,7 @@
         <v>951</v>
       </c>
       <c r="C928" t="s">
-        <v>1978</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="929" spans="1:3">
@@ -16857,7 +16809,7 @@
         <v>952</v>
       </c>
       <c r="C929" t="s">
-        <v>1979</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="930" spans="1:3">
@@ -16868,7 +16820,7 @@
         <v>953</v>
       </c>
       <c r="C930" t="s">
-        <v>1980</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="931" spans="1:3">
@@ -16879,7 +16831,7 @@
         <v>954</v>
       </c>
       <c r="C931" t="s">
-        <v>1981</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="932" spans="1:3">
@@ -16890,7 +16842,7 @@
         <v>955</v>
       </c>
       <c r="C932" t="s">
-        <v>1982</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="933" spans="1:3">
@@ -16901,7 +16853,7 @@
         <v>956</v>
       </c>
       <c r="C933" t="s">
-        <v>1983</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="934" spans="1:3">
@@ -16912,95 +16864,95 @@
         <v>957</v>
       </c>
       <c r="C934" t="s">
-        <v>1984</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="935" spans="1:3">
       <c r="A935" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B935" t="s">
         <v>958</v>
       </c>
       <c r="C935" t="s">
-        <v>1985</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="936" spans="1:3">
       <c r="A936" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B936" t="s">
         <v>959</v>
       </c>
       <c r="C936" t="s">
-        <v>1986</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="937" spans="1:3">
       <c r="A937" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B937" t="s">
         <v>960</v>
       </c>
       <c r="C937" t="s">
-        <v>1987</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="938" spans="1:3">
       <c r="A938" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B938" t="s">
         <v>961</v>
       </c>
       <c r="C938" t="s">
-        <v>1988</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="939" spans="1:3">
       <c r="A939" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B939" t="s">
         <v>962</v>
       </c>
       <c r="C939" t="s">
-        <v>1989</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="940" spans="1:3">
       <c r="A940" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B940" t="s">
         <v>963</v>
       </c>
       <c r="C940" t="s">
-        <v>1990</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="941" spans="1:3">
       <c r="A941" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B941" t="s">
         <v>964</v>
       </c>
       <c r="C941" t="s">
-        <v>1991</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="942" spans="1:3">
       <c r="A942" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B942" t="s">
         <v>965</v>
       </c>
       <c r="C942" t="s">
-        <v>1992</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="943" spans="1:3">
@@ -17011,7 +16963,7 @@
         <v>966</v>
       </c>
       <c r="C943" t="s">
-        <v>1993</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="944" spans="1:3">
@@ -17022,7 +16974,7 @@
         <v>967</v>
       </c>
       <c r="C944" t="s">
-        <v>1994</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="945" spans="1:3">
@@ -17033,7 +16985,7 @@
         <v>968</v>
       </c>
       <c r="C945" t="s">
-        <v>1995</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="946" spans="1:3">
@@ -17044,7 +16996,7 @@
         <v>969</v>
       </c>
       <c r="C946" t="s">
-        <v>1996</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="947" spans="1:3">
@@ -17055,7 +17007,7 @@
         <v>970</v>
       </c>
       <c r="C947" t="s">
-        <v>1997</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="948" spans="1:3">
@@ -17066,7 +17018,7 @@
         <v>971</v>
       </c>
       <c r="C948" t="s">
-        <v>1998</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="949" spans="1:3">
@@ -17077,7 +17029,7 @@
         <v>972</v>
       </c>
       <c r="C949" t="s">
-        <v>1999</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="950" spans="1:3">
@@ -17088,7 +17040,7 @@
         <v>973</v>
       </c>
       <c r="C950" t="s">
-        <v>2000</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="951" spans="1:3">
@@ -17099,7 +17051,7 @@
         <v>974</v>
       </c>
       <c r="C951" t="s">
-        <v>2001</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="952" spans="1:3">
@@ -17110,7 +17062,7 @@
         <v>975</v>
       </c>
       <c r="C952" t="s">
-        <v>2002</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="953" spans="1:3">
@@ -17121,7 +17073,7 @@
         <v>976</v>
       </c>
       <c r="C953" t="s">
-        <v>2003</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="954" spans="1:3">
@@ -17132,7 +17084,7 @@
         <v>977</v>
       </c>
       <c r="C954" t="s">
-        <v>2004</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="955" spans="1:3">
@@ -17143,7 +17095,7 @@
         <v>978</v>
       </c>
       <c r="C955" t="s">
-        <v>2005</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="956" spans="1:3">
@@ -17154,7 +17106,7 @@
         <v>979</v>
       </c>
       <c r="C956" t="s">
-        <v>2006</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="957" spans="1:3">
@@ -17165,7 +17117,7 @@
         <v>980</v>
       </c>
       <c r="C957" t="s">
-        <v>2007</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="958" spans="1:3">
@@ -17176,7 +17128,7 @@
         <v>981</v>
       </c>
       <c r="C958" t="s">
-        <v>2008</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="959" spans="1:3">
@@ -17187,7 +17139,7 @@
         <v>982</v>
       </c>
       <c r="C959" t="s">
-        <v>2009</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="960" spans="1:3">
@@ -17198,7 +17150,7 @@
         <v>983</v>
       </c>
       <c r="C960" t="s">
-        <v>2010</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="961" spans="1:3">
@@ -17209,7 +17161,7 @@
         <v>984</v>
       </c>
       <c r="C961" t="s">
-        <v>2011</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="962" spans="1:3">
@@ -17220,7 +17172,7 @@
         <v>985</v>
       </c>
       <c r="C962" t="s">
-        <v>2012</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="963" spans="1:3">
@@ -17231,7 +17183,7 @@
         <v>986</v>
       </c>
       <c r="C963" t="s">
-        <v>2013</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="964" spans="1:3">
@@ -17242,7 +17194,7 @@
         <v>987</v>
       </c>
       <c r="C964" t="s">
-        <v>2014</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="965" spans="1:3">
@@ -17253,7 +17205,7 @@
         <v>988</v>
       </c>
       <c r="C965" t="s">
-        <v>2015</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="966" spans="1:3">
@@ -17264,7 +17216,7 @@
         <v>989</v>
       </c>
       <c r="C966" t="s">
-        <v>2016</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="967" spans="1:3">
@@ -17275,7 +17227,7 @@
         <v>990</v>
       </c>
       <c r="C967" t="s">
-        <v>2017</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="968" spans="1:3">
@@ -17286,7 +17238,7 @@
         <v>991</v>
       </c>
       <c r="C968" t="s">
-        <v>2018</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="969" spans="1:3">
@@ -17297,7 +17249,7 @@
         <v>992</v>
       </c>
       <c r="C969" t="s">
-        <v>2019</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="970" spans="1:3">
@@ -17308,7 +17260,7 @@
         <v>993</v>
       </c>
       <c r="C970" t="s">
-        <v>2020</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="971" spans="1:3">
@@ -17319,7 +17271,7 @@
         <v>994</v>
       </c>
       <c r="C971" t="s">
-        <v>2021</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="972" spans="1:3">
@@ -17330,7 +17282,7 @@
         <v>995</v>
       </c>
       <c r="C972" t="s">
-        <v>2022</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="973" spans="1:3">
@@ -17341,7 +17293,7 @@
         <v>996</v>
       </c>
       <c r="C973" t="s">
-        <v>2023</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="974" spans="1:3">
@@ -17352,7 +17304,7 @@
         <v>997</v>
       </c>
       <c r="C974" t="s">
-        <v>2024</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="975" spans="1:3">
@@ -17363,7 +17315,7 @@
         <v>998</v>
       </c>
       <c r="C975" t="s">
-        <v>2025</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="976" spans="1:3">
@@ -17374,7 +17326,7 @@
         <v>999</v>
       </c>
       <c r="C976" t="s">
-        <v>2026</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="977" spans="1:3">
@@ -17385,7 +17337,7 @@
         <v>1000</v>
       </c>
       <c r="C977" t="s">
-        <v>2027</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="978" spans="1:3">
@@ -17396,7 +17348,7 @@
         <v>1001</v>
       </c>
       <c r="C978" t="s">
-        <v>2028</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="979" spans="1:3">
@@ -17407,7 +17359,7 @@
         <v>1002</v>
       </c>
       <c r="C979" t="s">
-        <v>2029</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="980" spans="1:3">
@@ -17418,7 +17370,7 @@
         <v>1003</v>
       </c>
       <c r="C980" t="s">
-        <v>2030</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="981" spans="1:3">
@@ -17429,7 +17381,7 @@
         <v>1004</v>
       </c>
       <c r="C981" t="s">
-        <v>2031</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="982" spans="1:3">
@@ -17440,7 +17392,7 @@
         <v>1005</v>
       </c>
       <c r="C982" t="s">
-        <v>2025</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="983" spans="1:3">
@@ -17451,7 +17403,7 @@
         <v>1006</v>
       </c>
       <c r="C983" t="s">
-        <v>2032</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="984" spans="1:3">
@@ -17462,7 +17414,7 @@
         <v>1007</v>
       </c>
       <c r="C984" t="s">
-        <v>2033</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="985" spans="1:3">
@@ -17473,7 +17425,7 @@
         <v>1008</v>
       </c>
       <c r="C985" t="s">
-        <v>2034</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="986" spans="1:3">
@@ -17484,7 +17436,7 @@
         <v>1009</v>
       </c>
       <c r="C986" t="s">
-        <v>2035</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="987" spans="1:3">
@@ -17495,7 +17447,7 @@
         <v>1010</v>
       </c>
       <c r="C987" t="s">
-        <v>2036</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="988" spans="1:3">
@@ -17506,7 +17458,7 @@
         <v>1011</v>
       </c>
       <c r="C988" t="s">
-        <v>2037</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="989" spans="1:3">
@@ -17517,7 +17469,7 @@
         <v>1012</v>
       </c>
       <c r="C989" t="s">
-        <v>2038</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="990" spans="1:3">
@@ -17528,7 +17480,7 @@
         <v>1013</v>
       </c>
       <c r="C990" t="s">
-        <v>2039</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="991" spans="1:3">
@@ -17539,7 +17491,7 @@
         <v>1014</v>
       </c>
       <c r="C991" t="s">
-        <v>2040</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="992" spans="1:3">
@@ -17550,7 +17502,7 @@
         <v>1015</v>
       </c>
       <c r="C992" t="s">
-        <v>2041</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="993" spans="1:3">
@@ -17561,7 +17513,7 @@
         <v>1016</v>
       </c>
       <c r="C993" t="s">
-        <v>2042</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="994" spans="1:3">
@@ -17572,7 +17524,7 @@
         <v>1017</v>
       </c>
       <c r="C994" t="s">
-        <v>2043</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="995" spans="1:3">
@@ -17583,7 +17535,7 @@
         <v>1018</v>
       </c>
       <c r="C995" t="s">
-        <v>2044</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="996" spans="1:3">
@@ -17594,7 +17546,7 @@
         <v>1019</v>
       </c>
       <c r="C996" t="s">
-        <v>2045</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="997" spans="1:3">
@@ -17605,7 +17557,7 @@
         <v>1020</v>
       </c>
       <c r="C997" t="s">
-        <v>2046</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="998" spans="1:3">
@@ -17616,7 +17568,7 @@
         <v>1021</v>
       </c>
       <c r="C998" t="s">
-        <v>2047</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="999" spans="1:3">
@@ -17627,7 +17579,7 @@
         <v>1022</v>
       </c>
       <c r="C999" t="s">
-        <v>2048</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="1000" spans="1:3">
@@ -17638,7 +17590,7 @@
         <v>1023</v>
       </c>
       <c r="C1000" t="s">
-        <v>2049</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="1001" spans="1:3">
@@ -17649,7 +17601,7 @@
         <v>1024</v>
       </c>
       <c r="C1001" t="s">
-        <v>2050</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="1002" spans="1:3">
@@ -17660,7 +17612,7 @@
         <v>1025</v>
       </c>
       <c r="C1002" t="s">
-        <v>2051</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="1003" spans="1:3">
@@ -17671,7 +17623,7 @@
         <v>1026</v>
       </c>
       <c r="C1003" t="s">
-        <v>2026</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="1004" spans="1:3">
@@ -17682,7 +17634,7 @@
         <v>1027</v>
       </c>
       <c r="C1004" t="s">
-        <v>2052</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="1005" spans="1:3">
@@ -17693,95 +17645,95 @@
         <v>1028</v>
       </c>
       <c r="C1005" t="s">
-        <v>2053</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="1006" spans="1:3">
       <c r="A1006" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1006" t="s">
         <v>1029</v>
       </c>
       <c r="C1006" t="s">
-        <v>2054</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="1007" spans="1:3">
       <c r="A1007" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1007" t="s">
         <v>1030</v>
       </c>
       <c r="C1007" t="s">
-        <v>2007</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="1008" spans="1:3">
       <c r="A1008" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1008" t="s">
         <v>1031</v>
       </c>
       <c r="C1008" t="s">
-        <v>2055</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="1009" spans="1:3">
       <c r="A1009" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1009" t="s">
         <v>1032</v>
       </c>
       <c r="C1009" t="s">
-        <v>2056</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="1010" spans="1:3">
       <c r="A1010" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1010" t="s">
         <v>1033</v>
       </c>
       <c r="C1010" t="s">
-        <v>2057</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="1011" spans="1:3">
       <c r="A1011" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1011" t="s">
         <v>1034</v>
       </c>
       <c r="C1011" t="s">
-        <v>2058</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="1012" spans="1:3">
       <c r="A1012" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1012" t="s">
         <v>1035</v>
       </c>
       <c r="C1012" t="s">
-        <v>2059</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="1013" spans="1:3">
       <c r="A1013" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1013" t="s">
         <v>1036</v>
       </c>
       <c r="C1013" t="s">
-        <v>2060</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1014" spans="1:3">
@@ -17792,7 +17744,7 @@
         <v>1037</v>
       </c>
       <c r="C1014" t="s">
-        <v>2061</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="1015" spans="1:3">
@@ -17803,7 +17755,7 @@
         <v>1038</v>
       </c>
       <c r="C1015" t="s">
-        <v>2062</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="1016" spans="1:3">
@@ -17814,7 +17766,7 @@
         <v>1039</v>
       </c>
       <c r="C1016" t="s">
-        <v>2063</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="1017" spans="1:3">
@@ -17825,7 +17777,7 @@
         <v>1040</v>
       </c>
       <c r="C1017" t="s">
-        <v>2064</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="1018" spans="1:3">
@@ -17836,7 +17788,7 @@
         <v>1041</v>
       </c>
       <c r="C1018" t="s">
-        <v>2065</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="1019" spans="1:3">
@@ -17847,7 +17799,7 @@
         <v>1042</v>
       </c>
       <c r="C1019" t="s">
-        <v>2066</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="1020" spans="1:3">
@@ -17858,7 +17810,7 @@
         <v>1043</v>
       </c>
       <c r="C1020" t="s">
-        <v>2067</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="1021" spans="1:3">
@@ -17869,7 +17821,7 @@
         <v>1044</v>
       </c>
       <c r="C1021" t="s">
-        <v>2068</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="1022" spans="1:3">
@@ -17880,7 +17832,7 @@
         <v>1045</v>
       </c>
       <c r="C1022" t="s">
-        <v>2069</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="1023" spans="1:3">
@@ -17891,7 +17843,7 @@
         <v>1046</v>
       </c>
       <c r="C1023" t="s">
-        <v>2070</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="1024" spans="1:3">
@@ -17902,7 +17854,7 @@
         <v>1047</v>
       </c>
       <c r="C1024" t="s">
-        <v>2071</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="1025" spans="1:3">
@@ -17913,7 +17865,7 @@
         <v>1048</v>
       </c>
       <c r="C1025" t="s">
-        <v>2072</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="1026" spans="1:3">
@@ -17924,7 +17876,7 @@
         <v>1049</v>
       </c>
       <c r="C1026" t="s">
-        <v>2073</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="1027" spans="1:3">
@@ -17935,7 +17887,7 @@
         <v>1050</v>
       </c>
       <c r="C1027" t="s">
-        <v>2074</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="1028" spans="1:3">
@@ -17946,7 +17898,7 @@
         <v>1051</v>
       </c>
       <c r="C1028" t="s">
-        <v>2075</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1029" spans="1:3">
@@ -17957,7 +17909,7 @@
         <v>1052</v>
       </c>
       <c r="C1029" t="s">
-        <v>2076</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="1030" spans="1:3">
@@ -17968,7 +17920,7 @@
         <v>1053</v>
       </c>
       <c r="C1030" t="s">
-        <v>2077</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="1031" spans="1:3">
@@ -17979,7 +17931,7 @@
         <v>1054</v>
       </c>
       <c r="C1031" t="s">
-        <v>2078</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="1032" spans="1:3">
@@ -17990,106 +17942,18 @@
         <v>1055</v>
       </c>
       <c r="C1032" t="s">
-        <v>2079</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="1033" spans="1:3">
       <c r="A1033" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1033" t="s">
         <v>1056</v>
       </c>
       <c r="C1033" t="s">
-        <v>2080</v>
-      </c>
-    </row>
-    <row r="1034" spans="1:3">
-      <c r="A1034" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1034" t="s">
-        <v>1057</v>
-      </c>
-      <c r="C1034" t="s">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="1035" spans="1:3">
-      <c r="A1035" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1035" t="s">
-        <v>1058</v>
-      </c>
-      <c r="C1035" t="s">
-        <v>2082</v>
-      </c>
-    </row>
-    <row r="1036" spans="1:3">
-      <c r="A1036" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1036" t="s">
-        <v>1059</v>
-      </c>
-      <c r="C1036" t="s">
-        <v>2083</v>
-      </c>
-    </row>
-    <row r="1037" spans="1:3">
-      <c r="A1037" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1037" t="s">
-        <v>1060</v>
-      </c>
-      <c r="C1037" t="s">
-        <v>2084</v>
-      </c>
-    </row>
-    <row r="1038" spans="1:3">
-      <c r="A1038" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1038" t="s">
-        <v>1061</v>
-      </c>
-      <c r="C1038" t="s">
-        <v>2085</v>
-      </c>
-    </row>
-    <row r="1039" spans="1:3">
-      <c r="A1039" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1039" t="s">
-        <v>1062</v>
-      </c>
-      <c r="C1039" t="s">
-        <v>2086</v>
-      </c>
-    </row>
-    <row r="1040" spans="1:3">
-      <c r="A1040" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1040" t="s">
-        <v>1063</v>
-      </c>
-      <c r="C1040" t="s">
-        <v>2087</v>
-      </c>
-    </row>
-    <row r="1041" spans="1:3">
-      <c r="A1041" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1041" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C1041" t="s">
-        <v>2088</v>
+        <v>2072</v>
       </c>
     </row>
   </sheetData>

--- a/faltantes_por_estados.xlsx
+++ b/faltantes_por_estados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3099" uniqueCount="2073">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3093" uniqueCount="2069">
   <si>
     <t>entidad</t>
   </si>
@@ -2623,9 +2623,6 @@
     <t>TCIMB000156</t>
   </si>
   <si>
-    <t>TCIMB000185</t>
-  </si>
-  <si>
     <t>TCIMB000535</t>
   </si>
   <si>
@@ -2863,9 +2860,6 @@
     <t>TCIMB004665</t>
   </si>
   <si>
-    <t>TCIMB004694</t>
-  </si>
-  <si>
     <t>TCIMB004706</t>
   </si>
   <si>
@@ -5680,9 +5674,6 @@
     <t>C.S. ARENAL</t>
   </si>
   <si>
-    <t>C.S. EL CHAMIZAL</t>
-  </si>
-  <si>
     <t>C.S. COL. ÁLVARO OBREGÓN</t>
   </si>
   <si>
@@ -5918,9 +5909,6 @@
   </si>
   <si>
     <t>CESSA BUENA VISTA ZONA INDIGENA YOKOT´AN</t>
-  </si>
-  <si>
-    <t>CENTRO DE SALUD CON UN NÚCLEO BÁSICO EJ. PARAÍSO EL TINTO, BALANCÁN , TABASCO</t>
   </si>
   <si>
     <t>CENTRO DE SALUD CON 2 NÚCLEOS BÁSICOS POB. SIMÓN SARLAT, CENTLA</t>
@@ -6590,7 +6578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1033"/>
+  <dimension ref="A1:C1031"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6612,7 +6600,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6623,7 +6611,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6634,7 +6622,7 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6645,7 +6633,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6656,7 +6644,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6667,7 +6655,7 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6678,7 +6666,7 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6689,7 +6677,7 @@
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6700,7 +6688,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6711,7 +6699,7 @@
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6722,7 +6710,7 @@
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6733,7 +6721,7 @@
         <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6744,7 +6732,7 @@
         <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6755,7 +6743,7 @@
         <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -6766,7 +6754,7 @@
         <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6788,7 +6776,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6799,7 +6787,7 @@
         <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6810,7 +6798,7 @@
         <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6821,7 +6809,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6832,7 +6820,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6843,7 +6831,7 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6854,7 +6842,7 @@
         <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6865,7 +6853,7 @@
         <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -6876,7 +6864,7 @@
         <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6898,7 +6886,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6920,7 +6908,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -6931,7 +6919,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -6942,7 +6930,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -6953,7 +6941,7 @@
         <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6964,7 +6952,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -6975,7 +6963,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6986,7 +6974,7 @@
         <v>59</v>
       </c>
       <c r="C36" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6997,7 +6985,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -7008,7 +6996,7 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -7019,7 +7007,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -7030,7 +7018,7 @@
         <v>63</v>
       </c>
       <c r="C40" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -7041,7 +7029,7 @@
         <v>64</v>
       </c>
       <c r="C41" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -7052,7 +7040,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -7063,7 +7051,7 @@
         <v>66</v>
       </c>
       <c r="C43" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -7074,7 +7062,7 @@
         <v>67</v>
       </c>
       <c r="C44" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -7085,7 +7073,7 @@
         <v>68</v>
       </c>
       <c r="C45" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -7096,7 +7084,7 @@
         <v>69</v>
       </c>
       <c r="C46" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -7107,7 +7095,7 @@
         <v>70</v>
       </c>
       <c r="C47" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -7118,7 +7106,7 @@
         <v>71</v>
       </c>
       <c r="C48" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -7129,7 +7117,7 @@
         <v>72</v>
       </c>
       <c r="C49" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -7140,7 +7128,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -7151,7 +7139,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -7162,7 +7150,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -7173,7 +7161,7 @@
         <v>76</v>
       </c>
       <c r="C53" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -7184,7 +7172,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -7195,7 +7183,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -7206,7 +7194,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -7217,7 +7205,7 @@
         <v>80</v>
       </c>
       <c r="C57" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -7228,7 +7216,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -7239,7 +7227,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -7261,7 +7249,7 @@
         <v>84</v>
       </c>
       <c r="C61" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -7272,7 +7260,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -7283,7 +7271,7 @@
         <v>86</v>
       </c>
       <c r="C63" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -7294,7 +7282,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -7305,7 +7293,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -7316,7 +7304,7 @@
         <v>89</v>
       </c>
       <c r="C66" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -7327,7 +7315,7 @@
         <v>90</v>
       </c>
       <c r="C67" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -7338,7 +7326,7 @@
         <v>91</v>
       </c>
       <c r="C68" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -7349,7 +7337,7 @@
         <v>92</v>
       </c>
       <c r="C69" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -7360,7 +7348,7 @@
         <v>93</v>
       </c>
       <c r="C70" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -7371,7 +7359,7 @@
         <v>94</v>
       </c>
       <c r="C71" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -7382,7 +7370,7 @@
         <v>95</v>
       </c>
       <c r="C72" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -7393,7 +7381,7 @@
         <v>96</v>
       </c>
       <c r="C73" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -7404,7 +7392,7 @@
         <v>97</v>
       </c>
       <c r="C74" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -7415,7 +7403,7 @@
         <v>98</v>
       </c>
       <c r="C75" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -7426,7 +7414,7 @@
         <v>99</v>
       </c>
       <c r="C76" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -7437,7 +7425,7 @@
         <v>100</v>
       </c>
       <c r="C77" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -7448,7 +7436,7 @@
         <v>101</v>
       </c>
       <c r="C78" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -7459,7 +7447,7 @@
         <v>102</v>
       </c>
       <c r="C79" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -7470,7 +7458,7 @@
         <v>103</v>
       </c>
       <c r="C80" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -7481,7 +7469,7 @@
         <v>104</v>
       </c>
       <c r="C81" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -7492,7 +7480,7 @@
         <v>105</v>
       </c>
       <c r="C82" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -7503,7 +7491,7 @@
         <v>106</v>
       </c>
       <c r="C83" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -7514,7 +7502,7 @@
         <v>107</v>
       </c>
       <c r="C84" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -7525,7 +7513,7 @@
         <v>108</v>
       </c>
       <c r="C85" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -7536,7 +7524,7 @@
         <v>109</v>
       </c>
       <c r="C86" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -7547,7 +7535,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -7558,7 +7546,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -7569,7 +7557,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -7580,7 +7568,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -7591,7 +7579,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -7602,7 +7590,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -7613,7 +7601,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -7624,7 +7612,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -7635,7 +7623,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -7646,7 +7634,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -7657,7 +7645,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -7668,7 +7656,7 @@
         <v>121</v>
       </c>
       <c r="C98" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -7679,7 +7667,7 @@
         <v>122</v>
       </c>
       <c r="C99" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -7690,7 +7678,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -7701,7 +7689,7 @@
         <v>124</v>
       </c>
       <c r="C101" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -7712,7 +7700,7 @@
         <v>125</v>
       </c>
       <c r="C102" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -7723,7 +7711,7 @@
         <v>126</v>
       </c>
       <c r="C103" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -7734,7 +7722,7 @@
         <v>127</v>
       </c>
       <c r="C104" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -7745,7 +7733,7 @@
         <v>128</v>
       </c>
       <c r="C105" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -7756,7 +7744,7 @@
         <v>129</v>
       </c>
       <c r="C106" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -7767,7 +7755,7 @@
         <v>130</v>
       </c>
       <c r="C107" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -7778,7 +7766,7 @@
         <v>131</v>
       </c>
       <c r="C108" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -7789,7 +7777,7 @@
         <v>132</v>
       </c>
       <c r="C109" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -7800,7 +7788,7 @@
         <v>133</v>
       </c>
       <c r="C110" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -7811,7 +7799,7 @@
         <v>134</v>
       </c>
       <c r="C111" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -7822,7 +7810,7 @@
         <v>135</v>
       </c>
       <c r="C112" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -7833,7 +7821,7 @@
         <v>136</v>
       </c>
       <c r="C113" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -7844,7 +7832,7 @@
         <v>137</v>
       </c>
       <c r="C114" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -7855,7 +7843,7 @@
         <v>138</v>
       </c>
       <c r="C115" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -7866,7 +7854,7 @@
         <v>139</v>
       </c>
       <c r="C116" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -7877,7 +7865,7 @@
         <v>140</v>
       </c>
       <c r="C117" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -7888,7 +7876,7 @@
         <v>141</v>
       </c>
       <c r="C118" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -7899,7 +7887,7 @@
         <v>142</v>
       </c>
       <c r="C119" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -7910,7 +7898,7 @@
         <v>143</v>
       </c>
       <c r="C120" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -7921,7 +7909,7 @@
         <v>144</v>
       </c>
       <c r="C121" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -7932,7 +7920,7 @@
         <v>145</v>
       </c>
       <c r="C122" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -7943,7 +7931,7 @@
         <v>146</v>
       </c>
       <c r="C123" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -7954,7 +7942,7 @@
         <v>147</v>
       </c>
       <c r="C124" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -7965,7 +7953,7 @@
         <v>148</v>
       </c>
       <c r="C125" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -7976,7 +7964,7 @@
         <v>149</v>
       </c>
       <c r="C126" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -7987,7 +7975,7 @@
         <v>150</v>
       </c>
       <c r="C127" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -7998,7 +7986,7 @@
         <v>151</v>
       </c>
       <c r="C128" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -8009,7 +7997,7 @@
         <v>152</v>
       </c>
       <c r="C129" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -8020,7 +8008,7 @@
         <v>153</v>
       </c>
       <c r="C130" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -8031,7 +8019,7 @@
         <v>154</v>
       </c>
       <c r="C131" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -8042,7 +8030,7 @@
         <v>155</v>
       </c>
       <c r="C132" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -8053,7 +8041,7 @@
         <v>156</v>
       </c>
       <c r="C133" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -8064,7 +8052,7 @@
         <v>157</v>
       </c>
       <c r="C134" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -8075,7 +8063,7 @@
         <v>158</v>
       </c>
       <c r="C135" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -8086,7 +8074,7 @@
         <v>159</v>
       </c>
       <c r="C136" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -8097,7 +8085,7 @@
         <v>160</v>
       </c>
       <c r="C137" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -8108,7 +8096,7 @@
         <v>161</v>
       </c>
       <c r="C138" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -8119,7 +8107,7 @@
         <v>162</v>
       </c>
       <c r="C139" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -8130,7 +8118,7 @@
         <v>163</v>
       </c>
       <c r="C140" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -8141,7 +8129,7 @@
         <v>164</v>
       </c>
       <c r="C141" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -8152,7 +8140,7 @@
         <v>165</v>
       </c>
       <c r="C142" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -8163,7 +8151,7 @@
         <v>166</v>
       </c>
       <c r="C143" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -8174,7 +8162,7 @@
         <v>167</v>
       </c>
       <c r="C144" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -8185,7 +8173,7 @@
         <v>168</v>
       </c>
       <c r="C145" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -8196,7 +8184,7 @@
         <v>169</v>
       </c>
       <c r="C146" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -8207,7 +8195,7 @@
         <v>170</v>
       </c>
       <c r="C147" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -8218,7 +8206,7 @@
         <v>171</v>
       </c>
       <c r="C148" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -8229,7 +8217,7 @@
         <v>172</v>
       </c>
       <c r="C149" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -8240,7 +8228,7 @@
         <v>173</v>
       </c>
       <c r="C150" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -8251,7 +8239,7 @@
         <v>174</v>
       </c>
       <c r="C151" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -8262,7 +8250,7 @@
         <v>175</v>
       </c>
       <c r="C152" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -8273,7 +8261,7 @@
         <v>176</v>
       </c>
       <c r="C153" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -8284,7 +8272,7 @@
         <v>177</v>
       </c>
       <c r="C154" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -8295,7 +8283,7 @@
         <v>178</v>
       </c>
       <c r="C155" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -8306,7 +8294,7 @@
         <v>179</v>
       </c>
       <c r="C156" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -8317,7 +8305,7 @@
         <v>180</v>
       </c>
       <c r="C157" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -8328,7 +8316,7 @@
         <v>181</v>
       </c>
       <c r="C158" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -8339,7 +8327,7 @@
         <v>182</v>
       </c>
       <c r="C159" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -8350,7 +8338,7 @@
         <v>183</v>
       </c>
       <c r="C160" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -8361,7 +8349,7 @@
         <v>184</v>
       </c>
       <c r="C161" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -8372,7 +8360,7 @@
         <v>185</v>
       </c>
       <c r="C162" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -8383,7 +8371,7 @@
         <v>186</v>
       </c>
       <c r="C163" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -8394,7 +8382,7 @@
         <v>187</v>
       </c>
       <c r="C164" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -8405,7 +8393,7 @@
         <v>188</v>
       </c>
       <c r="C165" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -8416,7 +8404,7 @@
         <v>189</v>
       </c>
       <c r="C166" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -8427,7 +8415,7 @@
         <v>190</v>
       </c>
       <c r="C167" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -8438,7 +8426,7 @@
         <v>191</v>
       </c>
       <c r="C168" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -8449,7 +8437,7 @@
         <v>192</v>
       </c>
       <c r="C169" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -8460,7 +8448,7 @@
         <v>193</v>
       </c>
       <c r="C170" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -8471,7 +8459,7 @@
         <v>194</v>
       </c>
       <c r="C171" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -8482,7 +8470,7 @@
         <v>195</v>
       </c>
       <c r="C172" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -8493,7 +8481,7 @@
         <v>196</v>
       </c>
       <c r="C173" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -8504,7 +8492,7 @@
         <v>197</v>
       </c>
       <c r="C174" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -8515,7 +8503,7 @@
         <v>198</v>
       </c>
       <c r="C175" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -8526,7 +8514,7 @@
         <v>199</v>
       </c>
       <c r="C176" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -8537,7 +8525,7 @@
         <v>200</v>
       </c>
       <c r="C177" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -8548,7 +8536,7 @@
         <v>201</v>
       </c>
       <c r="C178" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -8559,7 +8547,7 @@
         <v>202</v>
       </c>
       <c r="C179" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -8570,7 +8558,7 @@
         <v>203</v>
       </c>
       <c r="C180" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -8581,7 +8569,7 @@
         <v>204</v>
       </c>
       <c r="C181" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -8592,7 +8580,7 @@
         <v>205</v>
       </c>
       <c r="C182" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -8603,7 +8591,7 @@
         <v>206</v>
       </c>
       <c r="C183" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -8614,7 +8602,7 @@
         <v>207</v>
       </c>
       <c r="C184" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -8625,7 +8613,7 @@
         <v>208</v>
       </c>
       <c r="C185" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -8636,7 +8624,7 @@
         <v>209</v>
       </c>
       <c r="C186" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -8647,7 +8635,7 @@
         <v>210</v>
       </c>
       <c r="C187" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -8658,7 +8646,7 @@
         <v>211</v>
       </c>
       <c r="C188" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -8669,7 +8657,7 @@
         <v>212</v>
       </c>
       <c r="C189" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -8680,7 +8668,7 @@
         <v>213</v>
       </c>
       <c r="C190" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -8691,7 +8679,7 @@
         <v>214</v>
       </c>
       <c r="C191" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -8702,7 +8690,7 @@
         <v>215</v>
       </c>
       <c r="C192" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -8713,7 +8701,7 @@
         <v>216</v>
       </c>
       <c r="C193" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -8724,7 +8712,7 @@
         <v>217</v>
       </c>
       <c r="C194" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -8735,7 +8723,7 @@
         <v>218</v>
       </c>
       <c r="C195" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -8746,7 +8734,7 @@
         <v>219</v>
       </c>
       <c r="C196" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -8757,7 +8745,7 @@
         <v>220</v>
       </c>
       <c r="C197" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -8768,7 +8756,7 @@
         <v>221</v>
       </c>
       <c r="C198" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -8779,7 +8767,7 @@
         <v>222</v>
       </c>
       <c r="C199" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -8790,7 +8778,7 @@
         <v>223</v>
       </c>
       <c r="C200" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -8801,7 +8789,7 @@
         <v>224</v>
       </c>
       <c r="C201" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -8812,7 +8800,7 @@
         <v>225</v>
       </c>
       <c r="C202" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -8823,7 +8811,7 @@
         <v>226</v>
       </c>
       <c r="C203" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -8834,7 +8822,7 @@
         <v>227</v>
       </c>
       <c r="C204" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -8845,7 +8833,7 @@
         <v>228</v>
       </c>
       <c r="C205" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -8856,7 +8844,7 @@
         <v>229</v>
       </c>
       <c r="C206" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -8867,7 +8855,7 @@
         <v>230</v>
       </c>
       <c r="C207" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -8878,7 +8866,7 @@
         <v>231</v>
       </c>
       <c r="C208" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -8889,7 +8877,7 @@
         <v>232</v>
       </c>
       <c r="C209" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -8900,7 +8888,7 @@
         <v>233</v>
       </c>
       <c r="C210" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -8911,7 +8899,7 @@
         <v>234</v>
       </c>
       <c r="C211" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -8922,7 +8910,7 @@
         <v>235</v>
       </c>
       <c r="C212" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -8933,7 +8921,7 @@
         <v>236</v>
       </c>
       <c r="C213" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -8944,7 +8932,7 @@
         <v>237</v>
       </c>
       <c r="C214" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -8955,7 +8943,7 @@
         <v>238</v>
       </c>
       <c r="C215" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -8966,7 +8954,7 @@
         <v>239</v>
       </c>
       <c r="C216" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -8977,7 +8965,7 @@
         <v>240</v>
       </c>
       <c r="C217" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -8988,7 +8976,7 @@
         <v>241</v>
       </c>
       <c r="C218" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -8999,7 +8987,7 @@
         <v>242</v>
       </c>
       <c r="C219" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -9010,7 +8998,7 @@
         <v>243</v>
       </c>
       <c r="C220" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -9021,7 +9009,7 @@
         <v>244</v>
       </c>
       <c r="C221" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -9032,7 +9020,7 @@
         <v>245</v>
       </c>
       <c r="C222" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -9043,7 +9031,7 @@
         <v>246</v>
       </c>
       <c r="C223" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -9054,7 +9042,7 @@
         <v>247</v>
       </c>
       <c r="C224" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -9065,7 +9053,7 @@
         <v>248</v>
       </c>
       <c r="C225" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -9076,7 +9064,7 @@
         <v>249</v>
       </c>
       <c r="C226" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -9087,7 +9075,7 @@
         <v>250</v>
       </c>
       <c r="C227" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -9098,7 +9086,7 @@
         <v>251</v>
       </c>
       <c r="C228" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -9109,7 +9097,7 @@
         <v>252</v>
       </c>
       <c r="C229" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -9120,7 +9108,7 @@
         <v>253</v>
       </c>
       <c r="C230" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -9131,7 +9119,7 @@
         <v>254</v>
       </c>
       <c r="C231" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -9142,7 +9130,7 @@
         <v>255</v>
       </c>
       <c r="C232" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -9153,7 +9141,7 @@
         <v>256</v>
       </c>
       <c r="C233" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -9164,7 +9152,7 @@
         <v>257</v>
       </c>
       <c r="C234" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -9175,7 +9163,7 @@
         <v>258</v>
       </c>
       <c r="C235" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -9186,7 +9174,7 @@
         <v>259</v>
       </c>
       <c r="C236" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -9197,7 +9185,7 @@
         <v>260</v>
       </c>
       <c r="C237" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -9208,7 +9196,7 @@
         <v>261</v>
       </c>
       <c r="C238" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -9219,7 +9207,7 @@
         <v>262</v>
       </c>
       <c r="C239" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -9230,7 +9218,7 @@
         <v>263</v>
       </c>
       <c r="C240" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -9241,7 +9229,7 @@
         <v>264</v>
       </c>
       <c r="C241" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -9252,7 +9240,7 @@
         <v>265</v>
       </c>
       <c r="C242" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -9263,7 +9251,7 @@
         <v>266</v>
       </c>
       <c r="C243" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -9274,7 +9262,7 @@
         <v>267</v>
       </c>
       <c r="C244" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -9285,7 +9273,7 @@
         <v>268</v>
       </c>
       <c r="C245" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -9296,7 +9284,7 @@
         <v>269</v>
       </c>
       <c r="C246" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -9307,7 +9295,7 @@
         <v>270</v>
       </c>
       <c r="C247" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -9318,7 +9306,7 @@
         <v>271</v>
       </c>
       <c r="C248" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -9329,7 +9317,7 @@
         <v>272</v>
       </c>
       <c r="C249" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -9340,7 +9328,7 @@
         <v>273</v>
       </c>
       <c r="C250" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -9351,7 +9339,7 @@
         <v>274</v>
       </c>
       <c r="C251" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -9362,7 +9350,7 @@
         <v>275</v>
       </c>
       <c r="C252" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -9373,7 +9361,7 @@
         <v>276</v>
       </c>
       <c r="C253" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -9384,7 +9372,7 @@
         <v>277</v>
       </c>
       <c r="C254" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -9395,7 +9383,7 @@
         <v>278</v>
       </c>
       <c r="C255" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -9406,7 +9394,7 @@
         <v>279</v>
       </c>
       <c r="C256" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -9417,7 +9405,7 @@
         <v>280</v>
       </c>
       <c r="C257" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -9428,7 +9416,7 @@
         <v>281</v>
       </c>
       <c r="C258" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="259" spans="1:3">
@@ -9439,7 +9427,7 @@
         <v>282</v>
       </c>
       <c r="C259" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -9450,7 +9438,7 @@
         <v>283</v>
       </c>
       <c r="C260" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="261" spans="1:3">
@@ -9461,7 +9449,7 @@
         <v>284</v>
       </c>
       <c r="C261" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="262" spans="1:3">
@@ -9472,7 +9460,7 @@
         <v>285</v>
       </c>
       <c r="C262" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -9483,7 +9471,7 @@
         <v>286</v>
       </c>
       <c r="C263" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="264" spans="1:3">
@@ -9494,7 +9482,7 @@
         <v>287</v>
       </c>
       <c r="C264" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -9505,7 +9493,7 @@
         <v>288</v>
       </c>
       <c r="C265" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="266" spans="1:3">
@@ -9516,7 +9504,7 @@
         <v>289</v>
       </c>
       <c r="C266" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="267" spans="1:3">
@@ -9527,7 +9515,7 @@
         <v>290</v>
       </c>
       <c r="C267" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="268" spans="1:3">
@@ -9538,7 +9526,7 @@
         <v>291</v>
       </c>
       <c r="C268" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="269" spans="1:3">
@@ -9549,7 +9537,7 @@
         <v>292</v>
       </c>
       <c r="C269" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="270" spans="1:3">
@@ -9560,7 +9548,7 @@
         <v>293</v>
       </c>
       <c r="C270" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="271" spans="1:3">
@@ -9571,7 +9559,7 @@
         <v>294</v>
       </c>
       <c r="C271" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="272" spans="1:3">
@@ -9582,7 +9570,7 @@
         <v>295</v>
       </c>
       <c r="C272" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="273" spans="1:3">
@@ -9593,7 +9581,7 @@
         <v>296</v>
       </c>
       <c r="C273" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="274" spans="1:3">
@@ -9604,7 +9592,7 @@
         <v>297</v>
       </c>
       <c r="C274" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="275" spans="1:3">
@@ -9615,7 +9603,7 @@
         <v>298</v>
       </c>
       <c r="C275" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="276" spans="1:3">
@@ -9626,7 +9614,7 @@
         <v>299</v>
       </c>
       <c r="C276" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="277" spans="1:3">
@@ -9637,7 +9625,7 @@
         <v>300</v>
       </c>
       <c r="C277" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="278" spans="1:3">
@@ -9648,7 +9636,7 @@
         <v>301</v>
       </c>
       <c r="C278" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="279" spans="1:3">
@@ -9659,7 +9647,7 @@
         <v>302</v>
       </c>
       <c r="C279" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="280" spans="1:3">
@@ -9670,7 +9658,7 @@
         <v>303</v>
       </c>
       <c r="C280" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -9681,7 +9669,7 @@
         <v>304</v>
       </c>
       <c r="C281" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="282" spans="1:3">
@@ -9692,7 +9680,7 @@
         <v>305</v>
       </c>
       <c r="C282" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="283" spans="1:3">
@@ -9703,7 +9691,7 @@
         <v>306</v>
       </c>
       <c r="C283" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="284" spans="1:3">
@@ -9714,7 +9702,7 @@
         <v>307</v>
       </c>
       <c r="C284" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="285" spans="1:3">
@@ -9725,7 +9713,7 @@
         <v>308</v>
       </c>
       <c r="C285" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="286" spans="1:3">
@@ -9736,7 +9724,7 @@
         <v>309</v>
       </c>
       <c r="C286" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="287" spans="1:3">
@@ -9747,7 +9735,7 @@
         <v>310</v>
       </c>
       <c r="C287" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="288" spans="1:3">
@@ -9758,7 +9746,7 @@
         <v>311</v>
       </c>
       <c r="C288" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="289" spans="1:3">
@@ -9769,7 +9757,7 @@
         <v>312</v>
       </c>
       <c r="C289" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="290" spans="1:3">
@@ -9780,7 +9768,7 @@
         <v>313</v>
       </c>
       <c r="C290" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="291" spans="1:3">
@@ -9791,7 +9779,7 @@
         <v>314</v>
       </c>
       <c r="C291" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="292" spans="1:3">
@@ -9802,7 +9790,7 @@
         <v>315</v>
       </c>
       <c r="C292" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="293" spans="1:3">
@@ -9813,7 +9801,7 @@
         <v>316</v>
       </c>
       <c r="C293" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="294" spans="1:3">
@@ -9824,7 +9812,7 @@
         <v>317</v>
       </c>
       <c r="C294" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="295" spans="1:3">
@@ -9835,7 +9823,7 @@
         <v>318</v>
       </c>
       <c r="C295" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="296" spans="1:3">
@@ -9846,7 +9834,7 @@
         <v>319</v>
       </c>
       <c r="C296" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="297" spans="1:3">
@@ -9857,7 +9845,7 @@
         <v>320</v>
       </c>
       <c r="C297" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="298" spans="1:3">
@@ -9868,7 +9856,7 @@
         <v>321</v>
       </c>
       <c r="C298" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="299" spans="1:3">
@@ -9879,7 +9867,7 @@
         <v>322</v>
       </c>
       <c r="C299" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="300" spans="1:3">
@@ -9890,7 +9878,7 @@
         <v>323</v>
       </c>
       <c r="C300" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="301" spans="1:3">
@@ -9901,7 +9889,7 @@
         <v>324</v>
       </c>
       <c r="C301" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -9912,7 +9900,7 @@
         <v>325</v>
       </c>
       <c r="C302" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="303" spans="1:3">
@@ -9923,7 +9911,7 @@
         <v>326</v>
       </c>
       <c r="C303" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="304" spans="1:3">
@@ -9934,7 +9922,7 @@
         <v>327</v>
       </c>
       <c r="C304" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -9945,7 +9933,7 @@
         <v>328</v>
       </c>
       <c r="C305" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="306" spans="1:3">
@@ -9956,7 +9944,7 @@
         <v>329</v>
       </c>
       <c r="C306" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="307" spans="1:3">
@@ -9967,7 +9955,7 @@
         <v>330</v>
       </c>
       <c r="C307" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="308" spans="1:3">
@@ -9978,7 +9966,7 @@
         <v>331</v>
       </c>
       <c r="C308" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="309" spans="1:3">
@@ -9989,7 +9977,7 @@
         <v>332</v>
       </c>
       <c r="C309" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="310" spans="1:3">
@@ -10000,7 +9988,7 @@
         <v>333</v>
       </c>
       <c r="C310" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="311" spans="1:3">
@@ -10011,7 +9999,7 @@
         <v>334</v>
       </c>
       <c r="C311" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="312" spans="1:3">
@@ -10022,7 +10010,7 @@
         <v>335</v>
       </c>
       <c r="C312" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="313" spans="1:3">
@@ -10033,7 +10021,7 @@
         <v>336</v>
       </c>
       <c r="C313" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="314" spans="1:3">
@@ -10044,7 +10032,7 @@
         <v>337</v>
       </c>
       <c r="C314" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="315" spans="1:3">
@@ -10055,7 +10043,7 @@
         <v>338</v>
       </c>
       <c r="C315" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="316" spans="1:3">
@@ -10066,7 +10054,7 @@
         <v>339</v>
       </c>
       <c r="C316" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="317" spans="1:3">
@@ -10077,7 +10065,7 @@
         <v>340</v>
       </c>
       <c r="C317" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="318" spans="1:3">
@@ -10088,7 +10076,7 @@
         <v>341</v>
       </c>
       <c r="C318" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="319" spans="1:3">
@@ -10099,7 +10087,7 @@
         <v>342</v>
       </c>
       <c r="C319" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="320" spans="1:3">
@@ -10110,7 +10098,7 @@
         <v>343</v>
       </c>
       <c r="C320" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="321" spans="1:3">
@@ -10121,7 +10109,7 @@
         <v>344</v>
       </c>
       <c r="C321" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -10132,7 +10120,7 @@
         <v>345</v>
       </c>
       <c r="C322" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="323" spans="1:3">
@@ -10143,7 +10131,7 @@
         <v>346</v>
       </c>
       <c r="C323" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="324" spans="1:3">
@@ -10154,7 +10142,7 @@
         <v>347</v>
       </c>
       <c r="C324" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -10165,7 +10153,7 @@
         <v>348</v>
       </c>
       <c r="C325" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="326" spans="1:3">
@@ -10176,7 +10164,7 @@
         <v>349</v>
       </c>
       <c r="C326" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="327" spans="1:3">
@@ -10187,7 +10175,7 @@
         <v>350</v>
       </c>
       <c r="C327" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="328" spans="1:3">
@@ -10198,7 +10186,7 @@
         <v>351</v>
       </c>
       <c r="C328" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="329" spans="1:3">
@@ -10209,7 +10197,7 @@
         <v>352</v>
       </c>
       <c r="C329" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="330" spans="1:3">
@@ -10220,7 +10208,7 @@
         <v>353</v>
       </c>
       <c r="C330" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -10231,7 +10219,7 @@
         <v>354</v>
       </c>
       <c r="C331" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="332" spans="1:3">
@@ -10242,7 +10230,7 @@
         <v>355</v>
       </c>
       <c r="C332" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="333" spans="1:3">
@@ -10253,7 +10241,7 @@
         <v>356</v>
       </c>
       <c r="C333" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="334" spans="1:3">
@@ -10264,7 +10252,7 @@
         <v>357</v>
       </c>
       <c r="C334" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="335" spans="1:3">
@@ -10275,7 +10263,7 @@
         <v>358</v>
       </c>
       <c r="C335" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="336" spans="1:3">
@@ -10286,7 +10274,7 @@
         <v>359</v>
       </c>
       <c r="C336" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="337" spans="1:3">
@@ -10297,7 +10285,7 @@
         <v>360</v>
       </c>
       <c r="C337" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="338" spans="1:3">
@@ -10308,7 +10296,7 @@
         <v>361</v>
       </c>
       <c r="C338" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="339" spans="1:3">
@@ -10319,7 +10307,7 @@
         <v>362</v>
       </c>
       <c r="C339" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="340" spans="1:3">
@@ -10330,7 +10318,7 @@
         <v>363</v>
       </c>
       <c r="C340" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="341" spans="1:3">
@@ -10341,7 +10329,7 @@
         <v>364</v>
       </c>
       <c r="C341" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -10352,7 +10340,7 @@
         <v>365</v>
       </c>
       <c r="C342" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="343" spans="1:3">
@@ -10363,7 +10351,7 @@
         <v>366</v>
       </c>
       <c r="C343" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="344" spans="1:3">
@@ -10374,7 +10362,7 @@
         <v>367</v>
       </c>
       <c r="C344" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="345" spans="1:3">
@@ -10385,7 +10373,7 @@
         <v>368</v>
       </c>
       <c r="C345" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="346" spans="1:3">
@@ -10396,7 +10384,7 @@
         <v>369</v>
       </c>
       <c r="C346" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="347" spans="1:3">
@@ -10407,7 +10395,7 @@
         <v>370</v>
       </c>
       <c r="C347" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="348" spans="1:3">
@@ -10418,7 +10406,7 @@
         <v>371</v>
       </c>
       <c r="C348" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="349" spans="1:3">
@@ -10429,7 +10417,7 @@
         <v>372</v>
       </c>
       <c r="C349" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -10440,7 +10428,7 @@
         <v>373</v>
       </c>
       <c r="C350" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="351" spans="1:3">
@@ -10451,7 +10439,7 @@
         <v>374</v>
       </c>
       <c r="C351" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -10462,7 +10450,7 @@
         <v>375</v>
       </c>
       <c r="C352" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="353" spans="1:3">
@@ -10473,7 +10461,7 @@
         <v>376</v>
       </c>
       <c r="C353" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="354" spans="1:3">
@@ -10484,7 +10472,7 @@
         <v>377</v>
       </c>
       <c r="C354" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -10495,7 +10483,7 @@
         <v>378</v>
       </c>
       <c r="C355" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="356" spans="1:3">
@@ -10506,7 +10494,7 @@
         <v>379</v>
       </c>
       <c r="C356" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="357" spans="1:3">
@@ -10517,7 +10505,7 @@
         <v>380</v>
       </c>
       <c r="C357" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="358" spans="1:3">
@@ -10528,7 +10516,7 @@
         <v>381</v>
       </c>
       <c r="C358" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="359" spans="1:3">
@@ -10539,7 +10527,7 @@
         <v>382</v>
       </c>
       <c r="C359" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -10550,7 +10538,7 @@
         <v>383</v>
       </c>
       <c r="C360" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="361" spans="1:3">
@@ -10561,7 +10549,7 @@
         <v>384</v>
       </c>
       <c r="C361" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="362" spans="1:3">
@@ -10572,7 +10560,7 @@
         <v>385</v>
       </c>
       <c r="C362" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="363" spans="1:3">
@@ -10583,7 +10571,7 @@
         <v>386</v>
       </c>
       <c r="C363" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="364" spans="1:3">
@@ -10594,7 +10582,7 @@
         <v>387</v>
       </c>
       <c r="C364" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="365" spans="1:3">
@@ -10605,7 +10593,7 @@
         <v>388</v>
       </c>
       <c r="C365" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="366" spans="1:3">
@@ -10616,7 +10604,7 @@
         <v>389</v>
       </c>
       <c r="C366" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="367" spans="1:3">
@@ -10627,7 +10615,7 @@
         <v>390</v>
       </c>
       <c r="C367" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="368" spans="1:3">
@@ -10638,7 +10626,7 @@
         <v>391</v>
       </c>
       <c r="C368" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="369" spans="1:3">
@@ -10649,7 +10637,7 @@
         <v>392</v>
       </c>
       <c r="C369" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="370" spans="1:3">
@@ -10660,7 +10648,7 @@
         <v>393</v>
       </c>
       <c r="C370" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="371" spans="1:3">
@@ -10671,7 +10659,7 @@
         <v>394</v>
       </c>
       <c r="C371" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -10682,7 +10670,7 @@
         <v>395</v>
       </c>
       <c r="C372" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="373" spans="1:3">
@@ -10693,7 +10681,7 @@
         <v>396</v>
       </c>
       <c r="C373" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="374" spans="1:3">
@@ -10704,7 +10692,7 @@
         <v>397</v>
       </c>
       <c r="C374" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="375" spans="1:3">
@@ -10715,7 +10703,7 @@
         <v>398</v>
       </c>
       <c r="C375" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="376" spans="1:3">
@@ -10726,7 +10714,7 @@
         <v>399</v>
       </c>
       <c r="C376" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="377" spans="1:3">
@@ -10737,7 +10725,7 @@
         <v>400</v>
       </c>
       <c r="C377" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="378" spans="1:3">
@@ -10748,7 +10736,7 @@
         <v>401</v>
       </c>
       <c r="C378" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="379" spans="1:3">
@@ -10759,7 +10747,7 @@
         <v>402</v>
       </c>
       <c r="C379" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="380" spans="1:3">
@@ -10770,7 +10758,7 @@
         <v>403</v>
       </c>
       <c r="C380" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="381" spans="1:3">
@@ -10781,7 +10769,7 @@
         <v>404</v>
       </c>
       <c r="C381" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="382" spans="1:3">
@@ -10792,7 +10780,7 @@
         <v>405</v>
       </c>
       <c r="C382" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="383" spans="1:3">
@@ -10803,7 +10791,7 @@
         <v>406</v>
       </c>
       <c r="C383" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="384" spans="1:3">
@@ -10814,7 +10802,7 @@
         <v>407</v>
       </c>
       <c r="C384" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="385" spans="1:3">
@@ -10825,7 +10813,7 @@
         <v>408</v>
       </c>
       <c r="C385" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="386" spans="1:3">
@@ -10836,7 +10824,7 @@
         <v>409</v>
       </c>
       <c r="C386" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="387" spans="1:3">
@@ -10847,7 +10835,7 @@
         <v>410</v>
       </c>
       <c r="C387" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="388" spans="1:3">
@@ -10858,7 +10846,7 @@
         <v>411</v>
       </c>
       <c r="C388" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="389" spans="1:3">
@@ -10869,7 +10857,7 @@
         <v>412</v>
       </c>
       <c r="C389" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="390" spans="1:3">
@@ -10880,7 +10868,7 @@
         <v>413</v>
       </c>
       <c r="C390" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="391" spans="1:3">
@@ -10891,7 +10879,7 @@
         <v>414</v>
       </c>
       <c r="C391" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="392" spans="1:3">
@@ -10902,7 +10890,7 @@
         <v>415</v>
       </c>
       <c r="C392" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="393" spans="1:3">
@@ -10913,7 +10901,7 @@
         <v>416</v>
       </c>
       <c r="C393" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="394" spans="1:3">
@@ -10924,7 +10912,7 @@
         <v>417</v>
       </c>
       <c r="C394" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="395" spans="1:3">
@@ -10935,7 +10923,7 @@
         <v>418</v>
       </c>
       <c r="C395" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="396" spans="1:3">
@@ -10946,7 +10934,7 @@
         <v>419</v>
       </c>
       <c r="C396" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="397" spans="1:3">
@@ -10957,7 +10945,7 @@
         <v>420</v>
       </c>
       <c r="C397" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="398" spans="1:3">
@@ -10968,7 +10956,7 @@
         <v>421</v>
       </c>
       <c r="C398" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="399" spans="1:3">
@@ -10979,7 +10967,7 @@
         <v>422</v>
       </c>
       <c r="C399" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="400" spans="1:3">
@@ -10990,7 +10978,7 @@
         <v>423</v>
       </c>
       <c r="C400" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="401" spans="1:3">
@@ -11001,7 +10989,7 @@
         <v>424</v>
       </c>
       <c r="C401" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="402" spans="1:3">
@@ -11012,7 +11000,7 @@
         <v>425</v>
       </c>
       <c r="C402" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="403" spans="1:3">
@@ -11023,7 +11011,7 @@
         <v>426</v>
       </c>
       <c r="C403" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="404" spans="1:3">
@@ -11034,7 +11022,7 @@
         <v>427</v>
       </c>
       <c r="C404" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="405" spans="1:3">
@@ -11045,7 +11033,7 @@
         <v>428</v>
       </c>
       <c r="C405" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="406" spans="1:3">
@@ -11056,7 +11044,7 @@
         <v>429</v>
       </c>
       <c r="C406" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="407" spans="1:3">
@@ -11067,7 +11055,7 @@
         <v>430</v>
       </c>
       <c r="C407" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="408" spans="1:3">
@@ -11078,7 +11066,7 @@
         <v>431</v>
       </c>
       <c r="C408" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="409" spans="1:3">
@@ -11089,7 +11077,7 @@
         <v>432</v>
       </c>
       <c r="C409" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="410" spans="1:3">
@@ -11100,7 +11088,7 @@
         <v>433</v>
       </c>
       <c r="C410" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="411" spans="1:3">
@@ -11111,7 +11099,7 @@
         <v>434</v>
       </c>
       <c r="C411" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="412" spans="1:3">
@@ -11122,7 +11110,7 @@
         <v>435</v>
       </c>
       <c r="C412" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="413" spans="1:3">
@@ -11133,7 +11121,7 @@
         <v>436</v>
       </c>
       <c r="C413" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="414" spans="1:3">
@@ -11144,7 +11132,7 @@
         <v>437</v>
       </c>
       <c r="C414" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="415" spans="1:3">
@@ -11155,7 +11143,7 @@
         <v>438</v>
       </c>
       <c r="C415" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="416" spans="1:3">
@@ -11166,7 +11154,7 @@
         <v>439</v>
       </c>
       <c r="C416" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="417" spans="1:3">
@@ -11177,7 +11165,7 @@
         <v>440</v>
       </c>
       <c r="C417" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="418" spans="1:3">
@@ -11188,7 +11176,7 @@
         <v>441</v>
       </c>
       <c r="C418" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="419" spans="1:3">
@@ -11199,7 +11187,7 @@
         <v>442</v>
       </c>
       <c r="C419" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="420" spans="1:3">
@@ -11210,7 +11198,7 @@
         <v>443</v>
       </c>
       <c r="C420" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="421" spans="1:3">
@@ -11221,7 +11209,7 @@
         <v>444</v>
       </c>
       <c r="C421" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="422" spans="1:3">
@@ -11232,7 +11220,7 @@
         <v>445</v>
       </c>
       <c r="C422" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="423" spans="1:3">
@@ -11243,7 +11231,7 @@
         <v>446</v>
       </c>
       <c r="C423" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="424" spans="1:3">
@@ -11254,7 +11242,7 @@
         <v>447</v>
       </c>
       <c r="C424" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="425" spans="1:3">
@@ -11265,7 +11253,7 @@
         <v>448</v>
       </c>
       <c r="C425" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="426" spans="1:3">
@@ -11276,7 +11264,7 @@
         <v>449</v>
       </c>
       <c r="C426" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="427" spans="1:3">
@@ -11287,7 +11275,7 @@
         <v>450</v>
       </c>
       <c r="C427" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="428" spans="1:3">
@@ -11298,7 +11286,7 @@
         <v>451</v>
       </c>
       <c r="C428" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="429" spans="1:3">
@@ -11309,7 +11297,7 @@
         <v>452</v>
       </c>
       <c r="C429" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="430" spans="1:3">
@@ -11320,7 +11308,7 @@
         <v>453</v>
       </c>
       <c r="C430" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="431" spans="1:3">
@@ -11331,7 +11319,7 @@
         <v>454</v>
       </c>
       <c r="C431" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="432" spans="1:3">
@@ -11342,7 +11330,7 @@
         <v>455</v>
       </c>
       <c r="C432" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="433" spans="1:3">
@@ -11353,7 +11341,7 @@
         <v>456</v>
       </c>
       <c r="C433" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="434" spans="1:3">
@@ -11364,7 +11352,7 @@
         <v>457</v>
       </c>
       <c r="C434" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="435" spans="1:3">
@@ -11375,7 +11363,7 @@
         <v>458</v>
       </c>
       <c r="C435" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="436" spans="1:3">
@@ -11386,7 +11374,7 @@
         <v>459</v>
       </c>
       <c r="C436" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="437" spans="1:3">
@@ -11397,7 +11385,7 @@
         <v>460</v>
       </c>
       <c r="C437" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="438" spans="1:3">
@@ -11408,7 +11396,7 @@
         <v>461</v>
       </c>
       <c r="C438" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="439" spans="1:3">
@@ -11419,7 +11407,7 @@
         <v>462</v>
       </c>
       <c r="C439" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="440" spans="1:3">
@@ -11430,7 +11418,7 @@
         <v>463</v>
       </c>
       <c r="C440" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="441" spans="1:3">
@@ -11441,7 +11429,7 @@
         <v>464</v>
       </c>
       <c r="C441" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="442" spans="1:3">
@@ -11452,7 +11440,7 @@
         <v>465</v>
       </c>
       <c r="C442" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="443" spans="1:3">
@@ -11463,7 +11451,7 @@
         <v>466</v>
       </c>
       <c r="C443" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="444" spans="1:3">
@@ -11474,7 +11462,7 @@
         <v>467</v>
       </c>
       <c r="C444" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="445" spans="1:3">
@@ -11485,7 +11473,7 @@
         <v>468</v>
       </c>
       <c r="C445" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="446" spans="1:3">
@@ -11496,7 +11484,7 @@
         <v>469</v>
       </c>
       <c r="C446" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="447" spans="1:3">
@@ -11507,7 +11495,7 @@
         <v>470</v>
       </c>
       <c r="C447" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="448" spans="1:3">
@@ -11518,7 +11506,7 @@
         <v>471</v>
       </c>
       <c r="C448" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="449" spans="1:3">
@@ -11529,7 +11517,7 @@
         <v>472</v>
       </c>
       <c r="C449" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="450" spans="1:3">
@@ -11540,7 +11528,7 @@
         <v>473</v>
       </c>
       <c r="C450" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="451" spans="1:3">
@@ -11551,7 +11539,7 @@
         <v>474</v>
       </c>
       <c r="C451" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="452" spans="1:3">
@@ -11562,7 +11550,7 @@
         <v>475</v>
       </c>
       <c r="C452" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="453" spans="1:3">
@@ -11573,7 +11561,7 @@
         <v>476</v>
       </c>
       <c r="C453" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="454" spans="1:3">
@@ -11584,7 +11572,7 @@
         <v>477</v>
       </c>
       <c r="C454" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="455" spans="1:3">
@@ -11595,7 +11583,7 @@
         <v>478</v>
       </c>
       <c r="C455" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="456" spans="1:3">
@@ -11606,7 +11594,7 @@
         <v>479</v>
       </c>
       <c r="C456" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="457" spans="1:3">
@@ -11617,7 +11605,7 @@
         <v>480</v>
       </c>
       <c r="C457" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="458" spans="1:3">
@@ -11628,7 +11616,7 @@
         <v>481</v>
       </c>
       <c r="C458" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="459" spans="1:3">
@@ -11639,7 +11627,7 @@
         <v>482</v>
       </c>
       <c r="C459" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="460" spans="1:3">
@@ -11650,7 +11638,7 @@
         <v>483</v>
       </c>
       <c r="C460" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="461" spans="1:3">
@@ -11661,7 +11649,7 @@
         <v>484</v>
       </c>
       <c r="C461" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="462" spans="1:3">
@@ -11672,7 +11660,7 @@
         <v>485</v>
       </c>
       <c r="C462" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="463" spans="1:3">
@@ -11683,7 +11671,7 @@
         <v>486</v>
       </c>
       <c r="C463" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="464" spans="1:3">
@@ -11694,7 +11682,7 @@
         <v>487</v>
       </c>
       <c r="C464" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="465" spans="1:3">
@@ -11705,7 +11693,7 @@
         <v>488</v>
       </c>
       <c r="C465" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="466" spans="1:3">
@@ -11716,7 +11704,7 @@
         <v>489</v>
       </c>
       <c r="C466" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="467" spans="1:3">
@@ -11727,7 +11715,7 @@
         <v>490</v>
       </c>
       <c r="C467" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="468" spans="1:3">
@@ -11738,7 +11726,7 @@
         <v>491</v>
       </c>
       <c r="C468" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="469" spans="1:3">
@@ -11749,7 +11737,7 @@
         <v>492</v>
       </c>
       <c r="C469" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="470" spans="1:3">
@@ -11760,7 +11748,7 @@
         <v>493</v>
       </c>
       <c r="C470" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="471" spans="1:3">
@@ -11771,7 +11759,7 @@
         <v>494</v>
       </c>
       <c r="C471" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="472" spans="1:3">
@@ -11782,7 +11770,7 @@
         <v>495</v>
       </c>
       <c r="C472" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="473" spans="1:3">
@@ -11793,7 +11781,7 @@
         <v>496</v>
       </c>
       <c r="C473" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="474" spans="1:3">
@@ -11804,7 +11792,7 @@
         <v>497</v>
       </c>
       <c r="C474" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="475" spans="1:3">
@@ -11815,7 +11803,7 @@
         <v>498</v>
       </c>
       <c r="C475" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="476" spans="1:3">
@@ -11826,7 +11814,7 @@
         <v>499</v>
       </c>
       <c r="C476" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="477" spans="1:3">
@@ -11837,7 +11825,7 @@
         <v>500</v>
       </c>
       <c r="C477" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="478" spans="1:3">
@@ -11848,7 +11836,7 @@
         <v>501</v>
       </c>
       <c r="C478" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="479" spans="1:3">
@@ -11859,7 +11847,7 @@
         <v>502</v>
       </c>
       <c r="C479" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="480" spans="1:3">
@@ -11870,7 +11858,7 @@
         <v>503</v>
       </c>
       <c r="C480" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="481" spans="1:3">
@@ -11881,7 +11869,7 @@
         <v>504</v>
       </c>
       <c r="C481" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="482" spans="1:3">
@@ -11892,7 +11880,7 @@
         <v>505</v>
       </c>
       <c r="C482" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="483" spans="1:3">
@@ -11903,7 +11891,7 @@
         <v>506</v>
       </c>
       <c r="C483" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="484" spans="1:3">
@@ -11914,7 +11902,7 @@
         <v>507</v>
       </c>
       <c r="C484" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="485" spans="1:3">
@@ -11925,7 +11913,7 @@
         <v>508</v>
       </c>
       <c r="C485" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="486" spans="1:3">
@@ -11936,7 +11924,7 @@
         <v>509</v>
       </c>
       <c r="C486" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="487" spans="1:3">
@@ -11947,7 +11935,7 @@
         <v>510</v>
       </c>
       <c r="C487" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="488" spans="1:3">
@@ -11958,7 +11946,7 @@
         <v>511</v>
       </c>
       <c r="C488" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="489" spans="1:3">
@@ -11969,7 +11957,7 @@
         <v>512</v>
       </c>
       <c r="C489" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="490" spans="1:3">
@@ -11980,7 +11968,7 @@
         <v>513</v>
       </c>
       <c r="C490" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="491" spans="1:3">
@@ -11991,7 +11979,7 @@
         <v>514</v>
       </c>
       <c r="C491" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="492" spans="1:3">
@@ -12002,7 +11990,7 @@
         <v>515</v>
       </c>
       <c r="C492" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="493" spans="1:3">
@@ -12013,7 +12001,7 @@
         <v>516</v>
       </c>
       <c r="C493" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="494" spans="1:3">
@@ -12024,7 +12012,7 @@
         <v>517</v>
       </c>
       <c r="C494" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="495" spans="1:3">
@@ -12035,7 +12023,7 @@
         <v>518</v>
       </c>
       <c r="C495" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="496" spans="1:3">
@@ -12046,7 +12034,7 @@
         <v>519</v>
       </c>
       <c r="C496" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="497" spans="1:3">
@@ -12057,7 +12045,7 @@
         <v>520</v>
       </c>
       <c r="C497" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="498" spans="1:3">
@@ -12068,7 +12056,7 @@
         <v>521</v>
       </c>
       <c r="C498" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="499" spans="1:3">
@@ -12079,7 +12067,7 @@
         <v>522</v>
       </c>
       <c r="C499" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="500" spans="1:3">
@@ -12090,7 +12078,7 @@
         <v>523</v>
       </c>
       <c r="C500" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="501" spans="1:3">
@@ -12101,7 +12089,7 @@
         <v>524</v>
       </c>
       <c r="C501" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="502" spans="1:3">
@@ -12112,7 +12100,7 @@
         <v>525</v>
       </c>
       <c r="C502" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="503" spans="1:3">
@@ -12123,7 +12111,7 @@
         <v>526</v>
       </c>
       <c r="C503" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="504" spans="1:3">
@@ -12134,7 +12122,7 @@
         <v>527</v>
       </c>
       <c r="C504" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="505" spans="1:3">
@@ -12145,7 +12133,7 @@
         <v>528</v>
       </c>
       <c r="C505" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="506" spans="1:3">
@@ -12156,7 +12144,7 @@
         <v>529</v>
       </c>
       <c r="C506" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="507" spans="1:3">
@@ -12167,7 +12155,7 @@
         <v>530</v>
       </c>
       <c r="C507" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="508" spans="1:3">
@@ -12178,7 +12166,7 @@
         <v>531</v>
       </c>
       <c r="C508" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="509" spans="1:3">
@@ -12189,7 +12177,7 @@
         <v>532</v>
       </c>
       <c r="C509" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="510" spans="1:3">
@@ -12200,7 +12188,7 @@
         <v>533</v>
       </c>
       <c r="C510" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="511" spans="1:3">
@@ -12211,7 +12199,7 @@
         <v>534</v>
       </c>
       <c r="C511" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="512" spans="1:3">
@@ -12222,7 +12210,7 @@
         <v>535</v>
       </c>
       <c r="C512" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="513" spans="1:3">
@@ -12233,7 +12221,7 @@
         <v>536</v>
       </c>
       <c r="C513" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="514" spans="1:3">
@@ -12244,7 +12232,7 @@
         <v>537</v>
       </c>
       <c r="C514" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="515" spans="1:3">
@@ -12255,7 +12243,7 @@
         <v>538</v>
       </c>
       <c r="C515" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="516" spans="1:3">
@@ -12266,7 +12254,7 @@
         <v>539</v>
       </c>
       <c r="C516" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="517" spans="1:3">
@@ -12277,7 +12265,7 @@
         <v>540</v>
       </c>
       <c r="C517" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="518" spans="1:3">
@@ -12288,7 +12276,7 @@
         <v>541</v>
       </c>
       <c r="C518" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="519" spans="1:3">
@@ -12299,7 +12287,7 @@
         <v>542</v>
       </c>
       <c r="C519" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="520" spans="1:3">
@@ -12310,7 +12298,7 @@
         <v>543</v>
       </c>
       <c r="C520" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="521" spans="1:3">
@@ -12321,7 +12309,7 @@
         <v>544</v>
       </c>
       <c r="C521" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="522" spans="1:3">
@@ -12332,7 +12320,7 @@
         <v>545</v>
       </c>
       <c r="C522" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="523" spans="1:3">
@@ -12343,7 +12331,7 @@
         <v>546</v>
       </c>
       <c r="C523" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="524" spans="1:3">
@@ -12354,7 +12342,7 @@
         <v>547</v>
       </c>
       <c r="C524" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="525" spans="1:3">
@@ -12365,7 +12353,7 @@
         <v>548</v>
       </c>
       <c r="C525" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="526" spans="1:3">
@@ -12376,7 +12364,7 @@
         <v>549</v>
       </c>
       <c r="C526" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="527" spans="1:3">
@@ -12387,7 +12375,7 @@
         <v>550</v>
       </c>
       <c r="C527" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="528" spans="1:3">
@@ -12398,7 +12386,7 @@
         <v>551</v>
       </c>
       <c r="C528" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="529" spans="1:3">
@@ -12409,7 +12397,7 @@
         <v>552</v>
       </c>
       <c r="C529" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="530" spans="1:3">
@@ -12420,7 +12408,7 @@
         <v>553</v>
       </c>
       <c r="C530" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="531" spans="1:3">
@@ -12431,7 +12419,7 @@
         <v>554</v>
       </c>
       <c r="C531" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="532" spans="1:3">
@@ -12442,7 +12430,7 @@
         <v>555</v>
       </c>
       <c r="C532" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="533" spans="1:3">
@@ -12453,7 +12441,7 @@
         <v>556</v>
       </c>
       <c r="C533" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="534" spans="1:3">
@@ -12464,7 +12452,7 @@
         <v>557</v>
       </c>
       <c r="C534" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="535" spans="1:3">
@@ -12475,7 +12463,7 @@
         <v>558</v>
       </c>
       <c r="C535" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="536" spans="1:3">
@@ -12486,7 +12474,7 @@
         <v>559</v>
       </c>
       <c r="C536" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="537" spans="1:3">
@@ -12497,7 +12485,7 @@
         <v>560</v>
       </c>
       <c r="C537" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="538" spans="1:3">
@@ -12508,7 +12496,7 @@
         <v>561</v>
       </c>
       <c r="C538" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="539" spans="1:3">
@@ -12519,7 +12507,7 @@
         <v>562</v>
       </c>
       <c r="C539" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="540" spans="1:3">
@@ -12530,7 +12518,7 @@
         <v>563</v>
       </c>
       <c r="C540" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="541" spans="1:3">
@@ -12541,7 +12529,7 @@
         <v>564</v>
       </c>
       <c r="C541" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="542" spans="1:3">
@@ -12552,7 +12540,7 @@
         <v>565</v>
       </c>
       <c r="C542" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="543" spans="1:3">
@@ -12563,7 +12551,7 @@
         <v>566</v>
       </c>
       <c r="C543" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="544" spans="1:3">
@@ -12574,7 +12562,7 @@
         <v>567</v>
       </c>
       <c r="C544" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="545" spans="1:3">
@@ -12585,7 +12573,7 @@
         <v>568</v>
       </c>
       <c r="C545" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="546" spans="1:3">
@@ -12596,7 +12584,7 @@
         <v>569</v>
       </c>
       <c r="C546" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="547" spans="1:3">
@@ -12607,7 +12595,7 @@
         <v>570</v>
       </c>
       <c r="C547" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="548" spans="1:3">
@@ -12618,7 +12606,7 @@
         <v>571</v>
       </c>
       <c r="C548" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="549" spans="1:3">
@@ -12629,7 +12617,7 @@
         <v>572</v>
       </c>
       <c r="C549" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="550" spans="1:3">
@@ -12640,7 +12628,7 @@
         <v>573</v>
       </c>
       <c r="C550" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="551" spans="1:3">
@@ -12651,7 +12639,7 @@
         <v>574</v>
       </c>
       <c r="C551" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="552" spans="1:3">
@@ -12662,7 +12650,7 @@
         <v>575</v>
       </c>
       <c r="C552" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="553" spans="1:3">
@@ -12673,7 +12661,7 @@
         <v>576</v>
       </c>
       <c r="C553" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="554" spans="1:3">
@@ -12684,7 +12672,7 @@
         <v>577</v>
       </c>
       <c r="C554" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="555" spans="1:3">
@@ -12695,7 +12683,7 @@
         <v>578</v>
       </c>
       <c r="C555" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="556" spans="1:3">
@@ -12706,7 +12694,7 @@
         <v>579</v>
       </c>
       <c r="C556" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="557" spans="1:3">
@@ -12717,7 +12705,7 @@
         <v>580</v>
       </c>
       <c r="C557" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="558" spans="1:3">
@@ -12728,7 +12716,7 @@
         <v>581</v>
       </c>
       <c r="C558" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="559" spans="1:3">
@@ -12739,7 +12727,7 @@
         <v>582</v>
       </c>
       <c r="C559" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="560" spans="1:3">
@@ -12750,7 +12738,7 @@
         <v>583</v>
       </c>
       <c r="C560" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="561" spans="1:3">
@@ -12761,7 +12749,7 @@
         <v>584</v>
       </c>
       <c r="C561" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="562" spans="1:3">
@@ -12772,7 +12760,7 @@
         <v>585</v>
       </c>
       <c r="C562" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="563" spans="1:3">
@@ -12783,7 +12771,7 @@
         <v>586</v>
       </c>
       <c r="C563" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="564" spans="1:3">
@@ -12794,7 +12782,7 @@
         <v>587</v>
       </c>
       <c r="C564" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="565" spans="1:3">
@@ -12805,7 +12793,7 @@
         <v>588</v>
       </c>
       <c r="C565" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="566" spans="1:3">
@@ -12816,7 +12804,7 @@
         <v>589</v>
       </c>
       <c r="C566" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="567" spans="1:3">
@@ -12827,7 +12815,7 @@
         <v>590</v>
       </c>
       <c r="C567" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="568" spans="1:3">
@@ -12838,7 +12826,7 @@
         <v>591</v>
       </c>
       <c r="C568" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="569" spans="1:3">
@@ -12849,7 +12837,7 @@
         <v>592</v>
       </c>
       <c r="C569" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="570" spans="1:3">
@@ -12860,7 +12848,7 @@
         <v>593</v>
       </c>
       <c r="C570" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="571" spans="1:3">
@@ -12871,7 +12859,7 @@
         <v>594</v>
       </c>
       <c r="C571" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="572" spans="1:3">
@@ -12882,7 +12870,7 @@
         <v>595</v>
       </c>
       <c r="C572" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="573" spans="1:3">
@@ -12893,7 +12881,7 @@
         <v>596</v>
       </c>
       <c r="C573" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="574" spans="1:3">
@@ -12904,7 +12892,7 @@
         <v>597</v>
       </c>
       <c r="C574" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="575" spans="1:3">
@@ -12915,7 +12903,7 @@
         <v>598</v>
       </c>
       <c r="C575" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="576" spans="1:3">
@@ -12926,7 +12914,7 @@
         <v>599</v>
       </c>
       <c r="C576" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="577" spans="1:3">
@@ -12937,7 +12925,7 @@
         <v>600</v>
       </c>
       <c r="C577" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="578" spans="1:3">
@@ -12948,7 +12936,7 @@
         <v>601</v>
       </c>
       <c r="C578" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="579" spans="1:3">
@@ -12959,7 +12947,7 @@
         <v>602</v>
       </c>
       <c r="C579" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="580" spans="1:3">
@@ -12970,7 +12958,7 @@
         <v>603</v>
       </c>
       <c r="C580" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="581" spans="1:3">
@@ -12981,7 +12969,7 @@
         <v>604</v>
       </c>
       <c r="C581" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="582" spans="1:3">
@@ -12992,7 +12980,7 @@
         <v>605</v>
       </c>
       <c r="C582" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="583" spans="1:3">
@@ -13003,7 +12991,7 @@
         <v>606</v>
       </c>
       <c r="C583" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="584" spans="1:3">
@@ -13014,7 +13002,7 @@
         <v>607</v>
       </c>
       <c r="C584" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="585" spans="1:3">
@@ -13025,7 +13013,7 @@
         <v>608</v>
       </c>
       <c r="C585" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="586" spans="1:3">
@@ -13036,7 +13024,7 @@
         <v>609</v>
       </c>
       <c r="C586" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="587" spans="1:3">
@@ -13047,7 +13035,7 @@
         <v>610</v>
       </c>
       <c r="C587" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="588" spans="1:3">
@@ -13058,7 +13046,7 @@
         <v>611</v>
       </c>
       <c r="C588" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="589" spans="1:3">
@@ -13069,7 +13057,7 @@
         <v>612</v>
       </c>
       <c r="C589" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="590" spans="1:3">
@@ -13080,7 +13068,7 @@
         <v>613</v>
       </c>
       <c r="C590" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="591" spans="1:3">
@@ -13091,7 +13079,7 @@
         <v>614</v>
       </c>
       <c r="C591" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="592" spans="1:3">
@@ -13102,7 +13090,7 @@
         <v>615</v>
       </c>
       <c r="C592" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="593" spans="1:3">
@@ -13113,7 +13101,7 @@
         <v>616</v>
       </c>
       <c r="C593" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="594" spans="1:3">
@@ -13124,7 +13112,7 @@
         <v>617</v>
       </c>
       <c r="C594" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="595" spans="1:3">
@@ -13135,7 +13123,7 @@
         <v>618</v>
       </c>
       <c r="C595" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="596" spans="1:3">
@@ -13146,7 +13134,7 @@
         <v>619</v>
       </c>
       <c r="C596" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="597" spans="1:3">
@@ -13157,7 +13145,7 @@
         <v>620</v>
       </c>
       <c r="C597" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="598" spans="1:3">
@@ -13168,7 +13156,7 @@
         <v>621</v>
       </c>
       <c r="C598" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="599" spans="1:3">
@@ -13179,7 +13167,7 @@
         <v>622</v>
       </c>
       <c r="C599" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="600" spans="1:3">
@@ -13190,7 +13178,7 @@
         <v>623</v>
       </c>
       <c r="C600" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="601" spans="1:3">
@@ -13201,7 +13189,7 @@
         <v>624</v>
       </c>
       <c r="C601" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="602" spans="1:3">
@@ -13212,7 +13200,7 @@
         <v>625</v>
       </c>
       <c r="C602" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="603" spans="1:3">
@@ -13223,7 +13211,7 @@
         <v>626</v>
       </c>
       <c r="C603" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="604" spans="1:3">
@@ -13234,7 +13222,7 @@
         <v>627</v>
       </c>
       <c r="C604" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="605" spans="1:3">
@@ -13245,7 +13233,7 @@
         <v>628</v>
       </c>
       <c r="C605" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="606" spans="1:3">
@@ -13256,7 +13244,7 @@
         <v>629</v>
       </c>
       <c r="C606" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="607" spans="1:3">
@@ -13267,7 +13255,7 @@
         <v>630</v>
       </c>
       <c r="C607" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="608" spans="1:3">
@@ -13278,7 +13266,7 @@
         <v>631</v>
       </c>
       <c r="C608" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="609" spans="1:3">
@@ -13289,7 +13277,7 @@
         <v>632</v>
       </c>
       <c r="C609" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="610" spans="1:3">
@@ -13300,7 +13288,7 @@
         <v>633</v>
       </c>
       <c r="C610" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="611" spans="1:3">
@@ -13311,7 +13299,7 @@
         <v>634</v>
       </c>
       <c r="C611" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="612" spans="1:3">
@@ -13322,7 +13310,7 @@
         <v>635</v>
       </c>
       <c r="C612" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="613" spans="1:3">
@@ -13333,7 +13321,7 @@
         <v>636</v>
       </c>
       <c r="C613" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="614" spans="1:3">
@@ -13344,7 +13332,7 @@
         <v>637</v>
       </c>
       <c r="C614" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="615" spans="1:3">
@@ -13355,7 +13343,7 @@
         <v>638</v>
       </c>
       <c r="C615" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="616" spans="1:3">
@@ -13366,7 +13354,7 @@
         <v>639</v>
       </c>
       <c r="C616" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="617" spans="1:3">
@@ -13377,7 +13365,7 @@
         <v>640</v>
       </c>
       <c r="C617" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="618" spans="1:3">
@@ -13388,7 +13376,7 @@
         <v>641</v>
       </c>
       <c r="C618" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="619" spans="1:3">
@@ -13399,7 +13387,7 @@
         <v>642</v>
       </c>
       <c r="C619" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="620" spans="1:3">
@@ -13410,7 +13398,7 @@
         <v>643</v>
       </c>
       <c r="C620" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="621" spans="1:3">
@@ -13421,7 +13409,7 @@
         <v>644</v>
       </c>
       <c r="C621" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="622" spans="1:3">
@@ -13432,7 +13420,7 @@
         <v>645</v>
       </c>
       <c r="C622" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="623" spans="1:3">
@@ -13443,7 +13431,7 @@
         <v>646</v>
       </c>
       <c r="C623" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="624" spans="1:3">
@@ -13454,7 +13442,7 @@
         <v>647</v>
       </c>
       <c r="C624" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="625" spans="1:3">
@@ -13465,7 +13453,7 @@
         <v>648</v>
       </c>
       <c r="C625" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="626" spans="1:3">
@@ -13476,7 +13464,7 @@
         <v>649</v>
       </c>
       <c r="C626" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="627" spans="1:3">
@@ -13487,7 +13475,7 @@
         <v>650</v>
       </c>
       <c r="C627" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="628" spans="1:3">
@@ -13498,7 +13486,7 @@
         <v>651</v>
       </c>
       <c r="C628" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="629" spans="1:3">
@@ -13509,7 +13497,7 @@
         <v>652</v>
       </c>
       <c r="C629" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="630" spans="1:3">
@@ -13520,7 +13508,7 @@
         <v>653</v>
       </c>
       <c r="C630" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="631" spans="1:3">
@@ -13531,7 +13519,7 @@
         <v>654</v>
       </c>
       <c r="C631" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="632" spans="1:3">
@@ -13542,7 +13530,7 @@
         <v>655</v>
       </c>
       <c r="C632" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="633" spans="1:3">
@@ -13553,7 +13541,7 @@
         <v>656</v>
       </c>
       <c r="C633" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="634" spans="1:3">
@@ -13564,7 +13552,7 @@
         <v>657</v>
       </c>
       <c r="C634" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="635" spans="1:3">
@@ -13575,7 +13563,7 @@
         <v>658</v>
       </c>
       <c r="C635" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="636" spans="1:3">
@@ -13586,7 +13574,7 @@
         <v>659</v>
       </c>
       <c r="C636" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="637" spans="1:3">
@@ -13597,7 +13585,7 @@
         <v>660</v>
       </c>
       <c r="C637" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="638" spans="1:3">
@@ -13608,7 +13596,7 @@
         <v>661</v>
       </c>
       <c r="C638" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="639" spans="1:3">
@@ -13619,7 +13607,7 @@
         <v>662</v>
       </c>
       <c r="C639" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="640" spans="1:3">
@@ -13630,7 +13618,7 @@
         <v>663</v>
       </c>
       <c r="C640" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="641" spans="1:3">
@@ -13641,7 +13629,7 @@
         <v>664</v>
       </c>
       <c r="C641" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="642" spans="1:3">
@@ -13652,7 +13640,7 @@
         <v>665</v>
       </c>
       <c r="C642" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="643" spans="1:3">
@@ -13663,7 +13651,7 @@
         <v>666</v>
       </c>
       <c r="C643" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="644" spans="1:3">
@@ -13674,7 +13662,7 @@
         <v>667</v>
       </c>
       <c r="C644" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="645" spans="1:3">
@@ -13685,7 +13673,7 @@
         <v>668</v>
       </c>
       <c r="C645" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="646" spans="1:3">
@@ -13696,7 +13684,7 @@
         <v>669</v>
       </c>
       <c r="C646" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="647" spans="1:3">
@@ -13707,7 +13695,7 @@
         <v>670</v>
       </c>
       <c r="C647" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="648" spans="1:3">
@@ -13718,7 +13706,7 @@
         <v>671</v>
       </c>
       <c r="C648" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="649" spans="1:3">
@@ -13729,7 +13717,7 @@
         <v>672</v>
       </c>
       <c r="C649" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="650" spans="1:3">
@@ -13740,7 +13728,7 @@
         <v>673</v>
       </c>
       <c r="C650" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="651" spans="1:3">
@@ -13751,7 +13739,7 @@
         <v>674</v>
       </c>
       <c r="C651" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="652" spans="1:3">
@@ -13762,7 +13750,7 @@
         <v>675</v>
       </c>
       <c r="C652" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="653" spans="1:3">
@@ -13773,7 +13761,7 @@
         <v>676</v>
       </c>
       <c r="C653" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="654" spans="1:3">
@@ -13784,7 +13772,7 @@
         <v>677</v>
       </c>
       <c r="C654" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="655" spans="1:3">
@@ -13795,7 +13783,7 @@
         <v>678</v>
       </c>
       <c r="C655" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="656" spans="1:3">
@@ -13806,7 +13794,7 @@
         <v>679</v>
       </c>
       <c r="C656" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="657" spans="1:3">
@@ -13817,7 +13805,7 @@
         <v>680</v>
       </c>
       <c r="C657" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="658" spans="1:3">
@@ -13828,7 +13816,7 @@
         <v>681</v>
       </c>
       <c r="C658" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="659" spans="1:3">
@@ -13839,7 +13827,7 @@
         <v>682</v>
       </c>
       <c r="C659" t="s">
-        <v>1703</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="660" spans="1:3">
@@ -13850,7 +13838,7 @@
         <v>683</v>
       </c>
       <c r="C660" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="661" spans="1:3">
@@ -13861,7 +13849,7 @@
         <v>684</v>
       </c>
       <c r="C661" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="662" spans="1:3">
@@ -13872,7 +13860,7 @@
         <v>685</v>
       </c>
       <c r="C662" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="663" spans="1:3">
@@ -13883,7 +13871,7 @@
         <v>686</v>
       </c>
       <c r="C663" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="664" spans="1:3">
@@ -13894,7 +13882,7 @@
         <v>687</v>
       </c>
       <c r="C664" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="665" spans="1:3">
@@ -13905,7 +13893,7 @@
         <v>688</v>
       </c>
       <c r="C665" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="666" spans="1:3">
@@ -13916,7 +13904,7 @@
         <v>689</v>
       </c>
       <c r="C666" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="667" spans="1:3">
@@ -13927,7 +13915,7 @@
         <v>690</v>
       </c>
       <c r="C667" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="668" spans="1:3">
@@ -13938,7 +13926,7 @@
         <v>691</v>
       </c>
       <c r="C668" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="669" spans="1:3">
@@ -13949,7 +13937,7 @@
         <v>692</v>
       </c>
       <c r="C669" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="670" spans="1:3">
@@ -13960,7 +13948,7 @@
         <v>693</v>
       </c>
       <c r="C670" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="671" spans="1:3">
@@ -13971,7 +13959,7 @@
         <v>694</v>
       </c>
       <c r="C671" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="672" spans="1:3">
@@ -13982,7 +13970,7 @@
         <v>695</v>
       </c>
       <c r="C672" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="673" spans="1:3">
@@ -13993,7 +13981,7 @@
         <v>696</v>
       </c>
       <c r="C673" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="674" spans="1:3">
@@ -14004,7 +13992,7 @@
         <v>697</v>
       </c>
       <c r="C674" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="675" spans="1:3">
@@ -14015,7 +14003,7 @@
         <v>698</v>
       </c>
       <c r="C675" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="676" spans="1:3">
@@ -14026,7 +14014,7 @@
         <v>699</v>
       </c>
       <c r="C676" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="677" spans="1:3">
@@ -14037,7 +14025,7 @@
         <v>700</v>
       </c>
       <c r="C677" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="678" spans="1:3">
@@ -14048,7 +14036,7 @@
         <v>701</v>
       </c>
       <c r="C678" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="679" spans="1:3">
@@ -14059,7 +14047,7 @@
         <v>702</v>
       </c>
       <c r="C679" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="680" spans="1:3">
@@ -14070,7 +14058,7 @@
         <v>703</v>
       </c>
       <c r="C680" t="s">
-        <v>1723</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="681" spans="1:3">
@@ -14081,7 +14069,7 @@
         <v>704</v>
       </c>
       <c r="C681" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="682" spans="1:3">
@@ -14092,7 +14080,7 @@
         <v>705</v>
       </c>
       <c r="C682" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="683" spans="1:3">
@@ -14103,7 +14091,7 @@
         <v>706</v>
       </c>
       <c r="C683" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="684" spans="1:3">
@@ -14114,7 +14102,7 @@
         <v>707</v>
       </c>
       <c r="C684" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="685" spans="1:3">
@@ -14125,7 +14113,7 @@
         <v>708</v>
       </c>
       <c r="C685" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="686" spans="1:3">
@@ -14136,7 +14124,7 @@
         <v>709</v>
       </c>
       <c r="C686" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="687" spans="1:3">
@@ -14147,7 +14135,7 @@
         <v>710</v>
       </c>
       <c r="C687" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="688" spans="1:3">
@@ -14158,7 +14146,7 @@
         <v>711</v>
       </c>
       <c r="C688" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="689" spans="1:3">
@@ -14169,7 +14157,7 @@
         <v>712</v>
       </c>
       <c r="C689" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="690" spans="1:3">
@@ -14180,7 +14168,7 @@
         <v>713</v>
       </c>
       <c r="C690" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="691" spans="1:3">
@@ -14191,7 +14179,7 @@
         <v>714</v>
       </c>
       <c r="C691" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="692" spans="1:3">
@@ -14202,7 +14190,7 @@
         <v>715</v>
       </c>
       <c r="C692" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="693" spans="1:3">
@@ -14213,7 +14201,7 @@
         <v>716</v>
       </c>
       <c r="C693" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="694" spans="1:3">
@@ -14224,7 +14212,7 @@
         <v>717</v>
       </c>
       <c r="C694" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="695" spans="1:3">
@@ -14235,7 +14223,7 @@
         <v>718</v>
       </c>
       <c r="C695" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="696" spans="1:3">
@@ -14246,7 +14234,7 @@
         <v>719</v>
       </c>
       <c r="C696" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="697" spans="1:3">
@@ -14257,7 +14245,7 @@
         <v>720</v>
       </c>
       <c r="C697" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="698" spans="1:3">
@@ -14268,7 +14256,7 @@
         <v>721</v>
       </c>
       <c r="C698" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="699" spans="1:3">
@@ -14279,7 +14267,7 @@
         <v>722</v>
       </c>
       <c r="C699" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="700" spans="1:3">
@@ -14290,7 +14278,7 @@
         <v>723</v>
       </c>
       <c r="C700" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="701" spans="1:3">
@@ -14301,7 +14289,7 @@
         <v>724</v>
       </c>
       <c r="C701" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="702" spans="1:3">
@@ -14312,7 +14300,7 @@
         <v>725</v>
       </c>
       <c r="C702" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="703" spans="1:3">
@@ -14323,7 +14311,7 @@
         <v>726</v>
       </c>
       <c r="C703" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="704" spans="1:3">
@@ -14334,7 +14322,7 @@
         <v>727</v>
       </c>
       <c r="C704" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="705" spans="1:3">
@@ -14345,7 +14333,7 @@
         <v>728</v>
       </c>
       <c r="C705" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="706" spans="1:3">
@@ -14356,7 +14344,7 @@
         <v>729</v>
       </c>
       <c r="C706" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="707" spans="1:3">
@@ -14367,7 +14355,7 @@
         <v>730</v>
       </c>
       <c r="C707" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="708" spans="1:3">
@@ -14378,7 +14366,7 @@
         <v>731</v>
       </c>
       <c r="C708" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="709" spans="1:3">
@@ -14389,7 +14377,7 @@
         <v>732</v>
       </c>
       <c r="C709" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="710" spans="1:3">
@@ -14400,7 +14388,7 @@
         <v>733</v>
       </c>
       <c r="C710" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="711" spans="1:3">
@@ -14411,7 +14399,7 @@
         <v>734</v>
       </c>
       <c r="C711" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="712" spans="1:3">
@@ -14422,7 +14410,7 @@
         <v>735</v>
       </c>
       <c r="C712" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="713" spans="1:3">
@@ -14433,7 +14421,7 @@
         <v>736</v>
       </c>
       <c r="C713" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="714" spans="1:3">
@@ -14444,7 +14432,7 @@
         <v>737</v>
       </c>
       <c r="C714" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="715" spans="1:3">
@@ -14455,7 +14443,7 @@
         <v>738</v>
       </c>
       <c r="C715" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="716" spans="1:3">
@@ -14466,7 +14454,7 @@
         <v>739</v>
       </c>
       <c r="C716" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="717" spans="1:3">
@@ -14477,7 +14465,7 @@
         <v>740</v>
       </c>
       <c r="C717" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="718" spans="1:3">
@@ -14488,7 +14476,7 @@
         <v>741</v>
       </c>
       <c r="C718" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="719" spans="1:3">
@@ -14499,7 +14487,7 @@
         <v>742</v>
       </c>
       <c r="C719" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="720" spans="1:3">
@@ -14510,7 +14498,7 @@
         <v>743</v>
       </c>
       <c r="C720" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="721" spans="1:3">
@@ -14521,7 +14509,7 @@
         <v>744</v>
       </c>
       <c r="C721" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="722" spans="1:3">
@@ -14532,7 +14520,7 @@
         <v>745</v>
       </c>
       <c r="C722" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="723" spans="1:3">
@@ -14543,7 +14531,7 @@
         <v>746</v>
       </c>
       <c r="C723" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="724" spans="1:3">
@@ -14554,7 +14542,7 @@
         <v>747</v>
       </c>
       <c r="C724" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="725" spans="1:3">
@@ -14565,7 +14553,7 @@
         <v>748</v>
       </c>
       <c r="C725" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="726" spans="1:3">
@@ -14576,7 +14564,7 @@
         <v>749</v>
       </c>
       <c r="C726" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="727" spans="1:3">
@@ -14587,7 +14575,7 @@
         <v>750</v>
       </c>
       <c r="C727" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="728" spans="1:3">
@@ -14598,7 +14586,7 @@
         <v>751</v>
       </c>
       <c r="C728" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="729" spans="1:3">
@@ -14609,7 +14597,7 @@
         <v>752</v>
       </c>
       <c r="C729" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="730" spans="1:3">
@@ -14620,7 +14608,7 @@
         <v>753</v>
       </c>
       <c r="C730" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="731" spans="1:3">
@@ -14631,7 +14619,7 @@
         <v>754</v>
       </c>
       <c r="C731" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="732" spans="1:3">
@@ -14642,7 +14630,7 @@
         <v>755</v>
       </c>
       <c r="C732" t="s">
-        <v>1775</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="733" spans="1:3">
@@ -14653,7 +14641,7 @@
         <v>756</v>
       </c>
       <c r="C733" t="s">
-        <v>1776</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="734" spans="1:3">
@@ -14664,7 +14652,7 @@
         <v>757</v>
       </c>
       <c r="C734" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="735" spans="1:3">
@@ -14675,7 +14663,7 @@
         <v>758</v>
       </c>
       <c r="C735" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="736" spans="1:3">
@@ -14686,7 +14674,7 @@
         <v>759</v>
       </c>
       <c r="C736" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="737" spans="1:3">
@@ -14697,7 +14685,7 @@
         <v>760</v>
       </c>
       <c r="C737" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="738" spans="1:3">
@@ -14708,7 +14696,7 @@
         <v>761</v>
       </c>
       <c r="C738" t="s">
-        <v>1781</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="739" spans="1:3">
@@ -14719,7 +14707,7 @@
         <v>762</v>
       </c>
       <c r="C739" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="740" spans="1:3">
@@ -14730,7 +14718,7 @@
         <v>763</v>
       </c>
       <c r="C740" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="741" spans="1:3">
@@ -14741,7 +14729,7 @@
         <v>764</v>
       </c>
       <c r="C741" t="s">
-        <v>1784</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="742" spans="1:3">
@@ -14752,7 +14740,7 @@
         <v>765</v>
       </c>
       <c r="C742" t="s">
-        <v>1785</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="743" spans="1:3">
@@ -14763,7 +14751,7 @@
         <v>766</v>
       </c>
       <c r="C743" t="s">
-        <v>1786</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="744" spans="1:3">
@@ -14774,7 +14762,7 @@
         <v>767</v>
       </c>
       <c r="C744" t="s">
-        <v>1787</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="745" spans="1:3">
@@ -14785,7 +14773,7 @@
         <v>768</v>
       </c>
       <c r="C745" t="s">
-        <v>1788</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="746" spans="1:3">
@@ -14796,7 +14784,7 @@
         <v>769</v>
       </c>
       <c r="C746" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="747" spans="1:3">
@@ -14807,7 +14795,7 @@
         <v>770</v>
       </c>
       <c r="C747" t="s">
-        <v>1790</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="748" spans="1:3">
@@ -14818,7 +14806,7 @@
         <v>771</v>
       </c>
       <c r="C748" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="749" spans="1:3">
@@ -14829,7 +14817,7 @@
         <v>772</v>
       </c>
       <c r="C749" t="s">
-        <v>1792</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="750" spans="1:3">
@@ -14840,7 +14828,7 @@
         <v>773</v>
       </c>
       <c r="C750" t="s">
-        <v>1793</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="751" spans="1:3">
@@ -14851,7 +14839,7 @@
         <v>774</v>
       </c>
       <c r="C751" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="752" spans="1:3">
@@ -14862,7 +14850,7 @@
         <v>775</v>
       </c>
       <c r="C752" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="753" spans="1:3">
@@ -14873,7 +14861,7 @@
         <v>776</v>
       </c>
       <c r="C753" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="754" spans="1:3">
@@ -14884,7 +14872,7 @@
         <v>777</v>
       </c>
       <c r="C754" t="s">
-        <v>1797</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="755" spans="1:3">
@@ -14895,7 +14883,7 @@
         <v>778</v>
       </c>
       <c r="C755" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="756" spans="1:3">
@@ -14906,7 +14894,7 @@
         <v>779</v>
       </c>
       <c r="C756" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="757" spans="1:3">
@@ -14917,7 +14905,7 @@
         <v>780</v>
       </c>
       <c r="C757" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="758" spans="1:3">
@@ -14928,7 +14916,7 @@
         <v>781</v>
       </c>
       <c r="C758" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="759" spans="1:3">
@@ -14939,7 +14927,7 @@
         <v>782</v>
       </c>
       <c r="C759" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="760" spans="1:3">
@@ -14950,7 +14938,7 @@
         <v>783</v>
       </c>
       <c r="C760" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="761" spans="1:3">
@@ -14961,7 +14949,7 @@
         <v>784</v>
       </c>
       <c r="C761" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="762" spans="1:3">
@@ -14972,7 +14960,7 @@
         <v>785</v>
       </c>
       <c r="C762" t="s">
-        <v>1805</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="763" spans="1:3">
@@ -14983,7 +14971,7 @@
         <v>786</v>
       </c>
       <c r="C763" t="s">
-        <v>1806</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="764" spans="1:3">
@@ -14994,7 +14982,7 @@
         <v>787</v>
       </c>
       <c r="C764" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="765" spans="1:3">
@@ -15005,7 +14993,7 @@
         <v>788</v>
       </c>
       <c r="C765" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="766" spans="1:3">
@@ -15016,7 +15004,7 @@
         <v>789</v>
       </c>
       <c r="C766" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="767" spans="1:3">
@@ -15027,7 +15015,7 @@
         <v>790</v>
       </c>
       <c r="C767" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="768" spans="1:3">
@@ -15038,7 +15026,7 @@
         <v>791</v>
       </c>
       <c r="C768" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="769" spans="1:3">
@@ -15049,7 +15037,7 @@
         <v>792</v>
       </c>
       <c r="C769" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="770" spans="1:3">
@@ -15060,7 +15048,7 @@
         <v>793</v>
       </c>
       <c r="C770" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="771" spans="1:3">
@@ -15071,7 +15059,7 @@
         <v>794</v>
       </c>
       <c r="C771" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="772" spans="1:3">
@@ -15082,7 +15070,7 @@
         <v>795</v>
       </c>
       <c r="C772" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="773" spans="1:3">
@@ -15093,7 +15081,7 @@
         <v>796</v>
       </c>
       <c r="C773" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="774" spans="1:3">
@@ -15104,7 +15092,7 @@
         <v>797</v>
       </c>
       <c r="C774" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="775" spans="1:3">
@@ -15115,7 +15103,7 @@
         <v>798</v>
       </c>
       <c r="C775" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="776" spans="1:3">
@@ -15126,7 +15114,7 @@
         <v>799</v>
       </c>
       <c r="C776" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="777" spans="1:3">
@@ -15137,7 +15125,7 @@
         <v>800</v>
       </c>
       <c r="C777" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="778" spans="1:3">
@@ -15148,7 +15136,7 @@
         <v>801</v>
       </c>
       <c r="C778" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="779" spans="1:3">
@@ -15159,7 +15147,7 @@
         <v>802</v>
       </c>
       <c r="C779" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="780" spans="1:3">
@@ -15170,7 +15158,7 @@
         <v>803</v>
       </c>
       <c r="C780" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="781" spans="1:3">
@@ -15181,7 +15169,7 @@
         <v>804</v>
       </c>
       <c r="C781" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="782" spans="1:3">
@@ -15192,7 +15180,7 @@
         <v>805</v>
       </c>
       <c r="C782" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="783" spans="1:3">
@@ -15203,7 +15191,7 @@
         <v>806</v>
       </c>
       <c r="C783" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="784" spans="1:3">
@@ -15214,7 +15202,7 @@
         <v>807</v>
       </c>
       <c r="C784" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="785" spans="1:3">
@@ -15225,7 +15213,7 @@
         <v>808</v>
       </c>
       <c r="C785" t="s">
-        <v>1827</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="786" spans="1:3">
@@ -15236,7 +15224,7 @@
         <v>809</v>
       </c>
       <c r="C786" t="s">
-        <v>1828</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="787" spans="1:3">
@@ -15247,7 +15235,7 @@
         <v>810</v>
       </c>
       <c r="C787" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="788" spans="1:3">
@@ -15258,7 +15246,7 @@
         <v>811</v>
       </c>
       <c r="C788" t="s">
-        <v>1830</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="789" spans="1:3">
@@ -15269,7 +15257,7 @@
         <v>812</v>
       </c>
       <c r="C789" t="s">
-        <v>1831</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="790" spans="1:3">
@@ -15280,7 +15268,7 @@
         <v>813</v>
       </c>
       <c r="C790" t="s">
-        <v>1832</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="791" spans="1:3">
@@ -15291,7 +15279,7 @@
         <v>814</v>
       </c>
       <c r="C791" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="792" spans="1:3">
@@ -15302,7 +15290,7 @@
         <v>815</v>
       </c>
       <c r="C792" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="793" spans="1:3">
@@ -15313,7 +15301,7 @@
         <v>816</v>
       </c>
       <c r="C793" t="s">
-        <v>1835</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="794" spans="1:3">
@@ -15324,7 +15312,7 @@
         <v>817</v>
       </c>
       <c r="C794" t="s">
-        <v>1836</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="795" spans="1:3">
@@ -15335,7 +15323,7 @@
         <v>818</v>
       </c>
       <c r="C795" t="s">
-        <v>1837</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="796" spans="1:3">
@@ -15346,7 +15334,7 @@
         <v>819</v>
       </c>
       <c r="C796" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="797" spans="1:3">
@@ -15357,7 +15345,7 @@
         <v>820</v>
       </c>
       <c r="C797" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="798" spans="1:3">
@@ -15368,7 +15356,7 @@
         <v>821</v>
       </c>
       <c r="C798" t="s">
-        <v>1840</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="799" spans="1:3">
@@ -15379,7 +15367,7 @@
         <v>822</v>
       </c>
       <c r="C799" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="800" spans="1:3">
@@ -15390,7 +15378,7 @@
         <v>823</v>
       </c>
       <c r="C800" t="s">
-        <v>1842</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="801" spans="1:3">
@@ -15401,7 +15389,7 @@
         <v>824</v>
       </c>
       <c r="C801" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="802" spans="1:3">
@@ -15412,7 +15400,7 @@
         <v>825</v>
       </c>
       <c r="C802" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="803" spans="1:3">
@@ -15423,7 +15411,7 @@
         <v>826</v>
       </c>
       <c r="C803" t="s">
-        <v>1845</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="804" spans="1:3">
@@ -15434,7 +15422,7 @@
         <v>827</v>
       </c>
       <c r="C804" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="805" spans="1:3">
@@ -15445,7 +15433,7 @@
         <v>828</v>
       </c>
       <c r="C805" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="806" spans="1:3">
@@ -15456,7 +15444,7 @@
         <v>829</v>
       </c>
       <c r="C806" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="807" spans="1:3">
@@ -15467,7 +15455,7 @@
         <v>830</v>
       </c>
       <c r="C807" t="s">
-        <v>1849</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="808" spans="1:3">
@@ -15478,7 +15466,7 @@
         <v>831</v>
       </c>
       <c r="C808" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="809" spans="1:3">
@@ -15489,7 +15477,7 @@
         <v>832</v>
       </c>
       <c r="C809" t="s">
-        <v>1851</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="810" spans="1:3">
@@ -15500,7 +15488,7 @@
         <v>833</v>
       </c>
       <c r="C810" t="s">
-        <v>1852</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="811" spans="1:3">
@@ -15511,7 +15499,7 @@
         <v>834</v>
       </c>
       <c r="C811" t="s">
-        <v>1853</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="812" spans="1:3">
@@ -15522,7 +15510,7 @@
         <v>835</v>
       </c>
       <c r="C812" t="s">
-        <v>1854</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="813" spans="1:3">
@@ -15533,7 +15521,7 @@
         <v>836</v>
       </c>
       <c r="C813" t="s">
-        <v>1855</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="814" spans="1:3">
@@ -15544,7 +15532,7 @@
         <v>837</v>
       </c>
       <c r="C814" t="s">
-        <v>1856</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="815" spans="1:3">
@@ -15555,7 +15543,7 @@
         <v>838</v>
       </c>
       <c r="C815" t="s">
-        <v>1857</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="816" spans="1:3">
@@ -15566,7 +15554,7 @@
         <v>839</v>
       </c>
       <c r="C816" t="s">
-        <v>1858</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="817" spans="1:3">
@@ -15577,7 +15565,7 @@
         <v>840</v>
       </c>
       <c r="C817" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="818" spans="1:3">
@@ -15588,7 +15576,7 @@
         <v>841</v>
       </c>
       <c r="C818" t="s">
-        <v>1860</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="819" spans="1:3">
@@ -15599,7 +15587,7 @@
         <v>842</v>
       </c>
       <c r="C819" t="s">
-        <v>1861</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="820" spans="1:3">
@@ -15610,7 +15598,7 @@
         <v>843</v>
       </c>
       <c r="C820" t="s">
-        <v>1862</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="821" spans="1:3">
@@ -15621,7 +15609,7 @@
         <v>844</v>
       </c>
       <c r="C821" t="s">
-        <v>1863</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="822" spans="1:3">
@@ -15632,7 +15620,7 @@
         <v>845</v>
       </c>
       <c r="C822" t="s">
-        <v>1864</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="823" spans="1:3">
@@ -15643,7 +15631,7 @@
         <v>846</v>
       </c>
       <c r="C823" t="s">
-        <v>1865</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="824" spans="1:3">
@@ -15654,7 +15642,7 @@
         <v>847</v>
       </c>
       <c r="C824" t="s">
-        <v>1866</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="825" spans="1:3">
@@ -15665,7 +15653,7 @@
         <v>848</v>
       </c>
       <c r="C825" t="s">
-        <v>1867</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="826" spans="1:3">
@@ -15676,7 +15664,7 @@
         <v>849</v>
       </c>
       <c r="C826" t="s">
-        <v>1868</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="827" spans="1:3">
@@ -15687,7 +15675,7 @@
         <v>850</v>
       </c>
       <c r="C827" t="s">
-        <v>1869</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="828" spans="1:3">
@@ -15698,7 +15686,7 @@
         <v>851</v>
       </c>
       <c r="C828" t="s">
-        <v>1870</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="829" spans="1:3">
@@ -15709,7 +15697,7 @@
         <v>852</v>
       </c>
       <c r="C829" t="s">
-        <v>1871</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="830" spans="1:3">
@@ -15720,7 +15708,7 @@
         <v>853</v>
       </c>
       <c r="C830" t="s">
-        <v>1872</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="831" spans="1:3">
@@ -15731,7 +15719,7 @@
         <v>854</v>
       </c>
       <c r="C831" t="s">
-        <v>1873</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="832" spans="1:3">
@@ -15742,7 +15730,7 @@
         <v>855</v>
       </c>
       <c r="C832" t="s">
-        <v>1874</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="833" spans="1:3">
@@ -15753,7 +15741,7 @@
         <v>856</v>
       </c>
       <c r="C833" t="s">
-        <v>1875</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="834" spans="1:3">
@@ -15764,7 +15752,7 @@
         <v>857</v>
       </c>
       <c r="C834" t="s">
-        <v>1876</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="835" spans="1:3">
@@ -15775,7 +15763,7 @@
         <v>858</v>
       </c>
       <c r="C835" t="s">
-        <v>1877</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="836" spans="1:3">
@@ -15786,7 +15774,7 @@
         <v>859</v>
       </c>
       <c r="C836" t="s">
-        <v>1878</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="837" spans="1:3">
@@ -15797,7 +15785,7 @@
         <v>860</v>
       </c>
       <c r="C837" t="s">
-        <v>1879</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="838" spans="1:3">
@@ -15808,7 +15796,7 @@
         <v>861</v>
       </c>
       <c r="C838" t="s">
-        <v>1880</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="839" spans="1:3">
@@ -15819,7 +15807,7 @@
         <v>862</v>
       </c>
       <c r="C839" t="s">
-        <v>1881</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="840" spans="1:3">
@@ -15830,7 +15818,7 @@
         <v>863</v>
       </c>
       <c r="C840" t="s">
-        <v>1882</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="841" spans="1:3">
@@ -15841,7 +15829,7 @@
         <v>864</v>
       </c>
       <c r="C841" t="s">
-        <v>1883</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="842" spans="1:3">
@@ -15852,7 +15840,7 @@
         <v>865</v>
       </c>
       <c r="C842" t="s">
-        <v>1884</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="843" spans="1:3">
@@ -15863,7 +15851,7 @@
         <v>866</v>
       </c>
       <c r="C843" t="s">
-        <v>1885</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="844" spans="1:3">
@@ -15874,7 +15862,7 @@
         <v>867</v>
       </c>
       <c r="C844" t="s">
-        <v>1886</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="845" spans="1:3">
@@ -15885,7 +15873,7 @@
         <v>868</v>
       </c>
       <c r="C845" t="s">
-        <v>1887</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="846" spans="1:3">
@@ -15896,7 +15884,7 @@
         <v>869</v>
       </c>
       <c r="C846" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="847" spans="1:3">
@@ -15907,7 +15895,7 @@
         <v>870</v>
       </c>
       <c r="C847" t="s">
-        <v>1889</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="848" spans="1:3">
@@ -15918,7 +15906,7 @@
         <v>871</v>
       </c>
       <c r="C848" t="s">
-        <v>1890</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="849" spans="1:3">
@@ -15929,7 +15917,7 @@
         <v>872</v>
       </c>
       <c r="C849" t="s">
-        <v>1891</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="850" spans="1:3">
@@ -15940,7 +15928,7 @@
         <v>873</v>
       </c>
       <c r="C850" t="s">
-        <v>1892</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="851" spans="1:3">
@@ -15951,7 +15939,7 @@
         <v>874</v>
       </c>
       <c r="C851" t="s">
-        <v>1893</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="852" spans="1:3">
@@ -15962,7 +15950,7 @@
         <v>875</v>
       </c>
       <c r="C852" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="853" spans="1:3">
@@ -15973,7 +15961,7 @@
         <v>876</v>
       </c>
       <c r="C853" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="854" spans="1:3">
@@ -15984,7 +15972,7 @@
         <v>877</v>
       </c>
       <c r="C854" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="855" spans="1:3">
@@ -15995,7 +15983,7 @@
         <v>878</v>
       </c>
       <c r="C855" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="856" spans="1:3">
@@ -16006,7 +15994,7 @@
         <v>879</v>
       </c>
       <c r="C856" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="857" spans="1:3">
@@ -16017,7 +16005,7 @@
         <v>880</v>
       </c>
       <c r="C857" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="858" spans="1:3">
@@ -16028,7 +16016,7 @@
         <v>881</v>
       </c>
       <c r="C858" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="859" spans="1:3">
@@ -16039,7 +16027,7 @@
         <v>882</v>
       </c>
       <c r="C859" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="860" spans="1:3">
@@ -16050,7 +16038,7 @@
         <v>883</v>
       </c>
       <c r="C860" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="861" spans="1:3">
@@ -16061,7 +16049,7 @@
         <v>884</v>
       </c>
       <c r="C861" t="s">
-        <v>1903</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="862" spans="1:3">
@@ -16072,7 +16060,7 @@
         <v>885</v>
       </c>
       <c r="C862" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="863" spans="1:3">
@@ -16083,7 +16071,7 @@
         <v>886</v>
       </c>
       <c r="C863" t="s">
-        <v>1905</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="864" spans="1:3">
@@ -16094,7 +16082,7 @@
         <v>887</v>
       </c>
       <c r="C864" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="865" spans="1:3">
@@ -16105,7 +16093,7 @@
         <v>888</v>
       </c>
       <c r="C865" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="866" spans="1:3">
@@ -16116,7 +16104,7 @@
         <v>889</v>
       </c>
       <c r="C866" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="867" spans="1:3">
@@ -16127,7 +16115,7 @@
         <v>890</v>
       </c>
       <c r="C867" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="868" spans="1:3">
@@ -16138,7 +16126,7 @@
         <v>891</v>
       </c>
       <c r="C868" t="s">
-        <v>1910</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="869" spans="1:3">
@@ -16149,7 +16137,7 @@
         <v>892</v>
       </c>
       <c r="C869" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="870" spans="1:3">
@@ -16160,7 +16148,7 @@
         <v>893</v>
       </c>
       <c r="C870" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="871" spans="1:3">
@@ -16171,7 +16159,7 @@
         <v>894</v>
       </c>
       <c r="C871" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="872" spans="1:3">
@@ -16182,7 +16170,7 @@
         <v>895</v>
       </c>
       <c r="C872" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="873" spans="1:3">
@@ -16193,7 +16181,7 @@
         <v>896</v>
       </c>
       <c r="C873" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="874" spans="1:3">
@@ -16204,7 +16192,7 @@
         <v>897</v>
       </c>
       <c r="C874" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="875" spans="1:3">
@@ -16215,7 +16203,7 @@
         <v>898</v>
       </c>
       <c r="C875" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="876" spans="1:3">
@@ -16226,7 +16214,7 @@
         <v>899</v>
       </c>
       <c r="C876" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="877" spans="1:3">
@@ -16237,7 +16225,7 @@
         <v>900</v>
       </c>
       <c r="C877" t="s">
-        <v>1919</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="878" spans="1:3">
@@ -16248,7 +16236,7 @@
         <v>901</v>
       </c>
       <c r="C878" t="s">
-        <v>1920</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="879" spans="1:3">
@@ -16259,7 +16247,7 @@
         <v>902</v>
       </c>
       <c r="C879" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="880" spans="1:3">
@@ -16270,7 +16258,7 @@
         <v>903</v>
       </c>
       <c r="C880" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="881" spans="1:3">
@@ -16281,7 +16269,7 @@
         <v>904</v>
       </c>
       <c r="C881" t="s">
-        <v>1923</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="882" spans="1:3">
@@ -16292,7 +16280,7 @@
         <v>905</v>
       </c>
       <c r="C882" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="883" spans="1:3">
@@ -16303,7 +16291,7 @@
         <v>906</v>
       </c>
       <c r="C883" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="884" spans="1:3">
@@ -16314,7 +16302,7 @@
         <v>907</v>
       </c>
       <c r="C884" t="s">
-        <v>1926</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="885" spans="1:3">
@@ -16325,7 +16313,7 @@
         <v>908</v>
       </c>
       <c r="C885" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="886" spans="1:3">
@@ -16336,7 +16324,7 @@
         <v>909</v>
       </c>
       <c r="C886" t="s">
-        <v>1928</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="887" spans="1:3">
@@ -16347,7 +16335,7 @@
         <v>910</v>
       </c>
       <c r="C887" t="s">
-        <v>1929</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="888" spans="1:3">
@@ -16358,7 +16346,7 @@
         <v>911</v>
       </c>
       <c r="C888" t="s">
-        <v>1930</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="889" spans="1:3">
@@ -16369,7 +16357,7 @@
         <v>912</v>
       </c>
       <c r="C889" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="890" spans="1:3">
@@ -16380,7 +16368,7 @@
         <v>913</v>
       </c>
       <c r="C890" t="s">
-        <v>1932</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="891" spans="1:3">
@@ -16391,7 +16379,7 @@
         <v>914</v>
       </c>
       <c r="C891" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="892" spans="1:3">
@@ -16402,7 +16390,7 @@
         <v>915</v>
       </c>
       <c r="C892" t="s">
-        <v>1934</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="893" spans="1:3">
@@ -16413,7 +16401,7 @@
         <v>916</v>
       </c>
       <c r="C893" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="894" spans="1:3">
@@ -16424,7 +16412,7 @@
         <v>917</v>
       </c>
       <c r="C894" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="895" spans="1:3">
@@ -16435,7 +16423,7 @@
         <v>918</v>
       </c>
       <c r="C895" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="896" spans="1:3">
@@ -16446,7 +16434,7 @@
         <v>919</v>
       </c>
       <c r="C896" t="s">
-        <v>1938</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="897" spans="1:3">
@@ -16457,7 +16445,7 @@
         <v>920</v>
       </c>
       <c r="C897" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="898" spans="1:3">
@@ -16468,7 +16456,7 @@
         <v>921</v>
       </c>
       <c r="C898" t="s">
-        <v>1940</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="899" spans="1:3">
@@ -16479,7 +16467,7 @@
         <v>922</v>
       </c>
       <c r="C899" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="900" spans="1:3">
@@ -16490,7 +16478,7 @@
         <v>923</v>
       </c>
       <c r="C900" t="s">
-        <v>1942</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="901" spans="1:3">
@@ -16501,7 +16489,7 @@
         <v>924</v>
       </c>
       <c r="C901" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="902" spans="1:3">
@@ -16512,7 +16500,7 @@
         <v>925</v>
       </c>
       <c r="C902" t="s">
-        <v>1944</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="903" spans="1:3">
@@ -16523,7 +16511,7 @@
         <v>926</v>
       </c>
       <c r="C903" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="904" spans="1:3">
@@ -16534,7 +16522,7 @@
         <v>927</v>
       </c>
       <c r="C904" t="s">
-        <v>1946</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="905" spans="1:3">
@@ -16545,7 +16533,7 @@
         <v>928</v>
       </c>
       <c r="C905" t="s">
-        <v>1947</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="906" spans="1:3">
@@ -16556,7 +16544,7 @@
         <v>929</v>
       </c>
       <c r="C906" t="s">
-        <v>1948</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="907" spans="1:3">
@@ -16567,7 +16555,7 @@
         <v>930</v>
       </c>
       <c r="C907" t="s">
-        <v>1949</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="908" spans="1:3">
@@ -16578,7 +16566,7 @@
         <v>931</v>
       </c>
       <c r="C908" t="s">
-        <v>1950</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="909" spans="1:3">
@@ -16589,7 +16577,7 @@
         <v>932</v>
       </c>
       <c r="C909" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="910" spans="1:3">
@@ -16600,7 +16588,7 @@
         <v>933</v>
       </c>
       <c r="C910" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="911" spans="1:3">
@@ -16611,7 +16599,7 @@
         <v>934</v>
       </c>
       <c r="C911" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="912" spans="1:3">
@@ -16622,7 +16610,7 @@
         <v>935</v>
       </c>
       <c r="C912" t="s">
-        <v>1954</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="913" spans="1:3">
@@ -16633,7 +16621,7 @@
         <v>936</v>
       </c>
       <c r="C913" t="s">
-        <v>1955</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="914" spans="1:3">
@@ -16644,7 +16632,7 @@
         <v>937</v>
       </c>
       <c r="C914" t="s">
-        <v>1956</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="915" spans="1:3">
@@ -16655,7 +16643,7 @@
         <v>938</v>
       </c>
       <c r="C915" t="s">
-        <v>1957</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="916" spans="1:3">
@@ -16666,7 +16654,7 @@
         <v>939</v>
       </c>
       <c r="C916" t="s">
-        <v>1958</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="917" spans="1:3">
@@ -16677,7 +16665,7 @@
         <v>940</v>
       </c>
       <c r="C917" t="s">
-        <v>1959</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="918" spans="1:3">
@@ -16688,7 +16676,7 @@
         <v>941</v>
       </c>
       <c r="C918" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="919" spans="1:3">
@@ -16699,7 +16687,7 @@
         <v>942</v>
       </c>
       <c r="C919" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="920" spans="1:3">
@@ -16710,7 +16698,7 @@
         <v>943</v>
       </c>
       <c r="C920" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="921" spans="1:3">
@@ -16721,7 +16709,7 @@
         <v>944</v>
       </c>
       <c r="C921" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="922" spans="1:3">
@@ -16732,7 +16720,7 @@
         <v>945</v>
       </c>
       <c r="C922" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="923" spans="1:3">
@@ -16743,7 +16731,7 @@
         <v>946</v>
       </c>
       <c r="C923" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="924" spans="1:3">
@@ -16754,7 +16742,7 @@
         <v>947</v>
       </c>
       <c r="C924" t="s">
-        <v>1966</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="925" spans="1:3">
@@ -16765,7 +16753,7 @@
         <v>948</v>
       </c>
       <c r="C925" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="926" spans="1:3">
@@ -16776,7 +16764,7 @@
         <v>949</v>
       </c>
       <c r="C926" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="927" spans="1:3">
@@ -16787,7 +16775,7 @@
         <v>950</v>
       </c>
       <c r="C927" t="s">
-        <v>1969</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="928" spans="1:3">
@@ -16798,7 +16786,7 @@
         <v>951</v>
       </c>
       <c r="C928" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="929" spans="1:3">
@@ -16809,7 +16797,7 @@
         <v>952</v>
       </c>
       <c r="C929" t="s">
-        <v>1971</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="930" spans="1:3">
@@ -16820,7 +16808,7 @@
         <v>953</v>
       </c>
       <c r="C930" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="931" spans="1:3">
@@ -16831,7 +16819,7 @@
         <v>954</v>
       </c>
       <c r="C931" t="s">
-        <v>1973</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="932" spans="1:3">
@@ -16842,29 +16830,29 @@
         <v>955</v>
       </c>
       <c r="C932" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="933" spans="1:3">
       <c r="A933" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B933" t="s">
         <v>956</v>
       </c>
       <c r="C933" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="934" spans="1:3">
       <c r="A934" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B934" t="s">
         <v>957</v>
       </c>
       <c r="C934" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="935" spans="1:3">
@@ -16875,7 +16863,7 @@
         <v>958</v>
       </c>
       <c r="C935" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="936" spans="1:3">
@@ -16886,7 +16874,7 @@
         <v>959</v>
       </c>
       <c r="C936" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="937" spans="1:3">
@@ -16897,7 +16885,7 @@
         <v>960</v>
       </c>
       <c r="C937" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="938" spans="1:3">
@@ -16908,7 +16896,7 @@
         <v>961</v>
       </c>
       <c r="C938" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="939" spans="1:3">
@@ -16919,7 +16907,7 @@
         <v>962</v>
       </c>
       <c r="C939" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="940" spans="1:3">
@@ -16930,7 +16918,7 @@
         <v>963</v>
       </c>
       <c r="C940" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="941" spans="1:3">
@@ -16941,7 +16929,7 @@
         <v>964</v>
       </c>
       <c r="C941" t="s">
-        <v>1983</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="942" spans="1:3">
@@ -16952,7 +16940,7 @@
         <v>965</v>
       </c>
       <c r="C942" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="943" spans="1:3">
@@ -16963,7 +16951,7 @@
         <v>966</v>
       </c>
       <c r="C943" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="944" spans="1:3">
@@ -16974,7 +16962,7 @@
         <v>967</v>
       </c>
       <c r="C944" t="s">
-        <v>1986</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="945" spans="1:3">
@@ -16985,7 +16973,7 @@
         <v>968</v>
       </c>
       <c r="C945" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="946" spans="1:3">
@@ -16996,7 +16984,7 @@
         <v>969</v>
       </c>
       <c r="C946" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="947" spans="1:3">
@@ -17007,7 +16995,7 @@
         <v>970</v>
       </c>
       <c r="C947" t="s">
-        <v>1989</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="948" spans="1:3">
@@ -17018,7 +17006,7 @@
         <v>971</v>
       </c>
       <c r="C948" t="s">
-        <v>1990</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="949" spans="1:3">
@@ -17029,7 +17017,7 @@
         <v>972</v>
       </c>
       <c r="C949" t="s">
-        <v>1991</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="950" spans="1:3">
@@ -17040,7 +17028,7 @@
         <v>973</v>
       </c>
       <c r="C950" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="951" spans="1:3">
@@ -17051,7 +17039,7 @@
         <v>974</v>
       </c>
       <c r="C951" t="s">
-        <v>1993</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="952" spans="1:3">
@@ -17062,7 +17050,7 @@
         <v>975</v>
       </c>
       <c r="C952" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="953" spans="1:3">
@@ -17073,7 +17061,7 @@
         <v>976</v>
       </c>
       <c r="C953" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="954" spans="1:3">
@@ -17084,7 +17072,7 @@
         <v>977</v>
       </c>
       <c r="C954" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="955" spans="1:3">
@@ -17095,7 +17083,7 @@
         <v>978</v>
       </c>
       <c r="C955" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="956" spans="1:3">
@@ -17106,7 +17094,7 @@
         <v>979</v>
       </c>
       <c r="C956" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="957" spans="1:3">
@@ -17117,7 +17105,7 @@
         <v>980</v>
       </c>
       <c r="C957" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="958" spans="1:3">
@@ -17128,7 +17116,7 @@
         <v>981</v>
       </c>
       <c r="C958" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="959" spans="1:3">
@@ -17139,7 +17127,7 @@
         <v>982</v>
       </c>
       <c r="C959" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="960" spans="1:3">
@@ -17150,7 +17138,7 @@
         <v>983</v>
       </c>
       <c r="C960" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="961" spans="1:3">
@@ -17161,7 +17149,7 @@
         <v>984</v>
       </c>
       <c r="C961" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="962" spans="1:3">
@@ -17172,7 +17160,7 @@
         <v>985</v>
       </c>
       <c r="C962" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="963" spans="1:3">
@@ -17183,7 +17171,7 @@
         <v>986</v>
       </c>
       <c r="C963" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="964" spans="1:3">
@@ -17194,7 +17182,7 @@
         <v>987</v>
       </c>
       <c r="C964" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="965" spans="1:3">
@@ -17205,7 +17193,7 @@
         <v>988</v>
       </c>
       <c r="C965" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="966" spans="1:3">
@@ -17216,7 +17204,7 @@
         <v>989</v>
       </c>
       <c r="C966" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="967" spans="1:3">
@@ -17227,7 +17215,7 @@
         <v>990</v>
       </c>
       <c r="C967" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="968" spans="1:3">
@@ -17238,7 +17226,7 @@
         <v>991</v>
       </c>
       <c r="C968" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="969" spans="1:3">
@@ -17249,7 +17237,7 @@
         <v>992</v>
       </c>
       <c r="C969" t="s">
-        <v>2011</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="970" spans="1:3">
@@ -17260,7 +17248,7 @@
         <v>993</v>
       </c>
       <c r="C970" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="971" spans="1:3">
@@ -17271,7 +17259,7 @@
         <v>994</v>
       </c>
       <c r="C971" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="972" spans="1:3">
@@ -17282,7 +17270,7 @@
         <v>995</v>
       </c>
       <c r="C972" t="s">
-        <v>2014</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="973" spans="1:3">
@@ -17293,7 +17281,7 @@
         <v>996</v>
       </c>
       <c r="C973" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="974" spans="1:3">
@@ -17304,7 +17292,7 @@
         <v>997</v>
       </c>
       <c r="C974" t="s">
-        <v>2009</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="975" spans="1:3">
@@ -17315,7 +17303,7 @@
         <v>998</v>
       </c>
       <c r="C975" t="s">
-        <v>2016</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="976" spans="1:3">
@@ -17326,7 +17314,7 @@
         <v>999</v>
       </c>
       <c r="C976" t="s">
-        <v>2017</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="977" spans="1:3">
@@ -17337,7 +17325,7 @@
         <v>1000</v>
       </c>
       <c r="C977" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="978" spans="1:3">
@@ -17348,7 +17336,7 @@
         <v>1001</v>
       </c>
       <c r="C978" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="979" spans="1:3">
@@ -17359,7 +17347,7 @@
         <v>1002</v>
       </c>
       <c r="C979" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="980" spans="1:3">
@@ -17370,7 +17358,7 @@
         <v>1003</v>
       </c>
       <c r="C980" t="s">
-        <v>2021</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="981" spans="1:3">
@@ -17381,7 +17369,7 @@
         <v>1004</v>
       </c>
       <c r="C981" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="982" spans="1:3">
@@ -17392,7 +17380,7 @@
         <v>1005</v>
       </c>
       <c r="C982" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="983" spans="1:3">
@@ -17403,7 +17391,7 @@
         <v>1006</v>
       </c>
       <c r="C983" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="984" spans="1:3">
@@ -17414,7 +17402,7 @@
         <v>1007</v>
       </c>
       <c r="C984" t="s">
-        <v>2025</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="985" spans="1:3">
@@ -17425,7 +17413,7 @@
         <v>1008</v>
       </c>
       <c r="C985" t="s">
-        <v>2026</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="986" spans="1:3">
@@ -17436,7 +17424,7 @@
         <v>1009</v>
       </c>
       <c r="C986" t="s">
-        <v>2027</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="987" spans="1:3">
@@ -17447,7 +17435,7 @@
         <v>1010</v>
       </c>
       <c r="C987" t="s">
-        <v>2028</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="988" spans="1:3">
@@ -17458,7 +17446,7 @@
         <v>1011</v>
       </c>
       <c r="C988" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="989" spans="1:3">
@@ -17469,7 +17457,7 @@
         <v>1012</v>
       </c>
       <c r="C989" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="990" spans="1:3">
@@ -17480,7 +17468,7 @@
         <v>1013</v>
       </c>
       <c r="C990" t="s">
-        <v>2031</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="991" spans="1:3">
@@ -17491,7 +17479,7 @@
         <v>1014</v>
       </c>
       <c r="C991" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="992" spans="1:3">
@@ -17502,7 +17490,7 @@
         <v>1015</v>
       </c>
       <c r="C992" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="993" spans="1:3">
@@ -17513,7 +17501,7 @@
         <v>1016</v>
       </c>
       <c r="C993" t="s">
-        <v>2034</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="994" spans="1:3">
@@ -17524,7 +17512,7 @@
         <v>1017</v>
       </c>
       <c r="C994" t="s">
-        <v>2035</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="995" spans="1:3">
@@ -17535,7 +17523,7 @@
         <v>1018</v>
       </c>
       <c r="C995" t="s">
-        <v>2010</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="996" spans="1:3">
@@ -17546,7 +17534,7 @@
         <v>1019</v>
       </c>
       <c r="C996" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="997" spans="1:3">
@@ -17557,7 +17545,7 @@
         <v>1020</v>
       </c>
       <c r="C997" t="s">
-        <v>2037</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="998" spans="1:3">
@@ -17568,7 +17556,7 @@
         <v>1021</v>
       </c>
       <c r="C998" t="s">
-        <v>2038</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="999" spans="1:3">
@@ -17579,7 +17567,7 @@
         <v>1022</v>
       </c>
       <c r="C999" t="s">
-        <v>1991</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1000" spans="1:3">
@@ -17590,7 +17578,7 @@
         <v>1023</v>
       </c>
       <c r="C1000" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="1001" spans="1:3">
@@ -17601,7 +17589,7 @@
         <v>1024</v>
       </c>
       <c r="C1001" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="1002" spans="1:3">
@@ -17612,7 +17600,7 @@
         <v>1025</v>
       </c>
       <c r="C1002" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="1003" spans="1:3">
@@ -17623,29 +17611,29 @@
         <v>1026</v>
       </c>
       <c r="C1003" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="1004" spans="1:3">
       <c r="A1004" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1004" t="s">
         <v>1027</v>
       </c>
       <c r="C1004" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="1005" spans="1:3">
       <c r="A1005" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1005" t="s">
         <v>1028</v>
       </c>
       <c r="C1005" t="s">
-        <v>2044</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="1006" spans="1:3">
@@ -17656,7 +17644,7 @@
         <v>1029</v>
       </c>
       <c r="C1006" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="1007" spans="1:3">
@@ -17667,7 +17655,7 @@
         <v>1030</v>
       </c>
       <c r="C1007" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="1008" spans="1:3">
@@ -17678,7 +17666,7 @@
         <v>1031</v>
       </c>
       <c r="C1008" t="s">
-        <v>2047</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="1009" spans="1:3">
@@ -17689,7 +17677,7 @@
         <v>1032</v>
       </c>
       <c r="C1009" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="1010" spans="1:3">
@@ -17700,7 +17688,7 @@
         <v>1033</v>
       </c>
       <c r="C1010" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="1011" spans="1:3">
@@ -17711,7 +17699,7 @@
         <v>1034</v>
       </c>
       <c r="C1011" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="1012" spans="1:3">
@@ -17722,7 +17710,7 @@
         <v>1035</v>
       </c>
       <c r="C1012" t="s">
-        <v>2051</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="1013" spans="1:3">
@@ -17733,7 +17721,7 @@
         <v>1036</v>
       </c>
       <c r="C1013" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="1014" spans="1:3">
@@ -17744,7 +17732,7 @@
         <v>1037</v>
       </c>
       <c r="C1014" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="1015" spans="1:3">
@@ -17755,7 +17743,7 @@
         <v>1038</v>
       </c>
       <c r="C1015" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1016" spans="1:3">
@@ -17766,7 +17754,7 @@
         <v>1039</v>
       </c>
       <c r="C1016" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="1017" spans="1:3">
@@ -17777,7 +17765,7 @@
         <v>1040</v>
       </c>
       <c r="C1017" t="s">
-        <v>2056</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="1018" spans="1:3">
@@ -17788,7 +17776,7 @@
         <v>1041</v>
       </c>
       <c r="C1018" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="1019" spans="1:3">
@@ -17799,7 +17787,7 @@
         <v>1042</v>
       </c>
       <c r="C1019" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="1020" spans="1:3">
@@ -17810,7 +17798,7 @@
         <v>1043</v>
       </c>
       <c r="C1020" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="1021" spans="1:3">
@@ -17821,7 +17809,7 @@
         <v>1044</v>
       </c>
       <c r="C1021" t="s">
-        <v>2060</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="1022" spans="1:3">
@@ -17832,7 +17820,7 @@
         <v>1045</v>
       </c>
       <c r="C1022" t="s">
-        <v>2061</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="1023" spans="1:3">
@@ -17843,7 +17831,7 @@
         <v>1046</v>
       </c>
       <c r="C1023" t="s">
-        <v>2062</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="1024" spans="1:3">
@@ -17854,7 +17842,7 @@
         <v>1047</v>
       </c>
       <c r="C1024" t="s">
-        <v>2063</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="1025" spans="1:3">
@@ -17865,7 +17853,7 @@
         <v>1048</v>
       </c>
       <c r="C1025" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="1026" spans="1:3">
@@ -17876,7 +17864,7 @@
         <v>1049</v>
       </c>
       <c r="C1026" t="s">
-        <v>2065</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="1027" spans="1:3">
@@ -17887,7 +17875,7 @@
         <v>1050</v>
       </c>
       <c r="C1027" t="s">
-        <v>2066</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="1028" spans="1:3">
@@ -17898,7 +17886,7 @@
         <v>1051</v>
       </c>
       <c r="C1028" t="s">
-        <v>2067</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="1029" spans="1:3">
@@ -17909,7 +17897,7 @@
         <v>1052</v>
       </c>
       <c r="C1029" t="s">
-        <v>2068</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="1030" spans="1:3">
@@ -17920,40 +17908,18 @@
         <v>1053</v>
       </c>
       <c r="C1030" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="1031" spans="1:3">
       <c r="A1031" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1031" t="s">
         <v>1054</v>
       </c>
       <c r="C1031" t="s">
-        <v>2070</v>
-      </c>
-    </row>
-    <row r="1032" spans="1:3">
-      <c r="A1032" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1032" t="s">
-        <v>1055</v>
-      </c>
-      <c r="C1032" t="s">
-        <v>2071</v>
-      </c>
-    </row>
-    <row r="1033" spans="1:3">
-      <c r="A1033" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1033" t="s">
-        <v>1056</v>
-      </c>
-      <c r="C1033" t="s">
-        <v>2072</v>
+        <v>2068</v>
       </c>
     </row>
   </sheetData>

--- a/faltantes_por_estados.xlsx
+++ b/faltantes_por_estados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3093" uniqueCount="2069">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3072" uniqueCount="2055">
   <si>
     <t>entidad</t>
   </si>
@@ -295,15 +295,9 @@
     <t>BSIMB000013</t>
   </si>
   <si>
-    <t>BSIMB000025</t>
-  </si>
-  <si>
     <t>BSIMB000066</t>
   </si>
   <si>
-    <t>BSIMB000071</t>
-  </si>
-  <si>
     <t>BSIMB000083</t>
   </si>
   <si>
@@ -1681,18 +1675,6 @@
     <t>HGIMB002456</t>
   </si>
   <si>
-    <t>HGIMB003173</t>
-  </si>
-  <si>
-    <t>HGIMB003190</t>
-  </si>
-  <si>
-    <t>HGIMB003400</t>
-  </si>
-  <si>
-    <t>HGIMB003762</t>
-  </si>
-  <si>
     <t>HGIMB003774</t>
   </si>
   <si>
@@ -2770,9 +2752,6 @@
     <t>TCIMB003644</t>
   </si>
   <si>
-    <t>TCIMB003702</t>
-  </si>
-  <si>
     <t>TCIMB003726</t>
   </si>
   <si>
@@ -3370,15 +3349,9 @@
     <t>CENTRO DE SALUD CIUDAD CONSTITUCIÓN</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD PUERTO ADOLFO LÓPEZ MATEOS</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD LA PURÍSIMA</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD PUERTO SAN CARLOS</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD SAN ISIDRO</t>
   </si>
   <si>
@@ -4741,18 +4714,6 @@
     <t>GUAYABOS</t>
   </si>
   <si>
-    <t>SAN IGNACIO NOPALA</t>
-  </si>
-  <si>
-    <t>SANTA MARÍA QUELITES</t>
-  </si>
-  <si>
-    <t>HUITZILA</t>
-  </si>
-  <si>
-    <t>BOMINTZHA</t>
-  </si>
-  <si>
     <t>XITHEJE DE REFORMA</t>
   </si>
   <si>
@@ -5819,9 +5780,6 @@
   </si>
   <si>
     <t>C.S. ESPERANZA NORTE</t>
-  </si>
-  <si>
-    <t>C.S. LA PALMA</t>
   </si>
   <si>
     <t>C.S. SANTO TOMAS</t>
@@ -6578,7 +6536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1031"/>
+  <dimension ref="A1:C1024"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6600,7 +6558,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>1055</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6611,7 +6569,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>1056</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6622,7 +6580,7 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>1057</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6633,7 +6591,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>1058</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6644,7 +6602,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>1059</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6655,7 +6613,7 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>1060</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6666,7 +6624,7 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>1061</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6677,7 +6635,7 @@
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>1062</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6688,7 +6646,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>1063</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6699,7 +6657,7 @@
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>1064</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6710,7 +6668,7 @@
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>1065</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6721,7 +6679,7 @@
         <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>1066</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6732,7 +6690,7 @@
         <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>1067</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6743,7 +6701,7 @@
         <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>1068</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -6754,7 +6712,7 @@
         <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>1069</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6776,7 +6734,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>1070</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6787,7 +6745,7 @@
         <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>1071</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6798,7 +6756,7 @@
         <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>1072</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6809,7 +6767,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>1073</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6820,7 +6778,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>1074</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6831,7 +6789,7 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>1075</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6842,7 +6800,7 @@
         <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>1076</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6853,7 +6811,7 @@
         <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>1077</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -6864,7 +6822,7 @@
         <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>1078</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6886,7 +6844,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="s">
-        <v>1079</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6908,7 +6866,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="s">
-        <v>1080</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -6919,7 +6877,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="s">
-        <v>1081</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -6930,7 +6888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="s">
-        <v>1070</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -6941,7 +6899,7 @@
         <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>1082</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6952,7 +6910,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="s">
-        <v>1083</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -6963,7 +6921,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="s">
-        <v>1084</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6974,7 +6932,7 @@
         <v>59</v>
       </c>
       <c r="C36" t="s">
-        <v>1085</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6985,7 +6943,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="s">
-        <v>1086</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -6996,7 +6954,7 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>1087</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -7007,7 +6965,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="s">
-        <v>1088</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -7018,7 +6976,7 @@
         <v>63</v>
       </c>
       <c r="C40" t="s">
-        <v>1089</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -7029,7 +6987,7 @@
         <v>64</v>
       </c>
       <c r="C41" t="s">
-        <v>1090</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -7040,7 +6998,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -7051,7 +7009,7 @@
         <v>66</v>
       </c>
       <c r="C43" t="s">
-        <v>1092</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -7062,7 +7020,7 @@
         <v>67</v>
       </c>
       <c r="C44" t="s">
-        <v>1093</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -7073,7 +7031,7 @@
         <v>68</v>
       </c>
       <c r="C45" t="s">
-        <v>1094</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -7084,7 +7042,7 @@
         <v>69</v>
       </c>
       <c r="C46" t="s">
-        <v>1095</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -7095,7 +7053,7 @@
         <v>70</v>
       </c>
       <c r="C47" t="s">
-        <v>1096</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -7106,7 +7064,7 @@
         <v>71</v>
       </c>
       <c r="C48" t="s">
-        <v>1097</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -7117,7 +7075,7 @@
         <v>72</v>
       </c>
       <c r="C49" t="s">
-        <v>1098</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -7128,7 +7086,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>1099</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -7139,7 +7097,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="s">
-        <v>1100</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -7150,7 +7108,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="s">
-        <v>1101</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -7161,7 +7119,7 @@
         <v>76</v>
       </c>
       <c r="C53" t="s">
-        <v>1102</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -7172,7 +7130,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>1103</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -7183,7 +7141,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="s">
-        <v>1104</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -7194,7 +7152,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="s">
-        <v>1105</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -7205,7 +7163,7 @@
         <v>80</v>
       </c>
       <c r="C57" t="s">
-        <v>1106</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -7216,7 +7174,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="s">
-        <v>1107</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -7227,7 +7185,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="s">
-        <v>1108</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -7249,7 +7207,7 @@
         <v>84</v>
       </c>
       <c r="C61" t="s">
-        <v>1109</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -7260,7 +7218,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="s">
-        <v>1110</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -7271,7 +7229,7 @@
         <v>86</v>
       </c>
       <c r="C63" t="s">
-        <v>1111</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -7282,7 +7240,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="s">
-        <v>1112</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -7293,7 +7251,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="s">
-        <v>1113</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -7304,7 +7262,7 @@
         <v>89</v>
       </c>
       <c r="C66" t="s">
-        <v>1114</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -7315,7 +7273,7 @@
         <v>90</v>
       </c>
       <c r="C67" t="s">
-        <v>1115</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -7326,7 +7284,7 @@
         <v>91</v>
       </c>
       <c r="C68" t="s">
-        <v>1116</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -7337,7 +7295,7 @@
         <v>92</v>
       </c>
       <c r="C69" t="s">
-        <v>1117</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -7348,7 +7306,7 @@
         <v>93</v>
       </c>
       <c r="C70" t="s">
-        <v>1118</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -7359,7 +7317,7 @@
         <v>94</v>
       </c>
       <c r="C71" t="s">
-        <v>1119</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -7370,7 +7328,7 @@
         <v>95</v>
       </c>
       <c r="C72" t="s">
-        <v>1120</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -7381,7 +7339,7 @@
         <v>96</v>
       </c>
       <c r="C73" t="s">
-        <v>1121</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -7392,7 +7350,7 @@
         <v>97</v>
       </c>
       <c r="C74" t="s">
-        <v>1122</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -7403,7 +7361,7 @@
         <v>98</v>
       </c>
       <c r="C75" t="s">
-        <v>1123</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -7414,7 +7372,7 @@
         <v>99</v>
       </c>
       <c r="C76" t="s">
-        <v>1124</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -7425,7 +7383,7 @@
         <v>100</v>
       </c>
       <c r="C77" t="s">
-        <v>1125</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -7436,7 +7394,7 @@
         <v>101</v>
       </c>
       <c r="C78" t="s">
-        <v>1126</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -7447,7 +7405,7 @@
         <v>102</v>
       </c>
       <c r="C79" t="s">
-        <v>1127</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -7458,7 +7416,7 @@
         <v>103</v>
       </c>
       <c r="C80" t="s">
-        <v>1128</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -7469,7 +7427,7 @@
         <v>104</v>
       </c>
       <c r="C81" t="s">
-        <v>1129</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -7480,7 +7438,7 @@
         <v>105</v>
       </c>
       <c r="C82" t="s">
-        <v>1130</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -7491,7 +7449,7 @@
         <v>106</v>
       </c>
       <c r="C83" t="s">
-        <v>1131</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -7502,7 +7460,7 @@
         <v>107</v>
       </c>
       <c r="C84" t="s">
-        <v>1132</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -7513,7 +7471,7 @@
         <v>108</v>
       </c>
       <c r="C85" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -7524,7 +7482,7 @@
         <v>109</v>
       </c>
       <c r="C86" t="s">
-        <v>1134</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -7535,7 +7493,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="s">
-        <v>1135</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -7546,7 +7504,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="s">
-        <v>1136</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -7557,7 +7515,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -7568,7 +7526,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -7579,7 +7537,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="s">
-        <v>1139</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -7590,7 +7548,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="s">
-        <v>1140</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -7601,7 +7559,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="s">
-        <v>1141</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -7612,7 +7570,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="s">
-        <v>1142</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -7623,7 +7581,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="s">
-        <v>1143</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -7634,7 +7592,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="s">
-        <v>1144</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -7645,7 +7603,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -7656,7 +7614,7 @@
         <v>121</v>
       </c>
       <c r="C98" t="s">
-        <v>1146</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -7667,7 +7625,7 @@
         <v>122</v>
       </c>
       <c r="C99" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -7678,7 +7636,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="s">
-        <v>1148</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -7689,7 +7647,7 @@
         <v>124</v>
       </c>
       <c r="C101" t="s">
-        <v>1149</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -7700,7 +7658,7 @@
         <v>125</v>
       </c>
       <c r="C102" t="s">
-        <v>1150</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -7711,7 +7669,7 @@
         <v>126</v>
       </c>
       <c r="C103" t="s">
-        <v>1151</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -7722,7 +7680,7 @@
         <v>127</v>
       </c>
       <c r="C104" t="s">
-        <v>1152</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -7733,7 +7691,7 @@
         <v>128</v>
       </c>
       <c r="C105" t="s">
-        <v>1153</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -7744,7 +7702,7 @@
         <v>129</v>
       </c>
       <c r="C106" t="s">
-        <v>1154</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -7755,29 +7713,29 @@
         <v>130</v>
       </c>
       <c r="C107" t="s">
-        <v>1155</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B108" t="s">
         <v>131</v>
       </c>
       <c r="C108" t="s">
-        <v>1156</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B109" t="s">
         <v>132</v>
       </c>
       <c r="C109" t="s">
-        <v>1157</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -7788,7 +7746,7 @@
         <v>133</v>
       </c>
       <c r="C110" t="s">
-        <v>1158</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -7799,7 +7757,7 @@
         <v>134</v>
       </c>
       <c r="C111" t="s">
-        <v>1159</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -7810,7 +7768,7 @@
         <v>135</v>
       </c>
       <c r="C112" t="s">
-        <v>1160</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -7821,7 +7779,7 @@
         <v>136</v>
       </c>
       <c r="C113" t="s">
-        <v>1161</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -7832,7 +7790,7 @@
         <v>137</v>
       </c>
       <c r="C114" t="s">
-        <v>1162</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -7843,7 +7801,7 @@
         <v>138</v>
       </c>
       <c r="C115" t="s">
-        <v>1163</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -7854,7 +7812,7 @@
         <v>139</v>
       </c>
       <c r="C116" t="s">
-        <v>1164</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -7865,7 +7823,7 @@
         <v>140</v>
       </c>
       <c r="C117" t="s">
-        <v>1165</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -7876,7 +7834,7 @@
         <v>141</v>
       </c>
       <c r="C118" t="s">
-        <v>1166</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -7887,7 +7845,7 @@
         <v>142</v>
       </c>
       <c r="C119" t="s">
-        <v>1167</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -7898,7 +7856,7 @@
         <v>143</v>
       </c>
       <c r="C120" t="s">
-        <v>1168</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -7909,7 +7867,7 @@
         <v>144</v>
       </c>
       <c r="C121" t="s">
-        <v>1169</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -7920,40 +7878,40 @@
         <v>145</v>
       </c>
       <c r="C122" t="s">
-        <v>1170</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B123" t="s">
         <v>146</v>
       </c>
       <c r="C123" t="s">
-        <v>1171</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B124" t="s">
         <v>147</v>
       </c>
       <c r="C124" t="s">
-        <v>1172</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B125" t="s">
         <v>148</v>
       </c>
       <c r="C125" t="s">
-        <v>1173</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -7964,7 +7922,7 @@
         <v>149</v>
       </c>
       <c r="C126" t="s">
-        <v>1174</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -7975,7 +7933,7 @@
         <v>150</v>
       </c>
       <c r="C127" t="s">
-        <v>1175</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -7986,7 +7944,7 @@
         <v>151</v>
       </c>
       <c r="C128" t="s">
-        <v>1176</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -7997,7 +7955,7 @@
         <v>152</v>
       </c>
       <c r="C129" t="s">
-        <v>1177</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -8008,7 +7966,7 @@
         <v>153</v>
       </c>
       <c r="C130" t="s">
-        <v>1178</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -8019,7 +7977,7 @@
         <v>154</v>
       </c>
       <c r="C131" t="s">
-        <v>1179</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -8030,7 +7988,7 @@
         <v>155</v>
       </c>
       <c r="C132" t="s">
-        <v>1180</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -8041,7 +7999,7 @@
         <v>156</v>
       </c>
       <c r="C133" t="s">
-        <v>1181</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -8052,7 +8010,7 @@
         <v>157</v>
       </c>
       <c r="C134" t="s">
-        <v>1182</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -8063,7 +8021,7 @@
         <v>158</v>
       </c>
       <c r="C135" t="s">
-        <v>1183</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -8074,7 +8032,7 @@
         <v>159</v>
       </c>
       <c r="C136" t="s">
-        <v>1184</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -8085,7 +8043,7 @@
         <v>160</v>
       </c>
       <c r="C137" t="s">
-        <v>1185</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -8096,7 +8054,7 @@
         <v>161</v>
       </c>
       <c r="C138" t="s">
-        <v>1186</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -8107,7 +8065,7 @@
         <v>162</v>
       </c>
       <c r="C139" t="s">
-        <v>1187</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -8118,7 +8076,7 @@
         <v>163</v>
       </c>
       <c r="C140" t="s">
-        <v>1188</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -8129,7 +8087,7 @@
         <v>164</v>
       </c>
       <c r="C141" t="s">
-        <v>1189</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -8140,7 +8098,7 @@
         <v>165</v>
       </c>
       <c r="C142" t="s">
-        <v>1190</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -8151,7 +8109,7 @@
         <v>166</v>
       </c>
       <c r="C143" t="s">
-        <v>1191</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -8162,7 +8120,7 @@
         <v>167</v>
       </c>
       <c r="C144" t="s">
-        <v>1192</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -8173,7 +8131,7 @@
         <v>168</v>
       </c>
       <c r="C145" t="s">
-        <v>1193</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -8184,7 +8142,7 @@
         <v>169</v>
       </c>
       <c r="C146" t="s">
-        <v>1194</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -8195,7 +8153,7 @@
         <v>170</v>
       </c>
       <c r="C147" t="s">
-        <v>1195</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -8206,7 +8164,7 @@
         <v>171</v>
       </c>
       <c r="C148" t="s">
-        <v>1196</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -8217,7 +8175,7 @@
         <v>172</v>
       </c>
       <c r="C149" t="s">
-        <v>1197</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -8228,7 +8186,7 @@
         <v>173</v>
       </c>
       <c r="C150" t="s">
-        <v>1198</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -8239,7 +8197,7 @@
         <v>174</v>
       </c>
       <c r="C151" t="s">
-        <v>1199</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -8250,7 +8208,7 @@
         <v>175</v>
       </c>
       <c r="C152" t="s">
-        <v>1200</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -8261,7 +8219,7 @@
         <v>176</v>
       </c>
       <c r="C153" t="s">
-        <v>1201</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -8272,7 +8230,7 @@
         <v>177</v>
       </c>
       <c r="C154" t="s">
-        <v>1202</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -8283,7 +8241,7 @@
         <v>178</v>
       </c>
       <c r="C155" t="s">
-        <v>1203</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -8294,7 +8252,7 @@
         <v>179</v>
       </c>
       <c r="C156" t="s">
-        <v>1204</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -8305,7 +8263,7 @@
         <v>180</v>
       </c>
       <c r="C157" t="s">
-        <v>1205</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -8316,7 +8274,7 @@
         <v>181</v>
       </c>
       <c r="C158" t="s">
-        <v>1206</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -8327,7 +8285,7 @@
         <v>182</v>
       </c>
       <c r="C159" t="s">
-        <v>1207</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -8338,7 +8296,7 @@
         <v>183</v>
       </c>
       <c r="C160" t="s">
-        <v>1208</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -8349,7 +8307,7 @@
         <v>184</v>
       </c>
       <c r="C161" t="s">
-        <v>1209</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -8360,7 +8318,7 @@
         <v>185</v>
       </c>
       <c r="C162" t="s">
-        <v>1210</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -8371,7 +8329,7 @@
         <v>186</v>
       </c>
       <c r="C163" t="s">
-        <v>1211</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -8382,7 +8340,7 @@
         <v>187</v>
       </c>
       <c r="C164" t="s">
-        <v>1212</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -8393,7 +8351,7 @@
         <v>188</v>
       </c>
       <c r="C165" t="s">
-        <v>1213</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -8404,7 +8362,7 @@
         <v>189</v>
       </c>
       <c r="C166" t="s">
-        <v>1214</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -8415,7 +8373,7 @@
         <v>190</v>
       </c>
       <c r="C167" t="s">
-        <v>1215</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -8426,7 +8384,7 @@
         <v>191</v>
       </c>
       <c r="C168" t="s">
-        <v>1216</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -8437,7 +8395,7 @@
         <v>192</v>
       </c>
       <c r="C169" t="s">
-        <v>1217</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -8448,7 +8406,7 @@
         <v>193</v>
       </c>
       <c r="C170" t="s">
-        <v>1218</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -8459,7 +8417,7 @@
         <v>194</v>
       </c>
       <c r="C171" t="s">
-        <v>1219</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -8470,7 +8428,7 @@
         <v>195</v>
       </c>
       <c r="C172" t="s">
-        <v>1220</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -8481,7 +8439,7 @@
         <v>196</v>
       </c>
       <c r="C173" t="s">
-        <v>1221</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -8492,7 +8450,7 @@
         <v>197</v>
       </c>
       <c r="C174" t="s">
-        <v>1222</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -8503,7 +8461,7 @@
         <v>198</v>
       </c>
       <c r="C175" t="s">
-        <v>1223</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -8514,7 +8472,7 @@
         <v>199</v>
       </c>
       <c r="C176" t="s">
-        <v>1224</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -8525,7 +8483,7 @@
         <v>200</v>
       </c>
       <c r="C177" t="s">
-        <v>1225</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -8536,7 +8494,7 @@
         <v>201</v>
       </c>
       <c r="C178" t="s">
-        <v>1226</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -8547,7 +8505,7 @@
         <v>202</v>
       </c>
       <c r="C179" t="s">
-        <v>1227</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -8558,7 +8516,7 @@
         <v>203</v>
       </c>
       <c r="C180" t="s">
-        <v>1228</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -8569,7 +8527,7 @@
         <v>204</v>
       </c>
       <c r="C181" t="s">
-        <v>1229</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -8580,7 +8538,7 @@
         <v>205</v>
       </c>
       <c r="C182" t="s">
-        <v>1230</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -8591,7 +8549,7 @@
         <v>206</v>
       </c>
       <c r="C183" t="s">
-        <v>1231</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -8602,7 +8560,7 @@
         <v>207</v>
       </c>
       <c r="C184" t="s">
-        <v>1232</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -8613,7 +8571,7 @@
         <v>208</v>
       </c>
       <c r="C185" t="s">
-        <v>1233</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -8624,7 +8582,7 @@
         <v>209</v>
       </c>
       <c r="C186" t="s">
-        <v>1234</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -8635,7 +8593,7 @@
         <v>210</v>
       </c>
       <c r="C187" t="s">
-        <v>1235</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -8646,7 +8604,7 @@
         <v>211</v>
       </c>
       <c r="C188" t="s">
-        <v>1236</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -8657,7 +8615,7 @@
         <v>212</v>
       </c>
       <c r="C189" t="s">
-        <v>1237</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -8668,7 +8626,7 @@
         <v>213</v>
       </c>
       <c r="C190" t="s">
-        <v>1238</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -8679,7 +8637,7 @@
         <v>214</v>
       </c>
       <c r="C191" t="s">
-        <v>1239</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -8690,7 +8648,7 @@
         <v>215</v>
       </c>
       <c r="C192" t="s">
-        <v>1240</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -8701,7 +8659,7 @@
         <v>216</v>
       </c>
       <c r="C193" t="s">
-        <v>1241</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -8712,7 +8670,7 @@
         <v>217</v>
       </c>
       <c r="C194" t="s">
-        <v>1242</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -8723,7 +8681,7 @@
         <v>218</v>
       </c>
       <c r="C195" t="s">
-        <v>1243</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -8734,7 +8692,7 @@
         <v>219</v>
       </c>
       <c r="C196" t="s">
-        <v>1244</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -8745,7 +8703,7 @@
         <v>220</v>
       </c>
       <c r="C197" t="s">
-        <v>1245</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -8756,7 +8714,7 @@
         <v>221</v>
       </c>
       <c r="C198" t="s">
-        <v>1246</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -8767,7 +8725,7 @@
         <v>222</v>
       </c>
       <c r="C199" t="s">
-        <v>1247</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -8778,7 +8736,7 @@
         <v>223</v>
       </c>
       <c r="C200" t="s">
-        <v>1248</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -8789,7 +8747,7 @@
         <v>224</v>
       </c>
       <c r="C201" t="s">
-        <v>1249</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -8800,7 +8758,7 @@
         <v>225</v>
       </c>
       <c r="C202" t="s">
-        <v>1250</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -8811,7 +8769,7 @@
         <v>226</v>
       </c>
       <c r="C203" t="s">
-        <v>1251</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -8822,7 +8780,7 @@
         <v>227</v>
       </c>
       <c r="C204" t="s">
-        <v>1252</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -8833,7 +8791,7 @@
         <v>228</v>
       </c>
       <c r="C205" t="s">
-        <v>1253</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -8844,7 +8802,7 @@
         <v>229</v>
       </c>
       <c r="C206" t="s">
-        <v>1254</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -8855,7 +8813,7 @@
         <v>230</v>
       </c>
       <c r="C207" t="s">
-        <v>1255</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -8866,7 +8824,7 @@
         <v>231</v>
       </c>
       <c r="C208" t="s">
-        <v>1256</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -8877,7 +8835,7 @@
         <v>232</v>
       </c>
       <c r="C209" t="s">
-        <v>1257</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -8888,7 +8846,7 @@
         <v>233</v>
       </c>
       <c r="C210" t="s">
-        <v>1258</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -8899,7 +8857,7 @@
         <v>234</v>
       </c>
       <c r="C211" t="s">
-        <v>1259</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -8910,7 +8868,7 @@
         <v>235</v>
       </c>
       <c r="C212" t="s">
-        <v>1260</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -8921,7 +8879,7 @@
         <v>236</v>
       </c>
       <c r="C213" t="s">
-        <v>1261</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -8932,7 +8890,7 @@
         <v>237</v>
       </c>
       <c r="C214" t="s">
-        <v>1262</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -8943,7 +8901,7 @@
         <v>238</v>
       </c>
       <c r="C215" t="s">
-        <v>1263</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -8954,7 +8912,7 @@
         <v>239</v>
       </c>
       <c r="C216" t="s">
-        <v>1264</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -8965,7 +8923,7 @@
         <v>240</v>
       </c>
       <c r="C217" t="s">
-        <v>1265</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -8976,7 +8934,7 @@
         <v>241</v>
       </c>
       <c r="C218" t="s">
-        <v>1266</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -8987,7 +8945,7 @@
         <v>242</v>
       </c>
       <c r="C219" t="s">
-        <v>1267</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -8998,7 +8956,7 @@
         <v>243</v>
       </c>
       <c r="C220" t="s">
-        <v>1268</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -9009,7 +8967,7 @@
         <v>244</v>
       </c>
       <c r="C221" t="s">
-        <v>1269</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -9020,7 +8978,7 @@
         <v>245</v>
       </c>
       <c r="C222" t="s">
-        <v>1270</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -9031,7 +8989,7 @@
         <v>246</v>
       </c>
       <c r="C223" t="s">
-        <v>1271</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -9042,7 +9000,7 @@
         <v>247</v>
       </c>
       <c r="C224" t="s">
-        <v>1272</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -9053,7 +9011,7 @@
         <v>248</v>
       </c>
       <c r="C225" t="s">
-        <v>1273</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -9064,7 +9022,7 @@
         <v>249</v>
       </c>
       <c r="C226" t="s">
-        <v>1274</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -9075,7 +9033,7 @@
         <v>250</v>
       </c>
       <c r="C227" t="s">
-        <v>1275</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -9086,7 +9044,7 @@
         <v>251</v>
       </c>
       <c r="C228" t="s">
-        <v>1276</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -9097,7 +9055,7 @@
         <v>252</v>
       </c>
       <c r="C229" t="s">
-        <v>1277</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -9108,7 +9066,7 @@
         <v>253</v>
       </c>
       <c r="C230" t="s">
-        <v>1278</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -9119,7 +9077,7 @@
         <v>254</v>
       </c>
       <c r="C231" t="s">
-        <v>1279</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -9130,7 +9088,7 @@
         <v>255</v>
       </c>
       <c r="C232" t="s">
-        <v>1280</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -9141,7 +9099,7 @@
         <v>256</v>
       </c>
       <c r="C233" t="s">
-        <v>1281</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -9152,7 +9110,7 @@
         <v>257</v>
       </c>
       <c r="C234" t="s">
-        <v>1282</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -9163,7 +9121,7 @@
         <v>258</v>
       </c>
       <c r="C235" t="s">
-        <v>1283</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -9174,7 +9132,7 @@
         <v>259</v>
       </c>
       <c r="C236" t="s">
-        <v>1284</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -9185,7 +9143,7 @@
         <v>260</v>
       </c>
       <c r="C237" t="s">
-        <v>1285</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -9196,7 +9154,7 @@
         <v>261</v>
       </c>
       <c r="C238" t="s">
-        <v>1286</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -9207,7 +9165,7 @@
         <v>262</v>
       </c>
       <c r="C239" t="s">
-        <v>1287</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -9218,7 +9176,7 @@
         <v>263</v>
       </c>
       <c r="C240" t="s">
-        <v>1288</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -9229,7 +9187,7 @@
         <v>264</v>
       </c>
       <c r="C241" t="s">
-        <v>1289</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -9240,7 +9198,7 @@
         <v>265</v>
       </c>
       <c r="C242" t="s">
-        <v>1290</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -9251,7 +9209,7 @@
         <v>266</v>
       </c>
       <c r="C243" t="s">
-        <v>1291</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -9262,7 +9220,7 @@
         <v>267</v>
       </c>
       <c r="C244" t="s">
-        <v>1292</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -9273,7 +9231,7 @@
         <v>268</v>
       </c>
       <c r="C245" t="s">
-        <v>1293</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -9284,7 +9242,7 @@
         <v>269</v>
       </c>
       <c r="C246" t="s">
-        <v>1294</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -9295,7 +9253,7 @@
         <v>270</v>
       </c>
       <c r="C247" t="s">
-        <v>1295</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -9306,7 +9264,7 @@
         <v>271</v>
       </c>
       <c r="C248" t="s">
-        <v>1296</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -9317,7 +9275,7 @@
         <v>272</v>
       </c>
       <c r="C249" t="s">
-        <v>1297</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -9328,7 +9286,7 @@
         <v>273</v>
       </c>
       <c r="C250" t="s">
-        <v>1298</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -9339,7 +9297,7 @@
         <v>274</v>
       </c>
       <c r="C251" t="s">
-        <v>1299</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -9350,7 +9308,7 @@
         <v>275</v>
       </c>
       <c r="C252" t="s">
-        <v>1300</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -9361,7 +9319,7 @@
         <v>276</v>
       </c>
       <c r="C253" t="s">
-        <v>1301</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -9372,7 +9330,7 @@
         <v>277</v>
       </c>
       <c r="C254" t="s">
-        <v>1302</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -9383,7 +9341,7 @@
         <v>278</v>
       </c>
       <c r="C255" t="s">
-        <v>1303</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -9394,7 +9352,7 @@
         <v>279</v>
       </c>
       <c r="C256" t="s">
-        <v>1304</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -9405,7 +9363,7 @@
         <v>280</v>
       </c>
       <c r="C257" t="s">
-        <v>1305</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -9416,7 +9374,7 @@
         <v>281</v>
       </c>
       <c r="C258" t="s">
-        <v>1306</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="259" spans="1:3">
@@ -9427,7 +9385,7 @@
         <v>282</v>
       </c>
       <c r="C259" t="s">
-        <v>1307</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -9438,7 +9396,7 @@
         <v>283</v>
       </c>
       <c r="C260" t="s">
-        <v>1308</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="261" spans="1:3">
@@ -9449,7 +9407,7 @@
         <v>284</v>
       </c>
       <c r="C261" t="s">
-        <v>1309</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="262" spans="1:3">
@@ -9460,7 +9418,7 @@
         <v>285</v>
       </c>
       <c r="C262" t="s">
-        <v>1310</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -9471,7 +9429,7 @@
         <v>286</v>
       </c>
       <c r="C263" t="s">
-        <v>1311</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="264" spans="1:3">
@@ -9482,7 +9440,7 @@
         <v>287</v>
       </c>
       <c r="C264" t="s">
-        <v>1312</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -9493,7 +9451,7 @@
         <v>288</v>
       </c>
       <c r="C265" t="s">
-        <v>1313</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="266" spans="1:3">
@@ -9504,7 +9462,7 @@
         <v>289</v>
       </c>
       <c r="C266" t="s">
-        <v>1314</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="267" spans="1:3">
@@ -9515,7 +9473,7 @@
         <v>290</v>
       </c>
       <c r="C267" t="s">
-        <v>1315</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="268" spans="1:3">
@@ -9526,7 +9484,7 @@
         <v>291</v>
       </c>
       <c r="C268" t="s">
-        <v>1316</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="269" spans="1:3">
@@ -9537,7 +9495,7 @@
         <v>292</v>
       </c>
       <c r="C269" t="s">
-        <v>1317</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="270" spans="1:3">
@@ -9548,7 +9506,7 @@
         <v>293</v>
       </c>
       <c r="C270" t="s">
-        <v>1318</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="271" spans="1:3">
@@ -9559,7 +9517,7 @@
         <v>294</v>
       </c>
       <c r="C271" t="s">
-        <v>1319</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="272" spans="1:3">
@@ -9570,7 +9528,7 @@
         <v>295</v>
       </c>
       <c r="C272" t="s">
-        <v>1320</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="273" spans="1:3">
@@ -9581,7 +9539,7 @@
         <v>296</v>
       </c>
       <c r="C273" t="s">
-        <v>1321</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="274" spans="1:3">
@@ -9592,7 +9550,7 @@
         <v>297</v>
       </c>
       <c r="C274" t="s">
-        <v>1322</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="275" spans="1:3">
@@ -9603,7 +9561,7 @@
         <v>298</v>
       </c>
       <c r="C275" t="s">
-        <v>1323</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="276" spans="1:3">
@@ -9614,7 +9572,7 @@
         <v>299</v>
       </c>
       <c r="C276" t="s">
-        <v>1324</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="277" spans="1:3">
@@ -9625,7 +9583,7 @@
         <v>300</v>
       </c>
       <c r="C277" t="s">
-        <v>1325</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="278" spans="1:3">
@@ -9636,7 +9594,7 @@
         <v>301</v>
       </c>
       <c r="C278" t="s">
-        <v>1326</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="279" spans="1:3">
@@ -9647,7 +9605,7 @@
         <v>302</v>
       </c>
       <c r="C279" t="s">
-        <v>1327</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="280" spans="1:3">
@@ -9658,7 +9616,7 @@
         <v>303</v>
       </c>
       <c r="C280" t="s">
-        <v>1328</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -9669,7 +9627,7 @@
         <v>304</v>
       </c>
       <c r="C281" t="s">
-        <v>1329</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="282" spans="1:3">
@@ -9680,7 +9638,7 @@
         <v>305</v>
       </c>
       <c r="C282" t="s">
-        <v>1330</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="283" spans="1:3">
@@ -9691,7 +9649,7 @@
         <v>306</v>
       </c>
       <c r="C283" t="s">
-        <v>1248</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="284" spans="1:3">
@@ -9702,7 +9660,7 @@
         <v>307</v>
       </c>
       <c r="C284" t="s">
-        <v>1331</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="285" spans="1:3">
@@ -9713,7 +9671,7 @@
         <v>308</v>
       </c>
       <c r="C285" t="s">
-        <v>1332</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="286" spans="1:3">
@@ -9724,7 +9682,7 @@
         <v>309</v>
       </c>
       <c r="C286" t="s">
-        <v>1333</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="287" spans="1:3">
@@ -9735,7 +9693,7 @@
         <v>310</v>
       </c>
       <c r="C287" t="s">
-        <v>1334</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="288" spans="1:3">
@@ -9746,7 +9704,7 @@
         <v>311</v>
       </c>
       <c r="C288" t="s">
-        <v>1335</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="289" spans="1:3">
@@ -9757,7 +9715,7 @@
         <v>312</v>
       </c>
       <c r="C289" t="s">
-        <v>1336</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="290" spans="1:3">
@@ -9768,7 +9726,7 @@
         <v>313</v>
       </c>
       <c r="C290" t="s">
-        <v>1337</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="291" spans="1:3">
@@ -9779,7 +9737,7 @@
         <v>314</v>
       </c>
       <c r="C291" t="s">
-        <v>1338</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="292" spans="1:3">
@@ -9790,7 +9748,7 @@
         <v>315</v>
       </c>
       <c r="C292" t="s">
-        <v>1339</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="293" spans="1:3">
@@ -9801,7 +9759,7 @@
         <v>316</v>
       </c>
       <c r="C293" t="s">
-        <v>1340</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="294" spans="1:3">
@@ -9812,7 +9770,7 @@
         <v>317</v>
       </c>
       <c r="C294" t="s">
-        <v>1341</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="295" spans="1:3">
@@ -9823,7 +9781,7 @@
         <v>318</v>
       </c>
       <c r="C295" t="s">
-        <v>1342</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="296" spans="1:3">
@@ -9834,7 +9792,7 @@
         <v>319</v>
       </c>
       <c r="C296" t="s">
-        <v>1343</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="297" spans="1:3">
@@ -9845,7 +9803,7 @@
         <v>320</v>
       </c>
       <c r="C297" t="s">
-        <v>1344</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="298" spans="1:3">
@@ -9856,7 +9814,7 @@
         <v>321</v>
       </c>
       <c r="C298" t="s">
-        <v>1345</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="299" spans="1:3">
@@ -9867,7 +9825,7 @@
         <v>322</v>
       </c>
       <c r="C299" t="s">
-        <v>1346</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="300" spans="1:3">
@@ -9878,7 +9836,7 @@
         <v>323</v>
       </c>
       <c r="C300" t="s">
-        <v>1347</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="301" spans="1:3">
@@ -9889,7 +9847,7 @@
         <v>324</v>
       </c>
       <c r="C301" t="s">
-        <v>1348</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -9900,7 +9858,7 @@
         <v>325</v>
       </c>
       <c r="C302" t="s">
-        <v>1349</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="303" spans="1:3">
@@ -9911,7 +9869,7 @@
         <v>326</v>
       </c>
       <c r="C303" t="s">
-        <v>1350</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="304" spans="1:3">
@@ -9922,7 +9880,7 @@
         <v>327</v>
       </c>
       <c r="C304" t="s">
-        <v>1351</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -9933,7 +9891,7 @@
         <v>328</v>
       </c>
       <c r="C305" t="s">
-        <v>1352</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="306" spans="1:3">
@@ -9944,7 +9902,7 @@
         <v>329</v>
       </c>
       <c r="C306" t="s">
-        <v>1353</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="307" spans="1:3">
@@ -9955,7 +9913,7 @@
         <v>330</v>
       </c>
       <c r="C307" t="s">
-        <v>1354</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="308" spans="1:3">
@@ -9966,7 +9924,7 @@
         <v>331</v>
       </c>
       <c r="C308" t="s">
-        <v>1355</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="309" spans="1:3">
@@ -9977,7 +9935,7 @@
         <v>332</v>
       </c>
       <c r="C309" t="s">
-        <v>1356</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="310" spans="1:3">
@@ -9988,7 +9946,7 @@
         <v>333</v>
       </c>
       <c r="C310" t="s">
-        <v>1357</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="311" spans="1:3">
@@ -9999,7 +9957,7 @@
         <v>334</v>
       </c>
       <c r="C311" t="s">
-        <v>1358</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="312" spans="1:3">
@@ -10010,7 +9968,7 @@
         <v>335</v>
       </c>
       <c r="C312" t="s">
-        <v>1359</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="313" spans="1:3">
@@ -10021,7 +9979,7 @@
         <v>336</v>
       </c>
       <c r="C313" t="s">
-        <v>1360</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="314" spans="1:3">
@@ -10032,7 +9990,7 @@
         <v>337</v>
       </c>
       <c r="C314" t="s">
-        <v>1361</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="315" spans="1:3">
@@ -10043,29 +10001,29 @@
         <v>338</v>
       </c>
       <c r="C315" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="316" spans="1:3">
       <c r="A316" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B316" t="s">
         <v>339</v>
       </c>
       <c r="C316" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="317" spans="1:3">
       <c r="A317" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B317" t="s">
         <v>340</v>
       </c>
       <c r="C317" t="s">
-        <v>1364</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="318" spans="1:3">
@@ -10076,7 +10034,7 @@
         <v>341</v>
       </c>
       <c r="C318" t="s">
-        <v>1365</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="319" spans="1:3">
@@ -10087,7 +10045,7 @@
         <v>342</v>
       </c>
       <c r="C319" t="s">
-        <v>1366</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="320" spans="1:3">
@@ -10098,7 +10056,7 @@
         <v>343</v>
       </c>
       <c r="C320" t="s">
-        <v>1367</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="321" spans="1:3">
@@ -10109,7 +10067,7 @@
         <v>344</v>
       </c>
       <c r="C321" t="s">
-        <v>1368</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -10120,7 +10078,7 @@
         <v>345</v>
       </c>
       <c r="C322" t="s">
-        <v>1369</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="323" spans="1:3">
@@ -10131,7 +10089,7 @@
         <v>346</v>
       </c>
       <c r="C323" t="s">
-        <v>1370</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="324" spans="1:3">
@@ -10142,7 +10100,7 @@
         <v>347</v>
       </c>
       <c r="C324" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -10153,7 +10111,7 @@
         <v>348</v>
       </c>
       <c r="C325" t="s">
-        <v>1144</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="326" spans="1:3">
@@ -10164,7 +10122,7 @@
         <v>349</v>
       </c>
       <c r="C326" t="s">
-        <v>1372</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="327" spans="1:3">
@@ -10175,7 +10133,7 @@
         <v>350</v>
       </c>
       <c r="C327" t="s">
-        <v>1373</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="328" spans="1:3">
@@ -10186,7 +10144,7 @@
         <v>351</v>
       </c>
       <c r="C328" t="s">
-        <v>1374</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="329" spans="1:3">
@@ -10197,7 +10155,7 @@
         <v>352</v>
       </c>
       <c r="C329" t="s">
-        <v>1375</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="330" spans="1:3">
@@ -10208,7 +10166,7 @@
         <v>353</v>
       </c>
       <c r="C330" t="s">
-        <v>1376</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -10219,7 +10177,7 @@
         <v>354</v>
       </c>
       <c r="C331" t="s">
-        <v>1377</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="332" spans="1:3">
@@ -10230,7 +10188,7 @@
         <v>355</v>
       </c>
       <c r="C332" t="s">
-        <v>1378</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="333" spans="1:3">
@@ -10241,7 +10199,7 @@
         <v>356</v>
       </c>
       <c r="C333" t="s">
-        <v>1379</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="334" spans="1:3">
@@ -10252,7 +10210,7 @@
         <v>357</v>
       </c>
       <c r="C334" t="s">
-        <v>1380</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="335" spans="1:3">
@@ -10263,7 +10221,7 @@
         <v>358</v>
       </c>
       <c r="C335" t="s">
-        <v>1381</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="336" spans="1:3">
@@ -10274,7 +10232,7 @@
         <v>359</v>
       </c>
       <c r="C336" t="s">
-        <v>1382</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="337" spans="1:3">
@@ -10285,7 +10243,7 @@
         <v>360</v>
       </c>
       <c r="C337" t="s">
-        <v>1383</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="338" spans="1:3">
@@ -10296,7 +10254,7 @@
         <v>361</v>
       </c>
       <c r="C338" t="s">
-        <v>1384</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="339" spans="1:3">
@@ -10307,7 +10265,7 @@
         <v>362</v>
       </c>
       <c r="C339" t="s">
-        <v>1385</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="340" spans="1:3">
@@ -10318,7 +10276,7 @@
         <v>363</v>
       </c>
       <c r="C340" t="s">
-        <v>1386</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="341" spans="1:3">
@@ -10329,7 +10287,7 @@
         <v>364</v>
       </c>
       <c r="C341" t="s">
-        <v>1387</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -10340,7 +10298,7 @@
         <v>365</v>
       </c>
       <c r="C342" t="s">
-        <v>1388</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="343" spans="1:3">
@@ -10351,7 +10309,7 @@
         <v>366</v>
       </c>
       <c r="C343" t="s">
-        <v>1135</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="344" spans="1:3">
@@ -10362,7 +10320,7 @@
         <v>367</v>
       </c>
       <c r="C344" t="s">
-        <v>1389</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="345" spans="1:3">
@@ -10373,7 +10331,7 @@
         <v>368</v>
       </c>
       <c r="C345" t="s">
-        <v>1390</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="346" spans="1:3">
@@ -10384,7 +10342,7 @@
         <v>369</v>
       </c>
       <c r="C346" t="s">
-        <v>1391</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="347" spans="1:3">
@@ -10395,7 +10353,7 @@
         <v>370</v>
       </c>
       <c r="C347" t="s">
-        <v>1392</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="348" spans="1:3">
@@ -10406,7 +10364,7 @@
         <v>371</v>
       </c>
       <c r="C348" t="s">
-        <v>1393</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="349" spans="1:3">
@@ -10417,7 +10375,7 @@
         <v>372</v>
       </c>
       <c r="C349" t="s">
-        <v>1394</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -10428,29 +10386,29 @@
         <v>373</v>
       </c>
       <c r="C350" t="s">
-        <v>1395</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="351" spans="1:3">
       <c r="A351" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B351" t="s">
         <v>374</v>
       </c>
       <c r="C351" t="s">
-        <v>1396</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="352" spans="1:3">
       <c r="A352" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B352" t="s">
         <v>375</v>
       </c>
       <c r="C352" t="s">
-        <v>1397</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="353" spans="1:3">
@@ -10461,7 +10419,7 @@
         <v>376</v>
       </c>
       <c r="C353" t="s">
-        <v>1398</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="354" spans="1:3">
@@ -10472,7 +10430,7 @@
         <v>377</v>
       </c>
       <c r="C354" t="s">
-        <v>1399</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -10483,7 +10441,7 @@
         <v>378</v>
       </c>
       <c r="C355" t="s">
-        <v>1400</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="356" spans="1:3">
@@ -10494,7 +10452,7 @@
         <v>379</v>
       </c>
       <c r="C356" t="s">
-        <v>1401</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="357" spans="1:3">
@@ -10505,7 +10463,7 @@
         <v>380</v>
       </c>
       <c r="C357" t="s">
-        <v>1402</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="358" spans="1:3">
@@ -10516,7 +10474,7 @@
         <v>381</v>
       </c>
       <c r="C358" t="s">
-        <v>1403</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="359" spans="1:3">
@@ -10527,7 +10485,7 @@
         <v>382</v>
       </c>
       <c r="C359" t="s">
-        <v>1404</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -10538,7 +10496,7 @@
         <v>383</v>
       </c>
       <c r="C360" t="s">
-        <v>1405</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="361" spans="1:3">
@@ -10549,7 +10507,7 @@
         <v>384</v>
       </c>
       <c r="C361" t="s">
-        <v>1406</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="362" spans="1:3">
@@ -10560,7 +10518,7 @@
         <v>385</v>
       </c>
       <c r="C362" t="s">
-        <v>1407</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="363" spans="1:3">
@@ -10571,7 +10529,7 @@
         <v>386</v>
       </c>
       <c r="C363" t="s">
-        <v>1408</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="364" spans="1:3">
@@ -10582,7 +10540,7 @@
         <v>387</v>
       </c>
       <c r="C364" t="s">
-        <v>1409</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="365" spans="1:3">
@@ -10593,7 +10551,7 @@
         <v>388</v>
       </c>
       <c r="C365" t="s">
-        <v>1410</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="366" spans="1:3">
@@ -10604,7 +10562,7 @@
         <v>389</v>
       </c>
       <c r="C366" t="s">
-        <v>1411</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="367" spans="1:3">
@@ -10615,7 +10573,7 @@
         <v>390</v>
       </c>
       <c r="C367" t="s">
-        <v>1412</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="368" spans="1:3">
@@ -10626,7 +10584,7 @@
         <v>391</v>
       </c>
       <c r="C368" t="s">
-        <v>1413</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="369" spans="1:3">
@@ -10637,7 +10595,7 @@
         <v>392</v>
       </c>
       <c r="C369" t="s">
-        <v>1414</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="370" spans="1:3">
@@ -10648,7 +10606,7 @@
         <v>393</v>
       </c>
       <c r="C370" t="s">
-        <v>1415</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="371" spans="1:3">
@@ -10659,7 +10617,7 @@
         <v>394</v>
       </c>
       <c r="C371" t="s">
-        <v>1416</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -10670,7 +10628,7 @@
         <v>395</v>
       </c>
       <c r="C372" t="s">
-        <v>1417</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="373" spans="1:3">
@@ -10681,7 +10639,7 @@
         <v>396</v>
       </c>
       <c r="C373" t="s">
-        <v>1418</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="374" spans="1:3">
@@ -10692,7 +10650,7 @@
         <v>397</v>
       </c>
       <c r="C374" t="s">
-        <v>1419</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="375" spans="1:3">
@@ -10703,7 +10661,7 @@
         <v>398</v>
       </c>
       <c r="C375" t="s">
-        <v>1420</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="376" spans="1:3">
@@ -10714,7 +10672,7 @@
         <v>399</v>
       </c>
       <c r="C376" t="s">
-        <v>1421</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="377" spans="1:3">
@@ -10725,7 +10683,7 @@
         <v>400</v>
       </c>
       <c r="C377" t="s">
-        <v>1422</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="378" spans="1:3">
@@ -10736,7 +10694,7 @@
         <v>401</v>
       </c>
       <c r="C378" t="s">
-        <v>1423</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="379" spans="1:3">
@@ -10747,7 +10705,7 @@
         <v>402</v>
       </c>
       <c r="C379" t="s">
-        <v>1424</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="380" spans="1:3">
@@ -10758,7 +10716,7 @@
         <v>403</v>
       </c>
       <c r="C380" t="s">
-        <v>1425</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="381" spans="1:3">
@@ -10769,7 +10727,7 @@
         <v>404</v>
       </c>
       <c r="C381" t="s">
-        <v>1426</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="382" spans="1:3">
@@ -10780,7 +10738,7 @@
         <v>405</v>
       </c>
       <c r="C382" t="s">
-        <v>1427</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="383" spans="1:3">
@@ -10791,7 +10749,7 @@
         <v>406</v>
       </c>
       <c r="C383" t="s">
-        <v>1428</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="384" spans="1:3">
@@ -10802,7 +10760,7 @@
         <v>407</v>
       </c>
       <c r="C384" t="s">
-        <v>1429</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="385" spans="1:3">
@@ -10813,7 +10771,7 @@
         <v>408</v>
       </c>
       <c r="C385" t="s">
-        <v>1430</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="386" spans="1:3">
@@ -10824,7 +10782,7 @@
         <v>409</v>
       </c>
       <c r="C386" t="s">
-        <v>1431</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="387" spans="1:3">
@@ -10835,7 +10793,7 @@
         <v>410</v>
       </c>
       <c r="C387" t="s">
-        <v>1432</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="388" spans="1:3">
@@ -10846,7 +10804,7 @@
         <v>411</v>
       </c>
       <c r="C388" t="s">
-        <v>1433</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="389" spans="1:3">
@@ -10857,7 +10815,7 @@
         <v>412</v>
       </c>
       <c r="C389" t="s">
-        <v>1434</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="390" spans="1:3">
@@ -10868,7 +10826,7 @@
         <v>413</v>
       </c>
       <c r="C390" t="s">
-        <v>1435</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="391" spans="1:3">
@@ -10879,7 +10837,7 @@
         <v>414</v>
       </c>
       <c r="C391" t="s">
-        <v>1436</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="392" spans="1:3">
@@ -10890,7 +10848,7 @@
         <v>415</v>
       </c>
       <c r="C392" t="s">
-        <v>1437</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="393" spans="1:3">
@@ -10901,7 +10859,7 @@
         <v>416</v>
       </c>
       <c r="C393" t="s">
-        <v>1438</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="394" spans="1:3">
@@ -10912,7 +10870,7 @@
         <v>417</v>
       </c>
       <c r="C394" t="s">
-        <v>1439</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="395" spans="1:3">
@@ -10923,7 +10881,7 @@
         <v>418</v>
       </c>
       <c r="C395" t="s">
-        <v>1440</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="396" spans="1:3">
@@ -10934,7 +10892,7 @@
         <v>419</v>
       </c>
       <c r="C396" t="s">
-        <v>1441</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="397" spans="1:3">
@@ -10945,7 +10903,7 @@
         <v>420</v>
       </c>
       <c r="C397" t="s">
-        <v>1442</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="398" spans="1:3">
@@ -10956,7 +10914,7 @@
         <v>421</v>
       </c>
       <c r="C398" t="s">
-        <v>1443</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="399" spans="1:3">
@@ -10967,7 +10925,7 @@
         <v>422</v>
       </c>
       <c r="C399" t="s">
-        <v>1444</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="400" spans="1:3">
@@ -10978,7 +10936,7 @@
         <v>423</v>
       </c>
       <c r="C400" t="s">
-        <v>1445</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="401" spans="1:3">
@@ -10989,7 +10947,7 @@
         <v>424</v>
       </c>
       <c r="C401" t="s">
-        <v>1446</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="402" spans="1:3">
@@ -11000,7 +10958,7 @@
         <v>425</v>
       </c>
       <c r="C402" t="s">
-        <v>1447</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="403" spans="1:3">
@@ -11011,7 +10969,7 @@
         <v>426</v>
       </c>
       <c r="C403" t="s">
-        <v>1448</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="404" spans="1:3">
@@ -11022,7 +10980,7 @@
         <v>427</v>
       </c>
       <c r="C404" t="s">
-        <v>1449</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="405" spans="1:3">
@@ -11033,7 +10991,7 @@
         <v>428</v>
       </c>
       <c r="C405" t="s">
-        <v>1450</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="406" spans="1:3">
@@ -11044,7 +11002,7 @@
         <v>429</v>
       </c>
       <c r="C406" t="s">
-        <v>1451</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="407" spans="1:3">
@@ -11055,7 +11013,7 @@
         <v>430</v>
       </c>
       <c r="C407" t="s">
-        <v>1452</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="408" spans="1:3">
@@ -11066,7 +11024,7 @@
         <v>431</v>
       </c>
       <c r="C408" t="s">
-        <v>1453</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="409" spans="1:3">
@@ -11077,7 +11035,7 @@
         <v>432</v>
       </c>
       <c r="C409" t="s">
-        <v>1454</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="410" spans="1:3">
@@ -11088,7 +11046,7 @@
         <v>433</v>
       </c>
       <c r="C410" t="s">
-        <v>1455</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="411" spans="1:3">
@@ -11099,7 +11057,7 @@
         <v>434</v>
       </c>
       <c r="C411" t="s">
-        <v>1456</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="412" spans="1:3">
@@ -11110,7 +11068,7 @@
         <v>435</v>
       </c>
       <c r="C412" t="s">
-        <v>1457</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="413" spans="1:3">
@@ -11121,7 +11079,7 @@
         <v>436</v>
       </c>
       <c r="C413" t="s">
-        <v>1458</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="414" spans="1:3">
@@ -11132,7 +11090,7 @@
         <v>437</v>
       </c>
       <c r="C414" t="s">
-        <v>1459</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="415" spans="1:3">
@@ -11143,7 +11101,7 @@
         <v>438</v>
       </c>
       <c r="C415" t="s">
-        <v>1460</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="416" spans="1:3">
@@ -11154,7 +11112,7 @@
         <v>439</v>
       </c>
       <c r="C416" t="s">
-        <v>1461</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="417" spans="1:3">
@@ -11165,7 +11123,7 @@
         <v>440</v>
       </c>
       <c r="C417" t="s">
-        <v>1462</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="418" spans="1:3">
@@ -11176,7 +11134,7 @@
         <v>441</v>
       </c>
       <c r="C418" t="s">
-        <v>1463</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="419" spans="1:3">
@@ -11187,7 +11145,7 @@
         <v>442</v>
       </c>
       <c r="C419" t="s">
-        <v>1464</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="420" spans="1:3">
@@ -11198,7 +11156,7 @@
         <v>443</v>
       </c>
       <c r="C420" t="s">
-        <v>1465</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="421" spans="1:3">
@@ -11209,7 +11167,7 @@
         <v>444</v>
       </c>
       <c r="C421" t="s">
-        <v>1466</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="422" spans="1:3">
@@ -11220,7 +11178,7 @@
         <v>445</v>
       </c>
       <c r="C422" t="s">
-        <v>1467</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="423" spans="1:3">
@@ -11231,7 +11189,7 @@
         <v>446</v>
       </c>
       <c r="C423" t="s">
-        <v>1468</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="424" spans="1:3">
@@ -11242,7 +11200,7 @@
         <v>447</v>
       </c>
       <c r="C424" t="s">
-        <v>1469</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="425" spans="1:3">
@@ -11253,7 +11211,7 @@
         <v>448</v>
       </c>
       <c r="C425" t="s">
-        <v>1470</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="426" spans="1:3">
@@ -11264,7 +11222,7 @@
         <v>449</v>
       </c>
       <c r="C426" t="s">
-        <v>1471</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="427" spans="1:3">
@@ -11275,7 +11233,7 @@
         <v>450</v>
       </c>
       <c r="C427" t="s">
-        <v>1472</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="428" spans="1:3">
@@ -11286,7 +11244,7 @@
         <v>451</v>
       </c>
       <c r="C428" t="s">
-        <v>1473</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="429" spans="1:3">
@@ -11297,7 +11255,7 @@
         <v>452</v>
       </c>
       <c r="C429" t="s">
-        <v>1474</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="430" spans="1:3">
@@ -11308,7 +11266,7 @@
         <v>453</v>
       </c>
       <c r="C430" t="s">
-        <v>1475</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="431" spans="1:3">
@@ -11319,7 +11277,7 @@
         <v>454</v>
       </c>
       <c r="C431" t="s">
-        <v>1476</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="432" spans="1:3">
@@ -11330,7 +11288,7 @@
         <v>455</v>
       </c>
       <c r="C432" t="s">
-        <v>1477</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="433" spans="1:3">
@@ -11341,7 +11299,7 @@
         <v>456</v>
       </c>
       <c r="C433" t="s">
-        <v>1478</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="434" spans="1:3">
@@ -11352,7 +11310,7 @@
         <v>457</v>
       </c>
       <c r="C434" t="s">
-        <v>1479</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="435" spans="1:3">
@@ -11363,7 +11321,7 @@
         <v>458</v>
       </c>
       <c r="C435" t="s">
-        <v>1480</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="436" spans="1:3">
@@ -11374,7 +11332,7 @@
         <v>459</v>
       </c>
       <c r="C436" t="s">
-        <v>1481</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="437" spans="1:3">
@@ -11385,7 +11343,7 @@
         <v>460</v>
       </c>
       <c r="C437" t="s">
-        <v>1482</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="438" spans="1:3">
@@ -11396,7 +11354,7 @@
         <v>461</v>
       </c>
       <c r="C438" t="s">
-        <v>1483</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="439" spans="1:3">
@@ -11407,7 +11365,7 @@
         <v>462</v>
       </c>
       <c r="C439" t="s">
-        <v>1484</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="440" spans="1:3">
@@ -11418,7 +11376,7 @@
         <v>463</v>
       </c>
       <c r="C440" t="s">
-        <v>1485</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="441" spans="1:3">
@@ -11429,7 +11387,7 @@
         <v>464</v>
       </c>
       <c r="C441" t="s">
-        <v>1486</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="442" spans="1:3">
@@ -11440,7 +11398,7 @@
         <v>465</v>
       </c>
       <c r="C442" t="s">
-        <v>1487</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="443" spans="1:3">
@@ -11451,7 +11409,7 @@
         <v>466</v>
       </c>
       <c r="C443" t="s">
-        <v>1488</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="444" spans="1:3">
@@ -11462,7 +11420,7 @@
         <v>467</v>
       </c>
       <c r="C444" t="s">
-        <v>1489</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="445" spans="1:3">
@@ -11473,7 +11431,7 @@
         <v>468</v>
       </c>
       <c r="C445" t="s">
-        <v>1490</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="446" spans="1:3">
@@ -11484,7 +11442,7 @@
         <v>469</v>
       </c>
       <c r="C446" t="s">
-        <v>1491</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="447" spans="1:3">
@@ -11495,7 +11453,7 @@
         <v>470</v>
       </c>
       <c r="C447" t="s">
-        <v>1492</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="448" spans="1:3">
@@ -11506,7 +11464,7 @@
         <v>471</v>
       </c>
       <c r="C448" t="s">
-        <v>1493</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="449" spans="1:3">
@@ -11517,7 +11475,7 @@
         <v>472</v>
       </c>
       <c r="C449" t="s">
-        <v>1494</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="450" spans="1:3">
@@ -11528,7 +11486,7 @@
         <v>473</v>
       </c>
       <c r="C450" t="s">
-        <v>1495</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="451" spans="1:3">
@@ -11539,7 +11497,7 @@
         <v>474</v>
       </c>
       <c r="C451" t="s">
-        <v>1496</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="452" spans="1:3">
@@ -11550,7 +11508,7 @@
         <v>475</v>
       </c>
       <c r="C452" t="s">
-        <v>1497</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="453" spans="1:3">
@@ -11561,7 +11519,7 @@
         <v>476</v>
       </c>
       <c r="C453" t="s">
-        <v>1498</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="454" spans="1:3">
@@ -11572,7 +11530,7 @@
         <v>477</v>
       </c>
       <c r="C454" t="s">
-        <v>1499</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="455" spans="1:3">
@@ -11583,7 +11541,7 @@
         <v>478</v>
       </c>
       <c r="C455" t="s">
-        <v>1500</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="456" spans="1:3">
@@ -11594,7 +11552,7 @@
         <v>479</v>
       </c>
       <c r="C456" t="s">
-        <v>1501</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="457" spans="1:3">
@@ -11605,7 +11563,7 @@
         <v>480</v>
       </c>
       <c r="C457" t="s">
-        <v>1502</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="458" spans="1:3">
@@ -11616,7 +11574,7 @@
         <v>481</v>
       </c>
       <c r="C458" t="s">
-        <v>1503</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="459" spans="1:3">
@@ -11627,7 +11585,7 @@
         <v>482</v>
       </c>
       <c r="C459" t="s">
-        <v>1504</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="460" spans="1:3">
@@ -11638,7 +11596,7 @@
         <v>483</v>
       </c>
       <c r="C460" t="s">
-        <v>1505</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="461" spans="1:3">
@@ -11649,7 +11607,7 @@
         <v>484</v>
       </c>
       <c r="C461" t="s">
-        <v>1474</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="462" spans="1:3">
@@ -11660,7 +11618,7 @@
         <v>485</v>
       </c>
       <c r="C462" t="s">
-        <v>1466</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="463" spans="1:3">
@@ -11671,7 +11629,7 @@
         <v>486</v>
       </c>
       <c r="C463" t="s">
-        <v>1506</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="464" spans="1:3">
@@ -11682,7 +11640,7 @@
         <v>487</v>
       </c>
       <c r="C464" t="s">
-        <v>1507</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="465" spans="1:3">
@@ -11693,7 +11651,7 @@
         <v>488</v>
       </c>
       <c r="C465" t="s">
-        <v>1508</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="466" spans="1:3">
@@ -11704,7 +11662,7 @@
         <v>489</v>
       </c>
       <c r="C466" t="s">
-        <v>1509</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="467" spans="1:3">
@@ -11715,7 +11673,7 @@
         <v>490</v>
       </c>
       <c r="C467" t="s">
-        <v>1510</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="468" spans="1:3">
@@ -11726,7 +11684,7 @@
         <v>491</v>
       </c>
       <c r="C468" t="s">
-        <v>1511</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="469" spans="1:3">
@@ -11737,7 +11695,7 @@
         <v>492</v>
       </c>
       <c r="C469" t="s">
-        <v>1512</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="470" spans="1:3">
@@ -11748,7 +11706,7 @@
         <v>493</v>
       </c>
       <c r="C470" t="s">
-        <v>1513</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="471" spans="1:3">
@@ -11759,7 +11717,7 @@
         <v>494</v>
       </c>
       <c r="C471" t="s">
-        <v>1514</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="472" spans="1:3">
@@ -11770,7 +11728,7 @@
         <v>495</v>
       </c>
       <c r="C472" t="s">
-        <v>1515</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="473" spans="1:3">
@@ -11781,7 +11739,7 @@
         <v>496</v>
       </c>
       <c r="C473" t="s">
-        <v>1516</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="474" spans="1:3">
@@ -11792,7 +11750,7 @@
         <v>497</v>
       </c>
       <c r="C474" t="s">
-        <v>1517</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="475" spans="1:3">
@@ -11803,7 +11761,7 @@
         <v>498</v>
       </c>
       <c r="C475" t="s">
-        <v>1518</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="476" spans="1:3">
@@ -11814,7 +11772,7 @@
         <v>499</v>
       </c>
       <c r="C476" t="s">
-        <v>1519</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="477" spans="1:3">
@@ -11825,7 +11783,7 @@
         <v>500</v>
       </c>
       <c r="C477" t="s">
-        <v>1520</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="478" spans="1:3">
@@ -11836,7 +11794,7 @@
         <v>501</v>
       </c>
       <c r="C478" t="s">
-        <v>1521</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="479" spans="1:3">
@@ -11847,7 +11805,7 @@
         <v>502</v>
       </c>
       <c r="C479" t="s">
-        <v>1522</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="480" spans="1:3">
@@ -11858,7 +11816,7 @@
         <v>503</v>
       </c>
       <c r="C480" t="s">
-        <v>1523</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="481" spans="1:3">
@@ -11869,7 +11827,7 @@
         <v>504</v>
       </c>
       <c r="C481" t="s">
-        <v>1524</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="482" spans="1:3">
@@ -11880,7 +11838,7 @@
         <v>505</v>
       </c>
       <c r="C482" t="s">
-        <v>1525</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="483" spans="1:3">
@@ -11891,7 +11849,7 @@
         <v>506</v>
       </c>
       <c r="C483" t="s">
-        <v>1526</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="484" spans="1:3">
@@ -11902,7 +11860,7 @@
         <v>507</v>
       </c>
       <c r="C484" t="s">
-        <v>1527</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="485" spans="1:3">
@@ -11913,7 +11871,7 @@
         <v>508</v>
       </c>
       <c r="C485" t="s">
-        <v>1528</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="486" spans="1:3">
@@ -11924,7 +11882,7 @@
         <v>509</v>
       </c>
       <c r="C486" t="s">
-        <v>1529</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="487" spans="1:3">
@@ -11935,7 +11893,7 @@
         <v>510</v>
       </c>
       <c r="C487" t="s">
-        <v>1530</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="488" spans="1:3">
@@ -11946,7 +11904,7 @@
         <v>511</v>
       </c>
       <c r="C488" t="s">
-        <v>1531</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="489" spans="1:3">
@@ -11957,7 +11915,7 @@
         <v>512</v>
       </c>
       <c r="C489" t="s">
-        <v>1532</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="490" spans="1:3">
@@ -11968,7 +11926,7 @@
         <v>513</v>
       </c>
       <c r="C490" t="s">
-        <v>1533</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="491" spans="1:3">
@@ -11979,7 +11937,7 @@
         <v>514</v>
       </c>
       <c r="C491" t="s">
-        <v>1534</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="492" spans="1:3">
@@ -11990,7 +11948,7 @@
         <v>515</v>
       </c>
       <c r="C492" t="s">
-        <v>1535</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="493" spans="1:3">
@@ -12001,7 +11959,7 @@
         <v>516</v>
       </c>
       <c r="C493" t="s">
-        <v>1536</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="494" spans="1:3">
@@ -12012,7 +11970,7 @@
         <v>517</v>
       </c>
       <c r="C494" t="s">
-        <v>1537</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="495" spans="1:3">
@@ -12023,7 +11981,7 @@
         <v>518</v>
       </c>
       <c r="C495" t="s">
-        <v>1538</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="496" spans="1:3">
@@ -12034,7 +11992,7 @@
         <v>519</v>
       </c>
       <c r="C496" t="s">
-        <v>1539</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="497" spans="1:3">
@@ -12045,7 +12003,7 @@
         <v>520</v>
       </c>
       <c r="C497" t="s">
-        <v>1540</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="498" spans="1:3">
@@ -12056,7 +12014,7 @@
         <v>521</v>
       </c>
       <c r="C498" t="s">
-        <v>1541</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="499" spans="1:3">
@@ -12067,7 +12025,7 @@
         <v>522</v>
       </c>
       <c r="C499" t="s">
-        <v>1542</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="500" spans="1:3">
@@ -12078,7 +12036,7 @@
         <v>523</v>
       </c>
       <c r="C500" t="s">
-        <v>1543</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="501" spans="1:3">
@@ -12089,7 +12047,7 @@
         <v>524</v>
       </c>
       <c r="C501" t="s">
-        <v>1544</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="502" spans="1:3">
@@ -12100,7 +12058,7 @@
         <v>525</v>
       </c>
       <c r="C502" t="s">
-        <v>1545</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="503" spans="1:3">
@@ -12111,7 +12069,7 @@
         <v>526</v>
       </c>
       <c r="C503" t="s">
-        <v>1546</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="504" spans="1:3">
@@ -12122,7 +12080,7 @@
         <v>527</v>
       </c>
       <c r="C504" t="s">
-        <v>1547</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="505" spans="1:3">
@@ -12133,7 +12091,7 @@
         <v>528</v>
       </c>
       <c r="C505" t="s">
-        <v>1548</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="506" spans="1:3">
@@ -12144,7 +12102,7 @@
         <v>529</v>
       </c>
       <c r="C506" t="s">
-        <v>1549</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="507" spans="1:3">
@@ -12155,7 +12113,7 @@
         <v>530</v>
       </c>
       <c r="C507" t="s">
-        <v>1550</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="508" spans="1:3">
@@ -12166,7 +12124,7 @@
         <v>531</v>
       </c>
       <c r="C508" t="s">
-        <v>1551</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="509" spans="1:3">
@@ -12177,7 +12135,7 @@
         <v>532</v>
       </c>
       <c r="C509" t="s">
-        <v>1552</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="510" spans="1:3">
@@ -12188,7 +12146,7 @@
         <v>533</v>
       </c>
       <c r="C510" t="s">
-        <v>1553</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="511" spans="1:3">
@@ -12199,7 +12157,7 @@
         <v>534</v>
       </c>
       <c r="C511" t="s">
-        <v>1554</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="512" spans="1:3">
@@ -12210,7 +12168,7 @@
         <v>535</v>
       </c>
       <c r="C512" t="s">
-        <v>1555</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="513" spans="1:3">
@@ -12221,7 +12179,7 @@
         <v>536</v>
       </c>
       <c r="C513" t="s">
-        <v>1556</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="514" spans="1:3">
@@ -12232,7 +12190,7 @@
         <v>537</v>
       </c>
       <c r="C514" t="s">
-        <v>1557</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="515" spans="1:3">
@@ -12243,7 +12201,7 @@
         <v>538</v>
       </c>
       <c r="C515" t="s">
-        <v>1558</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="516" spans="1:3">
@@ -12254,7 +12212,7 @@
         <v>539</v>
       </c>
       <c r="C516" t="s">
-        <v>1559</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="517" spans="1:3">
@@ -12265,7 +12223,7 @@
         <v>540</v>
       </c>
       <c r="C517" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="518" spans="1:3">
@@ -12276,7 +12234,7 @@
         <v>541</v>
       </c>
       <c r="C518" t="s">
-        <v>1561</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="519" spans="1:3">
@@ -12287,7 +12245,7 @@
         <v>542</v>
       </c>
       <c r="C519" t="s">
-        <v>1562</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="520" spans="1:3">
@@ -12298,7 +12256,7 @@
         <v>543</v>
       </c>
       <c r="C520" t="s">
-        <v>1563</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="521" spans="1:3">
@@ -12309,7 +12267,7 @@
         <v>544</v>
       </c>
       <c r="C521" t="s">
-        <v>1564</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="522" spans="1:3">
@@ -12320,7 +12278,7 @@
         <v>545</v>
       </c>
       <c r="C522" t="s">
-        <v>1565</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="523" spans="1:3">
@@ -12331,7 +12289,7 @@
         <v>546</v>
       </c>
       <c r="C523" t="s">
-        <v>1566</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="524" spans="1:3">
@@ -12342,7 +12300,7 @@
         <v>547</v>
       </c>
       <c r="C524" t="s">
-        <v>1567</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="525" spans="1:3">
@@ -12353,29 +12311,29 @@
         <v>548</v>
       </c>
       <c r="C525" t="s">
-        <v>1568</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="526" spans="1:3">
       <c r="A526" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B526" t="s">
         <v>549</v>
       </c>
       <c r="C526" t="s">
-        <v>1569</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="527" spans="1:3">
       <c r="A527" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B527" t="s">
         <v>550</v>
       </c>
       <c r="C527" t="s">
-        <v>1570</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="528" spans="1:3">
@@ -12386,7 +12344,7 @@
         <v>551</v>
       </c>
       <c r="C528" t="s">
-        <v>1571</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="529" spans="1:3">
@@ -12397,7 +12355,7 @@
         <v>552</v>
       </c>
       <c r="C529" t="s">
-        <v>1572</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="530" spans="1:3">
@@ -12408,7 +12366,7 @@
         <v>553</v>
       </c>
       <c r="C530" t="s">
-        <v>1573</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="531" spans="1:3">
@@ -12419,7 +12377,7 @@
         <v>554</v>
       </c>
       <c r="C531" t="s">
-        <v>1574</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="532" spans="1:3">
@@ -12430,7 +12388,7 @@
         <v>555</v>
       </c>
       <c r="C532" t="s">
-        <v>1575</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="533" spans="1:3">
@@ -12441,73 +12399,73 @@
         <v>556</v>
       </c>
       <c r="C533" t="s">
-        <v>1576</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="534" spans="1:3">
       <c r="A534" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B534" t="s">
         <v>557</v>
       </c>
       <c r="C534" t="s">
-        <v>1577</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="535" spans="1:3">
       <c r="A535" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B535" t="s">
         <v>558</v>
       </c>
       <c r="C535" t="s">
-        <v>1578</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="536" spans="1:3">
       <c r="A536" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B536" t="s">
         <v>559</v>
       </c>
       <c r="C536" t="s">
-        <v>1579</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="537" spans="1:3">
       <c r="A537" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B537" t="s">
         <v>560</v>
       </c>
       <c r="C537" t="s">
-        <v>1580</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="538" spans="1:3">
       <c r="A538" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B538" t="s">
         <v>561</v>
       </c>
       <c r="C538" t="s">
-        <v>1581</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="539" spans="1:3">
       <c r="A539" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B539" t="s">
         <v>562</v>
       </c>
       <c r="C539" t="s">
-        <v>1582</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="540" spans="1:3">
@@ -12518,7 +12476,7 @@
         <v>563</v>
       </c>
       <c r="C540" t="s">
-        <v>1583</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="541" spans="1:3">
@@ -12529,7 +12487,7 @@
         <v>564</v>
       </c>
       <c r="C541" t="s">
-        <v>1584</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="542" spans="1:3">
@@ -12540,7 +12498,7 @@
         <v>565</v>
       </c>
       <c r="C542" t="s">
-        <v>1585</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="543" spans="1:3">
@@ -12551,7 +12509,7 @@
         <v>566</v>
       </c>
       <c r="C543" t="s">
-        <v>1586</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="544" spans="1:3">
@@ -12562,7 +12520,7 @@
         <v>567</v>
       </c>
       <c r="C544" t="s">
-        <v>1587</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="545" spans="1:3">
@@ -12573,7 +12531,7 @@
         <v>568</v>
       </c>
       <c r="C545" t="s">
-        <v>1588</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="546" spans="1:3">
@@ -12584,7 +12542,7 @@
         <v>569</v>
       </c>
       <c r="C546" t="s">
-        <v>1589</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="547" spans="1:3">
@@ -12595,7 +12553,7 @@
         <v>570</v>
       </c>
       <c r="C547" t="s">
-        <v>1590</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="548" spans="1:3">
@@ -12606,7 +12564,7 @@
         <v>571</v>
       </c>
       <c r="C548" t="s">
-        <v>1591</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="549" spans="1:3">
@@ -12617,7 +12575,7 @@
         <v>572</v>
       </c>
       <c r="C549" t="s">
-        <v>1592</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="550" spans="1:3">
@@ -12628,7 +12586,7 @@
         <v>573</v>
       </c>
       <c r="C550" t="s">
-        <v>1593</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="551" spans="1:3">
@@ -12639,7 +12597,7 @@
         <v>574</v>
       </c>
       <c r="C551" t="s">
-        <v>1594</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="552" spans="1:3">
@@ -12650,7 +12608,7 @@
         <v>575</v>
       </c>
       <c r="C552" t="s">
-        <v>1595</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="553" spans="1:3">
@@ -12661,7 +12619,7 @@
         <v>576</v>
       </c>
       <c r="C553" t="s">
-        <v>1596</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="554" spans="1:3">
@@ -12672,7 +12630,7 @@
         <v>577</v>
       </c>
       <c r="C554" t="s">
-        <v>1597</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="555" spans="1:3">
@@ -12683,7 +12641,7 @@
         <v>578</v>
       </c>
       <c r="C555" t="s">
-        <v>1598</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="556" spans="1:3">
@@ -12694,7 +12652,7 @@
         <v>579</v>
       </c>
       <c r="C556" t="s">
-        <v>1599</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="557" spans="1:3">
@@ -12705,7 +12663,7 @@
         <v>580</v>
       </c>
       <c r="C557" t="s">
-        <v>1600</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="558" spans="1:3">
@@ -12716,7 +12674,7 @@
         <v>581</v>
       </c>
       <c r="C558" t="s">
-        <v>1601</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="559" spans="1:3">
@@ -12727,7 +12685,7 @@
         <v>582</v>
       </c>
       <c r="C559" t="s">
-        <v>1602</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="560" spans="1:3">
@@ -12738,7 +12696,7 @@
         <v>583</v>
       </c>
       <c r="C560" t="s">
-        <v>1603</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="561" spans="1:3">
@@ -12749,7 +12707,7 @@
         <v>584</v>
       </c>
       <c r="C561" t="s">
-        <v>1604</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="562" spans="1:3">
@@ -12760,7 +12718,7 @@
         <v>585</v>
       </c>
       <c r="C562" t="s">
-        <v>1605</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="563" spans="1:3">
@@ -12771,7 +12729,7 @@
         <v>586</v>
       </c>
       <c r="C563" t="s">
-        <v>1606</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="564" spans="1:3">
@@ -12782,7 +12740,7 @@
         <v>587</v>
       </c>
       <c r="C564" t="s">
-        <v>1607</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="565" spans="1:3">
@@ -12793,7 +12751,7 @@
         <v>588</v>
       </c>
       <c r="C565" t="s">
-        <v>1608</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="566" spans="1:3">
@@ -12804,7 +12762,7 @@
         <v>589</v>
       </c>
       <c r="C566" t="s">
-        <v>1609</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="567" spans="1:3">
@@ -12815,7 +12773,7 @@
         <v>590</v>
       </c>
       <c r="C567" t="s">
-        <v>1610</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="568" spans="1:3">
@@ -12826,7 +12784,7 @@
         <v>591</v>
       </c>
       <c r="C568" t="s">
-        <v>1611</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="569" spans="1:3">
@@ -12837,7 +12795,7 @@
         <v>592</v>
       </c>
       <c r="C569" t="s">
-        <v>1612</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="570" spans="1:3">
@@ -12848,7 +12806,7 @@
         <v>593</v>
       </c>
       <c r="C570" t="s">
-        <v>1613</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="571" spans="1:3">
@@ -12859,7 +12817,7 @@
         <v>594</v>
       </c>
       <c r="C571" t="s">
-        <v>1614</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="572" spans="1:3">
@@ -12870,7 +12828,7 @@
         <v>595</v>
       </c>
       <c r="C572" t="s">
-        <v>1615</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="573" spans="1:3">
@@ -12881,7 +12839,7 @@
         <v>596</v>
       </c>
       <c r="C573" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="574" spans="1:3">
@@ -12892,7 +12850,7 @@
         <v>597</v>
       </c>
       <c r="C574" t="s">
-        <v>1617</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="575" spans="1:3">
@@ -12903,7 +12861,7 @@
         <v>598</v>
       </c>
       <c r="C575" t="s">
-        <v>1618</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="576" spans="1:3">
@@ -12914,73 +12872,73 @@
         <v>599</v>
       </c>
       <c r="C576" t="s">
-        <v>1588</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="577" spans="1:3">
       <c r="A577" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B577" t="s">
         <v>600</v>
       </c>
       <c r="C577" t="s">
-        <v>1619</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="578" spans="1:3">
       <c r="A578" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B578" t="s">
         <v>601</v>
       </c>
       <c r="C578" t="s">
-        <v>1620</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="579" spans="1:3">
       <c r="A579" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B579" t="s">
         <v>602</v>
       </c>
       <c r="C579" t="s">
-        <v>1621</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="580" spans="1:3">
       <c r="A580" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B580" t="s">
         <v>603</v>
       </c>
       <c r="C580" t="s">
-        <v>1622</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="581" spans="1:3">
       <c r="A581" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B581" t="s">
         <v>604</v>
       </c>
       <c r="C581" t="s">
-        <v>1623</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="582" spans="1:3">
       <c r="A582" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B582" t="s">
         <v>605</v>
       </c>
       <c r="C582" t="s">
-        <v>1624</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="583" spans="1:3">
@@ -12991,73 +12949,73 @@
         <v>606</v>
       </c>
       <c r="C583" t="s">
-        <v>1625</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="584" spans="1:3">
       <c r="A584" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B584" t="s">
         <v>607</v>
       </c>
       <c r="C584" t="s">
-        <v>1626</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="585" spans="1:3">
       <c r="A585" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B585" t="s">
         <v>608</v>
       </c>
       <c r="C585" t="s">
-        <v>1627</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="586" spans="1:3">
       <c r="A586" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B586" t="s">
         <v>609</v>
       </c>
       <c r="C586" t="s">
-        <v>1628</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="587" spans="1:3">
       <c r="A587" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B587" t="s">
         <v>610</v>
       </c>
       <c r="C587" t="s">
-        <v>1629</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="588" spans="1:3">
       <c r="A588" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B588" t="s">
         <v>611</v>
       </c>
       <c r="C588" t="s">
-        <v>1630</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="589" spans="1:3">
       <c r="A589" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B589" t="s">
         <v>612</v>
       </c>
       <c r="C589" t="s">
-        <v>1631</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="590" spans="1:3">
@@ -13068,7 +13026,7 @@
         <v>613</v>
       </c>
       <c r="C590" t="s">
-        <v>1632</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="591" spans="1:3">
@@ -13079,7 +13037,7 @@
         <v>614</v>
       </c>
       <c r="C591" t="s">
-        <v>1633</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="592" spans="1:3">
@@ -13090,7 +13048,7 @@
         <v>615</v>
       </c>
       <c r="C592" t="s">
-        <v>1634</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="593" spans="1:3">
@@ -13101,7 +13059,7 @@
         <v>616</v>
       </c>
       <c r="C593" t="s">
-        <v>1635</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="594" spans="1:3">
@@ -13112,7 +13070,7 @@
         <v>617</v>
       </c>
       <c r="C594" t="s">
-        <v>1636</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="595" spans="1:3">
@@ -13123,7 +13081,7 @@
         <v>618</v>
       </c>
       <c r="C595" t="s">
-        <v>1637</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="596" spans="1:3">
@@ -13134,7 +13092,7 @@
         <v>619</v>
       </c>
       <c r="C596" t="s">
-        <v>1638</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="597" spans="1:3">
@@ -13145,7 +13103,7 @@
         <v>620</v>
       </c>
       <c r="C597" t="s">
-        <v>1639</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="598" spans="1:3">
@@ -13156,7 +13114,7 @@
         <v>621</v>
       </c>
       <c r="C598" t="s">
-        <v>1640</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="599" spans="1:3">
@@ -13167,7 +13125,7 @@
         <v>622</v>
       </c>
       <c r="C599" t="s">
-        <v>1641</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="600" spans="1:3">
@@ -13178,7 +13136,7 @@
         <v>623</v>
       </c>
       <c r="C600" t="s">
-        <v>1642</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="601" spans="1:3">
@@ -13189,7 +13147,7 @@
         <v>624</v>
       </c>
       <c r="C601" t="s">
-        <v>1643</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="602" spans="1:3">
@@ -13200,7 +13158,7 @@
         <v>625</v>
       </c>
       <c r="C602" t="s">
-        <v>1644</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="603" spans="1:3">
@@ -13211,7 +13169,7 @@
         <v>626</v>
       </c>
       <c r="C603" t="s">
-        <v>1645</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="604" spans="1:3">
@@ -13222,7 +13180,7 @@
         <v>627</v>
       </c>
       <c r="C604" t="s">
-        <v>1646</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="605" spans="1:3">
@@ -13233,7 +13191,7 @@
         <v>628</v>
       </c>
       <c r="C605" t="s">
-        <v>1647</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="606" spans="1:3">
@@ -13244,7 +13202,7 @@
         <v>629</v>
       </c>
       <c r="C606" t="s">
-        <v>1648</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="607" spans="1:3">
@@ -13255,7 +13213,7 @@
         <v>630</v>
       </c>
       <c r="C607" t="s">
-        <v>1649</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="608" spans="1:3">
@@ -13266,7 +13224,7 @@
         <v>631</v>
       </c>
       <c r="C608" t="s">
-        <v>1650</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="609" spans="1:3">
@@ -13277,73 +13235,73 @@
         <v>632</v>
       </c>
       <c r="C609" t="s">
-        <v>1651</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="610" spans="1:3">
       <c r="A610" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B610" t="s">
         <v>633</v>
       </c>
       <c r="C610" t="s">
-        <v>1652</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="611" spans="1:3">
       <c r="A611" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B611" t="s">
         <v>634</v>
       </c>
       <c r="C611" t="s">
-        <v>1653</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="612" spans="1:3">
       <c r="A612" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B612" t="s">
         <v>635</v>
       </c>
       <c r="C612" t="s">
-        <v>1654</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="613" spans="1:3">
       <c r="A613" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B613" t="s">
         <v>636</v>
       </c>
       <c r="C613" t="s">
-        <v>1655</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="614" spans="1:3">
       <c r="A614" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B614" t="s">
         <v>637</v>
       </c>
       <c r="C614" t="s">
-        <v>1656</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="615" spans="1:3">
       <c r="A615" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B615" t="s">
         <v>638</v>
       </c>
       <c r="C615" t="s">
-        <v>1657</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="616" spans="1:3">
@@ -13354,7 +13312,7 @@
         <v>639</v>
       </c>
       <c r="C616" t="s">
-        <v>1658</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="617" spans="1:3">
@@ -13365,7 +13323,7 @@
         <v>640</v>
       </c>
       <c r="C617" t="s">
-        <v>1659</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="618" spans="1:3">
@@ -13376,7 +13334,7 @@
         <v>641</v>
       </c>
       <c r="C618" t="s">
-        <v>1660</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="619" spans="1:3">
@@ -13387,7 +13345,7 @@
         <v>642</v>
       </c>
       <c r="C619" t="s">
-        <v>1661</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="620" spans="1:3">
@@ -13398,73 +13356,73 @@
         <v>643</v>
       </c>
       <c r="C620" t="s">
-        <v>1662</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="621" spans="1:3">
       <c r="A621" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B621" t="s">
         <v>644</v>
       </c>
       <c r="C621" t="s">
-        <v>1663</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="622" spans="1:3">
       <c r="A622" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B622" t="s">
         <v>645</v>
       </c>
       <c r="C622" t="s">
-        <v>1664</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="623" spans="1:3">
       <c r="A623" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B623" t="s">
         <v>646</v>
       </c>
       <c r="C623" t="s">
-        <v>1665</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="624" spans="1:3">
       <c r="A624" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B624" t="s">
         <v>647</v>
       </c>
       <c r="C624" t="s">
-        <v>1666</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="625" spans="1:3">
       <c r="A625" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B625" t="s">
         <v>648</v>
       </c>
       <c r="C625" t="s">
-        <v>1667</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="626" spans="1:3">
       <c r="A626" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B626" t="s">
         <v>649</v>
       </c>
       <c r="C626" t="s">
-        <v>1668</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="627" spans="1:3">
@@ -13475,7 +13433,7 @@
         <v>650</v>
       </c>
       <c r="C627" t="s">
-        <v>1669</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="628" spans="1:3">
@@ -13486,7 +13444,7 @@
         <v>651</v>
       </c>
       <c r="C628" t="s">
-        <v>1670</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="629" spans="1:3">
@@ -13497,7 +13455,7 @@
         <v>652</v>
       </c>
       <c r="C629" t="s">
-        <v>1671</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="630" spans="1:3">
@@ -13508,7 +13466,7 @@
         <v>653</v>
       </c>
       <c r="C630" t="s">
-        <v>1672</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="631" spans="1:3">
@@ -13519,7 +13477,7 @@
         <v>654</v>
       </c>
       <c r="C631" t="s">
-        <v>1673</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="632" spans="1:3">
@@ -13530,7 +13488,7 @@
         <v>655</v>
       </c>
       <c r="C632" t="s">
-        <v>1674</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="633" spans="1:3">
@@ -13541,7 +13499,7 @@
         <v>656</v>
       </c>
       <c r="C633" t="s">
-        <v>1675</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="634" spans="1:3">
@@ -13552,7 +13510,7 @@
         <v>657</v>
       </c>
       <c r="C634" t="s">
-        <v>1676</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="635" spans="1:3">
@@ -13563,7 +13521,7 @@
         <v>658</v>
       </c>
       <c r="C635" t="s">
-        <v>1677</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="636" spans="1:3">
@@ -13574,7 +13532,7 @@
         <v>659</v>
       </c>
       <c r="C636" t="s">
-        <v>1678</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="637" spans="1:3">
@@ -13585,7 +13543,7 @@
         <v>660</v>
       </c>
       <c r="C637" t="s">
-        <v>1679</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="638" spans="1:3">
@@ -13596,7 +13554,7 @@
         <v>661</v>
       </c>
       <c r="C638" t="s">
-        <v>1680</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="639" spans="1:3">
@@ -13607,7 +13565,7 @@
         <v>662</v>
       </c>
       <c r="C639" t="s">
-        <v>1681</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="640" spans="1:3">
@@ -13618,7 +13576,7 @@
         <v>663</v>
       </c>
       <c r="C640" t="s">
-        <v>1682</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="641" spans="1:3">
@@ -13629,7 +13587,7 @@
         <v>664</v>
       </c>
       <c r="C641" t="s">
-        <v>1683</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="642" spans="1:3">
@@ -13640,7 +13598,7 @@
         <v>665</v>
       </c>
       <c r="C642" t="s">
-        <v>1684</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="643" spans="1:3">
@@ -13651,7 +13609,7 @@
         <v>666</v>
       </c>
       <c r="C643" t="s">
-        <v>1685</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="644" spans="1:3">
@@ -13662,7 +13620,7 @@
         <v>667</v>
       </c>
       <c r="C644" t="s">
-        <v>1686</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="645" spans="1:3">
@@ -13673,73 +13631,73 @@
         <v>668</v>
       </c>
       <c r="C645" t="s">
-        <v>1687</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="646" spans="1:3">
       <c r="A646" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B646" t="s">
         <v>669</v>
       </c>
       <c r="C646" t="s">
-        <v>1688</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="647" spans="1:3">
       <c r="A647" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B647" t="s">
         <v>670</v>
       </c>
       <c r="C647" t="s">
-        <v>1689</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="648" spans="1:3">
       <c r="A648" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B648" t="s">
         <v>671</v>
       </c>
       <c r="C648" t="s">
-        <v>1690</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="649" spans="1:3">
       <c r="A649" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B649" t="s">
         <v>672</v>
       </c>
       <c r="C649" t="s">
-        <v>1691</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="650" spans="1:3">
       <c r="A650" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B650" t="s">
         <v>673</v>
       </c>
       <c r="C650" t="s">
-        <v>1692</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="651" spans="1:3">
       <c r="A651" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B651" t="s">
         <v>674</v>
       </c>
       <c r="C651" t="s">
-        <v>1693</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="652" spans="1:3">
@@ -13750,7 +13708,7 @@
         <v>675</v>
       </c>
       <c r="C652" t="s">
-        <v>1694</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="653" spans="1:3">
@@ -13761,7 +13719,7 @@
         <v>676</v>
       </c>
       <c r="C653" t="s">
-        <v>1695</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="654" spans="1:3">
@@ -13772,7 +13730,7 @@
         <v>677</v>
       </c>
       <c r="C654" t="s">
-        <v>1696</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="655" spans="1:3">
@@ -13783,7 +13741,7 @@
         <v>678</v>
       </c>
       <c r="C655" t="s">
-        <v>1697</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="656" spans="1:3">
@@ -13794,7 +13752,7 @@
         <v>679</v>
       </c>
       <c r="C656" t="s">
-        <v>1698</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="657" spans="1:3">
@@ -13805,7 +13763,7 @@
         <v>680</v>
       </c>
       <c r="C657" t="s">
-        <v>1699</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="658" spans="1:3">
@@ -13816,7 +13774,7 @@
         <v>681</v>
       </c>
       <c r="C658" t="s">
-        <v>1700</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="659" spans="1:3">
@@ -13827,7 +13785,7 @@
         <v>682</v>
       </c>
       <c r="C659" t="s">
-        <v>1701</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="660" spans="1:3">
@@ -13838,7 +13796,7 @@
         <v>683</v>
       </c>
       <c r="C660" t="s">
-        <v>1702</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="661" spans="1:3">
@@ -13849,73 +13807,73 @@
         <v>684</v>
       </c>
       <c r="C661" t="s">
-        <v>1703</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="662" spans="1:3">
       <c r="A662" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B662" t="s">
         <v>685</v>
       </c>
       <c r="C662" t="s">
-        <v>1704</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="663" spans="1:3">
       <c r="A663" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B663" t="s">
         <v>686</v>
       </c>
       <c r="C663" t="s">
-        <v>1705</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="664" spans="1:3">
       <c r="A664" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B664" t="s">
         <v>687</v>
       </c>
       <c r="C664" t="s">
-        <v>1706</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="665" spans="1:3">
       <c r="A665" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B665" t="s">
         <v>688</v>
       </c>
       <c r="C665" t="s">
-        <v>1707</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="666" spans="1:3">
       <c r="A666" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B666" t="s">
         <v>689</v>
       </c>
       <c r="C666" t="s">
-        <v>1708</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="667" spans="1:3">
       <c r="A667" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B667" t="s">
         <v>690</v>
       </c>
       <c r="C667" t="s">
-        <v>1143</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="668" spans="1:3">
@@ -13926,7 +13884,7 @@
         <v>691</v>
       </c>
       <c r="C668" t="s">
-        <v>1709</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="669" spans="1:3">
@@ -13937,7 +13895,7 @@
         <v>692</v>
       </c>
       <c r="C669" t="s">
-        <v>1710</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="670" spans="1:3">
@@ -13948,7 +13906,7 @@
         <v>693</v>
       </c>
       <c r="C670" t="s">
-        <v>1711</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="671" spans="1:3">
@@ -13959,7 +13917,7 @@
         <v>694</v>
       </c>
       <c r="C671" t="s">
-        <v>1712</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="672" spans="1:3">
@@ -13970,7 +13928,7 @@
         <v>695</v>
       </c>
       <c r="C672" t="s">
-        <v>1713</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="673" spans="1:3">
@@ -13981,7 +13939,7 @@
         <v>696</v>
       </c>
       <c r="C673" t="s">
-        <v>1714</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="674" spans="1:3">
@@ -13992,7 +13950,7 @@
         <v>697</v>
       </c>
       <c r="C674" t="s">
-        <v>1715</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="675" spans="1:3">
@@ -14003,7 +13961,7 @@
         <v>698</v>
       </c>
       <c r="C675" t="s">
-        <v>1716</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="676" spans="1:3">
@@ -14014,7 +13972,7 @@
         <v>699</v>
       </c>
       <c r="C676" t="s">
-        <v>1717</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="677" spans="1:3">
@@ -14025,7 +13983,7 @@
         <v>700</v>
       </c>
       <c r="C677" t="s">
-        <v>1718</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="678" spans="1:3">
@@ -14036,7 +13994,7 @@
         <v>701</v>
       </c>
       <c r="C678" t="s">
-        <v>1719</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="679" spans="1:3">
@@ -14047,7 +14005,7 @@
         <v>702</v>
       </c>
       <c r="C679" t="s">
-        <v>1720</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="680" spans="1:3">
@@ -14058,7 +14016,7 @@
         <v>703</v>
       </c>
       <c r="C680" t="s">
-        <v>1721</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="681" spans="1:3">
@@ -14069,7 +14027,7 @@
         <v>704</v>
       </c>
       <c r="C681" t="s">
-        <v>1722</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="682" spans="1:3">
@@ -14080,7 +14038,7 @@
         <v>705</v>
       </c>
       <c r="C682" t="s">
-        <v>1723</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="683" spans="1:3">
@@ -14091,7 +14049,7 @@
         <v>706</v>
       </c>
       <c r="C683" t="s">
-        <v>1724</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="684" spans="1:3">
@@ -14102,7 +14060,7 @@
         <v>707</v>
       </c>
       <c r="C684" t="s">
-        <v>1725</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="685" spans="1:3">
@@ -14113,7 +14071,7 @@
         <v>708</v>
       </c>
       <c r="C685" t="s">
-        <v>1726</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="686" spans="1:3">
@@ -14124,7 +14082,7 @@
         <v>709</v>
       </c>
       <c r="C686" t="s">
-        <v>1727</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="687" spans="1:3">
@@ -14135,7 +14093,7 @@
         <v>710</v>
       </c>
       <c r="C687" t="s">
-        <v>1728</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="688" spans="1:3">
@@ -14146,7 +14104,7 @@
         <v>711</v>
       </c>
       <c r="C688" t="s">
-        <v>1729</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="689" spans="1:3">
@@ -14157,7 +14115,7 @@
         <v>712</v>
       </c>
       <c r="C689" t="s">
-        <v>1730</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="690" spans="1:3">
@@ -14168,7 +14126,7 @@
         <v>713</v>
       </c>
       <c r="C690" t="s">
-        <v>1731</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="691" spans="1:3">
@@ -14179,7 +14137,7 @@
         <v>714</v>
       </c>
       <c r="C691" t="s">
-        <v>1732</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="692" spans="1:3">
@@ -14190,7 +14148,7 @@
         <v>715</v>
       </c>
       <c r="C692" t="s">
-        <v>1733</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="693" spans="1:3">
@@ -14201,7 +14159,7 @@
         <v>716</v>
       </c>
       <c r="C693" t="s">
-        <v>1734</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="694" spans="1:3">
@@ -14212,7 +14170,7 @@
         <v>717</v>
       </c>
       <c r="C694" t="s">
-        <v>1735</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="695" spans="1:3">
@@ -14223,7 +14181,7 @@
         <v>718</v>
       </c>
       <c r="C695" t="s">
-        <v>1736</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="696" spans="1:3">
@@ -14234,7 +14192,7 @@
         <v>719</v>
       </c>
       <c r="C696" t="s">
-        <v>1737</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="697" spans="1:3">
@@ -14245,7 +14203,7 @@
         <v>720</v>
       </c>
       <c r="C697" t="s">
-        <v>1738</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="698" spans="1:3">
@@ -14256,7 +14214,7 @@
         <v>721</v>
       </c>
       <c r="C698" t="s">
-        <v>1739</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="699" spans="1:3">
@@ -14267,7 +14225,7 @@
         <v>722</v>
       </c>
       <c r="C699" t="s">
-        <v>1740</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="700" spans="1:3">
@@ -14278,7 +14236,7 @@
         <v>723</v>
       </c>
       <c r="C700" t="s">
-        <v>1741</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="701" spans="1:3">
@@ -14289,7 +14247,7 @@
         <v>724</v>
       </c>
       <c r="C701" t="s">
-        <v>1742</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="702" spans="1:3">
@@ -14300,84 +14258,84 @@
         <v>725</v>
       </c>
       <c r="C702" t="s">
-        <v>1743</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="703" spans="1:3">
       <c r="A703" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B703" t="s">
         <v>726</v>
       </c>
       <c r="C703" t="s">
-        <v>1744</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="704" spans="1:3">
       <c r="A704" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B704" t="s">
         <v>727</v>
       </c>
       <c r="C704" t="s">
-        <v>1745</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="705" spans="1:3">
       <c r="A705" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B705" t="s">
         <v>728</v>
       </c>
       <c r="C705" t="s">
-        <v>1746</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="706" spans="1:3">
       <c r="A706" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B706" t="s">
         <v>729</v>
       </c>
       <c r="C706" t="s">
-        <v>1747</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="707" spans="1:3">
       <c r="A707" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B707" t="s">
         <v>730</v>
       </c>
       <c r="C707" t="s">
-        <v>1748</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="708" spans="1:3">
       <c r="A708" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B708" t="s">
         <v>731</v>
       </c>
       <c r="C708" t="s">
-        <v>1749</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="709" spans="1:3">
       <c r="A709" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B709" t="s">
         <v>732</v>
       </c>
       <c r="C709" t="s">
-        <v>1750</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="710" spans="1:3">
@@ -14388,73 +14346,73 @@
         <v>733</v>
       </c>
       <c r="C710" t="s">
-        <v>1751</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="711" spans="1:3">
       <c r="A711" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B711" t="s">
         <v>734</v>
       </c>
       <c r="C711" t="s">
-        <v>1752</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="712" spans="1:3">
       <c r="A712" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B712" t="s">
         <v>735</v>
       </c>
       <c r="C712" t="s">
-        <v>1753</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="713" spans="1:3">
       <c r="A713" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B713" t="s">
         <v>736</v>
       </c>
       <c r="C713" t="s">
-        <v>1754</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="714" spans="1:3">
       <c r="A714" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B714" t="s">
         <v>737</v>
       </c>
       <c r="C714" t="s">
-        <v>1755</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="715" spans="1:3">
       <c r="A715" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B715" t="s">
         <v>738</v>
       </c>
       <c r="C715" t="s">
-        <v>1756</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="716" spans="1:3">
       <c r="A716" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B716" t="s">
         <v>739</v>
       </c>
       <c r="C716" t="s">
-        <v>1757</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="717" spans="1:3">
@@ -14465,7 +14423,7 @@
         <v>740</v>
       </c>
       <c r="C717" t="s">
-        <v>1758</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="718" spans="1:3">
@@ -14476,7 +14434,7 @@
         <v>741</v>
       </c>
       <c r="C718" t="s">
-        <v>1759</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="719" spans="1:3">
@@ -14487,7 +14445,7 @@
         <v>742</v>
       </c>
       <c r="C719" t="s">
-        <v>1760</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="720" spans="1:3">
@@ -14498,7 +14456,7 @@
         <v>743</v>
       </c>
       <c r="C720" t="s">
-        <v>1761</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="721" spans="1:3">
@@ -14509,7 +14467,7 @@
         <v>744</v>
       </c>
       <c r="C721" t="s">
-        <v>1762</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="722" spans="1:3">
@@ -14520,7 +14478,7 @@
         <v>745</v>
       </c>
       <c r="C722" t="s">
-        <v>1763</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="723" spans="1:3">
@@ -14531,7 +14489,7 @@
         <v>746</v>
       </c>
       <c r="C723" t="s">
-        <v>1764</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="724" spans="1:3">
@@ -14542,7 +14500,7 @@
         <v>747</v>
       </c>
       <c r="C724" t="s">
-        <v>1765</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="725" spans="1:3">
@@ -14553,7 +14511,7 @@
         <v>748</v>
       </c>
       <c r="C725" t="s">
-        <v>1766</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="726" spans="1:3">
@@ -14564,7 +14522,7 @@
         <v>749</v>
       </c>
       <c r="C726" t="s">
-        <v>1767</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="727" spans="1:3">
@@ -14575,7 +14533,7 @@
         <v>750</v>
       </c>
       <c r="C727" t="s">
-        <v>1768</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="728" spans="1:3">
@@ -14586,7 +14544,7 @@
         <v>751</v>
       </c>
       <c r="C728" t="s">
-        <v>1769</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="729" spans="1:3">
@@ -14597,7 +14555,7 @@
         <v>752</v>
       </c>
       <c r="C729" t="s">
-        <v>1770</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="730" spans="1:3">
@@ -14608,7 +14566,7 @@
         <v>753</v>
       </c>
       <c r="C730" t="s">
-        <v>1771</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="731" spans="1:3">
@@ -14619,7 +14577,7 @@
         <v>754</v>
       </c>
       <c r="C731" t="s">
-        <v>1772</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="732" spans="1:3">
@@ -14630,7 +14588,7 @@
         <v>755</v>
       </c>
       <c r="C732" t="s">
-        <v>1773</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="733" spans="1:3">
@@ -14641,7 +14599,7 @@
         <v>756</v>
       </c>
       <c r="C733" t="s">
-        <v>1774</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="734" spans="1:3">
@@ -14652,7 +14610,7 @@
         <v>757</v>
       </c>
       <c r="C734" t="s">
-        <v>1775</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="735" spans="1:3">
@@ -14663,7 +14621,7 @@
         <v>758</v>
       </c>
       <c r="C735" t="s">
-        <v>1776</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="736" spans="1:3">
@@ -14674,7 +14632,7 @@
         <v>759</v>
       </c>
       <c r="C736" t="s">
-        <v>1777</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="737" spans="1:3">
@@ -14685,7 +14643,7 @@
         <v>760</v>
       </c>
       <c r="C737" t="s">
-        <v>1778</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="738" spans="1:3">
@@ -14696,7 +14654,7 @@
         <v>761</v>
       </c>
       <c r="C738" t="s">
-        <v>1779</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="739" spans="1:3">
@@ -14707,7 +14665,7 @@
         <v>762</v>
       </c>
       <c r="C739" t="s">
-        <v>1780</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="740" spans="1:3">
@@ -14718,7 +14676,7 @@
         <v>763</v>
       </c>
       <c r="C740" t="s">
-        <v>1781</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="741" spans="1:3">
@@ -14729,7 +14687,7 @@
         <v>764</v>
       </c>
       <c r="C741" t="s">
-        <v>1782</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="742" spans="1:3">
@@ -14740,7 +14698,7 @@
         <v>765</v>
       </c>
       <c r="C742" t="s">
-        <v>1783</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="743" spans="1:3">
@@ -14751,7 +14709,7 @@
         <v>766</v>
       </c>
       <c r="C743" t="s">
-        <v>1784</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="744" spans="1:3">
@@ -14762,7 +14720,7 @@
         <v>767</v>
       </c>
       <c r="C744" t="s">
-        <v>1785</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="745" spans="1:3">
@@ -14773,7 +14731,7 @@
         <v>768</v>
       </c>
       <c r="C745" t="s">
-        <v>1786</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="746" spans="1:3">
@@ -14784,7 +14742,7 @@
         <v>769</v>
       </c>
       <c r="C746" t="s">
-        <v>1787</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="747" spans="1:3">
@@ -14795,7 +14753,7 @@
         <v>770</v>
       </c>
       <c r="C747" t="s">
-        <v>1788</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="748" spans="1:3">
@@ -14806,7 +14764,7 @@
         <v>771</v>
       </c>
       <c r="C748" t="s">
-        <v>1789</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="749" spans="1:3">
@@ -14817,7 +14775,7 @@
         <v>772</v>
       </c>
       <c r="C749" t="s">
-        <v>1790</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="750" spans="1:3">
@@ -14828,7 +14786,7 @@
         <v>773</v>
       </c>
       <c r="C750" t="s">
-        <v>1791</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="751" spans="1:3">
@@ -14839,7 +14797,7 @@
         <v>774</v>
       </c>
       <c r="C751" t="s">
-        <v>1792</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="752" spans="1:3">
@@ -14850,7 +14808,7 @@
         <v>775</v>
       </c>
       <c r="C752" t="s">
-        <v>1793</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="753" spans="1:3">
@@ -14861,7 +14819,7 @@
         <v>776</v>
       </c>
       <c r="C753" t="s">
-        <v>1794</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="754" spans="1:3">
@@ -14872,7 +14830,7 @@
         <v>777</v>
       </c>
       <c r="C754" t="s">
-        <v>1795</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="755" spans="1:3">
@@ -14883,7 +14841,7 @@
         <v>778</v>
       </c>
       <c r="C755" t="s">
-        <v>1796</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="756" spans="1:3">
@@ -14894,7 +14852,7 @@
         <v>779</v>
       </c>
       <c r="C756" t="s">
-        <v>1797</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="757" spans="1:3">
@@ -14905,7 +14863,7 @@
         <v>780</v>
       </c>
       <c r="C757" t="s">
-        <v>1798</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="758" spans="1:3">
@@ -14916,7 +14874,7 @@
         <v>781</v>
       </c>
       <c r="C758" t="s">
-        <v>1799</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="759" spans="1:3">
@@ -14927,7 +14885,7 @@
         <v>782</v>
       </c>
       <c r="C759" t="s">
-        <v>1800</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="760" spans="1:3">
@@ -14938,7 +14896,7 @@
         <v>783</v>
       </c>
       <c r="C760" t="s">
-        <v>1801</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="761" spans="1:3">
@@ -14949,7 +14907,7 @@
         <v>784</v>
       </c>
       <c r="C761" t="s">
-        <v>1802</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="762" spans="1:3">
@@ -14960,7 +14918,7 @@
         <v>785</v>
       </c>
       <c r="C762" t="s">
-        <v>1803</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="763" spans="1:3">
@@ -14971,7 +14929,7 @@
         <v>786</v>
       </c>
       <c r="C763" t="s">
-        <v>1804</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="764" spans="1:3">
@@ -14982,7 +14940,7 @@
         <v>787</v>
       </c>
       <c r="C764" t="s">
-        <v>1805</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="765" spans="1:3">
@@ -14993,7 +14951,7 @@
         <v>788</v>
       </c>
       <c r="C765" t="s">
-        <v>1806</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="766" spans="1:3">
@@ -15004,7 +14962,7 @@
         <v>789</v>
       </c>
       <c r="C766" t="s">
-        <v>1807</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="767" spans="1:3">
@@ -15015,7 +14973,7 @@
         <v>790</v>
       </c>
       <c r="C767" t="s">
-        <v>1808</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="768" spans="1:3">
@@ -15026,7 +14984,7 @@
         <v>791</v>
       </c>
       <c r="C768" t="s">
-        <v>1732</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="769" spans="1:3">
@@ -15037,7 +14995,7 @@
         <v>792</v>
       </c>
       <c r="C769" t="s">
-        <v>1809</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="770" spans="1:3">
@@ -15048,7 +15006,7 @@
         <v>793</v>
       </c>
       <c r="C770" t="s">
-        <v>1810</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="771" spans="1:3">
@@ -15059,7 +15017,7 @@
         <v>794</v>
       </c>
       <c r="C771" t="s">
-        <v>1811</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="772" spans="1:3">
@@ -15070,7 +15028,7 @@
         <v>795</v>
       </c>
       <c r="C772" t="s">
-        <v>1812</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="773" spans="1:3">
@@ -15081,7 +15039,7 @@
         <v>796</v>
       </c>
       <c r="C773" t="s">
-        <v>1813</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="774" spans="1:3">
@@ -15092,7 +15050,7 @@
         <v>797</v>
       </c>
       <c r="C774" t="s">
-        <v>1814</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="775" spans="1:3">
@@ -15103,7 +15061,7 @@
         <v>798</v>
       </c>
       <c r="C775" t="s">
-        <v>1815</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="776" spans="1:3">
@@ -15114,7 +15072,7 @@
         <v>799</v>
       </c>
       <c r="C776" t="s">
-        <v>1816</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="777" spans="1:3">
@@ -15125,7 +15083,7 @@
         <v>800</v>
       </c>
       <c r="C777" t="s">
-        <v>1817</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="778" spans="1:3">
@@ -15136,7 +15094,7 @@
         <v>801</v>
       </c>
       <c r="C778" t="s">
-        <v>1818</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="779" spans="1:3">
@@ -15147,7 +15105,7 @@
         <v>802</v>
       </c>
       <c r="C779" t="s">
-        <v>1819</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="780" spans="1:3">
@@ -15158,7 +15116,7 @@
         <v>803</v>
       </c>
       <c r="C780" t="s">
-        <v>1820</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="781" spans="1:3">
@@ -15169,7 +15127,7 @@
         <v>804</v>
       </c>
       <c r="C781" t="s">
-        <v>1821</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="782" spans="1:3">
@@ -15180,7 +15138,7 @@
         <v>805</v>
       </c>
       <c r="C782" t="s">
-        <v>1822</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="783" spans="1:3">
@@ -15191,7 +15149,7 @@
         <v>806</v>
       </c>
       <c r="C783" t="s">
-        <v>1823</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="784" spans="1:3">
@@ -15202,7 +15160,7 @@
         <v>807</v>
       </c>
       <c r="C784" t="s">
-        <v>1824</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="785" spans="1:3">
@@ -15213,7 +15171,7 @@
         <v>808</v>
       </c>
       <c r="C785" t="s">
-        <v>1825</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="786" spans="1:3">
@@ -15224,7 +15182,7 @@
         <v>809</v>
       </c>
       <c r="C786" t="s">
-        <v>1826</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="787" spans="1:3">
@@ -15235,7 +15193,7 @@
         <v>810</v>
       </c>
       <c r="C787" t="s">
-        <v>1827</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="788" spans="1:3">
@@ -15246,7 +15204,7 @@
         <v>811</v>
       </c>
       <c r="C788" t="s">
-        <v>1828</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="789" spans="1:3">
@@ -15257,7 +15215,7 @@
         <v>812</v>
       </c>
       <c r="C789" t="s">
-        <v>1829</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="790" spans="1:3">
@@ -15268,7 +15226,7 @@
         <v>813</v>
       </c>
       <c r="C790" t="s">
-        <v>1830</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="791" spans="1:3">
@@ -15279,7 +15237,7 @@
         <v>814</v>
       </c>
       <c r="C791" t="s">
-        <v>1831</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="792" spans="1:3">
@@ -15290,7 +15248,7 @@
         <v>815</v>
       </c>
       <c r="C792" t="s">
-        <v>1832</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="793" spans="1:3">
@@ -15301,7 +15259,7 @@
         <v>816</v>
       </c>
       <c r="C793" t="s">
-        <v>1833</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="794" spans="1:3">
@@ -15312,7 +15270,7 @@
         <v>817</v>
       </c>
       <c r="C794" t="s">
-        <v>1834</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="795" spans="1:3">
@@ -15323,7 +15281,7 @@
         <v>818</v>
       </c>
       <c r="C795" t="s">
-        <v>1835</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="796" spans="1:3">
@@ -15334,7 +15292,7 @@
         <v>819</v>
       </c>
       <c r="C796" t="s">
-        <v>1836</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="797" spans="1:3">
@@ -15345,7 +15303,7 @@
         <v>820</v>
       </c>
       <c r="C797" t="s">
-        <v>1837</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="798" spans="1:3">
@@ -15356,7 +15314,7 @@
         <v>821</v>
       </c>
       <c r="C798" t="s">
-        <v>1838</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="799" spans="1:3">
@@ -15367,7 +15325,7 @@
         <v>822</v>
       </c>
       <c r="C799" t="s">
-        <v>1839</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="800" spans="1:3">
@@ -15378,7 +15336,7 @@
         <v>823</v>
       </c>
       <c r="C800" t="s">
-        <v>1840</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="801" spans="1:3">
@@ -15389,7 +15347,7 @@
         <v>824</v>
       </c>
       <c r="C801" t="s">
-        <v>1841</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="802" spans="1:3">
@@ -15400,7 +15358,7 @@
         <v>825</v>
       </c>
       <c r="C802" t="s">
-        <v>1842</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="803" spans="1:3">
@@ -15411,7 +15369,7 @@
         <v>826</v>
       </c>
       <c r="C803" t="s">
-        <v>1843</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="804" spans="1:3">
@@ -15422,7 +15380,7 @@
         <v>827</v>
       </c>
       <c r="C804" t="s">
-        <v>1844</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="805" spans="1:3">
@@ -15433,7 +15391,7 @@
         <v>828</v>
       </c>
       <c r="C805" t="s">
-        <v>1845</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="806" spans="1:3">
@@ -15444,7 +15402,7 @@
         <v>829</v>
       </c>
       <c r="C806" t="s">
-        <v>1846</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="807" spans="1:3">
@@ -15455,7 +15413,7 @@
         <v>830</v>
       </c>
       <c r="C807" t="s">
-        <v>1847</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="808" spans="1:3">
@@ -15466,7 +15424,7 @@
         <v>831</v>
       </c>
       <c r="C808" t="s">
-        <v>1848</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="809" spans="1:3">
@@ -15477,7 +15435,7 @@
         <v>832</v>
       </c>
       <c r="C809" t="s">
-        <v>1849</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="810" spans="1:3">
@@ -15488,7 +15446,7 @@
         <v>833</v>
       </c>
       <c r="C810" t="s">
-        <v>1850</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="811" spans="1:3">
@@ -15499,7 +15457,7 @@
         <v>834</v>
       </c>
       <c r="C811" t="s">
-        <v>1851</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="812" spans="1:3">
@@ -15510,7 +15468,7 @@
         <v>835</v>
       </c>
       <c r="C812" t="s">
-        <v>1852</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="813" spans="1:3">
@@ -15521,7 +15479,7 @@
         <v>836</v>
       </c>
       <c r="C813" t="s">
-        <v>1853</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="814" spans="1:3">
@@ -15532,7 +15490,7 @@
         <v>837</v>
       </c>
       <c r="C814" t="s">
-        <v>1854</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="815" spans="1:3">
@@ -15543,7 +15501,7 @@
         <v>838</v>
       </c>
       <c r="C815" t="s">
-        <v>1855</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="816" spans="1:3">
@@ -15554,7 +15512,7 @@
         <v>839</v>
       </c>
       <c r="C816" t="s">
-        <v>1856</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="817" spans="1:3">
@@ -15565,7 +15523,7 @@
         <v>840</v>
       </c>
       <c r="C817" t="s">
-        <v>1857</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="818" spans="1:3">
@@ -15576,7 +15534,7 @@
         <v>841</v>
       </c>
       <c r="C818" t="s">
-        <v>1858</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="819" spans="1:3">
@@ -15587,7 +15545,7 @@
         <v>842</v>
       </c>
       <c r="C819" t="s">
-        <v>1859</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="820" spans="1:3">
@@ -15598,7 +15556,7 @@
         <v>843</v>
       </c>
       <c r="C820" t="s">
-        <v>1860</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="821" spans="1:3">
@@ -15609,7 +15567,7 @@
         <v>844</v>
       </c>
       <c r="C821" t="s">
-        <v>1861</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="822" spans="1:3">
@@ -15620,7 +15578,7 @@
         <v>845</v>
       </c>
       <c r="C822" t="s">
-        <v>1862</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="823" spans="1:3">
@@ -15631,7 +15589,7 @@
         <v>846</v>
       </c>
       <c r="C823" t="s">
-        <v>1863</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="824" spans="1:3">
@@ -15642,7 +15600,7 @@
         <v>847</v>
       </c>
       <c r="C824" t="s">
-        <v>1864</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="825" spans="1:3">
@@ -15653,7 +15611,7 @@
         <v>848</v>
       </c>
       <c r="C825" t="s">
-        <v>1865</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="826" spans="1:3">
@@ -15664,7 +15622,7 @@
         <v>849</v>
       </c>
       <c r="C826" t="s">
-        <v>1866</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="827" spans="1:3">
@@ -15675,7 +15633,7 @@
         <v>850</v>
       </c>
       <c r="C827" t="s">
-        <v>1867</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="828" spans="1:3">
@@ -15686,7 +15644,7 @@
         <v>851</v>
       </c>
       <c r="C828" t="s">
-        <v>1868</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="829" spans="1:3">
@@ -15697,7 +15655,7 @@
         <v>852</v>
       </c>
       <c r="C829" t="s">
-        <v>1869</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="830" spans="1:3">
@@ -15708,7 +15666,7 @@
         <v>853</v>
       </c>
       <c r="C830" t="s">
-        <v>1870</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="831" spans="1:3">
@@ -15719,7 +15677,7 @@
         <v>854</v>
       </c>
       <c r="C831" t="s">
-        <v>1871</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="832" spans="1:3">
@@ -15730,7 +15688,7 @@
         <v>855</v>
       </c>
       <c r="C832" t="s">
-        <v>1872</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="833" spans="1:3">
@@ -15741,73 +15699,73 @@
         <v>856</v>
       </c>
       <c r="C833" t="s">
-        <v>1873</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="834" spans="1:3">
       <c r="A834" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B834" t="s">
         <v>857</v>
       </c>
       <c r="C834" t="s">
-        <v>1874</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="835" spans="1:3">
       <c r="A835" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B835" t="s">
         <v>858</v>
       </c>
       <c r="C835" t="s">
-        <v>1875</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="836" spans="1:3">
       <c r="A836" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B836" t="s">
         <v>859</v>
       </c>
       <c r="C836" t="s">
-        <v>1876</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="837" spans="1:3">
       <c r="A837" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B837" t="s">
         <v>860</v>
       </c>
       <c r="C837" t="s">
-        <v>1877</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="838" spans="1:3">
       <c r="A838" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B838" t="s">
         <v>861</v>
       </c>
       <c r="C838" t="s">
-        <v>1878</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="839" spans="1:3">
       <c r="A839" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B839" t="s">
         <v>862</v>
       </c>
       <c r="C839" t="s">
-        <v>1879</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="840" spans="1:3">
@@ -15818,7 +15776,7 @@
         <v>863</v>
       </c>
       <c r="C840" t="s">
-        <v>1880</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="841" spans="1:3">
@@ -15829,7 +15787,7 @@
         <v>864</v>
       </c>
       <c r="C841" t="s">
-        <v>1881</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="842" spans="1:3">
@@ -15840,7 +15798,7 @@
         <v>865</v>
       </c>
       <c r="C842" t="s">
-        <v>1882</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="843" spans="1:3">
@@ -15851,7 +15809,7 @@
         <v>866</v>
       </c>
       <c r="C843" t="s">
-        <v>1883</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="844" spans="1:3">
@@ -15862,7 +15820,7 @@
         <v>867</v>
       </c>
       <c r="C844" t="s">
-        <v>1884</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="845" spans="1:3">
@@ -15873,7 +15831,7 @@
         <v>868</v>
       </c>
       <c r="C845" t="s">
-        <v>1885</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="846" spans="1:3">
@@ -15884,7 +15842,7 @@
         <v>869</v>
       </c>
       <c r="C846" t="s">
-        <v>1886</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="847" spans="1:3">
@@ -15895,7 +15853,7 @@
         <v>870</v>
       </c>
       <c r="C847" t="s">
-        <v>1887</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="848" spans="1:3">
@@ -15906,7 +15864,7 @@
         <v>871</v>
       </c>
       <c r="C848" t="s">
-        <v>1888</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="849" spans="1:3">
@@ -15917,7 +15875,7 @@
         <v>872</v>
       </c>
       <c r="C849" t="s">
-        <v>1889</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="850" spans="1:3">
@@ -15928,7 +15886,7 @@
         <v>873</v>
       </c>
       <c r="C850" t="s">
-        <v>1890</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="851" spans="1:3">
@@ -15939,7 +15897,7 @@
         <v>874</v>
       </c>
       <c r="C851" t="s">
-        <v>1891</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="852" spans="1:3">
@@ -15950,7 +15908,7 @@
         <v>875</v>
       </c>
       <c r="C852" t="s">
-        <v>1892</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="853" spans="1:3">
@@ -15961,7 +15919,7 @@
         <v>876</v>
       </c>
       <c r="C853" t="s">
-        <v>1893</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="854" spans="1:3">
@@ -15972,7 +15930,7 @@
         <v>877</v>
       </c>
       <c r="C854" t="s">
-        <v>1894</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="855" spans="1:3">
@@ -15983,7 +15941,7 @@
         <v>878</v>
       </c>
       <c r="C855" t="s">
-        <v>1895</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="856" spans="1:3">
@@ -15994,7 +15952,7 @@
         <v>879</v>
       </c>
       <c r="C856" t="s">
-        <v>1896</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="857" spans="1:3">
@@ -16005,7 +15963,7 @@
         <v>880</v>
       </c>
       <c r="C857" t="s">
-        <v>1897</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="858" spans="1:3">
@@ -16016,7 +15974,7 @@
         <v>881</v>
       </c>
       <c r="C858" t="s">
-        <v>1898</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="859" spans="1:3">
@@ -16027,7 +15985,7 @@
         <v>882</v>
       </c>
       <c r="C859" t="s">
-        <v>1899</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="860" spans="1:3">
@@ -16038,7 +15996,7 @@
         <v>883</v>
       </c>
       <c r="C860" t="s">
-        <v>1900</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="861" spans="1:3">
@@ -16049,7 +16007,7 @@
         <v>884</v>
       </c>
       <c r="C861" t="s">
-        <v>1901</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="862" spans="1:3">
@@ -16060,7 +16018,7 @@
         <v>885</v>
       </c>
       <c r="C862" t="s">
-        <v>1902</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="863" spans="1:3">
@@ -16071,7 +16029,7 @@
         <v>886</v>
       </c>
       <c r="C863" t="s">
-        <v>1903</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="864" spans="1:3">
@@ -16082,7 +16040,7 @@
         <v>887</v>
       </c>
       <c r="C864" t="s">
-        <v>1904</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="865" spans="1:3">
@@ -16093,7 +16051,7 @@
         <v>888</v>
       </c>
       <c r="C865" t="s">
-        <v>1905</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="866" spans="1:3">
@@ -16104,7 +16062,7 @@
         <v>889</v>
       </c>
       <c r="C866" t="s">
-        <v>1906</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="867" spans="1:3">
@@ -16115,7 +16073,7 @@
         <v>890</v>
       </c>
       <c r="C867" t="s">
-        <v>1907</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="868" spans="1:3">
@@ -16126,7 +16084,7 @@
         <v>891</v>
       </c>
       <c r="C868" t="s">
-        <v>1908</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="869" spans="1:3">
@@ -16137,7 +16095,7 @@
         <v>892</v>
       </c>
       <c r="C869" t="s">
-        <v>1909</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="870" spans="1:3">
@@ -16148,7 +16106,7 @@
         <v>893</v>
       </c>
       <c r="C870" t="s">
-        <v>1910</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="871" spans="1:3">
@@ -16159,7 +16117,7 @@
         <v>894</v>
       </c>
       <c r="C871" t="s">
-        <v>1911</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="872" spans="1:3">
@@ -16170,7 +16128,7 @@
         <v>895</v>
       </c>
       <c r="C872" t="s">
-        <v>1912</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="873" spans="1:3">
@@ -16181,7 +16139,7 @@
         <v>896</v>
       </c>
       <c r="C873" t="s">
-        <v>1913</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="874" spans="1:3">
@@ -16192,7 +16150,7 @@
         <v>897</v>
       </c>
       <c r="C874" t="s">
-        <v>1914</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="875" spans="1:3">
@@ -16203,7 +16161,7 @@
         <v>898</v>
       </c>
       <c r="C875" t="s">
-        <v>1915</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="876" spans="1:3">
@@ -16214,7 +16172,7 @@
         <v>899</v>
       </c>
       <c r="C876" t="s">
-        <v>1916</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="877" spans="1:3">
@@ -16225,7 +16183,7 @@
         <v>900</v>
       </c>
       <c r="C877" t="s">
-        <v>1917</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="878" spans="1:3">
@@ -16236,7 +16194,7 @@
         <v>901</v>
       </c>
       <c r="C878" t="s">
-        <v>1918</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="879" spans="1:3">
@@ -16247,7 +16205,7 @@
         <v>902</v>
       </c>
       <c r="C879" t="s">
-        <v>1919</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="880" spans="1:3">
@@ -16258,7 +16216,7 @@
         <v>903</v>
       </c>
       <c r="C880" t="s">
-        <v>1920</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="881" spans="1:3">
@@ -16269,7 +16227,7 @@
         <v>904</v>
       </c>
       <c r="C881" t="s">
-        <v>1921</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="882" spans="1:3">
@@ -16280,7 +16238,7 @@
         <v>905</v>
       </c>
       <c r="C882" t="s">
-        <v>1922</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="883" spans="1:3">
@@ -16291,7 +16249,7 @@
         <v>906</v>
       </c>
       <c r="C883" t="s">
-        <v>1923</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="884" spans="1:3">
@@ -16302,7 +16260,7 @@
         <v>907</v>
       </c>
       <c r="C884" t="s">
-        <v>1924</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="885" spans="1:3">
@@ -16313,7 +16271,7 @@
         <v>908</v>
       </c>
       <c r="C885" t="s">
-        <v>1925</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="886" spans="1:3">
@@ -16324,7 +16282,7 @@
         <v>909</v>
       </c>
       <c r="C886" t="s">
-        <v>1926</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="887" spans="1:3">
@@ -16335,7 +16293,7 @@
         <v>910</v>
       </c>
       <c r="C887" t="s">
-        <v>1927</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="888" spans="1:3">
@@ -16346,7 +16304,7 @@
         <v>911</v>
       </c>
       <c r="C888" t="s">
-        <v>1928</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="889" spans="1:3">
@@ -16357,7 +16315,7 @@
         <v>912</v>
       </c>
       <c r="C889" t="s">
-        <v>1929</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="890" spans="1:3">
@@ -16368,7 +16326,7 @@
         <v>913</v>
       </c>
       <c r="C890" t="s">
-        <v>1930</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="891" spans="1:3">
@@ -16379,7 +16337,7 @@
         <v>914</v>
       </c>
       <c r="C891" t="s">
-        <v>1931</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="892" spans="1:3">
@@ -16390,7 +16348,7 @@
         <v>915</v>
       </c>
       <c r="C892" t="s">
-        <v>1932</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="893" spans="1:3">
@@ -16401,7 +16359,7 @@
         <v>916</v>
       </c>
       <c r="C893" t="s">
-        <v>1933</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="894" spans="1:3">
@@ -16412,7 +16370,7 @@
         <v>917</v>
       </c>
       <c r="C894" t="s">
-        <v>1934</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="895" spans="1:3">
@@ -16423,7 +16381,7 @@
         <v>918</v>
       </c>
       <c r="C895" t="s">
-        <v>1935</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="896" spans="1:3">
@@ -16434,7 +16392,7 @@
         <v>919</v>
       </c>
       <c r="C896" t="s">
-        <v>1936</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="897" spans="1:3">
@@ -16445,7 +16403,7 @@
         <v>920</v>
       </c>
       <c r="C897" t="s">
-        <v>1937</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="898" spans="1:3">
@@ -16456,7 +16414,7 @@
         <v>921</v>
       </c>
       <c r="C898" t="s">
-        <v>1938</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="899" spans="1:3">
@@ -16467,7 +16425,7 @@
         <v>922</v>
       </c>
       <c r="C899" t="s">
-        <v>1939</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="900" spans="1:3">
@@ -16478,7 +16436,7 @@
         <v>923</v>
       </c>
       <c r="C900" t="s">
-        <v>1940</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="901" spans="1:3">
@@ -16489,7 +16447,7 @@
         <v>924</v>
       </c>
       <c r="C901" t="s">
-        <v>1941</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="902" spans="1:3">
@@ -16500,7 +16458,7 @@
         <v>925</v>
       </c>
       <c r="C902" t="s">
-        <v>1942</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="903" spans="1:3">
@@ -16511,7 +16469,7 @@
         <v>926</v>
       </c>
       <c r="C903" t="s">
-        <v>1943</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="904" spans="1:3">
@@ -16522,7 +16480,7 @@
         <v>927</v>
       </c>
       <c r="C904" t="s">
-        <v>1944</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="905" spans="1:3">
@@ -16533,7 +16491,7 @@
         <v>928</v>
       </c>
       <c r="C905" t="s">
-        <v>1945</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="906" spans="1:3">
@@ -16544,7 +16502,7 @@
         <v>929</v>
       </c>
       <c r="C906" t="s">
-        <v>1946</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="907" spans="1:3">
@@ -16555,7 +16513,7 @@
         <v>930</v>
       </c>
       <c r="C907" t="s">
-        <v>1947</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="908" spans="1:3">
@@ -16566,7 +16524,7 @@
         <v>931</v>
       </c>
       <c r="C908" t="s">
-        <v>1948</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="909" spans="1:3">
@@ -16577,7 +16535,7 @@
         <v>932</v>
       </c>
       <c r="C909" t="s">
-        <v>1949</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="910" spans="1:3">
@@ -16588,7 +16546,7 @@
         <v>933</v>
       </c>
       <c r="C910" t="s">
-        <v>1950</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="911" spans="1:3">
@@ -16599,7 +16557,7 @@
         <v>934</v>
       </c>
       <c r="C911" t="s">
-        <v>1951</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="912" spans="1:3">
@@ -16610,7 +16568,7 @@
         <v>935</v>
       </c>
       <c r="C912" t="s">
-        <v>1952</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="913" spans="1:3">
@@ -16621,7 +16579,7 @@
         <v>936</v>
       </c>
       <c r="C913" t="s">
-        <v>1953</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="914" spans="1:3">
@@ -16632,7 +16590,7 @@
         <v>937</v>
       </c>
       <c r="C914" t="s">
-        <v>1954</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="915" spans="1:3">
@@ -16643,7 +16601,7 @@
         <v>938</v>
       </c>
       <c r="C915" t="s">
-        <v>1955</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="916" spans="1:3">
@@ -16654,7 +16612,7 @@
         <v>939</v>
       </c>
       <c r="C916" t="s">
-        <v>1956</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="917" spans="1:3">
@@ -16665,7 +16623,7 @@
         <v>940</v>
       </c>
       <c r="C917" t="s">
-        <v>1957</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="918" spans="1:3">
@@ -16676,7 +16634,7 @@
         <v>941</v>
       </c>
       <c r="C918" t="s">
-        <v>1958</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="919" spans="1:3">
@@ -16687,7 +16645,7 @@
         <v>942</v>
       </c>
       <c r="C919" t="s">
-        <v>1959</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="920" spans="1:3">
@@ -16698,7 +16656,7 @@
         <v>943</v>
       </c>
       <c r="C920" t="s">
-        <v>1960</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="921" spans="1:3">
@@ -16709,7 +16667,7 @@
         <v>944</v>
       </c>
       <c r="C921" t="s">
-        <v>1961</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="922" spans="1:3">
@@ -16720,7 +16678,7 @@
         <v>945</v>
       </c>
       <c r="C922" t="s">
-        <v>1962</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="923" spans="1:3">
@@ -16731,7 +16689,7 @@
         <v>946</v>
       </c>
       <c r="C923" t="s">
-        <v>1963</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="924" spans="1:3">
@@ -16742,7 +16700,7 @@
         <v>947</v>
       </c>
       <c r="C924" t="s">
-        <v>1964</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="925" spans="1:3">
@@ -16753,84 +16711,84 @@
         <v>948</v>
       </c>
       <c r="C925" t="s">
-        <v>1965</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="926" spans="1:3">
       <c r="A926" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B926" t="s">
         <v>949</v>
       </c>
       <c r="C926" t="s">
-        <v>1966</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="927" spans="1:3">
       <c r="A927" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B927" t="s">
         <v>950</v>
       </c>
       <c r="C927" t="s">
-        <v>1967</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="928" spans="1:3">
       <c r="A928" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B928" t="s">
         <v>951</v>
       </c>
       <c r="C928" t="s">
-        <v>1968</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="929" spans="1:3">
       <c r="A929" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B929" t="s">
         <v>952</v>
       </c>
       <c r="C929" t="s">
-        <v>1969</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="930" spans="1:3">
       <c r="A930" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B930" t="s">
         <v>953</v>
       </c>
       <c r="C930" t="s">
-        <v>1970</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="931" spans="1:3">
       <c r="A931" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B931" t="s">
         <v>954</v>
       </c>
       <c r="C931" t="s">
-        <v>1971</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="932" spans="1:3">
       <c r="A932" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B932" t="s">
         <v>955</v>
       </c>
       <c r="C932" t="s">
-        <v>1972</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="933" spans="1:3">
@@ -16841,7 +16799,7 @@
         <v>956</v>
       </c>
       <c r="C933" t="s">
-        <v>1973</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="934" spans="1:3">
@@ -16852,7 +16810,7 @@
         <v>957</v>
       </c>
       <c r="C934" t="s">
-        <v>1974</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="935" spans="1:3">
@@ -16863,7 +16821,7 @@
         <v>958</v>
       </c>
       <c r="C935" t="s">
-        <v>1975</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="936" spans="1:3">
@@ -16874,7 +16832,7 @@
         <v>959</v>
       </c>
       <c r="C936" t="s">
-        <v>1976</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="937" spans="1:3">
@@ -16885,7 +16843,7 @@
         <v>960</v>
       </c>
       <c r="C937" t="s">
-        <v>1977</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="938" spans="1:3">
@@ -16896,7 +16854,7 @@
         <v>961</v>
       </c>
       <c r="C938" t="s">
-        <v>1978</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="939" spans="1:3">
@@ -16907,7 +16865,7 @@
         <v>962</v>
       </c>
       <c r="C939" t="s">
-        <v>1979</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="940" spans="1:3">
@@ -16918,7 +16876,7 @@
         <v>963</v>
       </c>
       <c r="C940" t="s">
-        <v>1980</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="941" spans="1:3">
@@ -16929,7 +16887,7 @@
         <v>964</v>
       </c>
       <c r="C941" t="s">
-        <v>1981</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="942" spans="1:3">
@@ -16940,7 +16898,7 @@
         <v>965</v>
       </c>
       <c r="C942" t="s">
-        <v>1982</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="943" spans="1:3">
@@ -16951,7 +16909,7 @@
         <v>966</v>
       </c>
       <c r="C943" t="s">
-        <v>1983</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="944" spans="1:3">
@@ -16962,7 +16920,7 @@
         <v>967</v>
       </c>
       <c r="C944" t="s">
-        <v>1984</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="945" spans="1:3">
@@ -16973,7 +16931,7 @@
         <v>968</v>
       </c>
       <c r="C945" t="s">
-        <v>1985</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="946" spans="1:3">
@@ -16984,7 +16942,7 @@
         <v>969</v>
       </c>
       <c r="C946" t="s">
-        <v>1986</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="947" spans="1:3">
@@ -16995,7 +16953,7 @@
         <v>970</v>
       </c>
       <c r="C947" t="s">
-        <v>1987</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="948" spans="1:3">
@@ -17006,7 +16964,7 @@
         <v>971</v>
       </c>
       <c r="C948" t="s">
-        <v>1988</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="949" spans="1:3">
@@ -17017,7 +16975,7 @@
         <v>972</v>
       </c>
       <c r="C949" t="s">
-        <v>1989</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="950" spans="1:3">
@@ -17028,7 +16986,7 @@
         <v>973</v>
       </c>
       <c r="C950" t="s">
-        <v>1990</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="951" spans="1:3">
@@ -17039,7 +16997,7 @@
         <v>974</v>
       </c>
       <c r="C951" t="s">
-        <v>1991</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="952" spans="1:3">
@@ -17050,7 +17008,7 @@
         <v>975</v>
       </c>
       <c r="C952" t="s">
-        <v>1992</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="953" spans="1:3">
@@ -17061,7 +17019,7 @@
         <v>976</v>
       </c>
       <c r="C953" t="s">
-        <v>1993</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="954" spans="1:3">
@@ -17072,7 +17030,7 @@
         <v>977</v>
       </c>
       <c r="C954" t="s">
-        <v>1994</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="955" spans="1:3">
@@ -17083,7 +17041,7 @@
         <v>978</v>
       </c>
       <c r="C955" t="s">
-        <v>1995</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="956" spans="1:3">
@@ -17094,7 +17052,7 @@
         <v>979</v>
       </c>
       <c r="C956" t="s">
-        <v>1996</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="957" spans="1:3">
@@ -17105,7 +17063,7 @@
         <v>980</v>
       </c>
       <c r="C957" t="s">
-        <v>1997</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="958" spans="1:3">
@@ -17116,7 +17074,7 @@
         <v>981</v>
       </c>
       <c r="C958" t="s">
-        <v>1998</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="959" spans="1:3">
@@ -17127,7 +17085,7 @@
         <v>982</v>
       </c>
       <c r="C959" t="s">
-        <v>1999</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="960" spans="1:3">
@@ -17138,7 +17096,7 @@
         <v>983</v>
       </c>
       <c r="C960" t="s">
-        <v>2000</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="961" spans="1:3">
@@ -17149,7 +17107,7 @@
         <v>984</v>
       </c>
       <c r="C961" t="s">
-        <v>2001</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="962" spans="1:3">
@@ -17160,7 +17118,7 @@
         <v>985</v>
       </c>
       <c r="C962" t="s">
-        <v>2002</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="963" spans="1:3">
@@ -17171,7 +17129,7 @@
         <v>986</v>
       </c>
       <c r="C963" t="s">
-        <v>2003</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="964" spans="1:3">
@@ -17182,7 +17140,7 @@
         <v>987</v>
       </c>
       <c r="C964" t="s">
-        <v>2004</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="965" spans="1:3">
@@ -17193,7 +17151,7 @@
         <v>988</v>
       </c>
       <c r="C965" t="s">
-        <v>2005</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="966" spans="1:3">
@@ -17204,7 +17162,7 @@
         <v>989</v>
       </c>
       <c r="C966" t="s">
-        <v>2006</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="967" spans="1:3">
@@ -17215,7 +17173,7 @@
         <v>990</v>
       </c>
       <c r="C967" t="s">
-        <v>2007</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="968" spans="1:3">
@@ -17226,7 +17184,7 @@
         <v>991</v>
       </c>
       <c r="C968" t="s">
-        <v>2008</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="969" spans="1:3">
@@ -17237,7 +17195,7 @@
         <v>992</v>
       </c>
       <c r="C969" t="s">
-        <v>2009</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="970" spans="1:3">
@@ -17248,7 +17206,7 @@
         <v>993</v>
       </c>
       <c r="C970" t="s">
-        <v>2010</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="971" spans="1:3">
@@ -17259,7 +17217,7 @@
         <v>994</v>
       </c>
       <c r="C971" t="s">
-        <v>2011</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="972" spans="1:3">
@@ -17270,7 +17228,7 @@
         <v>995</v>
       </c>
       <c r="C972" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="973" spans="1:3">
@@ -17281,7 +17239,7 @@
         <v>996</v>
       </c>
       <c r="C973" t="s">
-        <v>2012</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="974" spans="1:3">
@@ -17292,7 +17250,7 @@
         <v>997</v>
       </c>
       <c r="C974" t="s">
-        <v>2013</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="975" spans="1:3">
@@ -17303,7 +17261,7 @@
         <v>998</v>
       </c>
       <c r="C975" t="s">
-        <v>2014</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="976" spans="1:3">
@@ -17314,7 +17272,7 @@
         <v>999</v>
       </c>
       <c r="C976" t="s">
-        <v>2015</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="977" spans="1:3">
@@ -17325,7 +17283,7 @@
         <v>1000</v>
       </c>
       <c r="C977" t="s">
-        <v>2016</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="978" spans="1:3">
@@ -17336,7 +17294,7 @@
         <v>1001</v>
       </c>
       <c r="C978" t="s">
-        <v>2017</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="979" spans="1:3">
@@ -17347,7 +17305,7 @@
         <v>1002</v>
       </c>
       <c r="C979" t="s">
-        <v>2018</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="980" spans="1:3">
@@ -17358,7 +17316,7 @@
         <v>1003</v>
       </c>
       <c r="C980" t="s">
-        <v>2019</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="981" spans="1:3">
@@ -17369,7 +17327,7 @@
         <v>1004</v>
       </c>
       <c r="C981" t="s">
-        <v>2020</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="982" spans="1:3">
@@ -17380,7 +17338,7 @@
         <v>1005</v>
       </c>
       <c r="C982" t="s">
-        <v>2021</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="983" spans="1:3">
@@ -17391,7 +17349,7 @@
         <v>1006</v>
       </c>
       <c r="C983" t="s">
-        <v>2022</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="984" spans="1:3">
@@ -17402,7 +17360,7 @@
         <v>1007</v>
       </c>
       <c r="C984" t="s">
-        <v>2023</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="985" spans="1:3">
@@ -17413,7 +17371,7 @@
         <v>1008</v>
       </c>
       <c r="C985" t="s">
-        <v>2024</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="986" spans="1:3">
@@ -17424,7 +17382,7 @@
         <v>1009</v>
       </c>
       <c r="C986" t="s">
-        <v>2025</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="987" spans="1:3">
@@ -17435,7 +17393,7 @@
         <v>1010</v>
       </c>
       <c r="C987" t="s">
-        <v>2026</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="988" spans="1:3">
@@ -17446,7 +17404,7 @@
         <v>1011</v>
       </c>
       <c r="C988" t="s">
-        <v>2027</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="989" spans="1:3">
@@ -17457,7 +17415,7 @@
         <v>1012</v>
       </c>
       <c r="C989" t="s">
-        <v>2028</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="990" spans="1:3">
@@ -17468,7 +17426,7 @@
         <v>1013</v>
       </c>
       <c r="C990" t="s">
-        <v>2029</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="991" spans="1:3">
@@ -17479,7 +17437,7 @@
         <v>1014</v>
       </c>
       <c r="C991" t="s">
-        <v>2030</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="992" spans="1:3">
@@ -17490,7 +17448,7 @@
         <v>1015</v>
       </c>
       <c r="C992" t="s">
-        <v>2031</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="993" spans="1:3">
@@ -17501,7 +17459,7 @@
         <v>1016</v>
       </c>
       <c r="C993" t="s">
-        <v>2006</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="994" spans="1:3">
@@ -17512,7 +17470,7 @@
         <v>1017</v>
       </c>
       <c r="C994" t="s">
-        <v>2032</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="995" spans="1:3">
@@ -17523,7 +17481,7 @@
         <v>1018</v>
       </c>
       <c r="C995" t="s">
-        <v>2033</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="996" spans="1:3">
@@ -17534,84 +17492,84 @@
         <v>1019</v>
       </c>
       <c r="C996" t="s">
-        <v>2034</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="997" spans="1:3">
       <c r="A997" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B997" t="s">
         <v>1020</v>
       </c>
       <c r="C997" t="s">
-        <v>1987</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="998" spans="1:3">
       <c r="A998" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B998" t="s">
         <v>1021</v>
       </c>
       <c r="C998" t="s">
-        <v>2035</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="999" spans="1:3">
       <c r="A999" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B999" t="s">
         <v>1022</v>
       </c>
       <c r="C999" t="s">
-        <v>2036</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="1000" spans="1:3">
       <c r="A1000" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1000" t="s">
         <v>1023</v>
       </c>
       <c r="C1000" t="s">
-        <v>2037</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="1001" spans="1:3">
       <c r="A1001" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1001" t="s">
         <v>1024</v>
       </c>
       <c r="C1001" t="s">
-        <v>2038</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="1002" spans="1:3">
       <c r="A1002" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1002" t="s">
         <v>1025</v>
       </c>
       <c r="C1002" t="s">
-        <v>2039</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="1003" spans="1:3">
       <c r="A1003" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1003" t="s">
         <v>1026</v>
       </c>
       <c r="C1003" t="s">
-        <v>2040</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="1004" spans="1:3">
@@ -17622,7 +17580,7 @@
         <v>1027</v>
       </c>
       <c r="C1004" t="s">
-        <v>2041</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="1005" spans="1:3">
@@ -17633,7 +17591,7 @@
         <v>1028</v>
       </c>
       <c r="C1005" t="s">
-        <v>2042</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="1006" spans="1:3">
@@ -17644,7 +17602,7 @@
         <v>1029</v>
       </c>
       <c r="C1006" t="s">
-        <v>2043</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1007" spans="1:3">
@@ -17655,7 +17613,7 @@
         <v>1030</v>
       </c>
       <c r="C1007" t="s">
-        <v>2044</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="1008" spans="1:3">
@@ -17666,7 +17624,7 @@
         <v>1031</v>
       </c>
       <c r="C1008" t="s">
-        <v>2045</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="1009" spans="1:3">
@@ -17677,7 +17635,7 @@
         <v>1032</v>
       </c>
       <c r="C1009" t="s">
-        <v>2046</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="1010" spans="1:3">
@@ -17688,7 +17646,7 @@
         <v>1033</v>
       </c>
       <c r="C1010" t="s">
-        <v>2047</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="1011" spans="1:3">
@@ -17699,7 +17657,7 @@
         <v>1034</v>
       </c>
       <c r="C1011" t="s">
-        <v>2048</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="1012" spans="1:3">
@@ -17710,7 +17668,7 @@
         <v>1035</v>
       </c>
       <c r="C1012" t="s">
-        <v>2049</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="1013" spans="1:3">
@@ -17721,7 +17679,7 @@
         <v>1036</v>
       </c>
       <c r="C1013" t="s">
-        <v>2050</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="1014" spans="1:3">
@@ -17732,7 +17690,7 @@
         <v>1037</v>
       </c>
       <c r="C1014" t="s">
-        <v>2051</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="1015" spans="1:3">
@@ -17743,7 +17701,7 @@
         <v>1038</v>
       </c>
       <c r="C1015" t="s">
-        <v>2052</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="1016" spans="1:3">
@@ -17754,7 +17712,7 @@
         <v>1039</v>
       </c>
       <c r="C1016" t="s">
-        <v>2053</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="1017" spans="1:3">
@@ -17765,7 +17723,7 @@
         <v>1040</v>
       </c>
       <c r="C1017" t="s">
-        <v>2054</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="1018" spans="1:3">
@@ -17776,7 +17734,7 @@
         <v>1041</v>
       </c>
       <c r="C1018" t="s">
-        <v>2055</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="1019" spans="1:3">
@@ -17787,7 +17745,7 @@
         <v>1042</v>
       </c>
       <c r="C1019" t="s">
-        <v>2056</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="1020" spans="1:3">
@@ -17798,7 +17756,7 @@
         <v>1043</v>
       </c>
       <c r="C1020" t="s">
-        <v>2057</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="1021" spans="1:3">
@@ -17809,7 +17767,7 @@
         <v>1044</v>
       </c>
       <c r="C1021" t="s">
-        <v>2058</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="1022" spans="1:3">
@@ -17820,7 +17778,7 @@
         <v>1045</v>
       </c>
       <c r="C1022" t="s">
-        <v>2059</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1023" spans="1:3">
@@ -17831,95 +17789,18 @@
         <v>1046</v>
       </c>
       <c r="C1023" t="s">
-        <v>2060</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="1024" spans="1:3">
       <c r="A1024" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1024" t="s">
         <v>1047</v>
       </c>
       <c r="C1024" t="s">
-        <v>2061</v>
-      </c>
-    </row>
-    <row r="1025" spans="1:3">
-      <c r="A1025" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1025" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C1025" t="s">
-        <v>2062</v>
-      </c>
-    </row>
-    <row r="1026" spans="1:3">
-      <c r="A1026" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1026" t="s">
-        <v>1049</v>
-      </c>
-      <c r="C1026" t="s">
-        <v>2063</v>
-      </c>
-    </row>
-    <row r="1027" spans="1:3">
-      <c r="A1027" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1027" t="s">
-        <v>1050</v>
-      </c>
-      <c r="C1027" t="s">
-        <v>2064</v>
-      </c>
-    </row>
-    <row r="1028" spans="1:3">
-      <c r="A1028" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1028" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C1028" t="s">
-        <v>2065</v>
-      </c>
-    </row>
-    <row r="1029" spans="1:3">
-      <c r="A1029" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1029" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C1029" t="s">
-        <v>2066</v>
-      </c>
-    </row>
-    <row r="1030" spans="1:3">
-      <c r="A1030" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1030" t="s">
-        <v>1053</v>
-      </c>
-      <c r="C1030" t="s">
-        <v>2067</v>
-      </c>
-    </row>
-    <row r="1031" spans="1:3">
-      <c r="A1031" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1031" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C1031" t="s">
-        <v>2068</v>
+        <v>2054</v>
       </c>
     </row>
   </sheetData>

--- a/faltantes_por_estados.xlsx
+++ b/faltantes_por_estados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2985" uniqueCount="1997">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2970" uniqueCount="1987">
   <si>
     <t>entidad</t>
   </si>
@@ -295,9 +295,6 @@
     <t>BSIMB000013</t>
   </si>
   <si>
-    <t>BSIMB000066</t>
-  </si>
-  <si>
     <t>BSIMB000083</t>
   </si>
   <si>
@@ -379,9 +376,6 @@
     <t>BSIMB000491</t>
   </si>
   <si>
-    <t>BSIMB000532</t>
-  </si>
-  <si>
     <t>BSIMB000684</t>
   </si>
   <si>
@@ -2131,9 +2125,6 @@
     <t>SPIMB001944</t>
   </si>
   <si>
-    <t>SLIMB000760</t>
-  </si>
-  <si>
     <t>SLIMB000801</t>
   </si>
   <si>
@@ -2869,9 +2860,6 @@
     <t>TSIMB001716</t>
   </si>
   <si>
-    <t>TSIMB001721</t>
-  </si>
-  <si>
     <t>TSIMB001762</t>
   </si>
   <si>
@@ -3067,9 +3055,6 @@
     <t>VZIMB008543</t>
   </si>
   <si>
-    <t>VZIMB008700</t>
-  </si>
-  <si>
     <t>ZSIMB001624</t>
   </si>
   <si>
@@ -3262,9 +3247,6 @@
     <t>CENTRO DE SALUD CIUDAD CONSTITUCIÓN</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD LA PURÍSIMA</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD SAN ISIDRO</t>
   </si>
   <si>
@@ -3346,9 +3328,6 @@
     <t>CENTRO DE SALUD MARQUEZ DE LEÓN, LA PAZ</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD SAN MIGUEL DE COMONDÚ</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD LA RIBERA</t>
   </si>
   <si>
@@ -5077,9 +5056,6 @@
     <t>SAN NICOLÁS DE LOS MONTES</t>
   </si>
   <si>
-    <t>HIGUERA DE ABUYA</t>
-  </si>
-  <si>
     <t>QUILA</t>
   </si>
   <si>
@@ -5812,9 +5788,6 @@
     <t>CENTRO DE SALUD LAS AMÉRICAS</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD COL. CARMEN ROMANO DE LÓPEZ PORTILLO</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD COL. NUEVO AMANECER</t>
   </si>
   <si>
@@ -5999,9 +5972,6 @@
   </si>
   <si>
     <t>C.S. JOPOY</t>
-  </si>
-  <si>
-    <t>COL. MORELOS</t>
   </si>
   <si>
     <t>CENTRO DE SALUD COL. ESTRELLA DE ORO</t>
@@ -6362,7 +6332,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C995"/>
+  <dimension ref="A1:C990"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6384,7 +6354,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6395,7 +6365,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6406,7 +6376,7 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6417,7 +6387,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6428,7 +6398,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6439,7 +6409,7 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6450,7 +6420,7 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6461,7 +6431,7 @@
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6472,7 +6442,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6483,7 +6453,7 @@
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6494,7 +6464,7 @@
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6505,7 +6475,7 @@
         <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6516,7 +6486,7 @@
         <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6527,7 +6497,7 @@
         <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -6538,7 +6508,7 @@
         <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6560,7 +6530,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6571,7 +6541,7 @@
         <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6582,7 +6552,7 @@
         <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6593,7 +6563,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6604,7 +6574,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6615,7 +6585,7 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6626,7 +6596,7 @@
         <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6637,7 +6607,7 @@
         <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -6648,7 +6618,7 @@
         <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6670,7 +6640,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6692,7 +6662,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -6703,7 +6673,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="s">
-        <v>1045</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -6714,7 +6684,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -6725,7 +6695,7 @@
         <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6736,7 +6706,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -6747,7 +6717,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6758,7 +6728,7 @@
         <v>59</v>
       </c>
       <c r="C36" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6769,7 +6739,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -6780,7 +6750,7 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -6791,7 +6761,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -6802,7 +6772,7 @@
         <v>63</v>
       </c>
       <c r="C40" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -6813,7 +6783,7 @@
         <v>64</v>
       </c>
       <c r="C41" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -6824,7 +6794,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -6835,7 +6805,7 @@
         <v>66</v>
       </c>
       <c r="C43" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -6846,7 +6816,7 @@
         <v>67</v>
       </c>
       <c r="C44" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -6857,7 +6827,7 @@
         <v>68</v>
       </c>
       <c r="C45" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -6868,7 +6838,7 @@
         <v>69</v>
       </c>
       <c r="C46" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -6879,7 +6849,7 @@
         <v>70</v>
       </c>
       <c r="C47" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -6890,7 +6860,7 @@
         <v>71</v>
       </c>
       <c r="C48" t="s">
-        <v>1061</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -6901,7 +6871,7 @@
         <v>72</v>
       </c>
       <c r="C49" t="s">
-        <v>1062</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -6912,7 +6882,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>1063</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -6923,7 +6893,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -6934,7 +6904,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="s">
-        <v>1065</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -6945,7 +6915,7 @@
         <v>76</v>
       </c>
       <c r="C53" t="s">
-        <v>1066</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -6956,7 +6926,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>1067</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -6967,7 +6937,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="s">
-        <v>1068</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -6978,7 +6948,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="s">
-        <v>1069</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -6989,7 +6959,7 @@
         <v>80</v>
       </c>
       <c r="C57" t="s">
-        <v>1070</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -7000,7 +6970,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="s">
-        <v>1071</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -7011,7 +6981,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="s">
-        <v>1072</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -7033,7 +7003,7 @@
         <v>84</v>
       </c>
       <c r="C61" t="s">
-        <v>1073</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -7044,7 +7014,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -7055,7 +7025,7 @@
         <v>86</v>
       </c>
       <c r="C63" t="s">
-        <v>1075</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -7066,7 +7036,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="s">
-        <v>1076</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -7077,7 +7047,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="s">
-        <v>1077</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -7088,7 +7058,7 @@
         <v>89</v>
       </c>
       <c r="C66" t="s">
-        <v>1078</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -7099,7 +7069,7 @@
         <v>90</v>
       </c>
       <c r="C67" t="s">
-        <v>1079</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -7110,7 +7080,7 @@
         <v>91</v>
       </c>
       <c r="C68" t="s">
-        <v>1080</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -7121,7 +7091,7 @@
         <v>92</v>
       </c>
       <c r="C69" t="s">
-        <v>1081</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -7132,7 +7102,7 @@
         <v>93</v>
       </c>
       <c r="C70" t="s">
-        <v>1082</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -7143,7 +7113,7 @@
         <v>94</v>
       </c>
       <c r="C71" t="s">
-        <v>1083</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -7154,7 +7124,7 @@
         <v>95</v>
       </c>
       <c r="C72" t="s">
-        <v>1084</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -7165,7 +7135,7 @@
         <v>96</v>
       </c>
       <c r="C73" t="s">
-        <v>1085</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -7176,7 +7146,7 @@
         <v>97</v>
       </c>
       <c r="C74" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -7187,7 +7157,7 @@
         <v>98</v>
       </c>
       <c r="C75" t="s">
-        <v>1087</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -7198,7 +7168,7 @@
         <v>99</v>
       </c>
       <c r="C76" t="s">
-        <v>1088</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -7209,7 +7179,7 @@
         <v>100</v>
       </c>
       <c r="C77" t="s">
-        <v>1089</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -7220,7 +7190,7 @@
         <v>101</v>
       </c>
       <c r="C78" t="s">
-        <v>1090</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -7231,7 +7201,7 @@
         <v>102</v>
       </c>
       <c r="C79" t="s">
-        <v>1091</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -7242,7 +7212,7 @@
         <v>103</v>
       </c>
       <c r="C80" t="s">
-        <v>1092</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -7253,7 +7223,7 @@
         <v>104</v>
       </c>
       <c r="C81" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -7264,7 +7234,7 @@
         <v>105</v>
       </c>
       <c r="C82" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -7275,7 +7245,7 @@
         <v>106</v>
       </c>
       <c r="C83" t="s">
-        <v>1095</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -7286,7 +7256,7 @@
         <v>107</v>
       </c>
       <c r="C84" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -7297,7 +7267,7 @@
         <v>108</v>
       </c>
       <c r="C85" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -7308,7 +7278,7 @@
         <v>109</v>
       </c>
       <c r="C86" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -7319,7 +7289,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="s">
-        <v>1099</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -7330,7 +7300,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -7341,7 +7311,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="s">
-        <v>1101</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -7352,7 +7322,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="s">
-        <v>1102</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -7363,7 +7333,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -7374,7 +7344,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="s">
-        <v>1104</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -7385,7 +7355,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="s">
-        <v>1105</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -7396,7 +7366,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="s">
-        <v>1106</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -7407,7 +7377,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -7418,7 +7388,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="s">
-        <v>1108</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -7429,7 +7399,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="s">
-        <v>1109</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -7440,7 +7410,7 @@
         <v>121</v>
       </c>
       <c r="C98" t="s">
-        <v>1110</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -7451,7 +7421,7 @@
         <v>122</v>
       </c>
       <c r="C99" t="s">
-        <v>1111</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -7462,7 +7432,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -7473,7 +7443,7 @@
         <v>124</v>
       </c>
       <c r="C101" t="s">
-        <v>1113</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -7484,29 +7454,29 @@
         <v>125</v>
       </c>
       <c r="C102" t="s">
-        <v>1114</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B103" t="s">
         <v>126</v>
       </c>
       <c r="C103" t="s">
-        <v>1115</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B104" t="s">
         <v>127</v>
       </c>
       <c r="C104" t="s">
-        <v>1116</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -7517,7 +7487,7 @@
         <v>128</v>
       </c>
       <c r="C105" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -7528,7 +7498,7 @@
         <v>129</v>
       </c>
       <c r="C106" t="s">
-        <v>1118</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -7539,7 +7509,7 @@
         <v>130</v>
       </c>
       <c r="C107" t="s">
-        <v>1119</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -7550,7 +7520,7 @@
         <v>131</v>
       </c>
       <c r="C108" t="s">
-        <v>1120</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -7561,7 +7531,7 @@
         <v>132</v>
       </c>
       <c r="C109" t="s">
-        <v>1121</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -7572,7 +7542,7 @@
         <v>133</v>
       </c>
       <c r="C110" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -7583,7 +7553,7 @@
         <v>134</v>
       </c>
       <c r="C111" t="s">
-        <v>1123</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -7594,7 +7564,7 @@
         <v>135</v>
       </c>
       <c r="C112" t="s">
-        <v>1124</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -7605,7 +7575,7 @@
         <v>136</v>
       </c>
       <c r="C113" t="s">
-        <v>1125</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -7616,7 +7586,7 @@
         <v>137</v>
       </c>
       <c r="C114" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -7627,7 +7597,7 @@
         <v>138</v>
       </c>
       <c r="C115" t="s">
-        <v>1127</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -7638,7 +7608,7 @@
         <v>139</v>
       </c>
       <c r="C116" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -7649,40 +7619,40 @@
         <v>140</v>
       </c>
       <c r="C117" t="s">
-        <v>1129</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B118" t="s">
         <v>141</v>
       </c>
       <c r="C118" t="s">
-        <v>1130</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B119" t="s">
         <v>142</v>
       </c>
       <c r="C119" t="s">
-        <v>1131</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B120" t="s">
         <v>143</v>
       </c>
       <c r="C120" t="s">
-        <v>1132</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -7693,7 +7663,7 @@
         <v>144</v>
       </c>
       <c r="C121" t="s">
-        <v>1133</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -7704,7 +7674,7 @@
         <v>145</v>
       </c>
       <c r="C122" t="s">
-        <v>1134</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -7715,7 +7685,7 @@
         <v>146</v>
       </c>
       <c r="C123" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -7726,7 +7696,7 @@
         <v>147</v>
       </c>
       <c r="C124" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -7737,7 +7707,7 @@
         <v>148</v>
       </c>
       <c r="C125" t="s">
-        <v>1137</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -7748,7 +7718,7 @@
         <v>149</v>
       </c>
       <c r="C126" t="s">
-        <v>1138</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -7759,7 +7729,7 @@
         <v>150</v>
       </c>
       <c r="C127" t="s">
-        <v>1139</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -7770,7 +7740,7 @@
         <v>151</v>
       </c>
       <c r="C128" t="s">
-        <v>1140</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -7781,7 +7751,7 @@
         <v>152</v>
       </c>
       <c r="C129" t="s">
-        <v>1141</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -7792,7 +7762,7 @@
         <v>153</v>
       </c>
       <c r="C130" t="s">
-        <v>1142</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -7803,7 +7773,7 @@
         <v>154</v>
       </c>
       <c r="C131" t="s">
-        <v>1143</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -7814,7 +7784,7 @@
         <v>155</v>
       </c>
       <c r="C132" t="s">
-        <v>1144</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -7825,7 +7795,7 @@
         <v>156</v>
       </c>
       <c r="C133" t="s">
-        <v>1145</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -7836,7 +7806,7 @@
         <v>157</v>
       </c>
       <c r="C134" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -7847,7 +7817,7 @@
         <v>158</v>
       </c>
       <c r="C135" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -7858,7 +7828,7 @@
         <v>159</v>
       </c>
       <c r="C136" t="s">
-        <v>1148</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -7869,7 +7839,7 @@
         <v>160</v>
       </c>
       <c r="C137" t="s">
-        <v>1149</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -7880,7 +7850,7 @@
         <v>161</v>
       </c>
       <c r="C138" t="s">
-        <v>1150</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -7891,7 +7861,7 @@
         <v>162</v>
       </c>
       <c r="C139" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -7902,7 +7872,7 @@
         <v>163</v>
       </c>
       <c r="C140" t="s">
-        <v>1152</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -7913,7 +7883,7 @@
         <v>164</v>
       </c>
       <c r="C141" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -7924,7 +7894,7 @@
         <v>165</v>
       </c>
       <c r="C142" t="s">
-        <v>1154</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -7935,7 +7905,7 @@
         <v>166</v>
       </c>
       <c r="C143" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -7946,7 +7916,7 @@
         <v>167</v>
       </c>
       <c r="C144" t="s">
-        <v>1156</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -7957,7 +7927,7 @@
         <v>168</v>
       </c>
       <c r="C145" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -7968,7 +7938,7 @@
         <v>169</v>
       </c>
       <c r="C146" t="s">
-        <v>1158</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -7979,7 +7949,7 @@
         <v>170</v>
       </c>
       <c r="C147" t="s">
-        <v>1159</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -7990,7 +7960,7 @@
         <v>171</v>
       </c>
       <c r="C148" t="s">
-        <v>1160</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -8001,7 +7971,7 @@
         <v>172</v>
       </c>
       <c r="C149" t="s">
-        <v>1161</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -8012,7 +7982,7 @@
         <v>173</v>
       </c>
       <c r="C150" t="s">
-        <v>1162</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -8023,7 +7993,7 @@
         <v>174</v>
       </c>
       <c r="C151" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -8034,7 +8004,7 @@
         <v>175</v>
       </c>
       <c r="C152" t="s">
-        <v>1164</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -8045,7 +8015,7 @@
         <v>176</v>
       </c>
       <c r="C153" t="s">
-        <v>1165</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -8056,7 +8026,7 @@
         <v>177</v>
       </c>
       <c r="C154" t="s">
-        <v>1166</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -8067,7 +8037,7 @@
         <v>178</v>
       </c>
       <c r="C155" t="s">
-        <v>1167</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -8078,7 +8048,7 @@
         <v>179</v>
       </c>
       <c r="C156" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -8089,7 +8059,7 @@
         <v>180</v>
       </c>
       <c r="C157" t="s">
-        <v>1169</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -8100,7 +8070,7 @@
         <v>181</v>
       </c>
       <c r="C158" t="s">
-        <v>1170</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -8111,7 +8081,7 @@
         <v>182</v>
       </c>
       <c r="C159" t="s">
-        <v>1171</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -8122,7 +8092,7 @@
         <v>183</v>
       </c>
       <c r="C160" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -8133,7 +8103,7 @@
         <v>184</v>
       </c>
       <c r="C161" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -8144,7 +8114,7 @@
         <v>185</v>
       </c>
       <c r="C162" t="s">
-        <v>1174</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -8155,7 +8125,7 @@
         <v>186</v>
       </c>
       <c r="C163" t="s">
-        <v>1175</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -8166,7 +8136,7 @@
         <v>187</v>
       </c>
       <c r="C164" t="s">
-        <v>1176</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -8177,7 +8147,7 @@
         <v>188</v>
       </c>
       <c r="C165" t="s">
-        <v>1177</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -8188,7 +8158,7 @@
         <v>189</v>
       </c>
       <c r="C166" t="s">
-        <v>1178</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -8199,7 +8169,7 @@
         <v>190</v>
       </c>
       <c r="C167" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -8210,7 +8180,7 @@
         <v>191</v>
       </c>
       <c r="C168" t="s">
-        <v>1180</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -8221,7 +8191,7 @@
         <v>192</v>
       </c>
       <c r="C169" t="s">
-        <v>1181</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -8232,7 +8202,7 @@
         <v>193</v>
       </c>
       <c r="C170" t="s">
-        <v>1182</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -8243,7 +8213,7 @@
         <v>194</v>
       </c>
       <c r="C171" t="s">
-        <v>1183</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -8254,7 +8224,7 @@
         <v>195</v>
       </c>
       <c r="C172" t="s">
-        <v>1184</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -8265,7 +8235,7 @@
         <v>196</v>
       </c>
       <c r="C173" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -8276,7 +8246,7 @@
         <v>197</v>
       </c>
       <c r="C174" t="s">
-        <v>1186</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -8287,7 +8257,7 @@
         <v>198</v>
       </c>
       <c r="C175" t="s">
-        <v>1187</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -8298,7 +8268,7 @@
         <v>199</v>
       </c>
       <c r="C176" t="s">
-        <v>1188</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -8309,7 +8279,7 @@
         <v>200</v>
       </c>
       <c r="C177" t="s">
-        <v>1189</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -8320,7 +8290,7 @@
         <v>201</v>
       </c>
       <c r="C178" t="s">
-        <v>1190</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -8331,7 +8301,7 @@
         <v>202</v>
       </c>
       <c r="C179" t="s">
-        <v>1191</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -8342,7 +8312,7 @@
         <v>203</v>
       </c>
       <c r="C180" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -8353,7 +8323,7 @@
         <v>204</v>
       </c>
       <c r="C181" t="s">
-        <v>1193</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -8364,7 +8334,7 @@
         <v>205</v>
       </c>
       <c r="C182" t="s">
-        <v>1194</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -8375,7 +8345,7 @@
         <v>206</v>
       </c>
       <c r="C183" t="s">
-        <v>1195</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -8386,7 +8356,7 @@
         <v>207</v>
       </c>
       <c r="C184" t="s">
-        <v>1196</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -8397,7 +8367,7 @@
         <v>208</v>
       </c>
       <c r="C185" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -8408,7 +8378,7 @@
         <v>209</v>
       </c>
       <c r="C186" t="s">
-        <v>1198</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -8419,7 +8389,7 @@
         <v>210</v>
       </c>
       <c r="C187" t="s">
-        <v>1199</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -8430,7 +8400,7 @@
         <v>211</v>
       </c>
       <c r="C188" t="s">
-        <v>1200</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -8441,7 +8411,7 @@
         <v>212</v>
       </c>
       <c r="C189" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -8452,7 +8422,7 @@
         <v>213</v>
       </c>
       <c r="C190" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -8463,7 +8433,7 @@
         <v>214</v>
       </c>
       <c r="C191" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -8474,7 +8444,7 @@
         <v>215</v>
       </c>
       <c r="C192" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -8485,7 +8455,7 @@
         <v>216</v>
       </c>
       <c r="C193" t="s">
-        <v>1205</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -8496,7 +8466,7 @@
         <v>217</v>
       </c>
       <c r="C194" t="s">
-        <v>1206</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -8507,7 +8477,7 @@
         <v>218</v>
       </c>
       <c r="C195" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -8518,7 +8488,7 @@
         <v>219</v>
       </c>
       <c r="C196" t="s">
-        <v>1208</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -8529,7 +8499,7 @@
         <v>220</v>
       </c>
       <c r="C197" t="s">
-        <v>1209</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -8540,7 +8510,7 @@
         <v>221</v>
       </c>
       <c r="C198" t="s">
-        <v>1210</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -8551,7 +8521,7 @@
         <v>222</v>
       </c>
       <c r="C199" t="s">
-        <v>1211</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -8562,7 +8532,7 @@
         <v>223</v>
       </c>
       <c r="C200" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -8573,7 +8543,7 @@
         <v>224</v>
       </c>
       <c r="C201" t="s">
-        <v>1213</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -8584,7 +8554,7 @@
         <v>225</v>
       </c>
       <c r="C202" t="s">
-        <v>1214</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -8595,7 +8565,7 @@
         <v>226</v>
       </c>
       <c r="C203" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -8606,7 +8576,7 @@
         <v>227</v>
       </c>
       <c r="C204" t="s">
-        <v>1216</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -8617,7 +8587,7 @@
         <v>228</v>
       </c>
       <c r="C205" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -8628,7 +8598,7 @@
         <v>229</v>
       </c>
       <c r="C206" t="s">
-        <v>1218</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -8639,7 +8609,7 @@
         <v>230</v>
       </c>
       <c r="C207" t="s">
-        <v>1219</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -8650,7 +8620,7 @@
         <v>231</v>
       </c>
       <c r="C208" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -8661,7 +8631,7 @@
         <v>232</v>
       </c>
       <c r="C209" t="s">
-        <v>1221</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -8672,7 +8642,7 @@
         <v>233</v>
       </c>
       <c r="C210" t="s">
-        <v>1222</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -8683,7 +8653,7 @@
         <v>234</v>
       </c>
       <c r="C211" t="s">
-        <v>1223</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -8694,7 +8664,7 @@
         <v>235</v>
       </c>
       <c r="C212" t="s">
-        <v>1224</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -8705,7 +8675,7 @@
         <v>236</v>
       </c>
       <c r="C213" t="s">
-        <v>1225</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -8716,7 +8686,7 @@
         <v>237</v>
       </c>
       <c r="C214" t="s">
-        <v>1226</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -8727,7 +8697,7 @@
         <v>238</v>
       </c>
       <c r="C215" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -8738,7 +8708,7 @@
         <v>239</v>
       </c>
       <c r="C216" t="s">
-        <v>1228</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -8749,7 +8719,7 @@
         <v>240</v>
       </c>
       <c r="C217" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -8760,7 +8730,7 @@
         <v>241</v>
       </c>
       <c r="C218" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -8771,7 +8741,7 @@
         <v>242</v>
       </c>
       <c r="C219" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -8782,7 +8752,7 @@
         <v>243</v>
       </c>
       <c r="C220" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -8793,7 +8763,7 @@
         <v>244</v>
       </c>
       <c r="C221" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -8804,7 +8774,7 @@
         <v>245</v>
       </c>
       <c r="C222" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -8815,7 +8785,7 @@
         <v>246</v>
       </c>
       <c r="C223" t="s">
-        <v>1235</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -8826,7 +8796,7 @@
         <v>247</v>
       </c>
       <c r="C224" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -8837,7 +8807,7 @@
         <v>248</v>
       </c>
       <c r="C225" t="s">
-        <v>1237</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -8848,7 +8818,7 @@
         <v>249</v>
       </c>
       <c r="C226" t="s">
-        <v>1238</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -8859,7 +8829,7 @@
         <v>250</v>
       </c>
       <c r="C227" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -8870,7 +8840,7 @@
         <v>251</v>
       </c>
       <c r="C228" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -8881,7 +8851,7 @@
         <v>252</v>
       </c>
       <c r="C229" t="s">
-        <v>1241</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -8892,7 +8862,7 @@
         <v>253</v>
       </c>
       <c r="C230" t="s">
-        <v>1242</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -8903,7 +8873,7 @@
         <v>254</v>
       </c>
       <c r="C231" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -8914,7 +8884,7 @@
         <v>255</v>
       </c>
       <c r="C232" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -8925,7 +8895,7 @@
         <v>256</v>
       </c>
       <c r="C233" t="s">
-        <v>1245</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -8936,7 +8906,7 @@
         <v>257</v>
       </c>
       <c r="C234" t="s">
-        <v>1246</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -8947,7 +8917,7 @@
         <v>258</v>
       </c>
       <c r="C235" t="s">
-        <v>1247</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -8958,7 +8928,7 @@
         <v>259</v>
       </c>
       <c r="C236" t="s">
-        <v>1248</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -8969,7 +8939,7 @@
         <v>260</v>
       </c>
       <c r="C237" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -8980,7 +8950,7 @@
         <v>261</v>
       </c>
       <c r="C238" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -8991,7 +8961,7 @@
         <v>262</v>
       </c>
       <c r="C239" t="s">
-        <v>1251</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -9002,7 +8972,7 @@
         <v>263</v>
       </c>
       <c r="C240" t="s">
-        <v>1252</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -9013,7 +8983,7 @@
         <v>264</v>
       </c>
       <c r="C241" t="s">
-        <v>1253</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -9024,7 +8994,7 @@
         <v>265</v>
       </c>
       <c r="C242" t="s">
-        <v>1254</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -9035,7 +9005,7 @@
         <v>266</v>
       </c>
       <c r="C243" t="s">
-        <v>1255</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -9046,7 +9016,7 @@
         <v>267</v>
       </c>
       <c r="C244" t="s">
-        <v>1256</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -9057,7 +9027,7 @@
         <v>268</v>
       </c>
       <c r="C245" t="s">
-        <v>1257</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -9068,7 +9038,7 @@
         <v>269</v>
       </c>
       <c r="C246" t="s">
-        <v>1258</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -9079,7 +9049,7 @@
         <v>270</v>
       </c>
       <c r="C247" t="s">
-        <v>1259</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -9090,7 +9060,7 @@
         <v>271</v>
       </c>
       <c r="C248" t="s">
-        <v>1260</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -9101,7 +9071,7 @@
         <v>272</v>
       </c>
       <c r="C249" t="s">
-        <v>1261</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -9112,7 +9082,7 @@
         <v>273</v>
       </c>
       <c r="C250" t="s">
-        <v>1262</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -9123,7 +9093,7 @@
         <v>274</v>
       </c>
       <c r="C251" t="s">
-        <v>1263</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -9134,7 +9104,7 @@
         <v>275</v>
       </c>
       <c r="C252" t="s">
-        <v>1264</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -9145,7 +9115,7 @@
         <v>276</v>
       </c>
       <c r="C253" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -9156,7 +9126,7 @@
         <v>277</v>
       </c>
       <c r="C254" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -9167,7 +9137,7 @@
         <v>278</v>
       </c>
       <c r="C255" t="s">
-        <v>1267</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -9178,7 +9148,7 @@
         <v>279</v>
       </c>
       <c r="C256" t="s">
-        <v>1268</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -9189,7 +9159,7 @@
         <v>280</v>
       </c>
       <c r="C257" t="s">
-        <v>1269</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -9200,7 +9170,7 @@
         <v>281</v>
       </c>
       <c r="C258" t="s">
-        <v>1270</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="259" spans="1:3">
@@ -9211,7 +9181,7 @@
         <v>282</v>
       </c>
       <c r="C259" t="s">
-        <v>1271</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -9222,7 +9192,7 @@
         <v>283</v>
       </c>
       <c r="C260" t="s">
-        <v>1272</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="261" spans="1:3">
@@ -9233,7 +9203,7 @@
         <v>284</v>
       </c>
       <c r="C261" t="s">
-        <v>1273</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="262" spans="1:3">
@@ -9244,7 +9214,7 @@
         <v>285</v>
       </c>
       <c r="C262" t="s">
-        <v>1274</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -9255,7 +9225,7 @@
         <v>286</v>
       </c>
       <c r="C263" t="s">
-        <v>1275</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="264" spans="1:3">
@@ -9266,7 +9236,7 @@
         <v>287</v>
       </c>
       <c r="C264" t="s">
-        <v>1276</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -9277,7 +9247,7 @@
         <v>288</v>
       </c>
       <c r="C265" t="s">
-        <v>1277</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="266" spans="1:3">
@@ -9288,7 +9258,7 @@
         <v>289</v>
       </c>
       <c r="C266" t="s">
-        <v>1278</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="267" spans="1:3">
@@ -9299,7 +9269,7 @@
         <v>290</v>
       </c>
       <c r="C267" t="s">
-        <v>1279</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="268" spans="1:3">
@@ -9310,7 +9280,7 @@
         <v>291</v>
       </c>
       <c r="C268" t="s">
-        <v>1280</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="269" spans="1:3">
@@ -9321,7 +9291,7 @@
         <v>292</v>
       </c>
       <c r="C269" t="s">
-        <v>1281</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="270" spans="1:3">
@@ -9332,7 +9302,7 @@
         <v>293</v>
       </c>
       <c r="C270" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="271" spans="1:3">
@@ -9343,7 +9313,7 @@
         <v>294</v>
       </c>
       <c r="C271" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="272" spans="1:3">
@@ -9354,7 +9324,7 @@
         <v>295</v>
       </c>
       <c r="C272" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="273" spans="1:3">
@@ -9365,7 +9335,7 @@
         <v>296</v>
       </c>
       <c r="C273" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="274" spans="1:3">
@@ -9376,7 +9346,7 @@
         <v>297</v>
       </c>
       <c r="C274" t="s">
-        <v>1286</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="275" spans="1:3">
@@ -9387,7 +9357,7 @@
         <v>298</v>
       </c>
       <c r="C275" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="276" spans="1:3">
@@ -9398,7 +9368,7 @@
         <v>299</v>
       </c>
       <c r="C276" t="s">
-        <v>1288</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="277" spans="1:3">
@@ -9409,7 +9379,7 @@
         <v>300</v>
       </c>
       <c r="C277" t="s">
-        <v>1289</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="278" spans="1:3">
@@ -9420,7 +9390,7 @@
         <v>301</v>
       </c>
       <c r="C278" t="s">
-        <v>1207</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="279" spans="1:3">
@@ -9431,7 +9401,7 @@
         <v>302</v>
       </c>
       <c r="C279" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="280" spans="1:3">
@@ -9442,7 +9412,7 @@
         <v>303</v>
       </c>
       <c r="C280" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -9453,7 +9423,7 @@
         <v>304</v>
       </c>
       <c r="C281" t="s">
-        <v>1292</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="282" spans="1:3">
@@ -9464,7 +9434,7 @@
         <v>305</v>
       </c>
       <c r="C282" t="s">
-        <v>1293</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="283" spans="1:3">
@@ -9475,7 +9445,7 @@
         <v>306</v>
       </c>
       <c r="C283" t="s">
-        <v>1294</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="284" spans="1:3">
@@ -9486,7 +9456,7 @@
         <v>307</v>
       </c>
       <c r="C284" t="s">
-        <v>1295</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="285" spans="1:3">
@@ -9497,7 +9467,7 @@
         <v>308</v>
       </c>
       <c r="C285" t="s">
-        <v>1296</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="286" spans="1:3">
@@ -9508,7 +9478,7 @@
         <v>309</v>
       </c>
       <c r="C286" t="s">
-        <v>1297</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="287" spans="1:3">
@@ -9519,7 +9489,7 @@
         <v>310</v>
       </c>
       <c r="C287" t="s">
-        <v>1298</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="288" spans="1:3">
@@ -9530,7 +9500,7 @@
         <v>311</v>
       </c>
       <c r="C288" t="s">
-        <v>1299</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="289" spans="1:3">
@@ -9541,7 +9511,7 @@
         <v>312</v>
       </c>
       <c r="C289" t="s">
-        <v>1300</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="290" spans="1:3">
@@ -9552,7 +9522,7 @@
         <v>313</v>
       </c>
       <c r="C290" t="s">
-        <v>1301</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="291" spans="1:3">
@@ -9563,7 +9533,7 @@
         <v>314</v>
       </c>
       <c r="C291" t="s">
-        <v>1302</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="292" spans="1:3">
@@ -9574,7 +9544,7 @@
         <v>315</v>
       </c>
       <c r="C292" t="s">
-        <v>1303</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="293" spans="1:3">
@@ -9585,7 +9555,7 @@
         <v>316</v>
       </c>
       <c r="C293" t="s">
-        <v>1304</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="294" spans="1:3">
@@ -9596,7 +9566,7 @@
         <v>317</v>
       </c>
       <c r="C294" t="s">
-        <v>1305</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="295" spans="1:3">
@@ -9607,7 +9577,7 @@
         <v>318</v>
       </c>
       <c r="C295" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="296" spans="1:3">
@@ -9618,7 +9588,7 @@
         <v>319</v>
       </c>
       <c r="C296" t="s">
-        <v>1307</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="297" spans="1:3">
@@ -9629,7 +9599,7 @@
         <v>320</v>
       </c>
       <c r="C297" t="s">
-        <v>1308</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="298" spans="1:3">
@@ -9640,7 +9610,7 @@
         <v>321</v>
       </c>
       <c r="C298" t="s">
-        <v>1309</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="299" spans="1:3">
@@ -9651,7 +9621,7 @@
         <v>322</v>
       </c>
       <c r="C299" t="s">
-        <v>1310</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="300" spans="1:3">
@@ -9662,7 +9632,7 @@
         <v>323</v>
       </c>
       <c r="C300" t="s">
-        <v>1311</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="301" spans="1:3">
@@ -9673,7 +9643,7 @@
         <v>324</v>
       </c>
       <c r="C301" t="s">
-        <v>1312</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -9684,7 +9654,7 @@
         <v>325</v>
       </c>
       <c r="C302" t="s">
-        <v>1313</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="303" spans="1:3">
@@ -9695,7 +9665,7 @@
         <v>326</v>
       </c>
       <c r="C303" t="s">
-        <v>1314</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="304" spans="1:3">
@@ -9706,7 +9676,7 @@
         <v>327</v>
       </c>
       <c r="C304" t="s">
-        <v>1315</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -9717,7 +9687,7 @@
         <v>328</v>
       </c>
       <c r="C305" t="s">
-        <v>1316</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="306" spans="1:3">
@@ -9728,7 +9698,7 @@
         <v>329</v>
       </c>
       <c r="C306" t="s">
-        <v>1317</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="307" spans="1:3">
@@ -9739,7 +9709,7 @@
         <v>330</v>
       </c>
       <c r="C307" t="s">
-        <v>1318</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="308" spans="1:3">
@@ -9750,7 +9720,7 @@
         <v>331</v>
       </c>
       <c r="C308" t="s">
-        <v>1319</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="309" spans="1:3">
@@ -9761,7 +9731,7 @@
         <v>332</v>
       </c>
       <c r="C309" t="s">
-        <v>1320</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="310" spans="1:3">
@@ -9772,29 +9742,29 @@
         <v>333</v>
       </c>
       <c r="C310" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="A311" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B311" t="s">
         <v>334</v>
       </c>
       <c r="C311" t="s">
-        <v>1322</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="312" spans="1:3">
       <c r="A312" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B312" t="s">
         <v>335</v>
       </c>
       <c r="C312" t="s">
-        <v>1323</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="313" spans="1:3">
@@ -9805,7 +9775,7 @@
         <v>336</v>
       </c>
       <c r="C313" t="s">
-        <v>1324</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="314" spans="1:3">
@@ -9816,7 +9786,7 @@
         <v>337</v>
       </c>
       <c r="C314" t="s">
-        <v>1325</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="315" spans="1:3">
@@ -9827,7 +9797,7 @@
         <v>338</v>
       </c>
       <c r="C315" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="316" spans="1:3">
@@ -9838,7 +9808,7 @@
         <v>339</v>
       </c>
       <c r="C316" t="s">
-        <v>1327</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="317" spans="1:3">
@@ -9849,7 +9819,7 @@
         <v>340</v>
       </c>
       <c r="C317" t="s">
-        <v>1328</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="318" spans="1:3">
@@ -9860,7 +9830,7 @@
         <v>341</v>
       </c>
       <c r="C318" t="s">
-        <v>1104</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="319" spans="1:3">
@@ -9871,7 +9841,7 @@
         <v>342</v>
       </c>
       <c r="C319" t="s">
-        <v>1329</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="320" spans="1:3">
@@ -9882,7 +9852,7 @@
         <v>343</v>
       </c>
       <c r="C320" t="s">
-        <v>1330</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="321" spans="1:3">
@@ -9893,7 +9863,7 @@
         <v>344</v>
       </c>
       <c r="C321" t="s">
-        <v>1331</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -9904,7 +9874,7 @@
         <v>345</v>
       </c>
       <c r="C322" t="s">
-        <v>1332</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="323" spans="1:3">
@@ -9915,7 +9885,7 @@
         <v>346</v>
       </c>
       <c r="C323" t="s">
-        <v>1333</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="324" spans="1:3">
@@ -9926,7 +9896,7 @@
         <v>347</v>
       </c>
       <c r="C324" t="s">
-        <v>1095</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -9937,7 +9907,7 @@
         <v>348</v>
       </c>
       <c r="C325" t="s">
-        <v>1334</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="326" spans="1:3">
@@ -9948,7 +9918,7 @@
         <v>349</v>
       </c>
       <c r="C326" t="s">
-        <v>1335</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="327" spans="1:3">
@@ -9959,7 +9929,7 @@
         <v>350</v>
       </c>
       <c r="C327" t="s">
-        <v>1336</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="328" spans="1:3">
@@ -9970,29 +9940,29 @@
         <v>351</v>
       </c>
       <c r="C328" t="s">
-        <v>1337</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="329" spans="1:3">
       <c r="A329" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B329" t="s">
         <v>352</v>
       </c>
       <c r="C329" t="s">
-        <v>1338</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="330" spans="1:3">
       <c r="A330" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B330" t="s">
         <v>353</v>
       </c>
       <c r="C330" t="s">
-        <v>1339</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -10003,7 +9973,7 @@
         <v>354</v>
       </c>
       <c r="C331" t="s">
-        <v>1340</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="332" spans="1:3">
@@ -10014,7 +9984,7 @@
         <v>355</v>
       </c>
       <c r="C332" t="s">
-        <v>1341</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="333" spans="1:3">
@@ -10025,7 +9995,7 @@
         <v>356</v>
       </c>
       <c r="C333" t="s">
-        <v>1342</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="334" spans="1:3">
@@ -10036,7 +10006,7 @@
         <v>357</v>
       </c>
       <c r="C334" t="s">
-        <v>1343</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="335" spans="1:3">
@@ -10047,7 +10017,7 @@
         <v>358</v>
       </c>
       <c r="C335" t="s">
-        <v>1344</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="336" spans="1:3">
@@ -10058,7 +10028,7 @@
         <v>359</v>
       </c>
       <c r="C336" t="s">
-        <v>1345</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="337" spans="1:3">
@@ -10069,7 +10039,7 @@
         <v>360</v>
       </c>
       <c r="C337" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="338" spans="1:3">
@@ -10080,7 +10050,7 @@
         <v>361</v>
       </c>
       <c r="C338" t="s">
-        <v>1347</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="339" spans="1:3">
@@ -10091,7 +10061,7 @@
         <v>362</v>
       </c>
       <c r="C339" t="s">
-        <v>1348</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="340" spans="1:3">
@@ -10102,7 +10072,7 @@
         <v>363</v>
       </c>
       <c r="C340" t="s">
-        <v>1349</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="341" spans="1:3">
@@ -10113,7 +10083,7 @@
         <v>364</v>
       </c>
       <c r="C341" t="s">
-        <v>1350</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -10124,7 +10094,7 @@
         <v>365</v>
       </c>
       <c r="C342" t="s">
-        <v>1351</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="343" spans="1:3">
@@ -10135,7 +10105,7 @@
         <v>366</v>
       </c>
       <c r="C343" t="s">
-        <v>1352</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="344" spans="1:3">
@@ -10146,7 +10116,7 @@
         <v>367</v>
       </c>
       <c r="C344" t="s">
-        <v>1353</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="345" spans="1:3">
@@ -10157,7 +10127,7 @@
         <v>368</v>
       </c>
       <c r="C345" t="s">
-        <v>1354</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="346" spans="1:3">
@@ -10168,7 +10138,7 @@
         <v>369</v>
       </c>
       <c r="C346" t="s">
-        <v>1355</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="347" spans="1:3">
@@ -10179,7 +10149,7 @@
         <v>370</v>
       </c>
       <c r="C347" t="s">
-        <v>1356</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="348" spans="1:3">
@@ -10190,7 +10160,7 @@
         <v>371</v>
       </c>
       <c r="C348" t="s">
-        <v>1357</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="349" spans="1:3">
@@ -10201,7 +10171,7 @@
         <v>372</v>
       </c>
       <c r="C349" t="s">
-        <v>1358</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -10212,7 +10182,7 @@
         <v>373</v>
       </c>
       <c r="C350" t="s">
-        <v>1359</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="351" spans="1:3">
@@ -10223,7 +10193,7 @@
         <v>374</v>
       </c>
       <c r="C351" t="s">
-        <v>1360</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -10234,7 +10204,7 @@
         <v>375</v>
       </c>
       <c r="C352" t="s">
-        <v>1361</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="353" spans="1:3">
@@ -10245,7 +10215,7 @@
         <v>376</v>
       </c>
       <c r="C353" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="354" spans="1:3">
@@ -10256,7 +10226,7 @@
         <v>377</v>
       </c>
       <c r="C354" t="s">
-        <v>1363</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -10267,7 +10237,7 @@
         <v>378</v>
       </c>
       <c r="C355" t="s">
-        <v>1364</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="356" spans="1:3">
@@ -10278,7 +10248,7 @@
         <v>379</v>
       </c>
       <c r="C356" t="s">
-        <v>1365</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="357" spans="1:3">
@@ -10289,7 +10259,7 @@
         <v>380</v>
       </c>
       <c r="C357" t="s">
-        <v>1366</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="358" spans="1:3">
@@ -10300,7 +10270,7 @@
         <v>381</v>
       </c>
       <c r="C358" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="359" spans="1:3">
@@ -10311,7 +10281,7 @@
         <v>382</v>
       </c>
       <c r="C359" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -10322,7 +10292,7 @@
         <v>383</v>
       </c>
       <c r="C360" t="s">
-        <v>1369</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="361" spans="1:3">
@@ -10333,7 +10303,7 @@
         <v>384</v>
       </c>
       <c r="C361" t="s">
-        <v>1370</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="362" spans="1:3">
@@ -10344,7 +10314,7 @@
         <v>385</v>
       </c>
       <c r="C362" t="s">
-        <v>1371</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="363" spans="1:3">
@@ -10355,7 +10325,7 @@
         <v>386</v>
       </c>
       <c r="C363" t="s">
-        <v>1372</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="364" spans="1:3">
@@ -10366,7 +10336,7 @@
         <v>387</v>
       </c>
       <c r="C364" t="s">
-        <v>1373</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="365" spans="1:3">
@@ -10377,7 +10347,7 @@
         <v>388</v>
       </c>
       <c r="C365" t="s">
-        <v>1374</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="366" spans="1:3">
@@ -10388,7 +10358,7 @@
         <v>389</v>
       </c>
       <c r="C366" t="s">
-        <v>1375</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="367" spans="1:3">
@@ -10399,7 +10369,7 @@
         <v>390</v>
       </c>
       <c r="C367" t="s">
-        <v>1376</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="368" spans="1:3">
@@ -10410,7 +10380,7 @@
         <v>391</v>
       </c>
       <c r="C368" t="s">
-        <v>1377</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="369" spans="1:3">
@@ -10421,7 +10391,7 @@
         <v>392</v>
       </c>
       <c r="C369" t="s">
-        <v>1378</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="370" spans="1:3">
@@ -10432,7 +10402,7 @@
         <v>393</v>
       </c>
       <c r="C370" t="s">
-        <v>1379</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="371" spans="1:3">
@@ -10443,7 +10413,7 @@
         <v>394</v>
       </c>
       <c r="C371" t="s">
-        <v>1380</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -10454,7 +10424,7 @@
         <v>395</v>
       </c>
       <c r="C372" t="s">
-        <v>1381</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="373" spans="1:3">
@@ -10465,7 +10435,7 @@
         <v>396</v>
       </c>
       <c r="C373" t="s">
-        <v>1382</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="374" spans="1:3">
@@ -10476,7 +10446,7 @@
         <v>397</v>
       </c>
       <c r="C374" t="s">
-        <v>1383</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="375" spans="1:3">
@@ -10487,7 +10457,7 @@
         <v>398</v>
       </c>
       <c r="C375" t="s">
-        <v>1384</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="376" spans="1:3">
@@ -10498,7 +10468,7 @@
         <v>399</v>
       </c>
       <c r="C376" t="s">
-        <v>1385</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="377" spans="1:3">
@@ -10509,7 +10479,7 @@
         <v>400</v>
       </c>
       <c r="C377" t="s">
-        <v>1386</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="378" spans="1:3">
@@ -10520,7 +10490,7 @@
         <v>401</v>
       </c>
       <c r="C378" t="s">
-        <v>1387</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="379" spans="1:3">
@@ -10531,7 +10501,7 @@
         <v>402</v>
       </c>
       <c r="C379" t="s">
-        <v>1388</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="380" spans="1:3">
@@ -10542,7 +10512,7 @@
         <v>403</v>
       </c>
       <c r="C380" t="s">
-        <v>1389</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="381" spans="1:3">
@@ -10553,7 +10523,7 @@
         <v>404</v>
       </c>
       <c r="C381" t="s">
-        <v>1390</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="382" spans="1:3">
@@ -10564,7 +10534,7 @@
         <v>405</v>
       </c>
       <c r="C382" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="383" spans="1:3">
@@ -10575,7 +10545,7 @@
         <v>406</v>
       </c>
       <c r="C383" t="s">
-        <v>1392</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="384" spans="1:3">
@@ -10586,7 +10556,7 @@
         <v>407</v>
       </c>
       <c r="C384" t="s">
-        <v>1393</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="385" spans="1:3">
@@ -10597,7 +10567,7 @@
         <v>408</v>
       </c>
       <c r="C385" t="s">
-        <v>1394</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="386" spans="1:3">
@@ -10608,7 +10578,7 @@
         <v>409</v>
       </c>
       <c r="C386" t="s">
-        <v>1395</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="387" spans="1:3">
@@ -10619,7 +10589,7 @@
         <v>410</v>
       </c>
       <c r="C387" t="s">
-        <v>1396</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="388" spans="1:3">
@@ -10630,7 +10600,7 @@
         <v>411</v>
       </c>
       <c r="C388" t="s">
-        <v>1397</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="389" spans="1:3">
@@ -10641,7 +10611,7 @@
         <v>412</v>
       </c>
       <c r="C389" t="s">
-        <v>1398</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="390" spans="1:3">
@@ -10652,7 +10622,7 @@
         <v>413</v>
       </c>
       <c r="C390" t="s">
-        <v>1399</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="391" spans="1:3">
@@ -10663,7 +10633,7 @@
         <v>414</v>
       </c>
       <c r="C391" t="s">
-        <v>1400</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="392" spans="1:3">
@@ -10674,7 +10644,7 @@
         <v>415</v>
       </c>
       <c r="C392" t="s">
-        <v>1401</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="393" spans="1:3">
@@ -10685,7 +10655,7 @@
         <v>416</v>
       </c>
       <c r="C393" t="s">
-        <v>1402</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="394" spans="1:3">
@@ -10696,7 +10666,7 @@
         <v>417</v>
       </c>
       <c r="C394" t="s">
-        <v>1403</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="395" spans="1:3">
@@ -10707,7 +10677,7 @@
         <v>418</v>
       </c>
       <c r="C395" t="s">
-        <v>1404</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="396" spans="1:3">
@@ -10718,7 +10688,7 @@
         <v>419</v>
       </c>
       <c r="C396" t="s">
-        <v>1405</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="397" spans="1:3">
@@ -10729,7 +10699,7 @@
         <v>420</v>
       </c>
       <c r="C397" t="s">
-        <v>1406</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="398" spans="1:3">
@@ -10740,7 +10710,7 @@
         <v>421</v>
       </c>
       <c r="C398" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="399" spans="1:3">
@@ -10751,7 +10721,7 @@
         <v>422</v>
       </c>
       <c r="C399" t="s">
-        <v>1408</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="400" spans="1:3">
@@ -10762,7 +10732,7 @@
         <v>423</v>
       </c>
       <c r="C400" t="s">
-        <v>1409</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="401" spans="1:3">
@@ -10773,7 +10743,7 @@
         <v>424</v>
       </c>
       <c r="C401" t="s">
-        <v>1410</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="402" spans="1:3">
@@ -10784,7 +10754,7 @@
         <v>425</v>
       </c>
       <c r="C402" t="s">
-        <v>1411</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="403" spans="1:3">
@@ -10795,7 +10765,7 @@
         <v>426</v>
       </c>
       <c r="C403" t="s">
-        <v>1412</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="404" spans="1:3">
@@ -10806,7 +10776,7 @@
         <v>427</v>
       </c>
       <c r="C404" t="s">
-        <v>1413</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="405" spans="1:3">
@@ -10817,7 +10787,7 @@
         <v>428</v>
       </c>
       <c r="C405" t="s">
-        <v>1414</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="406" spans="1:3">
@@ -10828,7 +10798,7 @@
         <v>429</v>
       </c>
       <c r="C406" t="s">
-        <v>1415</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="407" spans="1:3">
@@ -10839,7 +10809,7 @@
         <v>430</v>
       </c>
       <c r="C407" t="s">
-        <v>1416</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="408" spans="1:3">
@@ -10850,7 +10820,7 @@
         <v>431</v>
       </c>
       <c r="C408" t="s">
-        <v>1417</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="409" spans="1:3">
@@ -10861,7 +10831,7 @@
         <v>432</v>
       </c>
       <c r="C409" t="s">
-        <v>1418</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="410" spans="1:3">
@@ -10872,7 +10842,7 @@
         <v>433</v>
       </c>
       <c r="C410" t="s">
-        <v>1419</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="411" spans="1:3">
@@ -10883,7 +10853,7 @@
         <v>434</v>
       </c>
       <c r="C411" t="s">
-        <v>1420</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="412" spans="1:3">
@@ -10894,7 +10864,7 @@
         <v>435</v>
       </c>
       <c r="C412" t="s">
-        <v>1421</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="413" spans="1:3">
@@ -10905,7 +10875,7 @@
         <v>436</v>
       </c>
       <c r="C413" t="s">
-        <v>1422</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="414" spans="1:3">
@@ -10916,7 +10886,7 @@
         <v>437</v>
       </c>
       <c r="C414" t="s">
-        <v>1423</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="415" spans="1:3">
@@ -10927,7 +10897,7 @@
         <v>438</v>
       </c>
       <c r="C415" t="s">
-        <v>1424</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="416" spans="1:3">
@@ -10938,7 +10908,7 @@
         <v>439</v>
       </c>
       <c r="C416" t="s">
-        <v>1425</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="417" spans="1:3">
@@ -10949,7 +10919,7 @@
         <v>440</v>
       </c>
       <c r="C417" t="s">
-        <v>1426</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="418" spans="1:3">
@@ -10960,7 +10930,7 @@
         <v>441</v>
       </c>
       <c r="C418" t="s">
-        <v>1427</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="419" spans="1:3">
@@ -10971,7 +10941,7 @@
         <v>442</v>
       </c>
       <c r="C419" t="s">
-        <v>1428</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="420" spans="1:3">
@@ -10982,7 +10952,7 @@
         <v>443</v>
       </c>
       <c r="C420" t="s">
-        <v>1429</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="421" spans="1:3">
@@ -10993,7 +10963,7 @@
         <v>444</v>
       </c>
       <c r="C421" t="s">
-        <v>1430</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="422" spans="1:3">
@@ -11004,7 +10974,7 @@
         <v>445</v>
       </c>
       <c r="C422" t="s">
-        <v>1431</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="423" spans="1:3">
@@ -11015,7 +10985,7 @@
         <v>446</v>
       </c>
       <c r="C423" t="s">
-        <v>1432</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="424" spans="1:3">
@@ -11026,7 +10996,7 @@
         <v>447</v>
       </c>
       <c r="C424" t="s">
-        <v>1433</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="425" spans="1:3">
@@ -11037,7 +11007,7 @@
         <v>448</v>
       </c>
       <c r="C425" t="s">
-        <v>1434</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="426" spans="1:3">
@@ -11048,7 +11018,7 @@
         <v>449</v>
       </c>
       <c r="C426" t="s">
-        <v>1435</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="427" spans="1:3">
@@ -11059,7 +11029,7 @@
         <v>450</v>
       </c>
       <c r="C427" t="s">
-        <v>1436</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="428" spans="1:3">
@@ -11070,7 +11040,7 @@
         <v>451</v>
       </c>
       <c r="C428" t="s">
-        <v>1437</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="429" spans="1:3">
@@ -11081,7 +11051,7 @@
         <v>452</v>
       </c>
       <c r="C429" t="s">
-        <v>1438</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="430" spans="1:3">
@@ -11092,7 +11062,7 @@
         <v>453</v>
       </c>
       <c r="C430" t="s">
-        <v>1439</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="431" spans="1:3">
@@ -11103,7 +11073,7 @@
         <v>454</v>
       </c>
       <c r="C431" t="s">
-        <v>1440</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="432" spans="1:3">
@@ -11114,7 +11084,7 @@
         <v>455</v>
       </c>
       <c r="C432" t="s">
-        <v>1441</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="433" spans="1:3">
@@ -11125,7 +11095,7 @@
         <v>456</v>
       </c>
       <c r="C433" t="s">
-        <v>1442</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="434" spans="1:3">
@@ -11136,7 +11106,7 @@
         <v>457</v>
       </c>
       <c r="C434" t="s">
-        <v>1443</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="435" spans="1:3">
@@ -11147,7 +11117,7 @@
         <v>458</v>
       </c>
       <c r="C435" t="s">
-        <v>1444</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="436" spans="1:3">
@@ -11158,7 +11128,7 @@
         <v>459</v>
       </c>
       <c r="C436" t="s">
-        <v>1445</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="437" spans="1:3">
@@ -11169,7 +11139,7 @@
         <v>460</v>
       </c>
       <c r="C437" t="s">
-        <v>1446</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="438" spans="1:3">
@@ -11180,7 +11150,7 @@
         <v>461</v>
       </c>
       <c r="C438" t="s">
-        <v>1447</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="439" spans="1:3">
@@ -11191,7 +11161,7 @@
         <v>462</v>
       </c>
       <c r="C439" t="s">
-        <v>1416</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="440" spans="1:3">
@@ -11202,7 +11172,7 @@
         <v>463</v>
       </c>
       <c r="C440" t="s">
-        <v>1408</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="441" spans="1:3">
@@ -11213,7 +11183,7 @@
         <v>464</v>
       </c>
       <c r="C441" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="442" spans="1:3">
@@ -11224,7 +11194,7 @@
         <v>465</v>
       </c>
       <c r="C442" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="443" spans="1:3">
@@ -11235,7 +11205,7 @@
         <v>466</v>
       </c>
       <c r="C443" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="444" spans="1:3">
@@ -11246,7 +11216,7 @@
         <v>467</v>
       </c>
       <c r="C444" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="445" spans="1:3">
@@ -11257,7 +11227,7 @@
         <v>468</v>
       </c>
       <c r="C445" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="446" spans="1:3">
@@ -11268,7 +11238,7 @@
         <v>469</v>
       </c>
       <c r="C446" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="447" spans="1:3">
@@ -11279,7 +11249,7 @@
         <v>470</v>
       </c>
       <c r="C447" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="448" spans="1:3">
@@ -11290,7 +11260,7 @@
         <v>471</v>
       </c>
       <c r="C448" t="s">
-        <v>1455</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="449" spans="1:3">
@@ -11301,7 +11271,7 @@
         <v>472</v>
       </c>
       <c r="C449" t="s">
-        <v>1456</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="450" spans="1:3">
@@ -11312,7 +11282,7 @@
         <v>473</v>
       </c>
       <c r="C450" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="451" spans="1:3">
@@ -11323,7 +11293,7 @@
         <v>474</v>
       </c>
       <c r="C451" t="s">
-        <v>1458</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="452" spans="1:3">
@@ -11334,7 +11304,7 @@
         <v>475</v>
       </c>
       <c r="C452" t="s">
-        <v>1459</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="453" spans="1:3">
@@ -11345,7 +11315,7 @@
         <v>476</v>
       </c>
       <c r="C453" t="s">
-        <v>1460</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="454" spans="1:3">
@@ -11356,7 +11326,7 @@
         <v>477</v>
       </c>
       <c r="C454" t="s">
-        <v>1461</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="455" spans="1:3">
@@ -11367,7 +11337,7 @@
         <v>478</v>
       </c>
       <c r="C455" t="s">
-        <v>1462</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="456" spans="1:3">
@@ -11378,7 +11348,7 @@
         <v>479</v>
       </c>
       <c r="C456" t="s">
-        <v>1463</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="457" spans="1:3">
@@ -11389,7 +11359,7 @@
         <v>480</v>
       </c>
       <c r="C457" t="s">
-        <v>1464</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="458" spans="1:3">
@@ -11400,7 +11370,7 @@
         <v>481</v>
       </c>
       <c r="C458" t="s">
-        <v>1465</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="459" spans="1:3">
@@ -11411,7 +11381,7 @@
         <v>482</v>
       </c>
       <c r="C459" t="s">
-        <v>1466</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="460" spans="1:3">
@@ -11422,7 +11392,7 @@
         <v>483</v>
       </c>
       <c r="C460" t="s">
-        <v>1467</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="461" spans="1:3">
@@ -11433,7 +11403,7 @@
         <v>484</v>
       </c>
       <c r="C461" t="s">
-        <v>1468</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="462" spans="1:3">
@@ -11444,7 +11414,7 @@
         <v>485</v>
       </c>
       <c r="C462" t="s">
-        <v>1469</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="463" spans="1:3">
@@ -11455,7 +11425,7 @@
         <v>486</v>
       </c>
       <c r="C463" t="s">
-        <v>1470</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="464" spans="1:3">
@@ -11466,7 +11436,7 @@
         <v>487</v>
       </c>
       <c r="C464" t="s">
-        <v>1471</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="465" spans="1:3">
@@ -11477,7 +11447,7 @@
         <v>488</v>
       </c>
       <c r="C465" t="s">
-        <v>1472</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="466" spans="1:3">
@@ -11488,7 +11458,7 @@
         <v>489</v>
       </c>
       <c r="C466" t="s">
-        <v>1473</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="467" spans="1:3">
@@ -11499,7 +11469,7 @@
         <v>490</v>
       </c>
       <c r="C467" t="s">
-        <v>1474</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="468" spans="1:3">
@@ -11510,7 +11480,7 @@
         <v>491</v>
       </c>
       <c r="C468" t="s">
-        <v>1475</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="469" spans="1:3">
@@ -11521,7 +11491,7 @@
         <v>492</v>
       </c>
       <c r="C469" t="s">
-        <v>1476</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="470" spans="1:3">
@@ -11532,7 +11502,7 @@
         <v>493</v>
       </c>
       <c r="C470" t="s">
-        <v>1477</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="471" spans="1:3">
@@ -11543,7 +11513,7 @@
         <v>494</v>
       </c>
       <c r="C471" t="s">
-        <v>1478</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="472" spans="1:3">
@@ -11554,7 +11524,7 @@
         <v>495</v>
       </c>
       <c r="C472" t="s">
-        <v>1479</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="473" spans="1:3">
@@ -11565,7 +11535,7 @@
         <v>496</v>
       </c>
       <c r="C473" t="s">
-        <v>1480</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="474" spans="1:3">
@@ -11576,7 +11546,7 @@
         <v>497</v>
       </c>
       <c r="C474" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="475" spans="1:3">
@@ -11587,7 +11557,7 @@
         <v>498</v>
       </c>
       <c r="C475" t="s">
-        <v>1482</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="476" spans="1:3">
@@ -11598,7 +11568,7 @@
         <v>499</v>
       </c>
       <c r="C476" t="s">
-        <v>1483</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="477" spans="1:3">
@@ -11609,7 +11579,7 @@
         <v>500</v>
       </c>
       <c r="C477" t="s">
-        <v>1484</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="478" spans="1:3">
@@ -11620,7 +11590,7 @@
         <v>501</v>
       </c>
       <c r="C478" t="s">
-        <v>1485</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="479" spans="1:3">
@@ -11631,7 +11601,7 @@
         <v>502</v>
       </c>
       <c r="C479" t="s">
-        <v>1486</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="480" spans="1:3">
@@ -11642,7 +11612,7 @@
         <v>503</v>
       </c>
       <c r="C480" t="s">
-        <v>1487</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="481" spans="1:3">
@@ -11653,7 +11623,7 @@
         <v>504</v>
       </c>
       <c r="C481" t="s">
-        <v>1488</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="482" spans="1:3">
@@ -11664,7 +11634,7 @@
         <v>505</v>
       </c>
       <c r="C482" t="s">
-        <v>1489</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="483" spans="1:3">
@@ -11675,7 +11645,7 @@
         <v>506</v>
       </c>
       <c r="C483" t="s">
-        <v>1490</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="484" spans="1:3">
@@ -11686,7 +11656,7 @@
         <v>507</v>
       </c>
       <c r="C484" t="s">
-        <v>1491</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="485" spans="1:3">
@@ -11697,7 +11667,7 @@
         <v>508</v>
       </c>
       <c r="C485" t="s">
-        <v>1492</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="486" spans="1:3">
@@ -11708,7 +11678,7 @@
         <v>509</v>
       </c>
       <c r="C486" t="s">
-        <v>1493</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="487" spans="1:3">
@@ -11719,7 +11689,7 @@
         <v>510</v>
       </c>
       <c r="C487" t="s">
-        <v>1494</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="488" spans="1:3">
@@ -11730,7 +11700,7 @@
         <v>511</v>
       </c>
       <c r="C488" t="s">
-        <v>1495</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="489" spans="1:3">
@@ -11741,7 +11711,7 @@
         <v>512</v>
       </c>
       <c r="C489" t="s">
-        <v>1496</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="490" spans="1:3">
@@ -11752,7 +11722,7 @@
         <v>513</v>
       </c>
       <c r="C490" t="s">
-        <v>1497</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="491" spans="1:3">
@@ -11763,7 +11733,7 @@
         <v>514</v>
       </c>
       <c r="C491" t="s">
-        <v>1498</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="492" spans="1:3">
@@ -11774,7 +11744,7 @@
         <v>515</v>
       </c>
       <c r="C492" t="s">
-        <v>1499</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="493" spans="1:3">
@@ -11785,7 +11755,7 @@
         <v>516</v>
       </c>
       <c r="C493" t="s">
-        <v>1500</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="494" spans="1:3">
@@ -11796,7 +11766,7 @@
         <v>517</v>
       </c>
       <c r="C494" t="s">
-        <v>1501</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="495" spans="1:3">
@@ -11807,7 +11777,7 @@
         <v>518</v>
       </c>
       <c r="C495" t="s">
-        <v>1502</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="496" spans="1:3">
@@ -11818,7 +11788,7 @@
         <v>519</v>
       </c>
       <c r="C496" t="s">
-        <v>1503</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="497" spans="1:3">
@@ -11829,7 +11799,7 @@
         <v>520</v>
       </c>
       <c r="C497" t="s">
-        <v>1504</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="498" spans="1:3">
@@ -11840,7 +11810,7 @@
         <v>521</v>
       </c>
       <c r="C498" t="s">
-        <v>1505</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="499" spans="1:3">
@@ -11851,7 +11821,7 @@
         <v>522</v>
       </c>
       <c r="C499" t="s">
-        <v>1506</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="500" spans="1:3">
@@ -11862,7 +11832,7 @@
         <v>523</v>
       </c>
       <c r="C500" t="s">
-        <v>1507</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="501" spans="1:3">
@@ -11873,7 +11843,7 @@
         <v>524</v>
       </c>
       <c r="C501" t="s">
-        <v>1508</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="502" spans="1:3">
@@ -11884,7 +11854,7 @@
         <v>525</v>
       </c>
       <c r="C502" t="s">
-        <v>1509</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="503" spans="1:3">
@@ -11895,29 +11865,29 @@
         <v>526</v>
       </c>
       <c r="C503" t="s">
-        <v>1510</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="504" spans="1:3">
       <c r="A504" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B504" t="s">
         <v>527</v>
       </c>
       <c r="C504" t="s">
-        <v>1511</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="505" spans="1:3">
       <c r="A505" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B505" t="s">
         <v>528</v>
       </c>
       <c r="C505" t="s">
-        <v>1512</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="506" spans="1:3">
@@ -11928,7 +11898,7 @@
         <v>529</v>
       </c>
       <c r="C506" t="s">
-        <v>1513</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="507" spans="1:3">
@@ -11939,7 +11909,7 @@
         <v>530</v>
       </c>
       <c r="C507" t="s">
-        <v>1514</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="508" spans="1:3">
@@ -11950,7 +11920,7 @@
         <v>531</v>
       </c>
       <c r="C508" t="s">
-        <v>1515</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="509" spans="1:3">
@@ -11961,7 +11931,7 @@
         <v>532</v>
       </c>
       <c r="C509" t="s">
-        <v>1516</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="510" spans="1:3">
@@ -11972,7 +11942,7 @@
         <v>533</v>
       </c>
       <c r="C510" t="s">
-        <v>1517</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="511" spans="1:3">
@@ -11983,29 +11953,29 @@
         <v>534</v>
       </c>
       <c r="C511" t="s">
-        <v>1518</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="512" spans="1:3">
       <c r="A512" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B512" t="s">
         <v>535</v>
       </c>
       <c r="C512" t="s">
-        <v>1519</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="513" spans="1:3">
       <c r="A513" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B513" t="s">
         <v>536</v>
       </c>
       <c r="C513" t="s">
-        <v>1520</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="514" spans="1:3">
@@ -12016,7 +11986,7 @@
         <v>537</v>
       </c>
       <c r="C514" t="s">
-        <v>1521</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="515" spans="1:3">
@@ -12027,7 +11997,7 @@
         <v>538</v>
       </c>
       <c r="C515" t="s">
-        <v>1522</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="516" spans="1:3">
@@ -12038,7 +12008,7 @@
         <v>539</v>
       </c>
       <c r="C516" t="s">
-        <v>1523</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="517" spans="1:3">
@@ -12049,7 +12019,7 @@
         <v>540</v>
       </c>
       <c r="C517" t="s">
-        <v>1524</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="518" spans="1:3">
@@ -12060,7 +12030,7 @@
         <v>541</v>
       </c>
       <c r="C518" t="s">
-        <v>1525</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="519" spans="1:3">
@@ -12071,7 +12041,7 @@
         <v>542</v>
       </c>
       <c r="C519" t="s">
-        <v>1526</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="520" spans="1:3">
@@ -12082,7 +12052,7 @@
         <v>543</v>
       </c>
       <c r="C520" t="s">
-        <v>1527</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="521" spans="1:3">
@@ -12093,7 +12063,7 @@
         <v>544</v>
       </c>
       <c r="C521" t="s">
-        <v>1528</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="522" spans="1:3">
@@ -12104,7 +12074,7 @@
         <v>545</v>
       </c>
       <c r="C522" t="s">
-        <v>1529</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="523" spans="1:3">
@@ -12115,7 +12085,7 @@
         <v>546</v>
       </c>
       <c r="C523" t="s">
-        <v>1530</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="524" spans="1:3">
@@ -12126,7 +12096,7 @@
         <v>547</v>
       </c>
       <c r="C524" t="s">
-        <v>1531</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="525" spans="1:3">
@@ -12137,7 +12107,7 @@
         <v>548</v>
       </c>
       <c r="C525" t="s">
-        <v>1532</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="526" spans="1:3">
@@ -12148,7 +12118,7 @@
         <v>549</v>
       </c>
       <c r="C526" t="s">
-        <v>1533</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="527" spans="1:3">
@@ -12159,7 +12129,7 @@
         <v>550</v>
       </c>
       <c r="C527" t="s">
-        <v>1534</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="528" spans="1:3">
@@ -12170,7 +12140,7 @@
         <v>551</v>
       </c>
       <c r="C528" t="s">
-        <v>1535</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="529" spans="1:3">
@@ -12181,7 +12151,7 @@
         <v>552</v>
       </c>
       <c r="C529" t="s">
-        <v>1536</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="530" spans="1:3">
@@ -12192,7 +12162,7 @@
         <v>553</v>
       </c>
       <c r="C530" t="s">
-        <v>1537</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="531" spans="1:3">
@@ -12203,7 +12173,7 @@
         <v>554</v>
       </c>
       <c r="C531" t="s">
-        <v>1538</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="532" spans="1:3">
@@ -12214,7 +12184,7 @@
         <v>555</v>
       </c>
       <c r="C532" t="s">
-        <v>1539</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="533" spans="1:3">
@@ -12225,7 +12195,7 @@
         <v>556</v>
       </c>
       <c r="C533" t="s">
-        <v>1540</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="534" spans="1:3">
@@ -12236,7 +12206,7 @@
         <v>557</v>
       </c>
       <c r="C534" t="s">
-        <v>1541</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="535" spans="1:3">
@@ -12247,7 +12217,7 @@
         <v>558</v>
       </c>
       <c r="C535" t="s">
-        <v>1542</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="536" spans="1:3">
@@ -12258,7 +12228,7 @@
         <v>559</v>
       </c>
       <c r="C536" t="s">
-        <v>1543</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="537" spans="1:3">
@@ -12269,7 +12239,7 @@
         <v>560</v>
       </c>
       <c r="C537" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="538" spans="1:3">
@@ -12280,7 +12250,7 @@
         <v>561</v>
       </c>
       <c r="C538" t="s">
-        <v>1545</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="539" spans="1:3">
@@ -12291,7 +12261,7 @@
         <v>562</v>
       </c>
       <c r="C539" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="540" spans="1:3">
@@ -12302,7 +12272,7 @@
         <v>563</v>
       </c>
       <c r="C540" t="s">
-        <v>1547</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="541" spans="1:3">
@@ -12313,7 +12283,7 @@
         <v>564</v>
       </c>
       <c r="C541" t="s">
-        <v>1548</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="542" spans="1:3">
@@ -12324,7 +12294,7 @@
         <v>565</v>
       </c>
       <c r="C542" t="s">
-        <v>1549</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="543" spans="1:3">
@@ -12335,7 +12305,7 @@
         <v>566</v>
       </c>
       <c r="C543" t="s">
-        <v>1550</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="544" spans="1:3">
@@ -12346,7 +12316,7 @@
         <v>567</v>
       </c>
       <c r="C544" t="s">
-        <v>1551</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="545" spans="1:3">
@@ -12357,7 +12327,7 @@
         <v>568</v>
       </c>
       <c r="C545" t="s">
-        <v>1552</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="546" spans="1:3">
@@ -12368,7 +12338,7 @@
         <v>569</v>
       </c>
       <c r="C546" t="s">
-        <v>1553</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="547" spans="1:3">
@@ -12379,7 +12349,7 @@
         <v>570</v>
       </c>
       <c r="C547" t="s">
-        <v>1554</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="548" spans="1:3">
@@ -12390,7 +12360,7 @@
         <v>571</v>
       </c>
       <c r="C548" t="s">
-        <v>1555</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="549" spans="1:3">
@@ -12401,7 +12371,7 @@
         <v>572</v>
       </c>
       <c r="C549" t="s">
-        <v>1556</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="550" spans="1:3">
@@ -12412,7 +12382,7 @@
         <v>573</v>
       </c>
       <c r="C550" t="s">
-        <v>1526</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="551" spans="1:3">
@@ -12423,7 +12393,7 @@
         <v>574</v>
       </c>
       <c r="C551" t="s">
-        <v>1557</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="552" spans="1:3">
@@ -12434,7 +12404,7 @@
         <v>575</v>
       </c>
       <c r="C552" t="s">
-        <v>1558</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="553" spans="1:3">
@@ -12445,7 +12415,7 @@
         <v>576</v>
       </c>
       <c r="C553" t="s">
-        <v>1559</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="554" spans="1:3">
@@ -12456,29 +12426,29 @@
         <v>577</v>
       </c>
       <c r="C554" t="s">
-        <v>1560</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="555" spans="1:3">
       <c r="A555" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B555" t="s">
         <v>578</v>
       </c>
       <c r="C555" t="s">
-        <v>1561</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="556" spans="1:3">
       <c r="A556" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B556" t="s">
         <v>579</v>
       </c>
       <c r="C556" t="s">
-        <v>1562</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="557" spans="1:3">
@@ -12489,7 +12459,7 @@
         <v>580</v>
       </c>
       <c r="C557" t="s">
-        <v>1563</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="558" spans="1:3">
@@ -12500,7 +12470,7 @@
         <v>581</v>
       </c>
       <c r="C558" t="s">
-        <v>1564</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="559" spans="1:3">
@@ -12511,7 +12481,7 @@
         <v>582</v>
       </c>
       <c r="C559" t="s">
-        <v>1565</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="560" spans="1:3">
@@ -12522,7 +12492,7 @@
         <v>583</v>
       </c>
       <c r="C560" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="561" spans="1:3">
@@ -12533,29 +12503,29 @@
         <v>584</v>
       </c>
       <c r="C561" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="562" spans="1:3">
       <c r="A562" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B562" t="s">
         <v>585</v>
       </c>
       <c r="C562" t="s">
-        <v>1568</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="563" spans="1:3">
       <c r="A563" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B563" t="s">
         <v>586</v>
       </c>
       <c r="C563" t="s">
-        <v>1569</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="564" spans="1:3">
@@ -12566,7 +12536,7 @@
         <v>587</v>
       </c>
       <c r="C564" t="s">
-        <v>1570</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="565" spans="1:3">
@@ -12577,7 +12547,7 @@
         <v>588</v>
       </c>
       <c r="C565" t="s">
-        <v>1571</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="566" spans="1:3">
@@ -12588,7 +12558,7 @@
         <v>589</v>
       </c>
       <c r="C566" t="s">
-        <v>1572</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="567" spans="1:3">
@@ -12599,7 +12569,7 @@
         <v>590</v>
       </c>
       <c r="C567" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="568" spans="1:3">
@@ -12610,7 +12580,7 @@
         <v>591</v>
       </c>
       <c r="C568" t="s">
-        <v>1574</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="569" spans="1:3">
@@ -12621,7 +12591,7 @@
         <v>592</v>
       </c>
       <c r="C569" t="s">
-        <v>1575</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="570" spans="1:3">
@@ -12632,7 +12602,7 @@
         <v>593</v>
       </c>
       <c r="C570" t="s">
-        <v>1576</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="571" spans="1:3">
@@ -12643,7 +12613,7 @@
         <v>594</v>
       </c>
       <c r="C571" t="s">
-        <v>1577</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="572" spans="1:3">
@@ -12654,7 +12624,7 @@
         <v>595</v>
       </c>
       <c r="C572" t="s">
-        <v>1578</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="573" spans="1:3">
@@ -12665,7 +12635,7 @@
         <v>596</v>
       </c>
       <c r="C573" t="s">
-        <v>1579</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="574" spans="1:3">
@@ -12676,7 +12646,7 @@
         <v>597</v>
       </c>
       <c r="C574" t="s">
-        <v>1580</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="575" spans="1:3">
@@ -12687,7 +12657,7 @@
         <v>598</v>
       </c>
       <c r="C575" t="s">
-        <v>1581</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="576" spans="1:3">
@@ -12698,7 +12668,7 @@
         <v>599</v>
       </c>
       <c r="C576" t="s">
-        <v>1582</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="577" spans="1:3">
@@ -12709,7 +12679,7 @@
         <v>600</v>
       </c>
       <c r="C577" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="578" spans="1:3">
@@ -12720,7 +12690,7 @@
         <v>601</v>
       </c>
       <c r="C578" t="s">
-        <v>1584</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="579" spans="1:3">
@@ -12731,7 +12701,7 @@
         <v>602</v>
       </c>
       <c r="C579" t="s">
-        <v>1585</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="580" spans="1:3">
@@ -12742,7 +12712,7 @@
         <v>603</v>
       </c>
       <c r="C580" t="s">
-        <v>1586</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="581" spans="1:3">
@@ -12753,7 +12723,7 @@
         <v>604</v>
       </c>
       <c r="C581" t="s">
-        <v>1587</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="582" spans="1:3">
@@ -12764,7 +12734,7 @@
         <v>605</v>
       </c>
       <c r="C582" t="s">
-        <v>1588</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="583" spans="1:3">
@@ -12775,7 +12745,7 @@
         <v>606</v>
       </c>
       <c r="C583" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="584" spans="1:3">
@@ -12786,7 +12756,7 @@
         <v>607</v>
       </c>
       <c r="C584" t="s">
-        <v>1590</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="585" spans="1:3">
@@ -12797,7 +12767,7 @@
         <v>608</v>
       </c>
       <c r="C585" t="s">
-        <v>1591</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="586" spans="1:3">
@@ -12808,7 +12778,7 @@
         <v>609</v>
       </c>
       <c r="C586" t="s">
-        <v>1592</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="587" spans="1:3">
@@ -12819,29 +12789,29 @@
         <v>610</v>
       </c>
       <c r="C587" t="s">
-        <v>1593</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="588" spans="1:3">
       <c r="A588" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B588" t="s">
         <v>611</v>
       </c>
       <c r="C588" t="s">
-        <v>1594</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="589" spans="1:3">
       <c r="A589" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B589" t="s">
         <v>612</v>
       </c>
       <c r="C589" t="s">
-        <v>1595</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="590" spans="1:3">
@@ -12852,7 +12822,7 @@
         <v>613</v>
       </c>
       <c r="C590" t="s">
-        <v>1596</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="591" spans="1:3">
@@ -12863,7 +12833,7 @@
         <v>614</v>
       </c>
       <c r="C591" t="s">
-        <v>1597</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="592" spans="1:3">
@@ -12874,7 +12844,7 @@
         <v>615</v>
       </c>
       <c r="C592" t="s">
-        <v>1598</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="593" spans="1:3">
@@ -12885,7 +12855,7 @@
         <v>616</v>
       </c>
       <c r="C593" t="s">
-        <v>1599</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="594" spans="1:3">
@@ -12896,7 +12866,7 @@
         <v>617</v>
       </c>
       <c r="C594" t="s">
-        <v>1600</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="595" spans="1:3">
@@ -12907,7 +12877,7 @@
         <v>618</v>
       </c>
       <c r="C595" t="s">
-        <v>1601</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="596" spans="1:3">
@@ -12918,7 +12888,7 @@
         <v>619</v>
       </c>
       <c r="C596" t="s">
-        <v>1602</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="597" spans="1:3">
@@ -12929,7 +12899,7 @@
         <v>620</v>
       </c>
       <c r="C597" t="s">
-        <v>1603</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="598" spans="1:3">
@@ -12940,29 +12910,29 @@
         <v>621</v>
       </c>
       <c r="C598" t="s">
-        <v>1604</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="599" spans="1:3">
       <c r="A599" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B599" t="s">
         <v>622</v>
       </c>
       <c r="C599" t="s">
-        <v>1605</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="600" spans="1:3">
       <c r="A600" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B600" t="s">
         <v>623</v>
       </c>
       <c r="C600" t="s">
-        <v>1606</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="601" spans="1:3">
@@ -12973,7 +12943,7 @@
         <v>624</v>
       </c>
       <c r="C601" t="s">
-        <v>1607</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="602" spans="1:3">
@@ -12984,7 +12954,7 @@
         <v>625</v>
       </c>
       <c r="C602" t="s">
-        <v>1608</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="603" spans="1:3">
@@ -12995,7 +12965,7 @@
         <v>626</v>
       </c>
       <c r="C603" t="s">
-        <v>1609</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="604" spans="1:3">
@@ -13006,7 +12976,7 @@
         <v>627</v>
       </c>
       <c r="C604" t="s">
-        <v>1610</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="605" spans="1:3">
@@ -13017,7 +12987,7 @@
         <v>628</v>
       </c>
       <c r="C605" t="s">
-        <v>1611</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="606" spans="1:3">
@@ -13028,7 +12998,7 @@
         <v>629</v>
       </c>
       <c r="C606" t="s">
-        <v>1612</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="607" spans="1:3">
@@ -13039,7 +13009,7 @@
         <v>630</v>
       </c>
       <c r="C607" t="s">
-        <v>1613</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="608" spans="1:3">
@@ -13050,7 +13020,7 @@
         <v>631</v>
       </c>
       <c r="C608" t="s">
-        <v>1614</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="609" spans="1:3">
@@ -13061,7 +13031,7 @@
         <v>632</v>
       </c>
       <c r="C609" t="s">
-        <v>1615</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="610" spans="1:3">
@@ -13072,7 +13042,7 @@
         <v>633</v>
       </c>
       <c r="C610" t="s">
-        <v>1616</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="611" spans="1:3">
@@ -13083,7 +13053,7 @@
         <v>634</v>
       </c>
       <c r="C611" t="s">
-        <v>1617</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="612" spans="1:3">
@@ -13094,7 +13064,7 @@
         <v>635</v>
       </c>
       <c r="C612" t="s">
-        <v>1618</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="613" spans="1:3">
@@ -13105,7 +13075,7 @@
         <v>636</v>
       </c>
       <c r="C613" t="s">
-        <v>1619</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="614" spans="1:3">
@@ -13116,7 +13086,7 @@
         <v>637</v>
       </c>
       <c r="C614" t="s">
-        <v>1620</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="615" spans="1:3">
@@ -13127,7 +13097,7 @@
         <v>638</v>
       </c>
       <c r="C615" t="s">
-        <v>1621</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="616" spans="1:3">
@@ -13138,7 +13108,7 @@
         <v>639</v>
       </c>
       <c r="C616" t="s">
-        <v>1622</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="617" spans="1:3">
@@ -13149,7 +13119,7 @@
         <v>640</v>
       </c>
       <c r="C617" t="s">
-        <v>1623</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="618" spans="1:3">
@@ -13160,7 +13130,7 @@
         <v>641</v>
       </c>
       <c r="C618" t="s">
-        <v>1624</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="619" spans="1:3">
@@ -13171,7 +13141,7 @@
         <v>642</v>
       </c>
       <c r="C619" t="s">
-        <v>1625</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="620" spans="1:3">
@@ -13182,7 +13152,7 @@
         <v>643</v>
       </c>
       <c r="C620" t="s">
-        <v>1626</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="621" spans="1:3">
@@ -13193,29 +13163,29 @@
         <v>644</v>
       </c>
       <c r="C621" t="s">
-        <v>1627</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="622" spans="1:3">
       <c r="A622" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B622" t="s">
         <v>645</v>
       </c>
       <c r="C622" t="s">
-        <v>1628</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="623" spans="1:3">
       <c r="A623" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B623" t="s">
         <v>646</v>
       </c>
       <c r="C623" t="s">
-        <v>1629</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="624" spans="1:3">
@@ -13226,7 +13196,7 @@
         <v>647</v>
       </c>
       <c r="C624" t="s">
-        <v>1630</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="625" spans="1:3">
@@ -13237,7 +13207,7 @@
         <v>648</v>
       </c>
       <c r="C625" t="s">
-        <v>1631</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="626" spans="1:3">
@@ -13248,7 +13218,7 @@
         <v>649</v>
       </c>
       <c r="C626" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="627" spans="1:3">
@@ -13259,7 +13229,7 @@
         <v>650</v>
       </c>
       <c r="C627" t="s">
-        <v>1633</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="628" spans="1:3">
@@ -13270,7 +13240,7 @@
         <v>651</v>
       </c>
       <c r="C628" t="s">
-        <v>1634</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="629" spans="1:3">
@@ -13281,7 +13251,7 @@
         <v>652</v>
       </c>
       <c r="C629" t="s">
-        <v>1635</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="630" spans="1:3">
@@ -13292,7 +13262,7 @@
         <v>653</v>
       </c>
       <c r="C630" t="s">
-        <v>1636</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="631" spans="1:3">
@@ -13303,7 +13273,7 @@
         <v>654</v>
       </c>
       <c r="C631" t="s">
-        <v>1637</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="632" spans="1:3">
@@ -13314,7 +13284,7 @@
         <v>655</v>
       </c>
       <c r="C632" t="s">
-        <v>1638</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="633" spans="1:3">
@@ -13325,7 +13295,7 @@
         <v>656</v>
       </c>
       <c r="C633" t="s">
-        <v>1639</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="634" spans="1:3">
@@ -13336,7 +13306,7 @@
         <v>657</v>
       </c>
       <c r="C634" t="s">
-        <v>1640</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="635" spans="1:3">
@@ -13347,7 +13317,7 @@
         <v>658</v>
       </c>
       <c r="C635" t="s">
-        <v>1641</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="636" spans="1:3">
@@ -13358,7 +13328,7 @@
         <v>659</v>
       </c>
       <c r="C636" t="s">
-        <v>1642</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="637" spans="1:3">
@@ -13369,29 +13339,29 @@
         <v>660</v>
       </c>
       <c r="C637" t="s">
-        <v>1643</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="638" spans="1:3">
       <c r="A638" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B638" t="s">
         <v>661</v>
       </c>
       <c r="C638" t="s">
-        <v>1644</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="639" spans="1:3">
       <c r="A639" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B639" t="s">
         <v>662</v>
       </c>
       <c r="C639" t="s">
-        <v>1103</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="640" spans="1:3">
@@ -13402,7 +13372,7 @@
         <v>663</v>
       </c>
       <c r="C640" t="s">
-        <v>1645</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="641" spans="1:3">
@@ -13413,7 +13383,7 @@
         <v>664</v>
       </c>
       <c r="C641" t="s">
-        <v>1646</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="642" spans="1:3">
@@ -13424,7 +13394,7 @@
         <v>665</v>
       </c>
       <c r="C642" t="s">
-        <v>1647</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="643" spans="1:3">
@@ -13435,7 +13405,7 @@
         <v>666</v>
       </c>
       <c r="C643" t="s">
-        <v>1648</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="644" spans="1:3">
@@ -13446,7 +13416,7 @@
         <v>667</v>
       </c>
       <c r="C644" t="s">
-        <v>1649</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="645" spans="1:3">
@@ -13457,7 +13427,7 @@
         <v>668</v>
       </c>
       <c r="C645" t="s">
-        <v>1650</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="646" spans="1:3">
@@ -13468,7 +13438,7 @@
         <v>669</v>
       </c>
       <c r="C646" t="s">
-        <v>1651</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="647" spans="1:3">
@@ -13479,7 +13449,7 @@
         <v>670</v>
       </c>
       <c r="C647" t="s">
-        <v>1652</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="648" spans="1:3">
@@ -13490,7 +13460,7 @@
         <v>671</v>
       </c>
       <c r="C648" t="s">
-        <v>1653</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="649" spans="1:3">
@@ -13501,7 +13471,7 @@
         <v>672</v>
       </c>
       <c r="C649" t="s">
-        <v>1654</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="650" spans="1:3">
@@ -13512,7 +13482,7 @@
         <v>673</v>
       </c>
       <c r="C650" t="s">
-        <v>1655</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="651" spans="1:3">
@@ -13523,7 +13493,7 @@
         <v>674</v>
       </c>
       <c r="C651" t="s">
-        <v>1656</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="652" spans="1:3">
@@ -13534,7 +13504,7 @@
         <v>675</v>
       </c>
       <c r="C652" t="s">
-        <v>1657</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="653" spans="1:3">
@@ -13545,7 +13515,7 @@
         <v>676</v>
       </c>
       <c r="C653" t="s">
-        <v>1658</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="654" spans="1:3">
@@ -13556,7 +13526,7 @@
         <v>677</v>
       </c>
       <c r="C654" t="s">
-        <v>1659</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="655" spans="1:3">
@@ -13567,7 +13537,7 @@
         <v>678</v>
       </c>
       <c r="C655" t="s">
-        <v>1660</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="656" spans="1:3">
@@ -13578,7 +13548,7 @@
         <v>679</v>
       </c>
       <c r="C656" t="s">
-        <v>1661</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="657" spans="1:3">
@@ -13589,7 +13559,7 @@
         <v>680</v>
       </c>
       <c r="C657" t="s">
-        <v>1662</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="658" spans="1:3">
@@ -13600,7 +13570,7 @@
         <v>681</v>
       </c>
       <c r="C658" t="s">
-        <v>1663</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="659" spans="1:3">
@@ -13611,7 +13581,7 @@
         <v>682</v>
       </c>
       <c r="C659" t="s">
-        <v>1664</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="660" spans="1:3">
@@ -13622,7 +13592,7 @@
         <v>683</v>
       </c>
       <c r="C660" t="s">
-        <v>1665</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="661" spans="1:3">
@@ -13633,7 +13603,7 @@
         <v>684</v>
       </c>
       <c r="C661" t="s">
-        <v>1666</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="662" spans="1:3">
@@ -13644,7 +13614,7 @@
         <v>685</v>
       </c>
       <c r="C662" t="s">
-        <v>1667</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="663" spans="1:3">
@@ -13655,7 +13625,7 @@
         <v>686</v>
       </c>
       <c r="C663" t="s">
-        <v>1668</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="664" spans="1:3">
@@ -13666,7 +13636,7 @@
         <v>687</v>
       </c>
       <c r="C664" t="s">
-        <v>1669</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="665" spans="1:3">
@@ -13677,7 +13647,7 @@
         <v>688</v>
       </c>
       <c r="C665" t="s">
-        <v>1670</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="666" spans="1:3">
@@ -13688,7 +13658,7 @@
         <v>689</v>
       </c>
       <c r="C666" t="s">
-        <v>1671</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="667" spans="1:3">
@@ -13699,7 +13669,7 @@
         <v>690</v>
       </c>
       <c r="C667" t="s">
-        <v>1672</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="668" spans="1:3">
@@ -13710,7 +13680,7 @@
         <v>691</v>
       </c>
       <c r="C668" t="s">
-        <v>1673</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="669" spans="1:3">
@@ -13721,7 +13691,7 @@
         <v>692</v>
       </c>
       <c r="C669" t="s">
-        <v>1674</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="670" spans="1:3">
@@ -13732,7 +13702,7 @@
         <v>693</v>
       </c>
       <c r="C670" t="s">
-        <v>1675</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="671" spans="1:3">
@@ -13743,7 +13713,7 @@
         <v>694</v>
       </c>
       <c r="C671" t="s">
-        <v>1676</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="672" spans="1:3">
@@ -13754,7 +13724,7 @@
         <v>695</v>
       </c>
       <c r="C672" t="s">
-        <v>1677</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="673" spans="1:3">
@@ -13765,7 +13735,7 @@
         <v>696</v>
       </c>
       <c r="C673" t="s">
-        <v>1678</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="674" spans="1:3">
@@ -13776,7 +13746,7 @@
         <v>697</v>
       </c>
       <c r="C674" t="s">
-        <v>1679</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="675" spans="1:3">
@@ -13787,7 +13757,7 @@
         <v>698</v>
       </c>
       <c r="C675" t="s">
-        <v>1680</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="676" spans="1:3">
@@ -13798,7 +13768,7 @@
         <v>699</v>
       </c>
       <c r="C676" t="s">
-        <v>1681</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="677" spans="1:3">
@@ -13809,7 +13779,7 @@
         <v>700</v>
       </c>
       <c r="C677" t="s">
-        <v>1682</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="678" spans="1:3">
@@ -13820,40 +13790,40 @@
         <v>701</v>
       </c>
       <c r="C678" t="s">
-        <v>1683</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="679" spans="1:3">
       <c r="A679" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B679" t="s">
         <v>702</v>
       </c>
       <c r="C679" t="s">
-        <v>1684</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="680" spans="1:3">
       <c r="A680" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B680" t="s">
         <v>703</v>
       </c>
       <c r="C680" t="s">
-        <v>1685</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="681" spans="1:3">
       <c r="A681" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B681" t="s">
         <v>704</v>
       </c>
       <c r="C681" t="s">
-        <v>1686</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="682" spans="1:3">
@@ -13864,7 +13834,7 @@
         <v>705</v>
       </c>
       <c r="C682" t="s">
-        <v>1687</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="683" spans="1:3">
@@ -13875,7 +13845,7 @@
         <v>706</v>
       </c>
       <c r="C683" t="s">
-        <v>1688</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="684" spans="1:3">
@@ -13886,7 +13856,7 @@
         <v>707</v>
       </c>
       <c r="C684" t="s">
-        <v>1689</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="685" spans="1:3">
@@ -13897,40 +13867,40 @@
         <v>708</v>
       </c>
       <c r="C685" t="s">
-        <v>1690</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="686" spans="1:3">
       <c r="A686" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B686" t="s">
         <v>709</v>
       </c>
       <c r="C686" t="s">
-        <v>1691</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="687" spans="1:3">
       <c r="A687" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B687" t="s">
         <v>710</v>
       </c>
       <c r="C687" t="s">
-        <v>1692</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="688" spans="1:3">
       <c r="A688" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B688" t="s">
         <v>711</v>
       </c>
       <c r="C688" t="s">
-        <v>1693</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="689" spans="1:3">
@@ -13941,7 +13911,7 @@
         <v>712</v>
       </c>
       <c r="C689" t="s">
-        <v>1694</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="690" spans="1:3">
@@ -13952,7 +13922,7 @@
         <v>713</v>
       </c>
       <c r="C690" t="s">
-        <v>1695</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="691" spans="1:3">
@@ -13963,7 +13933,7 @@
         <v>714</v>
       </c>
       <c r="C691" t="s">
-        <v>1696</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="692" spans="1:3">
@@ -13974,7 +13944,7 @@
         <v>715</v>
       </c>
       <c r="C692" t="s">
-        <v>1697</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="693" spans="1:3">
@@ -13985,7 +13955,7 @@
         <v>716</v>
       </c>
       <c r="C693" t="s">
-        <v>1698</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="694" spans="1:3">
@@ -13996,7 +13966,7 @@
         <v>717</v>
       </c>
       <c r="C694" t="s">
-        <v>1699</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="695" spans="1:3">
@@ -14007,7 +13977,7 @@
         <v>718</v>
       </c>
       <c r="C695" t="s">
-        <v>1700</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="696" spans="1:3">
@@ -14018,7 +13988,7 @@
         <v>719</v>
       </c>
       <c r="C696" t="s">
-        <v>1701</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="697" spans="1:3">
@@ -14029,7 +13999,7 @@
         <v>720</v>
       </c>
       <c r="C697" t="s">
-        <v>1702</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="698" spans="1:3">
@@ -14040,7 +14010,7 @@
         <v>721</v>
       </c>
       <c r="C698" t="s">
-        <v>1703</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="699" spans="1:3">
@@ -14051,7 +14021,7 @@
         <v>722</v>
       </c>
       <c r="C699" t="s">
-        <v>1704</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="700" spans="1:3">
@@ -14062,7 +14032,7 @@
         <v>723</v>
       </c>
       <c r="C700" t="s">
-        <v>1705</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="701" spans="1:3">
@@ -14073,7 +14043,7 @@
         <v>724</v>
       </c>
       <c r="C701" t="s">
-        <v>1706</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="702" spans="1:3">
@@ -14084,7 +14054,7 @@
         <v>725</v>
       </c>
       <c r="C702" t="s">
-        <v>1707</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="703" spans="1:3">
@@ -14095,7 +14065,7 @@
         <v>726</v>
       </c>
       <c r="C703" t="s">
-        <v>1708</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="704" spans="1:3">
@@ -14106,7 +14076,7 @@
         <v>727</v>
       </c>
       <c r="C704" t="s">
-        <v>1709</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="705" spans="1:3">
@@ -14117,7 +14087,7 @@
         <v>728</v>
       </c>
       <c r="C705" t="s">
-        <v>1710</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="706" spans="1:3">
@@ -14128,7 +14098,7 @@
         <v>729</v>
       </c>
       <c r="C706" t="s">
-        <v>1711</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="707" spans="1:3">
@@ -14139,7 +14109,7 @@
         <v>730</v>
       </c>
       <c r="C707" t="s">
-        <v>1712</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="708" spans="1:3">
@@ -14150,7 +14120,7 @@
         <v>731</v>
       </c>
       <c r="C708" t="s">
-        <v>1713</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="709" spans="1:3">
@@ -14161,7 +14131,7 @@
         <v>732</v>
       </c>
       <c r="C709" t="s">
-        <v>1714</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="710" spans="1:3">
@@ -14172,7 +14142,7 @@
         <v>733</v>
       </c>
       <c r="C710" t="s">
-        <v>1715</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="711" spans="1:3">
@@ -14183,7 +14153,7 @@
         <v>734</v>
       </c>
       <c r="C711" t="s">
-        <v>1716</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="712" spans="1:3">
@@ -14194,7 +14164,7 @@
         <v>735</v>
       </c>
       <c r="C712" t="s">
-        <v>1717</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="713" spans="1:3">
@@ -14205,7 +14175,7 @@
         <v>736</v>
       </c>
       <c r="C713" t="s">
-        <v>1718</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="714" spans="1:3">
@@ -14216,7 +14186,7 @@
         <v>737</v>
       </c>
       <c r="C714" t="s">
-        <v>1719</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="715" spans="1:3">
@@ -14227,7 +14197,7 @@
         <v>738</v>
       </c>
       <c r="C715" t="s">
-        <v>1720</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="716" spans="1:3">
@@ -14238,7 +14208,7 @@
         <v>739</v>
       </c>
       <c r="C716" t="s">
-        <v>1721</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="717" spans="1:3">
@@ -14249,7 +14219,7 @@
         <v>740</v>
       </c>
       <c r="C717" t="s">
-        <v>1722</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="718" spans="1:3">
@@ -14260,7 +14230,7 @@
         <v>741</v>
       </c>
       <c r="C718" t="s">
-        <v>1723</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="719" spans="1:3">
@@ -14271,7 +14241,7 @@
         <v>742</v>
       </c>
       <c r="C719" t="s">
-        <v>1724</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="720" spans="1:3">
@@ -14282,7 +14252,7 @@
         <v>743</v>
       </c>
       <c r="C720" t="s">
-        <v>1725</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="721" spans="1:3">
@@ -14293,7 +14263,7 @@
         <v>744</v>
       </c>
       <c r="C721" t="s">
-        <v>1726</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="722" spans="1:3">
@@ -14304,7 +14274,7 @@
         <v>745</v>
       </c>
       <c r="C722" t="s">
-        <v>1727</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="723" spans="1:3">
@@ -14315,7 +14285,7 @@
         <v>746</v>
       </c>
       <c r="C723" t="s">
-        <v>1728</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="724" spans="1:3">
@@ -14326,7 +14296,7 @@
         <v>747</v>
       </c>
       <c r="C724" t="s">
-        <v>1729</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="725" spans="1:3">
@@ -14337,7 +14307,7 @@
         <v>748</v>
       </c>
       <c r="C725" t="s">
-        <v>1730</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="726" spans="1:3">
@@ -14348,7 +14318,7 @@
         <v>749</v>
       </c>
       <c r="C726" t="s">
-        <v>1731</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="727" spans="1:3">
@@ -14359,7 +14329,7 @@
         <v>750</v>
       </c>
       <c r="C727" t="s">
-        <v>1732</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="728" spans="1:3">
@@ -14370,7 +14340,7 @@
         <v>751</v>
       </c>
       <c r="C728" t="s">
-        <v>1733</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="729" spans="1:3">
@@ -14381,7 +14351,7 @@
         <v>752</v>
       </c>
       <c r="C729" t="s">
-        <v>1734</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="730" spans="1:3">
@@ -14392,7 +14362,7 @@
         <v>753</v>
       </c>
       <c r="C730" t="s">
-        <v>1735</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="731" spans="1:3">
@@ -14403,7 +14373,7 @@
         <v>754</v>
       </c>
       <c r="C731" t="s">
-        <v>1736</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="732" spans="1:3">
@@ -14414,7 +14384,7 @@
         <v>755</v>
       </c>
       <c r="C732" t="s">
-        <v>1737</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="733" spans="1:3">
@@ -14425,7 +14395,7 @@
         <v>756</v>
       </c>
       <c r="C733" t="s">
-        <v>1738</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="734" spans="1:3">
@@ -14436,7 +14406,7 @@
         <v>757</v>
       </c>
       <c r="C734" t="s">
-        <v>1739</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="735" spans="1:3">
@@ -14447,7 +14417,7 @@
         <v>758</v>
       </c>
       <c r="C735" t="s">
-        <v>1740</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="736" spans="1:3">
@@ -14458,7 +14428,7 @@
         <v>759</v>
       </c>
       <c r="C736" t="s">
-        <v>1741</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="737" spans="1:3">
@@ -14469,7 +14439,7 @@
         <v>760</v>
       </c>
       <c r="C737" t="s">
-        <v>1742</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="738" spans="1:3">
@@ -14480,7 +14450,7 @@
         <v>761</v>
       </c>
       <c r="C738" t="s">
-        <v>1743</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="739" spans="1:3">
@@ -14491,7 +14461,7 @@
         <v>762</v>
       </c>
       <c r="C739" t="s">
-        <v>1744</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="740" spans="1:3">
@@ -14502,7 +14472,7 @@
         <v>763</v>
       </c>
       <c r="C740" t="s">
-        <v>1668</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="741" spans="1:3">
@@ -14513,7 +14483,7 @@
         <v>764</v>
       </c>
       <c r="C741" t="s">
-        <v>1745</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="742" spans="1:3">
@@ -14524,7 +14494,7 @@
         <v>765</v>
       </c>
       <c r="C742" t="s">
-        <v>1746</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="743" spans="1:3">
@@ -14535,7 +14505,7 @@
         <v>766</v>
       </c>
       <c r="C743" t="s">
-        <v>1747</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="744" spans="1:3">
@@ -14546,7 +14516,7 @@
         <v>767</v>
       </c>
       <c r="C744" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="745" spans="1:3">
@@ -14557,7 +14527,7 @@
         <v>768</v>
       </c>
       <c r="C745" t="s">
-        <v>1749</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="746" spans="1:3">
@@ -14568,7 +14538,7 @@
         <v>769</v>
       </c>
       <c r="C746" t="s">
-        <v>1750</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="747" spans="1:3">
@@ -14579,7 +14549,7 @@
         <v>770</v>
       </c>
       <c r="C747" t="s">
-        <v>1751</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="748" spans="1:3">
@@ -14590,7 +14560,7 @@
         <v>771</v>
       </c>
       <c r="C748" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="749" spans="1:3">
@@ -14601,7 +14571,7 @@
         <v>772</v>
       </c>
       <c r="C749" t="s">
-        <v>1753</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="750" spans="1:3">
@@ -14612,7 +14582,7 @@
         <v>773</v>
       </c>
       <c r="C750" t="s">
-        <v>1754</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="751" spans="1:3">
@@ -14623,7 +14593,7 @@
         <v>774</v>
       </c>
       <c r="C751" t="s">
-        <v>1755</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="752" spans="1:3">
@@ -14634,7 +14604,7 @@
         <v>775</v>
       </c>
       <c r="C752" t="s">
-        <v>1756</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="753" spans="1:3">
@@ -14645,7 +14615,7 @@
         <v>776</v>
       </c>
       <c r="C753" t="s">
-        <v>1757</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="754" spans="1:3">
@@ -14656,7 +14626,7 @@
         <v>777</v>
       </c>
       <c r="C754" t="s">
-        <v>1758</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="755" spans="1:3">
@@ -14667,7 +14637,7 @@
         <v>778</v>
       </c>
       <c r="C755" t="s">
-        <v>1759</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="756" spans="1:3">
@@ -14678,7 +14648,7 @@
         <v>779</v>
       </c>
       <c r="C756" t="s">
-        <v>1760</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="757" spans="1:3">
@@ -14689,7 +14659,7 @@
         <v>780</v>
       </c>
       <c r="C757" t="s">
-        <v>1761</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="758" spans="1:3">
@@ -14700,7 +14670,7 @@
         <v>781</v>
       </c>
       <c r="C758" t="s">
-        <v>1762</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="759" spans="1:3">
@@ -14711,7 +14681,7 @@
         <v>782</v>
       </c>
       <c r="C759" t="s">
-        <v>1763</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="760" spans="1:3">
@@ -14722,7 +14692,7 @@
         <v>783</v>
       </c>
       <c r="C760" t="s">
-        <v>1764</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="761" spans="1:3">
@@ -14733,7 +14703,7 @@
         <v>784</v>
       </c>
       <c r="C761" t="s">
-        <v>1765</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="762" spans="1:3">
@@ -14744,7 +14714,7 @@
         <v>785</v>
       </c>
       <c r="C762" t="s">
-        <v>1766</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="763" spans="1:3">
@@ -14755,7 +14725,7 @@
         <v>786</v>
       </c>
       <c r="C763" t="s">
-        <v>1767</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="764" spans="1:3">
@@ -14766,7 +14736,7 @@
         <v>787</v>
       </c>
       <c r="C764" t="s">
-        <v>1768</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="765" spans="1:3">
@@ -14777,7 +14747,7 @@
         <v>788</v>
       </c>
       <c r="C765" t="s">
-        <v>1769</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="766" spans="1:3">
@@ -14788,7 +14758,7 @@
         <v>789</v>
       </c>
       <c r="C766" t="s">
-        <v>1770</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="767" spans="1:3">
@@ -14799,7 +14769,7 @@
         <v>790</v>
       </c>
       <c r="C767" t="s">
-        <v>1771</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="768" spans="1:3">
@@ -14810,7 +14780,7 @@
         <v>791</v>
       </c>
       <c r="C768" t="s">
-        <v>1772</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="769" spans="1:3">
@@ -14821,7 +14791,7 @@
         <v>792</v>
       </c>
       <c r="C769" t="s">
-        <v>1773</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="770" spans="1:3">
@@ -14832,7 +14802,7 @@
         <v>793</v>
       </c>
       <c r="C770" t="s">
-        <v>1774</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="771" spans="1:3">
@@ -14843,7 +14813,7 @@
         <v>794</v>
       </c>
       <c r="C771" t="s">
-        <v>1775</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="772" spans="1:3">
@@ -14854,7 +14824,7 @@
         <v>795</v>
       </c>
       <c r="C772" t="s">
-        <v>1776</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="773" spans="1:3">
@@ -14865,7 +14835,7 @@
         <v>796</v>
       </c>
       <c r="C773" t="s">
-        <v>1777</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="774" spans="1:3">
@@ -14876,7 +14846,7 @@
         <v>797</v>
       </c>
       <c r="C774" t="s">
-        <v>1778</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="775" spans="1:3">
@@ -14887,7 +14857,7 @@
         <v>798</v>
       </c>
       <c r="C775" t="s">
-        <v>1779</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="776" spans="1:3">
@@ -14898,7 +14868,7 @@
         <v>799</v>
       </c>
       <c r="C776" t="s">
-        <v>1780</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="777" spans="1:3">
@@ -14909,7 +14879,7 @@
         <v>800</v>
       </c>
       <c r="C777" t="s">
-        <v>1781</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="778" spans="1:3">
@@ -14920,7 +14890,7 @@
         <v>801</v>
       </c>
       <c r="C778" t="s">
-        <v>1782</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="779" spans="1:3">
@@ -14931,7 +14901,7 @@
         <v>802</v>
       </c>
       <c r="C779" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="780" spans="1:3">
@@ -14942,7 +14912,7 @@
         <v>803</v>
       </c>
       <c r="C780" t="s">
-        <v>1784</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="781" spans="1:3">
@@ -14953,7 +14923,7 @@
         <v>804</v>
       </c>
       <c r="C781" t="s">
-        <v>1785</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="782" spans="1:3">
@@ -14964,7 +14934,7 @@
         <v>805</v>
       </c>
       <c r="C782" t="s">
-        <v>1786</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="783" spans="1:3">
@@ -14975,7 +14945,7 @@
         <v>806</v>
       </c>
       <c r="C783" t="s">
-        <v>1787</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="784" spans="1:3">
@@ -14986,7 +14956,7 @@
         <v>807</v>
       </c>
       <c r="C784" t="s">
-        <v>1788</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="785" spans="1:3">
@@ -14997,7 +14967,7 @@
         <v>808</v>
       </c>
       <c r="C785" t="s">
-        <v>1789</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="786" spans="1:3">
@@ -15008,7 +14978,7 @@
         <v>809</v>
       </c>
       <c r="C786" t="s">
-        <v>1790</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="787" spans="1:3">
@@ -15019,7 +14989,7 @@
         <v>810</v>
       </c>
       <c r="C787" t="s">
-        <v>1791</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="788" spans="1:3">
@@ -15030,7 +15000,7 @@
         <v>811</v>
       </c>
       <c r="C788" t="s">
-        <v>1792</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="789" spans="1:3">
@@ -15041,7 +15011,7 @@
         <v>812</v>
       </c>
       <c r="C789" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="790" spans="1:3">
@@ -15052,7 +15022,7 @@
         <v>813</v>
       </c>
       <c r="C790" t="s">
-        <v>1794</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="791" spans="1:3">
@@ -15063,7 +15033,7 @@
         <v>814</v>
       </c>
       <c r="C791" t="s">
-        <v>1795</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="792" spans="1:3">
@@ -15074,7 +15044,7 @@
         <v>815</v>
       </c>
       <c r="C792" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="793" spans="1:3">
@@ -15085,7 +15055,7 @@
         <v>816</v>
       </c>
       <c r="C793" t="s">
-        <v>1797</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="794" spans="1:3">
@@ -15096,7 +15066,7 @@
         <v>817</v>
       </c>
       <c r="C794" t="s">
-        <v>1798</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="795" spans="1:3">
@@ -15107,7 +15077,7 @@
         <v>818</v>
       </c>
       <c r="C795" t="s">
-        <v>1799</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="796" spans="1:3">
@@ -15118,7 +15088,7 @@
         <v>819</v>
       </c>
       <c r="C796" t="s">
-        <v>1800</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="797" spans="1:3">
@@ -15129,7 +15099,7 @@
         <v>820</v>
       </c>
       <c r="C797" t="s">
-        <v>1801</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="798" spans="1:3">
@@ -15140,7 +15110,7 @@
         <v>821</v>
       </c>
       <c r="C798" t="s">
-        <v>1802</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="799" spans="1:3">
@@ -15151,7 +15121,7 @@
         <v>822</v>
       </c>
       <c r="C799" t="s">
-        <v>1803</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="800" spans="1:3">
@@ -15162,7 +15132,7 @@
         <v>823</v>
       </c>
       <c r="C800" t="s">
-        <v>1804</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="801" spans="1:3">
@@ -15173,7 +15143,7 @@
         <v>824</v>
       </c>
       <c r="C801" t="s">
-        <v>1805</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="802" spans="1:3">
@@ -15184,7 +15154,7 @@
         <v>825</v>
       </c>
       <c r="C802" t="s">
-        <v>1806</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="803" spans="1:3">
@@ -15195,7 +15165,7 @@
         <v>826</v>
       </c>
       <c r="C803" t="s">
-        <v>1807</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="804" spans="1:3">
@@ -15206,7 +15176,7 @@
         <v>827</v>
       </c>
       <c r="C804" t="s">
-        <v>1808</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="805" spans="1:3">
@@ -15217,7 +15187,7 @@
         <v>828</v>
       </c>
       <c r="C805" t="s">
-        <v>1809</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="806" spans="1:3">
@@ -15228,7 +15198,7 @@
         <v>829</v>
       </c>
       <c r="C806" t="s">
-        <v>1810</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="807" spans="1:3">
@@ -15239,7 +15209,7 @@
         <v>830</v>
       </c>
       <c r="C807" t="s">
-        <v>1811</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="808" spans="1:3">
@@ -15250,40 +15220,40 @@
         <v>831</v>
       </c>
       <c r="C808" t="s">
-        <v>1812</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="809" spans="1:3">
       <c r="A809" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B809" t="s">
         <v>832</v>
       </c>
       <c r="C809" t="s">
-        <v>1813</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="810" spans="1:3">
       <c r="A810" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B810" t="s">
         <v>833</v>
       </c>
       <c r="C810" t="s">
-        <v>1814</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="811" spans="1:3">
       <c r="A811" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B811" t="s">
         <v>834</v>
       </c>
       <c r="C811" t="s">
-        <v>1815</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="812" spans="1:3">
@@ -15294,7 +15264,7 @@
         <v>835</v>
       </c>
       <c r="C812" t="s">
-        <v>1816</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="813" spans="1:3">
@@ -15305,7 +15275,7 @@
         <v>836</v>
       </c>
       <c r="C813" t="s">
-        <v>1817</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="814" spans="1:3">
@@ -15316,7 +15286,7 @@
         <v>837</v>
       </c>
       <c r="C814" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="815" spans="1:3">
@@ -15327,7 +15297,7 @@
         <v>838</v>
       </c>
       <c r="C815" t="s">
-        <v>1819</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="816" spans="1:3">
@@ -15338,7 +15308,7 @@
         <v>839</v>
       </c>
       <c r="C816" t="s">
-        <v>1820</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="817" spans="1:3">
@@ -15349,7 +15319,7 @@
         <v>840</v>
       </c>
       <c r="C817" t="s">
-        <v>1821</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="818" spans="1:3">
@@ -15360,7 +15330,7 @@
         <v>841</v>
       </c>
       <c r="C818" t="s">
-        <v>1822</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="819" spans="1:3">
@@ -15371,7 +15341,7 @@
         <v>842</v>
       </c>
       <c r="C819" t="s">
-        <v>1823</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="820" spans="1:3">
@@ -15382,7 +15352,7 @@
         <v>843</v>
       </c>
       <c r="C820" t="s">
-        <v>1824</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="821" spans="1:3">
@@ -15393,7 +15363,7 @@
         <v>844</v>
       </c>
       <c r="C821" t="s">
-        <v>1825</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="822" spans="1:3">
@@ -15404,7 +15374,7 @@
         <v>845</v>
       </c>
       <c r="C822" t="s">
-        <v>1826</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="823" spans="1:3">
@@ -15415,7 +15385,7 @@
         <v>846</v>
       </c>
       <c r="C823" t="s">
-        <v>1827</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="824" spans="1:3">
@@ -15426,7 +15396,7 @@
         <v>847</v>
       </c>
       <c r="C824" t="s">
-        <v>1828</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="825" spans="1:3">
@@ -15437,7 +15407,7 @@
         <v>848</v>
       </c>
       <c r="C825" t="s">
-        <v>1829</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="826" spans="1:3">
@@ -15448,7 +15418,7 @@
         <v>849</v>
       </c>
       <c r="C826" t="s">
-        <v>1830</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="827" spans="1:3">
@@ -15459,7 +15429,7 @@
         <v>850</v>
       </c>
       <c r="C827" t="s">
-        <v>1831</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="828" spans="1:3">
@@ -15470,7 +15440,7 @@
         <v>851</v>
       </c>
       <c r="C828" t="s">
-        <v>1832</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="829" spans="1:3">
@@ -15481,7 +15451,7 @@
         <v>852</v>
       </c>
       <c r="C829" t="s">
-        <v>1833</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="830" spans="1:3">
@@ -15492,7 +15462,7 @@
         <v>853</v>
       </c>
       <c r="C830" t="s">
-        <v>1834</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="831" spans="1:3">
@@ -15503,7 +15473,7 @@
         <v>854</v>
       </c>
       <c r="C831" t="s">
-        <v>1835</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="832" spans="1:3">
@@ -15514,7 +15484,7 @@
         <v>855</v>
       </c>
       <c r="C832" t="s">
-        <v>1836</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="833" spans="1:3">
@@ -15525,7 +15495,7 @@
         <v>856</v>
       </c>
       <c r="C833" t="s">
-        <v>1837</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="834" spans="1:3">
@@ -15536,7 +15506,7 @@
         <v>857</v>
       </c>
       <c r="C834" t="s">
-        <v>1838</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="835" spans="1:3">
@@ -15547,7 +15517,7 @@
         <v>858</v>
       </c>
       <c r="C835" t="s">
-        <v>1839</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="836" spans="1:3">
@@ -15558,7 +15528,7 @@
         <v>859</v>
       </c>
       <c r="C836" t="s">
-        <v>1840</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="837" spans="1:3">
@@ -15569,7 +15539,7 @@
         <v>860</v>
       </c>
       <c r="C837" t="s">
-        <v>1841</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="838" spans="1:3">
@@ -15580,7 +15550,7 @@
         <v>861</v>
       </c>
       <c r="C838" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="839" spans="1:3">
@@ -15591,7 +15561,7 @@
         <v>862</v>
       </c>
       <c r="C839" t="s">
-        <v>1843</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="840" spans="1:3">
@@ -15602,7 +15572,7 @@
         <v>863</v>
       </c>
       <c r="C840" t="s">
-        <v>1844</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="841" spans="1:3">
@@ -15613,7 +15583,7 @@
         <v>864</v>
       </c>
       <c r="C841" t="s">
-        <v>1845</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="842" spans="1:3">
@@ -15624,7 +15594,7 @@
         <v>865</v>
       </c>
       <c r="C842" t="s">
-        <v>1846</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="843" spans="1:3">
@@ -15635,7 +15605,7 @@
         <v>866</v>
       </c>
       <c r="C843" t="s">
-        <v>1847</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="844" spans="1:3">
@@ -15646,7 +15616,7 @@
         <v>867</v>
       </c>
       <c r="C844" t="s">
-        <v>1848</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="845" spans="1:3">
@@ -15657,7 +15627,7 @@
         <v>868</v>
       </c>
       <c r="C845" t="s">
-        <v>1849</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="846" spans="1:3">
@@ -15668,7 +15638,7 @@
         <v>869</v>
       </c>
       <c r="C846" t="s">
-        <v>1850</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="847" spans="1:3">
@@ -15679,7 +15649,7 @@
         <v>870</v>
       </c>
       <c r="C847" t="s">
-        <v>1851</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="848" spans="1:3">
@@ -15690,7 +15660,7 @@
         <v>871</v>
       </c>
       <c r="C848" t="s">
-        <v>1852</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="849" spans="1:3">
@@ -15701,7 +15671,7 @@
         <v>872</v>
       </c>
       <c r="C849" t="s">
-        <v>1853</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="850" spans="1:3">
@@ -15712,7 +15682,7 @@
         <v>873</v>
       </c>
       <c r="C850" t="s">
-        <v>1854</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="851" spans="1:3">
@@ -15723,7 +15693,7 @@
         <v>874</v>
       </c>
       <c r="C851" t="s">
-        <v>1855</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="852" spans="1:3">
@@ -15734,7 +15704,7 @@
         <v>875</v>
       </c>
       <c r="C852" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="853" spans="1:3">
@@ -15745,7 +15715,7 @@
         <v>876</v>
       </c>
       <c r="C853" t="s">
-        <v>1857</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="854" spans="1:3">
@@ -15756,7 +15726,7 @@
         <v>877</v>
       </c>
       <c r="C854" t="s">
-        <v>1858</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="855" spans="1:3">
@@ -15767,7 +15737,7 @@
         <v>878</v>
       </c>
       <c r="C855" t="s">
-        <v>1859</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="856" spans="1:3">
@@ -15778,7 +15748,7 @@
         <v>879</v>
       </c>
       <c r="C856" t="s">
-        <v>1860</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="857" spans="1:3">
@@ -15789,7 +15759,7 @@
         <v>880</v>
       </c>
       <c r="C857" t="s">
-        <v>1861</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="858" spans="1:3">
@@ -15800,7 +15770,7 @@
         <v>881</v>
       </c>
       <c r="C858" t="s">
-        <v>1862</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="859" spans="1:3">
@@ -15811,7 +15781,7 @@
         <v>882</v>
       </c>
       <c r="C859" t="s">
-        <v>1863</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="860" spans="1:3">
@@ -15822,7 +15792,7 @@
         <v>883</v>
       </c>
       <c r="C860" t="s">
-        <v>1864</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="861" spans="1:3">
@@ -15833,7 +15803,7 @@
         <v>884</v>
       </c>
       <c r="C861" t="s">
-        <v>1865</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="862" spans="1:3">
@@ -15844,7 +15814,7 @@
         <v>885</v>
       </c>
       <c r="C862" t="s">
-        <v>1866</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="863" spans="1:3">
@@ -15855,7 +15825,7 @@
         <v>886</v>
       </c>
       <c r="C863" t="s">
-        <v>1867</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="864" spans="1:3">
@@ -15866,7 +15836,7 @@
         <v>887</v>
       </c>
       <c r="C864" t="s">
-        <v>1868</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="865" spans="1:3">
@@ -15877,7 +15847,7 @@
         <v>888</v>
       </c>
       <c r="C865" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="866" spans="1:3">
@@ -15888,7 +15858,7 @@
         <v>889</v>
       </c>
       <c r="C866" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="867" spans="1:3">
@@ -15899,7 +15869,7 @@
         <v>890</v>
       </c>
       <c r="C867" t="s">
-        <v>1871</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="868" spans="1:3">
@@ -15910,7 +15880,7 @@
         <v>891</v>
       </c>
       <c r="C868" t="s">
-        <v>1872</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="869" spans="1:3">
@@ -15921,7 +15891,7 @@
         <v>892</v>
       </c>
       <c r="C869" t="s">
-        <v>1873</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="870" spans="1:3">
@@ -15932,7 +15902,7 @@
         <v>893</v>
       </c>
       <c r="C870" t="s">
-        <v>1874</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="871" spans="1:3">
@@ -15943,7 +15913,7 @@
         <v>894</v>
       </c>
       <c r="C871" t="s">
-        <v>1875</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="872" spans="1:3">
@@ -15954,7 +15924,7 @@
         <v>895</v>
       </c>
       <c r="C872" t="s">
-        <v>1876</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="873" spans="1:3">
@@ -15965,7 +15935,7 @@
         <v>896</v>
       </c>
       <c r="C873" t="s">
-        <v>1877</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="874" spans="1:3">
@@ -15976,7 +15946,7 @@
         <v>897</v>
       </c>
       <c r="C874" t="s">
-        <v>1878</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="875" spans="1:3">
@@ -15987,7 +15957,7 @@
         <v>898</v>
       </c>
       <c r="C875" t="s">
-        <v>1879</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="876" spans="1:3">
@@ -15998,7 +15968,7 @@
         <v>899</v>
       </c>
       <c r="C876" t="s">
-        <v>1880</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="877" spans="1:3">
@@ -16009,7 +15979,7 @@
         <v>900</v>
       </c>
       <c r="C877" t="s">
-        <v>1881</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="878" spans="1:3">
@@ -16020,7 +15990,7 @@
         <v>901</v>
       </c>
       <c r="C878" t="s">
-        <v>1882</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="879" spans="1:3">
@@ -16031,7 +16001,7 @@
         <v>902</v>
       </c>
       <c r="C879" t="s">
-        <v>1883</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="880" spans="1:3">
@@ -16042,7 +16012,7 @@
         <v>903</v>
       </c>
       <c r="C880" t="s">
-        <v>1884</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="881" spans="1:3">
@@ -16053,7 +16023,7 @@
         <v>904</v>
       </c>
       <c r="C881" t="s">
-        <v>1885</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="882" spans="1:3">
@@ -16064,7 +16034,7 @@
         <v>905</v>
       </c>
       <c r="C882" t="s">
-        <v>1886</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="883" spans="1:3">
@@ -16075,7 +16045,7 @@
         <v>906</v>
       </c>
       <c r="C883" t="s">
-        <v>1887</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="884" spans="1:3">
@@ -16086,7 +16056,7 @@
         <v>907</v>
       </c>
       <c r="C884" t="s">
-        <v>1888</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="885" spans="1:3">
@@ -16097,7 +16067,7 @@
         <v>908</v>
       </c>
       <c r="C885" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="886" spans="1:3">
@@ -16108,7 +16078,7 @@
         <v>909</v>
       </c>
       <c r="C886" t="s">
-        <v>1890</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="887" spans="1:3">
@@ -16119,7 +16089,7 @@
         <v>910</v>
       </c>
       <c r="C887" t="s">
-        <v>1891</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="888" spans="1:3">
@@ -16130,7 +16100,7 @@
         <v>911</v>
       </c>
       <c r="C888" t="s">
-        <v>1892</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="889" spans="1:3">
@@ -16141,7 +16111,7 @@
         <v>912</v>
       </c>
       <c r="C889" t="s">
-        <v>1893</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="890" spans="1:3">
@@ -16152,7 +16122,7 @@
         <v>913</v>
       </c>
       <c r="C890" t="s">
-        <v>1894</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="891" spans="1:3">
@@ -16163,7 +16133,7 @@
         <v>914</v>
       </c>
       <c r="C891" t="s">
-        <v>1895</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="892" spans="1:3">
@@ -16174,7 +16144,7 @@
         <v>915</v>
       </c>
       <c r="C892" t="s">
-        <v>1896</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="893" spans="1:3">
@@ -16185,40 +16155,40 @@
         <v>916</v>
       </c>
       <c r="C893" t="s">
-        <v>1897</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="894" spans="1:3">
       <c r="A894" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B894" t="s">
         <v>917</v>
       </c>
       <c r="C894" t="s">
-        <v>1898</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="895" spans="1:3">
       <c r="A895" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B895" t="s">
         <v>918</v>
       </c>
       <c r="C895" t="s">
-        <v>1899</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="896" spans="1:3">
       <c r="A896" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B896" t="s">
         <v>919</v>
       </c>
       <c r="C896" t="s">
-        <v>1900</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="897" spans="1:3">
@@ -16229,7 +16199,7 @@
         <v>920</v>
       </c>
       <c r="C897" t="s">
-        <v>1901</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="898" spans="1:3">
@@ -16240,7 +16210,7 @@
         <v>921</v>
       </c>
       <c r="C898" t="s">
-        <v>1902</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="899" spans="1:3">
@@ -16251,7 +16221,7 @@
         <v>922</v>
       </c>
       <c r="C899" t="s">
-        <v>1903</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="900" spans="1:3">
@@ -16262,7 +16232,7 @@
         <v>923</v>
       </c>
       <c r="C900" t="s">
-        <v>1904</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="901" spans="1:3">
@@ -16273,7 +16243,7 @@
         <v>924</v>
       </c>
       <c r="C901" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="902" spans="1:3">
@@ -16284,7 +16254,7 @@
         <v>925</v>
       </c>
       <c r="C902" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="903" spans="1:3">
@@ -16295,7 +16265,7 @@
         <v>926</v>
       </c>
       <c r="C903" t="s">
-        <v>1907</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="904" spans="1:3">
@@ -16306,7 +16276,7 @@
         <v>927</v>
       </c>
       <c r="C904" t="s">
-        <v>1908</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="905" spans="1:3">
@@ -16317,7 +16287,7 @@
         <v>928</v>
       </c>
       <c r="C905" t="s">
-        <v>1909</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="906" spans="1:3">
@@ -16328,7 +16298,7 @@
         <v>929</v>
       </c>
       <c r="C906" t="s">
-        <v>1910</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="907" spans="1:3">
@@ -16339,7 +16309,7 @@
         <v>930</v>
       </c>
       <c r="C907" t="s">
-        <v>1911</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="908" spans="1:3">
@@ -16350,7 +16320,7 @@
         <v>931</v>
       </c>
       <c r="C908" t="s">
-        <v>1912</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="909" spans="1:3">
@@ -16361,7 +16331,7 @@
         <v>932</v>
       </c>
       <c r="C909" t="s">
-        <v>1913</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="910" spans="1:3">
@@ -16372,7 +16342,7 @@
         <v>933</v>
       </c>
       <c r="C910" t="s">
-        <v>1914</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="911" spans="1:3">
@@ -16383,7 +16353,7 @@
         <v>934</v>
       </c>
       <c r="C911" t="s">
-        <v>1915</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="912" spans="1:3">
@@ -16394,7 +16364,7 @@
         <v>935</v>
       </c>
       <c r="C912" t="s">
-        <v>1916</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="913" spans="1:3">
@@ -16405,7 +16375,7 @@
         <v>936</v>
       </c>
       <c r="C913" t="s">
-        <v>1917</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="914" spans="1:3">
@@ -16416,7 +16386,7 @@
         <v>937</v>
       </c>
       <c r="C914" t="s">
-        <v>1918</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="915" spans="1:3">
@@ -16427,7 +16397,7 @@
         <v>938</v>
       </c>
       <c r="C915" t="s">
-        <v>1919</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="916" spans="1:3">
@@ -16438,7 +16408,7 @@
         <v>939</v>
       </c>
       <c r="C916" t="s">
-        <v>1920</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="917" spans="1:3">
@@ -16449,7 +16419,7 @@
         <v>940</v>
       </c>
       <c r="C917" t="s">
-        <v>1921</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="918" spans="1:3">
@@ -16460,7 +16430,7 @@
         <v>941</v>
       </c>
       <c r="C918" t="s">
-        <v>1922</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="919" spans="1:3">
@@ -16471,7 +16441,7 @@
         <v>942</v>
       </c>
       <c r="C919" t="s">
-        <v>1923</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="920" spans="1:3">
@@ -16482,7 +16452,7 @@
         <v>943</v>
       </c>
       <c r="C920" t="s">
-        <v>1924</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="921" spans="1:3">
@@ -16493,7 +16463,7 @@
         <v>944</v>
       </c>
       <c r="C921" t="s">
-        <v>1925</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="922" spans="1:3">
@@ -16504,7 +16474,7 @@
         <v>945</v>
       </c>
       <c r="C922" t="s">
-        <v>1926</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="923" spans="1:3">
@@ -16515,7 +16485,7 @@
         <v>946</v>
       </c>
       <c r="C923" t="s">
-        <v>1927</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="924" spans="1:3">
@@ -16526,7 +16496,7 @@
         <v>947</v>
       </c>
       <c r="C924" t="s">
-        <v>1928</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="925" spans="1:3">
@@ -16537,7 +16507,7 @@
         <v>948</v>
       </c>
       <c r="C925" t="s">
-        <v>1929</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="926" spans="1:3">
@@ -16548,7 +16518,7 @@
         <v>949</v>
       </c>
       <c r="C926" t="s">
-        <v>1930</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="927" spans="1:3">
@@ -16559,7 +16529,7 @@
         <v>950</v>
       </c>
       <c r="C927" t="s">
-        <v>1931</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="928" spans="1:3">
@@ -16570,7 +16540,7 @@
         <v>951</v>
       </c>
       <c r="C928" t="s">
-        <v>1932</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="929" spans="1:3">
@@ -16581,7 +16551,7 @@
         <v>952</v>
       </c>
       <c r="C929" t="s">
-        <v>1933</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="930" spans="1:3">
@@ -16592,7 +16562,7 @@
         <v>953</v>
       </c>
       <c r="C930" t="s">
-        <v>1934</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="931" spans="1:3">
@@ -16603,7 +16573,7 @@
         <v>954</v>
       </c>
       <c r="C931" t="s">
-        <v>1935</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="932" spans="1:3">
@@ -16614,7 +16584,7 @@
         <v>955</v>
       </c>
       <c r="C932" t="s">
-        <v>1936</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="933" spans="1:3">
@@ -16625,7 +16595,7 @@
         <v>956</v>
       </c>
       <c r="C933" t="s">
-        <v>1937</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="934" spans="1:3">
@@ -16636,7 +16606,7 @@
         <v>957</v>
       </c>
       <c r="C934" t="s">
-        <v>1938</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="935" spans="1:3">
@@ -16647,7 +16617,7 @@
         <v>958</v>
       </c>
       <c r="C935" t="s">
-        <v>1939</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="936" spans="1:3">
@@ -16658,7 +16628,7 @@
         <v>959</v>
       </c>
       <c r="C936" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="937" spans="1:3">
@@ -16669,7 +16639,7 @@
         <v>960</v>
       </c>
       <c r="C937" t="s">
-        <v>1940</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="938" spans="1:3">
@@ -16680,7 +16650,7 @@
         <v>961</v>
       </c>
       <c r="C938" t="s">
-        <v>1941</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="939" spans="1:3">
@@ -16691,7 +16661,7 @@
         <v>962</v>
       </c>
       <c r="C939" t="s">
-        <v>1942</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="940" spans="1:3">
@@ -16702,7 +16672,7 @@
         <v>963</v>
       </c>
       <c r="C940" t="s">
-        <v>1943</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="941" spans="1:3">
@@ -16713,7 +16683,7 @@
         <v>964</v>
       </c>
       <c r="C941" t="s">
-        <v>1944</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="942" spans="1:3">
@@ -16724,7 +16694,7 @@
         <v>965</v>
       </c>
       <c r="C942" t="s">
-        <v>1945</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="943" spans="1:3">
@@ -16735,7 +16705,7 @@
         <v>966</v>
       </c>
       <c r="C943" t="s">
-        <v>1946</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="944" spans="1:3">
@@ -16746,7 +16716,7 @@
         <v>967</v>
       </c>
       <c r="C944" t="s">
-        <v>1947</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="945" spans="1:3">
@@ -16757,7 +16727,7 @@
         <v>968</v>
       </c>
       <c r="C945" t="s">
-        <v>1948</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="946" spans="1:3">
@@ -16768,7 +16738,7 @@
         <v>969</v>
       </c>
       <c r="C946" t="s">
-        <v>1949</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="947" spans="1:3">
@@ -16779,7 +16749,7 @@
         <v>970</v>
       </c>
       <c r="C947" t="s">
-        <v>1950</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="948" spans="1:3">
@@ -16790,7 +16760,7 @@
         <v>971</v>
       </c>
       <c r="C948" t="s">
-        <v>1951</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="949" spans="1:3">
@@ -16801,7 +16771,7 @@
         <v>972</v>
       </c>
       <c r="C949" t="s">
-        <v>1952</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="950" spans="1:3">
@@ -16812,7 +16782,7 @@
         <v>973</v>
       </c>
       <c r="C950" t="s">
-        <v>1953</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="951" spans="1:3">
@@ -16823,7 +16793,7 @@
         <v>974</v>
       </c>
       <c r="C951" t="s">
-        <v>1954</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="952" spans="1:3">
@@ -16834,7 +16804,7 @@
         <v>975</v>
       </c>
       <c r="C952" t="s">
-        <v>1955</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="953" spans="1:3">
@@ -16845,7 +16815,7 @@
         <v>976</v>
       </c>
       <c r="C953" t="s">
-        <v>1956</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="954" spans="1:3">
@@ -16856,7 +16826,7 @@
         <v>977</v>
       </c>
       <c r="C954" t="s">
-        <v>1957</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="955" spans="1:3">
@@ -16867,7 +16837,7 @@
         <v>978</v>
       </c>
       <c r="C955" t="s">
-        <v>1958</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="956" spans="1:3">
@@ -16878,7 +16848,7 @@
         <v>979</v>
       </c>
       <c r="C956" t="s">
-        <v>1959</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="957" spans="1:3">
@@ -16889,7 +16859,7 @@
         <v>980</v>
       </c>
       <c r="C957" t="s">
-        <v>1934</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="958" spans="1:3">
@@ -16900,7 +16870,7 @@
         <v>981</v>
       </c>
       <c r="C958" t="s">
-        <v>1960</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="959" spans="1:3">
@@ -16911,7 +16881,7 @@
         <v>982</v>
       </c>
       <c r="C959" t="s">
-        <v>1961</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="960" spans="1:3">
@@ -16922,7 +16892,7 @@
         <v>983</v>
       </c>
       <c r="C960" t="s">
-        <v>1962</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="961" spans="1:3">
@@ -16933,7 +16903,7 @@
         <v>984</v>
       </c>
       <c r="C961" t="s">
-        <v>1915</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="962" spans="1:3">
@@ -16944,7 +16914,7 @@
         <v>985</v>
       </c>
       <c r="C962" t="s">
-        <v>1963</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="963" spans="1:3">
@@ -16955,51 +16925,51 @@
         <v>986</v>
       </c>
       <c r="C963" t="s">
-        <v>1964</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="964" spans="1:3">
       <c r="A964" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B964" t="s">
         <v>987</v>
       </c>
       <c r="C964" t="s">
-        <v>1965</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="965" spans="1:3">
       <c r="A965" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B965" t="s">
         <v>988</v>
       </c>
       <c r="C965" t="s">
-        <v>1966</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="966" spans="1:3">
       <c r="A966" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B966" t="s">
         <v>989</v>
       </c>
       <c r="C966" t="s">
-        <v>1967</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="967" spans="1:3">
       <c r="A967" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B967" t="s">
         <v>990</v>
       </c>
       <c r="C967" t="s">
-        <v>1968</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="968" spans="1:3">
@@ -17010,7 +16980,7 @@
         <v>991</v>
       </c>
       <c r="C968" t="s">
-        <v>1969</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="969" spans="1:3">
@@ -17021,7 +16991,7 @@
         <v>992</v>
       </c>
       <c r="C969" t="s">
-        <v>1970</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="970" spans="1:3">
@@ -17032,7 +17002,7 @@
         <v>993</v>
       </c>
       <c r="C970" t="s">
-        <v>1971</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="971" spans="1:3">
@@ -17043,7 +17013,7 @@
         <v>994</v>
       </c>
       <c r="C971" t="s">
-        <v>1972</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="972" spans="1:3">
@@ -17054,7 +17024,7 @@
         <v>995</v>
       </c>
       <c r="C972" t="s">
-        <v>1973</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="973" spans="1:3">
@@ -17065,7 +17035,7 @@
         <v>996</v>
       </c>
       <c r="C973" t="s">
-        <v>1974</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="974" spans="1:3">
@@ -17076,7 +17046,7 @@
         <v>997</v>
       </c>
       <c r="C974" t="s">
-        <v>1975</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="975" spans="1:3">
@@ -17087,7 +17057,7 @@
         <v>998</v>
       </c>
       <c r="C975" t="s">
-        <v>1976</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="976" spans="1:3">
@@ -17098,7 +17068,7 @@
         <v>999</v>
       </c>
       <c r="C976" t="s">
-        <v>1977</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="977" spans="1:3">
@@ -17109,7 +17079,7 @@
         <v>1000</v>
       </c>
       <c r="C977" t="s">
-        <v>1978</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="978" spans="1:3">
@@ -17120,7 +17090,7 @@
         <v>1001</v>
       </c>
       <c r="C978" t="s">
-        <v>1979</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="979" spans="1:3">
@@ -17131,7 +17101,7 @@
         <v>1002</v>
       </c>
       <c r="C979" t="s">
-        <v>1980</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="980" spans="1:3">
@@ -17142,7 +17112,7 @@
         <v>1003</v>
       </c>
       <c r="C980" t="s">
-        <v>1981</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="981" spans="1:3">
@@ -17153,7 +17123,7 @@
         <v>1004</v>
       </c>
       <c r="C981" t="s">
-        <v>1982</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="982" spans="1:3">
@@ -17164,7 +17134,7 @@
         <v>1005</v>
       </c>
       <c r="C982" t="s">
-        <v>1983</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="983" spans="1:3">
@@ -17175,7 +17145,7 @@
         <v>1006</v>
       </c>
       <c r="C983" t="s">
-        <v>1984</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="984" spans="1:3">
@@ -17186,7 +17156,7 @@
         <v>1007</v>
       </c>
       <c r="C984" t="s">
-        <v>1985</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="985" spans="1:3">
@@ -17197,7 +17167,7 @@
         <v>1008</v>
       </c>
       <c r="C985" t="s">
-        <v>1986</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="986" spans="1:3">
@@ -17208,7 +17178,7 @@
         <v>1009</v>
       </c>
       <c r="C986" t="s">
-        <v>1987</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="987" spans="1:3">
@@ -17219,7 +17189,7 @@
         <v>1010</v>
       </c>
       <c r="C987" t="s">
-        <v>1988</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="988" spans="1:3">
@@ -17230,7 +17200,7 @@
         <v>1011</v>
       </c>
       <c r="C988" t="s">
-        <v>1989</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="989" spans="1:3">
@@ -17241,73 +17211,18 @@
         <v>1012</v>
       </c>
       <c r="C989" t="s">
-        <v>1990</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="990" spans="1:3">
       <c r="A990" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B990" t="s">
         <v>1013</v>
       </c>
       <c r="C990" t="s">
-        <v>1991</v>
-      </c>
-    </row>
-    <row r="991" spans="1:3">
-      <c r="A991" t="s">
-        <v>23</v>
-      </c>
-      <c r="B991" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C991" t="s">
-        <v>1992</v>
-      </c>
-    </row>
-    <row r="992" spans="1:3">
-      <c r="A992" t="s">
-        <v>23</v>
-      </c>
-      <c r="B992" t="s">
-        <v>1015</v>
-      </c>
-      <c r="C992" t="s">
-        <v>1993</v>
-      </c>
-    </row>
-    <row r="993" spans="1:3">
-      <c r="A993" t="s">
-        <v>23</v>
-      </c>
-      <c r="B993" t="s">
-        <v>1016</v>
-      </c>
-      <c r="C993" t="s">
-        <v>1994</v>
-      </c>
-    </row>
-    <row r="994" spans="1:3">
-      <c r="A994" t="s">
-        <v>23</v>
-      </c>
-      <c r="B994" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C994" t="s">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="995" spans="1:3">
-      <c r="A995" t="s">
-        <v>24</v>
-      </c>
-      <c r="B995" t="s">
-        <v>1018</v>
-      </c>
-      <c r="C995" t="s">
-        <v>1996</v>
+        <v>1986</v>
       </c>
     </row>
   </sheetData>

--- a/faltantes_por_estados.xlsx
+++ b/faltantes_por_estados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2970" uniqueCount="1987">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2946" uniqueCount="1971">
   <si>
     <t>entidad</t>
   </si>
@@ -1603,9 +1603,6 @@
     <t>HGIMB002350</t>
   </si>
   <si>
-    <t>HGIMB002403</t>
-  </si>
-  <si>
     <t>HGIMB002456</t>
   </si>
   <si>
@@ -1660,15 +1657,9 @@
     <t>MCIMB002203</t>
   </si>
   <si>
-    <t>MCIMB002430</t>
-  </si>
-  <si>
     <t>MCIMB002442</t>
   </si>
   <si>
-    <t>MCIMB002454</t>
-  </si>
-  <si>
     <t>MCIMB002466</t>
   </si>
   <si>
@@ -1684,12 +1675,6 @@
     <t>MCIMB002500</t>
   </si>
   <si>
-    <t>MCIMB002524</t>
-  </si>
-  <si>
-    <t>MCIMB002536</t>
-  </si>
-  <si>
     <t>MCIMB003854</t>
   </si>
   <si>
@@ -1699,15 +1684,6 @@
     <t>MCIMB005382</t>
   </si>
   <si>
-    <t>MCIMB006596</t>
-  </si>
-  <si>
-    <t>MCIMB006613</t>
-  </si>
-  <si>
-    <t>MCIMB006765</t>
-  </si>
-  <si>
     <t>MCIMB008054</t>
   </si>
   <si>
@@ -4540,9 +4516,6 @@
     <t>LA ALCANTARILLA</t>
   </si>
   <si>
-    <t>PACHUCA (DR. JESÚS DEL ROSAL)</t>
-  </si>
-  <si>
     <t>GUAYABOS</t>
   </si>
   <si>
@@ -4597,15 +4570,9 @@
     <t>SANTA MARÍA TULPETLAC</t>
   </si>
   <si>
-    <t>COLONIA CHOCOLINES</t>
-  </si>
-  <si>
     <t>COLONIA VALLE VERDE</t>
   </si>
   <si>
-    <t>IXTAPALUCA</t>
-  </si>
-  <si>
     <t>ALFREDO DEL MAZO</t>
   </si>
   <si>
@@ -4621,12 +4588,6 @@
     <t>COLONIA TEJOLOTE</t>
   </si>
   <si>
-    <t>COATEPEC</t>
-  </si>
-  <si>
-    <t>GENERAL MANUEL ÁVILA CAMACHO</t>
-  </si>
-  <si>
     <t>OLIMPIADA 68</t>
   </si>
   <si>
@@ -4634,15 +4595,6 @@
   </si>
   <si>
     <t>CEAPS TEMAMATLA</t>
-  </si>
-  <si>
-    <t>CEAPS TLALMANALCO EPIGMENIO DE LA PIEDRA</t>
-  </si>
-  <si>
-    <t>SAN RAFAEL</t>
-  </si>
-  <si>
-    <t>SAN LUCAS PATONI</t>
   </si>
   <si>
     <t>COLONIA SANTIAGO</t>
@@ -6332,7 +6284,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C990"/>
+  <dimension ref="A1:C982"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6354,7 +6306,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6365,7 +6317,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>1015</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6376,7 +6328,7 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>1016</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6387,7 +6339,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>1017</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6398,7 +6350,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>1018</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6409,7 +6361,7 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>1019</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6420,7 +6372,7 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>1020</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6431,7 +6383,7 @@
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>1021</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6442,7 +6394,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>1022</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6453,7 +6405,7 @@
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>1023</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6464,7 +6416,7 @@
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>1024</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6475,7 +6427,7 @@
         <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>1025</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6486,7 +6438,7 @@
         <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>1026</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6497,7 +6449,7 @@
         <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>1027</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -6508,7 +6460,7 @@
         <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>1028</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6530,7 +6482,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>1029</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6541,7 +6493,7 @@
         <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>1030</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6552,7 +6504,7 @@
         <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>1031</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6563,7 +6515,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>1032</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6574,7 +6526,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>1033</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6585,7 +6537,7 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>1034</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6596,7 +6548,7 @@
         <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>1035</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6607,7 +6559,7 @@
         <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>1036</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -6618,7 +6570,7 @@
         <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>1037</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6640,7 +6592,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="s">
-        <v>1038</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6662,7 +6614,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="s">
-        <v>1039</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -6673,7 +6625,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="s">
-        <v>1040</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -6684,7 +6636,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="s">
-        <v>1029</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -6695,7 +6647,7 @@
         <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>1041</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6706,7 +6658,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="s">
-        <v>1042</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -6717,7 +6669,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="s">
-        <v>1043</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6728,7 +6680,7 @@
         <v>59</v>
       </c>
       <c r="C36" t="s">
-        <v>1044</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6739,7 +6691,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="s">
-        <v>1045</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -6750,7 +6702,7 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>1046</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -6761,7 +6713,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="s">
-        <v>1047</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -6772,7 +6724,7 @@
         <v>63</v>
       </c>
       <c r="C40" t="s">
-        <v>1048</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -6783,7 +6735,7 @@
         <v>64</v>
       </c>
       <c r="C41" t="s">
-        <v>1049</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -6794,7 +6746,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="s">
-        <v>1050</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -6805,7 +6757,7 @@
         <v>66</v>
       </c>
       <c r="C43" t="s">
-        <v>1051</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -6816,7 +6768,7 @@
         <v>67</v>
       </c>
       <c r="C44" t="s">
-        <v>1052</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -6827,7 +6779,7 @@
         <v>68</v>
       </c>
       <c r="C45" t="s">
-        <v>1053</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -6838,7 +6790,7 @@
         <v>69</v>
       </c>
       <c r="C46" t="s">
-        <v>1054</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -6849,7 +6801,7 @@
         <v>70</v>
       </c>
       <c r="C47" t="s">
-        <v>1055</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -6860,7 +6812,7 @@
         <v>71</v>
       </c>
       <c r="C48" t="s">
-        <v>1056</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -6871,7 +6823,7 @@
         <v>72</v>
       </c>
       <c r="C49" t="s">
-        <v>1057</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -6882,7 +6834,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>1058</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -6893,7 +6845,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="s">
-        <v>1059</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -6904,7 +6856,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="s">
-        <v>1060</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -6915,7 +6867,7 @@
         <v>76</v>
       </c>
       <c r="C53" t="s">
-        <v>1061</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -6926,7 +6878,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>1062</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -6937,7 +6889,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="s">
-        <v>1063</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -6948,7 +6900,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="s">
-        <v>1064</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -6959,7 +6911,7 @@
         <v>80</v>
       </c>
       <c r="C57" t="s">
-        <v>1065</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -6970,7 +6922,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="s">
-        <v>1066</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -6981,7 +6933,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="s">
-        <v>1067</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -7003,7 +6955,7 @@
         <v>84</v>
       </c>
       <c r="C61" t="s">
-        <v>1068</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -7014,7 +6966,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="s">
-        <v>1069</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -7025,7 +6977,7 @@
         <v>86</v>
       </c>
       <c r="C63" t="s">
-        <v>1070</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -7036,7 +6988,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="s">
-        <v>1071</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -7047,7 +6999,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="s">
-        <v>1072</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -7058,7 +7010,7 @@
         <v>89</v>
       </c>
       <c r="C66" t="s">
-        <v>1073</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -7069,7 +7021,7 @@
         <v>90</v>
       </c>
       <c r="C67" t="s">
-        <v>1074</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -7080,7 +7032,7 @@
         <v>91</v>
       </c>
       <c r="C68" t="s">
-        <v>1075</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -7091,7 +7043,7 @@
         <v>92</v>
       </c>
       <c r="C69" t="s">
-        <v>1076</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -7102,7 +7054,7 @@
         <v>93</v>
       </c>
       <c r="C70" t="s">
-        <v>1077</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -7113,7 +7065,7 @@
         <v>94</v>
       </c>
       <c r="C71" t="s">
-        <v>1078</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -7124,7 +7076,7 @@
         <v>95</v>
       </c>
       <c r="C72" t="s">
-        <v>1079</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -7135,7 +7087,7 @@
         <v>96</v>
       </c>
       <c r="C73" t="s">
-        <v>1080</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -7146,7 +7098,7 @@
         <v>97</v>
       </c>
       <c r="C74" t="s">
-        <v>1081</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -7157,7 +7109,7 @@
         <v>98</v>
       </c>
       <c r="C75" t="s">
-        <v>1082</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -7168,7 +7120,7 @@
         <v>99</v>
       </c>
       <c r="C76" t="s">
-        <v>1083</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -7179,7 +7131,7 @@
         <v>100</v>
       </c>
       <c r="C77" t="s">
-        <v>1084</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -7190,7 +7142,7 @@
         <v>101</v>
       </c>
       <c r="C78" t="s">
-        <v>1085</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -7201,7 +7153,7 @@
         <v>102</v>
       </c>
       <c r="C79" t="s">
-        <v>1086</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -7212,7 +7164,7 @@
         <v>103</v>
       </c>
       <c r="C80" t="s">
-        <v>1087</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -7223,7 +7175,7 @@
         <v>104</v>
       </c>
       <c r="C81" t="s">
-        <v>1088</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -7234,7 +7186,7 @@
         <v>105</v>
       </c>
       <c r="C82" t="s">
-        <v>1089</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -7245,7 +7197,7 @@
         <v>106</v>
       </c>
       <c r="C83" t="s">
-        <v>1090</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -7256,7 +7208,7 @@
         <v>107</v>
       </c>
       <c r="C84" t="s">
-        <v>1091</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -7267,7 +7219,7 @@
         <v>108</v>
       </c>
       <c r="C85" t="s">
-        <v>1092</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -7278,7 +7230,7 @@
         <v>109</v>
       </c>
       <c r="C86" t="s">
-        <v>1093</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -7289,7 +7241,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="s">
-        <v>1094</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -7300,7 +7252,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="s">
-        <v>1095</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -7311,7 +7263,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="s">
-        <v>1096</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -7322,7 +7274,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="s">
-        <v>1097</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -7333,7 +7285,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="s">
-        <v>1098</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -7344,7 +7296,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="s">
-        <v>1099</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -7355,7 +7307,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="s">
-        <v>1100</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -7366,7 +7318,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="s">
-        <v>1101</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -7377,7 +7329,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="s">
-        <v>1102</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -7388,7 +7340,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="s">
-        <v>1103</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -7399,7 +7351,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="s">
-        <v>1104</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -7410,7 +7362,7 @@
         <v>121</v>
       </c>
       <c r="C98" t="s">
-        <v>1105</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -7421,7 +7373,7 @@
         <v>122</v>
       </c>
       <c r="C99" t="s">
-        <v>1106</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -7432,7 +7384,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="s">
-        <v>1107</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -7443,7 +7395,7 @@
         <v>124</v>
       </c>
       <c r="C101" t="s">
-        <v>1108</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -7454,7 +7406,7 @@
         <v>125</v>
       </c>
       <c r="C102" t="s">
-        <v>1109</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -7465,7 +7417,7 @@
         <v>126</v>
       </c>
       <c r="C103" t="s">
-        <v>1110</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -7476,7 +7428,7 @@
         <v>127</v>
       </c>
       <c r="C104" t="s">
-        <v>1111</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -7487,7 +7439,7 @@
         <v>128</v>
       </c>
       <c r="C105" t="s">
-        <v>1112</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -7498,7 +7450,7 @@
         <v>129</v>
       </c>
       <c r="C106" t="s">
-        <v>1113</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -7509,7 +7461,7 @@
         <v>130</v>
       </c>
       <c r="C107" t="s">
-        <v>1114</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -7520,7 +7472,7 @@
         <v>131</v>
       </c>
       <c r="C108" t="s">
-        <v>1115</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -7531,7 +7483,7 @@
         <v>132</v>
       </c>
       <c r="C109" t="s">
-        <v>1116</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -7542,7 +7494,7 @@
         <v>133</v>
       </c>
       <c r="C110" t="s">
-        <v>1117</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -7553,7 +7505,7 @@
         <v>134</v>
       </c>
       <c r="C111" t="s">
-        <v>1118</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -7564,7 +7516,7 @@
         <v>135</v>
       </c>
       <c r="C112" t="s">
-        <v>1119</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -7575,7 +7527,7 @@
         <v>136</v>
       </c>
       <c r="C113" t="s">
-        <v>1120</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -7586,7 +7538,7 @@
         <v>137</v>
       </c>
       <c r="C114" t="s">
-        <v>1121</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -7597,7 +7549,7 @@
         <v>138</v>
       </c>
       <c r="C115" t="s">
-        <v>1122</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -7608,7 +7560,7 @@
         <v>139</v>
       </c>
       <c r="C116" t="s">
-        <v>1123</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -7619,7 +7571,7 @@
         <v>140</v>
       </c>
       <c r="C117" t="s">
-        <v>1124</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -7630,7 +7582,7 @@
         <v>141</v>
       </c>
       <c r="C118" t="s">
-        <v>1125</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -7641,7 +7593,7 @@
         <v>142</v>
       </c>
       <c r="C119" t="s">
-        <v>1126</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -7652,7 +7604,7 @@
         <v>143</v>
       </c>
       <c r="C120" t="s">
-        <v>1127</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -7663,7 +7615,7 @@
         <v>144</v>
       </c>
       <c r="C121" t="s">
-        <v>1128</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -7674,7 +7626,7 @@
         <v>145</v>
       </c>
       <c r="C122" t="s">
-        <v>1129</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -7685,7 +7637,7 @@
         <v>146</v>
       </c>
       <c r="C123" t="s">
-        <v>1130</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -7696,7 +7648,7 @@
         <v>147</v>
       </c>
       <c r="C124" t="s">
-        <v>1131</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -7707,7 +7659,7 @@
         <v>148</v>
       </c>
       <c r="C125" t="s">
-        <v>1132</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -7718,7 +7670,7 @@
         <v>149</v>
       </c>
       <c r="C126" t="s">
-        <v>1133</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -7729,7 +7681,7 @@
         <v>150</v>
       </c>
       <c r="C127" t="s">
-        <v>1134</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -7740,7 +7692,7 @@
         <v>151</v>
       </c>
       <c r="C128" t="s">
-        <v>1135</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -7751,7 +7703,7 @@
         <v>152</v>
       </c>
       <c r="C129" t="s">
-        <v>1136</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -7762,7 +7714,7 @@
         <v>153</v>
       </c>
       <c r="C130" t="s">
-        <v>1137</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -7773,7 +7725,7 @@
         <v>154</v>
       </c>
       <c r="C131" t="s">
-        <v>1138</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -7784,7 +7736,7 @@
         <v>155</v>
       </c>
       <c r="C132" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -7795,7 +7747,7 @@
         <v>156</v>
       </c>
       <c r="C133" t="s">
-        <v>1140</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -7806,7 +7758,7 @@
         <v>157</v>
       </c>
       <c r="C134" t="s">
-        <v>1141</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -7817,7 +7769,7 @@
         <v>158</v>
       </c>
       <c r="C135" t="s">
-        <v>1142</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -7828,7 +7780,7 @@
         <v>159</v>
       </c>
       <c r="C136" t="s">
-        <v>1143</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -7839,7 +7791,7 @@
         <v>160</v>
       </c>
       <c r="C137" t="s">
-        <v>1144</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -7850,7 +7802,7 @@
         <v>161</v>
       </c>
       <c r="C138" t="s">
-        <v>1145</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -7861,7 +7813,7 @@
         <v>162</v>
       </c>
       <c r="C139" t="s">
-        <v>1146</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -7872,7 +7824,7 @@
         <v>163</v>
       </c>
       <c r="C140" t="s">
-        <v>1147</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -7883,7 +7835,7 @@
         <v>164</v>
       </c>
       <c r="C141" t="s">
-        <v>1148</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -7894,7 +7846,7 @@
         <v>165</v>
       </c>
       <c r="C142" t="s">
-        <v>1149</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -7905,7 +7857,7 @@
         <v>166</v>
       </c>
       <c r="C143" t="s">
-        <v>1150</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -7916,7 +7868,7 @@
         <v>167</v>
       </c>
       <c r="C144" t="s">
-        <v>1151</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -7927,7 +7879,7 @@
         <v>168</v>
       </c>
       <c r="C145" t="s">
-        <v>1152</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -7938,7 +7890,7 @@
         <v>169</v>
       </c>
       <c r="C146" t="s">
-        <v>1153</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -7949,7 +7901,7 @@
         <v>170</v>
       </c>
       <c r="C147" t="s">
-        <v>1154</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -7960,7 +7912,7 @@
         <v>171</v>
       </c>
       <c r="C148" t="s">
-        <v>1155</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -7971,7 +7923,7 @@
         <v>172</v>
       </c>
       <c r="C149" t="s">
-        <v>1156</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -7982,7 +7934,7 @@
         <v>173</v>
       </c>
       <c r="C150" t="s">
-        <v>1157</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -7993,7 +7945,7 @@
         <v>174</v>
       </c>
       <c r="C151" t="s">
-        <v>1158</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -8004,7 +7956,7 @@
         <v>175</v>
       </c>
       <c r="C152" t="s">
-        <v>1159</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -8015,7 +7967,7 @@
         <v>176</v>
       </c>
       <c r="C153" t="s">
-        <v>1160</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -8026,7 +7978,7 @@
         <v>177</v>
       </c>
       <c r="C154" t="s">
-        <v>1161</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -8037,7 +7989,7 @@
         <v>178</v>
       </c>
       <c r="C155" t="s">
-        <v>1162</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -8048,7 +8000,7 @@
         <v>179</v>
       </c>
       <c r="C156" t="s">
-        <v>1163</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -8059,7 +8011,7 @@
         <v>180</v>
       </c>
       <c r="C157" t="s">
-        <v>1164</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -8070,7 +8022,7 @@
         <v>181</v>
       </c>
       <c r="C158" t="s">
-        <v>1165</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -8081,7 +8033,7 @@
         <v>182</v>
       </c>
       <c r="C159" t="s">
-        <v>1166</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -8092,7 +8044,7 @@
         <v>183</v>
       </c>
       <c r="C160" t="s">
-        <v>1167</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -8103,7 +8055,7 @@
         <v>184</v>
       </c>
       <c r="C161" t="s">
-        <v>1168</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -8114,7 +8066,7 @@
         <v>185</v>
       </c>
       <c r="C162" t="s">
-        <v>1169</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -8125,7 +8077,7 @@
         <v>186</v>
       </c>
       <c r="C163" t="s">
-        <v>1170</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -8136,7 +8088,7 @@
         <v>187</v>
       </c>
       <c r="C164" t="s">
-        <v>1171</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -8147,7 +8099,7 @@
         <v>188</v>
       </c>
       <c r="C165" t="s">
-        <v>1172</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -8158,7 +8110,7 @@
         <v>189</v>
       </c>
       <c r="C166" t="s">
-        <v>1173</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -8169,7 +8121,7 @@
         <v>190</v>
       </c>
       <c r="C167" t="s">
-        <v>1174</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -8180,7 +8132,7 @@
         <v>191</v>
       </c>
       <c r="C168" t="s">
-        <v>1175</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -8191,7 +8143,7 @@
         <v>192</v>
       </c>
       <c r="C169" t="s">
-        <v>1176</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -8202,7 +8154,7 @@
         <v>193</v>
       </c>
       <c r="C170" t="s">
-        <v>1177</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -8213,7 +8165,7 @@
         <v>194</v>
       </c>
       <c r="C171" t="s">
-        <v>1178</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -8224,7 +8176,7 @@
         <v>195</v>
       </c>
       <c r="C172" t="s">
-        <v>1179</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -8235,7 +8187,7 @@
         <v>196</v>
       </c>
       <c r="C173" t="s">
-        <v>1180</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -8246,7 +8198,7 @@
         <v>197</v>
       </c>
       <c r="C174" t="s">
-        <v>1181</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -8257,7 +8209,7 @@
         <v>198</v>
       </c>
       <c r="C175" t="s">
-        <v>1182</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -8268,7 +8220,7 @@
         <v>199</v>
       </c>
       <c r="C176" t="s">
-        <v>1183</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -8279,7 +8231,7 @@
         <v>200</v>
       </c>
       <c r="C177" t="s">
-        <v>1184</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -8290,7 +8242,7 @@
         <v>201</v>
       </c>
       <c r="C178" t="s">
-        <v>1185</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -8301,7 +8253,7 @@
         <v>202</v>
       </c>
       <c r="C179" t="s">
-        <v>1186</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -8312,7 +8264,7 @@
         <v>203</v>
       </c>
       <c r="C180" t="s">
-        <v>1187</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -8323,7 +8275,7 @@
         <v>204</v>
       </c>
       <c r="C181" t="s">
-        <v>1188</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -8334,7 +8286,7 @@
         <v>205</v>
       </c>
       <c r="C182" t="s">
-        <v>1189</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -8345,7 +8297,7 @@
         <v>206</v>
       </c>
       <c r="C183" t="s">
-        <v>1190</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -8356,7 +8308,7 @@
         <v>207</v>
       </c>
       <c r="C184" t="s">
-        <v>1191</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -8367,7 +8319,7 @@
         <v>208</v>
       </c>
       <c r="C185" t="s">
-        <v>1192</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -8378,7 +8330,7 @@
         <v>209</v>
       </c>
       <c r="C186" t="s">
-        <v>1193</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -8389,7 +8341,7 @@
         <v>210</v>
       </c>
       <c r="C187" t="s">
-        <v>1194</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -8400,7 +8352,7 @@
         <v>211</v>
       </c>
       <c r="C188" t="s">
-        <v>1195</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -8411,7 +8363,7 @@
         <v>212</v>
       </c>
       <c r="C189" t="s">
-        <v>1196</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -8422,7 +8374,7 @@
         <v>213</v>
       </c>
       <c r="C190" t="s">
-        <v>1197</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -8433,7 +8385,7 @@
         <v>214</v>
       </c>
       <c r="C191" t="s">
-        <v>1198</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -8444,7 +8396,7 @@
         <v>215</v>
       </c>
       <c r="C192" t="s">
-        <v>1199</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -8455,7 +8407,7 @@
         <v>216</v>
       </c>
       <c r="C193" t="s">
-        <v>1200</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -8466,7 +8418,7 @@
         <v>217</v>
       </c>
       <c r="C194" t="s">
-        <v>1201</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -8477,7 +8429,7 @@
         <v>218</v>
       </c>
       <c r="C195" t="s">
-        <v>1202</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -8488,7 +8440,7 @@
         <v>219</v>
       </c>
       <c r="C196" t="s">
-        <v>1203</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -8499,7 +8451,7 @@
         <v>220</v>
       </c>
       <c r="C197" t="s">
-        <v>1204</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -8510,7 +8462,7 @@
         <v>221</v>
       </c>
       <c r="C198" t="s">
-        <v>1205</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -8521,7 +8473,7 @@
         <v>222</v>
       </c>
       <c r="C199" t="s">
-        <v>1206</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -8532,7 +8484,7 @@
         <v>223</v>
       </c>
       <c r="C200" t="s">
-        <v>1207</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -8543,7 +8495,7 @@
         <v>224</v>
       </c>
       <c r="C201" t="s">
-        <v>1208</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -8554,7 +8506,7 @@
         <v>225</v>
       </c>
       <c r="C202" t="s">
-        <v>1209</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -8565,7 +8517,7 @@
         <v>226</v>
       </c>
       <c r="C203" t="s">
-        <v>1210</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -8576,7 +8528,7 @@
         <v>227</v>
       </c>
       <c r="C204" t="s">
-        <v>1211</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -8587,7 +8539,7 @@
         <v>228</v>
       </c>
       <c r="C205" t="s">
-        <v>1212</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -8598,7 +8550,7 @@
         <v>229</v>
       </c>
       <c r="C206" t="s">
-        <v>1213</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -8609,7 +8561,7 @@
         <v>230</v>
       </c>
       <c r="C207" t="s">
-        <v>1214</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -8620,7 +8572,7 @@
         <v>231</v>
       </c>
       <c r="C208" t="s">
-        <v>1215</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -8631,7 +8583,7 @@
         <v>232</v>
       </c>
       <c r="C209" t="s">
-        <v>1216</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -8642,7 +8594,7 @@
         <v>233</v>
       </c>
       <c r="C210" t="s">
-        <v>1217</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -8653,7 +8605,7 @@
         <v>234</v>
       </c>
       <c r="C211" t="s">
-        <v>1218</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -8664,7 +8616,7 @@
         <v>235</v>
       </c>
       <c r="C212" t="s">
-        <v>1219</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -8675,7 +8627,7 @@
         <v>236</v>
       </c>
       <c r="C213" t="s">
-        <v>1220</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -8686,7 +8638,7 @@
         <v>237</v>
       </c>
       <c r="C214" t="s">
-        <v>1221</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -8697,7 +8649,7 @@
         <v>238</v>
       </c>
       <c r="C215" t="s">
-        <v>1222</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -8708,7 +8660,7 @@
         <v>239</v>
       </c>
       <c r="C216" t="s">
-        <v>1223</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -8719,7 +8671,7 @@
         <v>240</v>
       </c>
       <c r="C217" t="s">
-        <v>1224</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -8730,7 +8682,7 @@
         <v>241</v>
       </c>
       <c r="C218" t="s">
-        <v>1225</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -8741,7 +8693,7 @@
         <v>242</v>
       </c>
       <c r="C219" t="s">
-        <v>1226</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -8752,7 +8704,7 @@
         <v>243</v>
       </c>
       <c r="C220" t="s">
-        <v>1227</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -8763,7 +8715,7 @@
         <v>244</v>
       </c>
       <c r="C221" t="s">
-        <v>1228</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -8774,7 +8726,7 @@
         <v>245</v>
       </c>
       <c r="C222" t="s">
-        <v>1229</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -8785,7 +8737,7 @@
         <v>246</v>
       </c>
       <c r="C223" t="s">
-        <v>1230</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -8796,7 +8748,7 @@
         <v>247</v>
       </c>
       <c r="C224" t="s">
-        <v>1231</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -8807,7 +8759,7 @@
         <v>248</v>
       </c>
       <c r="C225" t="s">
-        <v>1232</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -8818,7 +8770,7 @@
         <v>249</v>
       </c>
       <c r="C226" t="s">
-        <v>1233</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -8829,7 +8781,7 @@
         <v>250</v>
       </c>
       <c r="C227" t="s">
-        <v>1234</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -8840,7 +8792,7 @@
         <v>251</v>
       </c>
       <c r="C228" t="s">
-        <v>1235</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -8851,7 +8803,7 @@
         <v>252</v>
       </c>
       <c r="C229" t="s">
-        <v>1236</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -8862,7 +8814,7 @@
         <v>253</v>
       </c>
       <c r="C230" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -8873,7 +8825,7 @@
         <v>254</v>
       </c>
       <c r="C231" t="s">
-        <v>1238</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -8884,7 +8836,7 @@
         <v>255</v>
       </c>
       <c r="C232" t="s">
-        <v>1239</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -8895,7 +8847,7 @@
         <v>256</v>
       </c>
       <c r="C233" t="s">
-        <v>1240</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -8906,7 +8858,7 @@
         <v>257</v>
       </c>
       <c r="C234" t="s">
-        <v>1241</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -8917,7 +8869,7 @@
         <v>258</v>
       </c>
       <c r="C235" t="s">
-        <v>1242</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -8928,7 +8880,7 @@
         <v>259</v>
       </c>
       <c r="C236" t="s">
-        <v>1243</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -8939,7 +8891,7 @@
         <v>260</v>
       </c>
       <c r="C237" t="s">
-        <v>1244</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -8950,7 +8902,7 @@
         <v>261</v>
       </c>
       <c r="C238" t="s">
-        <v>1245</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -8961,7 +8913,7 @@
         <v>262</v>
       </c>
       <c r="C239" t="s">
-        <v>1246</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -8972,7 +8924,7 @@
         <v>263</v>
       </c>
       <c r="C240" t="s">
-        <v>1247</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -8983,7 +8935,7 @@
         <v>264</v>
       </c>
       <c r="C241" t="s">
-        <v>1248</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -8994,7 +8946,7 @@
         <v>265</v>
       </c>
       <c r="C242" t="s">
-        <v>1249</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -9005,7 +8957,7 @@
         <v>266</v>
       </c>
       <c r="C243" t="s">
-        <v>1250</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -9016,7 +8968,7 @@
         <v>267</v>
       </c>
       <c r="C244" t="s">
-        <v>1251</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -9027,7 +8979,7 @@
         <v>268</v>
       </c>
       <c r="C245" t="s">
-        <v>1252</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -9038,7 +8990,7 @@
         <v>269</v>
       </c>
       <c r="C246" t="s">
-        <v>1253</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -9049,7 +9001,7 @@
         <v>270</v>
       </c>
       <c r="C247" t="s">
-        <v>1254</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -9060,7 +9012,7 @@
         <v>271</v>
       </c>
       <c r="C248" t="s">
-        <v>1255</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -9071,7 +9023,7 @@
         <v>272</v>
       </c>
       <c r="C249" t="s">
-        <v>1256</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -9082,7 +9034,7 @@
         <v>273</v>
       </c>
       <c r="C250" t="s">
-        <v>1257</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -9093,7 +9045,7 @@
         <v>274</v>
       </c>
       <c r="C251" t="s">
-        <v>1258</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -9104,7 +9056,7 @@
         <v>275</v>
       </c>
       <c r="C252" t="s">
-        <v>1259</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -9115,7 +9067,7 @@
         <v>276</v>
       </c>
       <c r="C253" t="s">
-        <v>1260</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -9126,7 +9078,7 @@
         <v>277</v>
       </c>
       <c r="C254" t="s">
-        <v>1261</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -9137,7 +9089,7 @@
         <v>278</v>
       </c>
       <c r="C255" t="s">
-        <v>1262</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -9148,7 +9100,7 @@
         <v>279</v>
       </c>
       <c r="C256" t="s">
-        <v>1263</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -9159,7 +9111,7 @@
         <v>280</v>
       </c>
       <c r="C257" t="s">
-        <v>1264</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -9170,7 +9122,7 @@
         <v>281</v>
       </c>
       <c r="C258" t="s">
-        <v>1265</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="259" spans="1:3">
@@ -9181,7 +9133,7 @@
         <v>282</v>
       </c>
       <c r="C259" t="s">
-        <v>1266</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -9192,7 +9144,7 @@
         <v>283</v>
       </c>
       <c r="C260" t="s">
-        <v>1267</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="261" spans="1:3">
@@ -9203,7 +9155,7 @@
         <v>284</v>
       </c>
       <c r="C261" t="s">
-        <v>1268</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="262" spans="1:3">
@@ -9214,7 +9166,7 @@
         <v>285</v>
       </c>
       <c r="C262" t="s">
-        <v>1269</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -9225,7 +9177,7 @@
         <v>286</v>
       </c>
       <c r="C263" t="s">
-        <v>1270</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="264" spans="1:3">
@@ -9236,7 +9188,7 @@
         <v>287</v>
       </c>
       <c r="C264" t="s">
-        <v>1271</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -9247,7 +9199,7 @@
         <v>288</v>
       </c>
       <c r="C265" t="s">
-        <v>1272</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="266" spans="1:3">
@@ -9258,7 +9210,7 @@
         <v>289</v>
       </c>
       <c r="C266" t="s">
-        <v>1273</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="267" spans="1:3">
@@ -9269,7 +9221,7 @@
         <v>290</v>
       </c>
       <c r="C267" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="268" spans="1:3">
@@ -9280,7 +9232,7 @@
         <v>291</v>
       </c>
       <c r="C268" t="s">
-        <v>1275</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="269" spans="1:3">
@@ -9291,7 +9243,7 @@
         <v>292</v>
       </c>
       <c r="C269" t="s">
-        <v>1276</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="270" spans="1:3">
@@ -9302,7 +9254,7 @@
         <v>293</v>
       </c>
       <c r="C270" t="s">
-        <v>1277</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="271" spans="1:3">
@@ -9313,7 +9265,7 @@
         <v>294</v>
       </c>
       <c r="C271" t="s">
-        <v>1278</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="272" spans="1:3">
@@ -9324,7 +9276,7 @@
         <v>295</v>
       </c>
       <c r="C272" t="s">
-        <v>1279</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="273" spans="1:3">
@@ -9335,7 +9287,7 @@
         <v>296</v>
       </c>
       <c r="C273" t="s">
-        <v>1280</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="274" spans="1:3">
@@ -9346,7 +9298,7 @@
         <v>297</v>
       </c>
       <c r="C274" t="s">
-        <v>1281</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="275" spans="1:3">
@@ -9357,7 +9309,7 @@
         <v>298</v>
       </c>
       <c r="C275" t="s">
-        <v>1282</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="276" spans="1:3">
@@ -9368,7 +9320,7 @@
         <v>299</v>
       </c>
       <c r="C276" t="s">
-        <v>1200</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="277" spans="1:3">
@@ -9379,7 +9331,7 @@
         <v>300</v>
       </c>
       <c r="C277" t="s">
-        <v>1283</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="278" spans="1:3">
@@ -9390,7 +9342,7 @@
         <v>301</v>
       </c>
       <c r="C278" t="s">
-        <v>1284</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="279" spans="1:3">
@@ -9401,7 +9353,7 @@
         <v>302</v>
       </c>
       <c r="C279" t="s">
-        <v>1285</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="280" spans="1:3">
@@ -9412,7 +9364,7 @@
         <v>303</v>
       </c>
       <c r="C280" t="s">
-        <v>1286</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -9423,7 +9375,7 @@
         <v>304</v>
       </c>
       <c r="C281" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="282" spans="1:3">
@@ -9434,7 +9386,7 @@
         <v>305</v>
       </c>
       <c r="C282" t="s">
-        <v>1288</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="283" spans="1:3">
@@ -9445,7 +9397,7 @@
         <v>306</v>
       </c>
       <c r="C283" t="s">
-        <v>1289</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="284" spans="1:3">
@@ -9456,7 +9408,7 @@
         <v>307</v>
       </c>
       <c r="C284" t="s">
-        <v>1290</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="285" spans="1:3">
@@ -9467,7 +9419,7 @@
         <v>308</v>
       </c>
       <c r="C285" t="s">
-        <v>1291</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="286" spans="1:3">
@@ -9478,7 +9430,7 @@
         <v>309</v>
       </c>
       <c r="C286" t="s">
-        <v>1292</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="287" spans="1:3">
@@ -9489,7 +9441,7 @@
         <v>310</v>
       </c>
       <c r="C287" t="s">
-        <v>1293</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="288" spans="1:3">
@@ -9500,7 +9452,7 @@
         <v>311</v>
       </c>
       <c r="C288" t="s">
-        <v>1294</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="289" spans="1:3">
@@ -9511,7 +9463,7 @@
         <v>312</v>
       </c>
       <c r="C289" t="s">
-        <v>1295</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="290" spans="1:3">
@@ -9522,7 +9474,7 @@
         <v>313</v>
       </c>
       <c r="C290" t="s">
-        <v>1296</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="291" spans="1:3">
@@ -9533,7 +9485,7 @@
         <v>314</v>
       </c>
       <c r="C291" t="s">
-        <v>1297</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="292" spans="1:3">
@@ -9544,7 +9496,7 @@
         <v>315</v>
       </c>
       <c r="C292" t="s">
-        <v>1298</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="293" spans="1:3">
@@ -9555,7 +9507,7 @@
         <v>316</v>
       </c>
       <c r="C293" t="s">
-        <v>1299</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="294" spans="1:3">
@@ -9566,7 +9518,7 @@
         <v>317</v>
       </c>
       <c r="C294" t="s">
-        <v>1300</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="295" spans="1:3">
@@ -9577,7 +9529,7 @@
         <v>318</v>
       </c>
       <c r="C295" t="s">
-        <v>1301</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="296" spans="1:3">
@@ -9588,7 +9540,7 @@
         <v>319</v>
       </c>
       <c r="C296" t="s">
-        <v>1302</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="297" spans="1:3">
@@ -9599,7 +9551,7 @@
         <v>320</v>
       </c>
       <c r="C297" t="s">
-        <v>1303</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="298" spans="1:3">
@@ -9610,7 +9562,7 @@
         <v>321</v>
       </c>
       <c r="C298" t="s">
-        <v>1304</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="299" spans="1:3">
@@ -9621,7 +9573,7 @@
         <v>322</v>
       </c>
       <c r="C299" t="s">
-        <v>1305</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="300" spans="1:3">
@@ -9632,7 +9584,7 @@
         <v>323</v>
       </c>
       <c r="C300" t="s">
-        <v>1306</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="301" spans="1:3">
@@ -9643,7 +9595,7 @@
         <v>324</v>
       </c>
       <c r="C301" t="s">
-        <v>1307</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -9654,7 +9606,7 @@
         <v>325</v>
       </c>
       <c r="C302" t="s">
-        <v>1308</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="303" spans="1:3">
@@ -9665,7 +9617,7 @@
         <v>326</v>
       </c>
       <c r="C303" t="s">
-        <v>1309</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="304" spans="1:3">
@@ -9676,7 +9628,7 @@
         <v>327</v>
       </c>
       <c r="C304" t="s">
-        <v>1310</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -9687,7 +9639,7 @@
         <v>328</v>
       </c>
       <c r="C305" t="s">
-        <v>1311</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="306" spans="1:3">
@@ -9698,7 +9650,7 @@
         <v>329</v>
       </c>
       <c r="C306" t="s">
-        <v>1312</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="307" spans="1:3">
@@ -9709,7 +9661,7 @@
         <v>330</v>
       </c>
       <c r="C307" t="s">
-        <v>1313</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="308" spans="1:3">
@@ -9720,7 +9672,7 @@
         <v>331</v>
       </c>
       <c r="C308" t="s">
-        <v>1314</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="309" spans="1:3">
@@ -9731,7 +9683,7 @@
         <v>332</v>
       </c>
       <c r="C309" t="s">
-        <v>1315</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="310" spans="1:3">
@@ -9742,7 +9694,7 @@
         <v>333</v>
       </c>
       <c r="C310" t="s">
-        <v>1316</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="311" spans="1:3">
@@ -9753,7 +9705,7 @@
         <v>334</v>
       </c>
       <c r="C311" t="s">
-        <v>1317</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="312" spans="1:3">
@@ -9764,7 +9716,7 @@
         <v>335</v>
       </c>
       <c r="C312" t="s">
-        <v>1318</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="313" spans="1:3">
@@ -9775,7 +9727,7 @@
         <v>336</v>
       </c>
       <c r="C313" t="s">
-        <v>1319</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="314" spans="1:3">
@@ -9786,7 +9738,7 @@
         <v>337</v>
       </c>
       <c r="C314" t="s">
-        <v>1320</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="315" spans="1:3">
@@ -9797,7 +9749,7 @@
         <v>338</v>
       </c>
       <c r="C315" t="s">
-        <v>1321</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="316" spans="1:3">
@@ -9808,7 +9760,7 @@
         <v>339</v>
       </c>
       <c r="C316" t="s">
-        <v>1098</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="317" spans="1:3">
@@ -9819,7 +9771,7 @@
         <v>340</v>
       </c>
       <c r="C317" t="s">
-        <v>1322</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="318" spans="1:3">
@@ -9830,7 +9782,7 @@
         <v>341</v>
       </c>
       <c r="C318" t="s">
-        <v>1323</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="319" spans="1:3">
@@ -9841,7 +9793,7 @@
         <v>342</v>
       </c>
       <c r="C319" t="s">
-        <v>1324</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="320" spans="1:3">
@@ -9852,7 +9804,7 @@
         <v>343</v>
       </c>
       <c r="C320" t="s">
-        <v>1325</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="321" spans="1:3">
@@ -9863,7 +9815,7 @@
         <v>344</v>
       </c>
       <c r="C321" t="s">
-        <v>1326</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -9874,7 +9826,7 @@
         <v>345</v>
       </c>
       <c r="C322" t="s">
-        <v>1089</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="323" spans="1:3">
@@ -9885,7 +9837,7 @@
         <v>346</v>
       </c>
       <c r="C323" t="s">
-        <v>1327</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="324" spans="1:3">
@@ -9896,7 +9848,7 @@
         <v>347</v>
       </c>
       <c r="C324" t="s">
-        <v>1328</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -9907,7 +9859,7 @@
         <v>348</v>
       </c>
       <c r="C325" t="s">
-        <v>1329</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="326" spans="1:3">
@@ -9918,7 +9870,7 @@
         <v>349</v>
       </c>
       <c r="C326" t="s">
-        <v>1330</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="327" spans="1:3">
@@ -9929,7 +9881,7 @@
         <v>350</v>
       </c>
       <c r="C327" t="s">
-        <v>1331</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="328" spans="1:3">
@@ -9940,7 +9892,7 @@
         <v>351</v>
       </c>
       <c r="C328" t="s">
-        <v>1332</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="329" spans="1:3">
@@ -9951,7 +9903,7 @@
         <v>352</v>
       </c>
       <c r="C329" t="s">
-        <v>1333</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="330" spans="1:3">
@@ -9962,7 +9914,7 @@
         <v>353</v>
       </c>
       <c r="C330" t="s">
-        <v>1334</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -9973,7 +9925,7 @@
         <v>354</v>
       </c>
       <c r="C331" t="s">
-        <v>1335</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="332" spans="1:3">
@@ -9984,7 +9936,7 @@
         <v>355</v>
       </c>
       <c r="C332" t="s">
-        <v>1336</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="333" spans="1:3">
@@ -9995,7 +9947,7 @@
         <v>356</v>
       </c>
       <c r="C333" t="s">
-        <v>1337</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="334" spans="1:3">
@@ -10006,7 +9958,7 @@
         <v>357</v>
       </c>
       <c r="C334" t="s">
-        <v>1338</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="335" spans="1:3">
@@ -10017,7 +9969,7 @@
         <v>358</v>
       </c>
       <c r="C335" t="s">
-        <v>1339</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="336" spans="1:3">
@@ -10028,7 +9980,7 @@
         <v>359</v>
       </c>
       <c r="C336" t="s">
-        <v>1340</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="337" spans="1:3">
@@ -10039,7 +9991,7 @@
         <v>360</v>
       </c>
       <c r="C337" t="s">
-        <v>1341</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="338" spans="1:3">
@@ -10050,7 +10002,7 @@
         <v>361</v>
       </c>
       <c r="C338" t="s">
-        <v>1342</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="339" spans="1:3">
@@ -10061,7 +10013,7 @@
         <v>362</v>
       </c>
       <c r="C339" t="s">
-        <v>1343</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="340" spans="1:3">
@@ -10072,7 +10024,7 @@
         <v>363</v>
       </c>
       <c r="C340" t="s">
-        <v>1344</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="341" spans="1:3">
@@ -10083,7 +10035,7 @@
         <v>364</v>
       </c>
       <c r="C341" t="s">
-        <v>1345</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -10094,7 +10046,7 @@
         <v>365</v>
       </c>
       <c r="C342" t="s">
-        <v>1346</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="343" spans="1:3">
@@ -10105,7 +10057,7 @@
         <v>366</v>
       </c>
       <c r="C343" t="s">
-        <v>1347</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="344" spans="1:3">
@@ -10116,7 +10068,7 @@
         <v>367</v>
       </c>
       <c r="C344" t="s">
-        <v>1348</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="345" spans="1:3">
@@ -10127,7 +10079,7 @@
         <v>368</v>
       </c>
       <c r="C345" t="s">
-        <v>1349</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="346" spans="1:3">
@@ -10138,7 +10090,7 @@
         <v>369</v>
       </c>
       <c r="C346" t="s">
-        <v>1350</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="347" spans="1:3">
@@ -10149,7 +10101,7 @@
         <v>370</v>
       </c>
       <c r="C347" t="s">
-        <v>1351</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="348" spans="1:3">
@@ -10160,7 +10112,7 @@
         <v>371</v>
       </c>
       <c r="C348" t="s">
-        <v>1352</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="349" spans="1:3">
@@ -10171,7 +10123,7 @@
         <v>372</v>
       </c>
       <c r="C349" t="s">
-        <v>1353</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -10182,7 +10134,7 @@
         <v>373</v>
       </c>
       <c r="C350" t="s">
-        <v>1354</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="351" spans="1:3">
@@ -10193,7 +10145,7 @@
         <v>374</v>
       </c>
       <c r="C351" t="s">
-        <v>1355</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -10204,7 +10156,7 @@
         <v>375</v>
       </c>
       <c r="C352" t="s">
-        <v>1356</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="353" spans="1:3">
@@ -10215,7 +10167,7 @@
         <v>376</v>
       </c>
       <c r="C353" t="s">
-        <v>1357</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="354" spans="1:3">
@@ -10226,7 +10178,7 @@
         <v>377</v>
       </c>
       <c r="C354" t="s">
-        <v>1358</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -10237,7 +10189,7 @@
         <v>378</v>
       </c>
       <c r="C355" t="s">
-        <v>1359</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="356" spans="1:3">
@@ -10248,7 +10200,7 @@
         <v>379</v>
       </c>
       <c r="C356" t="s">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="357" spans="1:3">
@@ -10259,7 +10211,7 @@
         <v>380</v>
       </c>
       <c r="C357" t="s">
-        <v>1361</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="358" spans="1:3">
@@ -10270,7 +10222,7 @@
         <v>381</v>
       </c>
       <c r="C358" t="s">
-        <v>1362</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="359" spans="1:3">
@@ -10281,7 +10233,7 @@
         <v>382</v>
       </c>
       <c r="C359" t="s">
-        <v>1363</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -10292,7 +10244,7 @@
         <v>383</v>
       </c>
       <c r="C360" t="s">
-        <v>1364</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="361" spans="1:3">
@@ -10303,7 +10255,7 @@
         <v>384</v>
       </c>
       <c r="C361" t="s">
-        <v>1365</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="362" spans="1:3">
@@ -10314,7 +10266,7 @@
         <v>385</v>
       </c>
       <c r="C362" t="s">
-        <v>1366</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="363" spans="1:3">
@@ -10325,7 +10277,7 @@
         <v>386</v>
       </c>
       <c r="C363" t="s">
-        <v>1367</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="364" spans="1:3">
@@ -10336,7 +10288,7 @@
         <v>387</v>
       </c>
       <c r="C364" t="s">
-        <v>1368</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="365" spans="1:3">
@@ -10347,7 +10299,7 @@
         <v>388</v>
       </c>
       <c r="C365" t="s">
-        <v>1369</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="366" spans="1:3">
@@ -10358,7 +10310,7 @@
         <v>389</v>
       </c>
       <c r="C366" t="s">
-        <v>1370</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="367" spans="1:3">
@@ -10369,7 +10321,7 @@
         <v>390</v>
       </c>
       <c r="C367" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="368" spans="1:3">
@@ -10380,7 +10332,7 @@
         <v>391</v>
       </c>
       <c r="C368" t="s">
-        <v>1372</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="369" spans="1:3">
@@ -10391,7 +10343,7 @@
         <v>392</v>
       </c>
       <c r="C369" t="s">
-        <v>1373</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="370" spans="1:3">
@@ -10402,7 +10354,7 @@
         <v>393</v>
       </c>
       <c r="C370" t="s">
-        <v>1374</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="371" spans="1:3">
@@ -10413,7 +10365,7 @@
         <v>394</v>
       </c>
       <c r="C371" t="s">
-        <v>1375</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -10424,7 +10376,7 @@
         <v>395</v>
       </c>
       <c r="C372" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="373" spans="1:3">
@@ -10435,7 +10387,7 @@
         <v>396</v>
       </c>
       <c r="C373" t="s">
-        <v>1377</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="374" spans="1:3">
@@ -10446,7 +10398,7 @@
         <v>397</v>
       </c>
       <c r="C374" t="s">
-        <v>1378</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="375" spans="1:3">
@@ -10457,7 +10409,7 @@
         <v>398</v>
       </c>
       <c r="C375" t="s">
-        <v>1379</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="376" spans="1:3">
@@ -10468,7 +10420,7 @@
         <v>399</v>
       </c>
       <c r="C376" t="s">
-        <v>1380</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="377" spans="1:3">
@@ -10479,7 +10431,7 @@
         <v>400</v>
       </c>
       <c r="C377" t="s">
-        <v>1381</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="378" spans="1:3">
@@ -10490,7 +10442,7 @@
         <v>401</v>
       </c>
       <c r="C378" t="s">
-        <v>1382</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="379" spans="1:3">
@@ -10501,7 +10453,7 @@
         <v>402</v>
       </c>
       <c r="C379" t="s">
-        <v>1383</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="380" spans="1:3">
@@ -10512,7 +10464,7 @@
         <v>403</v>
       </c>
       <c r="C380" t="s">
-        <v>1384</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="381" spans="1:3">
@@ -10523,7 +10475,7 @@
         <v>404</v>
       </c>
       <c r="C381" t="s">
-        <v>1385</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="382" spans="1:3">
@@ -10534,7 +10486,7 @@
         <v>405</v>
       </c>
       <c r="C382" t="s">
-        <v>1386</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="383" spans="1:3">
@@ -10545,7 +10497,7 @@
         <v>406</v>
       </c>
       <c r="C383" t="s">
-        <v>1387</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="384" spans="1:3">
@@ -10556,7 +10508,7 @@
         <v>407</v>
       </c>
       <c r="C384" t="s">
-        <v>1388</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="385" spans="1:3">
@@ -10567,7 +10519,7 @@
         <v>408</v>
       </c>
       <c r="C385" t="s">
-        <v>1389</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="386" spans="1:3">
@@ -10578,7 +10530,7 @@
         <v>409</v>
       </c>
       <c r="C386" t="s">
-        <v>1390</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="387" spans="1:3">
@@ -10589,7 +10541,7 @@
         <v>410</v>
       </c>
       <c r="C387" t="s">
-        <v>1391</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="388" spans="1:3">
@@ -10600,7 +10552,7 @@
         <v>411</v>
       </c>
       <c r="C388" t="s">
-        <v>1392</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="389" spans="1:3">
@@ -10611,7 +10563,7 @@
         <v>412</v>
       </c>
       <c r="C389" t="s">
-        <v>1393</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="390" spans="1:3">
@@ -10622,7 +10574,7 @@
         <v>413</v>
       </c>
       <c r="C390" t="s">
-        <v>1394</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="391" spans="1:3">
@@ -10633,7 +10585,7 @@
         <v>414</v>
       </c>
       <c r="C391" t="s">
-        <v>1395</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="392" spans="1:3">
@@ -10644,7 +10596,7 @@
         <v>415</v>
       </c>
       <c r="C392" t="s">
-        <v>1396</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="393" spans="1:3">
@@ -10655,7 +10607,7 @@
         <v>416</v>
       </c>
       <c r="C393" t="s">
-        <v>1397</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="394" spans="1:3">
@@ -10666,7 +10618,7 @@
         <v>417</v>
       </c>
       <c r="C394" t="s">
-        <v>1398</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="395" spans="1:3">
@@ -10677,7 +10629,7 @@
         <v>418</v>
       </c>
       <c r="C395" t="s">
-        <v>1399</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="396" spans="1:3">
@@ -10688,7 +10640,7 @@
         <v>419</v>
       </c>
       <c r="C396" t="s">
-        <v>1400</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="397" spans="1:3">
@@ -10699,7 +10651,7 @@
         <v>420</v>
       </c>
       <c r="C397" t="s">
-        <v>1401</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="398" spans="1:3">
@@ -10710,7 +10662,7 @@
         <v>421</v>
       </c>
       <c r="C398" t="s">
-        <v>1402</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="399" spans="1:3">
@@ -10721,7 +10673,7 @@
         <v>422</v>
       </c>
       <c r="C399" t="s">
-        <v>1403</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="400" spans="1:3">
@@ -10732,7 +10684,7 @@
         <v>423</v>
       </c>
       <c r="C400" t="s">
-        <v>1404</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="401" spans="1:3">
@@ -10743,7 +10695,7 @@
         <v>424</v>
       </c>
       <c r="C401" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="402" spans="1:3">
@@ -10754,7 +10706,7 @@
         <v>425</v>
       </c>
       <c r="C402" t="s">
-        <v>1406</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="403" spans="1:3">
@@ -10765,7 +10717,7 @@
         <v>426</v>
       </c>
       <c r="C403" t="s">
-        <v>1407</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="404" spans="1:3">
@@ -10776,7 +10728,7 @@
         <v>427</v>
       </c>
       <c r="C404" t="s">
-        <v>1408</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="405" spans="1:3">
@@ -10787,7 +10739,7 @@
         <v>428</v>
       </c>
       <c r="C405" t="s">
-        <v>1409</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="406" spans="1:3">
@@ -10798,7 +10750,7 @@
         <v>429</v>
       </c>
       <c r="C406" t="s">
-        <v>1410</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="407" spans="1:3">
@@ -10809,7 +10761,7 @@
         <v>430</v>
       </c>
       <c r="C407" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="408" spans="1:3">
@@ -10820,7 +10772,7 @@
         <v>431</v>
       </c>
       <c r="C408" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="409" spans="1:3">
@@ -10831,7 +10783,7 @@
         <v>432</v>
       </c>
       <c r="C409" t="s">
-        <v>1413</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="410" spans="1:3">
@@ -10842,7 +10794,7 @@
         <v>433</v>
       </c>
       <c r="C410" t="s">
-        <v>1414</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="411" spans="1:3">
@@ -10853,7 +10805,7 @@
         <v>434</v>
       </c>
       <c r="C411" t="s">
-        <v>1415</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="412" spans="1:3">
@@ -10864,7 +10816,7 @@
         <v>435</v>
       </c>
       <c r="C412" t="s">
-        <v>1416</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="413" spans="1:3">
@@ -10875,7 +10827,7 @@
         <v>436</v>
       </c>
       <c r="C413" t="s">
-        <v>1417</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="414" spans="1:3">
@@ -10886,7 +10838,7 @@
         <v>437</v>
       </c>
       <c r="C414" t="s">
-        <v>1418</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="415" spans="1:3">
@@ -10897,7 +10849,7 @@
         <v>438</v>
       </c>
       <c r="C415" t="s">
-        <v>1419</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="416" spans="1:3">
@@ -10908,7 +10860,7 @@
         <v>439</v>
       </c>
       <c r="C416" t="s">
-        <v>1420</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="417" spans="1:3">
@@ -10919,7 +10871,7 @@
         <v>440</v>
       </c>
       <c r="C417" t="s">
-        <v>1421</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="418" spans="1:3">
@@ -10930,7 +10882,7 @@
         <v>441</v>
       </c>
       <c r="C418" t="s">
-        <v>1422</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="419" spans="1:3">
@@ -10941,7 +10893,7 @@
         <v>442</v>
       </c>
       <c r="C419" t="s">
-        <v>1423</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="420" spans="1:3">
@@ -10952,7 +10904,7 @@
         <v>443</v>
       </c>
       <c r="C420" t="s">
-        <v>1424</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="421" spans="1:3">
@@ -10963,7 +10915,7 @@
         <v>444</v>
       </c>
       <c r="C421" t="s">
-        <v>1425</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="422" spans="1:3">
@@ -10974,7 +10926,7 @@
         <v>445</v>
       </c>
       <c r="C422" t="s">
-        <v>1426</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="423" spans="1:3">
@@ -10985,7 +10937,7 @@
         <v>446</v>
       </c>
       <c r="C423" t="s">
-        <v>1427</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="424" spans="1:3">
@@ -10996,7 +10948,7 @@
         <v>447</v>
       </c>
       <c r="C424" t="s">
-        <v>1428</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="425" spans="1:3">
@@ -11007,7 +10959,7 @@
         <v>448</v>
       </c>
       <c r="C425" t="s">
-        <v>1429</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="426" spans="1:3">
@@ -11018,7 +10970,7 @@
         <v>449</v>
       </c>
       <c r="C426" t="s">
-        <v>1430</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="427" spans="1:3">
@@ -11029,7 +10981,7 @@
         <v>450</v>
       </c>
       <c r="C427" t="s">
-        <v>1431</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="428" spans="1:3">
@@ -11040,7 +10992,7 @@
         <v>451</v>
       </c>
       <c r="C428" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="429" spans="1:3">
@@ -11051,7 +11003,7 @@
         <v>452</v>
       </c>
       <c r="C429" t="s">
-        <v>1433</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="430" spans="1:3">
@@ -11062,7 +11014,7 @@
         <v>453</v>
       </c>
       <c r="C430" t="s">
-        <v>1434</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="431" spans="1:3">
@@ -11073,7 +11025,7 @@
         <v>454</v>
       </c>
       <c r="C431" t="s">
-        <v>1435</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="432" spans="1:3">
@@ -11084,7 +11036,7 @@
         <v>455</v>
       </c>
       <c r="C432" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="433" spans="1:3">
@@ -11095,7 +11047,7 @@
         <v>456</v>
       </c>
       <c r="C433" t="s">
-        <v>1437</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="434" spans="1:3">
@@ -11106,7 +11058,7 @@
         <v>457</v>
       </c>
       <c r="C434" t="s">
-        <v>1438</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="435" spans="1:3">
@@ -11117,7 +11069,7 @@
         <v>458</v>
       </c>
       <c r="C435" t="s">
-        <v>1439</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="436" spans="1:3">
@@ -11128,7 +11080,7 @@
         <v>459</v>
       </c>
       <c r="C436" t="s">
-        <v>1440</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="437" spans="1:3">
@@ -11139,7 +11091,7 @@
         <v>460</v>
       </c>
       <c r="C437" t="s">
-        <v>1409</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="438" spans="1:3">
@@ -11150,7 +11102,7 @@
         <v>461</v>
       </c>
       <c r="C438" t="s">
-        <v>1401</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="439" spans="1:3">
@@ -11161,7 +11113,7 @@
         <v>462</v>
       </c>
       <c r="C439" t="s">
-        <v>1441</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="440" spans="1:3">
@@ -11172,7 +11124,7 @@
         <v>463</v>
       </c>
       <c r="C440" t="s">
-        <v>1442</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="441" spans="1:3">
@@ -11183,7 +11135,7 @@
         <v>464</v>
       </c>
       <c r="C441" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="442" spans="1:3">
@@ -11194,7 +11146,7 @@
         <v>465</v>
       </c>
       <c r="C442" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="443" spans="1:3">
@@ -11205,7 +11157,7 @@
         <v>466</v>
       </c>
       <c r="C443" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="444" spans="1:3">
@@ -11216,7 +11168,7 @@
         <v>467</v>
       </c>
       <c r="C444" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="445" spans="1:3">
@@ -11227,7 +11179,7 @@
         <v>468</v>
       </c>
       <c r="C445" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="446" spans="1:3">
@@ -11238,7 +11190,7 @@
         <v>469</v>
       </c>
       <c r="C446" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="447" spans="1:3">
@@ -11249,7 +11201,7 @@
         <v>470</v>
       </c>
       <c r="C447" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="448" spans="1:3">
@@ -11260,7 +11212,7 @@
         <v>471</v>
       </c>
       <c r="C448" t="s">
-        <v>1450</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="449" spans="1:3">
@@ -11271,7 +11223,7 @@
         <v>472</v>
       </c>
       <c r="C449" t="s">
-        <v>1451</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="450" spans="1:3">
@@ -11282,7 +11234,7 @@
         <v>473</v>
       </c>
       <c r="C450" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="451" spans="1:3">
@@ -11293,7 +11245,7 @@
         <v>474</v>
       </c>
       <c r="C451" t="s">
-        <v>1453</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="452" spans="1:3">
@@ -11304,7 +11256,7 @@
         <v>475</v>
       </c>
       <c r="C452" t="s">
-        <v>1454</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="453" spans="1:3">
@@ -11315,7 +11267,7 @@
         <v>476</v>
       </c>
       <c r="C453" t="s">
-        <v>1455</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="454" spans="1:3">
@@ -11326,7 +11278,7 @@
         <v>477</v>
       </c>
       <c r="C454" t="s">
-        <v>1456</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="455" spans="1:3">
@@ -11337,7 +11289,7 @@
         <v>478</v>
       </c>
       <c r="C455" t="s">
-        <v>1457</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="456" spans="1:3">
@@ -11348,7 +11300,7 @@
         <v>479</v>
       </c>
       <c r="C456" t="s">
-        <v>1458</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="457" spans="1:3">
@@ -11359,7 +11311,7 @@
         <v>480</v>
       </c>
       <c r="C457" t="s">
-        <v>1459</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="458" spans="1:3">
@@ -11370,7 +11322,7 @@
         <v>481</v>
       </c>
       <c r="C458" t="s">
-        <v>1460</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="459" spans="1:3">
@@ -11381,7 +11333,7 @@
         <v>482</v>
       </c>
       <c r="C459" t="s">
-        <v>1461</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="460" spans="1:3">
@@ -11392,7 +11344,7 @@
         <v>483</v>
       </c>
       <c r="C460" t="s">
-        <v>1462</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="461" spans="1:3">
@@ -11403,7 +11355,7 @@
         <v>484</v>
       </c>
       <c r="C461" t="s">
-        <v>1463</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="462" spans="1:3">
@@ -11414,7 +11366,7 @@
         <v>485</v>
       </c>
       <c r="C462" t="s">
-        <v>1464</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="463" spans="1:3">
@@ -11425,7 +11377,7 @@
         <v>486</v>
       </c>
       <c r="C463" t="s">
-        <v>1465</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="464" spans="1:3">
@@ -11436,7 +11388,7 @@
         <v>487</v>
       </c>
       <c r="C464" t="s">
-        <v>1466</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="465" spans="1:3">
@@ -11447,7 +11399,7 @@
         <v>488</v>
       </c>
       <c r="C465" t="s">
-        <v>1467</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="466" spans="1:3">
@@ -11458,7 +11410,7 @@
         <v>489</v>
       </c>
       <c r="C466" t="s">
-        <v>1468</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="467" spans="1:3">
@@ -11469,7 +11421,7 @@
         <v>490</v>
       </c>
       <c r="C467" t="s">
-        <v>1469</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="468" spans="1:3">
@@ -11480,7 +11432,7 @@
         <v>491</v>
       </c>
       <c r="C468" t="s">
-        <v>1470</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="469" spans="1:3">
@@ -11491,7 +11443,7 @@
         <v>492</v>
       </c>
       <c r="C469" t="s">
-        <v>1471</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="470" spans="1:3">
@@ -11502,7 +11454,7 @@
         <v>493</v>
       </c>
       <c r="C470" t="s">
-        <v>1472</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="471" spans="1:3">
@@ -11513,7 +11465,7 @@
         <v>494</v>
       </c>
       <c r="C471" t="s">
-        <v>1473</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="472" spans="1:3">
@@ -11524,7 +11476,7 @@
         <v>495</v>
       </c>
       <c r="C472" t="s">
-        <v>1474</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="473" spans="1:3">
@@ -11535,7 +11487,7 @@
         <v>496</v>
       </c>
       <c r="C473" t="s">
-        <v>1475</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="474" spans="1:3">
@@ -11546,7 +11498,7 @@
         <v>497</v>
       </c>
       <c r="C474" t="s">
-        <v>1476</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="475" spans="1:3">
@@ -11557,7 +11509,7 @@
         <v>498</v>
       </c>
       <c r="C475" t="s">
-        <v>1477</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="476" spans="1:3">
@@ -11568,7 +11520,7 @@
         <v>499</v>
       </c>
       <c r="C476" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="477" spans="1:3">
@@ -11579,7 +11531,7 @@
         <v>500</v>
       </c>
       <c r="C477" t="s">
-        <v>1479</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="478" spans="1:3">
@@ -11590,7 +11542,7 @@
         <v>501</v>
       </c>
       <c r="C478" t="s">
-        <v>1480</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="479" spans="1:3">
@@ -11601,7 +11553,7 @@
         <v>502</v>
       </c>
       <c r="C479" t="s">
-        <v>1481</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="480" spans="1:3">
@@ -11612,7 +11564,7 @@
         <v>503</v>
       </c>
       <c r="C480" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="481" spans="1:3">
@@ -11623,7 +11575,7 @@
         <v>504</v>
       </c>
       <c r="C481" t="s">
-        <v>1483</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="482" spans="1:3">
@@ -11634,7 +11586,7 @@
         <v>505</v>
       </c>
       <c r="C482" t="s">
-        <v>1484</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="483" spans="1:3">
@@ -11645,7 +11597,7 @@
         <v>506</v>
       </c>
       <c r="C483" t="s">
-        <v>1485</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="484" spans="1:3">
@@ -11656,7 +11608,7 @@
         <v>507</v>
       </c>
       <c r="C484" t="s">
-        <v>1486</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="485" spans="1:3">
@@ -11667,7 +11619,7 @@
         <v>508</v>
       </c>
       <c r="C485" t="s">
-        <v>1487</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="486" spans="1:3">
@@ -11678,7 +11630,7 @@
         <v>509</v>
       </c>
       <c r="C486" t="s">
-        <v>1488</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="487" spans="1:3">
@@ -11689,7 +11641,7 @@
         <v>510</v>
       </c>
       <c r="C487" t="s">
-        <v>1489</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="488" spans="1:3">
@@ -11700,7 +11652,7 @@
         <v>511</v>
       </c>
       <c r="C488" t="s">
-        <v>1490</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="489" spans="1:3">
@@ -11711,7 +11663,7 @@
         <v>512</v>
       </c>
       <c r="C489" t="s">
-        <v>1491</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="490" spans="1:3">
@@ -11722,7 +11674,7 @@
         <v>513</v>
       </c>
       <c r="C490" t="s">
-        <v>1492</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="491" spans="1:3">
@@ -11733,7 +11685,7 @@
         <v>514</v>
       </c>
       <c r="C491" t="s">
-        <v>1493</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="492" spans="1:3">
@@ -11744,7 +11696,7 @@
         <v>515</v>
       </c>
       <c r="C492" t="s">
-        <v>1494</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="493" spans="1:3">
@@ -11755,7 +11707,7 @@
         <v>516</v>
       </c>
       <c r="C493" t="s">
-        <v>1495</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="494" spans="1:3">
@@ -11766,7 +11718,7 @@
         <v>517</v>
       </c>
       <c r="C494" t="s">
-        <v>1496</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="495" spans="1:3">
@@ -11777,7 +11729,7 @@
         <v>518</v>
       </c>
       <c r="C495" t="s">
-        <v>1497</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="496" spans="1:3">
@@ -11788,7 +11740,7 @@
         <v>519</v>
       </c>
       <c r="C496" t="s">
-        <v>1498</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="497" spans="1:3">
@@ -11799,7 +11751,7 @@
         <v>520</v>
       </c>
       <c r="C497" t="s">
-        <v>1499</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="498" spans="1:3">
@@ -11810,7 +11762,7 @@
         <v>521</v>
       </c>
       <c r="C498" t="s">
-        <v>1500</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="499" spans="1:3">
@@ -11821,7 +11773,7 @@
         <v>522</v>
       </c>
       <c r="C499" t="s">
-        <v>1501</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="500" spans="1:3">
@@ -11832,7 +11784,7 @@
         <v>523</v>
       </c>
       <c r="C500" t="s">
-        <v>1502</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="501" spans="1:3">
@@ -11843,7 +11795,7 @@
         <v>524</v>
       </c>
       <c r="C501" t="s">
-        <v>1503</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="502" spans="1:3">
@@ -11854,7 +11806,7 @@
         <v>525</v>
       </c>
       <c r="C502" t="s">
-        <v>1504</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="503" spans="1:3">
@@ -11865,7 +11817,7 @@
         <v>526</v>
       </c>
       <c r="C503" t="s">
-        <v>1505</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="504" spans="1:3">
@@ -11876,7 +11828,7 @@
         <v>527</v>
       </c>
       <c r="C504" t="s">
-        <v>1506</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="505" spans="1:3">
@@ -11887,7 +11839,7 @@
         <v>528</v>
       </c>
       <c r="C505" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="506" spans="1:3">
@@ -11898,7 +11850,7 @@
         <v>529</v>
       </c>
       <c r="C506" t="s">
-        <v>1508</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="507" spans="1:3">
@@ -11909,7 +11861,7 @@
         <v>530</v>
       </c>
       <c r="C507" t="s">
-        <v>1509</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="508" spans="1:3">
@@ -11920,7 +11872,7 @@
         <v>531</v>
       </c>
       <c r="C508" t="s">
-        <v>1510</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="509" spans="1:3">
@@ -11931,7 +11883,7 @@
         <v>532</v>
       </c>
       <c r="C509" t="s">
-        <v>1511</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="510" spans="1:3">
@@ -11942,18 +11894,18 @@
         <v>533</v>
       </c>
       <c r="C510" t="s">
-        <v>1512</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="511" spans="1:3">
       <c r="A511" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B511" t="s">
         <v>534</v>
       </c>
       <c r="C511" t="s">
-        <v>1513</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="512" spans="1:3">
@@ -11964,7 +11916,7 @@
         <v>535</v>
       </c>
       <c r="C512" t="s">
-        <v>1514</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="513" spans="1:3">
@@ -11975,7 +11927,7 @@
         <v>536</v>
       </c>
       <c r="C513" t="s">
-        <v>1515</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="514" spans="1:3">
@@ -11986,7 +11938,7 @@
         <v>537</v>
       </c>
       <c r="C514" t="s">
-        <v>1516</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="515" spans="1:3">
@@ -11997,7 +11949,7 @@
         <v>538</v>
       </c>
       <c r="C515" t="s">
-        <v>1517</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="516" spans="1:3">
@@ -12008,7 +11960,7 @@
         <v>539</v>
       </c>
       <c r="C516" t="s">
-        <v>1518</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="517" spans="1:3">
@@ -12019,7 +11971,7 @@
         <v>540</v>
       </c>
       <c r="C517" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="518" spans="1:3">
@@ -12030,7 +11982,7 @@
         <v>541</v>
       </c>
       <c r="C518" t="s">
-        <v>1520</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="519" spans="1:3">
@@ -12041,7 +11993,7 @@
         <v>542</v>
       </c>
       <c r="C519" t="s">
-        <v>1521</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="520" spans="1:3">
@@ -12052,7 +12004,7 @@
         <v>543</v>
       </c>
       <c r="C520" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="521" spans="1:3">
@@ -12063,7 +12015,7 @@
         <v>544</v>
       </c>
       <c r="C521" t="s">
-        <v>1523</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="522" spans="1:3">
@@ -12074,7 +12026,7 @@
         <v>545</v>
       </c>
       <c r="C522" t="s">
-        <v>1524</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="523" spans="1:3">
@@ -12085,7 +12037,7 @@
         <v>546</v>
       </c>
       <c r="C523" t="s">
-        <v>1525</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="524" spans="1:3">
@@ -12096,7 +12048,7 @@
         <v>547</v>
       </c>
       <c r="C524" t="s">
-        <v>1526</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="525" spans="1:3">
@@ -12107,7 +12059,7 @@
         <v>548</v>
       </c>
       <c r="C525" t="s">
-        <v>1527</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="526" spans="1:3">
@@ -12118,7 +12070,7 @@
         <v>549</v>
       </c>
       <c r="C526" t="s">
-        <v>1528</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="527" spans="1:3">
@@ -12129,7 +12081,7 @@
         <v>550</v>
       </c>
       <c r="C527" t="s">
-        <v>1529</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="528" spans="1:3">
@@ -12140,7 +12092,7 @@
         <v>551</v>
       </c>
       <c r="C528" t="s">
-        <v>1530</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="529" spans="1:3">
@@ -12151,7 +12103,7 @@
         <v>552</v>
       </c>
       <c r="C529" t="s">
-        <v>1531</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="530" spans="1:3">
@@ -12162,7 +12114,7 @@
         <v>553</v>
       </c>
       <c r="C530" t="s">
-        <v>1532</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="531" spans="1:3">
@@ -12173,7 +12125,7 @@
         <v>554</v>
       </c>
       <c r="C531" t="s">
-        <v>1533</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="532" spans="1:3">
@@ -12184,7 +12136,7 @@
         <v>555</v>
       </c>
       <c r="C532" t="s">
-        <v>1534</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="533" spans="1:3">
@@ -12195,7 +12147,7 @@
         <v>556</v>
       </c>
       <c r="C533" t="s">
-        <v>1535</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="534" spans="1:3">
@@ -12206,7 +12158,7 @@
         <v>557</v>
       </c>
       <c r="C534" t="s">
-        <v>1536</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="535" spans="1:3">
@@ -12217,7 +12169,7 @@
         <v>558</v>
       </c>
       <c r="C535" t="s">
-        <v>1537</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="536" spans="1:3">
@@ -12228,7 +12180,7 @@
         <v>559</v>
       </c>
       <c r="C536" t="s">
-        <v>1538</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="537" spans="1:3">
@@ -12239,7 +12191,7 @@
         <v>560</v>
       </c>
       <c r="C537" t="s">
-        <v>1539</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="538" spans="1:3">
@@ -12250,7 +12202,7 @@
         <v>561</v>
       </c>
       <c r="C538" t="s">
-        <v>1540</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="539" spans="1:3">
@@ -12261,7 +12213,7 @@
         <v>562</v>
       </c>
       <c r="C539" t="s">
-        <v>1541</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="540" spans="1:3">
@@ -12272,7 +12224,7 @@
         <v>563</v>
       </c>
       <c r="C540" t="s">
-        <v>1542</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="541" spans="1:3">
@@ -12283,7 +12235,7 @@
         <v>564</v>
       </c>
       <c r="C541" t="s">
-        <v>1543</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="542" spans="1:3">
@@ -12294,7 +12246,7 @@
         <v>565</v>
       </c>
       <c r="C542" t="s">
-        <v>1544</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="543" spans="1:3">
@@ -12305,7 +12257,7 @@
         <v>566</v>
       </c>
       <c r="C543" t="s">
-        <v>1545</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="544" spans="1:3">
@@ -12316,7 +12268,7 @@
         <v>567</v>
       </c>
       <c r="C544" t="s">
-        <v>1546</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="545" spans="1:3">
@@ -12327,7 +12279,7 @@
         <v>568</v>
       </c>
       <c r="C545" t="s">
-        <v>1547</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="546" spans="1:3">
@@ -12338,172 +12290,172 @@
         <v>569</v>
       </c>
       <c r="C546" t="s">
-        <v>1548</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="547" spans="1:3">
       <c r="A547" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B547" t="s">
         <v>570</v>
       </c>
       <c r="C547" t="s">
-        <v>1549</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="548" spans="1:3">
       <c r="A548" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B548" t="s">
         <v>571</v>
       </c>
       <c r="C548" t="s">
-        <v>1519</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="549" spans="1:3">
       <c r="A549" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B549" t="s">
         <v>572</v>
       </c>
       <c r="C549" t="s">
-        <v>1550</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="550" spans="1:3">
       <c r="A550" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B550" t="s">
         <v>573</v>
       </c>
       <c r="C550" t="s">
-        <v>1551</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="551" spans="1:3">
       <c r="A551" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B551" t="s">
         <v>574</v>
       </c>
       <c r="C551" t="s">
-        <v>1552</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="552" spans="1:3">
       <c r="A552" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B552" t="s">
         <v>575</v>
       </c>
       <c r="C552" t="s">
-        <v>1553</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="553" spans="1:3">
       <c r="A553" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B553" t="s">
         <v>576</v>
       </c>
       <c r="C553" t="s">
-        <v>1554</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="554" spans="1:3">
       <c r="A554" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B554" t="s">
         <v>577</v>
       </c>
       <c r="C554" t="s">
-        <v>1555</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="555" spans="1:3">
       <c r="A555" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B555" t="s">
         <v>578</v>
       </c>
       <c r="C555" t="s">
-        <v>1556</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="556" spans="1:3">
       <c r="A556" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B556" t="s">
         <v>579</v>
       </c>
       <c r="C556" t="s">
-        <v>1557</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="557" spans="1:3">
       <c r="A557" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B557" t="s">
         <v>580</v>
       </c>
       <c r="C557" t="s">
-        <v>1558</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="558" spans="1:3">
       <c r="A558" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B558" t="s">
         <v>581</v>
       </c>
       <c r="C558" t="s">
-        <v>1559</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="559" spans="1:3">
       <c r="A559" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B559" t="s">
         <v>582</v>
       </c>
       <c r="C559" t="s">
-        <v>1560</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="560" spans="1:3">
       <c r="A560" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B560" t="s">
         <v>583</v>
       </c>
       <c r="C560" t="s">
-        <v>1561</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="561" spans="1:3">
       <c r="A561" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B561" t="s">
         <v>584</v>
       </c>
       <c r="C561" t="s">
-        <v>1562</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="562" spans="1:3">
@@ -12514,7 +12466,7 @@
         <v>585</v>
       </c>
       <c r="C562" t="s">
-        <v>1563</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="563" spans="1:3">
@@ -12525,7 +12477,7 @@
         <v>586</v>
       </c>
       <c r="C563" t="s">
-        <v>1564</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="564" spans="1:3">
@@ -12536,7 +12488,7 @@
         <v>587</v>
       </c>
       <c r="C564" t="s">
-        <v>1565</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="565" spans="1:3">
@@ -12547,7 +12499,7 @@
         <v>588</v>
       </c>
       <c r="C565" t="s">
-        <v>1566</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="566" spans="1:3">
@@ -12558,7 +12510,7 @@
         <v>589</v>
       </c>
       <c r="C566" t="s">
-        <v>1567</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="567" spans="1:3">
@@ -12569,7 +12521,7 @@
         <v>590</v>
       </c>
       <c r="C567" t="s">
-        <v>1568</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="568" spans="1:3">
@@ -12580,7 +12532,7 @@
         <v>591</v>
       </c>
       <c r="C568" t="s">
-        <v>1569</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="569" spans="1:3">
@@ -12591,7 +12543,7 @@
         <v>592</v>
       </c>
       <c r="C569" t="s">
-        <v>1570</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="570" spans="1:3">
@@ -12602,7 +12554,7 @@
         <v>593</v>
       </c>
       <c r="C570" t="s">
-        <v>1571</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="571" spans="1:3">
@@ -12613,7 +12565,7 @@
         <v>594</v>
       </c>
       <c r="C571" t="s">
-        <v>1572</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="572" spans="1:3">
@@ -12624,7 +12576,7 @@
         <v>595</v>
       </c>
       <c r="C572" t="s">
-        <v>1573</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="573" spans="1:3">
@@ -12635,7 +12587,7 @@
         <v>596</v>
       </c>
       <c r="C573" t="s">
-        <v>1574</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="574" spans="1:3">
@@ -12646,7 +12598,7 @@
         <v>597</v>
       </c>
       <c r="C574" t="s">
-        <v>1575</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="575" spans="1:3">
@@ -12657,7 +12609,7 @@
         <v>598</v>
       </c>
       <c r="C575" t="s">
-        <v>1576</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="576" spans="1:3">
@@ -12668,7 +12620,7 @@
         <v>599</v>
       </c>
       <c r="C576" t="s">
-        <v>1577</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="577" spans="1:3">
@@ -12679,7 +12631,7 @@
         <v>600</v>
       </c>
       <c r="C577" t="s">
-        <v>1578</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="578" spans="1:3">
@@ -12690,7 +12642,7 @@
         <v>601</v>
       </c>
       <c r="C578" t="s">
-        <v>1579</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="579" spans="1:3">
@@ -12701,95 +12653,95 @@
         <v>602</v>
       </c>
       <c r="C579" t="s">
-        <v>1580</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="580" spans="1:3">
       <c r="A580" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B580" t="s">
         <v>603</v>
       </c>
       <c r="C580" t="s">
-        <v>1581</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="581" spans="1:3">
       <c r="A581" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B581" t="s">
         <v>604</v>
       </c>
       <c r="C581" t="s">
-        <v>1582</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="582" spans="1:3">
       <c r="A582" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B582" t="s">
         <v>605</v>
       </c>
       <c r="C582" t="s">
-        <v>1583</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="583" spans="1:3">
       <c r="A583" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B583" t="s">
         <v>606</v>
       </c>
       <c r="C583" t="s">
-        <v>1584</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="584" spans="1:3">
       <c r="A584" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B584" t="s">
         <v>607</v>
       </c>
       <c r="C584" t="s">
-        <v>1585</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="585" spans="1:3">
       <c r="A585" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B585" t="s">
         <v>608</v>
       </c>
       <c r="C585" t="s">
-        <v>1586</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="586" spans="1:3">
       <c r="A586" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B586" t="s">
         <v>609</v>
       </c>
       <c r="C586" t="s">
-        <v>1587</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="587" spans="1:3">
       <c r="A587" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B587" t="s">
         <v>610</v>
       </c>
       <c r="C587" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="588" spans="1:3">
@@ -12800,7 +12752,7 @@
         <v>611</v>
       </c>
       <c r="C588" t="s">
-        <v>1589</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="589" spans="1:3">
@@ -12811,7 +12763,7 @@
         <v>612</v>
       </c>
       <c r="C589" t="s">
-        <v>1590</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="590" spans="1:3">
@@ -12822,95 +12774,95 @@
         <v>613</v>
       </c>
       <c r="C590" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="591" spans="1:3">
       <c r="A591" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B591" t="s">
         <v>614</v>
       </c>
       <c r="C591" t="s">
-        <v>1592</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="592" spans="1:3">
       <c r="A592" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B592" t="s">
         <v>615</v>
       </c>
       <c r="C592" t="s">
-        <v>1593</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="593" spans="1:3">
       <c r="A593" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B593" t="s">
         <v>616</v>
       </c>
       <c r="C593" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="594" spans="1:3">
       <c r="A594" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B594" t="s">
         <v>617</v>
       </c>
       <c r="C594" t="s">
-        <v>1595</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="595" spans="1:3">
       <c r="A595" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B595" t="s">
         <v>618</v>
       </c>
       <c r="C595" t="s">
-        <v>1596</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="596" spans="1:3">
       <c r="A596" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B596" t="s">
         <v>619</v>
       </c>
       <c r="C596" t="s">
-        <v>1597</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="597" spans="1:3">
       <c r="A597" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B597" t="s">
         <v>620</v>
       </c>
       <c r="C597" t="s">
-        <v>1598</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="598" spans="1:3">
       <c r="A598" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B598" t="s">
         <v>621</v>
       </c>
       <c r="C598" t="s">
-        <v>1599</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="599" spans="1:3">
@@ -12921,7 +12873,7 @@
         <v>622</v>
       </c>
       <c r="C599" t="s">
-        <v>1600</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="600" spans="1:3">
@@ -12932,7 +12884,7 @@
         <v>623</v>
       </c>
       <c r="C600" t="s">
-        <v>1601</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="601" spans="1:3">
@@ -12943,7 +12895,7 @@
         <v>624</v>
       </c>
       <c r="C601" t="s">
-        <v>1602</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="602" spans="1:3">
@@ -12954,7 +12906,7 @@
         <v>625</v>
       </c>
       <c r="C602" t="s">
-        <v>1603</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="603" spans="1:3">
@@ -12965,7 +12917,7 @@
         <v>626</v>
       </c>
       <c r="C603" t="s">
-        <v>1604</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="604" spans="1:3">
@@ -12976,7 +12928,7 @@
         <v>627</v>
       </c>
       <c r="C604" t="s">
-        <v>1605</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="605" spans="1:3">
@@ -12987,7 +12939,7 @@
         <v>628</v>
       </c>
       <c r="C605" t="s">
-        <v>1606</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="606" spans="1:3">
@@ -12998,7 +12950,7 @@
         <v>629</v>
       </c>
       <c r="C606" t="s">
-        <v>1607</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="607" spans="1:3">
@@ -13009,7 +12961,7 @@
         <v>630</v>
       </c>
       <c r="C607" t="s">
-        <v>1608</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="608" spans="1:3">
@@ -13020,7 +12972,7 @@
         <v>631</v>
       </c>
       <c r="C608" t="s">
-        <v>1609</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="609" spans="1:3">
@@ -13031,7 +12983,7 @@
         <v>632</v>
       </c>
       <c r="C609" t="s">
-        <v>1610</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="610" spans="1:3">
@@ -13042,7 +12994,7 @@
         <v>633</v>
       </c>
       <c r="C610" t="s">
-        <v>1611</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="611" spans="1:3">
@@ -13053,7 +13005,7 @@
         <v>634</v>
       </c>
       <c r="C611" t="s">
-        <v>1612</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="612" spans="1:3">
@@ -13064,7 +13016,7 @@
         <v>635</v>
       </c>
       <c r="C612" t="s">
-        <v>1613</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="613" spans="1:3">
@@ -13075,95 +13027,95 @@
         <v>636</v>
       </c>
       <c r="C613" t="s">
-        <v>1614</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="614" spans="1:3">
       <c r="A614" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B614" t="s">
         <v>637</v>
       </c>
       <c r="C614" t="s">
-        <v>1615</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="615" spans="1:3">
       <c r="A615" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B615" t="s">
         <v>638</v>
       </c>
       <c r="C615" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="616" spans="1:3">
       <c r="A616" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B616" t="s">
         <v>639</v>
       </c>
       <c r="C616" t="s">
-        <v>1617</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="617" spans="1:3">
       <c r="A617" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B617" t="s">
         <v>640</v>
       </c>
       <c r="C617" t="s">
-        <v>1618</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="618" spans="1:3">
       <c r="A618" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B618" t="s">
         <v>641</v>
       </c>
       <c r="C618" t="s">
-        <v>1619</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="619" spans="1:3">
       <c r="A619" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B619" t="s">
         <v>642</v>
       </c>
       <c r="C619" t="s">
-        <v>1620</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="620" spans="1:3">
       <c r="A620" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B620" t="s">
         <v>643</v>
       </c>
       <c r="C620" t="s">
-        <v>1621</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="621" spans="1:3">
       <c r="A621" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B621" t="s">
         <v>644</v>
       </c>
       <c r="C621" t="s">
-        <v>1622</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="622" spans="1:3">
@@ -13174,7 +13126,7 @@
         <v>645</v>
       </c>
       <c r="C622" t="s">
-        <v>1623</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="623" spans="1:3">
@@ -13185,7 +13137,7 @@
         <v>646</v>
       </c>
       <c r="C623" t="s">
-        <v>1624</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="624" spans="1:3">
@@ -13196,7 +13148,7 @@
         <v>647</v>
       </c>
       <c r="C624" t="s">
-        <v>1625</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="625" spans="1:3">
@@ -13207,7 +13159,7 @@
         <v>648</v>
       </c>
       <c r="C625" t="s">
-        <v>1626</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="626" spans="1:3">
@@ -13218,7 +13170,7 @@
         <v>649</v>
       </c>
       <c r="C626" t="s">
-        <v>1627</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="627" spans="1:3">
@@ -13229,7 +13181,7 @@
         <v>650</v>
       </c>
       <c r="C627" t="s">
-        <v>1628</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="628" spans="1:3">
@@ -13240,7 +13192,7 @@
         <v>651</v>
       </c>
       <c r="C628" t="s">
-        <v>1629</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="629" spans="1:3">
@@ -13251,95 +13203,95 @@
         <v>652</v>
       </c>
       <c r="C629" t="s">
-        <v>1630</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="630" spans="1:3">
       <c r="A630" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B630" t="s">
         <v>653</v>
       </c>
       <c r="C630" t="s">
-        <v>1631</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="631" spans="1:3">
       <c r="A631" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B631" t="s">
         <v>654</v>
       </c>
       <c r="C631" t="s">
-        <v>1632</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="632" spans="1:3">
       <c r="A632" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B632" t="s">
         <v>655</v>
       </c>
       <c r="C632" t="s">
-        <v>1633</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="633" spans="1:3">
       <c r="A633" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B633" t="s">
         <v>656</v>
       </c>
       <c r="C633" t="s">
-        <v>1634</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="634" spans="1:3">
       <c r="A634" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B634" t="s">
         <v>657</v>
       </c>
       <c r="C634" t="s">
-        <v>1635</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="635" spans="1:3">
       <c r="A635" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B635" t="s">
         <v>658</v>
       </c>
       <c r="C635" t="s">
-        <v>1636</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="636" spans="1:3">
       <c r="A636" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B636" t="s">
         <v>659</v>
       </c>
       <c r="C636" t="s">
-        <v>1637</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="637" spans="1:3">
       <c r="A637" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B637" t="s">
         <v>660</v>
       </c>
       <c r="C637" t="s">
-        <v>1097</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="638" spans="1:3">
@@ -13350,7 +13302,7 @@
         <v>661</v>
       </c>
       <c r="C638" t="s">
-        <v>1638</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="639" spans="1:3">
@@ -13361,7 +13313,7 @@
         <v>662</v>
       </c>
       <c r="C639" t="s">
-        <v>1639</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="640" spans="1:3">
@@ -13372,7 +13324,7 @@
         <v>663</v>
       </c>
       <c r="C640" t="s">
-        <v>1640</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="641" spans="1:3">
@@ -13383,7 +13335,7 @@
         <v>664</v>
       </c>
       <c r="C641" t="s">
-        <v>1641</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="642" spans="1:3">
@@ -13394,7 +13346,7 @@
         <v>665</v>
       </c>
       <c r="C642" t="s">
-        <v>1642</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="643" spans="1:3">
@@ -13405,7 +13357,7 @@
         <v>666</v>
       </c>
       <c r="C643" t="s">
-        <v>1643</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="644" spans="1:3">
@@ -13416,7 +13368,7 @@
         <v>667</v>
       </c>
       <c r="C644" t="s">
-        <v>1644</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="645" spans="1:3">
@@ -13427,7 +13379,7 @@
         <v>668</v>
       </c>
       <c r="C645" t="s">
-        <v>1645</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="646" spans="1:3">
@@ -13438,7 +13390,7 @@
         <v>669</v>
       </c>
       <c r="C646" t="s">
-        <v>1646</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="647" spans="1:3">
@@ -13449,7 +13401,7 @@
         <v>670</v>
       </c>
       <c r="C647" t="s">
-        <v>1647</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="648" spans="1:3">
@@ -13460,7 +13412,7 @@
         <v>671</v>
       </c>
       <c r="C648" t="s">
-        <v>1648</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="649" spans="1:3">
@@ -13471,7 +13423,7 @@
         <v>672</v>
       </c>
       <c r="C649" t="s">
-        <v>1649</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="650" spans="1:3">
@@ -13482,7 +13434,7 @@
         <v>673</v>
       </c>
       <c r="C650" t="s">
-        <v>1650</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="651" spans="1:3">
@@ -13493,7 +13445,7 @@
         <v>674</v>
       </c>
       <c r="C651" t="s">
-        <v>1651</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="652" spans="1:3">
@@ -13504,7 +13456,7 @@
         <v>675</v>
       </c>
       <c r="C652" t="s">
-        <v>1652</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="653" spans="1:3">
@@ -13515,7 +13467,7 @@
         <v>676</v>
       </c>
       <c r="C653" t="s">
-        <v>1653</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="654" spans="1:3">
@@ -13526,7 +13478,7 @@
         <v>677</v>
       </c>
       <c r="C654" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="655" spans="1:3">
@@ -13537,7 +13489,7 @@
         <v>678</v>
       </c>
       <c r="C655" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="656" spans="1:3">
@@ -13548,7 +13500,7 @@
         <v>679</v>
       </c>
       <c r="C656" t="s">
-        <v>1656</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="657" spans="1:3">
@@ -13559,7 +13511,7 @@
         <v>680</v>
       </c>
       <c r="C657" t="s">
-        <v>1657</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="658" spans="1:3">
@@ -13570,7 +13522,7 @@
         <v>681</v>
       </c>
       <c r="C658" t="s">
-        <v>1658</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="659" spans="1:3">
@@ -13581,7 +13533,7 @@
         <v>682</v>
       </c>
       <c r="C659" t="s">
-        <v>1659</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="660" spans="1:3">
@@ -13592,7 +13544,7 @@
         <v>683</v>
       </c>
       <c r="C660" t="s">
-        <v>1660</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="661" spans="1:3">
@@ -13603,7 +13555,7 @@
         <v>684</v>
       </c>
       <c r="C661" t="s">
-        <v>1661</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="662" spans="1:3">
@@ -13614,7 +13566,7 @@
         <v>685</v>
       </c>
       <c r="C662" t="s">
-        <v>1662</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="663" spans="1:3">
@@ -13625,7 +13577,7 @@
         <v>686</v>
       </c>
       <c r="C663" t="s">
-        <v>1663</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="664" spans="1:3">
@@ -13636,7 +13588,7 @@
         <v>687</v>
       </c>
       <c r="C664" t="s">
-        <v>1664</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="665" spans="1:3">
@@ -13647,7 +13599,7 @@
         <v>688</v>
       </c>
       <c r="C665" t="s">
-        <v>1665</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="666" spans="1:3">
@@ -13658,7 +13610,7 @@
         <v>689</v>
       </c>
       <c r="C666" t="s">
-        <v>1666</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="667" spans="1:3">
@@ -13669,7 +13621,7 @@
         <v>690</v>
       </c>
       <c r="C667" t="s">
-        <v>1667</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="668" spans="1:3">
@@ -13680,7 +13632,7 @@
         <v>691</v>
       </c>
       <c r="C668" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="669" spans="1:3">
@@ -13691,7 +13643,7 @@
         <v>692</v>
       </c>
       <c r="C669" t="s">
-        <v>1669</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="670" spans="1:3">
@@ -13702,172 +13654,172 @@
         <v>693</v>
       </c>
       <c r="C670" t="s">
-        <v>1670</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="671" spans="1:3">
       <c r="A671" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B671" t="s">
         <v>694</v>
       </c>
       <c r="C671" t="s">
-        <v>1671</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="672" spans="1:3">
       <c r="A672" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B672" t="s">
         <v>695</v>
       </c>
       <c r="C672" t="s">
-        <v>1672</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="673" spans="1:3">
       <c r="A673" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B673" t="s">
         <v>696</v>
       </c>
       <c r="C673" t="s">
-        <v>1673</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="674" spans="1:3">
       <c r="A674" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B674" t="s">
         <v>697</v>
       </c>
       <c r="C674" t="s">
-        <v>1674</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="675" spans="1:3">
       <c r="A675" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B675" t="s">
         <v>698</v>
       </c>
       <c r="C675" t="s">
-        <v>1675</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="676" spans="1:3">
       <c r="A676" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B676" t="s">
         <v>699</v>
       </c>
       <c r="C676" t="s">
-        <v>1676</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="677" spans="1:3">
       <c r="A677" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B677" t="s">
         <v>700</v>
       </c>
       <c r="C677" t="s">
-        <v>1677</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="678" spans="1:3">
       <c r="A678" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B678" t="s">
         <v>701</v>
       </c>
       <c r="C678" t="s">
-        <v>1678</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="679" spans="1:3">
       <c r="A679" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B679" t="s">
         <v>702</v>
       </c>
       <c r="C679" t="s">
-        <v>1679</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="680" spans="1:3">
       <c r="A680" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B680" t="s">
         <v>703</v>
       </c>
       <c r="C680" t="s">
-        <v>1680</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="681" spans="1:3">
       <c r="A681" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B681" t="s">
         <v>704</v>
       </c>
       <c r="C681" t="s">
-        <v>1681</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="682" spans="1:3">
       <c r="A682" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B682" t="s">
         <v>705</v>
       </c>
       <c r="C682" t="s">
-        <v>1682</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="683" spans="1:3">
       <c r="A683" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B683" t="s">
         <v>706</v>
       </c>
       <c r="C683" t="s">
-        <v>1683</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="684" spans="1:3">
       <c r="A684" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B684" t="s">
         <v>707</v>
       </c>
       <c r="C684" t="s">
-        <v>1684</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="685" spans="1:3">
       <c r="A685" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B685" t="s">
         <v>708</v>
       </c>
       <c r="C685" t="s">
-        <v>1685</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="686" spans="1:3">
@@ -13878,7 +13830,7 @@
         <v>709</v>
       </c>
       <c r="C686" t="s">
-        <v>1686</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="687" spans="1:3">
@@ -13889,7 +13841,7 @@
         <v>710</v>
       </c>
       <c r="C687" t="s">
-        <v>1687</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="688" spans="1:3">
@@ -13900,7 +13852,7 @@
         <v>711</v>
       </c>
       <c r="C688" t="s">
-        <v>1688</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="689" spans="1:3">
@@ -13911,7 +13863,7 @@
         <v>712</v>
       </c>
       <c r="C689" t="s">
-        <v>1689</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="690" spans="1:3">
@@ -13922,7 +13874,7 @@
         <v>713</v>
       </c>
       <c r="C690" t="s">
-        <v>1690</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="691" spans="1:3">
@@ -13933,7 +13885,7 @@
         <v>714</v>
       </c>
       <c r="C691" t="s">
-        <v>1691</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="692" spans="1:3">
@@ -13944,7 +13896,7 @@
         <v>715</v>
       </c>
       <c r="C692" t="s">
-        <v>1692</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="693" spans="1:3">
@@ -13955,7 +13907,7 @@
         <v>716</v>
       </c>
       <c r="C693" t="s">
-        <v>1693</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="694" spans="1:3">
@@ -13966,7 +13918,7 @@
         <v>717</v>
       </c>
       <c r="C694" t="s">
-        <v>1694</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="695" spans="1:3">
@@ -13977,7 +13929,7 @@
         <v>718</v>
       </c>
       <c r="C695" t="s">
-        <v>1695</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="696" spans="1:3">
@@ -13988,7 +13940,7 @@
         <v>719</v>
       </c>
       <c r="C696" t="s">
-        <v>1696</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="697" spans="1:3">
@@ -13999,7 +13951,7 @@
         <v>720</v>
       </c>
       <c r="C697" t="s">
-        <v>1697</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="698" spans="1:3">
@@ -14010,7 +13962,7 @@
         <v>721</v>
       </c>
       <c r="C698" t="s">
-        <v>1698</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="699" spans="1:3">
@@ -14021,7 +13973,7 @@
         <v>722</v>
       </c>
       <c r="C699" t="s">
-        <v>1699</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="700" spans="1:3">
@@ -14032,7 +13984,7 @@
         <v>723</v>
       </c>
       <c r="C700" t="s">
-        <v>1700</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="701" spans="1:3">
@@ -14043,7 +13995,7 @@
         <v>724</v>
       </c>
       <c r="C701" t="s">
-        <v>1701</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="702" spans="1:3">
@@ -14054,7 +14006,7 @@
         <v>725</v>
       </c>
       <c r="C702" t="s">
-        <v>1702</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="703" spans="1:3">
@@ -14065,7 +14017,7 @@
         <v>726</v>
       </c>
       <c r="C703" t="s">
-        <v>1703</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="704" spans="1:3">
@@ -14076,7 +14028,7 @@
         <v>727</v>
       </c>
       <c r="C704" t="s">
-        <v>1704</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="705" spans="1:3">
@@ -14087,7 +14039,7 @@
         <v>728</v>
       </c>
       <c r="C705" t="s">
-        <v>1705</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="706" spans="1:3">
@@ -14098,7 +14050,7 @@
         <v>729</v>
       </c>
       <c r="C706" t="s">
-        <v>1706</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="707" spans="1:3">
@@ -14109,7 +14061,7 @@
         <v>730</v>
       </c>
       <c r="C707" t="s">
-        <v>1707</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="708" spans="1:3">
@@ -14120,7 +14072,7 @@
         <v>731</v>
       </c>
       <c r="C708" t="s">
-        <v>1708</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="709" spans="1:3">
@@ -14131,7 +14083,7 @@
         <v>732</v>
       </c>
       <c r="C709" t="s">
-        <v>1709</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="710" spans="1:3">
@@ -14142,7 +14094,7 @@
         <v>733</v>
       </c>
       <c r="C710" t="s">
-        <v>1710</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="711" spans="1:3">
@@ -14153,7 +14105,7 @@
         <v>734</v>
       </c>
       <c r="C711" t="s">
-        <v>1711</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="712" spans="1:3">
@@ -14164,7 +14116,7 @@
         <v>735</v>
       </c>
       <c r="C712" t="s">
-        <v>1712</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="713" spans="1:3">
@@ -14175,7 +14127,7 @@
         <v>736</v>
       </c>
       <c r="C713" t="s">
-        <v>1713</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="714" spans="1:3">
@@ -14186,7 +14138,7 @@
         <v>737</v>
       </c>
       <c r="C714" t="s">
-        <v>1714</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="715" spans="1:3">
@@ -14197,7 +14149,7 @@
         <v>738</v>
       </c>
       <c r="C715" t="s">
-        <v>1715</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="716" spans="1:3">
@@ -14208,7 +14160,7 @@
         <v>739</v>
       </c>
       <c r="C716" t="s">
-        <v>1716</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="717" spans="1:3">
@@ -14219,7 +14171,7 @@
         <v>740</v>
       </c>
       <c r="C717" t="s">
-        <v>1717</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="718" spans="1:3">
@@ -14230,7 +14182,7 @@
         <v>741</v>
       </c>
       <c r="C718" t="s">
-        <v>1718</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="719" spans="1:3">
@@ -14241,7 +14193,7 @@
         <v>742</v>
       </c>
       <c r="C719" t="s">
-        <v>1719</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="720" spans="1:3">
@@ -14252,7 +14204,7 @@
         <v>743</v>
       </c>
       <c r="C720" t="s">
-        <v>1720</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="721" spans="1:3">
@@ -14263,7 +14215,7 @@
         <v>744</v>
       </c>
       <c r="C721" t="s">
-        <v>1721</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="722" spans="1:3">
@@ -14274,7 +14226,7 @@
         <v>745</v>
       </c>
       <c r="C722" t="s">
-        <v>1722</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="723" spans="1:3">
@@ -14285,7 +14237,7 @@
         <v>746</v>
       </c>
       <c r="C723" t="s">
-        <v>1723</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="724" spans="1:3">
@@ -14296,7 +14248,7 @@
         <v>747</v>
       </c>
       <c r="C724" t="s">
-        <v>1724</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="725" spans="1:3">
@@ -14307,7 +14259,7 @@
         <v>748</v>
       </c>
       <c r="C725" t="s">
-        <v>1725</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="726" spans="1:3">
@@ -14318,7 +14270,7 @@
         <v>749</v>
       </c>
       <c r="C726" t="s">
-        <v>1726</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="727" spans="1:3">
@@ -14329,7 +14281,7 @@
         <v>750</v>
       </c>
       <c r="C727" t="s">
-        <v>1727</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="728" spans="1:3">
@@ -14340,7 +14292,7 @@
         <v>751</v>
       </c>
       <c r="C728" t="s">
-        <v>1728</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="729" spans="1:3">
@@ -14351,7 +14303,7 @@
         <v>752</v>
       </c>
       <c r="C729" t="s">
-        <v>1729</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="730" spans="1:3">
@@ -14362,7 +14314,7 @@
         <v>753</v>
       </c>
       <c r="C730" t="s">
-        <v>1730</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="731" spans="1:3">
@@ -14373,7 +14325,7 @@
         <v>754</v>
       </c>
       <c r="C731" t="s">
-        <v>1731</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="732" spans="1:3">
@@ -14384,7 +14336,7 @@
         <v>755</v>
       </c>
       <c r="C732" t="s">
-        <v>1732</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="733" spans="1:3">
@@ -14395,7 +14347,7 @@
         <v>756</v>
       </c>
       <c r="C733" t="s">
-        <v>1733</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="734" spans="1:3">
@@ -14406,7 +14358,7 @@
         <v>757</v>
       </c>
       <c r="C734" t="s">
-        <v>1734</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="735" spans="1:3">
@@ -14417,7 +14369,7 @@
         <v>758</v>
       </c>
       <c r="C735" t="s">
-        <v>1735</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="736" spans="1:3">
@@ -14428,7 +14380,7 @@
         <v>759</v>
       </c>
       <c r="C736" t="s">
-        <v>1736</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="737" spans="1:3">
@@ -14439,7 +14391,7 @@
         <v>760</v>
       </c>
       <c r="C737" t="s">
-        <v>1661</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="738" spans="1:3">
@@ -14450,7 +14402,7 @@
         <v>761</v>
       </c>
       <c r="C738" t="s">
-        <v>1737</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="739" spans="1:3">
@@ -14461,7 +14413,7 @@
         <v>762</v>
       </c>
       <c r="C739" t="s">
-        <v>1738</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="740" spans="1:3">
@@ -14472,7 +14424,7 @@
         <v>763</v>
       </c>
       <c r="C740" t="s">
-        <v>1739</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="741" spans="1:3">
@@ -14483,7 +14435,7 @@
         <v>764</v>
       </c>
       <c r="C741" t="s">
-        <v>1740</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="742" spans="1:3">
@@ -14494,7 +14446,7 @@
         <v>765</v>
       </c>
       <c r="C742" t="s">
-        <v>1741</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="743" spans="1:3">
@@ -14505,7 +14457,7 @@
         <v>766</v>
       </c>
       <c r="C743" t="s">
-        <v>1742</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="744" spans="1:3">
@@ -14516,7 +14468,7 @@
         <v>767</v>
       </c>
       <c r="C744" t="s">
-        <v>1743</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="745" spans="1:3">
@@ -14527,7 +14479,7 @@
         <v>768</v>
       </c>
       <c r="C745" t="s">
-        <v>1744</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="746" spans="1:3">
@@ -14538,7 +14490,7 @@
         <v>769</v>
       </c>
       <c r="C746" t="s">
-        <v>1745</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="747" spans="1:3">
@@ -14549,7 +14501,7 @@
         <v>770</v>
       </c>
       <c r="C747" t="s">
-        <v>1746</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="748" spans="1:3">
@@ -14560,7 +14512,7 @@
         <v>771</v>
       </c>
       <c r="C748" t="s">
-        <v>1747</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="749" spans="1:3">
@@ -14571,7 +14523,7 @@
         <v>772</v>
       </c>
       <c r="C749" t="s">
-        <v>1748</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="750" spans="1:3">
@@ -14582,7 +14534,7 @@
         <v>773</v>
       </c>
       <c r="C750" t="s">
-        <v>1749</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="751" spans="1:3">
@@ -14593,7 +14545,7 @@
         <v>774</v>
       </c>
       <c r="C751" t="s">
-        <v>1750</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="752" spans="1:3">
@@ -14604,7 +14556,7 @@
         <v>775</v>
       </c>
       <c r="C752" t="s">
-        <v>1751</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="753" spans="1:3">
@@ -14615,7 +14567,7 @@
         <v>776</v>
       </c>
       <c r="C753" t="s">
-        <v>1752</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="754" spans="1:3">
@@ -14626,7 +14578,7 @@
         <v>777</v>
       </c>
       <c r="C754" t="s">
-        <v>1753</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="755" spans="1:3">
@@ -14637,7 +14589,7 @@
         <v>778</v>
       </c>
       <c r="C755" t="s">
-        <v>1754</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="756" spans="1:3">
@@ -14648,7 +14600,7 @@
         <v>779</v>
       </c>
       <c r="C756" t="s">
-        <v>1755</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="757" spans="1:3">
@@ -14659,7 +14611,7 @@
         <v>780</v>
       </c>
       <c r="C757" t="s">
-        <v>1756</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="758" spans="1:3">
@@ -14670,7 +14622,7 @@
         <v>781</v>
       </c>
       <c r="C758" t="s">
-        <v>1757</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="759" spans="1:3">
@@ -14681,7 +14633,7 @@
         <v>782</v>
       </c>
       <c r="C759" t="s">
-        <v>1758</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="760" spans="1:3">
@@ -14692,7 +14644,7 @@
         <v>783</v>
       </c>
       <c r="C760" t="s">
-        <v>1759</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="761" spans="1:3">
@@ -14703,7 +14655,7 @@
         <v>784</v>
       </c>
       <c r="C761" t="s">
-        <v>1760</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="762" spans="1:3">
@@ -14714,7 +14666,7 @@
         <v>785</v>
       </c>
       <c r="C762" t="s">
-        <v>1761</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="763" spans="1:3">
@@ -14725,7 +14677,7 @@
         <v>786</v>
       </c>
       <c r="C763" t="s">
-        <v>1762</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="764" spans="1:3">
@@ -14736,7 +14688,7 @@
         <v>787</v>
       </c>
       <c r="C764" t="s">
-        <v>1763</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="765" spans="1:3">
@@ -14747,7 +14699,7 @@
         <v>788</v>
       </c>
       <c r="C765" t="s">
-        <v>1764</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="766" spans="1:3">
@@ -14758,7 +14710,7 @@
         <v>789</v>
       </c>
       <c r="C766" t="s">
-        <v>1765</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="767" spans="1:3">
@@ -14769,7 +14721,7 @@
         <v>790</v>
       </c>
       <c r="C767" t="s">
-        <v>1766</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="768" spans="1:3">
@@ -14780,7 +14732,7 @@
         <v>791</v>
       </c>
       <c r="C768" t="s">
-        <v>1767</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="769" spans="1:3">
@@ -14791,7 +14743,7 @@
         <v>792</v>
       </c>
       <c r="C769" t="s">
-        <v>1768</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="770" spans="1:3">
@@ -14802,7 +14754,7 @@
         <v>793</v>
       </c>
       <c r="C770" t="s">
-        <v>1769</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="771" spans="1:3">
@@ -14813,7 +14765,7 @@
         <v>794</v>
       </c>
       <c r="C771" t="s">
-        <v>1770</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="772" spans="1:3">
@@ -14824,7 +14776,7 @@
         <v>795</v>
       </c>
       <c r="C772" t="s">
-        <v>1771</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="773" spans="1:3">
@@ -14835,7 +14787,7 @@
         <v>796</v>
       </c>
       <c r="C773" t="s">
-        <v>1772</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="774" spans="1:3">
@@ -14846,7 +14798,7 @@
         <v>797</v>
       </c>
       <c r="C774" t="s">
-        <v>1773</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="775" spans="1:3">
@@ -14857,7 +14809,7 @@
         <v>798</v>
       </c>
       <c r="C775" t="s">
-        <v>1774</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="776" spans="1:3">
@@ -14868,7 +14820,7 @@
         <v>799</v>
       </c>
       <c r="C776" t="s">
-        <v>1775</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="777" spans="1:3">
@@ -14879,7 +14831,7 @@
         <v>800</v>
       </c>
       <c r="C777" t="s">
-        <v>1776</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="778" spans="1:3">
@@ -14890,7 +14842,7 @@
         <v>801</v>
       </c>
       <c r="C778" t="s">
-        <v>1777</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="779" spans="1:3">
@@ -14901,7 +14853,7 @@
         <v>802</v>
       </c>
       <c r="C779" t="s">
-        <v>1778</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="780" spans="1:3">
@@ -14912,7 +14864,7 @@
         <v>803</v>
       </c>
       <c r="C780" t="s">
-        <v>1779</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="781" spans="1:3">
@@ -14923,7 +14875,7 @@
         <v>804</v>
       </c>
       <c r="C781" t="s">
-        <v>1780</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="782" spans="1:3">
@@ -14934,7 +14886,7 @@
         <v>805</v>
       </c>
       <c r="C782" t="s">
-        <v>1781</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="783" spans="1:3">
@@ -14945,7 +14897,7 @@
         <v>806</v>
       </c>
       <c r="C783" t="s">
-        <v>1782</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="784" spans="1:3">
@@ -14956,7 +14908,7 @@
         <v>807</v>
       </c>
       <c r="C784" t="s">
-        <v>1783</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="785" spans="1:3">
@@ -14967,7 +14919,7 @@
         <v>808</v>
       </c>
       <c r="C785" t="s">
-        <v>1784</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="786" spans="1:3">
@@ -14978,7 +14930,7 @@
         <v>809</v>
       </c>
       <c r="C786" t="s">
-        <v>1785</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="787" spans="1:3">
@@ -14989,7 +14941,7 @@
         <v>810</v>
       </c>
       <c r="C787" t="s">
-        <v>1786</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="788" spans="1:3">
@@ -15000,7 +14952,7 @@
         <v>811</v>
       </c>
       <c r="C788" t="s">
-        <v>1787</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="789" spans="1:3">
@@ -15011,7 +14963,7 @@
         <v>812</v>
       </c>
       <c r="C789" t="s">
-        <v>1788</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="790" spans="1:3">
@@ -15022,7 +14974,7 @@
         <v>813</v>
       </c>
       <c r="C790" t="s">
-        <v>1789</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="791" spans="1:3">
@@ -15033,7 +14985,7 @@
         <v>814</v>
       </c>
       <c r="C791" t="s">
-        <v>1790</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="792" spans="1:3">
@@ -15044,7 +14996,7 @@
         <v>815</v>
       </c>
       <c r="C792" t="s">
-        <v>1791</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="793" spans="1:3">
@@ -15055,7 +15007,7 @@
         <v>816</v>
       </c>
       <c r="C793" t="s">
-        <v>1792</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="794" spans="1:3">
@@ -15066,7 +15018,7 @@
         <v>817</v>
       </c>
       <c r="C794" t="s">
-        <v>1793</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="795" spans="1:3">
@@ -15077,7 +15029,7 @@
         <v>818</v>
       </c>
       <c r="C795" t="s">
-        <v>1794</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="796" spans="1:3">
@@ -15088,7 +15040,7 @@
         <v>819</v>
       </c>
       <c r="C796" t="s">
-        <v>1795</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="797" spans="1:3">
@@ -15099,7 +15051,7 @@
         <v>820</v>
       </c>
       <c r="C797" t="s">
-        <v>1796</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="798" spans="1:3">
@@ -15110,7 +15062,7 @@
         <v>821</v>
       </c>
       <c r="C798" t="s">
-        <v>1797</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="799" spans="1:3">
@@ -15121,7 +15073,7 @@
         <v>822</v>
       </c>
       <c r="C799" t="s">
-        <v>1798</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="800" spans="1:3">
@@ -15132,95 +15084,95 @@
         <v>823</v>
       </c>
       <c r="C800" t="s">
-        <v>1799</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="801" spans="1:3">
       <c r="A801" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B801" t="s">
         <v>824</v>
       </c>
       <c r="C801" t="s">
-        <v>1800</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="802" spans="1:3">
       <c r="A802" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B802" t="s">
         <v>825</v>
       </c>
       <c r="C802" t="s">
-        <v>1801</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="803" spans="1:3">
       <c r="A803" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B803" t="s">
         <v>826</v>
       </c>
       <c r="C803" t="s">
-        <v>1802</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="804" spans="1:3">
       <c r="A804" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B804" t="s">
         <v>827</v>
       </c>
       <c r="C804" t="s">
-        <v>1803</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="805" spans="1:3">
       <c r="A805" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B805" t="s">
         <v>828</v>
       </c>
       <c r="C805" t="s">
-        <v>1804</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="806" spans="1:3">
       <c r="A806" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B806" t="s">
         <v>829</v>
       </c>
       <c r="C806" t="s">
-        <v>1805</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="807" spans="1:3">
       <c r="A807" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B807" t="s">
         <v>830</v>
       </c>
       <c r="C807" t="s">
-        <v>1806</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="808" spans="1:3">
       <c r="A808" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B808" t="s">
         <v>831</v>
       </c>
       <c r="C808" t="s">
-        <v>1807</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="809" spans="1:3">
@@ -15231,7 +15183,7 @@
         <v>832</v>
       </c>
       <c r="C809" t="s">
-        <v>1808</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="810" spans="1:3">
@@ -15242,7 +15194,7 @@
         <v>833</v>
       </c>
       <c r="C810" t="s">
-        <v>1809</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="811" spans="1:3">
@@ -15253,7 +15205,7 @@
         <v>834</v>
       </c>
       <c r="C811" t="s">
-        <v>1810</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="812" spans="1:3">
@@ -15264,7 +15216,7 @@
         <v>835</v>
       </c>
       <c r="C812" t="s">
-        <v>1811</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="813" spans="1:3">
@@ -15275,7 +15227,7 @@
         <v>836</v>
       </c>
       <c r="C813" t="s">
-        <v>1812</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="814" spans="1:3">
@@ -15286,7 +15238,7 @@
         <v>837</v>
       </c>
       <c r="C814" t="s">
-        <v>1813</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="815" spans="1:3">
@@ -15297,7 +15249,7 @@
         <v>838</v>
       </c>
       <c r="C815" t="s">
-        <v>1814</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="816" spans="1:3">
@@ -15308,7 +15260,7 @@
         <v>839</v>
       </c>
       <c r="C816" t="s">
-        <v>1815</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="817" spans="1:3">
@@ -15319,7 +15271,7 @@
         <v>840</v>
       </c>
       <c r="C817" t="s">
-        <v>1816</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="818" spans="1:3">
@@ -15330,7 +15282,7 @@
         <v>841</v>
       </c>
       <c r="C818" t="s">
-        <v>1817</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="819" spans="1:3">
@@ -15341,7 +15293,7 @@
         <v>842</v>
       </c>
       <c r="C819" t="s">
-        <v>1818</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="820" spans="1:3">
@@ -15352,7 +15304,7 @@
         <v>843</v>
       </c>
       <c r="C820" t="s">
-        <v>1819</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="821" spans="1:3">
@@ -15363,7 +15315,7 @@
         <v>844</v>
       </c>
       <c r="C821" t="s">
-        <v>1820</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="822" spans="1:3">
@@ -15374,7 +15326,7 @@
         <v>845</v>
       </c>
       <c r="C822" t="s">
-        <v>1821</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="823" spans="1:3">
@@ -15385,7 +15337,7 @@
         <v>846</v>
       </c>
       <c r="C823" t="s">
-        <v>1822</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="824" spans="1:3">
@@ -15396,7 +15348,7 @@
         <v>847</v>
       </c>
       <c r="C824" t="s">
-        <v>1823</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="825" spans="1:3">
@@ -15407,7 +15359,7 @@
         <v>848</v>
       </c>
       <c r="C825" t="s">
-        <v>1824</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="826" spans="1:3">
@@ -15418,7 +15370,7 @@
         <v>849</v>
       </c>
       <c r="C826" t="s">
-        <v>1825</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="827" spans="1:3">
@@ -15429,7 +15381,7 @@
         <v>850</v>
       </c>
       <c r="C827" t="s">
-        <v>1826</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="828" spans="1:3">
@@ -15440,7 +15392,7 @@
         <v>851</v>
       </c>
       <c r="C828" t="s">
-        <v>1827</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="829" spans="1:3">
@@ -15451,7 +15403,7 @@
         <v>852</v>
       </c>
       <c r="C829" t="s">
-        <v>1828</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="830" spans="1:3">
@@ -15462,7 +15414,7 @@
         <v>853</v>
       </c>
       <c r="C830" t="s">
-        <v>1829</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="831" spans="1:3">
@@ -15473,7 +15425,7 @@
         <v>854</v>
       </c>
       <c r="C831" t="s">
-        <v>1830</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="832" spans="1:3">
@@ -15484,7 +15436,7 @@
         <v>855</v>
       </c>
       <c r="C832" t="s">
-        <v>1831</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="833" spans="1:3">
@@ -15495,7 +15447,7 @@
         <v>856</v>
       </c>
       <c r="C833" t="s">
-        <v>1832</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="834" spans="1:3">
@@ -15506,7 +15458,7 @@
         <v>857</v>
       </c>
       <c r="C834" t="s">
-        <v>1833</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="835" spans="1:3">
@@ -15517,7 +15469,7 @@
         <v>858</v>
       </c>
       <c r="C835" t="s">
-        <v>1834</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="836" spans="1:3">
@@ -15528,7 +15480,7 @@
         <v>859</v>
       </c>
       <c r="C836" t="s">
-        <v>1835</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="837" spans="1:3">
@@ -15539,7 +15491,7 @@
         <v>860</v>
       </c>
       <c r="C837" t="s">
-        <v>1836</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="838" spans="1:3">
@@ -15550,7 +15502,7 @@
         <v>861</v>
       </c>
       <c r="C838" t="s">
-        <v>1837</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="839" spans="1:3">
@@ -15561,7 +15513,7 @@
         <v>862</v>
       </c>
       <c r="C839" t="s">
-        <v>1838</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="840" spans="1:3">
@@ -15572,7 +15524,7 @@
         <v>863</v>
       </c>
       <c r="C840" t="s">
-        <v>1839</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="841" spans="1:3">
@@ -15583,7 +15535,7 @@
         <v>864</v>
       </c>
       <c r="C841" t="s">
-        <v>1840</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="842" spans="1:3">
@@ -15594,7 +15546,7 @@
         <v>865</v>
       </c>
       <c r="C842" t="s">
-        <v>1841</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="843" spans="1:3">
@@ -15605,7 +15557,7 @@
         <v>866</v>
       </c>
       <c r="C843" t="s">
-        <v>1842</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="844" spans="1:3">
@@ -15616,7 +15568,7 @@
         <v>867</v>
       </c>
       <c r="C844" t="s">
-        <v>1843</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="845" spans="1:3">
@@ -15627,7 +15579,7 @@
         <v>868</v>
       </c>
       <c r="C845" t="s">
-        <v>1844</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="846" spans="1:3">
@@ -15638,7 +15590,7 @@
         <v>869</v>
       </c>
       <c r="C846" t="s">
-        <v>1845</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="847" spans="1:3">
@@ -15649,7 +15601,7 @@
         <v>870</v>
       </c>
       <c r="C847" t="s">
-        <v>1846</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="848" spans="1:3">
@@ -15660,7 +15612,7 @@
         <v>871</v>
       </c>
       <c r="C848" t="s">
-        <v>1847</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="849" spans="1:3">
@@ -15671,7 +15623,7 @@
         <v>872</v>
       </c>
       <c r="C849" t="s">
-        <v>1848</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="850" spans="1:3">
@@ -15682,7 +15634,7 @@
         <v>873</v>
       </c>
       <c r="C850" t="s">
-        <v>1849</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="851" spans="1:3">
@@ -15693,7 +15645,7 @@
         <v>874</v>
       </c>
       <c r="C851" t="s">
-        <v>1850</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="852" spans="1:3">
@@ -15704,7 +15656,7 @@
         <v>875</v>
       </c>
       <c r="C852" t="s">
-        <v>1851</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="853" spans="1:3">
@@ -15715,7 +15667,7 @@
         <v>876</v>
       </c>
       <c r="C853" t="s">
-        <v>1852</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="854" spans="1:3">
@@ -15726,7 +15678,7 @@
         <v>877</v>
       </c>
       <c r="C854" t="s">
-        <v>1853</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="855" spans="1:3">
@@ -15737,7 +15689,7 @@
         <v>878</v>
       </c>
       <c r="C855" t="s">
-        <v>1854</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="856" spans="1:3">
@@ -15748,7 +15700,7 @@
         <v>879</v>
       </c>
       <c r="C856" t="s">
-        <v>1855</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="857" spans="1:3">
@@ -15759,7 +15711,7 @@
         <v>880</v>
       </c>
       <c r="C857" t="s">
-        <v>1856</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="858" spans="1:3">
@@ -15770,7 +15722,7 @@
         <v>881</v>
       </c>
       <c r="C858" t="s">
-        <v>1857</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="859" spans="1:3">
@@ -15781,7 +15733,7 @@
         <v>882</v>
       </c>
       <c r="C859" t="s">
-        <v>1858</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="860" spans="1:3">
@@ -15792,7 +15744,7 @@
         <v>883</v>
       </c>
       <c r="C860" t="s">
-        <v>1859</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="861" spans="1:3">
@@ -15803,7 +15755,7 @@
         <v>884</v>
       </c>
       <c r="C861" t="s">
-        <v>1860</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="862" spans="1:3">
@@ -15814,7 +15766,7 @@
         <v>885</v>
       </c>
       <c r="C862" t="s">
-        <v>1861</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="863" spans="1:3">
@@ -15825,7 +15777,7 @@
         <v>886</v>
       </c>
       <c r="C863" t="s">
-        <v>1862</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="864" spans="1:3">
@@ -15836,7 +15788,7 @@
         <v>887</v>
       </c>
       <c r="C864" t="s">
-        <v>1863</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="865" spans="1:3">
@@ -15847,7 +15799,7 @@
         <v>888</v>
       </c>
       <c r="C865" t="s">
-        <v>1864</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="866" spans="1:3">
@@ -15858,7 +15810,7 @@
         <v>889</v>
       </c>
       <c r="C866" t="s">
-        <v>1865</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="867" spans="1:3">
@@ -15869,7 +15821,7 @@
         <v>890</v>
       </c>
       <c r="C867" t="s">
-        <v>1866</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="868" spans="1:3">
@@ -15880,7 +15832,7 @@
         <v>891</v>
       </c>
       <c r="C868" t="s">
-        <v>1867</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="869" spans="1:3">
@@ -15891,7 +15843,7 @@
         <v>892</v>
       </c>
       <c r="C869" t="s">
-        <v>1868</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="870" spans="1:3">
@@ -15902,7 +15854,7 @@
         <v>893</v>
       </c>
       <c r="C870" t="s">
-        <v>1869</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="871" spans="1:3">
@@ -15913,7 +15865,7 @@
         <v>894</v>
       </c>
       <c r="C871" t="s">
-        <v>1870</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="872" spans="1:3">
@@ -15924,7 +15876,7 @@
         <v>895</v>
       </c>
       <c r="C872" t="s">
-        <v>1871</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="873" spans="1:3">
@@ -15935,7 +15887,7 @@
         <v>896</v>
       </c>
       <c r="C873" t="s">
-        <v>1872</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="874" spans="1:3">
@@ -15946,7 +15898,7 @@
         <v>897</v>
       </c>
       <c r="C874" t="s">
-        <v>1873</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="875" spans="1:3">
@@ -15957,7 +15909,7 @@
         <v>898</v>
       </c>
       <c r="C875" t="s">
-        <v>1874</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="876" spans="1:3">
@@ -15968,7 +15920,7 @@
         <v>899</v>
       </c>
       <c r="C876" t="s">
-        <v>1875</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="877" spans="1:3">
@@ -15979,7 +15931,7 @@
         <v>900</v>
       </c>
       <c r="C877" t="s">
-        <v>1876</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="878" spans="1:3">
@@ -15990,7 +15942,7 @@
         <v>901</v>
       </c>
       <c r="C878" t="s">
-        <v>1877</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="879" spans="1:3">
@@ -16001,7 +15953,7 @@
         <v>902</v>
       </c>
       <c r="C879" t="s">
-        <v>1878</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="880" spans="1:3">
@@ -16012,7 +15964,7 @@
         <v>903</v>
       </c>
       <c r="C880" t="s">
-        <v>1879</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="881" spans="1:3">
@@ -16023,7 +15975,7 @@
         <v>904</v>
       </c>
       <c r="C881" t="s">
-        <v>1880</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="882" spans="1:3">
@@ -16034,7 +15986,7 @@
         <v>905</v>
       </c>
       <c r="C882" t="s">
-        <v>1881</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="883" spans="1:3">
@@ -16045,7 +15997,7 @@
         <v>906</v>
       </c>
       <c r="C883" t="s">
-        <v>1882</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="884" spans="1:3">
@@ -16056,7 +16008,7 @@
         <v>907</v>
       </c>
       <c r="C884" t="s">
-        <v>1883</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="885" spans="1:3">
@@ -16067,95 +16019,95 @@
         <v>908</v>
       </c>
       <c r="C885" t="s">
-        <v>1884</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="886" spans="1:3">
       <c r="A886" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B886" t="s">
         <v>909</v>
       </c>
       <c r="C886" t="s">
-        <v>1885</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="887" spans="1:3">
       <c r="A887" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B887" t="s">
         <v>910</v>
       </c>
       <c r="C887" t="s">
-        <v>1886</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="888" spans="1:3">
       <c r="A888" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B888" t="s">
         <v>911</v>
       </c>
       <c r="C888" t="s">
-        <v>1887</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="889" spans="1:3">
       <c r="A889" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B889" t="s">
         <v>912</v>
       </c>
       <c r="C889" t="s">
-        <v>1888</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="890" spans="1:3">
       <c r="A890" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B890" t="s">
         <v>913</v>
       </c>
       <c r="C890" t="s">
-        <v>1889</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="891" spans="1:3">
       <c r="A891" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B891" t="s">
         <v>914</v>
       </c>
       <c r="C891" t="s">
-        <v>1890</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="892" spans="1:3">
       <c r="A892" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B892" t="s">
         <v>915</v>
       </c>
       <c r="C892" t="s">
-        <v>1891</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="893" spans="1:3">
       <c r="A893" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B893" t="s">
         <v>916</v>
       </c>
       <c r="C893" t="s">
-        <v>1892</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="894" spans="1:3">
@@ -16166,7 +16118,7 @@
         <v>917</v>
       </c>
       <c r="C894" t="s">
-        <v>1893</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="895" spans="1:3">
@@ -16177,7 +16129,7 @@
         <v>918</v>
       </c>
       <c r="C895" t="s">
-        <v>1894</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="896" spans="1:3">
@@ -16188,7 +16140,7 @@
         <v>919</v>
       </c>
       <c r="C896" t="s">
-        <v>1895</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="897" spans="1:3">
@@ -16199,7 +16151,7 @@
         <v>920</v>
       </c>
       <c r="C897" t="s">
-        <v>1896</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="898" spans="1:3">
@@ -16210,7 +16162,7 @@
         <v>921</v>
       </c>
       <c r="C898" t="s">
-        <v>1897</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="899" spans="1:3">
@@ -16221,7 +16173,7 @@
         <v>922</v>
       </c>
       <c r="C899" t="s">
-        <v>1898</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="900" spans="1:3">
@@ -16232,7 +16184,7 @@
         <v>923</v>
       </c>
       <c r="C900" t="s">
-        <v>1899</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="901" spans="1:3">
@@ -16243,7 +16195,7 @@
         <v>924</v>
       </c>
       <c r="C901" t="s">
-        <v>1900</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="902" spans="1:3">
@@ -16254,7 +16206,7 @@
         <v>925</v>
       </c>
       <c r="C902" t="s">
-        <v>1901</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="903" spans="1:3">
@@ -16265,7 +16217,7 @@
         <v>926</v>
       </c>
       <c r="C903" t="s">
-        <v>1902</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="904" spans="1:3">
@@ -16276,7 +16228,7 @@
         <v>927</v>
       </c>
       <c r="C904" t="s">
-        <v>1903</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="905" spans="1:3">
@@ -16287,7 +16239,7 @@
         <v>928</v>
       </c>
       <c r="C905" t="s">
-        <v>1904</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="906" spans="1:3">
@@ -16298,7 +16250,7 @@
         <v>929</v>
       </c>
       <c r="C906" t="s">
-        <v>1905</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="907" spans="1:3">
@@ -16309,7 +16261,7 @@
         <v>930</v>
       </c>
       <c r="C907" t="s">
-        <v>1906</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="908" spans="1:3">
@@ -16320,7 +16272,7 @@
         <v>931</v>
       </c>
       <c r="C908" t="s">
-        <v>1907</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="909" spans="1:3">
@@ -16331,7 +16283,7 @@
         <v>932</v>
       </c>
       <c r="C909" t="s">
-        <v>1908</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="910" spans="1:3">
@@ -16342,7 +16294,7 @@
         <v>933</v>
       </c>
       <c r="C910" t="s">
-        <v>1909</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="911" spans="1:3">
@@ -16353,7 +16305,7 @@
         <v>934</v>
       </c>
       <c r="C911" t="s">
-        <v>1910</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="912" spans="1:3">
@@ -16364,7 +16316,7 @@
         <v>935</v>
       </c>
       <c r="C912" t="s">
-        <v>1911</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="913" spans="1:3">
@@ -16375,7 +16327,7 @@
         <v>936</v>
       </c>
       <c r="C913" t="s">
-        <v>1912</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="914" spans="1:3">
@@ -16386,7 +16338,7 @@
         <v>937</v>
       </c>
       <c r="C914" t="s">
-        <v>1913</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="915" spans="1:3">
@@ -16397,7 +16349,7 @@
         <v>938</v>
       </c>
       <c r="C915" t="s">
-        <v>1914</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="916" spans="1:3">
@@ -16408,7 +16360,7 @@
         <v>939</v>
       </c>
       <c r="C916" t="s">
-        <v>1915</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="917" spans="1:3">
@@ -16419,7 +16371,7 @@
         <v>940</v>
       </c>
       <c r="C917" t="s">
-        <v>1916</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="918" spans="1:3">
@@ -16430,7 +16382,7 @@
         <v>941</v>
       </c>
       <c r="C918" t="s">
-        <v>1917</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="919" spans="1:3">
@@ -16441,7 +16393,7 @@
         <v>942</v>
       </c>
       <c r="C919" t="s">
-        <v>1918</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="920" spans="1:3">
@@ -16452,7 +16404,7 @@
         <v>943</v>
       </c>
       <c r="C920" t="s">
-        <v>1919</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="921" spans="1:3">
@@ -16463,7 +16415,7 @@
         <v>944</v>
       </c>
       <c r="C921" t="s">
-        <v>1920</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="922" spans="1:3">
@@ -16474,7 +16426,7 @@
         <v>945</v>
       </c>
       <c r="C922" t="s">
-        <v>1921</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="923" spans="1:3">
@@ -16485,7 +16437,7 @@
         <v>946</v>
       </c>
       <c r="C923" t="s">
-        <v>1922</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="924" spans="1:3">
@@ -16496,7 +16448,7 @@
         <v>947</v>
       </c>
       <c r="C924" t="s">
-        <v>1923</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="925" spans="1:3">
@@ -16507,7 +16459,7 @@
         <v>948</v>
       </c>
       <c r="C925" t="s">
-        <v>1924</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="926" spans="1:3">
@@ -16518,7 +16470,7 @@
         <v>949</v>
       </c>
       <c r="C926" t="s">
-        <v>1925</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="927" spans="1:3">
@@ -16529,7 +16481,7 @@
         <v>950</v>
       </c>
       <c r="C927" t="s">
-        <v>1926</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="928" spans="1:3">
@@ -16540,7 +16492,7 @@
         <v>951</v>
       </c>
       <c r="C928" t="s">
-        <v>1927</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="929" spans="1:3">
@@ -16551,7 +16503,7 @@
         <v>952</v>
       </c>
       <c r="C929" t="s">
-        <v>1928</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="930" spans="1:3">
@@ -16562,7 +16514,7 @@
         <v>953</v>
       </c>
       <c r="C930" t="s">
-        <v>1929</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="931" spans="1:3">
@@ -16573,7 +16525,7 @@
         <v>954</v>
       </c>
       <c r="C931" t="s">
-        <v>1930</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="932" spans="1:3">
@@ -16584,7 +16536,7 @@
         <v>955</v>
       </c>
       <c r="C932" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="933" spans="1:3">
@@ -16595,7 +16547,7 @@
         <v>956</v>
       </c>
       <c r="C933" t="s">
-        <v>1931</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="934" spans="1:3">
@@ -16606,7 +16558,7 @@
         <v>957</v>
       </c>
       <c r="C934" t="s">
-        <v>1932</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="935" spans="1:3">
@@ -16617,7 +16569,7 @@
         <v>958</v>
       </c>
       <c r="C935" t="s">
-        <v>1933</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="936" spans="1:3">
@@ -16628,7 +16580,7 @@
         <v>959</v>
       </c>
       <c r="C936" t="s">
-        <v>1934</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="937" spans="1:3">
@@ -16639,7 +16591,7 @@
         <v>960</v>
       </c>
       <c r="C937" t="s">
-        <v>1935</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="938" spans="1:3">
@@ -16650,7 +16602,7 @@
         <v>961</v>
       </c>
       <c r="C938" t="s">
-        <v>1936</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="939" spans="1:3">
@@ -16661,7 +16613,7 @@
         <v>962</v>
       </c>
       <c r="C939" t="s">
-        <v>1937</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="940" spans="1:3">
@@ -16672,7 +16624,7 @@
         <v>963</v>
       </c>
       <c r="C940" t="s">
-        <v>1938</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="941" spans="1:3">
@@ -16683,7 +16635,7 @@
         <v>964</v>
       </c>
       <c r="C941" t="s">
-        <v>1939</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="942" spans="1:3">
@@ -16694,7 +16646,7 @@
         <v>965</v>
       </c>
       <c r="C942" t="s">
-        <v>1940</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="943" spans="1:3">
@@ -16705,7 +16657,7 @@
         <v>966</v>
       </c>
       <c r="C943" t="s">
-        <v>1941</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="944" spans="1:3">
@@ -16716,7 +16668,7 @@
         <v>967</v>
       </c>
       <c r="C944" t="s">
-        <v>1942</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="945" spans="1:3">
@@ -16727,7 +16679,7 @@
         <v>968</v>
       </c>
       <c r="C945" t="s">
-        <v>1943</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="946" spans="1:3">
@@ -16738,7 +16690,7 @@
         <v>969</v>
       </c>
       <c r="C946" t="s">
-        <v>1944</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="947" spans="1:3">
@@ -16749,7 +16701,7 @@
         <v>970</v>
       </c>
       <c r="C947" t="s">
-        <v>1945</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="948" spans="1:3">
@@ -16760,7 +16712,7 @@
         <v>971</v>
       </c>
       <c r="C948" t="s">
-        <v>1946</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="949" spans="1:3">
@@ -16771,7 +16723,7 @@
         <v>972</v>
       </c>
       <c r="C949" t="s">
-        <v>1947</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="950" spans="1:3">
@@ -16782,7 +16734,7 @@
         <v>973</v>
       </c>
       <c r="C950" t="s">
-        <v>1948</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="951" spans="1:3">
@@ -16793,7 +16745,7 @@
         <v>974</v>
       </c>
       <c r="C951" t="s">
-        <v>1949</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="952" spans="1:3">
@@ -16804,7 +16756,7 @@
         <v>975</v>
       </c>
       <c r="C952" t="s">
-        <v>1950</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="953" spans="1:3">
@@ -16815,7 +16767,7 @@
         <v>976</v>
       </c>
       <c r="C953" t="s">
-        <v>1925</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="954" spans="1:3">
@@ -16826,7 +16778,7 @@
         <v>977</v>
       </c>
       <c r="C954" t="s">
-        <v>1951</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="955" spans="1:3">
@@ -16837,95 +16789,95 @@
         <v>978</v>
       </c>
       <c r="C955" t="s">
-        <v>1952</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="956" spans="1:3">
       <c r="A956" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B956" t="s">
         <v>979</v>
       </c>
       <c r="C956" t="s">
-        <v>1953</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="957" spans="1:3">
       <c r="A957" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B957" t="s">
         <v>980</v>
       </c>
       <c r="C957" t="s">
-        <v>1907</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="958" spans="1:3">
       <c r="A958" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B958" t="s">
         <v>981</v>
       </c>
       <c r="C958" t="s">
-        <v>1954</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="959" spans="1:3">
       <c r="A959" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B959" t="s">
         <v>982</v>
       </c>
       <c r="C959" t="s">
-        <v>1955</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="960" spans="1:3">
       <c r="A960" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B960" t="s">
         <v>983</v>
       </c>
       <c r="C960" t="s">
-        <v>1956</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="961" spans="1:3">
       <c r="A961" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B961" t="s">
         <v>984</v>
       </c>
       <c r="C961" t="s">
-        <v>1957</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="962" spans="1:3">
       <c r="A962" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B962" t="s">
         <v>985</v>
       </c>
       <c r="C962" t="s">
-        <v>1958</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="963" spans="1:3">
       <c r="A963" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B963" t="s">
         <v>986</v>
       </c>
       <c r="C963" t="s">
-        <v>1959</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="964" spans="1:3">
@@ -16936,7 +16888,7 @@
         <v>987</v>
       </c>
       <c r="C964" t="s">
-        <v>1960</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="965" spans="1:3">
@@ -16947,7 +16899,7 @@
         <v>988</v>
       </c>
       <c r="C965" t="s">
-        <v>1961</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="966" spans="1:3">
@@ -16958,7 +16910,7 @@
         <v>989</v>
       </c>
       <c r="C966" t="s">
-        <v>1962</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="967" spans="1:3">
@@ -16969,7 +16921,7 @@
         <v>990</v>
       </c>
       <c r="C967" t="s">
-        <v>1963</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="968" spans="1:3">
@@ -16980,7 +16932,7 @@
         <v>991</v>
       </c>
       <c r="C968" t="s">
-        <v>1964</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="969" spans="1:3">
@@ -16991,7 +16943,7 @@
         <v>992</v>
       </c>
       <c r="C969" t="s">
-        <v>1965</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="970" spans="1:3">
@@ -17002,7 +16954,7 @@
         <v>993</v>
       </c>
       <c r="C970" t="s">
-        <v>1966</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="971" spans="1:3">
@@ -17013,7 +16965,7 @@
         <v>994</v>
       </c>
       <c r="C971" t="s">
-        <v>1967</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="972" spans="1:3">
@@ -17024,7 +16976,7 @@
         <v>995</v>
       </c>
       <c r="C972" t="s">
-        <v>1968</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="973" spans="1:3">
@@ -17035,7 +16987,7 @@
         <v>996</v>
       </c>
       <c r="C973" t="s">
-        <v>1969</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="974" spans="1:3">
@@ -17046,7 +16998,7 @@
         <v>997</v>
       </c>
       <c r="C974" t="s">
-        <v>1970</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="975" spans="1:3">
@@ -17057,7 +17009,7 @@
         <v>998</v>
       </c>
       <c r="C975" t="s">
-        <v>1971</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="976" spans="1:3">
@@ -17068,7 +17020,7 @@
         <v>999</v>
       </c>
       <c r="C976" t="s">
-        <v>1972</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="977" spans="1:3">
@@ -17079,7 +17031,7 @@
         <v>1000</v>
       </c>
       <c r="C977" t="s">
-        <v>1973</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="978" spans="1:3">
@@ -17090,7 +17042,7 @@
         <v>1001</v>
       </c>
       <c r="C978" t="s">
-        <v>1974</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="979" spans="1:3">
@@ -17101,7 +17053,7 @@
         <v>1002</v>
       </c>
       <c r="C979" t="s">
-        <v>1975</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="980" spans="1:3">
@@ -17112,7 +17064,7 @@
         <v>1003</v>
       </c>
       <c r="C980" t="s">
-        <v>1976</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="981" spans="1:3">
@@ -17123,106 +17075,18 @@
         <v>1004</v>
       </c>
       <c r="C981" t="s">
-        <v>1977</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="982" spans="1:3">
       <c r="A982" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B982" t="s">
         <v>1005</v>
       </c>
       <c r="C982" t="s">
-        <v>1978</v>
-      </c>
-    </row>
-    <row r="983" spans="1:3">
-      <c r="A983" t="s">
-        <v>23</v>
-      </c>
-      <c r="B983" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C983" t="s">
-        <v>1979</v>
-      </c>
-    </row>
-    <row r="984" spans="1:3">
-      <c r="A984" t="s">
-        <v>23</v>
-      </c>
-      <c r="B984" t="s">
-        <v>1007</v>
-      </c>
-      <c r="C984" t="s">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="985" spans="1:3">
-      <c r="A985" t="s">
-        <v>23</v>
-      </c>
-      <c r="B985" t="s">
-        <v>1008</v>
-      </c>
-      <c r="C985" t="s">
-        <v>1981</v>
-      </c>
-    </row>
-    <row r="986" spans="1:3">
-      <c r="A986" t="s">
-        <v>23</v>
-      </c>
-      <c r="B986" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C986" t="s">
-        <v>1982</v>
-      </c>
-    </row>
-    <row r="987" spans="1:3">
-      <c r="A987" t="s">
-        <v>23</v>
-      </c>
-      <c r="B987" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C987" t="s">
-        <v>1983</v>
-      </c>
-    </row>
-    <row r="988" spans="1:3">
-      <c r="A988" t="s">
-        <v>23</v>
-      </c>
-      <c r="B988" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C988" t="s">
-        <v>1984</v>
-      </c>
-    </row>
-    <row r="989" spans="1:3">
-      <c r="A989" t="s">
-        <v>23</v>
-      </c>
-      <c r="B989" t="s">
-        <v>1012</v>
-      </c>
-      <c r="C989" t="s">
-        <v>1985</v>
-      </c>
-    </row>
-    <row r="990" spans="1:3">
-      <c r="A990" t="s">
-        <v>24</v>
-      </c>
-      <c r="B990" t="s">
-        <v>1013</v>
-      </c>
-      <c r="C990" t="s">
-        <v>1986</v>
+        <v>1970</v>
       </c>
     </row>
   </sheetData>

--- a/faltantes_por_estados.xlsx
+++ b/faltantes_por_estados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2946" uniqueCount="1971">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2880" uniqueCount="1928">
   <si>
     <t>entidad</t>
   </si>
@@ -319,9 +319,6 @@
     <t>BSIMB000211</t>
   </si>
   <si>
-    <t>BSIMB000235</t>
-  </si>
-  <si>
     <t>BSIMB000264</t>
   </si>
   <si>
@@ -1606,12 +1603,6 @@
     <t>HGIMB002456</t>
   </si>
   <si>
-    <t>HGIMB003774</t>
-  </si>
-  <si>
-    <t>HGIMB003844</t>
-  </si>
-  <si>
     <t>HGIMB003890</t>
   </si>
   <si>
@@ -1621,12 +1612,6 @@
     <t>MCIMB001713</t>
   </si>
   <si>
-    <t>MCIMB002075</t>
-  </si>
-  <si>
-    <t>MCIMB002080</t>
-  </si>
-  <si>
     <t>MCIMB002092</t>
   </si>
   <si>
@@ -1657,24 +1642,6 @@
     <t>MCIMB002203</t>
   </si>
   <si>
-    <t>MCIMB002442</t>
-  </si>
-  <si>
-    <t>MCIMB002466</t>
-  </si>
-  <si>
-    <t>MCIMB002471</t>
-  </si>
-  <si>
-    <t>MCIMB002483</t>
-  </si>
-  <si>
-    <t>MCIMB002495</t>
-  </si>
-  <si>
-    <t>MCIMB002500</t>
-  </si>
-  <si>
     <t>MCIMB003854</t>
   </si>
   <si>
@@ -1684,33 +1651,9 @@
     <t>MCIMB005382</t>
   </si>
   <si>
-    <t>MCIMB008054</t>
-  </si>
-  <si>
-    <t>MCIMB008066</t>
-  </si>
-  <si>
-    <t>MCIMB008071</t>
-  </si>
-  <si>
-    <t>MCIMB008865</t>
-  </si>
-  <si>
-    <t>MCIMB008870</t>
-  </si>
-  <si>
-    <t>MCIMB008882</t>
-  </si>
-  <si>
     <t>MCIMB008906</t>
   </si>
   <si>
-    <t>MCIMB009010</t>
-  </si>
-  <si>
-    <t>MCIMB009244</t>
-  </si>
-  <si>
     <t>MCIMB009565</t>
   </si>
   <si>
@@ -1720,9 +1663,6 @@
     <t>MCIMB009582</t>
   </si>
   <si>
-    <t>MCIMB010026</t>
-  </si>
-  <si>
     <t>MCIMB011093</t>
   </si>
   <si>
@@ -2101,12 +2041,6 @@
     <t>SPIMB001944</t>
   </si>
   <si>
-    <t>SLIMB000801</t>
-  </si>
-  <si>
-    <t>SLIMB001472</t>
-  </si>
-  <si>
     <t>SLIMB001781</t>
   </si>
   <si>
@@ -3247,9 +3181,6 @@
     <t>CENTRO DE SALUD FLORES MAGÓN, LA PAZ</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD LÁZARO CÁRDENAS, LA PAZ</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD LAS POCITAS</t>
   </si>
   <si>
@@ -4519,12 +4450,6 @@
     <t>GUAYABOS</t>
   </si>
   <si>
-    <t>XITHEJE DE REFORMA</t>
-  </si>
-  <si>
-    <t>TULANCINGO</t>
-  </si>
-  <si>
     <t>EJIDO EL PARAÍSO</t>
   </si>
   <si>
@@ -4534,12 +4459,6 @@
     <t>CEAPS SAN MIGUEL CHAPULTEPEC BICENTENARIO</t>
   </si>
   <si>
-    <t>JARDINES DE MORELOS</t>
-  </si>
-  <si>
-    <t>JOSÉ MA.MORELOS Y PAVÓN</t>
-  </si>
-  <si>
     <t>SANTA CLARA</t>
   </si>
   <si>
@@ -4570,24 +4489,6 @@
     <t>SANTA MARÍA TULPETLAC</t>
   </si>
   <si>
-    <t>COLONIA VALLE VERDE</t>
-  </si>
-  <si>
-    <t>ALFREDO DEL MAZO</t>
-  </si>
-  <si>
-    <t>COLONIA AYOTLA</t>
-  </si>
-  <si>
-    <t>LOMA BONITA</t>
-  </si>
-  <si>
-    <t>EL MOLINITO</t>
-  </si>
-  <si>
-    <t>COLONIA TEJOLOTE</t>
-  </si>
-  <si>
     <t>OLIMPIADA 68</t>
   </si>
   <si>
@@ -4597,30 +4498,9 @@
     <t>CEAPS TEMAMATLA</t>
   </si>
   <si>
-    <t>COLONIA SANTIAGO</t>
-  </si>
-  <si>
-    <t>COLONIA MARÍA ISABEL</t>
-  </si>
-  <si>
-    <t>COLONIA SAN ISIDRO</t>
-  </si>
-  <si>
-    <t>CITLALMINA</t>
-  </si>
-  <si>
-    <t>COL. DARÍO MARTÍNEZ</t>
-  </si>
-  <si>
-    <t>COL. SAN JUAN TLALPIZAHUAC</t>
-  </si>
-  <si>
     <t>COL. TEJALPA</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD CUATRO VIENTOS</t>
-  </si>
-  <si>
     <t>CENTRO DE SALUD LOS HÉROES</t>
   </si>
   <si>
@@ -4630,9 +4510,6 @@
     <t>CENTRO DE SALUD LUIS CÓRDOVA</t>
   </si>
   <si>
-    <t>CENTRO DE SALUD MELCHOR OCAMPO</t>
-  </si>
-  <si>
     <t>CSU VISIÓN MUNDIAL, PLAN DE AYALA</t>
   </si>
   <si>
@@ -5006,12 +4883,6 @@
   </si>
   <si>
     <t>SAN NICOLÁS DE LOS MONTES</t>
-  </si>
-  <si>
-    <t>QUILA</t>
-  </si>
-  <si>
-    <t>LA NORIA DE SAN ANTONIO (LA NORIA)</t>
   </si>
   <si>
     <t>COLONIA VEINTISIETE DE NOVIEMBRE</t>
@@ -6284,7 +6155,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C982"/>
+  <dimension ref="A1:C960"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6306,7 +6177,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>1006</v>
+        <v>984</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6317,7 +6188,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>1007</v>
+        <v>985</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6328,7 +6199,7 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>1008</v>
+        <v>986</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6339,7 +6210,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>1009</v>
+        <v>987</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6350,7 +6221,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>1010</v>
+        <v>988</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6361,7 +6232,7 @@
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>1011</v>
+        <v>989</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6372,7 +6243,7 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>1012</v>
+        <v>990</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6383,7 +6254,7 @@
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>1013</v>
+        <v>991</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6394,7 +6265,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>1014</v>
+        <v>992</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6405,7 +6276,7 @@
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>1015</v>
+        <v>993</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6416,7 +6287,7 @@
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>1016</v>
+        <v>994</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6427,7 +6298,7 @@
         <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>1017</v>
+        <v>995</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6438,7 +6309,7 @@
         <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>1018</v>
+        <v>996</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6449,7 +6320,7 @@
         <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>1019</v>
+        <v>997</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -6460,7 +6331,7 @@
         <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>1020</v>
+        <v>998</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6482,7 +6353,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>1021</v>
+        <v>999</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6493,7 +6364,7 @@
         <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>1022</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6504,7 +6375,7 @@
         <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>1023</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6515,7 +6386,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>1024</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6526,7 +6397,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>1025</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6537,7 +6408,7 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>1026</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6548,7 +6419,7 @@
         <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>1027</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6559,7 +6430,7 @@
         <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>1028</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -6570,7 +6441,7 @@
         <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>1029</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6592,7 +6463,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="s">
-        <v>1030</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6614,7 +6485,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="s">
-        <v>1031</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -6625,7 +6496,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="s">
-        <v>1032</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -6636,7 +6507,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="s">
-        <v>1021</v>
+        <v>999</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -6647,7 +6518,7 @@
         <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>1033</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6658,7 +6529,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="s">
-        <v>1034</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -6669,7 +6540,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="s">
-        <v>1035</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6680,7 +6551,7 @@
         <v>59</v>
       </c>
       <c r="C36" t="s">
-        <v>1036</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6691,7 +6562,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="s">
-        <v>1037</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -6702,7 +6573,7 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>1038</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -6713,7 +6584,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="s">
-        <v>1039</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -6724,7 +6595,7 @@
         <v>63</v>
       </c>
       <c r="C40" t="s">
-        <v>1040</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -6735,7 +6606,7 @@
         <v>64</v>
       </c>
       <c r="C41" t="s">
-        <v>1041</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -6746,7 +6617,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="s">
-        <v>1042</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -6757,7 +6628,7 @@
         <v>66</v>
       </c>
       <c r="C43" t="s">
-        <v>1043</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -6768,7 +6639,7 @@
         <v>67</v>
       </c>
       <c r="C44" t="s">
-        <v>1044</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -6779,7 +6650,7 @@
         <v>68</v>
       </c>
       <c r="C45" t="s">
-        <v>1045</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -6790,7 +6661,7 @@
         <v>69</v>
       </c>
       <c r="C46" t="s">
-        <v>1046</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -6801,7 +6672,7 @@
         <v>70</v>
       </c>
       <c r="C47" t="s">
-        <v>1047</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -6812,7 +6683,7 @@
         <v>71</v>
       </c>
       <c r="C48" t="s">
-        <v>1048</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -6823,7 +6694,7 @@
         <v>72</v>
       </c>
       <c r="C49" t="s">
-        <v>1049</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -6834,7 +6705,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>1050</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -6845,7 +6716,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="s">
-        <v>1051</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -6856,7 +6727,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="s">
-        <v>1052</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -6867,7 +6738,7 @@
         <v>76</v>
       </c>
       <c r="C53" t="s">
-        <v>1053</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -6878,7 +6749,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="s">
-        <v>1054</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -6889,7 +6760,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="s">
-        <v>1055</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -6900,7 +6771,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="s">
-        <v>1056</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -6911,7 +6782,7 @@
         <v>80</v>
       </c>
       <c r="C57" t="s">
-        <v>1057</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -6922,7 +6793,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="s">
-        <v>1058</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -6933,7 +6804,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="s">
-        <v>1059</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -6955,7 +6826,7 @@
         <v>84</v>
       </c>
       <c r="C61" t="s">
-        <v>1060</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -6966,7 +6837,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="s">
-        <v>1061</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -6977,7 +6848,7 @@
         <v>86</v>
       </c>
       <c r="C63" t="s">
-        <v>1062</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -6988,7 +6859,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="s">
-        <v>1063</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -6999,7 +6870,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="s">
-        <v>1064</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -7010,7 +6881,7 @@
         <v>89</v>
       </c>
       <c r="C66" t="s">
-        <v>1065</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -7021,7 +6892,7 @@
         <v>90</v>
       </c>
       <c r="C67" t="s">
-        <v>1066</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -7032,7 +6903,7 @@
         <v>91</v>
       </c>
       <c r="C68" t="s">
-        <v>1067</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -7043,7 +6914,7 @@
         <v>92</v>
       </c>
       <c r="C69" t="s">
-        <v>1068</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -7054,7 +6925,7 @@
         <v>93</v>
       </c>
       <c r="C70" t="s">
-        <v>1069</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -7065,7 +6936,7 @@
         <v>94</v>
       </c>
       <c r="C71" t="s">
-        <v>1070</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -7076,7 +6947,7 @@
         <v>95</v>
       </c>
       <c r="C72" t="s">
-        <v>1071</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -7087,7 +6958,7 @@
         <v>96</v>
       </c>
       <c r="C73" t="s">
-        <v>1072</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -7098,7 +6969,7 @@
         <v>97</v>
       </c>
       <c r="C74" t="s">
-        <v>1073</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -7109,7 +6980,7 @@
         <v>98</v>
       </c>
       <c r="C75" t="s">
-        <v>1074</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -7120,7 +6991,7 @@
         <v>99</v>
       </c>
       <c r="C76" t="s">
-        <v>1075</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -7131,7 +7002,7 @@
         <v>100</v>
       </c>
       <c r="C77" t="s">
-        <v>1076</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -7142,7 +7013,7 @@
         <v>101</v>
       </c>
       <c r="C78" t="s">
-        <v>1077</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -7153,7 +7024,7 @@
         <v>102</v>
       </c>
       <c r="C79" t="s">
-        <v>1078</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -7164,7 +7035,7 @@
         <v>103</v>
       </c>
       <c r="C80" t="s">
-        <v>1079</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -7175,7 +7046,7 @@
         <v>104</v>
       </c>
       <c r="C81" t="s">
-        <v>1080</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -7186,7 +7057,7 @@
         <v>105</v>
       </c>
       <c r="C82" t="s">
-        <v>1081</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -7197,7 +7068,7 @@
         <v>106</v>
       </c>
       <c r="C83" t="s">
-        <v>1082</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -7208,7 +7079,7 @@
         <v>107</v>
       </c>
       <c r="C84" t="s">
-        <v>1083</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -7219,7 +7090,7 @@
         <v>108</v>
       </c>
       <c r="C85" t="s">
-        <v>1084</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -7230,7 +7101,7 @@
         <v>109</v>
       </c>
       <c r="C86" t="s">
-        <v>1085</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -7241,7 +7112,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="s">
-        <v>1086</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -7252,7 +7123,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="s">
-        <v>1087</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -7263,7 +7134,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="s">
-        <v>1088</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -7274,7 +7145,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="s">
-        <v>1089</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -7285,7 +7156,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="s">
-        <v>1090</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -7296,7 +7167,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="s">
-        <v>1091</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -7307,7 +7178,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="s">
-        <v>1092</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -7318,7 +7189,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="s">
-        <v>1093</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -7329,7 +7200,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="s">
-        <v>1094</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -7340,7 +7211,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="s">
-        <v>1095</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -7351,7 +7222,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="s">
-        <v>1096</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -7362,7 +7233,7 @@
         <v>121</v>
       </c>
       <c r="C98" t="s">
-        <v>1097</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -7373,7 +7244,7 @@
         <v>122</v>
       </c>
       <c r="C99" t="s">
-        <v>1098</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -7384,7 +7255,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="s">
-        <v>1099</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -7395,18 +7266,18 @@
         <v>124</v>
       </c>
       <c r="C101" t="s">
-        <v>1100</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B102" t="s">
         <v>125</v>
       </c>
       <c r="C102" t="s">
-        <v>1101</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -7417,7 +7288,7 @@
         <v>126</v>
       </c>
       <c r="C103" t="s">
-        <v>1102</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="104" spans="1:3">
@@ -7428,7 +7299,7 @@
         <v>127</v>
       </c>
       <c r="C104" t="s">
-        <v>1103</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -7439,7 +7310,7 @@
         <v>128</v>
       </c>
       <c r="C105" t="s">
-        <v>1104</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -7450,7 +7321,7 @@
         <v>129</v>
       </c>
       <c r="C106" t="s">
-        <v>1105</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -7461,7 +7332,7 @@
         <v>130</v>
       </c>
       <c r="C107" t="s">
-        <v>1106</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -7472,7 +7343,7 @@
         <v>131</v>
       </c>
       <c r="C108" t="s">
-        <v>1107</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -7483,7 +7354,7 @@
         <v>132</v>
       </c>
       <c r="C109" t="s">
-        <v>1108</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -7494,7 +7365,7 @@
         <v>133</v>
       </c>
       <c r="C110" t="s">
-        <v>1109</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -7505,7 +7376,7 @@
         <v>134</v>
       </c>
       <c r="C111" t="s">
-        <v>1110</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -7516,7 +7387,7 @@
         <v>135</v>
       </c>
       <c r="C112" t="s">
-        <v>1111</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -7527,7 +7398,7 @@
         <v>136</v>
       </c>
       <c r="C113" t="s">
-        <v>1112</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -7538,7 +7409,7 @@
         <v>137</v>
       </c>
       <c r="C114" t="s">
-        <v>1113</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -7549,7 +7420,7 @@
         <v>138</v>
       </c>
       <c r="C115" t="s">
-        <v>1114</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -7560,29 +7431,29 @@
         <v>139</v>
       </c>
       <c r="C116" t="s">
-        <v>1115</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B117" t="s">
         <v>140</v>
       </c>
       <c r="C117" t="s">
-        <v>1116</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B118" t="s">
         <v>141</v>
       </c>
       <c r="C118" t="s">
-        <v>1117</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -7593,7 +7464,7 @@
         <v>142</v>
       </c>
       <c r="C119" t="s">
-        <v>1118</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -7604,7 +7475,7 @@
         <v>143</v>
       </c>
       <c r="C120" t="s">
-        <v>1119</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -7615,7 +7486,7 @@
         <v>144</v>
       </c>
       <c r="C121" t="s">
-        <v>1120</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -7626,7 +7497,7 @@
         <v>145</v>
       </c>
       <c r="C122" t="s">
-        <v>1121</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -7637,7 +7508,7 @@
         <v>146</v>
       </c>
       <c r="C123" t="s">
-        <v>1122</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -7648,7 +7519,7 @@
         <v>147</v>
       </c>
       <c r="C124" t="s">
-        <v>1123</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -7659,7 +7530,7 @@
         <v>148</v>
       </c>
       <c r="C125" t="s">
-        <v>1124</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -7670,7 +7541,7 @@
         <v>149</v>
       </c>
       <c r="C126" t="s">
-        <v>1125</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -7681,7 +7552,7 @@
         <v>150</v>
       </c>
       <c r="C127" t="s">
-        <v>1126</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -7692,7 +7563,7 @@
         <v>151</v>
       </c>
       <c r="C128" t="s">
-        <v>1127</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -7703,7 +7574,7 @@
         <v>152</v>
       </c>
       <c r="C129" t="s">
-        <v>1128</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -7714,7 +7585,7 @@
         <v>153</v>
       </c>
       <c r="C130" t="s">
-        <v>1129</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -7725,7 +7596,7 @@
         <v>154</v>
       </c>
       <c r="C131" t="s">
-        <v>1130</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -7736,7 +7607,7 @@
         <v>155</v>
       </c>
       <c r="C132" t="s">
-        <v>1131</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -7747,7 +7618,7 @@
         <v>156</v>
       </c>
       <c r="C133" t="s">
-        <v>1132</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -7758,7 +7629,7 @@
         <v>157</v>
       </c>
       <c r="C134" t="s">
-        <v>1133</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -7769,7 +7640,7 @@
         <v>158</v>
       </c>
       <c r="C135" t="s">
-        <v>1134</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -7780,7 +7651,7 @@
         <v>159</v>
       </c>
       <c r="C136" t="s">
-        <v>1135</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -7791,7 +7662,7 @@
         <v>160</v>
       </c>
       <c r="C137" t="s">
-        <v>1136</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -7802,7 +7673,7 @@
         <v>161</v>
       </c>
       <c r="C138" t="s">
-        <v>1137</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -7813,7 +7684,7 @@
         <v>162</v>
       </c>
       <c r="C139" t="s">
-        <v>1138</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -7824,7 +7695,7 @@
         <v>163</v>
       </c>
       <c r="C140" t="s">
-        <v>1139</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -7835,7 +7706,7 @@
         <v>164</v>
       </c>
       <c r="C141" t="s">
-        <v>1140</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -7846,7 +7717,7 @@
         <v>165</v>
       </c>
       <c r="C142" t="s">
-        <v>1141</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -7857,7 +7728,7 @@
         <v>166</v>
       </c>
       <c r="C143" t="s">
-        <v>1142</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -7868,7 +7739,7 @@
         <v>167</v>
       </c>
       <c r="C144" t="s">
-        <v>1143</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -7879,7 +7750,7 @@
         <v>168</v>
       </c>
       <c r="C145" t="s">
-        <v>1144</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -7890,7 +7761,7 @@
         <v>169</v>
       </c>
       <c r="C146" t="s">
-        <v>1145</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -7901,7 +7772,7 @@
         <v>170</v>
       </c>
       <c r="C147" t="s">
-        <v>1146</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -7912,7 +7783,7 @@
         <v>171</v>
       </c>
       <c r="C148" t="s">
-        <v>1147</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -7923,7 +7794,7 @@
         <v>172</v>
       </c>
       <c r="C149" t="s">
-        <v>1148</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -7934,7 +7805,7 @@
         <v>173</v>
       </c>
       <c r="C150" t="s">
-        <v>1149</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -7945,7 +7816,7 @@
         <v>174</v>
       </c>
       <c r="C151" t="s">
-        <v>1150</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -7956,7 +7827,7 @@
         <v>175</v>
       </c>
       <c r="C152" t="s">
-        <v>1151</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -7967,7 +7838,7 @@
         <v>176</v>
       </c>
       <c r="C153" t="s">
-        <v>1152</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -7978,7 +7849,7 @@
         <v>177</v>
       </c>
       <c r="C154" t="s">
-        <v>1153</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -7989,7 +7860,7 @@
         <v>178</v>
       </c>
       <c r="C155" t="s">
-        <v>1154</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -8000,7 +7871,7 @@
         <v>179</v>
       </c>
       <c r="C156" t="s">
-        <v>1155</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -8011,7 +7882,7 @@
         <v>180</v>
       </c>
       <c r="C157" t="s">
-        <v>1156</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -8022,7 +7893,7 @@
         <v>181</v>
       </c>
       <c r="C158" t="s">
-        <v>1157</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -8033,7 +7904,7 @@
         <v>182</v>
       </c>
       <c r="C159" t="s">
-        <v>1158</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -8044,7 +7915,7 @@
         <v>183</v>
       </c>
       <c r="C160" t="s">
-        <v>1159</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -8055,7 +7926,7 @@
         <v>184</v>
       </c>
       <c r="C161" t="s">
-        <v>1160</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -8066,7 +7937,7 @@
         <v>185</v>
       </c>
       <c r="C162" t="s">
-        <v>1161</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -8077,7 +7948,7 @@
         <v>186</v>
       </c>
       <c r="C163" t="s">
-        <v>1162</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -8088,7 +7959,7 @@
         <v>187</v>
       </c>
       <c r="C164" t="s">
-        <v>1163</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -8099,7 +7970,7 @@
         <v>188</v>
       </c>
       <c r="C165" t="s">
-        <v>1164</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -8110,7 +7981,7 @@
         <v>189</v>
       </c>
       <c r="C166" t="s">
-        <v>1165</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="167" spans="1:3">
@@ -8121,7 +7992,7 @@
         <v>190</v>
       </c>
       <c r="C167" t="s">
-        <v>1166</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="168" spans="1:3">
@@ -8132,7 +8003,7 @@
         <v>191</v>
       </c>
       <c r="C168" t="s">
-        <v>1167</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="169" spans="1:3">
@@ -8143,7 +8014,7 @@
         <v>192</v>
       </c>
       <c r="C169" t="s">
-        <v>1168</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="170" spans="1:3">
@@ -8154,7 +8025,7 @@
         <v>193</v>
       </c>
       <c r="C170" t="s">
-        <v>1169</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="171" spans="1:3">
@@ -8165,7 +8036,7 @@
         <v>194</v>
       </c>
       <c r="C171" t="s">
-        <v>1170</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="172" spans="1:3">
@@ -8176,7 +8047,7 @@
         <v>195</v>
       </c>
       <c r="C172" t="s">
-        <v>1171</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="173" spans="1:3">
@@ -8187,7 +8058,7 @@
         <v>196</v>
       </c>
       <c r="C173" t="s">
-        <v>1172</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="174" spans="1:3">
@@ -8198,7 +8069,7 @@
         <v>197</v>
       </c>
       <c r="C174" t="s">
-        <v>1173</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -8209,7 +8080,7 @@
         <v>198</v>
       </c>
       <c r="C175" t="s">
-        <v>1174</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="176" spans="1:3">
@@ -8220,7 +8091,7 @@
         <v>199</v>
       </c>
       <c r="C176" t="s">
-        <v>1175</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -8231,7 +8102,7 @@
         <v>200</v>
       </c>
       <c r="C177" t="s">
-        <v>1176</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -8242,7 +8113,7 @@
         <v>201</v>
       </c>
       <c r="C178" t="s">
-        <v>1177</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="179" spans="1:3">
@@ -8253,7 +8124,7 @@
         <v>202</v>
       </c>
       <c r="C179" t="s">
-        <v>1178</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="180" spans="1:3">
@@ -8264,7 +8135,7 @@
         <v>203</v>
       </c>
       <c r="C180" t="s">
-        <v>1179</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="181" spans="1:3">
@@ -8275,7 +8146,7 @@
         <v>204</v>
       </c>
       <c r="C181" t="s">
-        <v>1180</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -8286,7 +8157,7 @@
         <v>205</v>
       </c>
       <c r="C182" t="s">
-        <v>1181</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -8297,7 +8168,7 @@
         <v>206</v>
       </c>
       <c r="C183" t="s">
-        <v>1182</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -8308,7 +8179,7 @@
         <v>207</v>
       </c>
       <c r="C184" t="s">
-        <v>1183</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -8319,7 +8190,7 @@
         <v>208</v>
       </c>
       <c r="C185" t="s">
-        <v>1184</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -8330,7 +8201,7 @@
         <v>209</v>
       </c>
       <c r="C186" t="s">
-        <v>1185</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -8341,7 +8212,7 @@
         <v>210</v>
       </c>
       <c r="C187" t="s">
-        <v>1186</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -8352,7 +8223,7 @@
         <v>211</v>
       </c>
       <c r="C188" t="s">
-        <v>1187</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -8363,7 +8234,7 @@
         <v>212</v>
       </c>
       <c r="C189" t="s">
-        <v>1188</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -8374,7 +8245,7 @@
         <v>213</v>
       </c>
       <c r="C190" t="s">
-        <v>1189</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -8385,7 +8256,7 @@
         <v>214</v>
       </c>
       <c r="C191" t="s">
-        <v>1190</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -8396,7 +8267,7 @@
         <v>215</v>
       </c>
       <c r="C192" t="s">
-        <v>1191</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -8407,7 +8278,7 @@
         <v>216</v>
       </c>
       <c r="C193" t="s">
-        <v>1192</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -8418,7 +8289,7 @@
         <v>217</v>
       </c>
       <c r="C194" t="s">
-        <v>1193</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -8429,7 +8300,7 @@
         <v>218</v>
       </c>
       <c r="C195" t="s">
-        <v>1194</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -8440,7 +8311,7 @@
         <v>219</v>
       </c>
       <c r="C196" t="s">
-        <v>1195</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -8451,7 +8322,7 @@
         <v>220</v>
       </c>
       <c r="C197" t="s">
-        <v>1196</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -8462,7 +8333,7 @@
         <v>221</v>
       </c>
       <c r="C198" t="s">
-        <v>1197</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -8473,7 +8344,7 @@
         <v>222</v>
       </c>
       <c r="C199" t="s">
-        <v>1198</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -8484,7 +8355,7 @@
         <v>223</v>
       </c>
       <c r="C200" t="s">
-        <v>1199</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -8495,7 +8366,7 @@
         <v>224</v>
       </c>
       <c r="C201" t="s">
-        <v>1200</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -8506,7 +8377,7 @@
         <v>225</v>
       </c>
       <c r="C202" t="s">
-        <v>1201</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -8517,7 +8388,7 @@
         <v>226</v>
       </c>
       <c r="C203" t="s">
-        <v>1202</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -8528,7 +8399,7 @@
         <v>227</v>
       </c>
       <c r="C204" t="s">
-        <v>1203</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -8539,7 +8410,7 @@
         <v>228</v>
       </c>
       <c r="C205" t="s">
-        <v>1204</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -8550,7 +8421,7 @@
         <v>229</v>
       </c>
       <c r="C206" t="s">
-        <v>1205</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -8561,7 +8432,7 @@
         <v>230</v>
       </c>
       <c r="C207" t="s">
-        <v>1206</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -8572,7 +8443,7 @@
         <v>231</v>
       </c>
       <c r="C208" t="s">
-        <v>1207</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -8583,7 +8454,7 @@
         <v>232</v>
       </c>
       <c r="C209" t="s">
-        <v>1208</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -8594,7 +8465,7 @@
         <v>233</v>
       </c>
       <c r="C210" t="s">
-        <v>1209</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -8605,7 +8476,7 @@
         <v>234</v>
       </c>
       <c r="C211" t="s">
-        <v>1210</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -8616,7 +8487,7 @@
         <v>235</v>
       </c>
       <c r="C212" t="s">
-        <v>1211</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -8627,7 +8498,7 @@
         <v>236</v>
       </c>
       <c r="C213" t="s">
-        <v>1212</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -8638,7 +8509,7 @@
         <v>237</v>
       </c>
       <c r="C214" t="s">
-        <v>1213</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -8649,7 +8520,7 @@
         <v>238</v>
       </c>
       <c r="C215" t="s">
-        <v>1214</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -8660,7 +8531,7 @@
         <v>239</v>
       </c>
       <c r="C216" t="s">
-        <v>1215</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -8671,7 +8542,7 @@
         <v>240</v>
       </c>
       <c r="C217" t="s">
-        <v>1216</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -8682,7 +8553,7 @@
         <v>241</v>
       </c>
       <c r="C218" t="s">
-        <v>1217</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -8693,7 +8564,7 @@
         <v>242</v>
       </c>
       <c r="C219" t="s">
-        <v>1218</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -8704,7 +8575,7 @@
         <v>243</v>
       </c>
       <c r="C220" t="s">
-        <v>1219</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -8715,7 +8586,7 @@
         <v>244</v>
       </c>
       <c r="C221" t="s">
-        <v>1220</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -8726,7 +8597,7 @@
         <v>245</v>
       </c>
       <c r="C222" t="s">
-        <v>1221</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -8737,7 +8608,7 @@
         <v>246</v>
       </c>
       <c r="C223" t="s">
-        <v>1222</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -8748,7 +8619,7 @@
         <v>247</v>
       </c>
       <c r="C224" t="s">
-        <v>1223</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -8759,7 +8630,7 @@
         <v>248</v>
       </c>
       <c r="C225" t="s">
-        <v>1224</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -8770,7 +8641,7 @@
         <v>249</v>
       </c>
       <c r="C226" t="s">
-        <v>1225</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -8781,7 +8652,7 @@
         <v>250</v>
       </c>
       <c r="C227" t="s">
-        <v>1226</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -8792,7 +8663,7 @@
         <v>251</v>
       </c>
       <c r="C228" t="s">
-        <v>1227</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -8803,7 +8674,7 @@
         <v>252</v>
       </c>
       <c r="C229" t="s">
-        <v>1228</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -8814,7 +8685,7 @@
         <v>253</v>
       </c>
       <c r="C230" t="s">
-        <v>1229</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -8825,7 +8696,7 @@
         <v>254</v>
       </c>
       <c r="C231" t="s">
-        <v>1230</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -8836,7 +8707,7 @@
         <v>255</v>
       </c>
       <c r="C232" t="s">
-        <v>1231</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -8847,7 +8718,7 @@
         <v>256</v>
       </c>
       <c r="C233" t="s">
-        <v>1232</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -8858,7 +8729,7 @@
         <v>257</v>
       </c>
       <c r="C234" t="s">
-        <v>1233</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -8869,7 +8740,7 @@
         <v>258</v>
       </c>
       <c r="C235" t="s">
-        <v>1234</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -8880,7 +8751,7 @@
         <v>259</v>
       </c>
       <c r="C236" t="s">
-        <v>1235</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -8891,7 +8762,7 @@
         <v>260</v>
       </c>
       <c r="C237" t="s">
-        <v>1236</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -8902,7 +8773,7 @@
         <v>261</v>
       </c>
       <c r="C238" t="s">
-        <v>1237</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -8913,7 +8784,7 @@
         <v>262</v>
       </c>
       <c r="C239" t="s">
-        <v>1238</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -8924,7 +8795,7 @@
         <v>263</v>
       </c>
       <c r="C240" t="s">
-        <v>1239</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -8935,7 +8806,7 @@
         <v>264</v>
       </c>
       <c r="C241" t="s">
-        <v>1240</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -8946,7 +8817,7 @@
         <v>265</v>
       </c>
       <c r="C242" t="s">
-        <v>1241</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -8957,7 +8828,7 @@
         <v>266</v>
       </c>
       <c r="C243" t="s">
-        <v>1242</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -8968,7 +8839,7 @@
         <v>267</v>
       </c>
       <c r="C244" t="s">
-        <v>1243</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -8979,7 +8850,7 @@
         <v>268</v>
       </c>
       <c r="C245" t="s">
-        <v>1244</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -8990,7 +8861,7 @@
         <v>269</v>
       </c>
       <c r="C246" t="s">
-        <v>1245</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -9001,7 +8872,7 @@
         <v>270</v>
       </c>
       <c r="C247" t="s">
-        <v>1246</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -9012,7 +8883,7 @@
         <v>271</v>
       </c>
       <c r="C248" t="s">
-        <v>1247</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="249" spans="1:3">
@@ -9023,7 +8894,7 @@
         <v>272</v>
       </c>
       <c r="C249" t="s">
-        <v>1248</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="250" spans="1:3">
@@ -9034,7 +8905,7 @@
         <v>273</v>
       </c>
       <c r="C250" t="s">
-        <v>1249</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -9045,7 +8916,7 @@
         <v>274</v>
       </c>
       <c r="C251" t="s">
-        <v>1250</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -9056,7 +8927,7 @@
         <v>275</v>
       </c>
       <c r="C252" t="s">
-        <v>1251</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="253" spans="1:3">
@@ -9067,7 +8938,7 @@
         <v>276</v>
       </c>
       <c r="C253" t="s">
-        <v>1252</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="254" spans="1:3">
@@ -9078,7 +8949,7 @@
         <v>277</v>
       </c>
       <c r="C254" t="s">
-        <v>1253</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -9089,7 +8960,7 @@
         <v>278</v>
       </c>
       <c r="C255" t="s">
-        <v>1254</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -9100,7 +8971,7 @@
         <v>279</v>
       </c>
       <c r="C256" t="s">
-        <v>1255</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="257" spans="1:3">
@@ -9111,7 +8982,7 @@
         <v>280</v>
       </c>
       <c r="C257" t="s">
-        <v>1256</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -9122,7 +8993,7 @@
         <v>281</v>
       </c>
       <c r="C258" t="s">
-        <v>1257</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="259" spans="1:3">
@@ -9133,7 +9004,7 @@
         <v>282</v>
       </c>
       <c r="C259" t="s">
-        <v>1258</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -9144,7 +9015,7 @@
         <v>283</v>
       </c>
       <c r="C260" t="s">
-        <v>1259</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="261" spans="1:3">
@@ -9155,7 +9026,7 @@
         <v>284</v>
       </c>
       <c r="C261" t="s">
-        <v>1260</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="262" spans="1:3">
@@ -9166,7 +9037,7 @@
         <v>285</v>
       </c>
       <c r="C262" t="s">
-        <v>1261</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -9177,7 +9048,7 @@
         <v>286</v>
       </c>
       <c r="C263" t="s">
-        <v>1262</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="264" spans="1:3">
@@ -9188,7 +9059,7 @@
         <v>287</v>
       </c>
       <c r="C264" t="s">
-        <v>1263</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -9199,7 +9070,7 @@
         <v>288</v>
       </c>
       <c r="C265" t="s">
-        <v>1264</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="266" spans="1:3">
@@ -9210,7 +9081,7 @@
         <v>289</v>
       </c>
       <c r="C266" t="s">
-        <v>1265</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="267" spans="1:3">
@@ -9221,7 +9092,7 @@
         <v>290</v>
       </c>
       <c r="C267" t="s">
-        <v>1266</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="268" spans="1:3">
@@ -9232,7 +9103,7 @@
         <v>291</v>
       </c>
       <c r="C268" t="s">
-        <v>1267</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="269" spans="1:3">
@@ -9243,7 +9114,7 @@
         <v>292</v>
       </c>
       <c r="C269" t="s">
-        <v>1268</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="270" spans="1:3">
@@ -9254,7 +9125,7 @@
         <v>293</v>
       </c>
       <c r="C270" t="s">
-        <v>1269</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="271" spans="1:3">
@@ -9265,7 +9136,7 @@
         <v>294</v>
       </c>
       <c r="C271" t="s">
-        <v>1270</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="272" spans="1:3">
@@ -9276,7 +9147,7 @@
         <v>295</v>
       </c>
       <c r="C272" t="s">
-        <v>1271</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="273" spans="1:3">
@@ -9287,7 +9158,7 @@
         <v>296</v>
       </c>
       <c r="C273" t="s">
-        <v>1272</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="274" spans="1:3">
@@ -9298,7 +9169,7 @@
         <v>297</v>
       </c>
       <c r="C274" t="s">
-        <v>1273</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="275" spans="1:3">
@@ -9309,7 +9180,7 @@
         <v>298</v>
       </c>
       <c r="C275" t="s">
-        <v>1274</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="276" spans="1:3">
@@ -9320,7 +9191,7 @@
         <v>299</v>
       </c>
       <c r="C276" t="s">
-        <v>1192</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="277" spans="1:3">
@@ -9331,7 +9202,7 @@
         <v>300</v>
       </c>
       <c r="C277" t="s">
-        <v>1275</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="278" spans="1:3">
@@ -9342,7 +9213,7 @@
         <v>301</v>
       </c>
       <c r="C278" t="s">
-        <v>1276</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="279" spans="1:3">
@@ -9353,7 +9224,7 @@
         <v>302</v>
       </c>
       <c r="C279" t="s">
-        <v>1277</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="280" spans="1:3">
@@ -9364,7 +9235,7 @@
         <v>303</v>
       </c>
       <c r="C280" t="s">
-        <v>1278</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -9375,7 +9246,7 @@
         <v>304</v>
       </c>
       <c r="C281" t="s">
-        <v>1279</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="282" spans="1:3">
@@ -9386,7 +9257,7 @@
         <v>305</v>
       </c>
       <c r="C282" t="s">
-        <v>1280</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="283" spans="1:3">
@@ -9397,7 +9268,7 @@
         <v>306</v>
       </c>
       <c r="C283" t="s">
-        <v>1281</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="284" spans="1:3">
@@ -9408,7 +9279,7 @@
         <v>307</v>
       </c>
       <c r="C284" t="s">
-        <v>1282</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="285" spans="1:3">
@@ -9419,7 +9290,7 @@
         <v>308</v>
       </c>
       <c r="C285" t="s">
-        <v>1283</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="286" spans="1:3">
@@ -9430,7 +9301,7 @@
         <v>309</v>
       </c>
       <c r="C286" t="s">
-        <v>1284</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="287" spans="1:3">
@@ -9441,7 +9312,7 @@
         <v>310</v>
       </c>
       <c r="C287" t="s">
-        <v>1285</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="288" spans="1:3">
@@ -9452,7 +9323,7 @@
         <v>311</v>
       </c>
       <c r="C288" t="s">
-        <v>1286</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="289" spans="1:3">
@@ -9463,7 +9334,7 @@
         <v>312</v>
       </c>
       <c r="C289" t="s">
-        <v>1287</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="290" spans="1:3">
@@ -9474,7 +9345,7 @@
         <v>313</v>
       </c>
       <c r="C290" t="s">
-        <v>1288</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="291" spans="1:3">
@@ -9485,7 +9356,7 @@
         <v>314</v>
       </c>
       <c r="C291" t="s">
-        <v>1289</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="292" spans="1:3">
@@ -9496,7 +9367,7 @@
         <v>315</v>
       </c>
       <c r="C292" t="s">
-        <v>1290</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="293" spans="1:3">
@@ -9507,7 +9378,7 @@
         <v>316</v>
       </c>
       <c r="C293" t="s">
-        <v>1291</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="294" spans="1:3">
@@ -9518,7 +9389,7 @@
         <v>317</v>
       </c>
       <c r="C294" t="s">
-        <v>1292</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="295" spans="1:3">
@@ -9529,7 +9400,7 @@
         <v>318</v>
       </c>
       <c r="C295" t="s">
-        <v>1293</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="296" spans="1:3">
@@ -9540,7 +9411,7 @@
         <v>319</v>
       </c>
       <c r="C296" t="s">
-        <v>1294</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="297" spans="1:3">
@@ -9551,7 +9422,7 @@
         <v>320</v>
       </c>
       <c r="C297" t="s">
-        <v>1295</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="298" spans="1:3">
@@ -9562,7 +9433,7 @@
         <v>321</v>
       </c>
       <c r="C298" t="s">
-        <v>1296</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="299" spans="1:3">
@@ -9573,7 +9444,7 @@
         <v>322</v>
       </c>
       <c r="C299" t="s">
-        <v>1297</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="300" spans="1:3">
@@ -9584,7 +9455,7 @@
         <v>323</v>
       </c>
       <c r="C300" t="s">
-        <v>1298</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="301" spans="1:3">
@@ -9595,7 +9466,7 @@
         <v>324</v>
       </c>
       <c r="C301" t="s">
-        <v>1299</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -9606,7 +9477,7 @@
         <v>325</v>
       </c>
       <c r="C302" t="s">
-        <v>1300</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="303" spans="1:3">
@@ -9617,7 +9488,7 @@
         <v>326</v>
       </c>
       <c r="C303" t="s">
-        <v>1301</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="304" spans="1:3">
@@ -9628,7 +9499,7 @@
         <v>327</v>
       </c>
       <c r="C304" t="s">
-        <v>1302</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="305" spans="1:3">
@@ -9639,7 +9510,7 @@
         <v>328</v>
       </c>
       <c r="C305" t="s">
-        <v>1303</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="306" spans="1:3">
@@ -9650,7 +9521,7 @@
         <v>329</v>
       </c>
       <c r="C306" t="s">
-        <v>1304</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="307" spans="1:3">
@@ -9661,7 +9532,7 @@
         <v>330</v>
       </c>
       <c r="C307" t="s">
-        <v>1305</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="308" spans="1:3">
@@ -9672,7 +9543,7 @@
         <v>331</v>
       </c>
       <c r="C308" t="s">
-        <v>1306</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="309" spans="1:3">
@@ -9683,18 +9554,18 @@
         <v>332</v>
       </c>
       <c r="C309" t="s">
-        <v>1307</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="310" spans="1:3">
       <c r="A310" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B310" t="s">
         <v>333</v>
       </c>
       <c r="C310" t="s">
-        <v>1308</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="311" spans="1:3">
@@ -9705,7 +9576,7 @@
         <v>334</v>
       </c>
       <c r="C311" t="s">
-        <v>1309</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="312" spans="1:3">
@@ -9716,7 +9587,7 @@
         <v>335</v>
       </c>
       <c r="C312" t="s">
-        <v>1310</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="313" spans="1:3">
@@ -9727,7 +9598,7 @@
         <v>336</v>
       </c>
       <c r="C313" t="s">
-        <v>1311</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="314" spans="1:3">
@@ -9738,7 +9609,7 @@
         <v>337</v>
       </c>
       <c r="C314" t="s">
-        <v>1312</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="315" spans="1:3">
@@ -9749,7 +9620,7 @@
         <v>338</v>
       </c>
       <c r="C315" t="s">
-        <v>1313</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="316" spans="1:3">
@@ -9760,7 +9631,7 @@
         <v>339</v>
       </c>
       <c r="C316" t="s">
-        <v>1090</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="317" spans="1:3">
@@ -9771,7 +9642,7 @@
         <v>340</v>
       </c>
       <c r="C317" t="s">
-        <v>1314</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="318" spans="1:3">
@@ -9782,7 +9653,7 @@
         <v>341</v>
       </c>
       <c r="C318" t="s">
-        <v>1315</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="319" spans="1:3">
@@ -9793,7 +9664,7 @@
         <v>342</v>
       </c>
       <c r="C319" t="s">
-        <v>1316</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="320" spans="1:3">
@@ -9804,7 +9675,7 @@
         <v>343</v>
       </c>
       <c r="C320" t="s">
-        <v>1317</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="321" spans="1:3">
@@ -9815,7 +9686,7 @@
         <v>344</v>
       </c>
       <c r="C321" t="s">
-        <v>1318</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -9826,7 +9697,7 @@
         <v>345</v>
       </c>
       <c r="C322" t="s">
-        <v>1081</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="323" spans="1:3">
@@ -9837,7 +9708,7 @@
         <v>346</v>
       </c>
       <c r="C323" t="s">
-        <v>1319</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="324" spans="1:3">
@@ -9848,7 +9719,7 @@
         <v>347</v>
       </c>
       <c r="C324" t="s">
-        <v>1320</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -9859,7 +9730,7 @@
         <v>348</v>
       </c>
       <c r="C325" t="s">
-        <v>1321</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="326" spans="1:3">
@@ -9870,7 +9741,7 @@
         <v>349</v>
       </c>
       <c r="C326" t="s">
-        <v>1322</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="327" spans="1:3">
@@ -9881,18 +9752,18 @@
         <v>350</v>
       </c>
       <c r="C327" t="s">
-        <v>1323</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B328" t="s">
         <v>351</v>
       </c>
       <c r="C328" t="s">
-        <v>1324</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="329" spans="1:3">
@@ -9903,7 +9774,7 @@
         <v>352</v>
       </c>
       <c r="C329" t="s">
-        <v>1325</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="330" spans="1:3">
@@ -9914,7 +9785,7 @@
         <v>353</v>
       </c>
       <c r="C330" t="s">
-        <v>1326</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -9925,7 +9796,7 @@
         <v>354</v>
       </c>
       <c r="C331" t="s">
-        <v>1327</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="332" spans="1:3">
@@ -9936,7 +9807,7 @@
         <v>355</v>
       </c>
       <c r="C332" t="s">
-        <v>1328</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="333" spans="1:3">
@@ -9947,7 +9818,7 @@
         <v>356</v>
       </c>
       <c r="C333" t="s">
-        <v>1329</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="334" spans="1:3">
@@ -9958,7 +9829,7 @@
         <v>357</v>
       </c>
       <c r="C334" t="s">
-        <v>1330</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="335" spans="1:3">
@@ -9969,7 +9840,7 @@
         <v>358</v>
       </c>
       <c r="C335" t="s">
-        <v>1331</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="336" spans="1:3">
@@ -9980,7 +9851,7 @@
         <v>359</v>
       </c>
       <c r="C336" t="s">
-        <v>1332</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="337" spans="1:3">
@@ -9991,7 +9862,7 @@
         <v>360</v>
       </c>
       <c r="C337" t="s">
-        <v>1333</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="338" spans="1:3">
@@ -10002,7 +9873,7 @@
         <v>361</v>
       </c>
       <c r="C338" t="s">
-        <v>1334</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="339" spans="1:3">
@@ -10013,7 +9884,7 @@
         <v>362</v>
       </c>
       <c r="C339" t="s">
-        <v>1335</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="340" spans="1:3">
@@ -10024,7 +9895,7 @@
         <v>363</v>
       </c>
       <c r="C340" t="s">
-        <v>1336</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="341" spans="1:3">
@@ -10035,7 +9906,7 @@
         <v>364</v>
       </c>
       <c r="C341" t="s">
-        <v>1337</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -10046,7 +9917,7 @@
         <v>365</v>
       </c>
       <c r="C342" t="s">
-        <v>1338</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="343" spans="1:3">
@@ -10057,7 +9928,7 @@
         <v>366</v>
       </c>
       <c r="C343" t="s">
-        <v>1339</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="344" spans="1:3">
@@ -10068,7 +9939,7 @@
         <v>367</v>
       </c>
       <c r="C344" t="s">
-        <v>1340</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="345" spans="1:3">
@@ -10079,7 +9950,7 @@
         <v>368</v>
       </c>
       <c r="C345" t="s">
-        <v>1341</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="346" spans="1:3">
@@ -10090,7 +9961,7 @@
         <v>369</v>
       </c>
       <c r="C346" t="s">
-        <v>1342</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="347" spans="1:3">
@@ -10101,7 +9972,7 @@
         <v>370</v>
       </c>
       <c r="C347" t="s">
-        <v>1343</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="348" spans="1:3">
@@ -10112,7 +9983,7 @@
         <v>371</v>
       </c>
       <c r="C348" t="s">
-        <v>1344</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="349" spans="1:3">
@@ -10123,7 +9994,7 @@
         <v>372</v>
       </c>
       <c r="C349" t="s">
-        <v>1345</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="350" spans="1:3">
@@ -10134,7 +10005,7 @@
         <v>373</v>
       </c>
       <c r="C350" t="s">
-        <v>1346</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="351" spans="1:3">
@@ -10145,7 +10016,7 @@
         <v>374</v>
       </c>
       <c r="C351" t="s">
-        <v>1347</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -10156,7 +10027,7 @@
         <v>375</v>
       </c>
       <c r="C352" t="s">
-        <v>1348</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="353" spans="1:3">
@@ -10167,7 +10038,7 @@
         <v>376</v>
       </c>
       <c r="C353" t="s">
-        <v>1349</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="354" spans="1:3">
@@ -10178,7 +10049,7 @@
         <v>377</v>
       </c>
       <c r="C354" t="s">
-        <v>1350</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -10189,7 +10060,7 @@
         <v>378</v>
       </c>
       <c r="C355" t="s">
-        <v>1351</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="356" spans="1:3">
@@ -10200,7 +10071,7 @@
         <v>379</v>
       </c>
       <c r="C356" t="s">
-        <v>1352</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="357" spans="1:3">
@@ -10211,7 +10082,7 @@
         <v>380</v>
       </c>
       <c r="C357" t="s">
-        <v>1353</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="358" spans="1:3">
@@ -10222,7 +10093,7 @@
         <v>381</v>
       </c>
       <c r="C358" t="s">
-        <v>1354</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="359" spans="1:3">
@@ -10233,7 +10104,7 @@
         <v>382</v>
       </c>
       <c r="C359" t="s">
-        <v>1355</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -10244,7 +10115,7 @@
         <v>383</v>
       </c>
       <c r="C360" t="s">
-        <v>1356</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="361" spans="1:3">
@@ -10255,7 +10126,7 @@
         <v>384</v>
       </c>
       <c r="C361" t="s">
-        <v>1357</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="362" spans="1:3">
@@ -10266,7 +10137,7 @@
         <v>385</v>
       </c>
       <c r="C362" t="s">
-        <v>1358</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="363" spans="1:3">
@@ -10277,7 +10148,7 @@
         <v>386</v>
       </c>
       <c r="C363" t="s">
-        <v>1359</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="364" spans="1:3">
@@ -10288,7 +10159,7 @@
         <v>387</v>
       </c>
       <c r="C364" t="s">
-        <v>1360</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="365" spans="1:3">
@@ -10299,7 +10170,7 @@
         <v>388</v>
       </c>
       <c r="C365" t="s">
-        <v>1361</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="366" spans="1:3">
@@ -10310,7 +10181,7 @@
         <v>389</v>
       </c>
       <c r="C366" t="s">
-        <v>1362</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="367" spans="1:3">
@@ -10321,7 +10192,7 @@
         <v>390</v>
       </c>
       <c r="C367" t="s">
-        <v>1363</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="368" spans="1:3">
@@ -10332,7 +10203,7 @@
         <v>391</v>
       </c>
       <c r="C368" t="s">
-        <v>1364</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="369" spans="1:3">
@@ -10343,7 +10214,7 @@
         <v>392</v>
       </c>
       <c r="C369" t="s">
-        <v>1365</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="370" spans="1:3">
@@ -10354,7 +10225,7 @@
         <v>393</v>
       </c>
       <c r="C370" t="s">
-        <v>1366</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="371" spans="1:3">
@@ -10365,7 +10236,7 @@
         <v>394</v>
       </c>
       <c r="C371" t="s">
-        <v>1367</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -10376,7 +10247,7 @@
         <v>395</v>
       </c>
       <c r="C372" t="s">
-        <v>1368</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="373" spans="1:3">
@@ -10387,7 +10258,7 @@
         <v>396</v>
       </c>
       <c r="C373" t="s">
-        <v>1369</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="374" spans="1:3">
@@ -10398,7 +10269,7 @@
         <v>397</v>
       </c>
       <c r="C374" t="s">
-        <v>1370</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="375" spans="1:3">
@@ -10409,7 +10280,7 @@
         <v>398</v>
       </c>
       <c r="C375" t="s">
-        <v>1371</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="376" spans="1:3">
@@ -10420,7 +10291,7 @@
         <v>399</v>
       </c>
       <c r="C376" t="s">
-        <v>1372</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="377" spans="1:3">
@@ -10431,7 +10302,7 @@
         <v>400</v>
       </c>
       <c r="C377" t="s">
-        <v>1373</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="378" spans="1:3">
@@ -10442,7 +10313,7 @@
         <v>401</v>
       </c>
       <c r="C378" t="s">
-        <v>1374</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="379" spans="1:3">
@@ -10453,7 +10324,7 @@
         <v>402</v>
       </c>
       <c r="C379" t="s">
-        <v>1375</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="380" spans="1:3">
@@ -10464,7 +10335,7 @@
         <v>403</v>
       </c>
       <c r="C380" t="s">
-        <v>1376</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="381" spans="1:3">
@@ -10475,7 +10346,7 @@
         <v>404</v>
       </c>
       <c r="C381" t="s">
-        <v>1377</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="382" spans="1:3">
@@ -10486,7 +10357,7 @@
         <v>405</v>
       </c>
       <c r="C382" t="s">
-        <v>1378</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="383" spans="1:3">
@@ -10497,7 +10368,7 @@
         <v>406</v>
       </c>
       <c r="C383" t="s">
-        <v>1379</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="384" spans="1:3">
@@ -10508,7 +10379,7 @@
         <v>407</v>
       </c>
       <c r="C384" t="s">
-        <v>1380</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="385" spans="1:3">
@@ -10519,7 +10390,7 @@
         <v>408</v>
       </c>
       <c r="C385" t="s">
-        <v>1381</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="386" spans="1:3">
@@ -10530,7 +10401,7 @@
         <v>409</v>
       </c>
       <c r="C386" t="s">
-        <v>1382</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="387" spans="1:3">
@@ -10541,7 +10412,7 @@
         <v>410</v>
       </c>
       <c r="C387" t="s">
-        <v>1383</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="388" spans="1:3">
@@ -10552,7 +10423,7 @@
         <v>411</v>
       </c>
       <c r="C388" t="s">
-        <v>1384</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="389" spans="1:3">
@@ -10563,7 +10434,7 @@
         <v>412</v>
       </c>
       <c r="C389" t="s">
-        <v>1385</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="390" spans="1:3">
@@ -10574,7 +10445,7 @@
         <v>413</v>
       </c>
       <c r="C390" t="s">
-        <v>1386</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="391" spans="1:3">
@@ -10585,7 +10456,7 @@
         <v>414</v>
       </c>
       <c r="C391" t="s">
-        <v>1387</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="392" spans="1:3">
@@ -10596,7 +10467,7 @@
         <v>415</v>
       </c>
       <c r="C392" t="s">
-        <v>1388</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="393" spans="1:3">
@@ -10607,7 +10478,7 @@
         <v>416</v>
       </c>
       <c r="C393" t="s">
-        <v>1389</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="394" spans="1:3">
@@ -10618,7 +10489,7 @@
         <v>417</v>
       </c>
       <c r="C394" t="s">
-        <v>1390</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="395" spans="1:3">
@@ -10629,7 +10500,7 @@
         <v>418</v>
       </c>
       <c r="C395" t="s">
-        <v>1391</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="396" spans="1:3">
@@ -10640,7 +10511,7 @@
         <v>419</v>
       </c>
       <c r="C396" t="s">
-        <v>1392</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="397" spans="1:3">
@@ -10651,7 +10522,7 @@
         <v>420</v>
       </c>
       <c r="C397" t="s">
-        <v>1393</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="398" spans="1:3">
@@ -10662,7 +10533,7 @@
         <v>421</v>
       </c>
       <c r="C398" t="s">
-        <v>1394</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="399" spans="1:3">
@@ -10673,7 +10544,7 @@
         <v>422</v>
       </c>
       <c r="C399" t="s">
-        <v>1395</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="400" spans="1:3">
@@ -10684,7 +10555,7 @@
         <v>423</v>
       </c>
       <c r="C400" t="s">
-        <v>1396</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="401" spans="1:3">
@@ -10695,7 +10566,7 @@
         <v>424</v>
       </c>
       <c r="C401" t="s">
-        <v>1397</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="402" spans="1:3">
@@ -10706,7 +10577,7 @@
         <v>425</v>
       </c>
       <c r="C402" t="s">
-        <v>1398</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="403" spans="1:3">
@@ -10717,7 +10588,7 @@
         <v>426</v>
       </c>
       <c r="C403" t="s">
-        <v>1399</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="404" spans="1:3">
@@ -10728,7 +10599,7 @@
         <v>427</v>
       </c>
       <c r="C404" t="s">
-        <v>1400</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="405" spans="1:3">
@@ -10739,7 +10610,7 @@
         <v>428</v>
       </c>
       <c r="C405" t="s">
-        <v>1401</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="406" spans="1:3">
@@ -10750,7 +10621,7 @@
         <v>429</v>
       </c>
       <c r="C406" t="s">
-        <v>1402</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="407" spans="1:3">
@@ -10761,7 +10632,7 @@
         <v>430</v>
       </c>
       <c r="C407" t="s">
-        <v>1403</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="408" spans="1:3">
@@ -10772,7 +10643,7 @@
         <v>431</v>
       </c>
       <c r="C408" t="s">
-        <v>1404</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="409" spans="1:3">
@@ -10783,7 +10654,7 @@
         <v>432</v>
       </c>
       <c r="C409" t="s">
-        <v>1405</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="410" spans="1:3">
@@ -10794,7 +10665,7 @@
         <v>433</v>
       </c>
       <c r="C410" t="s">
-        <v>1406</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="411" spans="1:3">
@@ -10805,7 +10676,7 @@
         <v>434</v>
       </c>
       <c r="C411" t="s">
-        <v>1407</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="412" spans="1:3">
@@ -10816,7 +10687,7 @@
         <v>435</v>
       </c>
       <c r="C412" t="s">
-        <v>1408</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="413" spans="1:3">
@@ -10827,7 +10698,7 @@
         <v>436</v>
       </c>
       <c r="C413" t="s">
-        <v>1409</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="414" spans="1:3">
@@ -10838,7 +10709,7 @@
         <v>437</v>
       </c>
       <c r="C414" t="s">
-        <v>1410</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="415" spans="1:3">
@@ -10849,7 +10720,7 @@
         <v>438</v>
       </c>
       <c r="C415" t="s">
-        <v>1411</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="416" spans="1:3">
@@ -10860,7 +10731,7 @@
         <v>439</v>
       </c>
       <c r="C416" t="s">
-        <v>1412</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="417" spans="1:3">
@@ -10871,7 +10742,7 @@
         <v>440</v>
       </c>
       <c r="C417" t="s">
-        <v>1413</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="418" spans="1:3">
@@ -10882,7 +10753,7 @@
         <v>441</v>
       </c>
       <c r="C418" t="s">
-        <v>1414</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="419" spans="1:3">
@@ -10893,7 +10764,7 @@
         <v>442</v>
       </c>
       <c r="C419" t="s">
-        <v>1415</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="420" spans="1:3">
@@ -10904,7 +10775,7 @@
         <v>443</v>
       </c>
       <c r="C420" t="s">
-        <v>1416</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="421" spans="1:3">
@@ -10915,7 +10786,7 @@
         <v>444</v>
       </c>
       <c r="C421" t="s">
-        <v>1417</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="422" spans="1:3">
@@ -10926,7 +10797,7 @@
         <v>445</v>
       </c>
       <c r="C422" t="s">
-        <v>1418</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="423" spans="1:3">
@@ -10937,7 +10808,7 @@
         <v>446</v>
       </c>
       <c r="C423" t="s">
-        <v>1419</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="424" spans="1:3">
@@ -10948,7 +10819,7 @@
         <v>447</v>
       </c>
       <c r="C424" t="s">
-        <v>1420</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="425" spans="1:3">
@@ -10959,7 +10830,7 @@
         <v>448</v>
       </c>
       <c r="C425" t="s">
-        <v>1421</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="426" spans="1:3">
@@ -10970,7 +10841,7 @@
         <v>449</v>
       </c>
       <c r="C426" t="s">
-        <v>1422</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="427" spans="1:3">
@@ -10981,7 +10852,7 @@
         <v>450</v>
       </c>
       <c r="C427" t="s">
-        <v>1423</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="428" spans="1:3">
@@ -10992,7 +10863,7 @@
         <v>451</v>
       </c>
       <c r="C428" t="s">
-        <v>1424</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="429" spans="1:3">
@@ -11003,7 +10874,7 @@
         <v>452</v>
       </c>
       <c r="C429" t="s">
-        <v>1425</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="430" spans="1:3">
@@ -11014,7 +10885,7 @@
         <v>453</v>
       </c>
       <c r="C430" t="s">
-        <v>1426</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="431" spans="1:3">
@@ -11025,7 +10896,7 @@
         <v>454</v>
       </c>
       <c r="C431" t="s">
-        <v>1427</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="432" spans="1:3">
@@ -11036,7 +10907,7 @@
         <v>455</v>
       </c>
       <c r="C432" t="s">
-        <v>1428</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="433" spans="1:3">
@@ -11047,7 +10918,7 @@
         <v>456</v>
       </c>
       <c r="C433" t="s">
-        <v>1429</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="434" spans="1:3">
@@ -11058,7 +10929,7 @@
         <v>457</v>
       </c>
       <c r="C434" t="s">
-        <v>1430</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="435" spans="1:3">
@@ -11069,7 +10940,7 @@
         <v>458</v>
       </c>
       <c r="C435" t="s">
-        <v>1431</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="436" spans="1:3">
@@ -11080,7 +10951,7 @@
         <v>459</v>
       </c>
       <c r="C436" t="s">
-        <v>1432</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="437" spans="1:3">
@@ -11091,7 +10962,7 @@
         <v>460</v>
       </c>
       <c r="C437" t="s">
-        <v>1401</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="438" spans="1:3">
@@ -11102,7 +10973,7 @@
         <v>461</v>
       </c>
       <c r="C438" t="s">
-        <v>1393</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="439" spans="1:3">
@@ -11113,7 +10984,7 @@
         <v>462</v>
       </c>
       <c r="C439" t="s">
-        <v>1433</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="440" spans="1:3">
@@ -11124,7 +10995,7 @@
         <v>463</v>
       </c>
       <c r="C440" t="s">
-        <v>1434</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="441" spans="1:3">
@@ -11135,7 +11006,7 @@
         <v>464</v>
       </c>
       <c r="C441" t="s">
-        <v>1435</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="442" spans="1:3">
@@ -11146,7 +11017,7 @@
         <v>465</v>
       </c>
       <c r="C442" t="s">
-        <v>1436</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="443" spans="1:3">
@@ -11157,7 +11028,7 @@
         <v>466</v>
       </c>
       <c r="C443" t="s">
-        <v>1437</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="444" spans="1:3">
@@ -11168,7 +11039,7 @@
         <v>467</v>
       </c>
       <c r="C444" t="s">
-        <v>1438</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="445" spans="1:3">
@@ -11179,7 +11050,7 @@
         <v>468</v>
       </c>
       <c r="C445" t="s">
-        <v>1439</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="446" spans="1:3">
@@ -11190,7 +11061,7 @@
         <v>469</v>
       </c>
       <c r="C446" t="s">
-        <v>1440</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="447" spans="1:3">
@@ -11201,7 +11072,7 @@
         <v>470</v>
       </c>
       <c r="C447" t="s">
-        <v>1441</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="448" spans="1:3">
@@ -11212,7 +11083,7 @@
         <v>471</v>
       </c>
       <c r="C448" t="s">
-        <v>1442</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="449" spans="1:3">
@@ -11223,7 +11094,7 @@
         <v>472</v>
       </c>
       <c r="C449" t="s">
-        <v>1443</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="450" spans="1:3">
@@ -11234,7 +11105,7 @@
         <v>473</v>
       </c>
       <c r="C450" t="s">
-        <v>1444</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="451" spans="1:3">
@@ -11245,7 +11116,7 @@
         <v>474</v>
       </c>
       <c r="C451" t="s">
-        <v>1445</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="452" spans="1:3">
@@ -11256,7 +11127,7 @@
         <v>475</v>
       </c>
       <c r="C452" t="s">
-        <v>1446</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="453" spans="1:3">
@@ -11267,7 +11138,7 @@
         <v>476</v>
       </c>
       <c r="C453" t="s">
-        <v>1447</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="454" spans="1:3">
@@ -11278,7 +11149,7 @@
         <v>477</v>
       </c>
       <c r="C454" t="s">
-        <v>1448</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="455" spans="1:3">
@@ -11289,7 +11160,7 @@
         <v>478</v>
       </c>
       <c r="C455" t="s">
-        <v>1449</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="456" spans="1:3">
@@ -11300,7 +11171,7 @@
         <v>479</v>
       </c>
       <c r="C456" t="s">
-        <v>1450</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="457" spans="1:3">
@@ -11311,7 +11182,7 @@
         <v>480</v>
       </c>
       <c r="C457" t="s">
-        <v>1451</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="458" spans="1:3">
@@ -11322,7 +11193,7 @@
         <v>481</v>
       </c>
       <c r="C458" t="s">
-        <v>1452</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="459" spans="1:3">
@@ -11333,7 +11204,7 @@
         <v>482</v>
       </c>
       <c r="C459" t="s">
-        <v>1453</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="460" spans="1:3">
@@ -11344,7 +11215,7 @@
         <v>483</v>
       </c>
       <c r="C460" t="s">
-        <v>1454</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="461" spans="1:3">
@@ -11355,7 +11226,7 @@
         <v>484</v>
       </c>
       <c r="C461" t="s">
-        <v>1455</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="462" spans="1:3">
@@ -11366,7 +11237,7 @@
         <v>485</v>
       </c>
       <c r="C462" t="s">
-        <v>1456</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="463" spans="1:3">
@@ -11377,7 +11248,7 @@
         <v>486</v>
       </c>
       <c r="C463" t="s">
-        <v>1457</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="464" spans="1:3">
@@ -11388,7 +11259,7 @@
         <v>487</v>
       </c>
       <c r="C464" t="s">
-        <v>1458</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="465" spans="1:3">
@@ -11399,7 +11270,7 @@
         <v>488</v>
       </c>
       <c r="C465" t="s">
-        <v>1459</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="466" spans="1:3">
@@ -11410,7 +11281,7 @@
         <v>489</v>
       </c>
       <c r="C466" t="s">
-        <v>1460</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="467" spans="1:3">
@@ -11421,7 +11292,7 @@
         <v>490</v>
       </c>
       <c r="C467" t="s">
-        <v>1461</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="468" spans="1:3">
@@ -11432,7 +11303,7 @@
         <v>491</v>
       </c>
       <c r="C468" t="s">
-        <v>1462</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="469" spans="1:3">
@@ -11443,7 +11314,7 @@
         <v>492</v>
       </c>
       <c r="C469" t="s">
-        <v>1463</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="470" spans="1:3">
@@ -11454,7 +11325,7 @@
         <v>493</v>
       </c>
       <c r="C470" t="s">
-        <v>1464</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="471" spans="1:3">
@@ -11465,7 +11336,7 @@
         <v>494</v>
       </c>
       <c r="C471" t="s">
-        <v>1465</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="472" spans="1:3">
@@ -11476,7 +11347,7 @@
         <v>495</v>
       </c>
       <c r="C472" t="s">
-        <v>1466</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="473" spans="1:3">
@@ -11487,7 +11358,7 @@
         <v>496</v>
       </c>
       <c r="C473" t="s">
-        <v>1467</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="474" spans="1:3">
@@ -11498,7 +11369,7 @@
         <v>497</v>
       </c>
       <c r="C474" t="s">
-        <v>1468</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="475" spans="1:3">
@@ -11509,7 +11380,7 @@
         <v>498</v>
       </c>
       <c r="C475" t="s">
-        <v>1469</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="476" spans="1:3">
@@ -11520,7 +11391,7 @@
         <v>499</v>
       </c>
       <c r="C476" t="s">
-        <v>1470</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="477" spans="1:3">
@@ -11531,7 +11402,7 @@
         <v>500</v>
       </c>
       <c r="C477" t="s">
-        <v>1471</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="478" spans="1:3">
@@ -11542,7 +11413,7 @@
         <v>501</v>
       </c>
       <c r="C478" t="s">
-        <v>1472</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="479" spans="1:3">
@@ -11553,7 +11424,7 @@
         <v>502</v>
       </c>
       <c r="C479" t="s">
-        <v>1473</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="480" spans="1:3">
@@ -11564,7 +11435,7 @@
         <v>503</v>
       </c>
       <c r="C480" t="s">
-        <v>1474</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="481" spans="1:3">
@@ -11575,7 +11446,7 @@
         <v>504</v>
       </c>
       <c r="C481" t="s">
-        <v>1475</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="482" spans="1:3">
@@ -11586,7 +11457,7 @@
         <v>505</v>
       </c>
       <c r="C482" t="s">
-        <v>1476</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="483" spans="1:3">
@@ -11597,7 +11468,7 @@
         <v>506</v>
       </c>
       <c r="C483" t="s">
-        <v>1477</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="484" spans="1:3">
@@ -11608,7 +11479,7 @@
         <v>507</v>
       </c>
       <c r="C484" t="s">
-        <v>1478</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="485" spans="1:3">
@@ -11619,7 +11490,7 @@
         <v>508</v>
       </c>
       <c r="C485" t="s">
-        <v>1479</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="486" spans="1:3">
@@ -11630,7 +11501,7 @@
         <v>509</v>
       </c>
       <c r="C486" t="s">
-        <v>1480</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="487" spans="1:3">
@@ -11641,7 +11512,7 @@
         <v>510</v>
       </c>
       <c r="C487" t="s">
-        <v>1481</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="488" spans="1:3">
@@ -11652,7 +11523,7 @@
         <v>511</v>
       </c>
       <c r="C488" t="s">
-        <v>1482</v>
+        <v>14